--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -1084,13 +1084,13 @@
         <v>0</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>15070</v>
+        <v>15325</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -1113,13 +1113,13 @@
         <v>0</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>6735</v>
+        <v>6795</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -1142,13 +1142,13 @@
         <v>0</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>12474</v>
+        <v>12594</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>104</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         <v>0</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>3821</v>
+        <v>4031</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -1229,13 +1229,13 @@
         <v>0</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -1287,13 +1287,13 @@
         <v>0</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>1139</v>
+        <v>1229</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
@@ -1461,13 +1461,13 @@
         <v>0</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>7837</v>
+        <v>7897</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
@@ -1683,16 +1683,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="20" t="n">
-        <v>9973.1</v>
+        <v>9987.1</v>
       </c>
       <c r="F3" s="20" t="n">
-        <v>9973</v>
+        <v>9987</v>
       </c>
       <c r="G3" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="20" t="n">
-        <v>9973</v>
+        <v>9987</v>
       </c>
       <c r="I3" s="19" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J3" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 9973 ud.</t>
+          <t>GESTIONAR EXTERNO 9987 ud.</t>
         </is>
       </c>
     </row>
@@ -1723,16 +1723,16 @@
         <v>0</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>6319</v>
+        <v>6315.2</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>6319</v>
+        <v>6315</v>
       </c>
       <c r="G4" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="20" t="n">
-        <v>6319</v>
+        <v>6315</v>
       </c>
       <c r="I4" s="19" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="J4" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 6319 ud.</t>
+          <t>GESTIONAR EXTERNO 6315 ud.</t>
         </is>
       </c>
     </row>
@@ -1763,16 +1763,16 @@
         <v>0</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>3873.7</v>
+        <v>3886</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>3874</v>
+        <v>3886</v>
       </c>
       <c r="G5" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>3874</v>
+        <v>3886</v>
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="J5" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3874 ud.</t>
+          <t>GESTIONAR EXTERNO 3886 ud.</t>
         </is>
       </c>
     </row>
@@ -1803,16 +1803,16 @@
         <v>0</v>
       </c>
       <c r="E6" s="20" t="n">
-        <v>2922.8</v>
+        <v>2930.1</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>2923</v>
+        <v>2930</v>
       </c>
       <c r="G6" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>2923</v>
+        <v>2930</v>
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2923 ud.</t>
+          <t>GESTIONAR EXTERNO 2930 ud.</t>
         </is>
       </c>
     </row>
@@ -1843,16 +1843,16 @@
         <v>0</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>1846.2</v>
+        <v>1849.1</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>1846</v>
+        <v>1849</v>
       </c>
       <c r="G7" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>1846</v>
+        <v>1849</v>
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1846 ud.</t>
+          <t>GESTIONAR EXTERNO 1849 ud.</t>
         </is>
       </c>
     </row>
@@ -1923,16 +1923,16 @@
         <v>0</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>867.2</v>
+        <v>873.5</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="G9" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 867 ud.</t>
+          <t>GESTIONAR EXTERNO 874 ud.</t>
         </is>
       </c>
     </row>
@@ -2083,16 +2083,16 @@
         <v>0</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>313.7</v>
+        <v>317.4</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G13" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="I13" s="19" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 314 ud.</t>
+          <t>GESTIONAR EXTERNO 317 ud.</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="F20" s="20" t="n">
         <v>25</v>
@@ -3083,16 +3083,16 @@
         <v>0.9</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>10587.8</v>
+        <v>10620.2</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>8780</v>
+        <v>8812</v>
       </c>
       <c r="G38" s="22" t="n">
         <v>7800</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>980</v>
+        <v>1012</v>
       </c>
       <c r="I38" s="21" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J38" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 980 ud.</t>
+          <t>GESTIONAR EXTERNO 1012 ud.</t>
         </is>
       </c>
     </row>
@@ -3123,16 +3123,16 @@
         <v>0.3</v>
       </c>
       <c r="E39" s="22" t="n">
-        <v>9952.4</v>
+        <v>9959</v>
       </c>
       <c r="F39" s="22" t="n">
-        <v>9379</v>
+        <v>9386</v>
       </c>
       <c r="G39" s="22" t="n">
         <v>7550</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>1829</v>
+        <v>1836</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="J39" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1829 ud.</t>
+          <t>GESTIONAR EXTERNO 1836 ud.</t>
         </is>
       </c>
     </row>
@@ -3163,16 +3163,16 @@
         <v>0.8</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>9471</v>
+        <v>9474.299999999999</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>7975</v>
+        <v>7978</v>
       </c>
       <c r="G40" s="22" t="n">
         <v>1568</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>6407</v>
+        <v>6410</v>
       </c>
       <c r="I40" s="21" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="J40" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 6407 ud.</t>
+          <t>GESTIONAR EXTERNO 6410 ud.</t>
         </is>
       </c>
     </row>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="E41" s="22" t="n">
-        <v>8046</v>
+        <v>8053.3</v>
       </c>
       <c r="F41" s="22" t="n">
-        <v>7978</v>
+        <v>7985</v>
       </c>
       <c r="G41" s="22" t="n">
         <v>4800</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>3178</v>
+        <v>3185</v>
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3178 ud.</t>
+          <t>GESTIONAR EXTERNO 3185 ud.</t>
         </is>
       </c>
     </row>
@@ -3243,16 +3243,16 @@
         <v>0</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>8301.4</v>
+        <v>8314</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>8301</v>
+        <v>8314</v>
       </c>
       <c r="G42" s="22" t="n">
         <v>7100</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="I42" s="21" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="J42" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1201 ud.</t>
+          <t>GESTIONAR EXTERNO 1214 ud.</t>
         </is>
       </c>
     </row>
@@ -3283,16 +3283,16 @@
         <v>0.6</v>
       </c>
       <c r="E43" s="22" t="n">
-        <v>6238.1</v>
+        <v>6243.4</v>
       </c>
       <c r="F43" s="22" t="n">
-        <v>5503</v>
+        <v>5508</v>
       </c>
       <c r="G43" s="22" t="n">
         <v>4260</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="J43" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1243 ud.</t>
+          <t>GESTIONAR EXTERNO 1248 ud.</t>
         </is>
       </c>
     </row>
@@ -3323,20 +3323,20 @@
         <v>1.9</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>5671.4</v>
+        <v>5690.9</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>3532</v>
+        <v>3552</v>
       </c>
       <c r="G44" s="22" t="n">
-        <v>3532</v>
+        <v>3552</v>
       </c>
       <c r="H44" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3532 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 3552 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J44" s="21" t="inlineStr"/>
@@ -3359,16 +3359,16 @@
         <v>1.1</v>
       </c>
       <c r="E45" s="22" t="n">
-        <v>5600.7</v>
+        <v>5604.4</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>4391</v>
+        <v>4394</v>
       </c>
       <c r="G45" s="22" t="n">
         <v>2500</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="J45" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1891 ud.</t>
+          <t>GESTIONAR EXTERNO 1894 ud.</t>
         </is>
       </c>
     </row>
@@ -3399,16 +3399,16 @@
         <v>0.2</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>5631.6</v>
+        <v>5634.5</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>5393</v>
+        <v>5396</v>
       </c>
       <c r="G46" s="22" t="n">
         <v>2310</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>3083</v>
+        <v>3086</v>
       </c>
       <c r="I46" s="21" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="J46" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3083 ud.</t>
+          <t>GESTIONAR EXTERNO 3086 ud.</t>
         </is>
       </c>
     </row>
@@ -3439,20 +3439,20 @@
         <v>1.5</v>
       </c>
       <c r="E47" s="22" t="n">
-        <v>5356.8</v>
+        <v>5374.8</v>
       </c>
       <c r="F47" s="22" t="n">
-        <v>3799</v>
+        <v>3817</v>
       </c>
       <c r="G47" s="22" t="n">
-        <v>3799</v>
+        <v>3817</v>
       </c>
       <c r="H47" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3799 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 3817 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J47" s="21" t="inlineStr"/>
@@ -3475,20 +3475,20 @@
         <v>0.3</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>4465</v>
+        <v>4478.6</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>4231</v>
+        <v>4245</v>
       </c>
       <c r="G48" s="22" t="n">
-        <v>4231</v>
+        <v>4245</v>
       </c>
       <c r="H48" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 4231 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 4245 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J48" s="21" t="inlineStr"/>
@@ -3511,16 +3511,16 @@
         <v>0.8</v>
       </c>
       <c r="E49" s="22" t="n">
-        <v>4813.3</v>
+        <v>4829.6</v>
       </c>
       <c r="F49" s="22" t="n">
-        <v>4054</v>
+        <v>4071</v>
       </c>
       <c r="G49" s="22" t="n">
         <v>2000</v>
       </c>
       <c r="H49" s="22" t="n">
-        <v>2054</v>
+        <v>2071</v>
       </c>
       <c r="I49" s="21" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J49" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2054 ud.</t>
+          <t>GESTIONAR EXTERNO 2071 ud.</t>
         </is>
       </c>
     </row>
@@ -3551,20 +3551,20 @@
         <v>0.9</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>4678.5</v>
+        <v>4674.2</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>3890</v>
+        <v>3885</v>
       </c>
       <c r="G50" s="22" t="n">
-        <v>3890</v>
+        <v>3885</v>
       </c>
       <c r="H50" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3890 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 3885 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J50" s="21" t="inlineStr"/>
@@ -3587,20 +3587,20 @@
         <v>1.2</v>
       </c>
       <c r="E51" s="22" t="n">
-        <v>4024.4</v>
+        <v>4040</v>
       </c>
       <c r="F51" s="22" t="n">
-        <v>3032</v>
+        <v>3048</v>
       </c>
       <c r="G51" s="22" t="n">
-        <v>3032</v>
+        <v>3048</v>
       </c>
       <c r="H51" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3032 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 3048 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J51" s="21" t="inlineStr"/>
@@ -3623,16 +3623,16 @@
         <v>0</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>3988.4</v>
+        <v>4002.5</v>
       </c>
       <c r="F52" s="22" t="n">
-        <v>3988</v>
+        <v>4002</v>
       </c>
       <c r="G52" s="22" t="n">
         <v>180</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>3808</v>
+        <v>3822</v>
       </c>
       <c r="I52" s="21" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="J52" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3808 ud.</t>
+          <t>GESTIONAR EXTERNO 3822 ud.</t>
         </is>
       </c>
     </row>
@@ -3663,16 +3663,16 @@
         <v>1.7</v>
       </c>
       <c r="E53" s="22" t="n">
-        <v>4025.6</v>
+        <v>4027.1</v>
       </c>
       <c r="F53" s="22" t="n">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="G53" s="22" t="n">
         <v>2100</v>
       </c>
       <c r="H53" s="22" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I53" s="21" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="J53" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 635 ud.</t>
+          <t>GESTIONAR EXTERNO 636 ud.</t>
         </is>
       </c>
     </row>
@@ -3703,16 +3703,16 @@
         <v>0.5</v>
       </c>
       <c r="E54" s="22" t="n">
-        <v>3837.1</v>
+        <v>3869.1</v>
       </c>
       <c r="F54" s="22" t="n">
-        <v>3461</v>
+        <v>3493</v>
       </c>
       <c r="G54" s="22" t="n">
         <v>1080</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>2381</v>
+        <v>2413</v>
       </c>
       <c r="I54" s="21" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="J54" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2381 ud.</t>
+          <t>GESTIONAR EXTERNO 2413 ud.</t>
         </is>
       </c>
     </row>
@@ -3743,16 +3743,16 @@
         <v>0</v>
       </c>
       <c r="E55" s="22" t="n">
-        <v>2911</v>
+        <v>2923.5</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>2911</v>
+        <v>2924</v>
       </c>
       <c r="G55" s="22" t="n">
         <v>1800</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>1111</v>
+        <v>1124</v>
       </c>
       <c r="I55" s="21" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="J55" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1111 ud.</t>
+          <t>GESTIONAR EXTERNO 1124 ud.</t>
         </is>
       </c>
     </row>
@@ -3783,16 +3783,16 @@
         <v>1.5</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>2890.1</v>
+        <v>2900.7</v>
       </c>
       <c r="F56" s="22" t="n">
-        <v>1978</v>
+        <v>1989</v>
       </c>
       <c r="G56" s="22" t="n">
         <v>1800</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="I56" s="21" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J56" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 178 ud.</t>
+          <t>GESTIONAR EXTERNO 189 ud.</t>
         </is>
       </c>
     </row>
@@ -3823,16 +3823,16 @@
         <v>1</v>
       </c>
       <c r="E57" s="22" t="n">
-        <v>2691.1</v>
+        <v>2696.8</v>
       </c>
       <c r="F57" s="22" t="n">
-        <v>2211</v>
+        <v>2217</v>
       </c>
       <c r="G57" s="22" t="n">
         <v>298</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>1913</v>
+        <v>1919</v>
       </c>
       <c r="I57" s="21" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="J57" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1913 ud.</t>
+          <t>GESTIONAR EXTERNO 1919 ud.</t>
         </is>
       </c>
     </row>
@@ -3899,20 +3899,20 @@
         <v>0.6</v>
       </c>
       <c r="E59" s="22" t="n">
-        <v>2033.9</v>
+        <v>2037.7</v>
       </c>
       <c r="F59" s="22" t="n">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="G59" s="22" t="n">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="H59" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1772 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1776 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J59" s="21" t="inlineStr"/>
@@ -3935,20 +3935,20 @@
         <v>1.2</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>2233.2</v>
+        <v>2234.8</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="G60" s="22" t="n">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="H60" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1739 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1741 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J60" s="21" t="inlineStr"/>
@@ -4004,23 +4004,23 @@
         <v>506</v>
       </c>
       <c r="D62" s="22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>1977.8</v>
+        <v>1995</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>1472</v>
+        <v>1489</v>
       </c>
       <c r="G62" s="22" t="n">
-        <v>1472</v>
+        <v>1489</v>
       </c>
       <c r="H62" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1472 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1489 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J62" s="21" t="inlineStr"/>
@@ -4043,16 +4043,16 @@
         <v>1.3</v>
       </c>
       <c r="E63" s="22" t="n">
-        <v>1503.5</v>
+        <v>1512.4</v>
       </c>
       <c r="F63" s="22" t="n">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="G63" s="22" t="n">
         <v>1071</v>
       </c>
       <c r="H63" s="22" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I63" s="21" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="J63" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 19 ud.</t>
+          <t>GESTIONAR EXTERNO 27 ud.</t>
         </is>
       </c>
     </row>
@@ -4083,20 +4083,20 @@
         <v>0.9</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>1660.8</v>
+        <v>1670.5</v>
       </c>
       <c r="F64" s="22" t="n">
-        <v>1375</v>
+        <v>1384</v>
       </c>
       <c r="G64" s="22" t="n">
-        <v>1375</v>
+        <v>1384</v>
       </c>
       <c r="H64" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1375 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1384 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J64" s="21" t="inlineStr"/>
@@ -4155,16 +4155,16 @@
         <v>1</v>
       </c>
       <c r="E66" s="22" t="n">
-        <v>1096.9</v>
+        <v>1095.5</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="G66" s="22" t="n">
         <v>600</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I66" s="21" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="J66" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 252 ud.</t>
+          <t>GESTIONAR EXTERNO 250 ud.</t>
         </is>
       </c>
     </row>
@@ -4195,20 +4195,20 @@
         <v>1.1</v>
       </c>
       <c r="E67" s="22" t="n">
-        <v>1291.4</v>
+        <v>1294.3</v>
       </c>
       <c r="F67" s="22" t="n">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="G67" s="22" t="n">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="H67" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1036 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1039 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J67" s="21" t="inlineStr"/>
@@ -4307,20 +4307,20 @@
         <v>1.2</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>633.8</v>
+        <v>635.1</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G70" s="22" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H70" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 500 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 501 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J70" s="21" t="inlineStr"/>
@@ -4571,16 +4571,16 @@
         <v>1.6</v>
       </c>
       <c r="E77" s="22" t="n">
-        <v>326.2</v>
+        <v>327.3</v>
       </c>
       <c r="F77" s="22" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G77" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="22" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="J77" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 218 ud.</t>
+          <t>GESTIONAR EXTERNO 219 ud.</t>
         </is>
       </c>
     </row>
@@ -4611,16 +4611,16 @@
         <v>1.8</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>260.7</v>
+        <v>261.6</v>
       </c>
       <c r="F78" s="22" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G78" s="22" t="n">
         <v>80</v>
       </c>
       <c r="H78" s="22" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I78" s="21" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="J78" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 97 ud.</t>
+          <t>GESTIONAR EXTERNO 98 ud.</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
         <v>1.9</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>110.4</v>
+        <v>110.5</v>
       </c>
       <c r="F83" s="22" t="n">
         <v>70</v>
@@ -5011,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>39.9</v>
+        <v>40.1</v>
       </c>
       <c r="F89" s="22" t="n">
         <v>40</v>
@@ -5123,16 +5123,16 @@
         <v>1.1</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G92" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I92" s="21" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="J92" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 16 ud.</t>
+          <t>GESTIONAR EXTERNO 17 ud.</t>
         </is>
       </c>
     </row>
@@ -5387,16 +5387,16 @@
         <v>2.3</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>17799</v>
+        <v>17853.3</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>9475</v>
+        <v>9529</v>
       </c>
       <c r="G99" s="4" t="n">
         <v>9000</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>475</v>
+        <v>529</v>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 475 ud.</t>
+          <t>GESTIONAR EXTERNO 529 ud.</t>
         </is>
       </c>
     </row>
@@ -5427,20 +5427,20 @@
         <v>4.8</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>7302.4</v>
+        <v>7309</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="H100" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 983 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 990 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr"/>
@@ -5463,16 +5463,16 @@
         <v>2.7</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>3752.5</v>
+        <v>3760.7</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1854</v>
+        <v>1862</v>
       </c>
       <c r="G101" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>1854</v>
+        <v>1862</v>
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1854 ud.</t>
+          <t>GESTIONAR EXTERNO 1862 ud.</t>
         </is>
       </c>
     </row>
@@ -5503,16 +5503,16 @@
         <v>3.7</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>2549.9</v>
+        <v>2558.4</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="G102" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 858 ud.</t>
+          <t>GESTIONAR EXTERNO 866 ud.</t>
         </is>
       </c>
     </row>
@@ -5543,16 +5543,16 @@
         <v>2.7</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>1836.7</v>
+        <v>1856.5</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>847</v>
+        <v>866</v>
       </c>
       <c r="G103" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>847</v>
+        <v>866</v>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 847 ud.</t>
+          <t>GESTIONAR EXTERNO 866 ud.</t>
         </is>
       </c>
     </row>
@@ -5623,20 +5623,20 @@
         <v>3.8</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>1635.4</v>
+        <v>1639.5</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="H105" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 355 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 360 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr"/>
@@ -5659,20 +5659,20 @@
         <v>3.5</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>1519.7</v>
+        <v>1525.1</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="H106" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 445 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 450 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr"/>
@@ -5695,20 +5695,20 @@
         <v>4</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>1287.6</v>
+        <v>1292.2</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H107" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 223 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 227 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr"/>
@@ -5728,23 +5728,23 @@
         <v>1061</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>1679.5</v>
+        <v>1681.9</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="H108" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 618 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 621 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr"/>
@@ -5767,16 +5767,16 @@
         <v>4.8</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>1626.6</v>
+        <v>1634.4</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="G109" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="4" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 407 ud.</t>
+          <t>GESTIONAR EXTERNO 414 ud.</t>
         </is>
       </c>
     </row>
@@ -5807,16 +5807,16 @@
         <v>4.5</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>1209.3</v>
+        <v>1218.2</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G110" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 61 ud.</t>
+          <t>GESTIONAR EXTERNO 70 ud.</t>
         </is>
       </c>
     </row>
@@ -5847,20 +5847,20 @@
         <v>2.1</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>1017.6</v>
+        <v>1024.7</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="H111" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 598 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 605 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr"/>
@@ -5923,20 +5923,20 @@
         <v>2.5</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>919.9</v>
+        <v>922.7</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="H113" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 495 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 498 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J113" s="3" t="inlineStr"/>
@@ -5959,20 +5959,20 @@
         <v>3.8</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>753.6</v>
+        <v>757.5</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H114" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 142 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 146 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr"/>
@@ -5995,16 +5995,16 @@
         <v>3.4</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>820.6</v>
+        <v>826</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="G115" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 276 ud.</t>
+          <t>GESTIONAR EXTERNO 281 ud.</t>
         </is>
       </c>
     </row>
@@ -6075,16 +6075,16 @@
         <v>4.2</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>669.3</v>
+        <v>675.3</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G117" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="4" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 95 ud.</t>
+          <t>GESTIONAR EXTERNO 101 ud.</t>
         </is>
       </c>
     </row>
@@ -6112,23 +6112,23 @@
         <v>539</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H118" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 196 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 203 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr"/>
@@ -6151,20 +6151,20 @@
         <v>2.5</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>631.5</v>
+        <v>633.8</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="H119" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 310 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 313 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr"/>
@@ -6259,20 +6259,20 @@
         <v>4.1</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>590</v>
+        <v>591.4</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H122" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 147 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 148 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr"/>
@@ -6295,20 +6295,20 @@
         <v>2.4</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>532</v>
+        <v>535.1</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H123" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 292 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 295 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr"/>
@@ -6331,16 +6331,16 @@
         <v>3.5</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>416.7</v>
+        <v>418.4</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G124" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 148 ud.</t>
+          <t>GESTIONAR EXTERNO 149 ud.</t>
         </is>
       </c>
     </row>
@@ -6591,20 +6591,20 @@
         <v>3</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>102.4</v>
+        <v>103</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H131" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 41 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 42 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr"/>
@@ -6739,7 +6739,7 @@
         <v>3.1</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F135" s="4" t="n">
         <v>34</v>
@@ -6808,23 +6808,23 @@
         <v>37</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>51.4</v>
+        <v>52.3</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H137" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 14 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 15 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J137" s="3" t="inlineStr"/>
@@ -6844,10 +6844,10 @@
         <v>37</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="F138" s="4" t="n">
         <v>11</v>
@@ -6887,7 +6887,7 @@
         <v>4.2</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="F139" s="4" t="n">
         <v>7</v>
@@ -6920,10 +6920,10 @@
         <v>4</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="F140" s="4" t="n">
         <v>6</v>
@@ -7200,17 +7200,17 @@
         <v>0</v>
       </c>
       <c r="E3" s="20" t="n">
-        <v>40029.4</v>
+        <v>40096.8</v>
       </c>
       <c r="F3" s="20" t="n">
-        <v>40029</v>
+        <v>40097</v>
       </c>
       <c r="G3" s="20" t="n">
         <v>214000</v>
       </c>
       <c r="H3" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 40029 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 40097 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I3" s="19" t="inlineStr"/>
@@ -7233,17 +7233,17 @@
         <v>0</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>24183.7</v>
+        <v>24224.9</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>24184</v>
+        <v>24225</v>
       </c>
       <c r="G4" s="20" t="n">
         <v>30000</v>
       </c>
       <c r="H4" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 24184 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 24225 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I4" s="19" t="inlineStr"/>
@@ -7266,17 +7266,17 @@
         <v>0</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>22164.6</v>
+        <v>22179.3</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>22165</v>
+        <v>22179</v>
       </c>
       <c r="G5" s="20" t="n">
         <v>54000</v>
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 22165 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 22179 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I5" s="19" t="inlineStr"/>
@@ -7299,10 +7299,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="20" t="n">
-        <v>22327.1</v>
+        <v>22311.8</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>22327</v>
+        <v>22312</v>
       </c>
       <c r="G6" s="20" t="n">
         <v>0</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 22327 ud.</t>
+          <t>COMPRA EXTERNA 22312 ud.</t>
         </is>
       </c>
     </row>
@@ -7336,17 +7336,17 @@
         <v>0</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>21921.2</v>
+        <v>21929</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>21921</v>
+        <v>21929</v>
       </c>
       <c r="G7" s="20" t="n">
         <v>33992</v>
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 21921 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 21929 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I7" s="19" t="inlineStr"/>
@@ -7369,10 +7369,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="20" t="n">
-        <v>17591.1</v>
+        <v>17607</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>17591</v>
+        <v>17607</v>
       </c>
       <c r="G8" s="20" t="n">
         <v>10400</v>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 7191 ud.</t>
+          <t>COMPRA EXTERNA 7207 ud.</t>
         </is>
       </c>
     </row>
@@ -7406,17 +7406,17 @@
         <v>0</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>18122.9</v>
+        <v>18111.9</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>18123</v>
+        <v>18112</v>
       </c>
       <c r="G9" s="20" t="n">
         <v>52900</v>
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 18123 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 18112 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I9" s="19" t="inlineStr"/>
@@ -7439,10 +7439,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>13907.6</v>
+        <v>13886.7</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>13908</v>
+        <v>13887</v>
       </c>
       <c r="G10" s="20" t="n">
         <v>1500</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 12408 ud.</t>
+          <t>COMPRA EXTERNA 12387 ud.</t>
         </is>
       </c>
     </row>
@@ -7476,17 +7476,17 @@
         <v>0</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>13868.2</v>
+        <v>13880</v>
       </c>
       <c r="F11" s="20" t="n">
-        <v>13868</v>
+        <v>13880</v>
       </c>
       <c r="G11" s="20" t="n">
         <v>17700</v>
       </c>
       <c r="H11" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 13868 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 13880 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I11" s="19" t="inlineStr"/>
@@ -7509,17 +7509,17 @@
         <v>0</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>12870.9</v>
+        <v>12879.2</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>12871</v>
+        <v>12879</v>
       </c>
       <c r="G12" s="20" t="n">
         <v>15500</v>
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 12871 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 12879 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr"/>
@@ -7542,10 +7542,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>13181.8</v>
+        <v>13188.7</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>13182</v>
+        <v>13189</v>
       </c>
       <c r="G13" s="20" t="n">
         <v>3930</v>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="I13" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 9252 ud.</t>
+          <t>COMPRA EXTERNA 9259 ud.</t>
         </is>
       </c>
     </row>
@@ -7579,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="20" t="n">
-        <v>10999.1</v>
+        <v>11022.2</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>10999</v>
+        <v>11022</v>
       </c>
       <c r="G14" s="20" t="n">
         <v>4000</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 6999 ud.</t>
+          <t>COMPRA EXTERNA 7022 ud.</t>
         </is>
       </c>
     </row>
@@ -7616,10 +7616,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>9365</v>
+        <v>9384.799999999999</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>9365</v>
+        <v>9385</v>
       </c>
       <c r="G15" s="20" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="I15" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 9365 ud.</t>
+          <t>COMPRA EXTERNA 9385 ud.</t>
         </is>
       </c>
     </row>
@@ -7653,10 +7653,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="20" t="n">
-        <v>8704</v>
+        <v>8719.799999999999</v>
       </c>
       <c r="F16" s="20" t="n">
-        <v>8704</v>
+        <v>8720</v>
       </c>
       <c r="G16" s="20" t="n">
         <v>0</v>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="I16" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 8704 ud.</t>
+          <t>COMPRA EXTERNA 8720 ud.</t>
         </is>
       </c>
     </row>
@@ -7690,10 +7690,10 @@
         <v>0</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>8313.1</v>
+        <v>8316.200000000001</v>
       </c>
       <c r="F17" s="20" t="n">
-        <v>8313</v>
+        <v>8316</v>
       </c>
       <c r="G17" s="20" t="n">
         <v>5700</v>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="I17" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2613 ud.</t>
+          <t>COMPRA EXTERNA 2616 ud.</t>
         </is>
       </c>
     </row>
@@ -7727,10 +7727,10 @@
         <v>0</v>
       </c>
       <c r="E18" s="20" t="n">
-        <v>8372.200000000001</v>
+        <v>8402.799999999999</v>
       </c>
       <c r="F18" s="20" t="n">
-        <v>8372</v>
+        <v>8403</v>
       </c>
       <c r="G18" s="20" t="n">
         <v>3000</v>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 5372 ud.</t>
+          <t>COMPRA EXTERNA 5403 ud.</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>8253.799999999999</v>
+        <v>8254.5</v>
       </c>
       <c r="F19" s="20" t="n">
         <v>8254</v>
@@ -7797,10 +7797,10 @@
         <v>0</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>6915.1</v>
+        <v>6916.8</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>6915</v>
+        <v>6917</v>
       </c>
       <c r="G20" s="20" t="n">
         <v>0</v>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="I20" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 6915 ud.</t>
+          <t>COMPRA EXTERNA 6917 ud.</t>
         </is>
       </c>
     </row>
@@ -7834,10 +7834,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>6674.1</v>
+        <v>6693.3</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>6674</v>
+        <v>6693</v>
       </c>
       <c r="G21" s="20" t="n">
         <v>3180</v>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="I21" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3494 ud.</t>
+          <t>COMPRA EXTERNA 3513 ud.</t>
         </is>
       </c>
     </row>
@@ -7871,10 +7871,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="20" t="n">
-        <v>5930.4</v>
+        <v>5944.7</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>5930</v>
+        <v>5945</v>
       </c>
       <c r="G22" s="20" t="n">
         <v>1200</v>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 4730 ud.</t>
+          <t>COMPRA EXTERNA 4745 ud.</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>6312.7</v>
+        <v>6313.2</v>
       </c>
       <c r="F23" s="20" t="n">
         <v>6313</v>
@@ -7945,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="20" t="n">
-        <v>5521.6</v>
+        <v>5521.9</v>
       </c>
       <c r="F24" s="20" t="n">
         <v>5522</v>
@@ -7982,17 +7982,17 @@
         <v>0</v>
       </c>
       <c r="E25" s="20" t="n">
-        <v>5403.3</v>
+        <v>5415.1</v>
       </c>
       <c r="F25" s="20" t="n">
-        <v>5403</v>
+        <v>5415</v>
       </c>
       <c r="G25" s="20" t="n">
         <v>26000</v>
       </c>
       <c r="H25" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 5403 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 5415 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I25" s="19" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>4451.1</v>
+        <v>4448.4</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>4451</v>
+        <v>4448</v>
       </c>
       <c r="G26" s="20" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="I26" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 4451 ud.</t>
+          <t>COMPRA EXTERNA 4448 ud.</t>
         </is>
       </c>
     </row>
@@ -8052,10 +8052,10 @@
         <v>0</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>4195.3</v>
+        <v>4210.5</v>
       </c>
       <c r="F27" s="20" t="n">
-        <v>4195</v>
+        <v>4210</v>
       </c>
       <c r="G27" s="20" t="n">
         <v>600</v>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="I27" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3595 ud.</t>
+          <t>COMPRA EXTERNA 3610 ud.</t>
         </is>
       </c>
     </row>
@@ -8122,10 +8122,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>3044.7</v>
+        <v>3051.2</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>3045</v>
+        <v>3051</v>
       </c>
       <c r="G29" s="20" t="n">
         <v>350</v>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="I29" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2695 ud.</t>
+          <t>COMPRA EXTERNA 2701 ud.</t>
         </is>
       </c>
     </row>
@@ -8159,17 +8159,17 @@
         <v>0</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>3318.1</v>
+        <v>3323.2</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>3318</v>
+        <v>3323</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>32000</v>
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 3318 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3323 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr"/>
@@ -8192,17 +8192,17 @@
         <v>0</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>3253.2</v>
+        <v>3259.9</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>3253</v>
+        <v>3260</v>
       </c>
       <c r="G31" s="20" t="n">
         <v>3810</v>
       </c>
       <c r="H31" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 3253 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3260 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I31" s="19" t="inlineStr"/>
@@ -8225,17 +8225,17 @@
         <v>0</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>3308.4</v>
+        <v>3314.9</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>3308</v>
+        <v>3315</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>17610</v>
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 3308 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3315 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I32" s="19" t="inlineStr"/>
@@ -8243,7 +8243,7 @@
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>SACUBITRILO VALSARTAN 50 MG</t>
+          <t>OLANZAPINA 10 MG CM UNIDAD</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
@@ -8258,29 +8258,25 @@
         <v>0</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>3213.8</v>
+        <v>2595.7</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>3214</v>
+        <v>2596</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H33" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I33" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 3214 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2596 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I33" s="19" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>OLANZAPINA 10 MG CM UNIDAD</t>
+          <t>SACUBITRILO VALSARTAN 50 MG</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
@@ -8295,20 +8291,24 @@
         <v>0</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>2583.5</v>
+        <v>3213.8</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>2584</v>
+        <v>3214</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H34" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 2584 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I34" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 3214 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
@@ -8328,17 +8328,17 @@
         <v>0</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>2529.1</v>
+        <v>2523.5</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>2529</v>
+        <v>2524</v>
       </c>
       <c r="G35" s="20" t="n">
         <v>14100</v>
       </c>
       <c r="H35" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 2529 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2524 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I35" s="19" t="inlineStr"/>
@@ -8464,10 +8464,10 @@
         <v>0</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>1992.2</v>
+        <v>2000.5</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>1992</v>
+        <v>2000</v>
       </c>
       <c r="G39" s="20" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="I39" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1992 ud.</t>
+          <t>COMPRA EXTERNA 2000 ud.</t>
         </is>
       </c>
     </row>
@@ -8501,10 +8501,10 @@
         <v>0</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>1882</v>
+        <v>1890.9</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>1882</v>
+        <v>1891</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>0</v>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="I40" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1882 ud.</t>
+          <t>COMPRA EXTERNA 1891 ud.</t>
         </is>
       </c>
     </row>
@@ -8538,10 +8538,10 @@
         <v>0</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>1620.2</v>
+        <v>1627</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>1620</v>
+        <v>1627</v>
       </c>
       <c r="G41" s="20" t="n">
         <v>1200</v>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="I41" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 420 ud.</t>
+          <t>COMPRA EXTERNA 427 ud.</t>
         </is>
       </c>
     </row>
@@ -8575,10 +8575,10 @@
         <v>0</v>
       </c>
       <c r="E42" s="20" t="n">
-        <v>1522.8</v>
+        <v>1529.5</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1523</v>
+        <v>1530</v>
       </c>
       <c r="G42" s="20" t="n">
         <v>0</v>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="I42" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1523 ud.</t>
+          <t>COMPRA EXTERNA 1530 ud.</t>
         </is>
       </c>
     </row>
@@ -8612,17 +8612,17 @@
         <v>0</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>1670.4</v>
+        <v>1675.5</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>1670</v>
+        <v>1676</v>
       </c>
       <c r="G43" s="20" t="n">
         <v>14040</v>
       </c>
       <c r="H43" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 1670 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1676 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I43" s="19" t="inlineStr"/>
@@ -8682,10 +8682,10 @@
         <v>0</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>1419.5</v>
+        <v>1425.1</v>
       </c>
       <c r="F45" s="20" t="n">
-        <v>1420</v>
+        <v>1425</v>
       </c>
       <c r="G45" s="20" t="n">
         <v>1400</v>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="I45" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 20 ud.</t>
+          <t>COMPRA EXTERNA 25 ud.</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="20" t="n">
-        <v>1470.2</v>
+        <v>1469.8</v>
       </c>
       <c r="F46" s="20" t="n">
         <v>1470</v>
@@ -8793,10 +8793,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="20" t="n">
-        <v>1427</v>
+        <v>1424.4</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="G48" s="20" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="I48" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1427 ud.</t>
+          <t>COMPRA EXTERNA 1424 ud.</t>
         </is>
       </c>
     </row>
@@ -8896,17 +8896,17 @@
         <v>0</v>
       </c>
       <c r="E51" s="20" t="n">
-        <v>952</v>
+        <v>954.3</v>
       </c>
       <c r="F51" s="20" t="n">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="G51" s="20" t="n">
         <v>1900</v>
       </c>
       <c r="H51" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 952 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 954 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I51" s="19" t="inlineStr"/>
@@ -8929,17 +8929,17 @@
         <v>0</v>
       </c>
       <c r="E52" s="20" t="n">
-        <v>806.3</v>
+        <v>808.7</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="G52" s="20" t="n">
         <v>3000</v>
       </c>
       <c r="H52" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 806 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 809 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I52" s="19" t="inlineStr"/>
@@ -8962,17 +8962,17 @@
         <v>0</v>
       </c>
       <c r="E53" s="20" t="n">
-        <v>784.8</v>
+        <v>785.9</v>
       </c>
       <c r="F53" s="20" t="n">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G53" s="20" t="n">
         <v>4950</v>
       </c>
       <c r="H53" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 785 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 786 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I53" s="19" t="inlineStr"/>
@@ -9069,17 +9069,17 @@
         <v>0</v>
       </c>
       <c r="E56" s="20" t="n">
-        <v>679.2</v>
+        <v>682.6</v>
       </c>
       <c r="F56" s="20" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G56" s="20" t="n">
         <v>19860</v>
       </c>
       <c r="H56" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 679 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 683 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I56" s="19" t="inlineStr"/>
@@ -9172,10 +9172,10 @@
         <v>0</v>
       </c>
       <c r="E59" s="20" t="n">
-        <v>748.8</v>
+        <v>750.3</v>
       </c>
       <c r="F59" s="20" t="n">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G59" s="20" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="I59" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 749 ud.</t>
+          <t>COMPRA EXTERNA 750 ud.</t>
         </is>
       </c>
     </row>
@@ -9390,10 +9390,10 @@
         <v>0</v>
       </c>
       <c r="E65" s="20" t="n">
-        <v>629</v>
+        <v>630.6</v>
       </c>
       <c r="F65" s="20" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="G65" s="20" t="n">
         <v>150</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="I65" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 479 ud.</t>
+          <t>COMPRA EXTERNA 481 ud.</t>
         </is>
       </c>
     </row>
@@ -9427,10 +9427,10 @@
         <v>0</v>
       </c>
       <c r="E66" s="20" t="n">
-        <v>552.2</v>
+        <v>555.7</v>
       </c>
       <c r="F66" s="20" t="n">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="G66" s="20" t="n">
         <v>0</v>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="I66" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 552 ud.</t>
+          <t>COMPRA EXTERNA 556 ud.</t>
         </is>
       </c>
     </row>
@@ -9497,10 +9497,10 @@
         <v>0</v>
       </c>
       <c r="E68" s="20" t="n">
-        <v>562.7</v>
+        <v>563.9</v>
       </c>
       <c r="F68" s="20" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="G68" s="20" t="n">
         <v>334</v>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="I68" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 229 ud.</t>
+          <t>COMPRA EXTERNA 230 ud.</t>
         </is>
       </c>
     </row>
@@ -9534,10 +9534,10 @@
         <v>0</v>
       </c>
       <c r="E69" s="20" t="n">
-        <v>754.3</v>
+        <v>757.8</v>
       </c>
       <c r="F69" s="20" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="G69" s="20" t="n">
         <v>0</v>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="I69" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 754 ud.</t>
+          <t>COMPRA EXTERNA 758 ud.</t>
         </is>
       </c>
     </row>
@@ -9674,17 +9674,17 @@
         <v>0</v>
       </c>
       <c r="E73" s="20" t="n">
-        <v>464.1</v>
+        <v>466.2</v>
       </c>
       <c r="F73" s="20" t="n">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G73" s="20" t="n">
         <v>2010</v>
       </c>
       <c r="H73" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 464 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 466 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I73" s="19" t="inlineStr"/>
@@ -9781,17 +9781,17 @@
         <v>0</v>
       </c>
       <c r="E76" s="20" t="n">
-        <v>444.8</v>
+        <v>446.9</v>
       </c>
       <c r="F76" s="20" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G76" s="20" t="n">
         <v>1000</v>
       </c>
       <c r="H76" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 445 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 447 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I76" s="19" t="inlineStr"/>
@@ -9917,17 +9917,17 @@
         <v>0</v>
       </c>
       <c r="E80" s="20" t="n">
-        <v>321</v>
+        <v>326.3</v>
       </c>
       <c r="F80" s="20" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G80" s="20" t="n">
         <v>1450</v>
       </c>
       <c r="H80" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 321 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 326 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I80" s="19" t="inlineStr"/>
@@ -10090,10 +10090,10 @@
         <v>0</v>
       </c>
       <c r="E85" s="20" t="n">
-        <v>239.9</v>
+        <v>241.6</v>
       </c>
       <c r="F85" s="20" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G85" s="20" t="n">
         <v>0</v>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="I85" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 240 ud.</t>
+          <t>COMPRA EXTERNA 242 ud.</t>
         </is>
       </c>
     </row>
@@ -10160,17 +10160,17 @@
         <v>0</v>
       </c>
       <c r="E87" s="20" t="n">
-        <v>213.4</v>
+        <v>214.9</v>
       </c>
       <c r="F87" s="20" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G87" s="20" t="n">
         <v>4000</v>
       </c>
       <c r="H87" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 213 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 215 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I87" s="19" t="inlineStr"/>
@@ -10193,7 +10193,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="20" t="n">
-        <v>278.7</v>
+        <v>278.8</v>
       </c>
       <c r="F88" s="20" t="n">
         <v>279</v>
@@ -10333,7 +10333,7 @@
         <v>0</v>
       </c>
       <c r="E92" s="20" t="n">
-        <v>207.2</v>
+        <v>207.3</v>
       </c>
       <c r="F92" s="20" t="n">
         <v>207</v>
@@ -10502,7 +10502,7 @@
         <v>0</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>142.8</v>
+        <v>142.7</v>
       </c>
       <c r="F97" s="20" t="n">
         <v>143</v>
@@ -10638,7 +10638,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="20" t="n">
-        <v>111.7</v>
+        <v>111.8</v>
       </c>
       <c r="F101" s="20" t="n">
         <v>112</v>
@@ -11072,7 +11072,7 @@
     <row r="114">
       <c r="A114" s="19" t="inlineStr">
         <is>
-          <t>VIGABATRINA 500 MG COMPRIMIDO</t>
+          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B114" s="19" t="inlineStr">
@@ -11087,25 +11087,29 @@
         <v>0</v>
       </c>
       <c r="E114" s="20" t="n">
-        <v>81.2</v>
+        <v>56</v>
       </c>
       <c r="F114" s="20" t="n">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="G114" s="20" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="H114" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 81 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I114" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I114" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 56 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="19" t="inlineStr">
         <is>
-          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>VIGABATRINA 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B115" s="19" t="inlineStr">
@@ -11120,24 +11124,20 @@
         <v>0</v>
       </c>
       <c r="E115" s="20" t="n">
-        <v>54.6</v>
+        <v>81.2</v>
       </c>
       <c r="F115" s="20" t="n">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="G115" s="20" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="H115" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I115" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 55 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 81 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I115" s="19" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="19" t="inlineStr">
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="20" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F116" s="20" t="n">
         <v>65</v>
@@ -11478,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="E125" s="20" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="F125" s="20" t="n">
         <v>41</v>
@@ -11673,7 +11673,7 @@
     <row r="131">
       <c r="A131" s="19" t="inlineStr">
         <is>
-          <t>MELOXICAM 15 MG COMPRIMIDO</t>
+          <t>FENTANILO 25 MCG/HORA PARCHE</t>
         </is>
       </c>
       <c r="B131" s="19" t="inlineStr">
@@ -11688,10 +11688,10 @@
         <v>0</v>
       </c>
       <c r="E131" s="20" t="n">
-        <v>19.3</v>
+        <v>33.1</v>
       </c>
       <c r="F131" s="20" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G131" s="20" t="n">
         <v>0</v>
@@ -11703,14 +11703,14 @@
       </c>
       <c r="I131" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 19 ud.</t>
+          <t>COMPRA EXTERNA 33 ud.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="19" t="inlineStr">
         <is>
-          <t>FENTANILO 25 MCG/HORA PARCHE</t>
+          <t>MELOXICAM 15 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B132" s="19" t="inlineStr">
@@ -11725,10 +11725,10 @@
         <v>0</v>
       </c>
       <c r="E132" s="20" t="n">
-        <v>32.6</v>
+        <v>19.3</v>
       </c>
       <c r="F132" s="20" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G132" s="20" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="I132" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 33 ud.</t>
+          <t>COMPRA EXTERNA 19 ud.</t>
         </is>
       </c>
     </row>
@@ -11836,7 +11836,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="20" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="F135" s="20" t="n">
         <v>21</v>
@@ -11920,7 +11920,7 @@
     <row r="138">
       <c r="A138" s="19" t="inlineStr">
         <is>
-          <t>BUPRENORFINA 10 MCG PARC TRANSDERMICO</t>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
         </is>
       </c>
       <c r="B138" s="19" t="inlineStr">
@@ -11935,10 +11935,10 @@
         <v>0</v>
       </c>
       <c r="E138" s="20" t="n">
-        <v>18.4</v>
+        <v>20.1</v>
       </c>
       <c r="F138" s="20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G138" s="20" t="n">
         <v>0</v>
@@ -11950,14 +11950,14 @@
       </c>
       <c r="I138" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 18 ud.</t>
+          <t>COMPRA EXTERNA 20 ud.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="19" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>BUPRENORFINA 10 MCG PARC TRANSDERMICO</t>
         </is>
       </c>
       <c r="B139" s="19" t="inlineStr">
@@ -11972,10 +11972,10 @@
         <v>0</v>
       </c>
       <c r="E139" s="20" t="n">
-        <v>19.6</v>
+        <v>18.4</v>
       </c>
       <c r="F139" s="20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G139" s="20" t="n">
         <v>0</v>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="I139" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 20 ud.</t>
+          <t>COMPRA EXTERNA 18 ud.</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
         <v>0</v>
       </c>
       <c r="E141" s="20" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="F141" s="20" t="n">
         <v>14</v>
@@ -12171,7 +12171,7 @@
     <row r="145">
       <c r="A145" s="19" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+          <t>APIXABAN 2,5 MG CM</t>
         </is>
       </c>
       <c r="B145" s="19" t="inlineStr">
@@ -12186,10 +12186,10 @@
         <v>0</v>
       </c>
       <c r="E145" s="20" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="F145" s="20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G145" s="20" t="n">
         <v>0</v>
@@ -12201,14 +12201,14 @@
       </c>
       <c r="I145" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 9 ud.</t>
+          <t>COMPRA EXTERNA 7 ud.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="19" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 150 MG/ML JER.PC UNIDAD</t>
+          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
         </is>
       </c>
       <c r="B146" s="19" t="inlineStr">
@@ -12223,10 +12223,10 @@
         <v>0</v>
       </c>
       <c r="E146" s="20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F146" s="20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G146" s="20" t="n">
         <v>0</v>
@@ -12238,14 +12238,14 @@
       </c>
       <c r="I146" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 8 ud.</t>
+          <t>COMPRA EXTERNA 9 ud.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="19" t="inlineStr">
         <is>
-          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
+          <t>PALIPERIDONA 150 MG/ML JER.PC UNIDAD</t>
         </is>
       </c>
       <c r="B147" s="19" t="inlineStr">
@@ -12260,10 +12260,10 @@
         <v>0</v>
       </c>
       <c r="E147" s="20" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F147" s="20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G147" s="20" t="n">
         <v>0</v>
@@ -12275,14 +12275,14 @@
       </c>
       <c r="I147" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 4 ud.</t>
+          <t>COMPRA EXTERNA 8 ud.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="19" t="inlineStr">
         <is>
-          <t>CEFTRIAXONA 1G FA</t>
+          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
         </is>
       </c>
       <c r="B148" s="19" t="inlineStr">
@@ -12297,25 +12297,29 @@
         <v>0</v>
       </c>
       <c r="E148" s="20" t="n">
-        <v>9.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="F148" s="20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G148" s="20" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="H148" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 10 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I148" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I148" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 4 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="19" t="inlineStr">
         <is>
-          <t>APIXABAN 2,5 MG CM</t>
+          <t>CEFTRIAXONA 1G FA</t>
         </is>
       </c>
       <c r="B149" s="19" t="inlineStr">
@@ -12330,24 +12334,20 @@
         <v>0</v>
       </c>
       <c r="E149" s="20" t="n">
-        <v>3.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F149" s="20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G149" s="20" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="H149" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I149" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 4 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 10 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I149" s="19" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="19" t="inlineStr">
@@ -13551,23 +13551,23 @@
         </is>
       </c>
       <c r="C184" s="22" t="n">
-        <v>1688</v>
+        <v>1668</v>
       </c>
       <c r="D184" s="22" t="n">
         <v>1.5</v>
       </c>
       <c r="E184" s="22" t="n">
-        <v>13242.5</v>
+        <v>13269.6</v>
       </c>
       <c r="F184" s="22" t="n">
-        <v>11554</v>
+        <v>11602</v>
       </c>
       <c r="G184" s="22" t="n">
         <v>25920</v>
       </c>
       <c r="H184" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 11554 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 11602 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I184" s="21" t="inlineStr"/>
@@ -13584,23 +13584,23 @@
         </is>
       </c>
       <c r="C185" s="22" t="n">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="D185" s="22" t="n">
         <v>0.2</v>
       </c>
       <c r="E185" s="22" t="n">
-        <v>12016</v>
+        <v>12040.6</v>
       </c>
       <c r="F185" s="22" t="n">
-        <v>11815</v>
+        <v>11858</v>
       </c>
       <c r="G185" s="22" t="n">
         <v>20500</v>
       </c>
       <c r="H185" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 11815 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 11858 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I185" s="21" t="inlineStr"/>
@@ -13617,23 +13617,23 @@
         </is>
       </c>
       <c r="C186" s="22" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="D186" s="22" t="n">
         <v>1.1</v>
       </c>
       <c r="E186" s="22" t="n">
-        <v>10034</v>
+        <v>10015.6</v>
       </c>
       <c r="F186" s="22" t="n">
-        <v>9124</v>
+        <v>9101</v>
       </c>
       <c r="G186" s="22" t="n">
         <v>45000</v>
       </c>
       <c r="H186" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 9124 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 9101 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I186" s="21" t="inlineStr"/>
@@ -13650,16 +13650,16 @@
         </is>
       </c>
       <c r="C187" s="22" t="n">
-        <v>2248</v>
+        <v>2232</v>
       </c>
       <c r="D187" s="22" t="n">
         <v>2.7</v>
       </c>
       <c r="E187" s="22" t="n">
-        <v>9608.200000000001</v>
+        <v>9631.5</v>
       </c>
       <c r="F187" s="22" t="n">
-        <v>7360</v>
+        <v>7400</v>
       </c>
       <c r="G187" s="22" t="n">
         <v>0</v>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="I187" s="21" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 7360 ud.</t>
+          <t>COMPRA EXTERNA 7400 ud.</t>
         </is>
       </c>
     </row>
@@ -13726,17 +13726,17 @@
         <v>2.8</v>
       </c>
       <c r="E189" s="22" t="n">
-        <v>4575.7</v>
+        <v>4581.9</v>
       </c>
       <c r="F189" s="22" t="n">
-        <v>3376</v>
+        <v>3382</v>
       </c>
       <c r="G189" s="22" t="n">
         <v>20500</v>
       </c>
       <c r="H189" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3376 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3382 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I189" s="21" t="inlineStr"/>
@@ -13753,23 +13753,23 @@
         </is>
       </c>
       <c r="C190" s="22" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D190" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="E190" s="22" t="n">
-        <v>4805.9</v>
+        <v>4804.1</v>
       </c>
       <c r="F190" s="22" t="n">
-        <v>4598</v>
+        <v>4600</v>
       </c>
       <c r="G190" s="22" t="n">
         <v>22000</v>
       </c>
       <c r="H190" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 4598 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 4600 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I190" s="21" t="inlineStr"/>
@@ -13819,23 +13819,23 @@
         </is>
       </c>
       <c r="C192" s="22" t="n">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="D192" s="22" t="n">
         <v>0.9</v>
       </c>
       <c r="E192" s="22" t="n">
-        <v>4118.8</v>
+        <v>4137</v>
       </c>
       <c r="F192" s="22" t="n">
-        <v>3791</v>
+        <v>3826</v>
       </c>
       <c r="G192" s="22" t="n">
         <v>20000</v>
       </c>
       <c r="H192" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3791 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3826 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I192" s="21" t="inlineStr"/>
@@ -13852,23 +13852,23 @@
         </is>
       </c>
       <c r="C193" s="22" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D193" s="22" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E193" s="22" t="n">
-        <v>3744.9</v>
+        <v>3746</v>
       </c>
       <c r="F193" s="22" t="n">
-        <v>3560</v>
+        <v>3566</v>
       </c>
       <c r="G193" s="22" t="n">
         <v>12240</v>
       </c>
       <c r="H193" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3560 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3566 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I193" s="21" t="inlineStr"/>
@@ -13918,23 +13918,23 @@
         </is>
       </c>
       <c r="C195" s="22" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D195" s="22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E195" s="22" t="n">
-        <v>2884.3</v>
+        <v>2882.5</v>
       </c>
       <c r="F195" s="22" t="n">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="G195" s="22" t="n">
         <v>16840</v>
       </c>
       <c r="H195" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 2502 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2504 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I195" s="21" t="inlineStr"/>
@@ -13951,23 +13951,23 @@
         </is>
       </c>
       <c r="C196" s="22" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D196" s="22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="E196" s="22" t="n">
-        <v>2861.8</v>
+        <v>2862.4</v>
       </c>
       <c r="F196" s="22" t="n">
-        <v>2398</v>
+        <v>2401</v>
       </c>
       <c r="G196" s="22" t="n">
         <v>10320</v>
       </c>
       <c r="H196" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 2398 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2401 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I196" s="21" t="inlineStr"/>
@@ -13984,23 +13984,23 @@
         </is>
       </c>
       <c r="C197" s="22" t="n">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D197" s="22" t="n">
         <v>2.9</v>
       </c>
       <c r="E197" s="22" t="n">
-        <v>2063.7</v>
+        <v>2067.5</v>
       </c>
       <c r="F197" s="22" t="n">
-        <v>1559</v>
+        <v>1566</v>
       </c>
       <c r="G197" s="22" t="n">
         <v>2700</v>
       </c>
       <c r="H197" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1559 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1566 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I197" s="21" t="inlineStr"/>
@@ -14017,23 +14017,23 @@
         </is>
       </c>
       <c r="C198" s="22" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D198" s="22" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E198" s="22" t="n">
-        <v>1368.9</v>
+        <v>1375.8</v>
       </c>
       <c r="F198" s="22" t="n">
-        <v>1265</v>
+        <v>1279</v>
       </c>
       <c r="G198" s="22" t="n">
         <v>2800</v>
       </c>
       <c r="H198" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1265 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1279 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I198" s="21" t="inlineStr"/>
@@ -14050,23 +14050,23 @@
         </is>
       </c>
       <c r="C199" s="22" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D199" s="22" t="n">
         <v>1.5</v>
       </c>
       <c r="E199" s="22" t="n">
-        <v>1270.8</v>
+        <v>1273.8</v>
       </c>
       <c r="F199" s="22" t="n">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="G199" s="22" t="n">
         <v>3500</v>
       </c>
       <c r="H199" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1081 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1087 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I199" s="21" t="inlineStr"/>
@@ -14083,23 +14083,23 @@
         </is>
       </c>
       <c r="C200" s="22" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D200" s="22" t="n">
         <v>1.1</v>
       </c>
       <c r="E200" s="22" t="n">
-        <v>1258.3</v>
+        <v>1259.8</v>
       </c>
       <c r="F200" s="22" t="n">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="G200" s="22" t="n">
         <v>7910</v>
       </c>
       <c r="H200" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1135 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1138 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I200" s="21" t="inlineStr"/>
@@ -14221,7 +14221,7 @@
         <v>0.9</v>
       </c>
       <c r="E204" s="22" t="n">
-        <v>240.2</v>
+        <v>240.4</v>
       </c>
       <c r="F204" s="22" t="n">
         <v>220</v>
@@ -14357,7 +14357,7 @@
         <v>1.1</v>
       </c>
       <c r="E208" s="22" t="n">
-        <v>184.3</v>
+        <v>184.4</v>
       </c>
       <c r="F208" s="22" t="n">
         <v>168</v>
@@ -14483,23 +14483,23 @@
         </is>
       </c>
       <c r="C212" s="26" t="n">
-        <v>4767</v>
+        <v>4760</v>
       </c>
       <c r="D212" s="26" t="n">
         <v>3.6</v>
       </c>
       <c r="E212" s="26" t="n">
-        <v>15589.7</v>
+        <v>15603.9</v>
       </c>
       <c r="F212" s="26" t="n">
-        <v>10823</v>
+        <v>10844</v>
       </c>
       <c r="G212" s="26" t="n">
         <v>89100</v>
       </c>
       <c r="H212" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 10823 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 10844 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I212" s="25" t="inlineStr"/>
@@ -14516,23 +14516,23 @@
         </is>
       </c>
       <c r="C213" s="26" t="n">
-        <v>3309</v>
+        <v>3295</v>
       </c>
       <c r="D213" s="26" t="n">
         <v>3.6</v>
       </c>
       <c r="E213" s="26" t="n">
-        <v>9508.5</v>
+        <v>9524.799999999999</v>
       </c>
       <c r="F213" s="26" t="n">
-        <v>6200</v>
+        <v>6230</v>
       </c>
       <c r="G213" s="26" t="n">
         <v>18580</v>
       </c>
       <c r="H213" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 6200 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 6230 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I213" s="25" t="inlineStr"/>
@@ -14549,23 +14549,23 @@
         </is>
       </c>
       <c r="C214" s="26" t="n">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="D214" s="26" t="n">
         <v>3</v>
       </c>
       <c r="E214" s="26" t="n">
-        <v>4531.6</v>
+        <v>4534.8</v>
       </c>
       <c r="F214" s="26" t="n">
-        <v>3271</v>
+        <v>3276</v>
       </c>
       <c r="G214" s="26" t="n">
         <v>24000</v>
       </c>
       <c r="H214" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 3271 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3276 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I214" s="25" t="inlineStr"/>
@@ -14588,10 +14588,10 @@
         <v>3.5</v>
       </c>
       <c r="E215" s="26" t="n">
-        <v>2885.7</v>
+        <v>2893.5</v>
       </c>
       <c r="F215" s="26" t="n">
-        <v>1896</v>
+        <v>1904</v>
       </c>
       <c r="G215" s="26" t="n">
         <v>1800</v>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="I215" s="25" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 96 ud.</t>
+          <t>COMPRA EXTERNA 104 ud.</t>
         </is>
       </c>
     </row>
@@ -14625,17 +14625,17 @@
         <v>3.7</v>
       </c>
       <c r="E216" s="26" t="n">
-        <v>3369.5</v>
+        <v>3375.5</v>
       </c>
       <c r="F216" s="26" t="n">
-        <v>2370</v>
+        <v>2376</v>
       </c>
       <c r="G216" s="26" t="n">
         <v>21000</v>
       </c>
       <c r="H216" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 2370 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2376 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I216" s="25" t="inlineStr"/>
@@ -14691,17 +14691,17 @@
         <v>4.2</v>
       </c>
       <c r="E218" s="26" t="n">
-        <v>2320.2</v>
+        <v>2324.4</v>
       </c>
       <c r="F218" s="26" t="n">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="G218" s="26" t="n">
         <v>39800</v>
       </c>
       <c r="H218" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 1470 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1474 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I218" s="25" t="inlineStr"/>
@@ -14718,23 +14718,23 @@
         </is>
       </c>
       <c r="C219" s="26" t="n">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="D219" s="26" t="n">
         <v>3.6</v>
       </c>
       <c r="E219" s="26" t="n">
-        <v>2174.6</v>
+        <v>2184.1</v>
       </c>
       <c r="F219" s="26" t="n">
-        <v>1453</v>
+        <v>1469</v>
       </c>
       <c r="G219" s="26" t="n">
         <v>2580</v>
       </c>
       <c r="H219" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 1453 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1469 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I219" s="25" t="inlineStr"/>
@@ -14817,23 +14817,23 @@
         </is>
       </c>
       <c r="C222" s="26" t="n">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D222" s="26" t="n">
         <v>4.6</v>
       </c>
       <c r="E222" s="26" t="n">
-        <v>1022.5</v>
+        <v>1025.1</v>
       </c>
       <c r="F222" s="26" t="n">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="G222" s="26" t="n">
         <v>7740</v>
       </c>
       <c r="H222" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 564 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 570 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I222" s="25" t="inlineStr"/>
@@ -15051,20 +15051,20 @@
         <v>100</v>
       </c>
       <c r="D229" s="26" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="E229" s="26" t="n">
-        <v>242.6</v>
+        <v>254</v>
       </c>
       <c r="F229" s="26" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G229" s="26" t="n">
         <v>2350</v>
       </c>
       <c r="H229" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 143 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 154 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I229" s="25" t="inlineStr"/>
@@ -15187,7 +15187,7 @@
         <v>5</v>
       </c>
       <c r="D233" s="26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="E233" s="26" t="n">
         <v>12.8</v>
@@ -15256,17 +15256,17 @@
         <v>9</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>8201</v>
+        <v>8202.799999999999</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="G235" s="4" t="n">
         <v>20000</v>
       </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 2201 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2203 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I235" s="3" t="inlineStr"/>
@@ -15289,7 +15289,7 @@
         <v>5</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>4997.7</v>
+        <v>4998.2</v>
       </c>
       <c r="F236" s="4" t="n">
         <v>2768</v>
@@ -15311,7 +15311,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>VENLAFAXINA 75 MG COMPRIMIDOS LIBERACION MODIFICADA</t>
+          <t>TRAMADOL CP 50 MG</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -15320,23 +15320,23 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>1555</v>
+        <v>1616</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>3319.4</v>
+        <v>3577.1</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>1764</v>
+        <v>1961</v>
       </c>
       <c r="G237" s="4" t="n">
-        <v>40500</v>
+        <v>7600</v>
       </c>
       <c r="H237" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1764 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1961 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I237" s="3" t="inlineStr"/>
@@ -15344,7 +15344,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>TRAMADOL CP 50 MG</t>
+          <t>VENLAFAXINA 75 MG COMPRIMIDOS LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -15353,23 +15353,23 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>1625</v>
+        <v>1550</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>3568.2</v>
+        <v>3327</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>1943</v>
+        <v>1777</v>
       </c>
       <c r="G238" s="4" t="n">
-        <v>7600</v>
+        <v>40500</v>
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1943 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1777 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I238" s="3" t="inlineStr"/>
@@ -15386,16 +15386,16 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>2277</v>
+        <v>2273</v>
       </c>
       <c r="D239" s="4" t="n">
         <v>8.6</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>2663.7</v>
+        <v>2669.8</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="G239" s="4" t="n">
         <v>0</v>
@@ -15407,7 +15407,7 @@
       </c>
       <c r="I239" s="3" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 387 ud.</t>
+          <t>COMPRA EXTERNA 397 ud.</t>
         </is>
       </c>
     </row>
@@ -15429,17 +15429,17 @@
         <v>7</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>2514.3</v>
+        <v>2513.2</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G240" s="4" t="n">
         <v>6000</v>
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1014 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1013 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I240" s="3" t="inlineStr"/>
@@ -15462,17 +15462,17 @@
         <v>7.5</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>1676.5</v>
+        <v>1684.2</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="G241" s="4" t="n">
         <v>19400</v>
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 376 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 384 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D247" s="4" t="n">
         <v>8.4</v>
@@ -15667,14 +15667,14 @@
         <v>1352.5</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G247" s="4" t="n">
         <v>1800</v>
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 412 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 414 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr"/>
@@ -15862,7 +15862,7 @@
         <v>5.7</v>
       </c>
       <c r="E253" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="F253" s="4" t="n">
         <v>30</v>
@@ -15895,7 +15895,7 @@
         <v>5.1</v>
       </c>
       <c r="E254" s="4" t="n">
-        <v>89.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F254" s="4" t="n">
         <v>51</v>
@@ -15928,17 +15928,17 @@
         <v>7.7</v>
       </c>
       <c r="E255" s="4" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="F255" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G255" s="4" t="n">
         <v>40</v>
       </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 18 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr"/>
@@ -15994,7 +15994,7 @@
         <v>9</v>
       </c>
       <c r="E257" s="4" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="F257" s="4" t="n">
         <v>2</v>
@@ -16027,17 +16027,17 @@
         <v>10.5</v>
       </c>
       <c r="E258" s="10" t="n">
-        <v>4125.3</v>
+        <v>4126.8</v>
       </c>
       <c r="F258" s="10" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G258" s="10" t="n">
         <v>11000</v>
       </c>
       <c r="H258" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR 125 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 127 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I258" s="9" t="inlineStr"/>
@@ -16060,17 +16060,17 @@
         <v>12.5</v>
       </c>
       <c r="E259" s="10" t="n">
-        <v>3812.4</v>
+        <v>3817.8</v>
       </c>
       <c r="F259" s="10" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="G259" s="10" t="n">
         <v>32400</v>
       </c>
       <c r="H259" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR 212 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 218 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I259" s="9" t="inlineStr"/>
@@ -16126,7 +16126,7 @@
         <v>10.1</v>
       </c>
       <c r="E261" s="10" t="n">
-        <v>133.9</v>
+        <v>134.3</v>
       </c>
       <c r="F261" s="10" t="n">
         <v>24</v>
@@ -16255,7 +16255,7 @@
         <v>10</v>
       </c>
       <c r="D265" s="10" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="E265" s="10" t="n">
         <v>15</v>
@@ -16430,22 +16430,22 @@
         <v>0</v>
       </c>
       <c r="E3" s="20" t="n">
-        <v>9973.1</v>
+        <v>9987.1</v>
       </c>
       <c r="F3" s="20" t="n">
         <v>7.2</v>
       </c>
       <c r="G3" s="20" t="n">
-        <v>9351.9</v>
+        <v>9358</v>
       </c>
       <c r="H3" s="20" t="n">
-        <v>9973</v>
+        <v>9987</v>
       </c>
       <c r="I3" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="20" t="n">
-        <v>9973</v>
+        <v>9987</v>
       </c>
       <c r="K3" s="19" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="L3" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 9973 ud.</t>
+          <t>GESTIONAR EXTERNO 9987 ud.</t>
         </is>
       </c>
     </row>
@@ -16476,22 +16476,22 @@
         <v>0</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>6319</v>
+        <v>6315.2</v>
       </c>
       <c r="F4" s="20" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>6013.5</v>
+        <v>6019.3</v>
       </c>
       <c r="H4" s="20" t="n">
-        <v>6319</v>
+        <v>6315</v>
       </c>
       <c r="I4" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="20" t="n">
-        <v>6319</v>
+        <v>6315</v>
       </c>
       <c r="K4" s="19" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="L4" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 6319 ud.</t>
+          <t>GESTIONAR EXTERNO 6315 ud.</t>
         </is>
       </c>
     </row>
@@ -16522,22 +16522,22 @@
         <v>0</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>3873.7</v>
+        <v>3886</v>
       </c>
       <c r="F5" s="20" t="n">
         <v>211.2</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>3735.1</v>
+        <v>3738</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>3874</v>
+        <v>3886</v>
       </c>
       <c r="I5" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="20" t="n">
-        <v>3874</v>
+        <v>3886</v>
       </c>
       <c r="K5" s="19" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
       </c>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3874 ud.</t>
+          <t>GESTIONAR EXTERNO 3886 ud.</t>
         </is>
       </c>
     </row>
@@ -16568,22 +16568,22 @@
         <v>0</v>
       </c>
       <c r="E6" s="20" t="n">
-        <v>2922.8</v>
+        <v>2930.1</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>12.5</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>3039.7</v>
+        <v>3044.8</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>2923</v>
+        <v>2930</v>
       </c>
       <c r="I6" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>2923</v>
+        <v>2930</v>
       </c>
       <c r="K6" s="19" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="L6" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2923 ud.</t>
+          <t>GESTIONAR EXTERNO 2930 ud.</t>
         </is>
       </c>
     </row>
@@ -16614,22 +16614,22 @@
         <v>0</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>867.2</v>
+        <v>873.5</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>7.2</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>835.7</v>
+        <v>837.8</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="I7" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="20" t="n">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="K7" s="19" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
       </c>
       <c r="L7" s="19" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 867 ud.</t>
+          <t>GESTIONAR EXTERNO 874 ud.</t>
         </is>
       </c>
     </row>
@@ -16936,13 +16936,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="20" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="F14" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="H14" s="20" t="n">
         <v>25</v>
@@ -17166,22 +17166,22 @@
         <v>0.9</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>10587.8</v>
+        <v>10620.2</v>
       </c>
       <c r="F19" s="22" t="n">
         <v>146</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>10475.8</v>
+        <v>10482.7</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>8780</v>
+        <v>8812</v>
       </c>
       <c r="I19" s="22" t="n">
         <v>7800</v>
       </c>
       <c r="J19" s="22" t="n">
-        <v>980</v>
+        <v>1012</v>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="L19" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 980 ud.</t>
+          <t>GESTIONAR EXTERNO 1012 ud.</t>
         </is>
       </c>
     </row>
@@ -17212,22 +17212,22 @@
         <v>0.3</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>9952.4</v>
+        <v>9959</v>
       </c>
       <c r="F20" s="22" t="n">
         <v>406.4</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>9104.700000000001</v>
+        <v>9110.9</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>9379</v>
+        <v>9386</v>
       </c>
       <c r="I20" s="22" t="n">
         <v>7550</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>1829</v>
+        <v>1836</v>
       </c>
       <c r="K20" s="21" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
       </c>
       <c r="L20" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1829 ud.</t>
+          <t>GESTIONAR EXTERNO 1836 ud.</t>
         </is>
       </c>
     </row>
@@ -17258,22 +17258,22 @@
         <v>0.8</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>9471</v>
+        <v>9474.299999999999</v>
       </c>
       <c r="F21" s="22" t="n">
         <v>87.7</v>
       </c>
       <c r="G21" s="22" t="n">
-        <v>9040.1</v>
+        <v>9043.299999999999</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>7975</v>
+        <v>7978</v>
       </c>
       <c r="I21" s="22" t="n">
         <v>1568</v>
       </c>
       <c r="J21" s="22" t="n">
-        <v>6407</v>
+        <v>6410</v>
       </c>
       <c r="K21" s="21" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
       </c>
       <c r="L21" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 6407 ud.</t>
+          <t>GESTIONAR EXTERNO 6410 ud.</t>
         </is>
       </c>
     </row>
@@ -17304,22 +17304,22 @@
         <v>0</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>8046</v>
+        <v>8053.3</v>
       </c>
       <c r="F22" s="22" t="n">
         <v>243.5</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>7764.1</v>
+        <v>7771.3</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>7978</v>
+        <v>7985</v>
       </c>
       <c r="I22" s="22" t="n">
         <v>4800</v>
       </c>
       <c r="J22" s="22" t="n">
-        <v>3178</v>
+        <v>3185</v>
       </c>
       <c r="K22" s="21" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3178 ud.</t>
+          <t>GESTIONAR EXTERNO 3185 ud.</t>
         </is>
       </c>
     </row>
@@ -17350,22 +17350,22 @@
         <v>0</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>8301.4</v>
+        <v>8314</v>
       </c>
       <c r="F23" s="22" t="n">
         <v>428.4</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>7391.3</v>
+        <v>7397.4</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>8301</v>
+        <v>8314</v>
       </c>
       <c r="I23" s="22" t="n">
         <v>7100</v>
       </c>
       <c r="J23" s="22" t="n">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="K23" s="21" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1201 ud.</t>
+          <t>GESTIONAR EXTERNO 1214 ud.</t>
         </is>
       </c>
     </row>
@@ -17396,22 +17396,22 @@
         <v>0.6</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>6238.1</v>
+        <v>6243.4</v>
       </c>
       <c r="F24" s="22" t="n">
         <v>71</v>
       </c>
       <c r="G24" s="22" t="n">
-        <v>5908.7</v>
+        <v>5913.8</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>5503</v>
+        <v>5508</v>
       </c>
       <c r="I24" s="22" t="n">
         <v>4260</v>
       </c>
       <c r="J24" s="22" t="n">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="K24" s="21" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="L24" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1243 ud.</t>
+          <t>GESTIONAR EXTERNO 1248 ud.</t>
         </is>
       </c>
     </row>
@@ -17442,22 +17442,22 @@
         <v>0.2</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>5631.6</v>
+        <v>5634.5</v>
       </c>
       <c r="F25" s="22" t="n">
         <v>35.7</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>5515.9</v>
+        <v>5518.8</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>5393</v>
+        <v>5396</v>
       </c>
       <c r="I25" s="22" t="n">
         <v>2310</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>3083</v>
+        <v>3086</v>
       </c>
       <c r="K25" s="21" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3083 ud.</t>
+          <t>GESTIONAR EXTERNO 3086 ud.</t>
         </is>
       </c>
     </row>
@@ -17488,26 +17488,26 @@
         <v>1.5</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>5356.8</v>
+        <v>5374.8</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="G26" s="22" t="n">
-        <v>5252.7</v>
+        <v>5257.8</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>3799</v>
+        <v>3817</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>3799</v>
+        <v>3817</v>
       </c>
       <c r="J26" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3799 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 3817 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr"/>
@@ -17530,26 +17530,26 @@
         <v>0.3</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>4465</v>
+        <v>4478.6</v>
       </c>
       <c r="F27" s="22" t="n">
         <v>15.9</v>
       </c>
       <c r="G27" s="22" t="n">
-        <v>4619.6</v>
+        <v>4622.2</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>4231</v>
+        <v>4245</v>
       </c>
       <c r="I27" s="22" t="n">
-        <v>4231</v>
+        <v>4245</v>
       </c>
       <c r="J27" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 4231 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 4245 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr"/>
@@ -17572,22 +17572,22 @@
         <v>0.8</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>4813.3</v>
+        <v>4829.6</v>
       </c>
       <c r="F28" s="22" t="n">
         <v>144.3</v>
       </c>
       <c r="G28" s="22" t="n">
-        <v>4431</v>
+        <v>4436.1</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>4054</v>
+        <v>4071</v>
       </c>
       <c r="I28" s="22" t="n">
         <v>2000</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>2054</v>
+        <v>2071</v>
       </c>
       <c r="K28" s="21" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
       </c>
       <c r="L28" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2054 ud.</t>
+          <t>GESTIONAR EXTERNO 2071 ud.</t>
         </is>
       </c>
     </row>
@@ -17618,26 +17618,26 @@
         <v>0.9</v>
       </c>
       <c r="E29" s="22" t="n">
-        <v>4678.5</v>
+        <v>4674.2</v>
       </c>
       <c r="F29" s="22" t="n">
         <v>268.7</v>
       </c>
       <c r="G29" s="22" t="n">
-        <v>3941.6</v>
+        <v>3943.8</v>
       </c>
       <c r="H29" s="22" t="n">
-        <v>3890</v>
+        <v>3885</v>
       </c>
       <c r="I29" s="22" t="n">
-        <v>3890</v>
+        <v>3885</v>
       </c>
       <c r="J29" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3890 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 3885 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr"/>
@@ -17660,22 +17660,22 @@
         <v>0</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>3988.4</v>
+        <v>4002.5</v>
       </c>
       <c r="F30" s="22" t="n">
         <v>2.2</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>4159.3</v>
+        <v>4163.6</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>3988</v>
+        <v>4002</v>
       </c>
       <c r="I30" s="22" t="n">
         <v>180</v>
       </c>
       <c r="J30" s="22" t="n">
-        <v>3808</v>
+        <v>3822</v>
       </c>
       <c r="K30" s="21" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="L30" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3808 ud.</t>
+          <t>GESTIONAR EXTERNO 3822 ud.</t>
         </is>
       </c>
     </row>
@@ -17706,22 +17706,22 @@
         <v>1.7</v>
       </c>
       <c r="E31" s="22" t="n">
-        <v>4025.6</v>
+        <v>4027.1</v>
       </c>
       <c r="F31" s="22" t="n">
         <v>160.8</v>
       </c>
       <c r="G31" s="22" t="n">
-        <v>3736.9</v>
+        <v>3738.4</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="I31" s="22" t="n">
         <v>2100</v>
       </c>
       <c r="J31" s="22" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="K31" s="21" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
       </c>
       <c r="L31" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 635 ud.</t>
+          <t>GESTIONAR EXTERNO 636 ud.</t>
         </is>
       </c>
     </row>
@@ -17752,22 +17752,22 @@
         <v>0.5</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>3837.1</v>
+        <v>3869.1</v>
       </c>
       <c r="F32" s="22" t="n">
         <v>107.7</v>
       </c>
       <c r="G32" s="22" t="n">
-        <v>3573.3</v>
+        <v>3584.2</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>3461</v>
+        <v>3493</v>
       </c>
       <c r="I32" s="22" t="n">
         <v>1080</v>
       </c>
       <c r="J32" s="22" t="n">
-        <v>2381</v>
+        <v>2413</v>
       </c>
       <c r="K32" s="21" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="L32" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2381 ud.</t>
+          <t>GESTIONAR EXTERNO 2413 ud.</t>
         </is>
       </c>
     </row>
@@ -17798,22 +17798,22 @@
         <v>1.5</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>2890.1</v>
+        <v>2900.7</v>
       </c>
       <c r="F33" s="22" t="n">
         <v>32</v>
       </c>
       <c r="G33" s="22" t="n">
-        <v>2948.7</v>
+        <v>2952.3</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>1978</v>
+        <v>1989</v>
       </c>
       <c r="I33" s="22" t="n">
         <v>1800</v>
       </c>
       <c r="J33" s="22" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="K33" s="21" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="L33" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 178 ud.</t>
+          <t>GESTIONAR EXTERNO 189 ud.</t>
         </is>
       </c>
     </row>
@@ -17844,22 +17844,22 @@
         <v>1</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>2691.1</v>
+        <v>2696.8</v>
       </c>
       <c r="F34" s="22" t="n">
         <v>15.2</v>
       </c>
       <c r="G34" s="22" t="n">
-        <v>2485.8</v>
+        <v>2489.2</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>2211</v>
+        <v>2217</v>
       </c>
       <c r="I34" s="22" t="n">
         <v>298</v>
       </c>
       <c r="J34" s="22" t="n">
-        <v>1913</v>
+        <v>1919</v>
       </c>
       <c r="K34" s="21" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="L34" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1913 ud.</t>
+          <t>GESTIONAR EXTERNO 1919 ud.</t>
         </is>
       </c>
     </row>
@@ -17932,26 +17932,26 @@
         <v>0.6</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>2033.9</v>
+        <v>2037.7</v>
       </c>
       <c r="F36" s="22" t="n">
         <v>11.1</v>
       </c>
       <c r="G36" s="22" t="n">
-        <v>2095.3</v>
+        <v>2097.4</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="J36" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1772 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1776 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L36" s="21" t="inlineStr"/>
@@ -18013,29 +18013,29 @@
         <v>506</v>
       </c>
       <c r="D38" s="22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>1977.8</v>
+        <v>1995</v>
       </c>
       <c r="F38" s="22" t="n">
         <v>80.7</v>
       </c>
       <c r="G38" s="22" t="n">
-        <v>1662.8</v>
+        <v>1669.3</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>1472</v>
+        <v>1489</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>1472</v>
+        <v>1489</v>
       </c>
       <c r="J38" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1472 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1489 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L38" s="21" t="inlineStr"/>
@@ -18058,22 +18058,22 @@
         <v>1.3</v>
       </c>
       <c r="E39" s="22" t="n">
-        <v>1503.5</v>
+        <v>1512.4</v>
       </c>
       <c r="F39" s="22" t="n">
         <v>0.3</v>
       </c>
       <c r="G39" s="22" t="n">
-        <v>1565.8</v>
+        <v>1569.9</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="I39" s="22" t="n">
         <v>1071</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K39" s="21" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
       </c>
       <c r="L39" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 19 ud.</t>
+          <t>GESTIONAR EXTERNO 27 ud.</t>
         </is>
       </c>
     </row>
@@ -18104,26 +18104,26 @@
         <v>0.9</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>1660.8</v>
+        <v>1670.5</v>
       </c>
       <c r="F40" s="22" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G40" s="22" t="n">
-        <v>1524.6</v>
+        <v>1528.9</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>1375</v>
+        <v>1384</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>1375</v>
+        <v>1384</v>
       </c>
       <c r="J40" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1375 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1384 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L40" s="21" t="inlineStr"/>
@@ -18188,22 +18188,22 @@
         <v>1</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>1096.9</v>
+        <v>1095.5</v>
       </c>
       <c r="F42" s="22" t="n">
         <v>29</v>
       </c>
       <c r="G42" s="22" t="n">
-        <v>1218.6</v>
+        <v>1219.3</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="I42" s="22" t="n">
         <v>600</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K42" s="21" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
       </c>
       <c r="L42" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 252 ud.</t>
+          <t>GESTIONAR EXTERNO 250 ud.</t>
         </is>
       </c>
     </row>
@@ -18234,26 +18234,26 @@
         <v>1.1</v>
       </c>
       <c r="E43" s="22" t="n">
-        <v>1291.4</v>
+        <v>1294.3</v>
       </c>
       <c r="F43" s="22" t="n">
         <v>12.9</v>
       </c>
       <c r="G43" s="22" t="n">
-        <v>1173.2</v>
+        <v>1175</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="I43" s="22" t="n">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="J43" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1036 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1039 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L43" s="21" t="inlineStr"/>
@@ -18452,22 +18452,22 @@
         <v>1.6</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>326.2</v>
+        <v>327.3</v>
       </c>
       <c r="F48" s="22" t="n">
         <v>0.3</v>
       </c>
       <c r="G48" s="22" t="n">
-        <v>328.9</v>
+        <v>329.2</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I48" s="22" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="22" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K48" s="21" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
       </c>
       <c r="L48" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 218 ud.</t>
+          <t>GESTIONAR EXTERNO 219 ud.</t>
         </is>
       </c>
     </row>
@@ -18498,22 +18498,22 @@
         <v>1.8</v>
       </c>
       <c r="E49" s="22" t="n">
-        <v>260.7</v>
+        <v>261.6</v>
       </c>
       <c r="F49" s="22" t="n">
         <v>3.8</v>
       </c>
       <c r="G49" s="22" t="n">
-        <v>235.1</v>
+        <v>235.4</v>
       </c>
       <c r="H49" s="22" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="22" t="n">
         <v>80</v>
       </c>
       <c r="J49" s="22" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K49" s="21" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="L49" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 97 ud.</t>
+          <t>GESTIONAR EXTERNO 98 ud.</t>
         </is>
       </c>
     </row>
@@ -18628,7 +18628,7 @@
         <v>1.9</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>110.4</v>
+        <v>110.5</v>
       </c>
       <c r="F52" s="22" t="n">
         <v>3.5</v>
@@ -18712,13 +18712,13 @@
         <v>0</v>
       </c>
       <c r="E54" s="22" t="n">
-        <v>39.9</v>
+        <v>40.1</v>
       </c>
       <c r="F54" s="22" t="n">
         <v>0.2</v>
       </c>
       <c r="G54" s="22" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="H54" s="22" t="n">
         <v>40</v>
@@ -18796,22 +18796,22 @@
         <v>1.1</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="F56" s="22" t="n">
         <v>8.4</v>
       </c>
       <c r="G56" s="22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I56" s="22" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K56" s="21" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
       </c>
       <c r="L56" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 16 ud.</t>
+          <t>GESTIONAR EXTERNO 17 ud.</t>
         </is>
       </c>
     </row>
@@ -18888,22 +18888,22 @@
         <v>2.3</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>17799</v>
+        <v>17853.3</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>239.8</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>18041.8</v>
+        <v>18052.5</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>9475</v>
+        <v>9529</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>9000</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>475</v>
+        <v>529</v>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 475 ud.</t>
+          <t>GESTIONAR EXTERNO 529 ud.</t>
         </is>
       </c>
     </row>
@@ -18934,26 +18934,26 @@
         <v>4.8</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>7302.4</v>
+        <v>7309</v>
       </c>
       <c r="F59" s="4" t="n">
         <v>590.7</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>6028.6</v>
+        <v>6034.7</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 983 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 990 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr"/>
@@ -18976,22 +18976,22 @@
         <v>2.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>3752.5</v>
+        <v>3760.7</v>
       </c>
       <c r="F60" s="4" t="n">
         <v>7.2</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>3498.5</v>
+        <v>3503.5</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1854</v>
+        <v>1862</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>1854</v>
+        <v>1862</v>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1854 ud.</t>
+          <t>GESTIONAR EXTERNO 1862 ud.</t>
         </is>
       </c>
     </row>
@@ -19022,22 +19022,22 @@
         <v>3.7</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2549.9</v>
+        <v>2558.4</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>235</v>
+        <v>235.5</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>2022.3</v>
+        <v>2024.5</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="I61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 858 ud.</t>
+          <t>GESTIONAR EXTERNO 866 ud.</t>
         </is>
       </c>
     </row>
@@ -19068,26 +19068,26 @@
         <v>4</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1287.6</v>
+        <v>1292.2</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>41.9</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>1276.3</v>
+        <v>1277.7</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 223 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 227 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr"/>
@@ -19107,29 +19107,29 @@
         <v>1061</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1679.5</v>
+        <v>1681.9</v>
       </c>
       <c r="F63" s="4" t="n">
         <v>442.6</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>867</v>
+        <v>868.1</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 618 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 621 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr"/>
@@ -19152,22 +19152,22 @@
         <v>4.8</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1626.6</v>
+        <v>1634.4</v>
       </c>
       <c r="F64" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>1264.7</v>
+        <v>1267.6</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 407 ud.</t>
+          <t>GESTIONAR EXTERNO 414 ud.</t>
         </is>
       </c>
     </row>
@@ -19198,26 +19198,26 @@
         <v>2.5</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>919.9</v>
+        <v>922.7</v>
       </c>
       <c r="F65" s="4" t="n">
         <v>29.2</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>834.7</v>
+        <v>835.4</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 495 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 498 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr"/>
@@ -19240,26 +19240,26 @@
         <v>2.5</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>631.5</v>
+        <v>633.8</v>
       </c>
       <c r="F66" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>622.6</v>
+        <v>623.3</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 310 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 313 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr"/>
@@ -19282,7 +19282,7 @@
         <v>4.1</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>590</v>
+        <v>591.4</v>
       </c>
       <c r="F67" s="4" t="n">
         <v>6</v>
@@ -19291,17 +19291,17 @@
         <v>538.3</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 147 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 148 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr"/>
@@ -19324,22 +19324,22 @@
         <v>3.5</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>416.7</v>
+        <v>418.4</v>
       </c>
       <c r="F68" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>387.9</v>
+        <v>388.6</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 148 ud.</t>
+          <t>GESTIONAR EXTERNO 149 ud.</t>
         </is>
       </c>
     </row>
@@ -19412,26 +19412,26 @@
         <v>3</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>102.4</v>
+        <v>103</v>
       </c>
       <c r="F70" s="4" t="n">
         <v>3.4</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 41 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 42 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr"/>
@@ -19454,13 +19454,13 @@
         <v>3.1</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F71" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="H71" s="4" t="n">
         <v>34</v>
@@ -19493,29 +19493,29 @@
         <v>37</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>51.4</v>
+        <v>52.3</v>
       </c>
       <c r="F72" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 14 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 15 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -19538,13 +19538,13 @@
         <v>4.2</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="F73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="H73" s="4" t="n">
         <v>7</v>
@@ -19759,23 +19759,23 @@
         <v>0</v>
       </c>
       <c r="E3" s="20" t="n">
-        <v>40029.4</v>
+        <v>40096.8</v>
       </c>
       <c r="F3" s="20" t="n">
         <v>239.8</v>
       </c>
       <c r="G3" s="20" t="n">
-        <v>18041.8</v>
+        <v>18052.5</v>
       </c>
       <c r="H3" s="20" t="n">
-        <v>40029</v>
+        <v>40097</v>
       </c>
       <c r="I3" s="20" t="n">
         <v>214000</v>
       </c>
       <c r="J3" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 40029 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 40097 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K3" s="19" t="inlineStr"/>
@@ -19798,23 +19798,23 @@
         <v>0</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>24183.7</v>
+        <v>24224.9</v>
       </c>
       <c r="F4" s="20" t="n">
         <v>146</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>10475.8</v>
+        <v>10482.7</v>
       </c>
       <c r="H4" s="20" t="n">
-        <v>24184</v>
+        <v>24225</v>
       </c>
       <c r="I4" s="20" t="n">
         <v>30000</v>
       </c>
       <c r="J4" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 24184 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 24225 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K4" s="19" t="inlineStr"/>
@@ -19837,23 +19837,23 @@
         <v>0</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>22164.6</v>
+        <v>22179.3</v>
       </c>
       <c r="F5" s="20" t="n">
         <v>406.4</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>9104.700000000001</v>
+        <v>9110.9</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>22165</v>
+        <v>22179</v>
       </c>
       <c r="I5" s="20" t="n">
         <v>54000</v>
       </c>
       <c r="J5" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 22165 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 22179 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K5" s="19" t="inlineStr"/>
@@ -19876,16 +19876,16 @@
         <v>0</v>
       </c>
       <c r="E6" s="20" t="n">
-        <v>22327.1</v>
+        <v>22311.8</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>7.2</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>9351.9</v>
+        <v>9358</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>22327</v>
+        <v>22312</v>
       </c>
       <c r="I6" s="20" t="n">
         <v>0</v>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="K6" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 22327 ud.</t>
+          <t>COMPRA EXTERNA 22312 ud.</t>
         </is>
       </c>
     </row>
@@ -19919,23 +19919,23 @@
         <v>0</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>21921.2</v>
+        <v>21929</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>87.7</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>9040.1</v>
+        <v>9043.299999999999</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>21921</v>
+        <v>21929</v>
       </c>
       <c r="I7" s="20" t="n">
         <v>33992</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 21921 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 21929 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K7" s="19" t="inlineStr"/>
@@ -19958,16 +19958,16 @@
         <v>0</v>
       </c>
       <c r="E8" s="20" t="n">
-        <v>17591.1</v>
+        <v>17607</v>
       </c>
       <c r="F8" s="20" t="n">
         <v>243.5</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>7764.1</v>
+        <v>7771.3</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>17591</v>
+        <v>17607</v>
       </c>
       <c r="I8" s="20" t="n">
         <v>10400</v>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="K8" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 7191 ud.</t>
+          <t>COMPRA EXTERNA 7207 ud.</t>
         </is>
       </c>
     </row>
@@ -20001,23 +20001,23 @@
         <v>0</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>18122.9</v>
+        <v>18111.9</v>
       </c>
       <c r="F9" s="20" t="n">
         <v>428.4</v>
       </c>
       <c r="G9" s="20" t="n">
-        <v>7391.3</v>
+        <v>7397.4</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>18123</v>
+        <v>18112</v>
       </c>
       <c r="I9" s="20" t="n">
         <v>52900</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 18123 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 18112 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K9" s="19" t="inlineStr"/>
@@ -20040,16 +20040,16 @@
         <v>0</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>13907.6</v>
+        <v>13886.7</v>
       </c>
       <c r="F10" s="20" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>6013.5</v>
+        <v>6019.3</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>13908</v>
+        <v>13887</v>
       </c>
       <c r="I10" s="20" t="n">
         <v>1500</v>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="K10" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 12408 ud.</t>
+          <t>COMPRA EXTERNA 12387 ud.</t>
         </is>
       </c>
     </row>
@@ -20083,23 +20083,23 @@
         <v>0</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>13868.2</v>
+        <v>13880</v>
       </c>
       <c r="F11" s="20" t="n">
         <v>71</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>5908.7</v>
+        <v>5913.8</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>13868</v>
+        <v>13880</v>
       </c>
       <c r="I11" s="20" t="n">
         <v>17700</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 13868 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 13880 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K11" s="19" t="inlineStr"/>
@@ -20122,16 +20122,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>13181.8</v>
+        <v>13188.7</v>
       </c>
       <c r="F12" s="20" t="n">
         <v>35.7</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>5515.9</v>
+        <v>5518.8</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>13182</v>
+        <v>13189</v>
       </c>
       <c r="I12" s="20" t="n">
         <v>3930</v>
@@ -20143,7 +20143,7 @@
       </c>
       <c r="K12" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 9252 ud.</t>
+          <t>COMPRA EXTERNA 9259 ud.</t>
         </is>
       </c>
     </row>
@@ -20165,16 +20165,16 @@
         <v>0</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>10999.1</v>
+        <v>11022.2</v>
       </c>
       <c r="F13" s="20" t="n">
         <v>144.3</v>
       </c>
       <c r="G13" s="20" t="n">
-        <v>4431</v>
+        <v>4436.1</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>10999</v>
+        <v>11022</v>
       </c>
       <c r="I13" s="20" t="n">
         <v>4000</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="K13" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 6999 ud.</t>
+          <t>COMPRA EXTERNA 7022 ud.</t>
         </is>
       </c>
     </row>
@@ -20208,16 +20208,16 @@
         <v>0</v>
       </c>
       <c r="E14" s="20" t="n">
-        <v>9365</v>
+        <v>9384.799999999999</v>
       </c>
       <c r="F14" s="20" t="n">
         <v>2.2</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>4159.3</v>
+        <v>4163.6</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>9365</v>
+        <v>9385</v>
       </c>
       <c r="I14" s="20" t="n">
         <v>0</v>
@@ -20229,7 +20229,7 @@
       </c>
       <c r="K14" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 9365 ud.</t>
+          <t>COMPRA EXTERNA 9385 ud.</t>
         </is>
       </c>
     </row>
@@ -20251,16 +20251,16 @@
         <v>0</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>8704</v>
+        <v>8719.799999999999</v>
       </c>
       <c r="F15" s="20" t="n">
         <v>211.2</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>3735.1</v>
+        <v>3738</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>8704</v>
+        <v>8720</v>
       </c>
       <c r="I15" s="20" t="n">
         <v>0</v>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="K15" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 8704 ud.</t>
+          <t>COMPRA EXTERNA 8720 ud.</t>
         </is>
       </c>
     </row>
@@ -20294,16 +20294,16 @@
         <v>0</v>
       </c>
       <c r="E16" s="20" t="n">
-        <v>8313.1</v>
+        <v>8316.200000000001</v>
       </c>
       <c r="F16" s="20" t="n">
         <v>160.8</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>3736.9</v>
+        <v>3738.4</v>
       </c>
       <c r="H16" s="20" t="n">
-        <v>8313</v>
+        <v>8316</v>
       </c>
       <c r="I16" s="20" t="n">
         <v>5700</v>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="K16" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2613 ud.</t>
+          <t>COMPRA EXTERNA 2616 ud.</t>
         </is>
       </c>
     </row>
@@ -20337,16 +20337,16 @@
         <v>0</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>8372.200000000001</v>
+        <v>8402.799999999999</v>
       </c>
       <c r="F17" s="20" t="n">
         <v>107.7</v>
       </c>
       <c r="G17" s="20" t="n">
-        <v>3573.3</v>
+        <v>3584.2</v>
       </c>
       <c r="H17" s="20" t="n">
-        <v>8372</v>
+        <v>8403</v>
       </c>
       <c r="I17" s="20" t="n">
         <v>3000</v>
@@ -20358,7 +20358,7 @@
       </c>
       <c r="K17" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 5372 ud.</t>
+          <t>COMPRA EXTERNA 5403 ud.</t>
         </is>
       </c>
     </row>
@@ -20380,13 +20380,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="20" t="n">
-        <v>8253.799999999999</v>
+        <v>8254.5</v>
       </c>
       <c r="F18" s="20" t="n">
         <v>7.2</v>
       </c>
       <c r="G18" s="20" t="n">
-        <v>3498.5</v>
+        <v>3503.5</v>
       </c>
       <c r="H18" s="20" t="n">
         <v>8254</v>
@@ -20419,16 +20419,16 @@
         <v>0</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>6915.1</v>
+        <v>6916.8</v>
       </c>
       <c r="F19" s="20" t="n">
         <v>12.5</v>
       </c>
       <c r="G19" s="20" t="n">
-        <v>3039.7</v>
+        <v>3044.8</v>
       </c>
       <c r="H19" s="20" t="n">
-        <v>6915</v>
+        <v>6917</v>
       </c>
       <c r="I19" s="20" t="n">
         <v>0</v>
@@ -20440,7 +20440,7 @@
       </c>
       <c r="K19" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 6915 ud.</t>
+          <t>COMPRA EXTERNA 6917 ud.</t>
         </is>
       </c>
     </row>
@@ -20462,16 +20462,16 @@
         <v>0</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>5930.4</v>
+        <v>5944.7</v>
       </c>
       <c r="F20" s="20" t="n">
         <v>32</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>2948.7</v>
+        <v>2952.3</v>
       </c>
       <c r="H20" s="20" t="n">
-        <v>5930</v>
+        <v>5945</v>
       </c>
       <c r="I20" s="20" t="n">
         <v>1200</v>
@@ -20483,7 +20483,7 @@
       </c>
       <c r="K20" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 4730 ud.</t>
+          <t>COMPRA EXTERNA 4745 ud.</t>
         </is>
       </c>
     </row>
@@ -20505,13 +20505,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>6312.7</v>
+        <v>6313.2</v>
       </c>
       <c r="F21" s="20" t="n">
         <v>15.2</v>
       </c>
       <c r="G21" s="20" t="n">
-        <v>2485.8</v>
+        <v>2489.2</v>
       </c>
       <c r="H21" s="20" t="n">
         <v>6313</v>
@@ -20548,23 +20548,23 @@
         <v>0</v>
       </c>
       <c r="E22" s="20" t="n">
-        <v>5403.3</v>
+        <v>5415.1</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>235</v>
+        <v>235.5</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>2022.3</v>
+        <v>2024.5</v>
       </c>
       <c r="H22" s="20" t="n">
-        <v>5403</v>
+        <v>5415</v>
       </c>
       <c r="I22" s="20" t="n">
         <v>26000</v>
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 5403 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 5415 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K22" s="19" t="inlineStr"/>
@@ -20587,16 +20587,16 @@
         <v>0</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>3044.7</v>
+        <v>3051.2</v>
       </c>
       <c r="F23" s="20" t="n">
         <v>0.3</v>
       </c>
       <c r="G23" s="20" t="n">
-        <v>1565.8</v>
+        <v>1569.9</v>
       </c>
       <c r="H23" s="20" t="n">
-        <v>3045</v>
+        <v>3051</v>
       </c>
       <c r="I23" s="20" t="n">
         <v>350</v>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="K23" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2695 ud.</t>
+          <t>COMPRA EXTERNA 2701 ud.</t>
         </is>
       </c>
     </row>
@@ -20630,23 +20630,23 @@
         <v>0</v>
       </c>
       <c r="E24" s="20" t="n">
-        <v>3318.1</v>
+        <v>3323.2</v>
       </c>
       <c r="F24" s="20" t="n">
         <v>7.1</v>
       </c>
       <c r="G24" s="20" t="n">
-        <v>1456.4</v>
+        <v>1457.1</v>
       </c>
       <c r="H24" s="20" t="n">
-        <v>3318</v>
+        <v>3323</v>
       </c>
       <c r="I24" s="20" t="n">
         <v>32000</v>
       </c>
       <c r="J24" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 3318 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3323 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K24" s="19" t="inlineStr"/>
@@ -20669,23 +20669,23 @@
         <v>0</v>
       </c>
       <c r="E25" s="20" t="n">
-        <v>3308.4</v>
+        <v>3314.9</v>
       </c>
       <c r="F25" s="20" t="n">
         <v>13.3</v>
       </c>
       <c r="G25" s="20" t="n">
-        <v>1264.7</v>
+        <v>1267.6</v>
       </c>
       <c r="H25" s="20" t="n">
-        <v>3308</v>
+        <v>3315</v>
       </c>
       <c r="I25" s="20" t="n">
         <v>17610</v>
       </c>
       <c r="J25" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 3308 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3315 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K25" s="19" t="inlineStr"/>
@@ -20708,23 +20708,23 @@
         <v>0</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>2529.1</v>
+        <v>2523.5</v>
       </c>
       <c r="F26" s="20" t="n">
         <v>29</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>1218.6</v>
+        <v>1219.3</v>
       </c>
       <c r="H26" s="20" t="n">
-        <v>2529</v>
+        <v>2524</v>
       </c>
       <c r="I26" s="20" t="n">
         <v>14100</v>
       </c>
       <c r="J26" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 2529 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2524 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K26" s="19" t="inlineStr"/>
@@ -20790,16 +20790,16 @@
         <v>0</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>1882</v>
+        <v>1890.9</v>
       </c>
       <c r="F28" s="20" t="n">
         <v>7.2</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>835.7</v>
+        <v>837.8</v>
       </c>
       <c r="H28" s="20" t="n">
-        <v>1882</v>
+        <v>1891</v>
       </c>
       <c r="I28" s="20" t="n">
         <v>0</v>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="K28" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1882 ud.</t>
+          <t>COMPRA EXTERNA 1891 ud.</t>
         </is>
       </c>
     </row>
@@ -20915,23 +20915,23 @@
         <v>0</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>806.3</v>
+        <v>808.7</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>387.9</v>
+        <v>388.6</v>
       </c>
       <c r="H31" s="20" t="n">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="I31" s="20" t="n">
         <v>3000</v>
       </c>
       <c r="J31" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 806 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 809 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K31" s="19" t="inlineStr"/>
@@ -20997,16 +20997,16 @@
         <v>0</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>748.8</v>
+        <v>750.3</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0.3</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>328.9</v>
+        <v>329.2</v>
       </c>
       <c r="H33" s="20" t="n">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="I33" s="20" t="n">
         <v>0</v>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="K33" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 749 ud.</t>
+          <t>COMPRA EXTERNA 750 ud.</t>
         </is>
       </c>
     </row>
@@ -21083,16 +21083,16 @@
         <v>0</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>629</v>
+        <v>630.6</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>1.6</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>250.4</v>
+        <v>250.7</v>
       </c>
       <c r="H35" s="20" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="I35" s="20" t="n">
         <v>150</v>
@@ -21104,7 +21104,7 @@
       </c>
       <c r="K35" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 479 ud.</t>
+          <t>COMPRA EXTERNA 481 ud.</t>
         </is>
       </c>
     </row>
@@ -21126,16 +21126,16 @@
         <v>0</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>562.7</v>
+        <v>563.9</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>3.8</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>235.1</v>
+        <v>235.4</v>
       </c>
       <c r="H36" s="20" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I36" s="20" t="n">
         <v>334</v>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="K36" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 229 ud.</t>
+          <t>COMPRA EXTERNA 230 ud.</t>
         </is>
       </c>
     </row>
@@ -21294,23 +21294,23 @@
         <v>0</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>321</v>
+        <v>326.3</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>130.6</v>
+        <v>133</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>19</v>
       </c>
       <c r="H40" s="20" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I40" s="20" t="n">
         <v>1450</v>
       </c>
       <c r="J40" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 321 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 326 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K40" s="19" t="inlineStr"/>
@@ -21454,16 +21454,16 @@
         <v>0</v>
       </c>
       <c r="E44" s="20" t="n">
-        <v>239.9</v>
+        <v>241.6</v>
       </c>
       <c r="F44" s="20" t="n">
         <v>1.3</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>112.1</v>
+        <v>112.8</v>
       </c>
       <c r="H44" s="20" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I44" s="20" t="n">
         <v>0</v>
@@ -21475,7 +21475,7 @@
       </c>
       <c r="K44" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 240 ud.</t>
+          <t>COMPRA EXTERNA 242 ud.</t>
         </is>
       </c>
     </row>
@@ -21497,7 +21497,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>142.8</v>
+        <v>142.7</v>
       </c>
       <c r="F45" s="20" t="n">
         <v>1.2</v>
@@ -21739,16 +21739,16 @@
         <v>0</v>
       </c>
       <c r="E51" s="20" t="n">
-        <v>54.6</v>
+        <v>56</v>
       </c>
       <c r="F51" s="20" t="n">
         <v>0.1</v>
       </c>
       <c r="G51" s="20" t="n">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
       <c r="H51" s="20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I51" s="20" t="n">
         <v>0</v>
@@ -21760,7 +21760,7 @@
       </c>
       <c r="K51" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 55 ud.</t>
+          <t>COMPRA EXTERNA 56 ud.</t>
         </is>
       </c>
     </row>
@@ -21782,13 +21782,13 @@
         <v>0</v>
       </c>
       <c r="E52" s="20" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F52" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="G52" s="20" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="H52" s="20" t="n">
         <v>65</v>
@@ -21864,13 +21864,13 @@
         <v>0</v>
       </c>
       <c r="E54" s="20" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="F54" s="20" t="n">
         <v>8.4</v>
       </c>
       <c r="G54" s="20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H54" s="20" t="n">
         <v>41</v>
@@ -22377,29 +22377,29 @@
         </is>
       </c>
       <c r="C67" s="22" t="n">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="D67" s="22" t="n">
         <v>0.2</v>
       </c>
       <c r="E67" s="22" t="n">
-        <v>12016</v>
+        <v>12040.6</v>
       </c>
       <c r="F67" s="22" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="G67" s="22" t="n">
-        <v>5252.7</v>
+        <v>5257.8</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>11815</v>
+        <v>11858</v>
       </c>
       <c r="I67" s="22" t="n">
         <v>20500</v>
       </c>
       <c r="J67" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 11815 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 11858 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K67" s="21" t="inlineStr"/>
@@ -22416,29 +22416,29 @@
         </is>
       </c>
       <c r="C68" s="22" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="D68" s="22" t="n">
         <v>1.1</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>10034</v>
+        <v>10015.6</v>
       </c>
       <c r="F68" s="22" t="n">
         <v>268.7</v>
       </c>
       <c r="G68" s="22" t="n">
-        <v>3941.6</v>
+        <v>3943.8</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>9124</v>
+        <v>9101</v>
       </c>
       <c r="I68" s="22" t="n">
         <v>45000</v>
       </c>
       <c r="J68" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 9124 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 9101 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K68" s="21" t="inlineStr"/>
@@ -22500,23 +22500,23 @@
         <v>2.8</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>4575.7</v>
+        <v>4581.9</v>
       </c>
       <c r="F70" s="22" t="n">
         <v>34.1</v>
       </c>
       <c r="G70" s="22" t="n">
-        <v>2126.7</v>
+        <v>2130.5</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>3376</v>
+        <v>3382</v>
       </c>
       <c r="I70" s="22" t="n">
         <v>20500</v>
       </c>
       <c r="J70" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3376 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3382 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K70" s="21" t="inlineStr"/>
@@ -22533,29 +22533,29 @@
         </is>
       </c>
       <c r="C71" s="22" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D71" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>4805.9</v>
+        <v>4804.1</v>
       </c>
       <c r="F71" s="22" t="n">
         <v>11.1</v>
       </c>
       <c r="G71" s="22" t="n">
-        <v>2095.3</v>
+        <v>2097.4</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>4598</v>
+        <v>4600</v>
       </c>
       <c r="I71" s="22" t="n">
         <v>22000</v>
       </c>
       <c r="J71" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 4598 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 4600 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K71" s="21" t="inlineStr"/>
@@ -22611,29 +22611,29 @@
         </is>
       </c>
       <c r="C73" s="22" t="n">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="D73" s="22" t="n">
         <v>0.9</v>
       </c>
       <c r="E73" s="22" t="n">
-        <v>4118.8</v>
+        <v>4137</v>
       </c>
       <c r="F73" s="22" t="n">
         <v>80.7</v>
       </c>
       <c r="G73" s="22" t="n">
-        <v>1662.8</v>
+        <v>1669.3</v>
       </c>
       <c r="H73" s="22" t="n">
-        <v>3791</v>
+        <v>3826</v>
       </c>
       <c r="I73" s="22" t="n">
         <v>20000</v>
       </c>
       <c r="J73" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3791 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3826 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K73" s="21" t="inlineStr"/>
@@ -22689,29 +22689,29 @@
         </is>
       </c>
       <c r="C75" s="22" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D75" s="22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E75" s="22" t="n">
-        <v>2884.3</v>
+        <v>2882.5</v>
       </c>
       <c r="F75" s="22" t="n">
         <v>442.6</v>
       </c>
       <c r="G75" s="22" t="n">
-        <v>867</v>
+        <v>868.1</v>
       </c>
       <c r="H75" s="22" t="n">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="I75" s="22" t="n">
         <v>16840</v>
       </c>
       <c r="J75" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 2502 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2504 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K75" s="21" t="inlineStr"/>
@@ -22728,29 +22728,29 @@
         </is>
       </c>
       <c r="C76" s="22" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D76" s="22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>2861.8</v>
+        <v>2862.4</v>
       </c>
       <c r="F76" s="22" t="n">
         <v>12.9</v>
       </c>
       <c r="G76" s="22" t="n">
-        <v>1173.2</v>
+        <v>1175</v>
       </c>
       <c r="H76" s="22" t="n">
-        <v>2398</v>
+        <v>2401</v>
       </c>
       <c r="I76" s="22" t="n">
         <v>10320</v>
       </c>
       <c r="J76" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 2398 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2401 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K76" s="21" t="inlineStr"/>
@@ -22767,29 +22767,29 @@
         </is>
       </c>
       <c r="C77" s="22" t="n">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D77" s="22" t="n">
         <v>2.9</v>
       </c>
       <c r="E77" s="22" t="n">
-        <v>2063.7</v>
+        <v>2067.5</v>
       </c>
       <c r="F77" s="22" t="n">
         <v>29.2</v>
       </c>
       <c r="G77" s="22" t="n">
-        <v>834.7</v>
+        <v>835.4</v>
       </c>
       <c r="H77" s="22" t="n">
-        <v>1559</v>
+        <v>1566</v>
       </c>
       <c r="I77" s="22" t="n">
         <v>2700</v>
       </c>
       <c r="J77" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1559 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1566 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K77" s="21" t="inlineStr"/>
@@ -22806,29 +22806,29 @@
         </is>
       </c>
       <c r="C78" s="22" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D78" s="22" t="n">
         <v>1.5</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>1270.8</v>
+        <v>1273.8</v>
       </c>
       <c r="F78" s="22" t="n">
         <v>19.2</v>
       </c>
       <c r="G78" s="22" t="n">
-        <v>622.6</v>
+        <v>623.3</v>
       </c>
       <c r="H78" s="22" t="n">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="I78" s="22" t="n">
         <v>3500</v>
       </c>
       <c r="J78" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1081 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1087 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K78" s="21" t="inlineStr"/>
@@ -22845,13 +22845,13 @@
         </is>
       </c>
       <c r="C79" s="22" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D79" s="22" t="n">
         <v>1.1</v>
       </c>
       <c r="E79" s="22" t="n">
-        <v>1258.3</v>
+        <v>1259.8</v>
       </c>
       <c r="F79" s="22" t="n">
         <v>6</v>
@@ -22860,14 +22860,14 @@
         <v>538.3</v>
       </c>
       <c r="H79" s="22" t="n">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="I79" s="22" t="n">
         <v>7910</v>
       </c>
       <c r="J79" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1135 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1138 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K79" s="21" t="inlineStr"/>
@@ -22968,7 +22968,7 @@
         <v>0.9</v>
       </c>
       <c r="E82" s="22" t="n">
-        <v>240.2</v>
+        <v>240.4</v>
       </c>
       <c r="F82" s="22" t="n">
         <v>3.5</v>
@@ -23007,13 +23007,13 @@
         <v>1.1</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>184.3</v>
+        <v>184.4</v>
       </c>
       <c r="F83" s="22" t="n">
         <v>1.6</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="H83" s="22" t="n">
         <v>168</v>
@@ -23079,29 +23079,29 @@
         </is>
       </c>
       <c r="C85" s="26" t="n">
-        <v>4767</v>
+        <v>4760</v>
       </c>
       <c r="D85" s="26" t="n">
         <v>3.6</v>
       </c>
       <c r="E85" s="26" t="n">
-        <v>15589.7</v>
+        <v>15603.9</v>
       </c>
       <c r="F85" s="26" t="n">
         <v>590.7</v>
       </c>
       <c r="G85" s="26" t="n">
-        <v>6028.6</v>
+        <v>6034.7</v>
       </c>
       <c r="H85" s="26" t="n">
-        <v>10823</v>
+        <v>10844</v>
       </c>
       <c r="I85" s="26" t="n">
         <v>89100</v>
       </c>
       <c r="J85" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 10823 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 10844 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K85" s="25" t="inlineStr"/>
@@ -23118,29 +23118,29 @@
         </is>
       </c>
       <c r="C86" s="26" t="n">
-        <v>3309</v>
+        <v>3295</v>
       </c>
       <c r="D86" s="26" t="n">
         <v>3.6</v>
       </c>
       <c r="E86" s="26" t="n">
-        <v>9508.5</v>
+        <v>9524.799999999999</v>
       </c>
       <c r="F86" s="26" t="n">
         <v>15.9</v>
       </c>
       <c r="G86" s="26" t="n">
-        <v>4619.6</v>
+        <v>4622.2</v>
       </c>
       <c r="H86" s="26" t="n">
-        <v>6200</v>
+        <v>6230</v>
       </c>
       <c r="I86" s="26" t="n">
         <v>18580</v>
       </c>
       <c r="J86" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 6200 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 6230 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K86" s="25" t="inlineStr"/>
@@ -23163,16 +23163,16 @@
         <v>3.5</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>2885.7</v>
+        <v>2893.5</v>
       </c>
       <c r="F87" s="26" t="n">
         <v>2.2</v>
       </c>
       <c r="G87" s="26" t="n">
-        <v>1419.1</v>
+        <v>1421.2</v>
       </c>
       <c r="H87" s="26" t="n">
-        <v>1896</v>
+        <v>1904</v>
       </c>
       <c r="I87" s="26" t="n">
         <v>1800</v>
@@ -23184,7 +23184,7 @@
       </c>
       <c r="K87" s="25" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 96 ud.</t>
+          <t>COMPRA EXTERNA 104 ud.</t>
         </is>
       </c>
     </row>
@@ -23281,26 +23281,26 @@
         <v>100</v>
       </c>
       <c r="D90" s="26" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="E90" s="26" t="n">
-        <v>242.6</v>
+        <v>254</v>
       </c>
       <c r="F90" s="26" t="n">
-        <v>119.6</v>
+        <v>124.4</v>
       </c>
       <c r="G90" s="26" t="n">
         <v>0.5</v>
       </c>
       <c r="H90" s="26" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="I90" s="26" t="n">
         <v>2350</v>
       </c>
       <c r="J90" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 143 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 154 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K90" s="25" t="inlineStr"/>
@@ -23320,7 +23320,7 @@
         <v>5</v>
       </c>
       <c r="D91" s="26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="E91" s="26" t="n">
         <v>12.8</v>
@@ -23329,7 +23329,7 @@
         <v>0.7</v>
       </c>
       <c r="G91" s="26" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="H91" s="26" t="n">
         <v>8</v>
@@ -23362,23 +23362,23 @@
         <v>9</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>8201</v>
+        <v>8202.799999999999</v>
       </c>
       <c r="F92" s="4" t="n">
         <v>28.7</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>3313.7</v>
+        <v>3314.4</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="I92" s="4" t="n">
         <v>20000</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 2201 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2203 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr"/>
@@ -23401,13 +23401,13 @@
         <v>5</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>4997.7</v>
+        <v>4998.2</v>
       </c>
       <c r="F93" s="4" t="n">
         <v>135.4</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>2090.2</v>
+        <v>2093.6</v>
       </c>
       <c r="H93" s="4" t="n">
         <v>2768</v>
@@ -23438,29 +23438,29 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>1625</v>
+        <v>1616</v>
       </c>
       <c r="D94" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>3568.2</v>
+        <v>3577.1</v>
       </c>
       <c r="F94" s="4" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>1524.6</v>
+        <v>1528.9</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>1943</v>
+        <v>1961</v>
       </c>
       <c r="I94" s="4" t="n">
         <v>7600</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1943 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1961 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr"/>
@@ -23477,22 +23477,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>2277</v>
+        <v>2273</v>
       </c>
       <c r="D95" s="4" t="n">
         <v>8.6</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>2663.7</v>
+        <v>2669.8</v>
       </c>
       <c r="F95" s="4" t="n">
         <v>41.9</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>1276.3</v>
+        <v>1277.7</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="I95" s="4" t="n">
         <v>0</v>
@@ -23504,7 +23504,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 387 ud.</t>
+          <t>COMPRA EXTERNA 397 ud.</t>
         </is>
       </c>
     </row>
@@ -23526,23 +23526,23 @@
         <v>7</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>2514.3</v>
+        <v>2513.2</v>
       </c>
       <c r="F96" s="4" t="n">
         <v>0.6</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>1065.1</v>
+        <v>1066.1</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="I96" s="4" t="n">
         <v>6000</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1014 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1013 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr"/>
@@ -23565,23 +23565,23 @@
         <v>7.5</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>1676.5</v>
+        <v>1684.2</v>
       </c>
       <c r="F97" s="4" t="n">
         <v>7.2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>862</v>
+        <v>865.2</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="I97" s="4" t="n">
         <v>19400</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 376 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 384 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr"/>
@@ -23643,13 +23643,13 @@
         <v>5.7</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="F99" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="H99" s="4" t="n">
         <v>30</v>
@@ -23682,13 +23682,13 @@
         <v>5.1</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>89.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F100" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="H100" s="4" t="n">
         <v>51</v>
@@ -23721,23 +23721,23 @@
         <v>7.7</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="F101" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I101" s="4" t="n">
         <v>40</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 18 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr"/>
@@ -23799,7 +23799,7 @@
         <v>9</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="F103" s="4" t="n">
         <v>0.4</v>
@@ -23838,23 +23838,23 @@
         <v>10.5</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>4125.3</v>
+        <v>4126.8</v>
       </c>
       <c r="F104" s="10" t="n">
         <v>75.40000000000001</v>
       </c>
       <c r="G104" s="10" t="n">
-        <v>1835.2</v>
+        <v>1835.9</v>
       </c>
       <c r="H104" s="10" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I104" s="10" t="n">
         <v>11000</v>
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR 125 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 127 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr"/>
@@ -23916,13 +23916,13 @@
         <v>10.1</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>133.9</v>
+        <v>134.3</v>
       </c>
       <c r="F106" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="G106" s="10" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="H106" s="10" t="n">
         <v>24</v>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -1591,7 +1591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3677,26 +3677,26 @@
         </is>
       </c>
       <c r="C53" s="22" t="n">
-        <v>6363</v>
+        <v>6243</v>
       </c>
       <c r="D53" s="22" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E53" s="22" t="n">
         <v>20628.2</v>
       </c>
       <c r="F53" s="22" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G53" s="22" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H53" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 2000 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J53" s="21" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="C54" s="22" t="n">
-        <v>3290</v>
+        <v>3230</v>
       </c>
       <c r="D54" s="22" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E54" s="22" t="n">
         <v>12484.3</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="C55" s="22" t="n">
-        <v>2755</v>
+        <v>2695</v>
       </c>
       <c r="D55" s="22" t="n">
         <v>1.5</v>
@@ -3758,17 +3758,17 @@
         <v>11461</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>1380</v>
+        <v>1440</v>
       </c>
       <c r="G55" s="22" t="n">
-        <v>1380</v>
+        <v>1440</v>
       </c>
       <c r="H55" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1380 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1440 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J55" s="21" t="inlineStr"/>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="C56" s="22" t="n">
-        <v>3317</v>
+        <v>3227</v>
       </c>
       <c r="D56" s="22" t="n">
         <v>1.8</v>
@@ -3794,17 +3794,17 @@
         <v>11370.1</v>
       </c>
       <c r="F56" s="22" t="n">
-        <v>607</v>
+        <v>697</v>
       </c>
       <c r="G56" s="22" t="n">
-        <v>607</v>
+        <v>697</v>
       </c>
       <c r="H56" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 607 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 697 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J56" s="21" t="inlineStr"/>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="C57" s="22" t="n">
-        <v>2632</v>
+        <v>2587</v>
       </c>
       <c r="D57" s="22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E57" s="22" t="n">
         <v>8968.299999999999</v>
@@ -3848,7 +3848,7 @@
     <row r="58">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>VILDAGLIPTINA 50 MG CM</t>
+          <t>DABIGATRAN ETEXILATO CP 150 MG</t>
         </is>
       </c>
       <c r="B58" s="21" t="inlineStr">
@@ -3857,38 +3857,34 @@
         </is>
       </c>
       <c r="C58" s="22" t="n">
-        <v>0</v>
+        <v>2199</v>
       </c>
       <c r="D58" s="22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="E58" s="22" t="n">
-        <v>4882.8</v>
+        <v>6899.2</v>
       </c>
       <c r="F58" s="22" t="n">
-        <v>1740</v>
+        <v>197</v>
       </c>
       <c r="G58" s="22" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="H58" s="22" t="n">
-        <v>1560</v>
+        <v>0</v>
       </c>
       <c r="I58" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J58" s="21" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 1560 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 197 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J58" s="21" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+          <t>VILDAGLIPTINA 50 MG CM</t>
         </is>
       </c>
       <c r="B59" s="21" t="inlineStr">
@@ -3897,34 +3893,38 @@
         </is>
       </c>
       <c r="C59" s="22" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="D59" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="22" t="n">
-        <v>4280.1</v>
+        <v>4882.8</v>
       </c>
       <c r="F59" s="22" t="n">
-        <v>840</v>
+        <v>1740</v>
       </c>
       <c r="G59" s="22" t="n">
-        <v>840</v>
+        <v>180</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>0</v>
+        <v>1560</v>
       </c>
       <c r="I59" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 840 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J59" s="21" t="inlineStr"/>
+          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J59" s="21" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1560 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
         </is>
       </c>
       <c r="B60" s="21" t="inlineStr">
@@ -3933,26 +3933,26 @@
         </is>
       </c>
       <c r="C60" s="22" t="n">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="D60" s="22" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>3455.3</v>
+        <v>4280.1</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>570</v>
+        <v>900</v>
       </c>
       <c r="G60" s="22" t="n">
-        <v>570</v>
+        <v>900</v>
       </c>
       <c r="H60" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 570 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 900 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J60" s="21" t="inlineStr"/>
@@ -3960,7 +3960,7 @@
     <row r="61">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>CLOPIDOGREL 75 MG COMPRIMIDO</t>
+          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
         </is>
       </c>
       <c r="B61" s="21" t="inlineStr">
@@ -3969,26 +3969,26 @@
         </is>
       </c>
       <c r="C61" s="22" t="n">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="D61" s="22" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="E61" s="22" t="n">
-        <v>2501.1</v>
+        <v>3455.3</v>
       </c>
       <c r="F61" s="22" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="G61" s="22" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="H61" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 570 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J61" s="21" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
     <row r="62">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>RIFAXIMINA 200 MG CP</t>
+          <t>CLOPIDOGREL 75 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
@@ -4005,26 +4005,26 @@
         </is>
       </c>
       <c r="C62" s="22" t="n">
-        <v>506</v>
+        <v>636</v>
       </c>
       <c r="D62" s="22" t="n">
         <v>1.5</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>1675.2</v>
+        <v>2501.1</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>216</v>
+        <v>1000</v>
       </c>
       <c r="G62" s="22" t="n">
-        <v>216</v>
+        <v>1000</v>
       </c>
       <c r="H62" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 216 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1000 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J62" s="21" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
     <row r="63">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
+          <t>RIFAXIMINA 200 MG CP</t>
         </is>
       </c>
       <c r="B63" s="21" t="inlineStr">
@@ -4041,26 +4041,26 @@
         </is>
       </c>
       <c r="C63" s="22" t="n">
-        <v>540</v>
+        <v>506</v>
       </c>
       <c r="D63" s="22" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="E63" s="22" t="n">
-        <v>1522.5</v>
+        <v>1675.2</v>
       </c>
       <c r="F63" s="22" t="n">
-        <v>66</v>
+        <v>216</v>
       </c>
       <c r="G63" s="22" t="n">
-        <v>66</v>
+        <v>216</v>
       </c>
       <c r="H63" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 66 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 216 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J63" s="21" t="inlineStr"/>
@@ -4068,7 +4068,7 @@
     <row r="64">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>METILDOPA 250 MG COMPRIMIDO</t>
+          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
         </is>
       </c>
       <c r="B64" s="21" t="inlineStr">
@@ -4077,26 +4077,26 @@
         </is>
       </c>
       <c r="C64" s="22" t="n">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="D64" s="22" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>1883.7</v>
+        <v>1522.5</v>
       </c>
       <c r="F64" s="22" t="n">
-        <v>300</v>
+        <v>66</v>
       </c>
       <c r="G64" s="22" t="n">
-        <v>300</v>
+        <v>66</v>
       </c>
       <c r="H64" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 300 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 66 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J64" s="21" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
     <row r="65">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>LAMOTRIGINA 100 MG COMPRIMIDO</t>
+          <t>METILDOPA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B65" s="21" t="inlineStr">
@@ -4113,26 +4113,26 @@
         </is>
       </c>
       <c r="C65" s="22" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="D65" s="22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E65" s="22" t="n">
-        <v>803.3</v>
+        <v>1883.7</v>
       </c>
       <c r="F65" s="22" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G65" s="22" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="H65" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 360 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 300 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J65" s="21" t="inlineStr"/>
@@ -4140,7 +4140,7 @@
     <row r="66">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>BICARBONATO DE SODIO CP. 500 M</t>
+          <t>LAMOTRIGINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
@@ -4149,38 +4149,34 @@
         </is>
       </c>
       <c r="C66" s="22" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="D66" s="22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="E66" s="22" t="n">
-        <v>718.4</v>
+        <v>803.3</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>114</v>
+        <v>360</v>
       </c>
       <c r="G66" s="22" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="I66" s="21" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J66" s="21" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 114 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 360 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J66" s="21" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>NAPROXENO 550 MG COMPRIMIDO</t>
+          <t>BICARBONATO DE SODIO CP. 500 M</t>
         </is>
       </c>
       <c r="B67" s="21" t="inlineStr">
@@ -4189,22 +4185,22 @@
         </is>
       </c>
       <c r="C67" s="22" t="n">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="D67" s="22" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="E67" s="22" t="n">
-        <v>384.7</v>
+        <v>718.4</v>
       </c>
       <c r="F67" s="22" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G67" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
@@ -4213,14 +4209,14 @@
       </c>
       <c r="J67" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 110 ud.</t>
+          <t>GESTIONAR EXTERNO 114 ud.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>PRAMIPEXOL 1 MG COMPRIMIDO</t>
+          <t>NAPROXENO 550 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B68" s="21" t="inlineStr">
@@ -4229,34 +4225,38 @@
         </is>
       </c>
       <c r="C68" s="22" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D68" s="22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>26.1</v>
+        <v>384.7</v>
       </c>
       <c r="F68" s="22" t="n">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="G68" s="22" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="I68" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 27 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J68" s="21" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J68" s="21" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 110 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>PRAMIPEXOL 1 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B69" s="21" t="inlineStr">
@@ -4265,38 +4265,34 @@
         </is>
       </c>
       <c r="C69" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D69" s="22" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E69" s="22" t="n">
-        <v>28</v>
+        <v>26.1</v>
       </c>
       <c r="F69" s="22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G69" s="22" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H69" s="22" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I69" s="21" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J69" s="21" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 25 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 27 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J69" s="21" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
@@ -4305,22 +4301,22 @@
         </is>
       </c>
       <c r="C70" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D70" s="22" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>20.4</v>
+        <v>28</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="G70" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I70" s="21" t="inlineStr">
         <is>
@@ -4329,14 +4325,14 @@
       </c>
       <c r="J70" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 7 ud.</t>
+          <t>GESTIONAR EXTERNO 25 ud.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="21" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B71" s="21" t="inlineStr">
@@ -4345,22 +4341,22 @@
         </is>
       </c>
       <c r="C71" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D71" s="22" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>16.4</v>
+        <v>20.4</v>
       </c>
       <c r="F71" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G71" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
@@ -4369,14 +4365,14 @@
       </c>
       <c r="J71" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 6 ud.</t>
+          <t>GESTIONAR EXTERNO 7 ud.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B72" s="21" t="inlineStr">
@@ -4385,38 +4381,38 @@
         </is>
       </c>
       <c r="C72" s="22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D72" s="22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E72" s="22" t="n">
-        <v>6.3</v>
+        <v>16.4</v>
       </c>
       <c r="F72" s="22" t="n">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="G72" s="22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H72" s="22" t="n">
-        <v>485</v>
+        <v>6</v>
       </c>
       <c r="I72" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 15 ud. DESDE BODEGA AA</t>
+          <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
       <c r="J72" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 485 ud.</t>
+          <t>GESTIONAR EXTERNO 6 ud.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+          <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
         </is>
       </c>
       <c r="B73" s="21" t="inlineStr">
@@ -4425,110 +4421,114 @@
         </is>
       </c>
       <c r="C73" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D73" s="22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E73" s="22" t="n">
-        <v>4.3</v>
+        <v>6.3</v>
       </c>
       <c r="F73" s="22" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="G73" s="22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H73" s="22" t="n">
-        <v>3</v>
+        <v>485</v>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
+          <t>TRASPASAR 15 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J73" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3 ud.</t>
+          <t>GESTIONAR EXTERNO 485 ud.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="21" t="inlineStr">
         <is>
+          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+        </is>
+      </c>
+      <c r="B74" s="21" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C74" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E74" s="22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F74" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I74" s="21" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J74" s="21" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 3 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
           <t>SALMETEROL 25 MCG/DOSIS AEROSOL PARA INHALACION</t>
         </is>
       </c>
-      <c r="B74" s="21" t="inlineStr">
+      <c r="B75" s="21" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C74" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="22" t="n">
+      <c r="C75" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="22" t="n">
         <v>3.4</v>
       </c>
-      <c r="F74" s="22" t="n">
+      <c r="F75" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="G74" s="22" t="n">
+      <c r="G75" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="H74" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="21" t="inlineStr">
+      <c r="H75" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="21" t="inlineStr">
         <is>
           <t>TRASPASAR 4 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="J74" s="21" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>OMEPRAZOL 20 MG CAPSULA</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>3790</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>11380.4</v>
-      </c>
-      <c r="F75" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="G75" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="H75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>TRASPASAR 250 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr"/>
+      <c r="J75" s="21" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>DABIGATRAN ETEXILATO CP 150 MG</t>
+          <t>OMEPRAZOL 20 MG CAPSULA</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4537,26 +4537,26 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>2319</v>
+        <v>3790</v>
       </c>
       <c r="D76" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>6899.2</v>
+        <v>11380.4</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="H76" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 77 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 250 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr"/>
@@ -4564,7 +4564,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>LEFLUNOMIDA 20 MG COMPRIMIDO</t>
+          <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4573,26 +4573,26 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>656</v>
+        <v>1809</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>1935.1</v>
+        <v>4821.4</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H77" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 20 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr"/>
@@ -4600,7 +4600,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>TRAMADOL CP 50 MG</t>
+          <t>LEFLUNOMIDA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4609,26 +4609,26 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>634</v>
+        <v>656</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1813.2</v>
+        <v>1935.1</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H78" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr"/>
@@ -4636,7 +4636,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>GABAPENTINA 300 MG CAPSULA</t>
+          <t>TRAMADOL CP 50 MG</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4645,26 +4645,26 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1649.2</v>
+        <v>1813.2</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H79" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 100 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr"/>
@@ -4672,7 +4672,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>CLORURO DE POTASIO 600 MG (POTASIO 8 MEQ) COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>GABAPENTINA 300 MG CAPSULA</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4681,26 +4681,26 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>67</v>
+        <v>642</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>176.8</v>
+        <v>1649.2</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="H80" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 110 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr"/>
@@ -4708,7 +4708,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO CP 300 MG</t>
+          <t>CLORURO DE POTASIO 600 MG (POTASIO 8 MEQ) COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4717,38 +4717,34 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>111.3</v>
+        <v>176.8</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 59 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 110 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>GEMFIBROZILO CP 300 MG</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4757,34 +4753,38 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>122.5</v>
+        <v>111.3</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 45 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J82" s="3" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 59 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>MICOFENOLATO MOFETILO 250 MG CAPSULA</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4793,38 +4793,34 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>183.7</v>
+        <v>122.5</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 94 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 46 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>MOMETASONA 50 MCG/DOSIS SUSPENSION NASAL</t>
+          <t>MICOFENOLATO MOFETILO 250 MG CAPSULA</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4833,34 +4829,38 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>112.2</v>
+        <v>183.7</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 47 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J84" s="3" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 94 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>MOMETASONA 50 MCG/DOSIS SUSPENSION NASAL</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4869,26 +4869,26 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>95.40000000000001</v>
+        <v>112.2</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="H85" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 24 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 47 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr"/>
@@ -4896,7 +4896,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4905,38 +4905,34 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>57.9</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 21 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 25 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
+          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4945,34 +4941,38 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>54.5</v>
+        <v>57.9</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 26 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 21 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>TRAMADOL FRASCO GOTAS 100 MG/ML /10 ML</t>
+          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4981,26 +4981,26 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>38.4</v>
+        <v>54.5</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H88" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 8 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 26 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr"/>
@@ -5008,7 +5008,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>SALMETEROL /FLUTICASONA 250 MG/25 MG INH UD</t>
+          <t>TRAMADOL FRASCO GOTAS 100 MG/ML /10 ML</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5017,26 +5017,26 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>46.3</v>
+        <v>38.4</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H89" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 18 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 8 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr"/>
@@ -5044,7 +5044,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>KETOCONAZOL 2% SHAMPOO 100 ML</t>
+          <t>SALMETEROL /FLUTICASONA 250 MG/25 MG INH UD</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -5053,26 +5053,26 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>13.7</v>
+        <v>46.3</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H90" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 6 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 18 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr"/>
@@ -5080,7 +5080,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>KETOCONAZOL 2% SHAMPOO 100 ML</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -5089,38 +5089,34 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>13.7</v>
       </c>
       <c r="F91" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 6 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 6 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>MEDROXIPROGESTERONA 104 MG/0,65 ML (160 MG/ML) INYECTABLE</t>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -5129,34 +5125,38 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>2.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J92" s="3" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 6 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
+          <t>MEDROXIPROGESTERONA 104 MG/0,65 ML (160 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -5165,38 +5165,34 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F93" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D93" s="4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E93" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F93" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="G93" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 3 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
+          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -5208,19 +5204,19 @@
         <v>1</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
@@ -5229,14 +5225,14 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2 ud.</t>
+          <t>GESTIONAR EXTERNO 3 ud.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10 MG/2 ML (5 MG/ML) INYECTABLE</t>
+          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -5248,71 +5244,75 @@
         <v>1</v>
       </c>
       <c r="D95" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 2 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>METOCLOPRAMIDA 10 MG/2 ML (5 MG/ML) INYECTABLE</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" s="4" t="n">
         <v>4.4</v>
       </c>
-      <c r="E95" s="4" t="n">
+      <c r="E96" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F96" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="4" t="n">
+      <c r="G96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="I95" s="3" t="inlineStr">
+      <c r="I96" s="3" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
-      <c r="J95" s="3" t="inlineStr">
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 24 ud.</t>
         </is>
       </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>LATANOPROST 0,005% COLIRIO</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>4-BAJO</t>
-        </is>
-      </c>
-      <c r="C96" s="10" t="n">
-        <v>136</v>
-      </c>
-      <c r="D96" s="10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>142.3</v>
-      </c>
-      <c r="F96" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="G96" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H96" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J96" s="9" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
+          <t>LATANOPROST 0,005% COLIRIO</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -5321,38 +5321,34 @@
         </is>
       </c>
       <c r="C97" s="10" t="n">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="D97" s="10" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>106.4</v>
+        <v>142.3</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G97" s="10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H97" s="10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 18 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>DORZOLAMIDA + TIMOLOL 2G/0,5G/100 ML SOL. OFT. FC 5 ML</t>
+          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -5361,34 +5357,38 @@
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>67.8</v>
+        <v>106.4</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H98" s="10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J98" s="9" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 18 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>VITAMINA D3 50.000 UI SOBRE</t>
+          <t>DORZOLAMIDA + TIMOLOL 2G/0,5G/100 ML SOL. OFT. FC 5 ML</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -5397,26 +5397,26 @@
         </is>
       </c>
       <c r="C99" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D99" s="10" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>61.5</v>
+        <v>67.8</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G99" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H99" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 8 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J99" s="9" t="inlineStr"/>
@@ -5424,7 +5424,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>TICAGRELOR 90 MG COMPRIMIDO</t>
+          <t>VITAMINA D3 50.000 UI SOBRE</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -5433,38 +5433,34 @@
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>55.2</v>
+        <v>61.5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G100" s="10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H100" s="10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J100" s="9" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 26 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>TICAGRELOR 90 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -5473,38 +5469,38 @@
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D101" s="10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>25.2</v>
+        <v>55.2</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="G101" s="10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H101" s="10" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR 20 ud. DESDE BODEGA AA</t>
+          <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 80 ud.</t>
+          <t>GESTIONAR EXTERNO 26 ud.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>TIMOLOL 0,5% (5 MG/ML) COLIRIO</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -5513,34 +5509,38 @@
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>25.9</v>
+        <v>25.2</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H102" s="10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR 5 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J102" s="9" t="inlineStr"/>
+          <t>TRASPASAR 20 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 80 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>BRIMONIDINA 0,2% (2 MG/ML) COLIRIO</t>
+          <t>TIMOLOL 0,5% (5 MG/ML) COLIRIO</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -5549,26 +5549,26 @@
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D103" s="10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>18.4</v>
+        <v>25.9</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G103" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H103" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR 3 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 5 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J103" s="9" t="inlineStr"/>
@@ -5576,7 +5576,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>LEVONORGESTREL + ETINILESTRADIOL 0.15 MG / 0.03MG X 28 COMPRIMIDOS.</t>
+          <t>BRIMONIDINA 0,2% (2 MG/ML) COLIRIO</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -5585,26 +5585,26 @@
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>9.1</v>
+        <v>5.9</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>8.1</v>
+        <v>18.4</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G104" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H104" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 3 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J104" s="9" t="inlineStr"/>
@@ -5612,76 +5612,112 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
+          <t>LEVONORGESTREL + ETINILESTRADIOL 0.15 MG / 0.03MG X 28 COMPRIMIDOS.</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>4-BAJO</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D105" s="10" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F105" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
           <t>LEVONORGESTREL 0,03 MG CICLO 28 O 35 CM</t>
         </is>
       </c>
-      <c r="B105" s="9" t="inlineStr">
+      <c r="B106" s="9" t="inlineStr">
         <is>
           <t>4-BAJO</t>
         </is>
       </c>
-      <c r="C105" s="10" t="n">
+      <c r="C106" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D105" s="10" t="n">
+      <c r="D106" s="10" t="n">
         <v>6.6</v>
       </c>
-      <c r="E105" s="10" t="n">
+      <c r="E106" s="10" t="n">
         <v>6.7</v>
       </c>
-      <c r="F105" s="10" t="n">
+      <c r="F106" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="G105" s="10" t="n">
+      <c r="G106" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="H105" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="9" t="inlineStr">
+      <c r="H106" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
         <is>
           <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="J105" s="9" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="11" t="inlineStr">
+      <c r="J106" s="9" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="12" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="13" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="14" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="14" t="inlineStr">
         <is>
           <t>ALTO / MODERADO  —  reponer pronto</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="15" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="15" t="inlineStr">
         <is>
           <t>BAJO  —  vigilar</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="16" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="16" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -5698,7 +5734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5824,7 +5860,7 @@
         <v>13249.7</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>8940</v>
+        <v>8970</v>
       </c>
       <c r="G4" s="20" t="n">
         <v>0</v>
@@ -5836,7 +5872,7 @@
       </c>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 8940 ud.</t>
+          <t>COMPRA EXTERNA 8970 ud.</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6389,7 @@
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>BACLOFENO 10 MG COMPRIMIDO</t>
+          <t>PROPANOLOL 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
@@ -6368,29 +6404,25 @@
         <v>0</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>1347.4</v>
+        <v>1306.5</v>
       </c>
       <c r="F19" s="20" t="n">
-        <v>1000</v>
+        <v>51</v>
       </c>
       <c r="G19" s="20" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="H19" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1000 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 51 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>BETAHISTINA 16 MG COMPRIMIDO</t>
+          <t>BACLOFENO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
@@ -6405,25 +6437,29 @@
         <v>0</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>736.8</v>
+        <v>1347.4</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>336</v>
+        <v>1000</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>4892</v>
+        <v>0</v>
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 336 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1000 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>NAPROXENO 550 MG COMPRIMIDO</t>
+          <t>BETAHISTINA 16 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
@@ -6438,29 +6474,25 @@
         <v>0</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>747.3</v>
+        <v>736.8</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>720</v>
+        <v>336</v>
       </c>
       <c r="G21" s="20" t="n">
-        <v>0</v>
+        <v>4892</v>
       </c>
       <c r="H21" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 720 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 336 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I21" s="19" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>COLCHICINA 0,5 MG COMPRIMIDO</t>
+          <t>NAPROXENO 550 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
@@ -6475,10 +6507,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="20" t="n">
-        <v>716</v>
+        <v>747.3</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="G22" s="20" t="n">
         <v>0</v>
@@ -6490,14 +6522,14 @@
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 716 ud.</t>
+          <t>COMPRA EXTERNA 720 ud.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>MICOFENOLATO 500 MG CR</t>
+          <t>COLCHICINA 0,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
@@ -6512,10 +6544,10 @@
         <v>0</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>580.8</v>
+        <v>716</v>
       </c>
       <c r="F23" s="20" t="n">
-        <v>581</v>
+        <v>716</v>
       </c>
       <c r="G23" s="20" t="n">
         <v>0</v>
@@ -6527,14 +6559,14 @@
       </c>
       <c r="I23" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 581 ud.</t>
+          <t>COMPRA EXTERNA 716 ud.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>DONEPEZILO 10 MG COMPRIMIDO</t>
+          <t>MICOFENOLATO 500 MG CR</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
@@ -6549,25 +6581,29 @@
         <v>0</v>
       </c>
       <c r="E24" s="20" t="n">
-        <v>763.4</v>
+        <v>580.8</v>
       </c>
       <c r="F24" s="20" t="n">
-        <v>300</v>
+        <v>581</v>
       </c>
       <c r="G24" s="20" t="n">
-        <v>2190</v>
+        <v>0</v>
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 300 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I24" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 581 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>DONEPEZILO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
@@ -6582,29 +6618,25 @@
         <v>0</v>
       </c>
       <c r="E25" s="20" t="n">
-        <v>750.8</v>
+        <v>763.4</v>
       </c>
       <c r="F25" s="20" t="n">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="G25" s="20" t="n">
-        <v>65</v>
+        <v>2190</v>
       </c>
       <c r="H25" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 65 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I25" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 228 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 300 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I25" s="19" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
+          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
@@ -6619,29 +6651,29 @@
         <v>0</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>726.8</v>
+        <v>750.8</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>750</v>
+        <v>293</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 600 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 65 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 150 ud.</t>
+          <t>COMPRA EXTERNA 228 ud.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
@@ -6656,29 +6688,29 @@
         <v>0</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>598.2</v>
+        <v>726.8</v>
       </c>
       <c r="F27" s="20" t="n">
-        <v>157</v>
+        <v>750</v>
       </c>
       <c r="G27" s="20" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H27" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
+          <t>TRASPASAR 600 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I27" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 157 ud.</t>
+          <t>COMPRA EXTERNA 150 ud.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>ACIDO FOLICO CM 1 MG</t>
+          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
@@ -6693,25 +6725,29 @@
         <v>0</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>381.8</v>
+        <v>598.2</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>1000</v>
+        <v>157</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>13640</v>
+        <v>0</v>
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I28" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 157 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>MULTIVITAMINICO COMPRIMIDO</t>
+          <t>ACIDO FOLICO CM 1 MG</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
@@ -6726,29 +6762,25 @@
         <v>0</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>686.1</v>
+        <v>381.8</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>687</v>
+        <v>1000</v>
       </c>
       <c r="G29" s="20" t="n">
-        <v>0</v>
+        <v>13640</v>
       </c>
       <c r="H29" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 687 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I29" s="19" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>MULTIVITAMINICO COMPRIMIDO</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
@@ -6763,10 +6795,10 @@
         <v>0</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>542.9</v>
+        <v>686.1</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>543</v>
+        <v>687</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>0</v>
@@ -6778,14 +6810,14 @@
       </c>
       <c r="I30" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 543 ud.</t>
+          <t>COMPRA EXTERNA 687 ud.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>MEMANTINA 10 MG COMPRIMIDO</t>
+          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
@@ -6800,10 +6832,10 @@
         <v>0</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>400.2</v>
+        <v>542.9</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>11</v>
+        <v>543</v>
       </c>
       <c r="G31" s="20" t="n">
         <v>0</v>
@@ -6815,14 +6847,14 @@
       </c>
       <c r="I31" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 11 ud.</t>
+          <t>COMPRA EXTERNA 543 ud.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>TRIMETAZIDINA 35 MG CM LIBERACION PROLONGADA (XR)</t>
+          <t>MEMANTINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
@@ -6837,25 +6869,29 @@
         <v>0</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>622</v>
+        <v>400.2</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 112 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I32" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I32" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 11 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>ATENOLOL 50 MG COMPRIMIDO</t>
+          <t>TRIMETAZIDINA 35 MG CM LIBERACION PROLONGADA (XR)</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
@@ -6870,17 +6906,17 @@
         <v>0</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>294.1</v>
+        <v>622</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
       <c r="H33" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 69 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 112 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I33" s="19" t="inlineStr"/>
@@ -6888,7 +6924,7 @@
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO CP 300 MG</t>
+          <t>ATENOLOL 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
@@ -6903,29 +6939,25 @@
         <v>0</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>163.4</v>
+        <v>294.1</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H34" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I34" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 111 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 69 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I34" s="19" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>ACETAZOLAMIDA CM 250 MG</t>
+          <t>GEMFIBROZILO CP 300 MG</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
@@ -6940,25 +6972,29 @@
         <v>0</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>394.8</v>
+        <v>163.4</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>2180</v>
+        <v>0</v>
       </c>
       <c r="H35" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I35" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 111 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>MICOFENOLATO MOFETILO 250 MG CAPSULA</t>
+          <t>ACETAZOLAMIDA CM 250 MG</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
@@ -6973,29 +7009,25 @@
         <v>0</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>338.6</v>
+        <v>394.8</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>249</v>
+        <v>100</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>0</v>
+        <v>2180</v>
       </c>
       <c r="H36" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I36" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 249 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I36" s="19" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
+          <t>MICOFENOLATO MOFETILO 250 MG CAPSULA</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
@@ -7010,10 +7042,10 @@
         <v>0</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>170.6</v>
+        <v>338.6</v>
       </c>
       <c r="F37" s="20" t="n">
-        <v>74</v>
+        <v>249</v>
       </c>
       <c r="G37" s="20" t="n">
         <v>0</v>
@@ -7025,14 +7057,14 @@
       </c>
       <c r="I37" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 74 ud.</t>
+          <t>COMPRA EXTERNA 249 ud.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
+          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
@@ -7047,10 +7079,10 @@
         <v>0</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>202.4</v>
+        <v>170.6</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>0</v>
@@ -7062,14 +7094,14 @@
       </c>
       <c r="I38" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 114 ud.</t>
+          <t>COMPRA EXTERNA 74 ud.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>HIDROXICARBAMIDA 500 MG CAPSULA</t>
+          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
@@ -7084,25 +7116,29 @@
         <v>0</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>140.5</v>
+        <v>202.4</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="G39" s="20" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="H39" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 44 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I39" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I39" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 114 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>ACIDO ALENDRONICO CM 70 MG</t>
+          <t>HIDROXICARBAMIDA 500 MG CAPSULA</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
@@ -7117,29 +7153,25 @@
         <v>0</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>135.5</v>
+        <v>140.5</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H40" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I40" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 21 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 44 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I40" s="19" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>MODAFINILO 200 MG COMPRIMIDO</t>
+          <t>ACIDO ALENDRONICO CM 70 MG</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
@@ -7154,25 +7186,29 @@
         <v>0</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>218</v>
+        <v>135.5</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="G41" s="20" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H41" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 78 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I41" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I41" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 21 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
+          <t>MODAFINILO 200 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
@@ -7187,29 +7223,25 @@
         <v>0</v>
       </c>
       <c r="E42" s="20" t="n">
-        <v>110.3</v>
+        <v>218</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H42" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I42" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 74 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 78 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I42" s="19" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
@@ -7224,25 +7256,29 @@
         <v>0</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>72.90000000000001</v>
+        <v>110.3</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G43" s="20" t="n">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="H43" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I43" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 74 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
@@ -7257,29 +7293,25 @@
         <v>0</v>
       </c>
       <c r="E44" s="20" t="n">
-        <v>110.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="H44" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I44" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 111 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I44" s="19" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B45" s="19" t="inlineStr">
@@ -7294,25 +7326,29 @@
         <v>0</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>70.7</v>
+        <v>110.2</v>
       </c>
       <c r="F45" s="20" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G45" s="20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H45" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I45" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I45" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 111 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>VIGABATRINA 500 MG COMPRIMIDO</t>
+          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
@@ -7327,17 +7363,17 @@
         <v>0</v>
       </c>
       <c r="E46" s="20" t="n">
-        <v>94.3</v>
+        <v>70.7</v>
       </c>
       <c r="F46" s="20" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="H46" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I46" s="19" t="inlineStr"/>
@@ -7345,7 +7381,7 @@
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>UREA 10% CREMA 20 GR</t>
+          <t>VIGABATRINA 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B47" s="19" t="inlineStr">
@@ -7360,29 +7396,25 @@
         <v>0</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>72.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="F47" s="20" t="n">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="G47" s="20" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="H47" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I47" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 73 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I47" s="19" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>UREA 10% CREMA 20 GR</t>
         </is>
       </c>
       <c r="B48" s="19" t="inlineStr">
@@ -7397,25 +7429,29 @@
         <v>0</v>
       </c>
       <c r="E48" s="20" t="n">
-        <v>58.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H48" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 56 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I48" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I48" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 73 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>TICAGRELOR 90 MG COMPRIMIDO</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B49" s="19" t="inlineStr">
@@ -7430,29 +7466,25 @@
         <v>0</v>
       </c>
       <c r="E49" s="20" t="n">
-        <v>103.4</v>
+        <v>58.2</v>
       </c>
       <c r="F49" s="20" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="G49" s="20" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H49" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I49" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 74 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 56 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I49" s="19" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>OXCARBAZEPINA 600 MG COMPRIMIDO</t>
+          <t>TICAGRELOR 90 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
@@ -7467,10 +7499,10 @@
         <v>0</v>
       </c>
       <c r="E50" s="20" t="n">
-        <v>42.5</v>
+        <v>103.4</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="G50" s="20" t="n">
         <v>0</v>
@@ -7482,14 +7514,14 @@
       </c>
       <c r="I50" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 43 ud.</t>
+          <t>COMPRA EXTERNA 74 ud.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>VERAPAMILO 80 MG CAPSULA</t>
+          <t>OXCARBAZEPINA 600 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B51" s="19" t="inlineStr">
@@ -7504,10 +7536,10 @@
         <v>0</v>
       </c>
       <c r="E51" s="20" t="n">
-        <v>83.3</v>
+        <v>42.5</v>
       </c>
       <c r="F51" s="20" t="n">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="G51" s="20" t="n">
         <v>0</v>
@@ -7519,14 +7551,14 @@
       </c>
       <c r="I51" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 84 ud.</t>
+          <t>COMPRA EXTERNA 43 ud.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>VERAPAMILO 80 MG CAPSULA</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
@@ -7541,29 +7573,29 @@
         <v>0</v>
       </c>
       <c r="E52" s="20" t="n">
-        <v>47.4</v>
+        <v>83.3</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="G52" s="20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H52" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 40 ud. DESDE BODEGA FARMACOS</t>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I52" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 60 ud.</t>
+          <t>COMPRA EXTERNA 84 ud.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>MORFINA 30 MG CAPSULA LIBERACION MODIFICADA</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B53" s="19" t="inlineStr">
@@ -7578,29 +7610,29 @@
         <v>0</v>
       </c>
       <c r="E53" s="20" t="n">
-        <v>56.3</v>
+        <v>47.4</v>
       </c>
       <c r="F53" s="20" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="G53" s="20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H53" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
+          <t>TRASPASAR 40 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I53" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 57 ud.</t>
+          <t>COMPRA EXTERNA 60 ud.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>MORFINA 30 MG CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
@@ -7615,25 +7647,29 @@
         <v>0</v>
       </c>
       <c r="E54" s="20" t="n">
-        <v>37.9</v>
+        <v>56.3</v>
       </c>
       <c r="F54" s="20" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G54" s="20" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="H54" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 34 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I54" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I54" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 57 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>ACIDO URSODESOXICOLICO CM 500 MG</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B55" s="19" t="inlineStr">
@@ -7648,29 +7684,25 @@
         <v>0</v>
       </c>
       <c r="E55" s="20" t="n">
-        <v>13.8</v>
+        <v>37.9</v>
       </c>
       <c r="F55" s="20" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G55" s="20" t="n">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="H55" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I55" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 14 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 34 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I55" s="19" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>ACIDO URSODESOXICOLICO CM 500 MG</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
@@ -7685,25 +7717,29 @@
         <v>0</v>
       </c>
       <c r="E56" s="20" t="n">
-        <v>33.2</v>
+        <v>13.8</v>
       </c>
       <c r="F56" s="20" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G56" s="20" t="n">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="H56" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 29 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I56" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I56" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 14 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
         <is>
-          <t>VASELINA SOLIDA UNGUENTO</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B57" s="19" t="inlineStr">
@@ -7718,29 +7754,25 @@
         <v>0</v>
       </c>
       <c r="E57" s="20" t="n">
-        <v>23.2</v>
+        <v>33.2</v>
       </c>
       <c r="F57" s="20" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G57" s="20" t="n">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="H57" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I57" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 24 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 29 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I57" s="19" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>INSULINA CRISTALINA 100 UI/ML FC 10 ML</t>
+          <t>VASELINA SOLIDA UNGUENTO</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
@@ -7755,25 +7787,29 @@
         <v>0</v>
       </c>
       <c r="E58" s="20" t="n">
-        <v>34.8</v>
+        <v>23.2</v>
       </c>
       <c r="F58" s="20" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G58" s="20" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H58" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 7 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I58" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I58" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 24 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="19" t="inlineStr">
         <is>
-          <t>FENTANILO 25 MCG/HORA PARCHE</t>
+          <t>INSULINA CRISTALINA 100 UI/ML FC 10 ML</t>
         </is>
       </c>
       <c r="B59" s="19" t="inlineStr">
@@ -7788,29 +7824,25 @@
         <v>0</v>
       </c>
       <c r="E59" s="20" t="n">
-        <v>33.9</v>
+        <v>34.8</v>
       </c>
       <c r="F59" s="20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G59" s="20" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H59" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I59" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 10 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 7 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I59" s="19" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="19" t="inlineStr">
         <is>
-          <t>RISPERIDONA 25 MG FA</t>
+          <t>FENTANILO 25 MCG/HORA PARCHE</t>
         </is>
       </c>
       <c r="B60" s="19" t="inlineStr">
@@ -7825,10 +7857,10 @@
         <v>0</v>
       </c>
       <c r="E60" s="20" t="n">
-        <v>16</v>
+        <v>33.9</v>
       </c>
       <c r="F60" s="20" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G60" s="20" t="n">
         <v>0</v>
@@ -7840,14 +7872,14 @@
       </c>
       <c r="I60" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 16 ud.</t>
+          <t>COMPRA EXTERNA 10 ud.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>ACIDO FOLICO 0,4 MG CM</t>
+          <t>RISPERIDONA 25 MG FA</t>
         </is>
       </c>
       <c r="B61" s="19" t="inlineStr">
@@ -7862,10 +7894,10 @@
         <v>0</v>
       </c>
       <c r="E61" s="20" t="n">
-        <v>6.3</v>
+        <v>16</v>
       </c>
       <c r="F61" s="20" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G61" s="20" t="n">
         <v>0</v>
@@ -7877,14 +7909,14 @@
       </c>
       <c r="I61" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 7 ud.</t>
+          <t>COMPRA EXTERNA 16 ud.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>ACIDO FOLICO 0,4 MG CM</t>
         </is>
       </c>
       <c r="B62" s="19" t="inlineStr">
@@ -7899,25 +7931,29 @@
         <v>0</v>
       </c>
       <c r="E62" s="20" t="n">
-        <v>19</v>
+        <v>6.3</v>
       </c>
       <c r="F62" s="20" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G62" s="20" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="H62" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I62" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I62" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 7 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B63" s="19" t="inlineStr">
@@ -7932,29 +7968,25 @@
         <v>0</v>
       </c>
       <c r="E63" s="20" t="n">
-        <v>16.4</v>
+        <v>19</v>
       </c>
       <c r="F63" s="20" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G63" s="20" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H63" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I63" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 15 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I63" s="19" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="19" t="inlineStr">
         <is>
-          <t>MONTELUKAST 4 MG COMPRIMIDO</t>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
         </is>
       </c>
       <c r="B64" s="19" t="inlineStr">
@@ -7969,25 +8001,29 @@
         <v>0</v>
       </c>
       <c r="E64" s="20" t="n">
-        <v>23.5</v>
+        <v>16.4</v>
       </c>
       <c r="F64" s="20" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G64" s="20" t="n">
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="H64" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 4 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I64" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I64" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 15 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
+          <t>MONTELUKAST 4 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
@@ -8002,29 +8038,25 @@
         <v>0</v>
       </c>
       <c r="E65" s="20" t="n">
-        <v>13.5</v>
+        <v>23.5</v>
       </c>
       <c r="F65" s="20" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G65" s="20" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="H65" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I65" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 14 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 4 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I65" s="19" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>MORFINA 10 MG/ML INYECTABLE</t>
+          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
         </is>
       </c>
       <c r="B66" s="19" t="inlineStr">
@@ -8039,10 +8071,10 @@
         <v>0</v>
       </c>
       <c r="E66" s="20" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="F66" s="20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G66" s="20" t="n">
         <v>0</v>
@@ -8054,14 +8086,14 @@
       </c>
       <c r="I66" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 11 ud.</t>
+          <t>COMPRA EXTERNA 14 ud.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="19" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+          <t>MORFINA 10 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B67" s="19" t="inlineStr">
@@ -8076,10 +8108,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="20" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="F67" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G67" s="20" t="n">
         <v>0</v>
@@ -8091,14 +8123,14 @@
       </c>
       <c r="I67" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 8 ud.</t>
+          <t>COMPRA EXTERNA 11 ud.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 150 MG/ML JER.PC UNIDAD</t>
+          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
@@ -8113,10 +8145,10 @@
         <v>0</v>
       </c>
       <c r="E68" s="20" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="F68" s="20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G68" s="20" t="n">
         <v>0</v>
@@ -8128,14 +8160,14 @@
       </c>
       <c r="I68" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 10 ud.</t>
+          <t>COMPRA EXTERNA 8 ud.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
+          <t>PALIPERIDONA 150 MG/ML JER.PC UNIDAD</t>
         </is>
       </c>
       <c r="B69" s="19" t="inlineStr">
@@ -8150,10 +8182,10 @@
         <v>0</v>
       </c>
       <c r="E69" s="20" t="n">
-        <v>4.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F69" s="20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G69" s="20" t="n">
         <v>0</v>
@@ -8165,14 +8197,14 @@
       </c>
       <c r="I69" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 5 ud.</t>
+          <t>COMPRA EXTERNA 10 ud.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="19" t="inlineStr">
         <is>
-          <t>MIDAZOLAM AMP 5 MG/ML</t>
+          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
         </is>
       </c>
       <c r="B70" s="19" t="inlineStr">
@@ -8187,10 +8219,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="20" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="F70" s="20" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G70" s="20" t="n">
         <v>0</v>
@@ -8202,14 +8234,14 @@
       </c>
       <c r="I70" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 100 ud.</t>
+          <t>COMPRA EXTERNA 5 ud.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="19" t="inlineStr">
         <is>
-          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
+          <t>MIDAZOLAM AMP 5 MG/ML</t>
         </is>
       </c>
       <c r="B71" s="19" t="inlineStr">
@@ -8224,10 +8256,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="F71" s="20" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="G71" s="20" t="n">
         <v>0</v>
@@ -8239,14 +8271,14 @@
       </c>
       <c r="I71" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 6 ud.</t>
+          <t>COMPRA EXTERNA 100 ud.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="19" t="inlineStr">
         <is>
-          <t>RIVAROXABAN 20 MG</t>
+          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B72" s="19" t="inlineStr">
@@ -8261,10 +8293,10 @@
         <v>0</v>
       </c>
       <c r="E72" s="20" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="F72" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G72" s="20" t="n">
         <v>0</v>
@@ -8276,14 +8308,14 @@
       </c>
       <c r="I72" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 4 ud.</t>
+          <t>COMPRA EXTERNA 6 ud.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="19" t="inlineStr">
         <is>
-          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
+          <t>RIVAROXABAN 20 MG</t>
         </is>
       </c>
       <c r="B73" s="19" t="inlineStr">
@@ -8298,10 +8330,10 @@
         <v>0</v>
       </c>
       <c r="E73" s="20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F73" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" s="20" t="n">
         <v>0</v>
@@ -8313,14 +8345,14 @@
       </c>
       <c r="I73" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3 ud.</t>
+          <t>COMPRA EXTERNA 4 ud.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="19" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10 MG/2 ML (5 MG/ML) INYECTABLE</t>
+          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
         </is>
       </c>
       <c r="B74" s="19" t="inlineStr">
@@ -8335,25 +8367,29 @@
         <v>0</v>
       </c>
       <c r="E74" s="20" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="F74" s="20" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G74" s="20" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="H74" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 24 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I74" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I74" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 3 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="19" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 75 MG JER.PC</t>
+          <t>METOCLOPRAMIDA 10 MG/2 ML (5 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B75" s="19" t="inlineStr">
@@ -8368,29 +8404,25 @@
         <v>0</v>
       </c>
       <c r="E75" s="20" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F75" s="20" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G75" s="20" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="H75" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I75" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 24 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I75" s="19" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="19" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>PALIPERIDONA 75 MG JER.PC</t>
         </is>
       </c>
       <c r="B76" s="19" t="inlineStr">
@@ -8405,25 +8437,29 @@
         <v>0</v>
       </c>
       <c r="E76" s="20" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="F76" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G76" s="20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H76" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 3 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I76" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I76" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="19" t="inlineStr">
         <is>
-          <t>ACIDO VALPROICO 250 MG/5 ML FC 120 ML</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B77" s="19" t="inlineStr">
@@ -8438,29 +8474,25 @@
         <v>0</v>
       </c>
       <c r="E77" s="20" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="F77" s="20" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="G77" s="20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H77" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I77" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 120 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 3 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I77" s="19" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="19" t="inlineStr">
         <is>
-          <t>BETAMETASONA FOSFATO DISODICO-ACETATO BETAMETASONA 3/3 MG FA 1 UD</t>
+          <t>ACIDO VALPROICO 250 MG/5 ML FC 120 ML</t>
         </is>
       </c>
       <c r="B78" s="19" t="inlineStr">
@@ -8478,7 +8510,7 @@
         <v>1.1</v>
       </c>
       <c r="F78" s="20" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="G78" s="20" t="n">
         <v>0</v>
@@ -8490,14 +8522,14 @@
       </c>
       <c r="I78" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2 ud.</t>
+          <t>COMPRA EXTERNA 120 ud.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="19" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 0,25 MG/ML SOL. P/NEBULIZAR FC</t>
+          <t>BETAMETASONA FOSFATO DISODICO-ACETATO BETAMETASONA 3/3 MG FA 1 UD</t>
         </is>
       </c>
       <c r="B79" s="19" t="inlineStr">
@@ -8518,19 +8550,23 @@
         <v>2</v>
       </c>
       <c r="G79" s="20" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H79" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I79" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I79" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 2 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="19" t="inlineStr">
         <is>
-          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
+          <t>BROMURO DE IPRATROPIO 0,25 MG/ML SOL. P/NEBULIZAR FC</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
@@ -8545,13 +8581,13 @@
         <v>0</v>
       </c>
       <c r="E80" s="20" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="F80" s="20" t="n">
         <v>2</v>
       </c>
       <c r="G80" s="20" t="n">
-        <v>850</v>
+        <v>106</v>
       </c>
       <c r="H80" s="19" t="inlineStr">
         <is>
@@ -8563,7 +8599,7 @@
     <row r="81">
       <c r="A81" s="19" t="inlineStr">
         <is>
-          <t>SODIO CLORURO 0.9% BS 500 ML</t>
+          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
         </is>
       </c>
       <c r="B81" s="19" t="inlineStr">
@@ -8578,17 +8614,17 @@
         <v>0</v>
       </c>
       <c r="E81" s="20" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="F81" s="20" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G81" s="20" t="n">
-        <v>1080</v>
+        <v>850</v>
       </c>
       <c r="H81" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 14 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I81" s="19" t="inlineStr"/>
@@ -8596,7 +8632,7 @@
     <row r="82">
       <c r="A82" s="19" t="inlineStr">
         <is>
-          <t>FITOMENADIONA 10 MG/ML INTRAMUSCULAR</t>
+          <t>SODIO CLORURO 0.9% BS 500 ML</t>
         </is>
       </c>
       <c r="B82" s="19" t="inlineStr">
@@ -8611,17 +8647,17 @@
         <v>0</v>
       </c>
       <c r="E82" s="20" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F82" s="20" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G82" s="20" t="n">
-        <v>300</v>
+        <v>1080</v>
       </c>
       <c r="H82" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 14 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I82" s="19" t="inlineStr"/>
@@ -8629,7 +8665,7 @@
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
         <is>
-          <t>MISOPROSTOL 200 MCG COMPRIMIDO</t>
+          <t>FITOMENADIONA 10 MG/ML INTRAMUSCULAR</t>
         </is>
       </c>
       <c r="B83" s="19" t="inlineStr">
@@ -8644,17 +8680,17 @@
         <v>0</v>
       </c>
       <c r="E83" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F83" s="20" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G83" s="20" t="n">
-        <v>112</v>
+        <v>300</v>
       </c>
       <c r="H83" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 28 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I83" s="19" t="inlineStr"/>
@@ -8662,7 +8698,7 @@
     <row r="84">
       <c r="A84" s="19" t="inlineStr">
         <is>
-          <t>KETOROLACO 30 MG/ML INYECTABLE</t>
+          <t>MISOPROSTOL 200 MCG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B84" s="19" t="inlineStr">
@@ -8677,29 +8713,25 @@
         <v>0</v>
       </c>
       <c r="E84" s="20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F84" s="20" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G84" s="20" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="H84" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I84" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 28 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I84" s="19" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="19" t="inlineStr">
         <is>
-          <t>ACIDO TRANEXAMICO 500 MG COMPRIMIDO</t>
+          <t>KETOROLACO 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B85" s="19" t="inlineStr">
@@ -8714,10 +8746,10 @@
         <v>0</v>
       </c>
       <c r="E85" s="20" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="F85" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85" s="20" t="n">
         <v>0</v>
@@ -8729,14 +8761,14 @@
       </c>
       <c r="I85" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2 ud.</t>
+          <t>COMPRA EXTERNA 1 ud.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="19" t="inlineStr">
         <is>
-          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
+          <t>ACIDO TRANEXAMICO 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B86" s="19" t="inlineStr">
@@ -8751,25 +8783,29 @@
         <v>0</v>
       </c>
       <c r="E86" s="20" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="F86" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" s="20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H86" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I86" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I86" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 2 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="19" t="inlineStr">
         <is>
-          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
         </is>
       </c>
       <c r="B87" s="19" t="inlineStr">
@@ -8784,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="E87" s="20" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F87" s="20" t="n">
         <v>1</v>
@@ -8802,7 +8838,7 @@
     <row r="88">
       <c r="A88" s="19" t="inlineStr">
         <is>
-          <t>VANCOMICINA FA 1000 MG</t>
+          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
         </is>
       </c>
       <c r="B88" s="19" t="inlineStr">
@@ -8823,7 +8859,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="20" t="n">
-        <v>650</v>
+        <v>100</v>
       </c>
       <c r="H88" s="19" t="inlineStr">
         <is>
@@ -8835,7 +8871,7 @@
     <row r="89">
       <c r="A89" s="19" t="inlineStr">
         <is>
-          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
+          <t>VANCOMICINA FA 1000 MG</t>
         </is>
       </c>
       <c r="B89" s="19" t="inlineStr">
@@ -8850,13 +8886,13 @@
         <v>0</v>
       </c>
       <c r="E89" s="20" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F89" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G89" s="20" t="n">
-        <v>400</v>
+        <v>650</v>
       </c>
       <c r="H89" s="19" t="inlineStr">
         <is>
@@ -8868,7 +8904,7 @@
     <row r="90">
       <c r="A90" s="19" t="inlineStr">
         <is>
-          <t>ACIDO PAMIDRONICO FA 90 MG</t>
+          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
         </is>
       </c>
       <c r="B90" s="19" t="inlineStr">
@@ -8883,13 +8919,13 @@
         <v>0</v>
       </c>
       <c r="E90" s="20" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F90" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G90" s="20" t="n">
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="H90" s="19" t="inlineStr">
         <is>
@@ -8901,7 +8937,7 @@
     <row r="91">
       <c r="A91" s="19" t="inlineStr">
         <is>
-          <t>ROCURONIO BROMURO AM 50 MG/5 ML</t>
+          <t>ACIDO PAMIDRONICO FA 90 MG</t>
         </is>
       </c>
       <c r="B91" s="19" t="inlineStr">
@@ -8916,13 +8952,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F91" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G91" s="20" t="n">
-        <v>1400</v>
+        <v>8</v>
       </c>
       <c r="H91" s="19" t="inlineStr">
         <is>
@@ -8934,7 +8970,7 @@
     <row r="92">
       <c r="A92" s="19" t="inlineStr">
         <is>
-          <t>HIERRO CARBOXIMALTOSA 500 MG/10 ML FA</t>
+          <t>ROCURONIO BROMURO AM 50 MG/5 ML</t>
         </is>
       </c>
       <c r="B92" s="19" t="inlineStr">
@@ -8955,23 +8991,19 @@
         <v>1</v>
       </c>
       <c r="G92" s="20" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H92" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I92" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I92" s="19" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="19" t="inlineStr">
         <is>
-          <t>ACIDO TRANEXAMICO 1.000 MG/10 ML AM</t>
+          <t>HIERRO CARBOXIMALTOSA 500 MG/10 ML FA</t>
         </is>
       </c>
       <c r="B93" s="19" t="inlineStr">
@@ -8986,7 +9018,7 @@
         <v>0</v>
       </c>
       <c r="E93" s="20" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F93" s="20" t="n">
         <v>1</v>
@@ -9008,7 +9040,7 @@
     <row r="94">
       <c r="A94" s="19" t="inlineStr">
         <is>
-          <t>ADALIMUMAB 40 MG/0,4 ML JER.PC 1 UD</t>
+          <t>ACIDO TRANEXAMICO 1.000 MG/10 ML AM</t>
         </is>
       </c>
       <c r="B94" s="19" t="inlineStr">
@@ -9045,7 +9077,7 @@
     <row r="95">
       <c r="A95" s="19" t="inlineStr">
         <is>
-          <t>CICLOPENTOLATO 1% (10 MG/ML) COLIRI</t>
+          <t>ADALIMUMAB 40 MG/0,4 ML JER.PC 1 UD</t>
         </is>
       </c>
       <c r="B95" s="19" t="inlineStr">
@@ -9060,25 +9092,29 @@
         <v>0</v>
       </c>
       <c r="E95" s="20" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F95" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G95" s="20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H95" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I95" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I95" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="19" t="inlineStr">
         <is>
-          <t>GENTAMICINA 80 MG/2 ML (40 MG/ML) INYECTABLE</t>
+          <t>CICLOPENTOLATO 1% (10 MG/ML) COLIRI</t>
         </is>
       </c>
       <c r="B96" s="19" t="inlineStr">
@@ -9099,7 +9135,7 @@
         <v>1</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H96" s="19" t="inlineStr">
         <is>
@@ -9111,7 +9147,7 @@
     <row r="97">
       <c r="A97" s="19" t="inlineStr">
         <is>
-          <t>TERLIPRESINA 1 MG INYECTABLE</t>
+          <t>GENTAMICINA 80 MG/2 ML (40 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B97" s="19" t="inlineStr">
@@ -9126,13 +9162,13 @@
         <v>0</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F97" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G97" s="20" t="n">
-        <v>420</v>
+        <v>100</v>
       </c>
       <c r="H97" s="19" t="inlineStr">
         <is>
@@ -9144,7 +9180,7 @@
     <row r="98">
       <c r="A98" s="19" t="inlineStr">
         <is>
-          <t>AGUA BIDESTILADA MATRAZ 500 ML</t>
+          <t>TERLIPRESINA 1 MG INYECTABLE</t>
         </is>
       </c>
       <c r="B98" s="19" t="inlineStr">
@@ -9159,13 +9195,13 @@
         <v>0</v>
       </c>
       <c r="E98" s="20" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F98" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G98" s="20" t="n">
-        <v>110</v>
+        <v>420</v>
       </c>
       <c r="H98" s="19" t="inlineStr">
         <is>
@@ -9177,7 +9213,7 @@
     <row r="99">
       <c r="A99" s="19" t="inlineStr">
         <is>
-          <t>IBUPROFENO 100 MG/5 ML SUSP 100 ML</t>
+          <t>AGUA BIDESTILADA MATRAZ 500 ML</t>
         </is>
       </c>
       <c r="B99" s="19" t="inlineStr">
@@ -9198,7 +9234,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>825</v>
+        <v>110</v>
       </c>
       <c r="H99" s="19" t="inlineStr">
         <is>
@@ -9210,7 +9246,7 @@
     <row r="100">
       <c r="A100" s="19" t="inlineStr">
         <is>
-          <t>PIRIDOXINA 10 MG CM</t>
+          <t>IBUPROFENO 100 MG/5 ML SUSP 100 ML</t>
         </is>
       </c>
       <c r="B100" s="19" t="inlineStr">
@@ -9231,23 +9267,19 @@
         <v>1</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="H100" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I100" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I100" s="19" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="19" t="inlineStr">
         <is>
-          <t>GENTAMICINA 3MG UNG. OFTALMICO POMO</t>
+          <t>PIRIDOXINA 10 MG CM</t>
         </is>
       </c>
       <c r="B101" s="19" t="inlineStr">
@@ -9262,25 +9294,29 @@
         <v>0</v>
       </c>
       <c r="E101" s="20" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F101" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G101" s="20" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="H101" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I101" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I101" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="19" t="inlineStr">
         <is>
-          <t>RISPERIDONA 37,5 MG FA</t>
+          <t>GENTAMICINA 3MG UNG. OFTALMICO POMO</t>
         </is>
       </c>
       <c r="B102" s="19" t="inlineStr">
@@ -9295,29 +9331,25 @@
         <v>0</v>
       </c>
       <c r="E102" s="20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F102" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="20" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="H102" s="19" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I102" s="19" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I102" s="19" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="19" t="inlineStr">
         <is>
-          <t>SEVOFLURANO 1 ML/ML LIQUIDO PARA INHALACION</t>
+          <t>RISPERIDONA 37,5 MG FA</t>
         </is>
       </c>
       <c r="B103" s="19" t="inlineStr">
@@ -9338,19 +9370,23 @@
         <v>1</v>
       </c>
       <c r="G103" s="20" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H103" s="19" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I103" s="19" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I103" s="19" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="19" t="inlineStr">
         <is>
-          <t>LEVONORGESTREL 1,5 MG CM</t>
+          <t>SEVOFLURANO 1 ML/ML LIQUIDO PARA INHALACION</t>
         </is>
       </c>
       <c r="B104" s="19" t="inlineStr">
@@ -9371,7 +9407,7 @@
         <v>1</v>
       </c>
       <c r="G104" s="20" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="H104" s="19" t="inlineStr">
         <is>
@@ -9383,7 +9419,7 @@
     <row r="105">
       <c r="A105" s="19" t="inlineStr">
         <is>
-          <t>PERMETRINA 1% (10 MG/ML) SHAMPOO</t>
+          <t>LEVONORGESTREL 1,5 MG CM</t>
         </is>
       </c>
       <c r="B105" s="19" t="inlineStr">
@@ -9404,60 +9440,56 @@
         <v>1</v>
       </c>
       <c r="G105" s="20" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H105" s="19" t="inlineStr">
         <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I105" s="19" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="19" t="inlineStr">
+        <is>
+          <t>PERMETRINA 1% (10 MG/ML) SHAMPOO</t>
+        </is>
+      </c>
+      <c r="B106" s="19" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F106" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="19" t="inlineStr">
+        <is>
           <t>SIN STOCK EN BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="I105" s="19" t="inlineStr">
+      <c r="I106" s="19" t="inlineStr">
         <is>
           <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="21" t="inlineStr">
-        <is>
-          <t>EMPAGLIFLOZINA 10 MG CM UD</t>
-        </is>
-      </c>
-      <c r="B106" s="21" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C106" s="22" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D106" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E106" s="22" t="n">
-        <v>21695.7</v>
-      </c>
-      <c r="F106" s="22" t="n">
-        <v>16080</v>
-      </c>
-      <c r="G106" s="22" t="n">
-        <v>10980</v>
-      </c>
-      <c r="H106" s="21" t="inlineStr">
-        <is>
-          <t>TRASPASAR 10980 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I106" s="21" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 5100 ud.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="21" t="inlineStr">
         <is>
-          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
+          <t>EMPAGLIFLOZINA 10 MG CM UD</t>
         </is>
       </c>
       <c r="B107" s="21" t="inlineStr">
@@ -9466,31 +9498,35 @@
         </is>
       </c>
       <c r="C107" s="22" t="n">
-        <v>2417</v>
+        <v>1440</v>
       </c>
       <c r="D107" s="22" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="E107" s="22" t="n">
-        <v>21834.9</v>
+        <v>21695.7</v>
       </c>
       <c r="F107" s="22" t="n">
-        <v>15494</v>
+        <v>16140</v>
       </c>
       <c r="G107" s="22" t="n">
-        <v>28000</v>
+        <v>10980</v>
       </c>
       <c r="H107" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 15494 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I107" s="21" t="inlineStr"/>
+          <t>TRASPASAR 10980 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I107" s="21" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 5160 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="21" t="inlineStr">
         <is>
-          <t>DABIGATRAN ETEXILATO CP 150 MG</t>
+          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B108" s="21" t="inlineStr">
@@ -9499,23 +9535,23 @@
         </is>
       </c>
       <c r="C108" s="22" t="n">
-        <v>2743</v>
+        <v>2327</v>
       </c>
       <c r="D108" s="22" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="E108" s="22" t="n">
-        <v>13392.4</v>
+        <v>21834.9</v>
       </c>
       <c r="F108" s="22" t="n">
-        <v>8254</v>
+        <v>15584</v>
       </c>
       <c r="G108" s="22" t="n">
-        <v>25920</v>
+        <v>28000</v>
       </c>
       <c r="H108" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 8254 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 15584 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I108" s="21" t="inlineStr"/>
@@ -9523,7 +9559,7 @@
     <row r="109">
       <c r="A109" s="21" t="inlineStr">
         <is>
-          <t>METFORMINA 1000 MG CM LIBERACION MODIFICADA</t>
+          <t>DABIGATRAN ETEXILATO CP 150 MG</t>
         </is>
       </c>
       <c r="B109" s="21" t="inlineStr">
@@ -9532,23 +9568,23 @@
         </is>
       </c>
       <c r="C109" s="22" t="n">
-        <v>3000</v>
+        <v>2623</v>
       </c>
       <c r="D109" s="22" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="E109" s="22" t="n">
-        <v>12706.8</v>
+        <v>13392.4</v>
       </c>
       <c r="F109" s="22" t="n">
-        <v>7000</v>
+        <v>8374</v>
       </c>
       <c r="G109" s="22" t="n">
-        <v>11500</v>
+        <v>25920</v>
       </c>
       <c r="H109" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 7000 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 8374 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I109" s="21" t="inlineStr"/>
@@ -9556,7 +9592,7 @@
     <row r="110">
       <c r="A110" s="21" t="inlineStr">
         <is>
-          <t>DABIGATRAN ETEXILATO CP 110 MG</t>
+          <t>METFORMINA 1000 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B110" s="21" t="inlineStr">
@@ -9565,35 +9601,31 @@
         </is>
       </c>
       <c r="C110" s="22" t="n">
-        <v>1320</v>
+        <v>3000</v>
       </c>
       <c r="D110" s="22" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="E110" s="22" t="n">
-        <v>9712.4</v>
+        <v>12706.8</v>
       </c>
       <c r="F110" s="22" t="n">
-        <v>5061</v>
+        <v>7000</v>
       </c>
       <c r="G110" s="22" t="n">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="H110" s="21" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I110" s="21" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 5061 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 7000 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I110" s="21" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="21" t="inlineStr">
         <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+          <t>DABIGATRAN ETEXILATO CP 110 MG</t>
         </is>
       </c>
       <c r="B111" s="21" t="inlineStr">
@@ -9602,16 +9634,16 @@
         </is>
       </c>
       <c r="C111" s="22" t="n">
-        <v>960</v>
+        <v>1320</v>
       </c>
       <c r="D111" s="22" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="E111" s="22" t="n">
-        <v>8213.799999999999</v>
+        <v>9712.4</v>
       </c>
       <c r="F111" s="22" t="n">
-        <v>5700</v>
+        <v>5061</v>
       </c>
       <c r="G111" s="22" t="n">
         <v>0</v>
@@ -9623,14 +9655,14 @@
       </c>
       <c r="I111" s="21" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 5700 ud.</t>
+          <t>COMPRA EXTERNA 5061 ud.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="21" t="inlineStr">
         <is>
-          <t>TRAMADOL + PARACETAMOL 37,5 MG/325 MG CM</t>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
         </is>
       </c>
       <c r="B112" s="21" t="inlineStr">
@@ -9639,16 +9671,16 @@
         </is>
       </c>
       <c r="C112" s="22" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="D112" s="22" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="E112" s="22" t="n">
-        <v>5715.7</v>
+        <v>8213.799999999999</v>
       </c>
       <c r="F112" s="22" t="n">
-        <v>2933</v>
+        <v>5760</v>
       </c>
       <c r="G112" s="22" t="n">
         <v>0</v>
@@ -9660,14 +9692,14 @@
       </c>
       <c r="I112" s="21" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2933 ud.</t>
+          <t>COMPRA EXTERNA 5760 ud.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="21" t="inlineStr">
         <is>
-          <t>RIFAXIMINA 200 MG CP</t>
+          <t>TRAMADOL + PARACETAMOL 37,5 MG/325 MG CM</t>
         </is>
       </c>
       <c r="B113" s="21" t="inlineStr">
@@ -9676,31 +9708,35 @@
         </is>
       </c>
       <c r="C113" s="22" t="n">
-        <v>648</v>
+        <v>1200</v>
       </c>
       <c r="D113" s="22" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="E113" s="22" t="n">
-        <v>3251.5</v>
+        <v>5715.7</v>
       </c>
       <c r="F113" s="22" t="n">
-        <v>1896</v>
+        <v>2983</v>
       </c>
       <c r="G113" s="22" t="n">
-        <v>21864</v>
+        <v>0</v>
       </c>
       <c r="H113" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1896 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I113" s="21" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I113" s="21" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 2983 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="21" t="inlineStr">
         <is>
-          <t>LEFLUNOMIDA 20 MG COMPRIMIDO</t>
+          <t>RIFAXIMINA 200 MG CP</t>
         </is>
       </c>
       <c r="B114" s="21" t="inlineStr">
@@ -9709,23 +9745,23 @@
         </is>
       </c>
       <c r="C114" s="22" t="n">
-        <v>480</v>
+        <v>648</v>
       </c>
       <c r="D114" s="22" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="E114" s="22" t="n">
-        <v>3754.6</v>
+        <v>3251.5</v>
       </c>
       <c r="F114" s="22" t="n">
-        <v>2580</v>
+        <v>1896</v>
       </c>
       <c r="G114" s="22" t="n">
-        <v>12240</v>
+        <v>21864</v>
       </c>
       <c r="H114" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 2580 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1896 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I114" s="21" t="inlineStr"/>
@@ -9733,7 +9769,7 @@
     <row r="115">
       <c r="A115" s="21" t="inlineStr">
         <is>
-          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
+          <t>LEFLUNOMIDA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B115" s="21" t="inlineStr">
@@ -9742,35 +9778,31 @@
         </is>
       </c>
       <c r="C115" s="22" t="n">
-        <v>53</v>
+        <v>480</v>
       </c>
       <c r="D115" s="22" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="E115" s="22" t="n">
-        <v>2921.4</v>
+        <v>3754.6</v>
       </c>
       <c r="F115" s="22" t="n">
-        <v>2263</v>
+        <v>2580</v>
       </c>
       <c r="G115" s="22" t="n">
-        <v>350</v>
+        <v>12240</v>
       </c>
       <c r="H115" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 350 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I115" s="21" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1913 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2580 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I115" s="21" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="21" t="inlineStr">
         <is>
-          <t>LEVODOPA 200 MG - BENSERAZIDA 50 MG COMPRIMIDO</t>
+          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
         </is>
       </c>
       <c r="B116" s="21" t="inlineStr">
@@ -9779,35 +9811,35 @@
         </is>
       </c>
       <c r="C116" s="22" t="n">
-        <v>300</v>
+        <v>53</v>
       </c>
       <c r="D116" s="22" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="E116" s="22" t="n">
-        <v>1346.8</v>
+        <v>2921.4</v>
       </c>
       <c r="F116" s="22" t="n">
-        <v>372</v>
+        <v>2263</v>
       </c>
       <c r="G116" s="22" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="H116" s="21" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
+          <t>TRASPASAR 350 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I116" s="21" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 372 ud.</t>
+          <t>COMPRA EXTERNA 1913 ud.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="21" t="inlineStr">
         <is>
-          <t>LATANOPROST 0,005% COLIRIO</t>
+          <t>LEVODOPA 200 MG - BENSERAZIDA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B117" s="21" t="inlineStr">
@@ -9816,16 +9848,16 @@
         </is>
       </c>
       <c r="C117" s="22" t="n">
-        <v>33</v>
+        <v>300</v>
       </c>
       <c r="D117" s="22" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="E117" s="22" t="n">
-        <v>260.6</v>
+        <v>1346.8</v>
       </c>
       <c r="F117" s="22" t="n">
-        <v>85</v>
+        <v>552</v>
       </c>
       <c r="G117" s="22" t="n">
         <v>0</v>
@@ -9837,14 +9869,14 @@
       </c>
       <c r="I117" s="21" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 85 ud.</t>
+          <t>COMPRA EXTERNA 552 ud.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="21" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>LATANOPROST 0,005% COLIRIO</t>
         </is>
       </c>
       <c r="B118" s="21" t="inlineStr">
@@ -9853,97 +9885,101 @@
         </is>
       </c>
       <c r="C118" s="22" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D118" s="22" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="E118" s="22" t="n">
-        <v>181.5</v>
+        <v>260.6</v>
       </c>
       <c r="F118" s="22" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G118" s="22" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H118" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 52 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I118" s="21" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I118" s="21" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 85 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="21" t="inlineStr">
         <is>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+        </is>
+      </c>
+      <c r="B119" s="21" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C119" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="D119" s="22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E119" s="22" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="F119" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="G119" s="22" t="n">
+        <v>180</v>
+      </c>
+      <c r="H119" s="21" t="inlineStr">
+        <is>
+          <t>TRASPASAR 53 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I119" s="21" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="21" t="inlineStr">
+        <is>
           <t>KETOCONAZOL 2% SHAMPOO 100 ML</t>
         </is>
       </c>
-      <c r="B119" s="21" t="inlineStr">
+      <c r="B120" s="21" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C119" s="22" t="n">
+      <c r="C120" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="D119" s="22" t="n">
+      <c r="D120" s="22" t="n">
         <v>1.9</v>
       </c>
-      <c r="E119" s="22" t="n">
+      <c r="E120" s="22" t="n">
         <v>24.8</v>
       </c>
-      <c r="F119" s="22" t="n">
+      <c r="F120" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="G119" s="22" t="n">
+      <c r="G120" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="H119" s="21" t="inlineStr">
+      <c r="H120" s="21" t="inlineStr">
         <is>
           <t>TRASPASAR 7 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="I119" s="21" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="25" t="inlineStr">
-        <is>
-          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B120" s="25" t="inlineStr">
-        <is>
-          <t>3-ALTO</t>
-        </is>
-      </c>
-      <c r="C120" s="26" t="n">
-        <v>6400</v>
-      </c>
-      <c r="D120" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E120" s="26" t="n">
-        <v>17268.7</v>
-      </c>
-      <c r="F120" s="26" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G120" s="26" t="n">
-        <v>22400</v>
-      </c>
-      <c r="H120" s="25" t="inlineStr">
-        <is>
-          <t>TRASPASAR 8000 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I120" s="25" t="inlineStr"/>
+      <c r="I120" s="21" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="25" t="inlineStr">
         <is>
-          <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
+          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B121" s="25" t="inlineStr">
@@ -9952,23 +9988,23 @@
         </is>
       </c>
       <c r="C121" s="26" t="n">
-        <v>4540</v>
+        <v>6400</v>
       </c>
       <c r="D121" s="26" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="E121" s="26" t="n">
-        <v>9561.799999999999</v>
+        <v>17268.7</v>
       </c>
       <c r="F121" s="26" t="n">
-        <v>3200</v>
+        <v>8000</v>
       </c>
       <c r="G121" s="26" t="n">
-        <v>32580</v>
+        <v>22400</v>
       </c>
       <c r="H121" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 3200 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 8000 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I121" s="25" t="inlineStr"/>
@@ -9976,7 +10012,7 @@
     <row r="122">
       <c r="A122" s="25" t="inlineStr">
         <is>
-          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
+          <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B122" s="25" t="inlineStr">
@@ -9985,35 +10021,31 @@
         </is>
       </c>
       <c r="C122" s="26" t="n">
-        <v>3000</v>
+        <v>4520</v>
       </c>
       <c r="D122" s="26" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="E122" s="26" t="n">
-        <v>10731.8</v>
+        <v>9561.799999999999</v>
       </c>
       <c r="F122" s="26" t="n">
-        <v>5700</v>
+        <v>3220</v>
       </c>
       <c r="G122" s="26" t="n">
-        <v>0</v>
+        <v>32580</v>
       </c>
       <c r="H122" s="25" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I122" s="25" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 5700 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 3220 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I122" s="25" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="25" t="inlineStr">
         <is>
-          <t>HIDROXICLOROQUINA CM 200 MG</t>
+          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
         </is>
       </c>
       <c r="B123" s="25" t="inlineStr">
@@ -10022,31 +10054,35 @@
         </is>
       </c>
       <c r="C123" s="26" t="n">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="D123" s="26" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="E123" s="26" t="n">
-        <v>7817.6</v>
+        <v>10731.8</v>
       </c>
       <c r="F123" s="26" t="n">
-        <v>3360</v>
+        <v>5700</v>
       </c>
       <c r="G123" s="26" t="n">
-        <v>51840</v>
+        <v>0</v>
       </c>
       <c r="H123" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 3360 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I123" s="25" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I123" s="25" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 5700 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="25" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
+          <t>HIDROXICLOROQUINA CM 200 MG</t>
         </is>
       </c>
       <c r="B124" s="25" t="inlineStr">
@@ -10055,23 +10091,23 @@
         </is>
       </c>
       <c r="C124" s="26" t="n">
-        <v>2610</v>
+        <v>2700</v>
       </c>
       <c r="D124" s="26" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="E124" s="26" t="n">
-        <v>6720</v>
+        <v>7817.6</v>
       </c>
       <c r="F124" s="26" t="n">
-        <v>2880</v>
+        <v>3360</v>
       </c>
       <c r="G124" s="26" t="n">
-        <v>6000</v>
+        <v>51840</v>
       </c>
       <c r="H124" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 2880 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3360 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I124" s="25" t="inlineStr"/>
@@ -10079,7 +10115,7 @@
     <row r="125">
       <c r="A125" s="25" t="inlineStr">
         <is>
-          <t>AMLODIPINO 10 MG COMPRIMIDO</t>
+          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
         </is>
       </c>
       <c r="B125" s="25" t="inlineStr">
@@ -10088,23 +10124,23 @@
         </is>
       </c>
       <c r="C125" s="26" t="n">
-        <v>2000</v>
+        <v>2610</v>
       </c>
       <c r="D125" s="26" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="E125" s="26" t="n">
-        <v>5070.1</v>
+        <v>6720</v>
       </c>
       <c r="F125" s="26" t="n">
-        <v>1000</v>
+        <v>2880</v>
       </c>
       <c r="G125" s="26" t="n">
-        <v>22000</v>
+        <v>6000</v>
       </c>
       <c r="H125" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2880 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I125" s="25" t="inlineStr"/>
@@ -10112,7 +10148,7 @@
     <row r="126">
       <c r="A126" s="25" t="inlineStr">
         <is>
-          <t>CLOPIDOGREL 75 MG COMPRIMIDO</t>
+          <t>AMLODIPINO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B126" s="25" t="inlineStr">
@@ -10124,20 +10160,20 @@
         <v>2000</v>
       </c>
       <c r="D126" s="26" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="E126" s="26" t="n">
-        <v>4952</v>
+        <v>5070.1</v>
       </c>
       <c r="F126" s="26" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G126" s="26" t="n">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="H126" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 2000 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I126" s="25" t="inlineStr"/>
@@ -10145,7 +10181,7 @@
     <row r="127">
       <c r="A127" s="25" t="inlineStr">
         <is>
-          <t>DULOXETINA 60 MG CAPSULA</t>
+          <t>CLOPIDOGREL 75 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B127" s="25" t="inlineStr">
@@ -10154,23 +10190,23 @@
         </is>
       </c>
       <c r="C127" s="26" t="n">
-        <v>780</v>
+        <v>2000</v>
       </c>
       <c r="D127" s="26" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="E127" s="26" t="n">
-        <v>2638</v>
+        <v>4952</v>
       </c>
       <c r="F127" s="26" t="n">
-        <v>1260</v>
+        <v>2000</v>
       </c>
       <c r="G127" s="26" t="n">
-        <v>3720</v>
+        <v>20000</v>
       </c>
       <c r="H127" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 1260 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2000 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I127" s="25" t="inlineStr"/>
@@ -10178,7 +10214,7 @@
     <row r="128">
       <c r="A128" s="25" t="inlineStr">
         <is>
-          <t>DULOXETINA 30 MG CAPSULA</t>
+          <t>DULOXETINA 60 MG CAPSULA</t>
         </is>
       </c>
       <c r="B128" s="25" t="inlineStr">
@@ -10190,20 +10226,20 @@
         <v>780</v>
       </c>
       <c r="D128" s="26" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="E128" s="26" t="n">
-        <v>2113.5</v>
+        <v>2638</v>
       </c>
       <c r="F128" s="26" t="n">
-        <v>840</v>
+        <v>1260</v>
       </c>
       <c r="G128" s="26" t="n">
-        <v>2580</v>
+        <v>3720</v>
       </c>
       <c r="H128" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 840 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1260 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I128" s="25" t="inlineStr"/>
@@ -10211,7 +10247,7 @@
     <row r="129">
       <c r="A129" s="25" t="inlineStr">
         <is>
-          <t>AZATIOPRINA 50 MG COMPRIMIDO</t>
+          <t>DULOXETINA 30 MG CAPSULA</t>
         </is>
       </c>
       <c r="B129" s="25" t="inlineStr">
@@ -10220,23 +10256,23 @@
         </is>
       </c>
       <c r="C129" s="26" t="n">
-        <v>500</v>
+        <v>780</v>
       </c>
       <c r="D129" s="26" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="E129" s="26" t="n">
-        <v>1439.6</v>
+        <v>2113.5</v>
       </c>
       <c r="F129" s="26" t="n">
-        <v>300</v>
+        <v>840</v>
       </c>
       <c r="G129" s="26" t="n">
-        <v>22200</v>
+        <v>2580</v>
       </c>
       <c r="H129" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 300 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 840 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I129" s="25" t="inlineStr"/>
@@ -10244,7 +10280,7 @@
     <row r="130">
       <c r="A130" s="25" t="inlineStr">
         <is>
-          <t>SACUBITRILO VALSARTAN 100 MG</t>
+          <t>AZATIOPRINA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B130" s="25" t="inlineStr">
@@ -10253,23 +10289,23 @@
         </is>
       </c>
       <c r="C130" s="26" t="n">
+        <v>500</v>
+      </c>
+      <c r="D130" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E130" s="26" t="n">
+        <v>1439.6</v>
+      </c>
+      <c r="F130" s="26" t="n">
         <v>300</v>
       </c>
-      <c r="D130" s="26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E130" s="26" t="n">
-        <v>1169.9</v>
-      </c>
-      <c r="F130" s="26" t="n">
-        <v>446</v>
-      </c>
       <c r="G130" s="26" t="n">
-        <v>2700</v>
+        <v>22200</v>
       </c>
       <c r="H130" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 446 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 300 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I130" s="25" t="inlineStr"/>
@@ -10277,73 +10313,73 @@
     <row r="131">
       <c r="A131" s="25" t="inlineStr">
         <is>
+          <t>SACUBITRILO VALSARTAN 100 MG</t>
+        </is>
+      </c>
+      <c r="B131" s="25" t="inlineStr">
+        <is>
+          <t>3-ALTO</t>
+        </is>
+      </c>
+      <c r="C131" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="D131" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E131" s="26" t="n">
+        <v>1169.9</v>
+      </c>
+      <c r="F131" s="26" t="n">
+        <v>446</v>
+      </c>
+      <c r="G131" s="26" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H131" s="25" t="inlineStr">
+        <is>
+          <t>TRASPASAR 446 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I131" s="25" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="25" t="inlineStr">
+        <is>
           <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
         </is>
       </c>
-      <c r="B131" s="25" t="inlineStr">
+      <c r="B132" s="25" t="inlineStr">
         <is>
           <t>3-ALTO</t>
         </is>
       </c>
-      <c r="C131" s="26" t="n">
+      <c r="C132" s="26" t="n">
         <v>39</v>
       </c>
-      <c r="D131" s="26" t="n">
+      <c r="D132" s="26" t="n">
         <v>4.7</v>
       </c>
-      <c r="E131" s="26" t="n">
+      <c r="E132" s="26" t="n">
         <v>103</v>
       </c>
-      <c r="F131" s="26" t="n">
+      <c r="F132" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="G131" s="26" t="n">
+      <c r="G132" s="26" t="n">
         <v>70</v>
       </c>
-      <c r="H131" s="25" t="inlineStr">
+      <c r="H132" s="25" t="inlineStr">
         <is>
           <t>TRASPASAR 9 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="I131" s="25" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>OMEPRAZOL 20 MG CAPSULA</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>4-MODERADO</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="n">
-        <v>17050</v>
-      </c>
-      <c r="D132" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E132" s="4" t="n">
-        <v>21658.3</v>
-      </c>
-      <c r="F132" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="G132" s="4" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>TRASPASAR 750 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I132" s="3" t="inlineStr"/>
+      <c r="I132" s="25" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
+          <t>OMEPRAZOL 20 MG CAPSULA</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -10352,23 +10388,23 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>12000</v>
+        <v>17050</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>17566.2</v>
+        <v>21658.3</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>998</v>
+        <v>750</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>62900</v>
+        <v>38000</v>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 998 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 750 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr"/>
@@ -10376,7 +10412,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 40 MG COMPRIMIDO</t>
+          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -10385,23 +10421,23 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>9260</v>
+        <v>12000</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>13670.3</v>
+        <v>17566.2</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1140</v>
+        <v>998</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>5700</v>
+        <v>62900</v>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1140 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 998 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr"/>
@@ -10409,7 +10445,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
+          <t>ATORVASTATINA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -10418,23 +10454,23 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
+        <v>9260</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E135" s="4" t="n">
+        <v>13670.3</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G135" s="4" t="n">
         <v>5700</v>
       </c>
-      <c r="D135" s="4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="E135" s="4" t="n">
-        <v>7920</v>
-      </c>
-      <c r="F135" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G135" s="4" t="n">
-        <v>10560</v>
-      </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1140 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr"/>
@@ -10442,7 +10478,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>TAMSULOSINA 400 MCG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -10451,23 +10487,23 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>1500</v>
+        <v>5700</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>2661.7</v>
+        <v>7920</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>527</v>
+        <v>60</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>12600</v>
+        <v>10560</v>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 527 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr"/>
@@ -10475,7 +10511,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>APIXABAN 5 MG CM</t>
+          <t>TAMSULOSINA 400 MCG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -10484,23 +10520,23 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>1988.1</v>
+        <v>2661.7</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>300</v>
+        <v>557</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>1800</v>
+        <v>12600</v>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 300 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 557 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr"/>
@@ -10508,7 +10544,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>LAMOTRIGINA 100 MG COMPRIMIDO</t>
+          <t>APIXABAN 5 MG CM</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -10517,105 +10553,138 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>840</v>
+        <v>900</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>1642.1</v>
+        <v>1988.1</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 480 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 300 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
+          <t>LAMOTRIGINA 100 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>4-MODERADO</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="n">
+        <v>840</v>
+      </c>
+      <c r="D139" s="4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E139" s="4" t="n">
+        <v>1642.1</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="G139" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 480 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
           <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t>4-MODERADO</t>
         </is>
       </c>
-      <c r="C139" s="4" t="n">
+      <c r="C140" s="4" t="n">
         <v>284</v>
       </c>
-      <c r="D139" s="4" t="n">
+      <c r="D140" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E139" s="4" t="n">
+      <c r="E140" s="4" t="n">
         <v>529.6</v>
       </c>
-      <c r="F139" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="G139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" s="3" t="inlineStr">
+      <c r="F140" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="G140" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="I139" s="3" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 115 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="11" t="inlineStr">
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 116 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="12" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="13" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="14" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="14" t="inlineStr">
         <is>
           <t>ALTO / MODERADO  —  reponer pronto</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="15" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="15" t="inlineStr">
         <is>
           <t>BAJO  —  vigilar</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="16" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="16" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -11374,10 +11443,10 @@
         </is>
       </c>
       <c r="C17" s="22" t="n">
-        <v>6363</v>
+        <v>6243</v>
       </c>
       <c r="D17" s="22" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E17" s="22" t="n">
         <v>20628.2</v>
@@ -11389,17 +11458,17 @@
         <v>17908.4</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>14265</v>
+        <v>14385</v>
       </c>
       <c r="I17" s="22" t="n">
-        <v>14265</v>
+        <v>14385</v>
       </c>
       <c r="J17" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 14265 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 14385 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr"/>
@@ -11416,10 +11485,10 @@
         </is>
       </c>
       <c r="C18" s="22" t="n">
-        <v>3290</v>
+        <v>3230</v>
       </c>
       <c r="D18" s="22" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E18" s="22" t="n">
         <v>12484.3</v>
@@ -11431,17 +11500,17 @@
         <v>10399.6</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>9194</v>
+        <v>9254</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>9194</v>
+        <v>9254</v>
       </c>
       <c r="J18" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 9194 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 9254 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr"/>
@@ -11458,7 +11527,7 @@
         </is>
       </c>
       <c r="C19" s="22" t="n">
-        <v>2755</v>
+        <v>2695</v>
       </c>
       <c r="D19" s="22" t="n">
         <v>1.5</v>
@@ -11473,13 +11542,13 @@
         <v>9283.5</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>8706</v>
+        <v>8766</v>
       </c>
       <c r="I19" s="22" t="n">
         <v>2880</v>
       </c>
       <c r="J19" s="22" t="n">
-        <v>5826</v>
+        <v>5886</v>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
@@ -11488,7 +11557,7 @@
       </c>
       <c r="L19" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 5826 ud.</t>
+          <t>GESTIONAR EXTERNO 5886 ud.</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11573,7 @@
         </is>
       </c>
       <c r="C20" s="22" t="n">
-        <v>3317</v>
+        <v>3227</v>
       </c>
       <c r="D20" s="22" t="n">
         <v>1.8</v>
@@ -11519,13 +11588,13 @@
         <v>8965.799999999999</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>8053</v>
+        <v>8143</v>
       </c>
       <c r="I20" s="22" t="n">
         <v>3024</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>5029</v>
+        <v>5119</v>
       </c>
       <c r="K20" s="21" t="inlineStr">
         <is>
@@ -11534,7 +11603,7 @@
       </c>
       <c r="L20" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 5029 ud.</t>
+          <t>GESTIONAR EXTERNO 5119 ud.</t>
         </is>
       </c>
     </row>
@@ -11550,10 +11619,10 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>2632</v>
+        <v>2587</v>
       </c>
       <c r="D21" s="22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E21" s="22" t="n">
         <v>8968.299999999999</v>
@@ -11565,17 +11634,17 @@
         <v>7709.4</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>6336</v>
+        <v>6381</v>
       </c>
       <c r="I21" s="22" t="n">
-        <v>6336</v>
+        <v>6381</v>
       </c>
       <c r="J21" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 6336 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 6381 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr"/>
@@ -11638,10 +11707,10 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="D23" s="22" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E23" s="22" t="n">
         <v>4280.1</v>
@@ -11653,13 +11722,13 @@
         <v>3561.4</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>3560</v>
+        <v>3620</v>
       </c>
       <c r="I23" s="22" t="n">
         <v>1800</v>
       </c>
       <c r="J23" s="22" t="n">
-        <v>1760</v>
+        <v>1820</v>
       </c>
       <c r="K23" s="21" t="inlineStr">
         <is>
@@ -11668,7 +11737,7 @@
       </c>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1760 ud.</t>
+          <t>GESTIONAR EXTERNO 1820 ud.</t>
         </is>
       </c>
     </row>
@@ -11684,10 +11753,10 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>666</v>
+        <v>636</v>
       </c>
       <c r="D24" s="22" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E24" s="22" t="n">
         <v>2501.1</v>
@@ -11699,17 +11768,17 @@
         <v>2078.8</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>1835</v>
+        <v>1865</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>1835</v>
+        <v>1865</v>
       </c>
       <c r="J24" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 1835 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1865 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr"/>
@@ -12250,7 +12319,7 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>4319</v>
+        <v>4289</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>3.9</v>
@@ -12265,13 +12334,13 @@
         <v>5472.4</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2542</v>
+        <v>2572</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>2542</v>
+        <v>2572</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -12280,7 +12349,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2542 ud.</t>
+          <t>GESTIONAR EXTERNO 2572 ud.</t>
         </is>
       </c>
     </row>
@@ -12296,10 +12365,10 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>3513</v>
+        <v>3482</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="E38" s="4" t="n">
         <v>6180.5</v>
@@ -12311,17 +12380,17 @@
         <v>5218.4</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2668</v>
+        <v>2698</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>2668</v>
+        <v>2698</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 2668 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 2698 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr"/>
@@ -12338,7 +12407,7 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1839</v>
+        <v>1809</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>2</v>
@@ -12353,17 +12422,17 @@
         <v>4584.8</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>2982</v>
+        <v>3012</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>2982</v>
+        <v>3012</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 2982 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 3012 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr"/>
@@ -12380,7 +12449,7 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>2127</v>
+        <v>2067</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>2.3</v>
@@ -12395,13 +12464,13 @@
         <v>4398.3</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>3551</v>
+        <v>3611</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>551</v>
+        <v>611</v>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
@@ -12410,7 +12479,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 551 ud.</t>
+          <t>GESTIONAR EXTERNO 611 ud.</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12495,7 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>2334</v>
+        <v>2304</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>2.8</v>
@@ -12441,17 +12510,17 @@
         <v>3912.5</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>2747</v>
+        <v>2777</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>2747</v>
+        <v>2777</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 2747 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 2777 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr"/>
@@ -12594,10 +12663,10 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1583</v>
+        <v>1533</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="E45" s="4" t="n">
         <v>2974.1</v>
@@ -12609,13 +12678,13 @@
         <v>2932.9</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1391</v>
+        <v>1441</v>
       </c>
       <c r="I45" s="4" t="n">
         <v>1200</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -12624,7 +12693,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 191 ud.</t>
+          <t>GESTIONAR EXTERNO 241 ud.</t>
         </is>
       </c>
     </row>
@@ -12934,10 +13003,10 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>635</v>
+        <v>605</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E53" s="4" t="n">
         <v>1307.1</v>
@@ -12949,17 +13018,17 @@
         <v>1209.1</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>672</v>
+        <v>702</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>672</v>
+        <v>702</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 672 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 702 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr"/>
@@ -13358,10 +13427,10 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>286</v>
@@ -13373,17 +13442,17 @@
         <v>233.5</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 155 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 156 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr"/>
@@ -13400,7 +13469,7 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>3.5</v>
@@ -13415,17 +13484,17 @@
         <v>101.8</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 48 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 50 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr"/>
@@ -13442,10 +13511,10 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="E65" s="4" t="n">
         <v>95.40000000000001</v>
@@ -13457,17 +13526,17 @@
         <v>73.2</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 25 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 26 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr"/>
@@ -13736,7 +13805,7 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D72" s="10" t="n">
         <v>5.6</v>
@@ -13751,17 +13820,17 @@
         <v>53.6</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I72" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 8 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L72" s="9" t="inlineStr"/>
@@ -16217,7 +16286,7 @@
         </is>
       </c>
       <c r="C57" s="22" t="n">
-        <v>864</v>
+        <v>819</v>
       </c>
       <c r="D57" s="22" t="n">
         <v>0.5</v>
@@ -16232,14 +16301,14 @@
         <v>7709.4</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>16405</v>
+        <v>16450</v>
       </c>
       <c r="I57" s="22" t="n">
         <v>22400</v>
       </c>
       <c r="J57" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 16405 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 16450 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K57" s="21" t="inlineStr"/>
@@ -16256,7 +16325,7 @@
         </is>
       </c>
       <c r="C58" s="22" t="n">
-        <v>1558</v>
+        <v>1528</v>
       </c>
       <c r="D58" s="22" t="n">
         <v>1.7</v>
@@ -16271,14 +16340,14 @@
         <v>4584.8</v>
       </c>
       <c r="H58" s="22" t="n">
-        <v>8004</v>
+        <v>8034</v>
       </c>
       <c r="I58" s="22" t="n">
         <v>32580</v>
       </c>
       <c r="J58" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 8004 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 8034 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K58" s="21" t="inlineStr"/>
@@ -16334,10 +16403,10 @@
         </is>
       </c>
       <c r="C60" s="22" t="n">
-        <v>1165</v>
+        <v>1135</v>
       </c>
       <c r="D60" s="22" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E60" s="22" t="n">
         <v>4952</v>
@@ -16349,14 +16418,14 @@
         <v>2078.8</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>3787</v>
+        <v>3817</v>
       </c>
       <c r="I60" s="22" t="n">
         <v>20000</v>
       </c>
       <c r="J60" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3787 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3817 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K60" s="21" t="inlineStr"/>
@@ -16373,7 +16442,7 @@
         </is>
       </c>
       <c r="C61" s="22" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D61" s="22" t="n">
         <v>2.7</v>
@@ -16388,7 +16457,7 @@
         <v>233.5</v>
       </c>
       <c r="H61" s="22" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I61" s="22" t="n">
         <v>0</v>
@@ -16400,7 +16469,7 @@
       </c>
       <c r="K61" s="21" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 401 ud.</t>
+          <t>COMPRA EXTERNA 402 ud.</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16485,7 @@
         </is>
       </c>
       <c r="C62" s="22" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D62" s="22" t="n">
         <v>2.3</v>
@@ -16431,14 +16500,14 @@
         <v>73.2</v>
       </c>
       <c r="H62" s="22" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I62" s="22" t="n">
         <v>180</v>
       </c>
       <c r="J62" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 146 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 148 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K62" s="21" t="inlineStr"/>
@@ -16615,10 +16684,10 @@
         </is>
       </c>
       <c r="C67" s="26" t="n">
-        <v>828</v>
+        <v>798</v>
       </c>
       <c r="D67" s="26" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E67" s="26" t="n">
         <v>2661.7</v>
@@ -16630,14 +16699,14 @@
         <v>1209.1</v>
       </c>
       <c r="H67" s="26" t="n">
-        <v>1834</v>
+        <v>1864</v>
       </c>
       <c r="I67" s="26" t="n">
         <v>12600</v>
       </c>
       <c r="J67" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 1834 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1864 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K67" s="25" t="inlineStr"/>
@@ -16672,7 +16741,7 @@
         <v>1279</v>
       </c>
       <c r="I68" s="26" t="n">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="J68" s="25" t="inlineStr">
         <is>
@@ -16927,7 +16996,7 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>24735</v>
+        <v>24615</v>
       </c>
       <c r="D75" s="4" t="n">
         <v>6.8</v>
@@ -16942,14 +17011,14 @@
         <v>17908.4</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>15520</v>
+        <v>15640</v>
       </c>
       <c r="I75" s="4" t="n">
         <v>154000</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 15520 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 15640 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr"/>
@@ -16966,7 +17035,7 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>14206</v>
+        <v>14146</v>
       </c>
       <c r="D76" s="4" t="n">
         <v>6.7</v>
@@ -16981,7 +17050,7 @@
         <v>10399.6</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>9944</v>
+        <v>10004</v>
       </c>
       <c r="I76" s="4" t="n">
         <v>9600</v>
@@ -16993,7 +17062,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 344 ud.</t>
+          <t>COMPRA EXTERNA 404 ud.</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17117,7 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>7332</v>
+        <v>7302</v>
       </c>
       <c r="D78" s="4" t="n">
         <v>7</v>
@@ -17063,14 +17132,14 @@
         <v>5218.4</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>4397</v>
+        <v>4427</v>
       </c>
       <c r="I78" s="4" t="n">
         <v>10500</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 4397 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 4427 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr"/>
@@ -17087,7 +17156,7 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>7053</v>
+        <v>7023</v>
       </c>
       <c r="D79" s="4" t="n">
         <v>8.4</v>
@@ -17102,14 +17171,14 @@
         <v>3912.5</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>2411</v>
+        <v>2441</v>
       </c>
       <c r="I79" s="4" t="n">
         <v>37000</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 2411 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2441 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr"/>
@@ -17801,10 +17870,10 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="E97" s="4" t="n">
         <v>236.2</v>
@@ -17816,14 +17885,14 @@
         <v>101.8</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I97" s="4" t="n">
         <v>1864</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 84 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 86 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr"/>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="C43" s="22" t="n">
-        <v>1433</v>
+        <v>1313</v>
       </c>
       <c r="D43" s="22" t="n">
         <v>0.4</v>
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="C45" s="22" t="n">
-        <v>1765</v>
+        <v>1735</v>
       </c>
       <c r="D45" s="22" t="n">
         <v>0.9</v>
@@ -3301,13 +3301,13 @@
         <v>12125.8</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>3090</v>
+        <v>3120</v>
       </c>
       <c r="G45" s="22" t="n">
         <v>1200</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>1890</v>
+        <v>1920</v>
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="J45" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1890 ud.</t>
+          <t>GESTIONAR EXTERNO 1920 ud.</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="C47" s="22" t="n">
-        <v>1285</v>
+        <v>1255</v>
       </c>
       <c r="D47" s="22" t="n">
         <v>1</v>
@@ -3381,13 +3381,13 @@
         <v>7445.9</v>
       </c>
       <c r="F47" s="22" t="n">
-        <v>1662</v>
+        <v>1692</v>
       </c>
       <c r="G47" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>1662</v>
+        <v>1692</v>
       </c>
       <c r="I47" s="21" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="J47" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1662 ud.</t>
+          <t>GESTIONAR EXTERNO 1692 ud.</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="C53" s="22" t="n">
-        <v>1202</v>
+        <v>1172</v>
       </c>
       <c r="D53" s="22" t="n">
         <v>1.6</v>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="C74" s="22" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D74" s="22" t="n">
         <v>1.7</v>
@@ -4389,17 +4389,17 @@
         <v>296.8</v>
       </c>
       <c r="F74" s="22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G74" s="22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H74" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 33 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 34 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J74" s="21" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>3369</v>
+        <v>3339</v>
       </c>
       <c r="D84" s="4" t="n">
         <v>2.1</v>
@@ -4769,17 +4769,17 @@
         <v>9625.5</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="H84" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 276 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 306 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr"/>
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>2525</v>
+        <v>2497</v>
       </c>
       <c r="D87" s="4" t="n">
         <v>2.3</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D112" s="10" t="n">
         <v>5.3</v>
@@ -5805,17 +5805,17 @@
         <v>148.6</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G112" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H112" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR 33 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 34 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J112" s="9" t="inlineStr"/>
@@ -6186,7 +6186,7 @@
         <v>20420.1</v>
       </c>
       <c r="F3" s="20" t="n">
-        <v>17460</v>
+        <v>17490</v>
       </c>
       <c r="G3" s="20" t="n">
         <v>10980</v>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="I3" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 6480 ud.</t>
+          <t>COMPRA EXTERNA 6510 ud.</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
         <v>13092.7</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>11808</v>
+        <v>11838</v>
       </c>
       <c r="G5" s="20" t="n">
         <v>0</v>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 11808 ud.</t>
+          <t>COMPRA EXTERNA 11838 ud.</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
         <v>12892.4</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>9330</v>
+        <v>9360</v>
       </c>
       <c r="G6" s="20" t="n">
         <v>0</v>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 9330 ud.</t>
+          <t>COMPRA EXTERNA 9360 ud.</t>
         </is>
       </c>
     </row>
@@ -10010,14 +10010,14 @@
         <v>7352.8</v>
       </c>
       <c r="F111" s="22" t="n">
-        <v>3480</v>
+        <v>3540</v>
       </c>
       <c r="G111" s="22" t="n">
         <v>51840</v>
       </c>
       <c r="H111" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 3480 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3540 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I111" s="21" t="inlineStr"/>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="C119" s="22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D119" s="22" t="n">
         <v>0.3</v>
@@ -10286,7 +10286,7 @@
         <v>236.4</v>
       </c>
       <c r="F119" s="22" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G119" s="22" t="n">
         <v>0</v>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="I119" s="21" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 81 ud.</t>
+          <t>COMPRA EXTERNA 82 ud.</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>11724</v>
+        <v>11694</v>
       </c>
       <c r="D131" s="4" t="n">
         <v>7.4</v>
@@ -10694,14 +10694,14 @@
         <v>16650.6</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1282</v>
+        <v>1312</v>
       </c>
       <c r="G131" s="4" t="n">
         <v>62900</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1282 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1312 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr"/>
@@ -11023,16 +11023,16 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="E141" s="4" t="n">
         <v>492.5</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G141" s="4" t="n">
         <v>0</v>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 125 ud.</t>
+          <t>COMPRA EXTERNA 126 ud.</t>
         </is>
       </c>
     </row>
@@ -11751,7 +11751,7 @@
         </is>
       </c>
       <c r="C15" s="22" t="n">
-        <v>1433</v>
+        <v>1313</v>
       </c>
       <c r="D15" s="22" t="n">
         <v>0.4</v>
@@ -11766,17 +11766,17 @@
         <v>18163.4</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>20426</v>
+        <v>20546</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>20426</v>
+        <v>20546</v>
       </c>
       <c r="J15" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 20426 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 20546 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr"/>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="C17" s="22" t="n">
-        <v>1765</v>
+        <v>1735</v>
       </c>
       <c r="D17" s="22" t="n">
         <v>0.9</v>
@@ -11850,13 +11850,13 @@
         <v>9495.9</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>10361</v>
+        <v>10391</v>
       </c>
       <c r="I17" s="22" t="n">
         <v>1200</v>
       </c>
       <c r="J17" s="22" t="n">
-        <v>9161</v>
+        <v>9191</v>
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 9161 ud.</t>
+          <t>GESTIONAR EXTERNO 9191 ud.</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="C19" s="22" t="n">
-        <v>1285</v>
+        <v>1255</v>
       </c>
       <c r="D19" s="22" t="n">
         <v>1</v>
@@ -11942,13 +11942,13 @@
         <v>6180.7</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>6161</v>
+        <v>6191</v>
       </c>
       <c r="I19" s="22" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="22" t="n">
-        <v>6161</v>
+        <v>6191</v>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
       </c>
       <c r="L19" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 6161 ud.</t>
+          <t>GESTIONAR EXTERNO 6191 ud.</t>
         </is>
       </c>
     </row>
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>1202</v>
+        <v>1172</v>
       </c>
       <c r="D23" s="22" t="n">
         <v>1.6</v>
@@ -12122,13 +12122,13 @@
         <v>3645.9</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>3211</v>
+        <v>3241</v>
       </c>
       <c r="I23" s="22" t="n">
         <v>2700</v>
       </c>
       <c r="J23" s="22" t="n">
-        <v>511</v>
+        <v>541</v>
       </c>
       <c r="K23" s="21" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
       </c>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 511 ud.</t>
+          <t>GESTIONAR EXTERNO 541 ud.</t>
         </is>
       </c>
     </row>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="C37" s="22" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D37" s="22" t="n">
         <v>1.7</v>
@@ -12734,17 +12734,17 @@
         <v>239.5</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J37" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="21" t="inlineStr">
         <is>
-          <t>TRASPASAR 213 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 214 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L37" s="21" t="inlineStr"/>
@@ -12937,10 +12937,10 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>7080</v>
+        <v>7020</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E42" s="4" t="n">
         <v>13348.6</v>
@@ -12952,17 +12952,17 @@
         <v>10727</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>6269</v>
+        <v>6329</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>6269</v>
+        <v>6329</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 6269 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 6329 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr"/>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>3369</v>
+        <v>3339</v>
       </c>
       <c r="D44" s="4" t="n">
         <v>2.1</v>
@@ -13040,17 +13040,17 @@
         <v>7468.8</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>6256</v>
+        <v>6286</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>6256</v>
+        <v>6286</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 6256 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 6286 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr"/>
@@ -13151,7 +13151,7 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>3585</v>
+        <v>3555</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>3.2</v>
@@ -13166,13 +13166,13 @@
         <v>5599.7</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>3853</v>
+        <v>3883</v>
       </c>
       <c r="I47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>3853</v>
+        <v>3883</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3853 ud.</t>
+          <t>GESTIONAR EXTERNO 3883 ud.</t>
         </is>
       </c>
     </row>
@@ -13197,7 +13197,7 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>2525</v>
+        <v>2497</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>2.3</v>
@@ -13212,17 +13212,17 @@
         <v>5381.6</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>4017</v>
+        <v>4045</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>4017</v>
+        <v>4045</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 4017 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 4045 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr"/>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>976</v>
+        <v>962</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>3.2</v>
@@ -13594,17 +13594,17 @@
         <v>1516.9</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>897</v>
+        <v>911</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>897</v>
+        <v>911</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 897 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 911 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr"/>
@@ -17421,10 +17421,10 @@
         </is>
       </c>
       <c r="C68" s="22" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D68" s="22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E68" s="22" t="n">
         <v>492.5</v>
@@ -17581,7 +17581,7 @@
         </is>
       </c>
       <c r="C72" s="26" t="n">
-        <v>5744</v>
+        <v>5714</v>
       </c>
       <c r="D72" s="26" t="n">
         <v>3.6</v>
@@ -17596,14 +17596,14 @@
         <v>7468.8</v>
       </c>
       <c r="H72" s="26" t="n">
-        <v>10907</v>
+        <v>10937</v>
       </c>
       <c r="I72" s="26" t="n">
         <v>62900</v>
       </c>
       <c r="J72" s="25" t="inlineStr">
         <is>
-          <t>TRASPASAR 10907 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 10937 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K72" s="25" t="inlineStr"/>
@@ -17940,7 +17940,7 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>18574</v>
+        <v>18454</v>
       </c>
       <c r="D81" s="4" t="n">
         <v>5</v>
@@ -17955,14 +17955,14 @@
         <v>18163.4</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>20787</v>
+        <v>20907</v>
       </c>
       <c r="I81" s="4" t="n">
         <v>154000</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 20787 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 20907 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr"/>
@@ -17979,7 +17979,7 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>11131</v>
+        <v>11071</v>
       </c>
       <c r="D82" s="4" t="n">
         <v>5.1</v>
@@ -17994,7 +17994,7 @@
         <v>10727</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>12262</v>
+        <v>12322</v>
       </c>
       <c r="I82" s="4" t="n">
         <v>9600</v>
@@ -18006,7 +18006,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2662 ud.</t>
+          <t>COMPRA EXTERNA 2722 ud.</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18061,7 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>5983</v>
+        <v>5955</v>
       </c>
       <c r="D84" s="4" t="n">
         <v>5.5</v>
@@ -18076,14 +18076,14 @@
         <v>5381.6</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>5287</v>
+        <v>5315</v>
       </c>
       <c r="I84" s="4" t="n">
         <v>10500</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 5287 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 5315 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr"/>
@@ -18416,7 +18416,7 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>2503</v>
+        <v>2489</v>
       </c>
       <c r="D93" s="4" t="n">
         <v>8.199999999999999</v>
@@ -18431,14 +18431,14 @@
         <v>1516.9</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="I93" s="4" t="n">
         <v>5600</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 687 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 701 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr"/>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="C42" s="21" t="n">
-        <v>535</v>
+        <v>505</v>
       </c>
       <c r="D42" s="21" t="n">
         <v>0.9</v>
@@ -3151,26 +3151,26 @@
         </is>
       </c>
       <c r="C43" s="21" t="n">
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="D43" s="21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E43" s="21" t="n">
         <v>2707</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="H43" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 360 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 420 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J43" s="20" t="inlineStr"/>
@@ -4551,26 +4551,26 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>848</v>
+        <v>818</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E81" s="4" t="n">
         <v>2325.6</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H81" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr"/>
@@ -5984,7 +5984,7 @@
         <v>367.5</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G29" s="19" t="n">
         <v>100</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="I29" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 78 ud.</t>
+          <t>COMPRA EXTERNA 79 ud.</t>
         </is>
       </c>
     </row>
@@ -7886,23 +7886,23 @@
         </is>
       </c>
       <c r="C84" s="27" t="n">
-        <v>1470</v>
+        <v>1440</v>
       </c>
       <c r="D84" s="27" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="E84" s="27" t="n">
         <v>4311</v>
       </c>
       <c r="F84" s="27" t="n">
-        <v>1980</v>
+        <v>2010</v>
       </c>
       <c r="G84" s="27" t="n">
         <v>5940</v>
       </c>
       <c r="H84" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1980 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2010 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I84" s="26" t="inlineStr"/>
@@ -8117,23 +8117,23 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>4140</v>
+        <v>4080</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E91" s="4" t="n">
         <v>5313.5</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G91" s="4" t="n">
         <v>1320</v>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr"/>
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="C20" s="21" t="n">
-        <v>535</v>
+        <v>505</v>
       </c>
       <c r="D20" s="21" t="n">
         <v>0.9</v>
@@ -9285,17 +9285,17 @@
         <v>2778.6</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>2520</v>
+        <v>2580</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>2520</v>
+        <v>2580</v>
       </c>
       <c r="J20" s="21" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 2520 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 2580 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr"/>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E21" s="21" t="n">
         <v>2707</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3165</v>
+        <v>3135</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>2.7</v>
@@ -10600,10 +10600,10 @@
         </is>
       </c>
       <c r="C51" s="23" t="n">
-        <v>1017</v>
+        <v>987</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="E51" s="23" t="n">
         <v>1022.1</v>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -1779,7 +1779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3825,26 +3825,26 @@
         </is>
       </c>
       <c r="C52" s="23" t="n">
-        <v>2801</v>
+        <v>2155</v>
       </c>
       <c r="D52" s="23" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="E52" s="23" t="n">
         <v>9350.700000000001</v>
       </c>
       <c r="F52" s="23" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G52" s="23" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="H52" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 3000 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 4000 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J52" s="22" t="inlineStr"/>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="C53" s="23" t="n">
-        <v>1350</v>
+        <v>1320</v>
       </c>
       <c r="D53" s="23" t="n">
         <v>1.5</v>
@@ -3870,17 +3870,17 @@
         <v>3698.1</v>
       </c>
       <c r="F53" s="23" t="n">
-        <v>666</v>
+        <v>696</v>
       </c>
       <c r="G53" s="23" t="n">
-        <v>666</v>
+        <v>696</v>
       </c>
       <c r="H53" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 666 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 696 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J53" s="22" t="inlineStr"/>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="C54" s="23" t="n">
-        <v>932</v>
+        <v>782</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="E54" s="23" t="n">
         <v>4012</v>
@@ -3933,26 +3933,26 @@
         </is>
       </c>
       <c r="C55" s="23" t="n">
-        <v>1001</v>
+        <v>941</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="E55" s="23" t="n">
         <v>3818.6</v>
       </c>
       <c r="F55" s="23" t="n">
-        <v>562</v>
+        <v>622</v>
       </c>
       <c r="G55" s="23" t="n">
-        <v>562</v>
+        <v>622</v>
       </c>
       <c r="H55" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 562 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 622 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J55" s="22" t="inlineStr"/>
@@ -4005,26 +4005,26 @@
         </is>
       </c>
       <c r="C57" s="23" t="n">
-        <v>790</v>
+        <v>670</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="E57" s="23" t="n">
         <v>1805.6</v>
       </c>
       <c r="F57" s="23" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="G57" s="23" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H57" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 150 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J57" s="22" t="inlineStr"/>
@@ -4041,22 +4041,22 @@
         </is>
       </c>
       <c r="C58" s="23" t="n">
-        <v>630</v>
+        <v>510</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="E58" s="23" t="n">
         <v>1733.6</v>
       </c>
       <c r="F58" s="23" t="n">
-        <v>254</v>
+        <v>374</v>
       </c>
       <c r="G58" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="23" t="n">
-        <v>254</v>
+        <v>374</v>
       </c>
       <c r="I58" s="22" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="J58" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 254 ud.</t>
+          <t>GESTIONAR EXTERNO 374 ud.</t>
         </is>
       </c>
     </row>
@@ -4121,26 +4121,26 @@
         </is>
       </c>
       <c r="C60" s="23" t="n">
-        <v>356</v>
+        <v>296</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E60" s="23" t="n">
         <v>1065</v>
       </c>
       <c r="F60" s="23" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="G60" s="23" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="H60" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 79 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 139 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J60" s="22" t="inlineStr"/>
@@ -4157,26 +4157,26 @@
         </is>
       </c>
       <c r="C61" s="23" t="n">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E61" s="23" t="n">
         <v>876.4</v>
       </c>
       <c r="F61" s="23" t="n">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="G61" s="23" t="n">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="H61" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 267 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 281 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J61" s="22" t="inlineStr"/>
@@ -4193,22 +4193,22 @@
         </is>
       </c>
       <c r="C62" s="23" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D62" s="23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E62" s="23" t="n">
         <v>662.7</v>
       </c>
       <c r="F62" s="23" t="n">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="G62" s="23" t="n">
         <v>360</v>
       </c>
       <c r="H62" s="23" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I62" s="22" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="J62" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 30 ud.</t>
+          <t>GESTIONAR EXTERNO 90 ud.</t>
         </is>
       </c>
     </row>
@@ -4493,26 +4493,26 @@
         </is>
       </c>
       <c r="C70" s="23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D70" s="23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E70" s="23" t="n">
         <v>200.8</v>
       </c>
       <c r="F70" s="23" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G70" s="23" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H70" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 80 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J70" s="22" t="inlineStr"/>
@@ -4972,7 +4972,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>OLANZAPINA 10 MG CM UNIDAD</t>
+          <t>ENALAPRIL 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4981,26 +4981,26 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>460</v>
+        <v>698</v>
       </c>
       <c r="D83" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>876</v>
+        <v>1306.8</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H83" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 2000 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr"/>
@@ -5008,7 +5008,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>METFORMINA 850 MG COMPRIMIDO</t>
+          <t>OLANZAPINA 10 MG CM UNIDAD</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -5017,26 +5017,26 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>295</v>
+        <v>460</v>
       </c>
       <c r="D84" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>591.3</v>
+        <v>876</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>45</v>
+        <v>1000</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>45</v>
+        <v>1000</v>
       </c>
       <c r="H84" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 45 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1000 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr"/>
@@ -5044,7 +5044,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>ESZOPICLONA 3 MG COMPRIMIDO</t>
+          <t>METFORMINA 850 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -5053,26 +5053,26 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>176</v>
+        <v>295</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>340.5</v>
+        <v>591.3</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H85" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 45 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr"/>
@@ -5080,7 +5080,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>DONEPEZILO 10 MG COMPRIMIDO</t>
+          <t>ESZOPICLONA 3 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -5089,26 +5089,26 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="D86" s="4" t="n">
         <v>2.2</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>282.1</v>
+        <v>340.5</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H86" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 90 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr"/>
@@ -5116,7 +5116,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>CLOBAZAM 10 MG COMPRIMIDO</t>
+          <t>DONEPEZILO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -5125,38 +5125,34 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>98</v>
+        <v>282.1</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 34 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 90 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>PROPANOLOL 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -5165,38 +5161,34 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>107.5</v>
+        <v>203.8</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 62 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 50 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
+          <t>CLOBAZAM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5205,34 +5197,38 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J89" s="3" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 34 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
+          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -5241,34 +5237,38 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>18.6</v>
+        <v>107.5</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 4 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J90" s="3" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 62 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>BRIMONIDINA 0,2% (2 MG/ML) COLIRIO</t>
+          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -5277,26 +5277,26 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>5.3</v>
+        <v>48</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H91" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr"/>
@@ -5304,7 +5304,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -5313,38 +5313,34 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F92" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D92" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E92" s="4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F92" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="G92" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 3 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 4 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
+          <t>BRIMONIDINA 0,2% (2 MG/ML) COLIRIO</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -5353,128 +5349,204 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 470 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 3 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>470</v>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 470 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
           <t>METILPREDNISOLONA ACETATO 40 MG/ML IM INTRARTICULAR</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>3-MODERADO</t>
         </is>
       </c>
-      <c r="C94" s="4" t="n">
+      <c r="C96" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D94" s="4" t="n">
+      <c r="D96" s="4" t="n">
         <v>2.7</v>
       </c>
-      <c r="E94" s="4" t="n">
+      <c r="E96" s="4" t="n">
         <v>2.3</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="F96" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G96" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="H96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
         <is>
           <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="J94" s="3" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="11" t="inlineStr">
+      <c r="J96" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="12" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="13" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="14" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="15" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="15" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="16" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="16" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="17" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -5691,14 +5763,14 @@
         <v>4500.6</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>3800</v>
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 300 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 500 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr"/>
@@ -5724,7 +5796,7 @@
         <v>3053.1</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>2424</v>
+        <v>2544</v>
       </c>
       <c r="G7" s="21" t="n">
         <v>0</v>
@@ -5736,7 +5808,7 @@
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2424 ud.</t>
+          <t>COMPRA EXTERNA 2544 ud.</t>
         </is>
       </c>
     </row>
@@ -5979,14 +6051,14 @@
         <v>1130.8</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>720</v>
+        <v>780</v>
       </c>
       <c r="G14" s="21" t="n">
         <v>4710</v>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 720 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 780 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr"/>
@@ -6815,14 +6887,14 @@
         <v>284</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G38" s="21" t="n">
         <v>540</v>
       </c>
       <c r="H38" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 90 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I38" s="20" t="inlineStr"/>
@@ -8342,7 +8414,7 @@
         </is>
       </c>
       <c r="C82" s="23" t="n">
-        <v>1828</v>
+        <v>1798</v>
       </c>
       <c r="D82" s="23" t="n">
         <v>2</v>
@@ -8351,14 +8423,14 @@
         <v>7308.9</v>
       </c>
       <c r="F82" s="23" t="n">
-        <v>3465</v>
+        <v>3495</v>
       </c>
       <c r="G82" s="23" t="n">
         <v>14952</v>
       </c>
       <c r="H82" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 3465 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3495 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I82" s="22" t="inlineStr"/>
@@ -8417,14 +8489,14 @@
         <v>5466.1</v>
       </c>
       <c r="F84" s="23" t="n">
-        <v>3194</v>
+        <v>3254</v>
       </c>
       <c r="G84" s="23" t="n">
         <v>30630</v>
       </c>
       <c r="H84" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 3194 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3254 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I84" s="22" t="inlineStr"/>
@@ -8511,16 +8583,16 @@
         </is>
       </c>
       <c r="C87" s="23" t="n">
-        <v>521</v>
+        <v>461</v>
       </c>
       <c r="D87" s="23" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="E87" s="23" t="n">
         <v>2374.5</v>
       </c>
       <c r="F87" s="23" t="n">
-        <v>1419</v>
+        <v>1479</v>
       </c>
       <c r="G87" s="23" t="n">
         <v>0</v>
@@ -8532,7 +8604,7 @@
       </c>
       <c r="I87" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1419 ud.</t>
+          <t>COMPRA EXTERNA 1479 ud.</t>
         </is>
       </c>
     </row>
@@ -8684,23 +8756,23 @@
         </is>
       </c>
       <c r="C92" s="27" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="D92" s="27" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="E92" s="27" t="n">
         <v>17570.3</v>
       </c>
       <c r="F92" s="27" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G92" s="27" t="n">
         <v>200000</v>
       </c>
       <c r="H92" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2000 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I92" s="26" t="inlineStr"/>
@@ -8726,14 +8798,14 @@
         <v>5247.4</v>
       </c>
       <c r="F93" s="27" t="n">
-        <v>1020</v>
+        <v>1200</v>
       </c>
       <c r="G93" s="27" t="n">
         <v>3720</v>
       </c>
       <c r="H93" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1020 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1200 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I93" s="26" t="inlineStr"/>
@@ -8759,14 +8831,14 @@
         <v>4804.9</v>
       </c>
       <c r="F94" s="27" t="n">
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="G94" s="27" t="n">
         <v>17010</v>
       </c>
       <c r="H94" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 690 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 720 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I94" s="26" t="inlineStr"/>
@@ -8792,14 +8864,14 @@
         <v>4382.8</v>
       </c>
       <c r="F95" s="27" t="n">
-        <v>489</v>
+        <v>549</v>
       </c>
       <c r="G95" s="27" t="n">
         <v>7260</v>
       </c>
       <c r="H95" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 489 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 549 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I95" s="26" t="inlineStr"/>
@@ -8928,14 +9000,14 @@
         <v>1067.3</v>
       </c>
       <c r="F99" s="27" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G99" s="27" t="n">
         <v>3100</v>
       </c>
       <c r="H99" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 80 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 160 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I99" s="26" t="inlineStr"/>
@@ -9010,10 +9082,10 @@
         </is>
       </c>
       <c r="C102" s="29" t="n">
-        <v>8838</v>
+        <v>8778</v>
       </c>
       <c r="D102" s="29" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="E102" s="29" t="n">
         <v>7196.9</v>
@@ -9184,10 +9256,10 @@
         </is>
       </c>
       <c r="C108" s="29" t="n">
-        <v>5460</v>
+        <v>5340</v>
       </c>
       <c r="D108" s="29" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="E108" s="29" t="n">
         <v>3296.6</v>
@@ -9242,10 +9314,10 @@
         </is>
       </c>
       <c r="C110" s="29" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="D110" s="29" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="E110" s="29" t="n">
         <v>2605.1</v>
@@ -9561,10 +9633,10 @@
         </is>
       </c>
       <c r="C121" s="29" t="n">
-        <v>3813</v>
+        <v>3799</v>
       </c>
       <c r="D121" s="29" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="E121" s="29" t="n">
         <v>1725.5</v>
@@ -11417,10 +11489,10 @@
         </is>
       </c>
       <c r="C185" s="29" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="D185" s="29" t="n">
-        <v>22.5</v>
+        <v>21.3</v>
       </c>
       <c r="E185" s="29" t="n">
         <v>365.4</v>
@@ -11562,10 +11634,10 @@
         </is>
       </c>
       <c r="C190" s="29" t="n">
-        <v>1540</v>
+        <v>1520</v>
       </c>
       <c r="D190" s="29" t="n">
-        <v>44.5</v>
+        <v>43.9</v>
       </c>
       <c r="E190" s="29" t="n">
         <v>379.6</v>
@@ -16960,7 +17032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -17702,10 +17774,10 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>2801</v>
+        <v>2155</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>9350.700000000001</v>
@@ -17717,17 +17789,17 @@
         <v>11319.5</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="J17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 7000 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 8000 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr"/>
@@ -17744,7 +17816,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>1350</v>
+        <v>1320</v>
       </c>
       <c r="D18" s="23" t="n">
         <v>1.5</v>
@@ -17759,17 +17831,17 @@
         <v>4515.3</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>2349</v>
+        <v>2379</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>2349</v>
+        <v>2379</v>
       </c>
       <c r="J18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 2349 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 2379 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr"/>
@@ -17786,10 +17858,10 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>932</v>
+        <v>782</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="E19" s="23" t="n">
         <v>4012</v>
@@ -17801,20 +17873,24 @@
         <v>4204.5</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>3200</v>
+        <v>4000</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>3200</v>
+        <v>3700</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K19" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 3200 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L19" s="22" t="inlineStr"/>
+          <t>TRASPASAR 3700 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 300 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
@@ -17828,10 +17904,10 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>1001</v>
+        <v>941</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>3818.6</v>
@@ -17843,17 +17919,17 @@
         <v>4001.8</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>2818</v>
+        <v>2878</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>2818</v>
+        <v>2878</v>
       </c>
       <c r="J20" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 2818 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 2878 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr"/>
@@ -17870,10 +17946,10 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>790</v>
+        <v>670</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="E21" s="23" t="n">
         <v>1805.6</v>
@@ -17885,17 +17961,17 @@
         <v>2019.3</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>1020</v>
+        <v>1140</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>1020</v>
+        <v>1140</v>
       </c>
       <c r="J21" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1020 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1140 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr"/>
@@ -17912,10 +17988,10 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>630</v>
+        <v>510</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>1733.6</v>
@@ -17927,13 +18003,13 @@
         <v>1736.8</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>1104</v>
+        <v>1224</v>
       </c>
       <c r="I22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="23" t="n">
-        <v>1104</v>
+        <v>1224</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -17942,7 +18018,7 @@
       </c>
       <c r="L22" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1104 ud.</t>
+          <t>GESTIONAR EXTERNO 1224 ud.</t>
         </is>
       </c>
     </row>
@@ -18004,10 +18080,10 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>356</v>
+        <v>296</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E24" s="23" t="n">
         <v>1065</v>
@@ -18019,13 +18095,13 @@
         <v>1273.8</v>
       </c>
       <c r="H24" s="23" t="n">
-        <v>709</v>
+        <v>769</v>
       </c>
       <c r="I24" s="23" t="n">
         <v>600</v>
       </c>
       <c r="J24" s="23" t="n">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="K24" s="22" t="inlineStr">
         <is>
@@ -18034,7 +18110,7 @@
       </c>
       <c r="L24" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 109 ud.</t>
+          <t>GESTIONAR EXTERNO 169 ud.</t>
         </is>
       </c>
     </row>
@@ -18356,10 +18432,10 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2666</v>
+        <v>2486</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>4544.8</v>
@@ -18371,17 +18447,17 @@
         <v>4921</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 2000 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 2250 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr"/>
@@ -18398,10 +18474,10 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2165</v>
+        <v>2005</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>2730</v>
@@ -18440,10 +18516,10 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1543</v>
+        <v>1363</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="E34" s="4" t="n">
         <v>2698.6</v>
@@ -18455,17 +18531,17 @@
         <v>3049.3</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1170</v>
+        <v>1350</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1170</v>
+        <v>1350</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1170 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1350 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr"/>
@@ -18482,10 +18558,10 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1603</v>
+        <v>1573</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>2310.9</v>
@@ -18497,17 +18573,17 @@
         <v>2946.8</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 720 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 750 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr"/>
@@ -18524,10 +18600,10 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1599</v>
+        <v>1509</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="4" t="n">
         <v>1643.8</v>
@@ -18539,17 +18615,17 @@
         <v>1845.5</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 45 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 135 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr"/>
@@ -18566,10 +18642,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>758</v>
+        <v>698</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>1306.8</v>
@@ -18692,10 +18768,10 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>544</v>
+        <v>424</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>1107.6</v>
@@ -18707,17 +18783,17 @@
         <v>745.5</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 600 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 700 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr"/>
@@ -18864,10 +18940,10 @@
         </is>
       </c>
       <c r="C44" s="33" t="n">
-        <v>1205</v>
+        <v>1115</v>
       </c>
       <c r="D44" s="33" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="E44" s="33" t="n">
         <v>1268.4</v>
@@ -18879,17 +18955,17 @@
         <v>846.7</v>
       </c>
       <c r="H44" s="33" t="n">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="I44" s="33" t="n">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="J44" s="33" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="32" t="inlineStr">
         <is>
-          <t>TRASPASAR 64 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 154 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L44" s="32" t="inlineStr"/>
@@ -18936,64 +19012,110 @@
       </c>
       <c r="L45" s="32" t="inlineStr"/>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="inlineStr">
+        <is>
+          <t>4-BAJO</t>
+        </is>
+      </c>
+      <c r="C46" s="33" t="n">
+        <v>118</v>
+      </c>
+      <c r="D46" s="33" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E46" s="33" t="n">
+        <v>180</v>
+      </c>
+      <c r="F46" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="G46" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="H46" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="I46" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="K46" s="32" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L46" s="32" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 90 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
+          <t>MODERADO  —  reponer pronto (Farmacia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
+          <t>BAJO  —  vigilar (Farmacia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -19093,7 +19215,7 @@
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>PREGABALINA 75 MG CAPSULA</t>
+          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B3" s="20" t="inlineStr">
@@ -19108,35 +19230,31 @@
         <v>0</v>
       </c>
       <c r="E3" s="21" t="n">
-        <v>5885.5</v>
+        <v>7364</v>
       </c>
       <c r="F3" s="21" t="n">
-        <v>35.8</v>
+        <v>137.5</v>
       </c>
       <c r="G3" s="21" t="n">
-        <v>3544.2</v>
+        <v>4204.5</v>
       </c>
       <c r="H3" s="21" t="n">
-        <v>5886</v>
+        <v>3200</v>
       </c>
       <c r="I3" s="21" t="n">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="J3" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K3" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 5886 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 3200 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K3" s="20" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>VILDAGLIPTINA 50 MG CM</t>
+          <t>PREGABALINA 75 MG CAPSULA</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
@@ -19151,16 +19269,16 @@
         <v>0</v>
       </c>
       <c r="E4" s="21" t="n">
-        <v>4009.7</v>
+        <v>5885.5</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>5</v>
+        <v>35.8</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>2765.7</v>
+        <v>3544.2</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>4020</v>
+        <v>5886</v>
       </c>
       <c r="I4" s="21" t="n">
         <v>0</v>
@@ -19172,14 +19290,14 @@
       </c>
       <c r="K4" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 4020 ud.</t>
+          <t>COMPRA EXTERNA 5886 ud.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
+          <t>VILDAGLIPTINA 50 MG CM</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
@@ -19194,31 +19312,35 @@
         <v>0</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>4500.6</v>
+        <v>4009.7</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>62.5</v>
+        <v>5</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>2611.3</v>
+        <v>2765.7</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>300</v>
+        <v>4020</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="J5" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 300 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K5" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 4020 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>ISOSORBIDA DINITRATO 10 MG COMPRIMIDO</t>
+          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
@@ -19233,35 +19355,31 @@
         <v>0</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>3053.1</v>
+        <v>4500.6</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>124.8</v>
+        <v>62.5</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>1736.8</v>
+        <v>2611.3</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>2424</v>
+        <v>500</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="J6" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K6" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 2424 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 500 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>ESOMEPRAZOL 20 MG CM</t>
+          <t>ISOSORBIDA DINITRATO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
@@ -19276,16 +19394,16 @@
         <v>0</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>2777.1</v>
+        <v>3053.1</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>10</v>
+        <v>124.8</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>1846.3</v>
+        <v>1736.8</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>2714</v>
+        <v>2544</v>
       </c>
       <c r="I7" s="21" t="n">
         <v>0</v>
@@ -19297,14 +19415,14 @@
       </c>
       <c r="K7" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2714 ud.</t>
+          <t>COMPRA EXTERNA 2544 ud.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
+          <t>ESOMEPRAZOL 20 MG CM</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
@@ -19319,16 +19437,16 @@
         <v>0</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>2374.5</v>
+        <v>2777.1</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>1273.8</v>
+        <v>1846.3</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>1419</v>
+        <v>2714</v>
       </c>
       <c r="I8" s="21" t="n">
         <v>0</v>
@@ -19340,14 +19458,14 @@
       </c>
       <c r="K8" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1419 ud.</t>
+          <t>COMPRA EXTERNA 2714 ud.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>FLUOXETINA 20 MG COMPRIMIDO</t>
+          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -19362,31 +19480,35 @@
         <v>0</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>1908.2</v>
+        <v>2374.5</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>1074.2</v>
+        <v>1273.8</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>1920</v>
+        <v>1479</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1920 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K9" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1479 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
+          <t>FLUOXETINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -19401,35 +19523,31 @@
         <v>0</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>316</v>
+        <v>1908.2</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>222.5</v>
+        <v>1074.2</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>90</v>
+        <v>1920</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J10" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K10" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 90 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1920 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -19444,16 +19562,16 @@
         <v>0</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>244.1</v>
+        <v>316</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>147.7</v>
+        <v>222.5</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>245</v>
+        <v>90</v>
       </c>
       <c r="I11" s="21" t="n">
         <v>0</v>
@@ -19465,14 +19583,14 @@
       </c>
       <c r="K11" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 245 ud.</t>
+          <t>COMPRA EXTERNA 90 ud.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
+          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -19487,16 +19605,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>232.2</v>
+        <v>244.1</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>136.8</v>
+        <v>147.7</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="I12" s="21" t="n">
         <v>0</v>
@@ -19508,14 +19626,14 @@
       </c>
       <c r="K12" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 233 ud.</t>
+          <t>COMPRA EXTERNA 245 ud.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>CLORURO DE POTASIO 600 MG (POTASIO 8 MEQ) COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -19530,31 +19648,35 @@
         <v>0</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>54.9</v>
+        <v>232.2</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>113</v>
+        <v>136.8</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>55</v>
+        <v>233</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 55 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K13" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 233 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
+          <t>CLORURO DE POTASIO 600 MG (POTASIO 8 MEQ) COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
@@ -19569,23 +19691,23 @@
         <v>0</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>284</v>
+        <v>54.9</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>35</v>
+        <v>1.7</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>540</v>
+        <v>2000</v>
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 90 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 55 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr"/>
@@ -19593,7 +19715,7 @@
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -19608,35 +19730,31 @@
         <v>0</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>89.7</v>
+        <v>284</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="J15" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K15" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 90 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 180 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -19651,31 +19769,35 @@
         <v>0</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>46.7</v>
+        <v>89.7</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>31.7</v>
+        <v>2</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>11.7</v>
+        <v>49.8</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>7900</v>
+        <v>0</v>
       </c>
       <c r="J16" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K16" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 90 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -19690,19 +19812,19 @@
         <v>0</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>35</v>
+        <v>31.7</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>100</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>900</v>
+        <v>7900</v>
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
@@ -19714,7 +19836,7 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
@@ -19729,23 +19851,23 @@
         <v>0</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>36.6</v>
+        <v>46.6</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>11.5</v>
+        <v>35</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 33 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr"/>
@@ -19753,7 +19875,7 @@
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -19768,35 +19890,31 @@
         <v>0</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>60</v>
+        <v>36.6</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>20</v>
+        <v>18.8</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K19" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 60 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 33 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
@@ -19811,35 +19929,35 @@
         <v>0</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>35.3</v>
+        <v>60</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="G20" s="21" t="n">
         <v>20</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 40 ud.</t>
+          <t>COMPRA EXTERNA 60 ud.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -19854,31 +19972,35 @@
         <v>0</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>31.6</v>
+        <v>35.3</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>6.3</v>
+        <v>0.2</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>2600</v>
+        <v>60</v>
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 32 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K21" s="20" t="inlineStr"/>
+          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 40 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -19893,23 +20015,23 @@
         <v>0</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>21.9</v>
+        <v>31.6</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>10.8</v>
+        <v>12.5</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>5700</v>
+        <v>2600</v>
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 32 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr"/>
@@ -19917,7 +20039,7 @@
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
@@ -19932,23 +20054,23 @@
         <v>0</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>8.5</v>
+        <v>21.9</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>3400</v>
+        <v>5700</v>
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 9 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr"/>
@@ -19956,7 +20078,7 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
@@ -19971,23 +20093,23 @@
         <v>0</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>0.8</v>
+        <v>9.5</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>50</v>
+        <v>3400</v>
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 3 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 9 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr"/>
@@ -19995,7 +20117,7 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -20010,23 +20132,23 @@
         <v>0</v>
       </c>
       <c r="E25" s="21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G25" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="F25" s="21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G25" s="21" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>450</v>
+        <v>50</v>
       </c>
       <c r="J25" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr"/>
@@ -20034,7 +20156,7 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>ALTEPLASA 50 MG FA UD</t>
+          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
@@ -20049,10 +20171,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G26" s="21" t="n">
         <v>0</v>
@@ -20061,62 +20183,62 @@
         <v>1</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="J26" s="20" t="inlineStr">
         <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>ALTEPLASA 50 MG FA UD</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
           <t>SIN STOCK EN BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="K26" s="20" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>COMPRA EXTERNA 1 ud.</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="n">
-        <v>145</v>
-      </c>
-      <c r="D27" s="23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E27" s="23" t="n">
-        <v>7308.9</v>
-      </c>
-      <c r="F27" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="G27" s="23" t="n">
-        <v>4515.3</v>
-      </c>
-      <c r="H27" s="23" t="n">
-        <v>3465</v>
-      </c>
-      <c r="I27" s="23" t="n">
-        <v>14952</v>
-      </c>
-      <c r="J27" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 3465 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K27" s="22" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
+          <t>PARACETAMOL 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
@@ -20125,29 +20247,29 @@
         </is>
       </c>
       <c r="C28" s="23" t="n">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="E28" s="23" t="n">
-        <v>7364</v>
+        <v>17570.3</v>
       </c>
       <c r="F28" s="23" t="n">
-        <v>137.5</v>
+        <v>83.8</v>
       </c>
       <c r="G28" s="23" t="n">
-        <v>4204.5</v>
+        <v>11319.5</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>3200</v>
+        <v>2000</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>12800</v>
+        <v>200000</v>
       </c>
       <c r="J28" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 3200 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2000 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr"/>
@@ -20155,7 +20277,7 @@
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B29" s="22" t="inlineStr">
@@ -20164,29 +20286,29 @@
         </is>
       </c>
       <c r="C29" s="23" t="n">
-        <v>1530</v>
+        <v>115</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="E29" s="23" t="n">
-        <v>5247.4</v>
+        <v>7308.9</v>
       </c>
       <c r="F29" s="23" t="n">
-        <v>71.2</v>
+        <v>30</v>
       </c>
       <c r="G29" s="23" t="n">
-        <v>3049.3</v>
+        <v>4515.3</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>1020</v>
+        <v>3495</v>
       </c>
       <c r="I29" s="23" t="n">
-        <v>3720</v>
+        <v>14952</v>
       </c>
       <c r="J29" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1020 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3495 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr"/>
@@ -20194,80 +20316,80 @@
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>5247.4</v>
+      </c>
+      <c r="F30" s="23" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G30" s="23" t="n">
+        <v>3049.3</v>
+      </c>
+      <c r="H30" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I30" s="23" t="n">
+        <v>3720</v>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1200 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K30" s="22" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
           <t>SALMETEROL /FLUTICASONA 250 MG/25 MG INH UD</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C31" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D31" s="23" t="n">
         <v>2.6</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E31" s="23" t="n">
         <v>34.2</v>
       </c>
-      <c r="F30" s="23" t="n">
+      <c r="F31" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="G30" s="23" t="n">
+      <c r="G31" s="23" t="n">
         <v>18.8</v>
       </c>
-      <c r="H30" s="23" t="n">
+      <c r="H31" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="I30" s="23" t="n">
+      <c r="I31" s="23" t="n">
         <v>520</v>
       </c>
-      <c r="J30" s="22" t="inlineStr">
+      <c r="J31" s="22" t="inlineStr">
         <is>
           <t>TRASPASAR 4 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="K30" s="22" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="26" t="inlineStr">
-        <is>
-          <t>PARACETAMOL 500 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="inlineStr">
-        <is>
-          <t>3-ALTO</t>
-        </is>
-      </c>
-      <c r="C31" s="27" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D31" s="27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E31" s="27" t="n">
-        <v>17570.3</v>
-      </c>
-      <c r="F31" s="27" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="G31" s="27" t="n">
-        <v>11319.5</v>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>200000</v>
-      </c>
-      <c r="J31" s="26" t="inlineStr">
-        <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K31" s="26" t="inlineStr"/>
+      <c r="K31" s="22" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="26" t="inlineStr">
@@ -20281,7 +20403,7 @@
         </is>
       </c>
       <c r="C32" s="27" t="n">
-        <v>1800</v>
+        <v>1770</v>
       </c>
       <c r="D32" s="27" t="n">
         <v>3</v>
@@ -20296,14 +20418,14 @@
         <v>2946.8</v>
       </c>
       <c r="H32" s="27" t="n">
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>17010</v>
       </c>
       <c r="J32" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 690 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 720 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K32" s="26" t="inlineStr"/>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -1652,7 +1652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="C45" s="21" t="n">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="D45" s="21" t="n">
         <v>0.2</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="C46" s="21" t="n">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="D46" s="21" t="n">
         <v>0.4</v>
@@ -3463,17 +3463,17 @@
         <v>3730.2</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>1223</v>
+        <v>1253</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>1223</v>
+        <v>1253</v>
       </c>
       <c r="H46" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1223 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1253 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J46" s="20" t="inlineStr"/>
@@ -3526,26 +3526,26 @@
         </is>
       </c>
       <c r="C48" s="21" t="n">
-        <v>534</v>
+        <v>474</v>
       </c>
       <c r="D48" s="21" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E48" s="21" t="n">
         <v>2160.1</v>
       </c>
       <c r="F48" s="21" t="n">
-        <v>552</v>
+        <v>612</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>552</v>
+        <v>612</v>
       </c>
       <c r="H48" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 552 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 612 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J48" s="20" t="inlineStr"/>
@@ -3746,26 +3746,26 @@
         </is>
       </c>
       <c r="C54" s="21" t="n">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="D54" s="21" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="E54" s="21" t="n">
         <v>508.1</v>
       </c>
       <c r="F54" s="21" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H54" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 150 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J54" s="20" t="inlineStr"/>
@@ -3809,7 +3809,7 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>COLCHICINA 0,5 MG COMPRIMIDO</t>
+          <t>PREDNISONA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
@@ -3824,20 +3824,20 @@
         <v>0</v>
       </c>
       <c r="E56" s="21" t="n">
-        <v>135.7</v>
+        <v>221.5</v>
       </c>
       <c r="F56" s="21" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="G56" s="21" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="H56" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 78 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 100 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J56" s="20" t="inlineStr"/>
@@ -3845,7 +3845,7 @@
     <row r="57">
       <c r="A57" s="20" t="inlineStr">
         <is>
-          <t>SACUBITRILO VALSARTAN 100 MG</t>
+          <t>MULTIVITAMINICO COMPRIMIDO</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
@@ -3860,20 +3860,20 @@
         <v>0</v>
       </c>
       <c r="E57" s="21" t="n">
-        <v>83.90000000000001</v>
+        <v>119.8</v>
       </c>
       <c r="F57" s="21" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="G57" s="21" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="H57" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 56 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 120 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J57" s="20" t="inlineStr"/>
@@ -3881,7 +3881,7 @@
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>PREDNISONA 20 MG COMPRIMIDO</t>
+          <t>FENITOINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B58" s="20" t="inlineStr">
@@ -3896,20 +3896,20 @@
         <v>0</v>
       </c>
       <c r="E58" s="21" t="n">
-        <v>221.5</v>
+        <v>104.6</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G58" s="21" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H58" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 120 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J58" s="20" t="inlineStr"/>
@@ -3917,7 +3917,7 @@
     <row r="59">
       <c r="A59" s="20" t="inlineStr">
         <is>
-          <t>MULTIVITAMINICO COMPRIMIDO</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B59" s="20" t="inlineStr">
@@ -3926,26 +3926,26 @@
         </is>
       </c>
       <c r="C59" s="21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D59" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="21" t="n">
-        <v>119.8</v>
+        <v>30.5</v>
       </c>
       <c r="F59" s="21" t="n">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="G59" s="21" t="n">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="H59" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 120 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 22 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J59" s="20" t="inlineStr"/>
@@ -3953,7 +3953,7 @@
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>FENITOINA 100 MG COMPRIMIDO</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B60" s="20" t="inlineStr">
@@ -3962,34 +3962,38 @@
         </is>
       </c>
       <c r="C60" s="21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D60" s="21" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E60" s="21" t="n">
-        <v>104.6</v>
+        <v>16.3</v>
       </c>
       <c r="F60" s="21" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="G60" s="21" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H60" s="21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I60" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 120 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J60" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J60" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 7 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="20" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B61" s="20" t="inlineStr">
@@ -3998,34 +4002,38 @@
         </is>
       </c>
       <c r="C61" s="21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D61" s="21" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E61" s="21" t="n">
-        <v>30.5</v>
+        <v>21.4</v>
       </c>
       <c r="F61" s="21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G61" s="21" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H61" s="21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 22 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J61" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J61" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 20 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>VIGABATRINA 500 MG COMPRIMIDO</t>
+          <t>ACIDO ACETILSALICILICO CM 500 MG</t>
         </is>
       </c>
       <c r="B62" s="20" t="inlineStr">
@@ -4040,20 +4048,20 @@
         <v>0</v>
       </c>
       <c r="E62" s="21" t="n">
-        <v>77.40000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="F62" s="21" t="n">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="G62" s="21" t="n">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="H62" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 120 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 6 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J62" s="20" t="inlineStr"/>
@@ -4061,7 +4069,7 @@
     <row r="63">
       <c r="A63" s="20" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
@@ -4070,38 +4078,34 @@
         </is>
       </c>
       <c r="C63" s="21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63" s="21" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="E63" s="21" t="n">
-        <v>16.3</v>
+        <v>18.8</v>
       </c>
       <c r="F63" s="21" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G63" s="21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H63" s="21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I63" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J63" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 7 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 14 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J63" s="20" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B64" s="20" t="inlineStr">
@@ -4110,38 +4114,38 @@
         </is>
       </c>
       <c r="C64" s="21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D64" s="21" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="E64" s="21" t="n">
-        <v>21.4</v>
+        <v>17.3</v>
       </c>
       <c r="F64" s="21" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G64" s="21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H64" s="21" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I64" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
+          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J64" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 20 ud.</t>
+          <t>GESTIONAR EXTERNO 90 ud.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="20" t="inlineStr">
         <is>
-          <t>ACIDO ACETILSALICILICO CM 500 MG</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B65" s="20" t="inlineStr">
@@ -4150,34 +4154,38 @@
         </is>
       </c>
       <c r="C65" s="21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D65" s="21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E65" s="21" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="F65" s="21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G65" s="21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H65" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I65" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 6 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J65" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J65" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 2 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
+          <t>NORETISTERONA/ESTRADIOL 50/5MG JRP</t>
         </is>
       </c>
       <c r="B66" s="20" t="inlineStr">
@@ -4186,150 +4194,154 @@
         </is>
       </c>
       <c r="C66" s="21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D66" s="21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E66" s="21" t="n">
-        <v>18.8</v>
+        <v>0.1</v>
       </c>
       <c r="F66" s="21" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G66" s="21" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H66" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 14 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J66" s="20" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="20" t="inlineStr">
-        <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
-        </is>
-      </c>
-      <c r="B67" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C67" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="D67" s="21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E67" s="21" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="F67" s="21" t="n">
-        <v>100</v>
-      </c>
-      <c r="G67" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="H67" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="I67" s="20" t="inlineStr">
-        <is>
-          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J67" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 90 ud.</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>MESALAZINA 500 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>336</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>1378.9</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 200 ud.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="20" t="inlineStr">
-        <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
-        </is>
-      </c>
-      <c r="B68" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C68" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="D68" s="21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E68" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="F68" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G68" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I68" s="20" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>CLOBAZAM 10 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
-      <c r="J68" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 2 ud.</t>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 16 ud.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="20" t="inlineStr">
-        <is>
-          <t>NORETISTERONA/ESTRADIOL 50/5MG JRP</t>
-        </is>
-      </c>
-      <c r="B69" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C69" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F69" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="20" t="inlineStr">
-        <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J69" s="20" t="inlineStr"/>
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 60 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MESALAZINA 500 MG COMPRIMIDO</t>
+          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4338,38 +4350,34 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>336</v>
+        <v>30</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1378.9</v>
+        <v>46.5</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 200 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>CLOBAZAM 10 MG COMPRIMIDO</t>
+          <t>UMECLIDINIO/VILANTEROL 55/22 INH</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4378,38 +4386,34 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>79.2</v>
+        <v>8.5</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 16 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 4 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>FLUTICASONA 125 MCG INH UNIDAD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4418,38 +4422,34 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>105.9</v>
+        <v>3.9</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 60 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4458,34 +4458,38 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>46.5</v>
+        <v>5.7</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 3 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>UMECLIDINIO/VILANTEROL 55/22 INH</t>
+          <t>ALUMINIO HIDROXIDO GEL 6% 180 ML FC</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4494,26 +4498,26 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>8.5</v>
+        <v>3.1</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H74" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 4 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr"/>
@@ -4521,7 +4525,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>FLUTICASONA 125 MCG INH UNIDAD</t>
+          <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4530,34 +4534,38 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr"/>
+          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 470 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>METILPREDNISOLONA ACETATO 40 MG/ML IM INTRARTICULAR</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4566,240 +4574,124 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 3 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>ALUMINIO HIDROXIDO GEL 6% 180 ML FC</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="G78" s="4" t="n">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>4-BAJO</t>
+        </is>
+      </c>
+      <c r="C77" s="23" t="n">
+        <v>118</v>
+      </c>
+      <c r="D77" s="23" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E77" s="23" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="F77" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H78" s="4" t="n">
-        <v>470</v>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="G77" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="H77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="22" t="inlineStr">
         <is>
           <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 470 ud.</t>
-        </is>
-      </c>
+      <c r="J77" s="22" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>METILPREDNISOLONA ACETATO 40 MG/ML IM INTRARTICULAR</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F79" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G79" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J79" s="3" t="inlineStr"/>
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="22" t="inlineStr">
-        <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B80" s="22" t="inlineStr">
-        <is>
-          <t>4-BAJO</t>
-        </is>
-      </c>
-      <c r="C80" s="23" t="n">
-        <v>118</v>
-      </c>
-      <c r="D80" s="23" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E80" s="23" t="n">
-        <v>224.5</v>
-      </c>
-      <c r="F80" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="G80" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="H80" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J80" s="22" t="inlineStr"/>
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>CRITICO  —  sin stock ni respaldo</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>URGENTE  —  cobertura critica</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>LEYENDA DE COLORES</t>
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO  —  sin stock ni respaldo</t>
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>URGENTE  —  cobertura critica</t>
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="13" t="inlineStr">
-        <is>
-          <t>MODERADO  —  reponer pronto (Farmacia)</t>
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="13" t="inlineStr">
-        <is>
-          <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="14" t="inlineStr">
-        <is>
-          <t>BAJO  —  vigilar (Farmacia)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="14" t="inlineStr">
-        <is>
-          <t>BAJO  —  stock suficiente (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="15" t="inlineStr">
+      <c r="A87" s="15" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -5296,7 +5188,7 @@
         <v>1350</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G14" s="19" t="n">
         <v>0</v>
@@ -5308,7 +5200,7 @@
       </c>
       <c r="I14" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 120 ud.</t>
+          <t>COMPRA EXTERNA 150 ud.</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7473,7 @@
         <v>2972.5</v>
       </c>
       <c r="F79" s="21" t="n">
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="G79" s="21" t="n">
         <v>0</v>
@@ -7593,7 +7485,7 @@
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 870 ud.</t>
+          <t>COMPRA EXTERNA 900 ud.</t>
         </is>
       </c>
     </row>
@@ -7782,23 +7674,23 @@
         </is>
       </c>
       <c r="C85" s="27" t="n">
-        <v>1788</v>
+        <v>1728</v>
       </c>
       <c r="D85" s="27" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="E85" s="27" t="n">
         <v>4082.8</v>
       </c>
       <c r="F85" s="27" t="n">
-        <v>1209</v>
+        <v>1269</v>
       </c>
       <c r="G85" s="27" t="n">
         <v>7260</v>
       </c>
       <c r="H85" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1209 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1269 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I85" s="26" t="inlineStr"/>
@@ -7857,7 +7749,7 @@
         <v>1144</v>
       </c>
       <c r="F87" s="27" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G87" s="27" t="n">
         <v>0</v>
@@ -7869,7 +7761,7 @@
       </c>
       <c r="I87" s="26" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 120 ud.</t>
+          <t>COMPRA EXTERNA 180 ud.</t>
         </is>
       </c>
     </row>
@@ -8104,10 +7996,10 @@
         </is>
       </c>
       <c r="C95" s="29" t="n">
-        <v>8177</v>
+        <v>8147</v>
       </c>
       <c r="D95" s="29" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="E95" s="29" t="n">
         <v>6908.6</v>
@@ -9206,10 +9098,10 @@
         </is>
       </c>
       <c r="C133" s="29" t="n">
-        <v>2340</v>
+        <v>2250</v>
       </c>
       <c r="D133" s="29" t="n">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="E133" s="29" t="n">
         <v>1008.1</v>
@@ -10830,10 +10722,10 @@
         </is>
       </c>
       <c r="C189" s="29" t="n">
-        <v>522</v>
+        <v>0</v>
       </c>
       <c r="D189" s="29" t="n">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="E189" s="29" t="n">
         <v>232.8</v>
@@ -10888,10 +10780,10 @@
         </is>
       </c>
       <c r="C191" s="29" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="D191" s="29" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="E191" s="29" t="n">
         <v>124.3</v>
@@ -11990,10 +11882,10 @@
         </is>
       </c>
       <c r="C229" s="29" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D229" s="29" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="E229" s="29" t="n">
         <v>59.2</v>
@@ -12164,10 +12056,10 @@
         </is>
       </c>
       <c r="C235" s="29" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D235" s="29" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="E235" s="29" t="n">
         <v>100.7</v>
@@ -15975,7 +15867,7 @@
         <v>0</v>
       </c>
       <c r="G366" s="29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H366" s="28" t="inlineStr"/>
       <c r="I366" s="28" t="inlineStr"/>
@@ -17910,7 +17802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -18560,7 +18452,7 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="D15" s="21" t="n">
         <v>0.2</v>
@@ -18602,7 +18494,7 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="D16" s="21" t="n">
         <v>0.4</v>
@@ -18617,17 +18509,17 @@
         <v>4037.6</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>3400</v>
+        <v>3430</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>3400</v>
+        <v>3430</v>
       </c>
       <c r="J16" s="21" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 3400 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 3430 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr"/>
@@ -18686,7 +18578,7 @@
         </is>
       </c>
       <c r="C18" s="21" t="n">
-        <v>1093</v>
+        <v>1063</v>
       </c>
       <c r="D18" s="21" t="n">
         <v>1.8</v>
@@ -18701,17 +18593,17 @@
         <v>2939.4</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>1140</v>
+        <v>1170</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>1140</v>
+        <v>1170</v>
       </c>
       <c r="J18" s="21" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1140 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1170 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr"/>
@@ -19113,7 +19005,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
+          <t>OMEPRAZOL 20 MG CAPSULA</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -19122,32 +19014,32 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3044</v>
+        <v>4342</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3255.7</v>
+        <v>4371.4</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>29</v>
+        <v>159.7</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4518.1</v>
+        <v>4956.6</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 212 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 250 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr"/>
@@ -19155,7 +19047,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
+          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -19164,32 +19056,32 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3382</v>
+        <v>2999</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3840</v>
+        <v>3255.7</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>133.1</v>
+        <v>29</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4210.8</v>
+        <v>4518.1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>800</v>
+        <v>257</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>800</v>
+        <v>257</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 800 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 257 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr"/>
@@ -19197,7 +19089,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CELECOXIB 200 MG CAPSULA</t>
+          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -19206,32 +19098,32 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1431</v>
+        <v>3382</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2452.5</v>
+        <v>3840</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>16.8</v>
+        <v>133.1</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3261.9</v>
+        <v>4210.8</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 1500 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 800 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr"/>
@@ -19239,7 +19131,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CINTA PARA DETERMINACION GLICEMIA USO PACIENTE UD.</t>
+          <t>CELECOXIB 200 MG CAPSULA</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -19248,44 +19140,40 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1996</v>
+        <v>1421</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2277.2</v>
+        <v>2452.5</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.8</v>
+        <v>16.8</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3029.8</v>
+        <v>3261.9</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>282</v>
+        <v>1500</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 282 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1500 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
+          <t>CINTA PARA DETERMINACION GLICEMIA USO PACIENTE UD.</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -19294,40 +19182,44 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>970</v>
+        <v>1996</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1773.5</v>
+        <v>2277.2</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>38.7</v>
+        <v>4.8</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2070.6</v>
+        <v>3029.8</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>810</v>
+        <v>282</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 810 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 282 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>TRAMADOL + PARACETAMOL 37,5 MG/325 MG CM</t>
+          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -19336,32 +19228,32 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>989</v>
+        <v>970</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1487.3</v>
+        <v>1773.5</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>25</v>
+        <v>38.7</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1895.6</v>
+        <v>2070.6</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>499</v>
+        <v>810</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>499</v>
+        <v>810</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 499 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 810 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr"/>
@@ -19369,7 +19261,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
+          <t>TRAMADOL + PARACETAMOL 37,5 MG/325 MG CM</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -19378,44 +19270,40 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>596</v>
+        <v>929</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1082.7</v>
+        <v>1487.3</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.8</v>
+        <v>25</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1305.3</v>
+        <v>1895.6</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>487</v>
+        <v>559</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>487</v>
+        <v>0</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 487 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 559 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>FLUOXETINA 20 MG COMPRIMIDO</t>
+          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -19424,40 +19312,44 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>800</v>
+        <v>596</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>931</v>
+        <v>1082.7</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>14.5</v>
+        <v>4.8</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1078.2</v>
+        <v>1305.3</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>140</v>
+        <v>487</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 140 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 487 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>HIDRALAZINA 50 MG COMPRIMIDO</t>
+          <t>FLUOXETINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -19466,32 +19358,32 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>975</v>
+        <v>800</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1397.2</v>
+        <v>931</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>200.8</v>
+        <v>14.5</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>833.9</v>
+        <v>1078.2</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>423</v>
+        <v>140</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>423</v>
+        <v>140</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 423 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 140 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr"/>
@@ -19499,7 +19391,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>AMOXICILINA + AC. CLAVULANICO 500/125 MG CM</t>
+          <t>HIDRALAZINA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -19508,32 +19400,32 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>6</v>
+        <v>975</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>11.4</v>
+        <v>1397.2</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>9.4</v>
+        <v>200.8</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>4.2</v>
+        <v>833.9</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>6</v>
+        <v>423</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>6</v>
+        <v>423</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>TRASPASAR 6 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 423 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr"/>
@@ -19541,95 +19433,95 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t>AMOXICILINA + AC. CLAVULANICO 500/125 MG CM</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>TRASPASAR 6 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
           <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>3-MODERADO</t>
         </is>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C39" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D39" s="4" t="n">
         <v>2.6</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E39" s="4" t="n">
         <v>4.3</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F39" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>3.2</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="I39" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="J39" s="4" t="n">
         <v>470</v>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 470 ud.</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>METILDOPA 250 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>4-BAJO</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="n">
-        <v>924</v>
-      </c>
-      <c r="D39" s="23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E39" s="23" t="n">
-        <v>1269.1</v>
-      </c>
-      <c r="F39" s="23" t="n">
-        <v>154.8</v>
-      </c>
-      <c r="G39" s="23" t="n">
-        <v>755.3</v>
-      </c>
-      <c r="H39" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="I39" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="J39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 400 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L39" s="22" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>ACETATO DE CALCIO 667 MG CM UD</t>
+          <t>METILDOPA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
@@ -19638,32 +19530,32 @@
         </is>
       </c>
       <c r="C40" s="23" t="n">
-        <v>414</v>
+        <v>924</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="E40" s="23" t="n">
-        <v>805.4</v>
+        <v>1269.1</v>
       </c>
       <c r="F40" s="23" t="n">
-        <v>135.5</v>
+        <v>154.8</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>131.1</v>
+        <v>755.3</v>
       </c>
       <c r="H40" s="23" t="n">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="J40" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 392 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 400 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L40" s="22" t="inlineStr"/>
@@ -19671,103 +19563,145 @@
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
+          <t>ACETATO DE CALCIO 667 MG CM UD</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>4-BAJO</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="n">
+        <v>414</v>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E41" s="23" t="n">
+        <v>805.4</v>
+      </c>
+      <c r="F41" s="23" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>392</v>
+      </c>
+      <c r="I41" s="23" t="n">
+        <v>392</v>
+      </c>
+      <c r="J41" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 392 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L41" s="22" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
           <t>CINACALCET 30 MG COMPRIMIDO</t>
         </is>
       </c>
-      <c r="B41" s="22" t="inlineStr">
+      <c r="B42" s="22" t="inlineStr">
         <is>
           <t>4-BAJO</t>
         </is>
       </c>
-      <c r="C41" s="23" t="n">
+      <c r="C42" s="23" t="n">
         <v>118</v>
       </c>
-      <c r="D41" s="23" t="n">
+      <c r="D42" s="23" t="n">
         <v>6.1</v>
       </c>
-      <c r="E41" s="23" t="n">
+      <c r="E42" s="23" t="n">
         <v>224.5</v>
       </c>
-      <c r="F41" s="23" t="n">
+      <c r="F42" s="23" t="n">
         <v>33.9</v>
       </c>
-      <c r="G41" s="23" t="n">
+      <c r="G42" s="23" t="n">
         <v>62.9</v>
       </c>
-      <c r="H41" s="23" t="n">
+      <c r="H42" s="23" t="n">
         <v>120</v>
       </c>
-      <c r="I41" s="23" t="n">
+      <c r="I42" s="23" t="n">
         <v>120</v>
       </c>
-      <c r="J41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="22" t="inlineStr">
+      <c r="J42" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="22" t="inlineStr">
         <is>
           <t>TRASPASAR 120 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="L41" s="22" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="L42" s="22" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
+          <t>MODERADO  —  reponer pronto (Farmacia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
+          <t>BAJO  —  vigilar (Farmacia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -1652,7 +1652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2929,7 +2929,7 @@
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
+          <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
@@ -2938,26 +2938,26 @@
         </is>
       </c>
       <c r="C33" s="21" t="n">
-        <v>71</v>
+        <v>763</v>
       </c>
       <c r="D33" s="21" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="E33" s="21" t="n">
-        <v>3393.5</v>
+        <v>1992.9</v>
       </c>
       <c r="F33" s="21" t="n">
-        <v>1227</v>
+        <v>30</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>1227</v>
+        <v>30</v>
       </c>
       <c r="H33" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1227 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+          <t>ISOSORBIDA DINITRATO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
@@ -2974,34 +2974,38 @@
         </is>
       </c>
       <c r="C34" s="21" t="n">
-        <v>463</v>
+        <v>120</v>
       </c>
       <c r="D34" s="21" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="E34" s="21" t="n">
-        <v>2098.9</v>
+        <v>1231.1</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 360 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J34" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 343 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>ISOSORBIDA DINITRATO 10 MG COMPRIMIDO</t>
+          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -3010,22 +3014,22 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>120</v>
+        <v>356</v>
       </c>
       <c r="D35" s="21" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="E35" s="21" t="n">
-        <v>1231.1</v>
+        <v>984.3</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>343</v>
+        <v>37</v>
       </c>
       <c r="G35" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="21" t="n">
-        <v>343</v>
+        <v>37</v>
       </c>
       <c r="I35" s="20" t="inlineStr">
         <is>
@@ -3034,14 +3038,14 @@
       </c>
       <c r="J35" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 343 ud.</t>
+          <t>GESTIONAR EXTERNO 37 ud.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>PREDNISONA 5 MG COMPRIMIDO</t>
+          <t>CARVEDILOL 12,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
@@ -3050,26 +3054,26 @@
         </is>
       </c>
       <c r="C36" s="21" t="n">
-        <v>318</v>
+        <v>245</v>
       </c>
       <c r="D36" s="21" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E36" s="21" t="n">
-        <v>958</v>
+        <v>1152.5</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>61</v>
+        <v>180</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>61</v>
+        <v>180</v>
       </c>
       <c r="H36" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 61 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J36" s="20" t="inlineStr"/>
@@ -3077,7 +3081,7 @@
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>CARVEDILOL 12,5 MG COMPRIMIDO</t>
+          <t>METFORMINA 850 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -3086,26 +3090,26 @@
         </is>
       </c>
       <c r="C37" s="21" t="n">
-        <v>245</v>
+        <v>85</v>
       </c>
       <c r="D37" s="21" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E37" s="21" t="n">
-        <v>1152.5</v>
+        <v>393.6</v>
       </c>
       <c r="F37" s="21" t="n">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="G37" s="21" t="n">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="H37" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 73 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J37" s="20" t="inlineStr"/>
@@ -3113,7 +3117,7 @@
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>METFORMINA 850 MG COMPRIMIDO</t>
+          <t>MULTIVITAMINICO COMPRIMIDO</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
@@ -3122,26 +3126,26 @@
         </is>
       </c>
       <c r="C38" s="21" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="D38" s="21" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E38" s="21" t="n">
-        <v>393.6</v>
+        <v>131</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="H38" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 43 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 131 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J38" s="20" t="inlineStr"/>
@@ -3149,7 +3153,7 @@
     <row r="39">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>HIDROCLOROTIAZIDA 25 MG + TRIAMTERENO 50 MG COMPRIMIDO</t>
+          <t>POLIESTIRENO SULFONATO CALCICO 15 GR SO</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
@@ -3158,26 +3162,26 @@
         </is>
       </c>
       <c r="C39" s="21" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D39" s="21" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E39" s="21" t="n">
-        <v>264.9</v>
+        <v>93.8</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="G39" s="21" t="n">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="H39" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 28 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 94 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J39" s="20" t="inlineStr"/>
@@ -3185,7 +3189,7 @@
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>PREDNISONA 20 MG COMPRIMIDO</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
@@ -3194,26 +3198,26 @@
         </is>
       </c>
       <c r="C40" s="21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>218.6</v>
+        <v>25.6</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="H40" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 19 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J40" s="20" t="inlineStr"/>
@@ -3221,7 +3225,7 @@
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>MULTIVITAMINICO COMPRIMIDO</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -3230,34 +3234,38 @@
         </is>
       </c>
       <c r="C41" s="21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E41" s="21" t="n">
-        <v>131</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H41" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 131 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J41" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J41" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 2 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>FENITOINA 100 MG COMPRIMIDO</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
@@ -3266,34 +3274,38 @@
         </is>
       </c>
       <c r="C42" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E42" s="21" t="n">
-        <v>75.09999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 90 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J42" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J42" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 17 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>MESALAZINA 500 MG SUPOSITORIO.</t>
+          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -3302,26 +3314,26 @@
         </is>
       </c>
       <c r="C43" s="21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D43" s="21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E43" s="21" t="n">
-        <v>112.4</v>
+        <v>17.5</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="H43" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 200 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 13 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J43" s="20" t="inlineStr"/>
@@ -3329,7 +3341,7 @@
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>POLIESTIRENO SULFONATO CALCICO 15 GR SO</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
@@ -3338,230 +3350,230 @@
         </is>
       </c>
       <c r="C44" s="21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44" s="21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E44" s="21" t="n">
-        <v>93.8</v>
+        <v>13.1</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G44" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" s="21" t="n">
+        <v>90</v>
+      </c>
+      <c r="I44" s="20" t="inlineStr">
+        <is>
+          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J44" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 90 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 57 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>VITAMINA D3 50.000 UI SOBRE</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 6 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>AMANTADINA 100 MG CAPSULA</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 30 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F48" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="H44" s="21" t="n">
-        <v>34</v>
-      </c>
-      <c r="I44" s="20" t="inlineStr">
+      <c r="G48" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="J44" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 34 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="D45" s="21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E45" s="21" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="F45" s="21" t="n">
-        <v>19</v>
-      </c>
-      <c r="G45" s="21" t="n">
-        <v>19</v>
-      </c>
-      <c r="H45" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="20" t="inlineStr">
-        <is>
-          <t>TRASPASAR 19 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J45" s="20" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C46" s="21" t="n">
+      <c r="J48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D46" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E46" s="21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F46" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" s="20" t="inlineStr">
+      <c r="D49" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
-      <c r="J46" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 2 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C47" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" s="21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E47" s="21" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F47" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="G47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="I47" s="20" t="inlineStr">
-        <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J47" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 17 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="D48" s="21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E48" s="21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F48" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="G48" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="H48" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="20" t="inlineStr">
-        <is>
-          <t>TRASPASAR 13 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J48" s="20" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C49" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D49" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E49" s="21" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F49" s="21" t="n">
-        <v>100</v>
-      </c>
-      <c r="G49" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="H49" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="I49" s="20" t="inlineStr">
-        <is>
-          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J49" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 90 ud.</t>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 3 ud.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>MESALAZINA 500 MG COMPRIMIDO</t>
+          <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -3570,38 +3582,38 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>336</v>
+        <v>2</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1461.9</v>
+        <v>4.4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>300</v>
+        <v>470</v>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
+          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 300 ud.</t>
+          <t>GESTIONAR EXTERNO 470 ud.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400 MG COMPRIMIDO</t>
+          <t>METILPREDNISOLONA ACETATO 40 MG/ML IM INTRARTICULAR</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -3610,352 +3622,160 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>106.6</v>
+        <v>3.1</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="H51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 3 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="D52" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E52" s="6" t="n">
-        <v>103</v>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="G52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 57 ud.</t>
-        </is>
-      </c>
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>4-BAJO</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="n">
+        <v>118</v>
+      </c>
+      <c r="D52" s="23" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E52" s="23" t="n">
+        <v>243.8</v>
+      </c>
+      <c r="F52" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="G52" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="H52" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J52" s="22" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>VITAMINA D3 50.000 UI SOBRE</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E53" s="6" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 6 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D54" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" s="6" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr"/>
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>MESALAZINA 500 MG SUPOSITORIO.</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>4-BAJO</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D53" s="23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E53" s="23" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="F53" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G53" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H53" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 100 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J53" s="22" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 3 ud.</t>
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D56" s="6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>470</v>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 470 ud.</t>
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>METILPREDNISOLONA ACETATO 40 MG/ML IM INTRARTICULAR</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 3 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr"/>
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>URGENTE  —  cobertura critica</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="inlineStr">
-        <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B58" s="22" t="inlineStr">
-        <is>
-          <t>4-BAJO</t>
-        </is>
-      </c>
-      <c r="C58" s="23" t="n">
-        <v>118</v>
-      </c>
-      <c r="D58" s="23" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E58" s="23" t="n">
-        <v>243.8</v>
-      </c>
-      <c r="F58" s="23" t="n">
-        <v>60</v>
-      </c>
-      <c r="G58" s="23" t="n">
-        <v>60</v>
-      </c>
-      <c r="H58" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J58" s="22" t="inlineStr"/>
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>MODERADO  —  reponer pronto (Farmacia)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>LEYENDA DE COLORES</t>
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO  —  sin stock ni respaldo</t>
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>URGENTE  —  cobertura critica</t>
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>MODERADO  —  reponer pronto (Farmacia)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>BAJO  —  vigilar (Farmacia)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="14" t="inlineStr">
-        <is>
-          <t>BAJO  —  stock suficiente (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="15" t="inlineStr">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -4209,7 +4029,7 @@
         <v>2373</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>1957</v>
+        <v>2017</v>
       </c>
       <c r="G7" s="19" t="n">
         <v>0</v>
@@ -4221,7 +4041,7 @@
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1957 ud.</t>
+          <t>COMPRA EXTERNA 2017 ud.</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4159,7 @@
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>MESALAZINA 500 MG COMPRIMIDO</t>
+          <t>LAMOTRIGINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
@@ -4354,20 +4174,24 @@
         <v>0</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>1725.9</v>
+        <v>1003.6</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>1400</v>
+        <v>60</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>9900</v>
+        <v>0</v>
       </c>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 1400 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 60 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
@@ -4390,7 +4214,7 @@
         <v>695.6</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>0</v>
@@ -4402,7 +4226,7 @@
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 70 ud.</t>
+          <t>COMPRA EXTERNA 160 ud.</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4691,7 @@
         <v>84.90000000000001</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>0</v>
@@ -4879,7 +4703,7 @@
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 10 ud.</t>
+          <t>COMPRA EXTERNA 13 ud.</t>
         </is>
       </c>
     </row>
@@ -4978,14 +4802,14 @@
         <v>150.2</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>3210</v>
       </c>
       <c r="H28" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I28" s="18" t="inlineStr"/>
@@ -4993,7 +4817,7 @@
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>POLIESTIRENO SULFONATO CALCICO 15 GR SO</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
@@ -5008,17 +4832,17 @@
         <v>0</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>93.8</v>
+        <v>31.2</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>420</v>
+        <v>7900</v>
       </c>
       <c r="H29" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 34 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I29" s="18" t="inlineStr"/>
@@ -5026,7 +4850,7 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
@@ -5041,13 +4865,13 @@
         <v>0</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>31.2</v>
+        <v>43.7</v>
       </c>
       <c r="F30" s="19" t="n">
         <v>100</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>7900</v>
+        <v>900</v>
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
@@ -5059,7 +4883,7 @@
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
+          <t>MODAFINILO 200 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
@@ -5074,17 +4898,17 @@
         <v>0</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>43.7</v>
+        <v>56.2</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>900</v>
+        <v>570</v>
       </c>
       <c r="H31" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I31" s="18" t="inlineStr"/>
@@ -5092,7 +4916,7 @@
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>MODAFINILO 200 MG COMPRIMIDO</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
@@ -5107,25 +4931,29 @@
         <v>0</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>56.2</v>
+        <v>56.3</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="G32" s="19" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="H32" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I32" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 57 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
@@ -5140,29 +4968,25 @@
         <v>0</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>56.3</v>
+        <v>24.4</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="H33" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I33" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 57 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 21 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I33" s="18" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
@@ -5177,25 +5001,29 @@
         <v>0</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>24.4</v>
+        <v>37.4</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="H34" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 21 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I34" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 36 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
@@ -5210,10 +5038,10 @@
         <v>0</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>37.4</v>
+        <v>27.5</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G35" s="19" t="n">
         <v>0</v>
@@ -5225,14 +5053,14 @@
       </c>
       <c r="I35" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 36 ud.</t>
+          <t>COMPRA EXTERNA 28 ud.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
@@ -5247,29 +5075,25 @@
         <v>0</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>27.5</v>
+        <v>24.4</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="H36" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I36" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 28 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 25 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
@@ -5284,25 +5108,29 @@
         <v>0</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>24.4</v>
+        <v>26.2</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>2600</v>
+        <v>50</v>
       </c>
       <c r="H37" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 25 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I37" s="18" t="inlineStr"/>
+          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 50 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>APIXABAN 2,5 MG CM</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
@@ -5317,29 +5145,25 @@
         <v>0</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>26.2</v>
+        <v>37.5</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="H38" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I38" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 50 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>APIXABAN 2,5 MG CM</t>
+          <t>SALMETEROL /FLUTICASONA 250 MG/25 MG INH UD</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
@@ -5354,17 +5178,17 @@
         <v>0</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>37.5</v>
+        <v>31.9</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>300</v>
+        <v>520</v>
       </c>
       <c r="H39" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 4 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I39" s="18" t="inlineStr"/>
@@ -5372,7 +5196,7 @@
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>SALMETEROL /FLUTICASONA 250 MG/25 MG INH UD</t>
+          <t>FENTANILO 25 MCG/HORA PARCHE</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
@@ -5387,25 +5211,29 @@
         <v>0</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>31.9</v>
+        <v>40</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G40" s="19" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="H40" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 4 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I40" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 6 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>FENTANILO 25 MCG/HORA PARCHE</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
@@ -5420,29 +5248,25 @@
         <v>0</v>
       </c>
       <c r="E41" s="19" t="n">
-        <v>40</v>
+        <v>16.2</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="H41" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I41" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 6 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 12 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>RISPERIDONA 25 MG FA</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
@@ -5457,25 +5281,29 @@
         <v>0</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G42" s="19" t="n">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="H42" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 12 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I42" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 16 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>RISPERIDONA 25 MG FA</t>
+          <t>VASELINA SOLIDA UNGUENTO</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
@@ -5490,10 +5318,10 @@
         <v>0</v>
       </c>
       <c r="E43" s="19" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G43" s="19" t="n">
         <v>0</v>
@@ -5505,14 +5333,14 @@
       </c>
       <c r="I43" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 16 ud.</t>
+          <t>COMPRA EXTERNA 15 ud.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>VASELINA SOLIDA UNGUENTO</t>
+          <t>UREA 10% CREMA 20 GR</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
@@ -5527,10 +5355,10 @@
         <v>0</v>
       </c>
       <c r="E44" s="19" t="n">
-        <v>14.4</v>
+        <v>26.8</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G44" s="19" t="n">
         <v>0</v>
@@ -5542,14 +5370,14 @@
       </c>
       <c r="I44" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 15 ud.</t>
+          <t>COMPRA EXTERNA 27 ud.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>UREA 10% CREMA 20 GR</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
@@ -5564,29 +5392,25 @@
         <v>0</v>
       </c>
       <c r="E45" s="19" t="n">
-        <v>26.8</v>
+        <v>6.2</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="H45" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I45" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 27 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 7 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
@@ -5601,25 +5425,29 @@
         <v>0</v>
       </c>
       <c r="E46" s="19" t="n">
-        <v>6.2</v>
+        <v>25.6</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G46" s="19" t="n">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H46" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 7 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I46" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 16 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
@@ -5634,10 +5462,10 @@
         <v>0</v>
       </c>
       <c r="E47" s="19" t="n">
-        <v>25.6</v>
+        <v>13.8</v>
       </c>
       <c r="F47" s="19" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G47" s="19" t="n">
         <v>0</v>
@@ -5649,14 +5477,14 @@
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 16 ud.</t>
+          <t>COMPRA EXTERNA 12 ud.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
@@ -5671,10 +5499,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="19" t="n">
-        <v>13.8</v>
+        <v>3.8</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G48" s="19" t="n">
         <v>0</v>
@@ -5686,14 +5514,14 @@
       </c>
       <c r="I48" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 12 ud.</t>
+          <t>COMPRA EXTERNA 4 ud.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
@@ -5708,29 +5536,25 @@
         <v>0</v>
       </c>
       <c r="E49" s="19" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G49" s="19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H49" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I49" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 4 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
@@ -5745,25 +5569,29 @@
         <v>0</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" s="19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H50" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I50" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 3 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
+          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
         </is>
       </c>
       <c r="B51" s="18" t="inlineStr">
@@ -5800,7 +5628,7 @@
     <row r="52">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
+          <t>ETONOGESTREL 68 MG IMPLANTE</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
@@ -5815,29 +5643,25 @@
         <v>0</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G52" s="19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H52" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I52" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 3 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>ETONOGESTREL 68 MG IMPLANTE</t>
+          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
         </is>
       </c>
       <c r="B53" s="18" t="inlineStr">
@@ -5858,7 +5682,7 @@
         <v>2</v>
       </c>
       <c r="G53" s="19" t="n">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
@@ -5870,7 +5694,7 @@
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
+          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
@@ -5891,7 +5715,7 @@
         <v>2</v>
       </c>
       <c r="G54" s="19" t="n">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="H54" s="18" t="inlineStr">
         <is>
@@ -5903,7 +5727,7 @@
     <row r="55">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
+          <t>ALTEPLASA 50 MG FA UD</t>
         </is>
       </c>
       <c r="B55" s="18" t="inlineStr">
@@ -5918,25 +5742,29 @@
         <v>0</v>
       </c>
       <c r="E55" s="19" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F55" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" s="19" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="H55" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I55" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>ALTEPLASA 50 MG FA UD</t>
+          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
         </is>
       </c>
       <c r="B56" s="18" t="inlineStr">
@@ -5957,23 +5785,19 @@
         <v>1</v>
       </c>
       <c r="G56" s="19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H56" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I56" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
+          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B57" s="18" t="inlineStr">
@@ -5994,7 +5818,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
@@ -6006,7 +5830,7 @@
     <row r="58">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
+          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
         </is>
       </c>
       <c r="B58" s="18" t="inlineStr">
@@ -6027,7 +5851,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="19" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="H58" s="18" t="inlineStr">
         <is>
@@ -6039,7 +5863,7 @@
     <row r="59">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+          <t>SALMETEROL Y FLUTICASONA 250 MG/25 MG INH UD</t>
         </is>
       </c>
       <c r="B59" s="18" t="inlineStr">
@@ -6060,56 +5884,60 @@
         <v>1</v>
       </c>
       <c r="G59" s="19" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H59" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I59" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I59" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
-        <is>
-          <t>SALMETEROL Y FLUTICASONA 250 MG/25 MG INH UD</t>
-        </is>
-      </c>
-      <c r="B60" s="18" t="inlineStr">
-        <is>
-          <t>1-CRITICO</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F60" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="18" t="inlineStr">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>PREGABALINA 75 MG CAPSULA</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>960</v>
+      </c>
+      <c r="D60" s="21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E60" s="21" t="n">
+        <v>5296.4</v>
+      </c>
+      <c r="F60" s="21" t="n">
+        <v>249</v>
+      </c>
+      <c r="G60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="20" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="I60" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
+      <c r="I60" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 249 ud.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="20" t="inlineStr">
         <is>
-          <t>PREGABALINA 75 MG CAPSULA</t>
+          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
         </is>
       </c>
       <c r="B61" s="20" t="inlineStr">
@@ -6118,16 +5946,16 @@
         </is>
       </c>
       <c r="C61" s="21" t="n">
-        <v>960</v>
+        <v>240</v>
       </c>
       <c r="D61" s="21" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="E61" s="21" t="n">
-        <v>5296.4</v>
+        <v>2702.1</v>
       </c>
       <c r="F61" s="21" t="n">
-        <v>179</v>
+        <v>810</v>
       </c>
       <c r="G61" s="21" t="n">
         <v>0</v>
@@ -6139,14 +5967,14 @@
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 179 ud.</t>
+          <t>COMPRA EXTERNA 810 ud.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
+          <t>HIDROXICLOROQUINA CM 200 MG</t>
         </is>
       </c>
       <c r="B62" s="20" t="inlineStr">
@@ -6155,35 +5983,31 @@
         </is>
       </c>
       <c r="C62" s="21" t="n">
-        <v>1140</v>
+        <v>1200</v>
       </c>
       <c r="D62" s="21" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="E62" s="21" t="n">
-        <v>2702.1</v>
+        <v>3223.6</v>
       </c>
       <c r="F62" s="21" t="n">
-        <v>780</v>
+        <v>240</v>
       </c>
       <c r="G62" s="21" t="n">
-        <v>0</v>
+        <v>45840</v>
       </c>
       <c r="H62" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I62" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 780 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 240 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I62" s="20" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="20" t="inlineStr">
         <is>
-          <t>HIDROXICLOROQUINA CM 200 MG</t>
+          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
@@ -6192,31 +6016,35 @@
         </is>
       </c>
       <c r="C63" s="21" t="n">
-        <v>1200</v>
+        <v>504</v>
       </c>
       <c r="D63" s="21" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="E63" s="21" t="n">
-        <v>3223.6</v>
+        <v>1414.9</v>
       </c>
       <c r="F63" s="21" t="n">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="G63" s="21" t="n">
-        <v>45840</v>
+        <v>0</v>
       </c>
       <c r="H63" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 180 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I63" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I63" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 128 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
+          <t>RIFAXIMINA 200 MG CP</t>
         </is>
       </c>
       <c r="B64" s="20" t="inlineStr">
@@ -6225,30 +6053,26 @@
         </is>
       </c>
       <c r="C64" s="21" t="n">
-        <v>504</v>
+        <v>240</v>
       </c>
       <c r="D64" s="21" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="E64" s="21" t="n">
-        <v>1414.9</v>
+        <v>619.6</v>
       </c>
       <c r="F64" s="21" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="G64" s="21" t="n">
-        <v>0</v>
+        <v>23640</v>
       </c>
       <c r="H64" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I64" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 128 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 192 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I64" s="20" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="20" t="inlineStr">
@@ -6290,7 +6114,7 @@
     <row r="66">
       <c r="A66" s="26" t="inlineStr">
         <is>
-          <t>LAMOTRIGINA 100 MG COMPRIMIDO</t>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
         </is>
       </c>
       <c r="B66" s="26" t="inlineStr">
@@ -6299,30 +6123,26 @@
         </is>
       </c>
       <c r="C66" s="27" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="D66" s="27" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="E66" s="27" t="n">
-        <v>1003.6</v>
+        <v>4687.9</v>
       </c>
       <c r="F66" s="27" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="G66" s="27" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="H66" s="26" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I66" s="26" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 60 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 330 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I66" s="26" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="26" t="inlineStr">
@@ -6360,7 +6180,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+          <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -6369,64 +6189,60 @@
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>3540</v>
+        <v>3690</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>4687.9</v>
+        <v>4558.7</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>330</v>
+        <v>90</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>2520</v>
+        <v>15810</v>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 330 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 90 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>4-MODERADO</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="n">
-        <v>3720</v>
-      </c>
-      <c r="D69" s="6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>4558.7</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G69" s="6" t="n">
-        <v>15810</v>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr"/>
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>PARACETAMOL 500 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B69" s="28" t="inlineStr">
+        <is>
+          <t>5-OK</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D69" s="29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E69" s="29" t="n">
+        <v>14918.7</v>
+      </c>
+      <c r="F69" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="29" t="n">
+        <v>190000</v>
+      </c>
+      <c r="H69" s="28" t="inlineStr"/>
+      <c r="I69" s="28" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="28" t="inlineStr">
         <is>
-          <t>PARACETAMOL 500 MG COMPRIMIDO</t>
+          <t>LOSARTAN 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B70" s="28" t="inlineStr">
@@ -6435,19 +6251,19 @@
         </is>
       </c>
       <c r="C70" s="29" t="n">
-        <v>16000</v>
+        <v>5700</v>
       </c>
       <c r="D70" s="29" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="E70" s="29" t="n">
-        <v>14918.7</v>
+        <v>8637.1</v>
       </c>
       <c r="F70" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="29" t="n">
-        <v>190000</v>
+        <v>32400</v>
       </c>
       <c r="H70" s="28" t="inlineStr"/>
       <c r="I70" s="28" t="inlineStr"/>
@@ -6455,7 +6271,7 @@
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>LOSARTAN 50 MG COMPRIMIDO</t>
+          <t>OMEPRAZOL 20 MG CAPSULA</t>
         </is>
       </c>
       <c r="B71" s="28" t="inlineStr">
@@ -6464,19 +6280,19 @@
         </is>
       </c>
       <c r="C71" s="29" t="n">
-        <v>5700</v>
+        <v>7550</v>
       </c>
       <c r="D71" s="29" t="n">
-        <v>4.6</v>
+        <v>7.3</v>
       </c>
       <c r="E71" s="29" t="n">
-        <v>8637.1</v>
+        <v>8132.9</v>
       </c>
       <c r="F71" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G71" s="29" t="n">
-        <v>32400</v>
+        <v>53000</v>
       </c>
       <c r="H71" s="28" t="inlineStr"/>
       <c r="I71" s="28" t="inlineStr"/>
@@ -6484,7 +6300,7 @@
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20 MG CAPSULA</t>
+          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
@@ -6493,19 +6309,19 @@
         </is>
       </c>
       <c r="C72" s="29" t="n">
-        <v>7550</v>
+        <v>4928</v>
       </c>
       <c r="D72" s="29" t="n">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="E72" s="29" t="n">
-        <v>8132.9</v>
+        <v>6521.9</v>
       </c>
       <c r="F72" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="29" t="n">
-        <v>53000</v>
+        <v>10024</v>
       </c>
       <c r="H72" s="28" t="inlineStr"/>
       <c r="I72" s="28" t="inlineStr"/>
@@ -6513,7 +6329,7 @@
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
+          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B73" s="28" t="inlineStr">
@@ -6522,19 +6338,19 @@
         </is>
       </c>
       <c r="C73" s="29" t="n">
-        <v>4928</v>
+        <v>4800</v>
       </c>
       <c r="D73" s="29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="E73" s="29" t="n">
-        <v>6521.9</v>
+        <v>6394.3</v>
       </c>
       <c r="F73" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="29" t="n">
-        <v>10024</v>
+        <v>8000</v>
       </c>
       <c r="H73" s="28" t="inlineStr"/>
       <c r="I73" s="28" t="inlineStr"/>
@@ -6542,7 +6358,7 @@
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
+          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
         </is>
       </c>
       <c r="B74" s="28" t="inlineStr">
@@ -6551,19 +6367,19 @@
         </is>
       </c>
       <c r="C74" s="29" t="n">
-        <v>4800</v>
+        <v>6400</v>
       </c>
       <c r="D74" s="29" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="E74" s="29" t="n">
-        <v>6394.3</v>
+        <v>6398.7</v>
       </c>
       <c r="F74" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="29" t="n">
-        <v>8000</v>
+        <v>45000</v>
       </c>
       <c r="H74" s="28" t="inlineStr"/>
       <c r="I74" s="28" t="inlineStr"/>
@@ -6571,7 +6387,7 @@
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
         <is>
-          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
+          <t>CALCIO CARBONATO C/VITAMINA D CM O CP</t>
         </is>
       </c>
       <c r="B75" s="28" t="inlineStr">
@@ -6580,19 +6396,19 @@
         </is>
       </c>
       <c r="C75" s="29" t="n">
-        <v>8173</v>
+        <v>10850</v>
       </c>
       <c r="D75" s="29" t="n">
-        <v>9.699999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="E75" s="29" t="n">
-        <v>6398.7</v>
+        <v>6609.6</v>
       </c>
       <c r="F75" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="29" t="n">
-        <v>45000</v>
+        <v>92100</v>
       </c>
       <c r="H75" s="28" t="inlineStr"/>
       <c r="I75" s="28" t="inlineStr"/>
@@ -6600,7 +6416,7 @@
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>CALCIO CARBONATO C/VITAMINA D CM O CP</t>
+          <t>METFORMINA 1000 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B76" s="28" t="inlineStr">
@@ -6609,19 +6425,19 @@
         </is>
       </c>
       <c r="C76" s="29" t="n">
-        <v>10850</v>
+        <v>4000</v>
       </c>
       <c r="D76" s="29" t="n">
-        <v>13.9</v>
+        <v>5.9</v>
       </c>
       <c r="E76" s="29" t="n">
-        <v>6609.6</v>
+        <v>4522.4</v>
       </c>
       <c r="F76" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="29" t="n">
-        <v>92100</v>
+        <v>9500</v>
       </c>
       <c r="H76" s="28" t="inlineStr"/>
       <c r="I76" s="28" t="inlineStr"/>
@@ -6629,7 +6445,7 @@
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
         <is>
-          <t>METFORMINA 1000 MG CM LIBERACION MODIFICADA</t>
+          <t>DABIGATRAN ETEXILATO CP 150 MG</t>
         </is>
       </c>
       <c r="B77" s="28" t="inlineStr">
@@ -6638,19 +6454,19 @@
         </is>
       </c>
       <c r="C77" s="29" t="n">
-        <v>4000</v>
+        <v>5190</v>
       </c>
       <c r="D77" s="29" t="n">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
       <c r="E77" s="29" t="n">
-        <v>4522.4</v>
+        <v>4878.7</v>
       </c>
       <c r="F77" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="29" t="n">
-        <v>9500</v>
+        <v>24420</v>
       </c>
       <c r="H77" s="28" t="inlineStr"/>
       <c r="I77" s="28" t="inlineStr"/>
@@ -6658,7 +6474,7 @@
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
         <is>
-          <t>DABIGATRAN ETEXILATO CP 150 MG</t>
+          <t>CELECOXIB 200 MG CAPSULA</t>
         </is>
       </c>
       <c r="B78" s="28" t="inlineStr">
@@ -6667,19 +6483,19 @@
         </is>
       </c>
       <c r="C78" s="29" t="n">
-        <v>5190</v>
+        <v>1000</v>
       </c>
       <c r="D78" s="29" t="n">
-        <v>7.7</v>
+        <v>1.5</v>
       </c>
       <c r="E78" s="29" t="n">
-        <v>4878.7</v>
+        <v>4666.3</v>
       </c>
       <c r="F78" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="29" t="n">
-        <v>24420</v>
+        <v>22500</v>
       </c>
       <c r="H78" s="28" t="inlineStr"/>
       <c r="I78" s="28" t="inlineStr"/>
@@ -6687,7 +6503,7 @@
     <row r="79">
       <c r="A79" s="28" t="inlineStr">
         <is>
-          <t>CELECOXIB 200 MG CAPSULA</t>
+          <t>ATORVASTATINA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B79" s="28" t="inlineStr">
@@ -6696,19 +6512,19 @@
         </is>
       </c>
       <c r="C79" s="29" t="n">
-        <v>1500</v>
+        <v>4520</v>
       </c>
       <c r="D79" s="29" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="E79" s="29" t="n">
-        <v>4666.3</v>
+        <v>4323.7</v>
       </c>
       <c r="F79" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="29" t="n">
-        <v>22500</v>
+        <v>11700</v>
       </c>
       <c r="H79" s="28" t="inlineStr"/>
       <c r="I79" s="28" t="inlineStr"/>
@@ -6716,7 +6532,7 @@
     <row r="80">
       <c r="A80" s="28" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 40 MG COMPRIMIDO</t>
+          <t>CINTA PARA DETERMINACION GLICEMIA USO PACIENTE UD.</t>
         </is>
       </c>
       <c r="B80" s="28" t="inlineStr">
@@ -6725,19 +6541,19 @@
         </is>
       </c>
       <c r="C80" s="29" t="n">
-        <v>4520</v>
+        <v>5000</v>
       </c>
       <c r="D80" s="29" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E80" s="29" t="n">
-        <v>4323.7</v>
+        <v>4160.5</v>
       </c>
       <c r="F80" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="29" t="n">
-        <v>11700</v>
+        <v>0</v>
       </c>
       <c r="H80" s="28" t="inlineStr"/>
       <c r="I80" s="28" t="inlineStr"/>
@@ -6745,7 +6561,7 @@
     <row r="81">
       <c r="A81" s="28" t="inlineStr">
         <is>
-          <t>CINTA PARA DETERMINACION GLICEMIA USO PACIENTE UD.</t>
+          <t>DABIGATRAN ETEXILATO CP 110 MG</t>
         </is>
       </c>
       <c r="B81" s="28" t="inlineStr">
@@ -6754,19 +6570,19 @@
         </is>
       </c>
       <c r="C81" s="29" t="n">
-        <v>5000</v>
+        <v>3840</v>
       </c>
       <c r="D81" s="29" t="n">
-        <v>8.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="E81" s="29" t="n">
-        <v>4160.5</v>
+        <v>3623.7</v>
       </c>
       <c r="F81" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="29" t="n">
-        <v>0</v>
+        <v>4260</v>
       </c>
       <c r="H81" s="28" t="inlineStr"/>
       <c r="I81" s="28" t="inlineStr"/>
@@ -6774,7 +6590,7 @@
     <row r="82">
       <c r="A82" s="28" t="inlineStr">
         <is>
-          <t>DABIGATRAN ETEXILATO CP 110 MG</t>
+          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
         </is>
       </c>
       <c r="B82" s="28" t="inlineStr">
@@ -6783,19 +6599,19 @@
         </is>
       </c>
       <c r="C82" s="29" t="n">
-        <v>3840</v>
+        <v>2200</v>
       </c>
       <c r="D82" s="29" t="n">
-        <v>6.7</v>
+        <v>4</v>
       </c>
       <c r="E82" s="29" t="n">
-        <v>3623.7</v>
+        <v>3766.9</v>
       </c>
       <c r="F82" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="29" t="n">
-        <v>4260</v>
+        <v>1600</v>
       </c>
       <c r="H82" s="28" t="inlineStr"/>
       <c r="I82" s="28" t="inlineStr"/>
@@ -6803,7 +6619,7 @@
     <row r="83">
       <c r="A83" s="28" t="inlineStr">
         <is>
-          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
+          <t>ATORVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B83" s="28" t="inlineStr">
@@ -6812,19 +6628,19 @@
         </is>
       </c>
       <c r="C83" s="29" t="n">
-        <v>2200</v>
+        <v>3800</v>
       </c>
       <c r="D83" s="29" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="E83" s="29" t="n">
-        <v>3766.9</v>
+        <v>3926.1</v>
       </c>
       <c r="F83" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="29" t="n">
-        <v>1600</v>
+        <v>47000</v>
       </c>
       <c r="H83" s="28" t="inlineStr"/>
       <c r="I83" s="28" t="inlineStr"/>
@@ -6832,7 +6648,7 @@
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 20 MG COMPRIMIDO</t>
+          <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B84" s="28" t="inlineStr">
@@ -6841,19 +6657,19 @@
         </is>
       </c>
       <c r="C84" s="29" t="n">
-        <v>3800</v>
+        <v>3300</v>
       </c>
       <c r="D84" s="29" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="E84" s="29" t="n">
-        <v>3926.1</v>
+        <v>2814.1</v>
       </c>
       <c r="F84" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="29" t="n">
-        <v>47000</v>
+        <v>25180</v>
       </c>
       <c r="H84" s="28" t="inlineStr"/>
       <c r="I84" s="28" t="inlineStr"/>
@@ -6861,7 +6677,7 @@
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
+          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B85" s="28" t="inlineStr">
@@ -6870,19 +6686,19 @@
         </is>
       </c>
       <c r="C85" s="29" t="n">
-        <v>3300</v>
+        <v>4890</v>
       </c>
       <c r="D85" s="29" t="n">
-        <v>7</v>
+        <v>11.6</v>
       </c>
       <c r="E85" s="29" t="n">
-        <v>2814.1</v>
+        <v>2847.2</v>
       </c>
       <c r="F85" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="29" t="n">
-        <v>25180</v>
+        <v>3060</v>
       </c>
       <c r="H85" s="28" t="inlineStr"/>
       <c r="I85" s="28" t="inlineStr"/>
@@ -6890,7 +6706,7 @@
     <row r="86">
       <c r="A86" s="28" t="inlineStr">
         <is>
-          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
+          <t>TRAMADOL + PARACETAMOL 37,5 MG/325 MG CM</t>
         </is>
       </c>
       <c r="B86" s="28" t="inlineStr">
@@ -6899,19 +6715,19 @@
         </is>
       </c>
       <c r="C86" s="29" t="n">
-        <v>4890</v>
+        <v>3600</v>
       </c>
       <c r="D86" s="29" t="n">
-        <v>11.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E86" s="29" t="n">
-        <v>2847.2</v>
+        <v>2562.8</v>
       </c>
       <c r="F86" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="29" t="n">
-        <v>3060</v>
+        <v>0</v>
       </c>
       <c r="H86" s="28" t="inlineStr"/>
       <c r="I86" s="28" t="inlineStr"/>
@@ -6919,7 +6735,7 @@
     <row r="87">
       <c r="A87" s="28" t="inlineStr">
         <is>
-          <t>TRAMADOL + PARACETAMOL 37,5 MG/325 MG CM</t>
+          <t>ENALAPRIL 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B87" s="28" t="inlineStr">
@@ -6928,19 +6744,19 @@
         </is>
       </c>
       <c r="C87" s="29" t="n">
-        <v>3600</v>
+        <v>2000</v>
       </c>
       <c r="D87" s="29" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="E87" s="29" t="n">
-        <v>2562.8</v>
+        <v>2323.5</v>
       </c>
       <c r="F87" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="29" t="n">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="H87" s="28" t="inlineStr"/>
       <c r="I87" s="28" t="inlineStr"/>
@@ -6948,7 +6764,7 @@
     <row r="88">
       <c r="A88" s="28" t="inlineStr">
         <is>
-          <t>ENALAPRIL 10 MG COMPRIMIDO</t>
+          <t>SERTRALINA CM 50 MG</t>
         </is>
       </c>
       <c r="B88" s="28" t="inlineStr">
@@ -6957,19 +6773,19 @@
         </is>
       </c>
       <c r="C88" s="29" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D88" s="29" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="E88" s="29" t="n">
-        <v>2323.5</v>
+        <v>2211.1</v>
       </c>
       <c r="F88" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="29" t="n">
-        <v>26000</v>
+        <v>14000</v>
       </c>
       <c r="H88" s="28" t="inlineStr"/>
       <c r="I88" s="28" t="inlineStr"/>
@@ -6977,7 +6793,7 @@
     <row r="89">
       <c r="A89" s="28" t="inlineStr">
         <is>
-          <t>SERTRALINA CM 50 MG</t>
+          <t>QUETIAPINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B89" s="28" t="inlineStr">
@@ -6986,19 +6802,19 @@
         </is>
       </c>
       <c r="C89" s="29" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D89" s="29" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="E89" s="29" t="n">
-        <v>2211.1</v>
+        <v>2493.2</v>
       </c>
       <c r="F89" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G89" s="29" t="n">
-        <v>14000</v>
+        <v>26000</v>
       </c>
       <c r="H89" s="28" t="inlineStr"/>
       <c r="I89" s="28" t="inlineStr"/>
@@ -7006,7 +6822,7 @@
     <row r="90">
       <c r="A90" s="28" t="inlineStr">
         <is>
-          <t>QUETIAPINA 100 MG COMPRIMIDO</t>
+          <t>QUETIAPINA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B90" s="28" t="inlineStr">
@@ -7018,16 +6834,16 @@
         <v>2000</v>
       </c>
       <c r="D90" s="29" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="E90" s="29" t="n">
-        <v>2493.2</v>
+        <v>1854.8</v>
       </c>
       <c r="F90" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="29" t="n">
-        <v>26000</v>
+        <v>17000</v>
       </c>
       <c r="H90" s="28" t="inlineStr"/>
       <c r="I90" s="28" t="inlineStr"/>
@@ -7035,7 +6851,7 @@
     <row r="91">
       <c r="A91" s="28" t="inlineStr">
         <is>
-          <t>QUETIAPINA 25 MG COMPRIMIDO</t>
+          <t>METOTREXATO 2,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B91" s="28" t="inlineStr">
@@ -7044,19 +6860,19 @@
         </is>
       </c>
       <c r="C91" s="29" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="D91" s="29" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="E91" s="29" t="n">
-        <v>1854.8</v>
+        <v>1730.5</v>
       </c>
       <c r="F91" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="29" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="H91" s="28" t="inlineStr"/>
       <c r="I91" s="28" t="inlineStr"/>
@@ -7064,7 +6880,7 @@
     <row r="92">
       <c r="A92" s="28" t="inlineStr">
         <is>
-          <t>METOTREXATO 2,5 MG COMPRIMIDO</t>
+          <t>CLOZAPINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B92" s="28" t="inlineStr">
@@ -7073,19 +6889,19 @@
         </is>
       </c>
       <c r="C92" s="29" t="n">
-        <v>0</v>
+        <v>1740</v>
       </c>
       <c r="D92" s="29" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="E92" s="29" t="n">
-        <v>1730.5</v>
+        <v>1884.8</v>
       </c>
       <c r="F92" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="29" t="n">
-        <v>0</v>
+        <v>2310</v>
       </c>
       <c r="H92" s="28" t="inlineStr"/>
       <c r="I92" s="28" t="inlineStr"/>
@@ -7093,7 +6909,7 @@
     <row r="93">
       <c r="A93" s="28" t="inlineStr">
         <is>
-          <t>CLOZAPINA 100 MG COMPRIMIDO</t>
+          <t>AMLODIPINO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B93" s="28" t="inlineStr">
@@ -7102,19 +6918,19 @@
         </is>
       </c>
       <c r="C93" s="29" t="n">
-        <v>2640</v>
+        <v>2000</v>
       </c>
       <c r="D93" s="29" t="n">
-        <v>9.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="E93" s="29" t="n">
-        <v>1884.8</v>
+        <v>2135.2</v>
       </c>
       <c r="F93" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="29" t="n">
-        <v>2310</v>
+        <v>26000</v>
       </c>
       <c r="H93" s="28" t="inlineStr"/>
       <c r="I93" s="28" t="inlineStr"/>
@@ -7122,7 +6938,7 @@
     <row r="94">
       <c r="A94" s="28" t="inlineStr">
         <is>
-          <t>AMLODIPINO 10 MG COMPRIMIDO</t>
+          <t>VENLAFAXINA 75 MG COMPRIMIDOS LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B94" s="28" t="inlineStr">
@@ -7134,16 +6950,16 @@
         <v>2000</v>
       </c>
       <c r="D94" s="29" t="n">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="E94" s="29" t="n">
-        <v>2135.2</v>
+        <v>1400.8</v>
       </c>
       <c r="F94" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="29" t="n">
-        <v>26000</v>
+        <v>40500</v>
       </c>
       <c r="H94" s="28" t="inlineStr"/>
       <c r="I94" s="28" t="inlineStr"/>
@@ -7151,7 +6967,7 @@
     <row r="95">
       <c r="A95" s="28" t="inlineStr">
         <is>
-          <t>VENLAFAXINA 75 MG COMPRIMIDOS LIBERACION MODIFICADA</t>
+          <t>ZOPICLONA CM 7,5 MG</t>
         </is>
       </c>
       <c r="B95" s="28" t="inlineStr">
@@ -7160,19 +6976,19 @@
         </is>
       </c>
       <c r="C95" s="29" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D95" s="29" t="n">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="E95" s="29" t="n">
-        <v>1400.8</v>
+        <v>1975.1</v>
       </c>
       <c r="F95" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="29" t="n">
-        <v>40500</v>
+        <v>3000</v>
       </c>
       <c r="H95" s="28" t="inlineStr"/>
       <c r="I95" s="28" t="inlineStr"/>
@@ -7180,7 +6996,7 @@
     <row r="96">
       <c r="A96" s="28" t="inlineStr">
         <is>
-          <t>ZOPICLONA CM 7,5 MG</t>
+          <t>PREDNISONA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B96" s="28" t="inlineStr">
@@ -7189,19 +7005,19 @@
         </is>
       </c>
       <c r="C96" s="29" t="n">
-        <v>2500</v>
+        <v>2110</v>
       </c>
       <c r="D96" s="29" t="n">
-        <v>10.1</v>
+        <v>9.1</v>
       </c>
       <c r="E96" s="29" t="n">
-        <v>1975.1</v>
+        <v>1800.3</v>
       </c>
       <c r="F96" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="29" t="n">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="H96" s="28" t="inlineStr"/>
       <c r="I96" s="28" t="inlineStr"/>
@@ -7209,7 +7025,7 @@
     <row r="97">
       <c r="A97" s="28" t="inlineStr">
         <is>
-          <t>PREDNISONA 5 MG COMPRIMIDO</t>
+          <t>JERINGA P/INSULINA C/AGUJA 1 ML 100 UI/A. FIJA 29-31G X 6MM</t>
         </is>
       </c>
       <c r="B97" s="28" t="inlineStr">
@@ -7218,19 +7034,19 @@
         </is>
       </c>
       <c r="C97" s="29" t="n">
-        <v>3049</v>
+        <v>0</v>
       </c>
       <c r="D97" s="29" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="E97" s="29" t="n">
-        <v>1800.3</v>
+        <v>1497.5</v>
       </c>
       <c r="F97" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="29" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="H97" s="28" t="inlineStr"/>
       <c r="I97" s="28" t="inlineStr"/>
@@ -7238,7 +7054,7 @@
     <row r="98">
       <c r="A98" s="28" t="inlineStr">
         <is>
-          <t>JERINGA P/INSULINA C/AGUJA 1 ML 100 UI/A. FIJA 29-31G X 6MM</t>
+          <t>OLANZAPINA 10 MG CM UNIDAD</t>
         </is>
       </c>
       <c r="B98" s="28" t="inlineStr">
@@ -7247,19 +7063,19 @@
         </is>
       </c>
       <c r="C98" s="29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D98" s="29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="E98" s="29" t="n">
-        <v>1497.5</v>
+        <v>1549.7</v>
       </c>
       <c r="F98" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="29" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="H98" s="28" t="inlineStr"/>
       <c r="I98" s="28" t="inlineStr"/>
@@ -7267,7 +7083,7 @@
     <row r="99">
       <c r="A99" s="28" t="inlineStr">
         <is>
-          <t>OLANZAPINA 10 MG CM UNIDAD</t>
+          <t>BUPROPION (ANFEBUTAMONA) 150 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B99" s="28" t="inlineStr">
@@ -7276,19 +7092,19 @@
         </is>
       </c>
       <c r="C99" s="29" t="n">
-        <v>1000</v>
+        <v>3360</v>
       </c>
       <c r="D99" s="29" t="n">
-        <v>4.4</v>
+        <v>15.1</v>
       </c>
       <c r="E99" s="29" t="n">
-        <v>1549.7</v>
+        <v>1537.5</v>
       </c>
       <c r="F99" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="29" t="n">
-        <v>9000</v>
+        <v>1650</v>
       </c>
       <c r="H99" s="28" t="inlineStr"/>
       <c r="I99" s="28" t="inlineStr"/>
@@ -7296,7 +7112,7 @@
     <row r="100">
       <c r="A100" s="28" t="inlineStr">
         <is>
-          <t>BUPROPION (ANFEBUTAMONA) 150 MG CM LIBERACION MODIFICADA</t>
+          <t>FLUOXETINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B100" s="28" t="inlineStr">
@@ -7305,19 +7121,19 @@
         </is>
       </c>
       <c r="C100" s="29" t="n">
-        <v>3360</v>
+        <v>2200</v>
       </c>
       <c r="D100" s="29" t="n">
-        <v>15.1</v>
+        <v>10</v>
       </c>
       <c r="E100" s="29" t="n">
-        <v>1537.5</v>
+        <v>1652.9</v>
       </c>
       <c r="F100" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="29" t="n">
-        <v>1650</v>
+        <v>2000</v>
       </c>
       <c r="H100" s="28" t="inlineStr"/>
       <c r="I100" s="28" t="inlineStr"/>
@@ -7325,7 +7141,7 @@
     <row r="101">
       <c r="A101" s="28" t="inlineStr">
         <is>
-          <t>FLUOXETINA 20 MG COMPRIMIDO</t>
+          <t>METILFENIDATO 10 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B101" s="28" t="inlineStr">
@@ -7334,19 +7150,19 @@
         </is>
       </c>
       <c r="C101" s="29" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="D101" s="29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E101" s="29" t="n">
-        <v>1652.9</v>
+        <v>1494.3</v>
       </c>
       <c r="F101" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="29" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H101" s="28" t="inlineStr"/>
       <c r="I101" s="28" t="inlineStr"/>
@@ -7354,7 +7170,7 @@
     <row r="102">
       <c r="A102" s="28" t="inlineStr">
         <is>
-          <t>METILFENIDATO 10 MG CM LIBERACION MODIFICADA</t>
+          <t>CARVEDILOL 12,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B102" s="28" t="inlineStr">
@@ -7363,19 +7179,19 @@
         </is>
       </c>
       <c r="C102" s="29" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="D102" s="29" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="E102" s="29" t="n">
-        <v>1494.3</v>
+        <v>1893.1</v>
       </c>
       <c r="F102" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G102" s="29" t="n">
-        <v>0</v>
+        <v>36390</v>
       </c>
       <c r="H102" s="28" t="inlineStr"/>
       <c r="I102" s="28" t="inlineStr"/>
@@ -7383,7 +7199,7 @@
     <row r="103">
       <c r="A103" s="28" t="inlineStr">
         <is>
-          <t>CARVEDILOL 12,5 MG COMPRIMIDO</t>
+          <t>DIVALPROATO SODICO CM 500 MG LIBRACION MODIFICADA</t>
         </is>
       </c>
       <c r="B103" s="28" t="inlineStr">
@@ -7392,19 +7208,19 @@
         </is>
       </c>
       <c r="C103" s="29" t="n">
-        <v>2100</v>
+        <v>1200</v>
       </c>
       <c r="D103" s="29" t="n">
-        <v>10.1</v>
+        <v>5.8</v>
       </c>
       <c r="E103" s="29" t="n">
-        <v>1893.1</v>
+        <v>1374.3</v>
       </c>
       <c r="F103" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G103" s="29" t="n">
-        <v>36390</v>
+        <v>43600</v>
       </c>
       <c r="H103" s="28" t="inlineStr"/>
       <c r="I103" s="28" t="inlineStr"/>
@@ -7412,7 +7228,7 @@
     <row r="104">
       <c r="A104" s="28" t="inlineStr">
         <is>
-          <t>DIVALPROATO SODICO CM 500 MG LIBRACION MODIFICADA</t>
+          <t>HIDRALAZINA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B104" s="28" t="inlineStr">
@@ -7421,19 +7237,19 @@
         </is>
       </c>
       <c r="C104" s="29" t="n">
-        <v>1200</v>
+        <v>2220</v>
       </c>
       <c r="D104" s="29" t="n">
-        <v>5.8</v>
+        <v>10.8</v>
       </c>
       <c r="E104" s="29" t="n">
-        <v>1374.3</v>
+        <v>1851.8</v>
       </c>
       <c r="F104" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G104" s="29" t="n">
-        <v>43600</v>
+        <v>53790</v>
       </c>
       <c r="H104" s="28" t="inlineStr"/>
       <c r="I104" s="28" t="inlineStr"/>
@@ -7441,7 +7257,7 @@
     <row r="105">
       <c r="A105" s="28" t="inlineStr">
         <is>
-          <t>HIDRALAZINA 50 MG COMPRIMIDO</t>
+          <t>CLOPIDOGREL 75 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B105" s="28" t="inlineStr">
@@ -7450,19 +7266,19 @@
         </is>
       </c>
       <c r="C105" s="29" t="n">
-        <v>2220</v>
+        <v>0</v>
       </c>
       <c r="D105" s="29" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="E105" s="29" t="n">
-        <v>1851.8</v>
+        <v>1462.9</v>
       </c>
       <c r="F105" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="29" t="n">
-        <v>53790</v>
+        <v>26000</v>
       </c>
       <c r="H105" s="28" t="inlineStr"/>
       <c r="I105" s="28" t="inlineStr"/>
@@ -7470,7 +7286,7 @@
     <row r="106">
       <c r="A106" s="28" t="inlineStr">
         <is>
-          <t>CLOPIDOGREL 75 MG COMPRIMIDO</t>
+          <t>TRAMADOL CP 50 MG</t>
         </is>
       </c>
       <c r="B106" s="28" t="inlineStr">
@@ -7479,19 +7295,19 @@
         </is>
       </c>
       <c r="C106" s="29" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="D106" s="29" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E106" s="29" t="n">
-        <v>1462.9</v>
+        <v>1728.1</v>
       </c>
       <c r="F106" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G106" s="29" t="n">
-        <v>26000</v>
+        <v>7700</v>
       </c>
       <c r="H106" s="28" t="inlineStr"/>
       <c r="I106" s="28" t="inlineStr"/>
@@ -7499,7 +7315,7 @@
     <row r="107">
       <c r="A107" s="28" t="inlineStr">
         <is>
-          <t>TRAMADOL CP 50 MG</t>
+          <t>PREGABALINA 150 MG CAPSULA</t>
         </is>
       </c>
       <c r="B107" s="28" t="inlineStr">
@@ -7508,19 +7324,19 @@
         </is>
       </c>
       <c r="C107" s="29" t="n">
-        <v>2200</v>
+        <v>2800</v>
       </c>
       <c r="D107" s="29" t="n">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="E107" s="29" t="n">
-        <v>1728.1</v>
+        <v>1086.7</v>
       </c>
       <c r="F107" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G107" s="29" t="n">
-        <v>7700</v>
+        <v>5600</v>
       </c>
       <c r="H107" s="28" t="inlineStr"/>
       <c r="I107" s="28" t="inlineStr"/>
@@ -7528,7 +7344,7 @@
     <row r="108">
       <c r="A108" s="28" t="inlineStr">
         <is>
-          <t>PREGABALINA 150 MG CAPSULA</t>
+          <t>LEFLUNOMIDA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B108" s="28" t="inlineStr">
@@ -7537,19 +7353,19 @@
         </is>
       </c>
       <c r="C108" s="29" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="D108" s="29" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="E108" s="29" t="n">
-        <v>1086.7</v>
+        <v>1499.3</v>
       </c>
       <c r="F108" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="29" t="n">
-        <v>5600</v>
+        <v>12840</v>
       </c>
       <c r="H108" s="28" t="inlineStr"/>
       <c r="I108" s="28" t="inlineStr"/>
@@ -7557,7 +7373,7 @@
     <row r="109">
       <c r="A109" s="28" t="inlineStr">
         <is>
-          <t>LEFLUNOMIDA 20 MG COMPRIMIDO</t>
+          <t>METILDOPA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B109" s="28" t="inlineStr">
@@ -7566,19 +7382,19 @@
         </is>
       </c>
       <c r="C109" s="29" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="D109" s="29" t="n">
-        <v>0</v>
+        <v>18.1</v>
       </c>
       <c r="E109" s="29" t="n">
-        <v>1499.3</v>
+        <v>1800.5</v>
       </c>
       <c r="F109" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="29" t="n">
-        <v>12840</v>
+        <v>36000</v>
       </c>
       <c r="H109" s="28" t="inlineStr"/>
       <c r="I109" s="28" t="inlineStr"/>
@@ -7586,7 +7402,7 @@
     <row r="110">
       <c r="A110" s="28" t="inlineStr">
         <is>
-          <t>METILDOPA 250 MG COMPRIMIDO</t>
+          <t>ARIPIPRAZOL 10 MG CM</t>
         </is>
       </c>
       <c r="B110" s="28" t="inlineStr">
@@ -7595,19 +7411,19 @@
         </is>
       </c>
       <c r="C110" s="29" t="n">
-        <v>3200</v>
+        <v>930</v>
       </c>
       <c r="D110" s="29" t="n">
-        <v>18.1</v>
+        <v>5.4</v>
       </c>
       <c r="E110" s="29" t="n">
-        <v>1800.5</v>
+        <v>1279.4</v>
       </c>
       <c r="F110" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="29" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="H110" s="28" t="inlineStr"/>
       <c r="I110" s="28" t="inlineStr"/>
@@ -7615,7 +7431,7 @@
     <row r="111">
       <c r="A111" s="28" t="inlineStr">
         <is>
-          <t>ARIPIPRAZOL 10 MG CM</t>
+          <t>RISPERIDONA CM 3 MG</t>
         </is>
       </c>
       <c r="B111" s="28" t="inlineStr">
@@ -7624,19 +7440,19 @@
         </is>
       </c>
       <c r="C111" s="29" t="n">
-        <v>930</v>
+        <v>1400</v>
       </c>
       <c r="D111" s="29" t="n">
-        <v>5.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E111" s="29" t="n">
-        <v>1279.4</v>
+        <v>1078.8</v>
       </c>
       <c r="F111" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="29" t="n">
-        <v>0</v>
+        <v>19700</v>
       </c>
       <c r="H111" s="28" t="inlineStr"/>
       <c r="I111" s="28" t="inlineStr"/>
@@ -7644,7 +7460,7 @@
     <row r="112">
       <c r="A112" s="28" t="inlineStr">
         <is>
-          <t>RISPERIDONA CM 3 MG</t>
+          <t>AMLODIPINO 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B112" s="28" t="inlineStr">
@@ -7653,19 +7469,19 @@
         </is>
       </c>
       <c r="C112" s="29" t="n">
-        <v>1900</v>
+        <v>1000</v>
       </c>
       <c r="D112" s="29" t="n">
-        <v>11.2</v>
+        <v>6</v>
       </c>
       <c r="E112" s="29" t="n">
-        <v>1078.8</v>
+        <v>1039.3</v>
       </c>
       <c r="F112" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="29" t="n">
-        <v>19700</v>
+        <v>12000</v>
       </c>
       <c r="H112" s="28" t="inlineStr"/>
       <c r="I112" s="28" t="inlineStr"/>
@@ -7673,7 +7489,7 @@
     <row r="113">
       <c r="A113" s="28" t="inlineStr">
         <is>
-          <t>AMLODIPINO 5 MG COMPRIMIDO</t>
+          <t>DULOXETINA 60 MG CAPSULA</t>
         </is>
       </c>
       <c r="B113" s="28" t="inlineStr">
@@ -7682,19 +7498,19 @@
         </is>
       </c>
       <c r="C113" s="29" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="D113" s="29" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="E113" s="29" t="n">
-        <v>1039.3</v>
+        <v>843.9</v>
       </c>
       <c r="F113" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G113" s="29" t="n">
-        <v>12000</v>
+        <v>3810</v>
       </c>
       <c r="H113" s="28" t="inlineStr"/>
       <c r="I113" s="28" t="inlineStr"/>
@@ -7702,7 +7518,7 @@
     <row r="114">
       <c r="A114" s="28" t="inlineStr">
         <is>
-          <t>DULOXETINA 60 MG CAPSULA</t>
+          <t>MESALAZINA 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B114" s="28" t="inlineStr">
@@ -7711,19 +7527,19 @@
         </is>
       </c>
       <c r="C114" s="29" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="D114" s="29" t="n">
-        <v>5.4</v>
+        <v>9.1</v>
       </c>
       <c r="E114" s="29" t="n">
-        <v>843.9</v>
+        <v>1725.9</v>
       </c>
       <c r="F114" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G114" s="29" t="n">
-        <v>3810</v>
+        <v>9900</v>
       </c>
       <c r="H114" s="28" t="inlineStr"/>
       <c r="I114" s="28" t="inlineStr"/>
@@ -7827,10 +7643,10 @@
         </is>
       </c>
       <c r="C118" s="29" t="n">
-        <v>2357</v>
+        <v>2327</v>
       </c>
       <c r="D118" s="29" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="E118" s="29" t="n">
         <v>900.9</v>
@@ -7934,7 +7750,7 @@
     <row r="122">
       <c r="A122" s="28" t="inlineStr">
         <is>
-          <t>RIFAXIMINA 200 MG CP</t>
+          <t>RISPERIDONA 1 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B122" s="28" t="inlineStr">
@@ -7943,19 +7759,19 @@
         </is>
       </c>
       <c r="C122" s="29" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="D122" s="29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E122" s="29" t="n">
-        <v>619.6</v>
+        <v>870</v>
       </c>
       <c r="F122" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G122" s="29" t="n">
-        <v>23640</v>
+        <v>16700</v>
       </c>
       <c r="H122" s="28" t="inlineStr"/>
       <c r="I122" s="28" t="inlineStr"/>
@@ -7963,7 +7779,7 @@
     <row r="123">
       <c r="A123" s="28" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG COMPRIMIDO</t>
+          <t>TRAZODONA CM 100 MG</t>
         </is>
       </c>
       <c r="B123" s="28" t="inlineStr">
@@ -7972,19 +7788,19 @@
         </is>
       </c>
       <c r="C123" s="29" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D123" s="29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="E123" s="29" t="n">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F123" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="29" t="n">
-        <v>16700</v>
+        <v>2700</v>
       </c>
       <c r="H123" s="28" t="inlineStr"/>
       <c r="I123" s="28" t="inlineStr"/>
@@ -7992,7 +7808,7 @@
     <row r="124">
       <c r="A124" s="28" t="inlineStr">
         <is>
-          <t>TRAZODONA CM 100 MG</t>
+          <t>TAMSULOSINA 400 MCG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B124" s="28" t="inlineStr">
@@ -8001,19 +7817,19 @@
         </is>
       </c>
       <c r="C124" s="29" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="D124" s="29" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="E124" s="29" t="n">
-        <v>869</v>
+        <v>899.8</v>
       </c>
       <c r="F124" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G124" s="29" t="n">
-        <v>2700</v>
+        <v>9900</v>
       </c>
       <c r="H124" s="28" t="inlineStr"/>
       <c r="I124" s="28" t="inlineStr"/>
@@ -8021,7 +7837,7 @@
     <row r="125">
       <c r="A125" s="28" t="inlineStr">
         <is>
-          <t>TAMSULOSINA 400 MCG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>DESLORATADINA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B125" s="28" t="inlineStr">
@@ -8030,19 +7846,19 @@
         </is>
       </c>
       <c r="C125" s="29" t="n">
-        <v>900</v>
+        <v>3000</v>
       </c>
       <c r="D125" s="29" t="n">
-        <v>7.3</v>
+        <v>24.6</v>
       </c>
       <c r="E125" s="29" t="n">
-        <v>899.8</v>
+        <v>708.7</v>
       </c>
       <c r="F125" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="29" t="n">
-        <v>9900</v>
+        <v>37000</v>
       </c>
       <c r="H125" s="28" t="inlineStr"/>
       <c r="I125" s="28" t="inlineStr"/>
@@ -8050,7 +7866,7 @@
     <row r="126">
       <c r="A126" s="28" t="inlineStr">
         <is>
-          <t>DESLORATADINA 5 MG COMPRIMIDO</t>
+          <t>ZOLPIDEM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B126" s="28" t="inlineStr">
@@ -8059,19 +7875,19 @@
         </is>
       </c>
       <c r="C126" s="29" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D126" s="29" t="n">
-        <v>24.6</v>
+        <v>0</v>
       </c>
       <c r="E126" s="29" t="n">
-        <v>708.7</v>
+        <v>703.5</v>
       </c>
       <c r="F126" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G126" s="29" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="H126" s="28" t="inlineStr"/>
       <c r="I126" s="28" t="inlineStr"/>
@@ -8079,7 +7895,7 @@
     <row r="127">
       <c r="A127" s="28" t="inlineStr">
         <is>
-          <t>ZOLPIDEM 10 MG COMPRIMIDO</t>
+          <t>APIXABAN 5 MG CM</t>
         </is>
       </c>
       <c r="B127" s="28" t="inlineStr">
@@ -8094,13 +7910,13 @@
         <v>0</v>
       </c>
       <c r="E127" s="29" t="n">
-        <v>703.5</v>
+        <v>823.9</v>
       </c>
       <c r="F127" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G127" s="29" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H127" s="28" t="inlineStr"/>
       <c r="I127" s="28" t="inlineStr"/>
@@ -8108,7 +7924,7 @@
     <row r="128">
       <c r="A128" s="28" t="inlineStr">
         <is>
-          <t>APIXABAN 5 MG CM</t>
+          <t>VENLAFAXINA 150 MG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B128" s="28" t="inlineStr">
@@ -8117,19 +7933,19 @@
         </is>
       </c>
       <c r="C128" s="29" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D128" s="29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="E128" s="29" t="n">
-        <v>823.9</v>
+        <v>769.3</v>
       </c>
       <c r="F128" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G128" s="29" t="n">
-        <v>2100</v>
+        <v>6990</v>
       </c>
       <c r="H128" s="28" t="inlineStr"/>
       <c r="I128" s="28" t="inlineStr"/>
@@ -8137,7 +7953,7 @@
     <row r="129">
       <c r="A129" s="28" t="inlineStr">
         <is>
-          <t>VENLAFAXINA 150 MG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>DOMPERIDONA 10 MG CAPSULA</t>
         </is>
       </c>
       <c r="B129" s="28" t="inlineStr">
@@ -8146,19 +7962,19 @@
         </is>
       </c>
       <c r="C129" s="29" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
       <c r="D129" s="29" t="n">
-        <v>5.5</v>
+        <v>14.1</v>
       </c>
       <c r="E129" s="29" t="n">
-        <v>769.3</v>
+        <v>579.8</v>
       </c>
       <c r="F129" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G129" s="29" t="n">
-        <v>6990</v>
+        <v>9000</v>
       </c>
       <c r="H129" s="28" t="inlineStr"/>
       <c r="I129" s="28" t="inlineStr"/>
@@ -8166,7 +7982,7 @@
     <row r="130">
       <c r="A130" s="28" t="inlineStr">
         <is>
-          <t>DOMPERIDONA 10 MG CAPSULA</t>
+          <t>ESCITALOPRAM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B130" s="28" t="inlineStr">
@@ -8175,19 +7991,19 @@
         </is>
       </c>
       <c r="C130" s="29" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D130" s="29" t="n">
-        <v>14.1</v>
+        <v>4.9</v>
       </c>
       <c r="E130" s="29" t="n">
-        <v>579.8</v>
+        <v>738</v>
       </c>
       <c r="F130" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G130" s="29" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="H130" s="28" t="inlineStr"/>
       <c r="I130" s="28" t="inlineStr"/>
@@ -8195,7 +8011,7 @@
     <row r="131">
       <c r="A131" s="28" t="inlineStr">
         <is>
-          <t>ESCITALOPRAM 10 MG COMPRIMIDO</t>
+          <t>BICARBONATO DE SODIO CP. 500 M</t>
         </is>
       </c>
       <c r="B131" s="28" t="inlineStr">
@@ -8204,19 +8020,19 @@
         </is>
       </c>
       <c r="C131" s="29" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D131" s="29" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="E131" s="29" t="n">
-        <v>738</v>
+        <v>488.5</v>
       </c>
       <c r="F131" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G131" s="29" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="H131" s="28" t="inlineStr"/>
       <c r="I131" s="28" t="inlineStr"/>
@@ -8224,7 +8040,7 @@
     <row r="132">
       <c r="A132" s="28" t="inlineStr">
         <is>
-          <t>BICARBONATO DE SODIO CP. 500 M</t>
+          <t>CARBONATO DE LITIO 450 MG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B132" s="28" t="inlineStr">
@@ -8239,13 +8055,13 @@
         <v>0</v>
       </c>
       <c r="E132" s="29" t="n">
-        <v>488.5</v>
+        <v>517.2</v>
       </c>
       <c r="F132" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G132" s="29" t="n">
-        <v>1800</v>
+        <v>22260</v>
       </c>
       <c r="H132" s="28" t="inlineStr"/>
       <c r="I132" s="28" t="inlineStr"/>
@@ -8253,7 +8069,7 @@
     <row r="133">
       <c r="A133" s="28" t="inlineStr">
         <is>
-          <t>CARBONATO DE LITIO 450 MG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>ACIDO URSODEOXICOLICO CM 250 MG</t>
         </is>
       </c>
       <c r="B133" s="28" t="inlineStr">
@@ -8262,19 +8078,19 @@
         </is>
       </c>
       <c r="C133" s="29" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="D133" s="29" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="E133" s="29" t="n">
-        <v>517.2</v>
+        <v>469.3</v>
       </c>
       <c r="F133" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G133" s="29" t="n">
-        <v>22260</v>
+        <v>4620</v>
       </c>
       <c r="H133" s="28" t="inlineStr"/>
       <c r="I133" s="28" t="inlineStr"/>
@@ -8282,7 +8098,7 @@
     <row r="134">
       <c r="A134" s="28" t="inlineStr">
         <is>
-          <t>ACIDO URSODEOXICOLICO CM 250 MG</t>
+          <t>CARBAMAZEPINA 200 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B134" s="28" t="inlineStr">
@@ -8291,19 +8107,19 @@
         </is>
       </c>
       <c r="C134" s="29" t="n">
-        <v>660</v>
+        <v>560</v>
       </c>
       <c r="D134" s="29" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="E134" s="29" t="n">
-        <v>469.3</v>
+        <v>531.3</v>
       </c>
       <c r="F134" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="29" t="n">
-        <v>4620</v>
+        <v>0</v>
       </c>
       <c r="H134" s="28" t="inlineStr"/>
       <c r="I134" s="28" t="inlineStr"/>
@@ -8311,7 +8127,7 @@
     <row r="135">
       <c r="A135" s="28" t="inlineStr">
         <is>
-          <t>CARBAMAZEPINA 200 MG COMPRIMIDO</t>
+          <t>HIDROCLOROTIAZIDA 25 MG + TRIAMTERENO 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B135" s="28" t="inlineStr">
@@ -8320,19 +8136,19 @@
         </is>
       </c>
       <c r="C135" s="29" t="n">
-        <v>560</v>
+        <v>180</v>
       </c>
       <c r="D135" s="29" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="E135" s="29" t="n">
-        <v>531.3</v>
+        <v>554.8</v>
       </c>
       <c r="F135" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G135" s="29" t="n">
-        <v>0</v>
+        <v>15060</v>
       </c>
       <c r="H135" s="28" t="inlineStr"/>
       <c r="I135" s="28" t="inlineStr"/>
@@ -8340,7 +8156,7 @@
     <row r="136">
       <c r="A136" s="28" t="inlineStr">
         <is>
-          <t>HIDROCLOROTIAZIDA 25 MG + TRIAMTERENO 50 MG COMPRIMIDO</t>
+          <t>AMIODARONA 200 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B136" s="28" t="inlineStr">
@@ -8349,19 +8165,19 @@
         </is>
       </c>
       <c r="C136" s="29" t="n">
-        <v>752</v>
+        <v>1005</v>
       </c>
       <c r="D136" s="29" t="n">
-        <v>8.5</v>
+        <v>12.2</v>
       </c>
       <c r="E136" s="29" t="n">
-        <v>554.8</v>
+        <v>449.9</v>
       </c>
       <c r="F136" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G136" s="29" t="n">
-        <v>15060</v>
+        <v>10050</v>
       </c>
       <c r="H136" s="28" t="inlineStr"/>
       <c r="I136" s="28" t="inlineStr"/>
@@ -8369,7 +8185,7 @@
     <row r="137">
       <c r="A137" s="28" t="inlineStr">
         <is>
-          <t>AMIODARONA 200 MG COMPRIMIDO</t>
+          <t>ESZOPICLONA 3 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B137" s="28" t="inlineStr">
@@ -8378,19 +8194,19 @@
         </is>
       </c>
       <c r="C137" s="29" t="n">
-        <v>1005</v>
+        <v>300</v>
       </c>
       <c r="D137" s="29" t="n">
-        <v>12.2</v>
+        <v>3.7</v>
       </c>
       <c r="E137" s="29" t="n">
-        <v>449.9</v>
+        <v>477.2</v>
       </c>
       <c r="F137" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G137" s="29" t="n">
-        <v>10050</v>
+        <v>1680</v>
       </c>
       <c r="H137" s="28" t="inlineStr"/>
       <c r="I137" s="28" t="inlineStr"/>
@@ -8398,7 +8214,7 @@
     <row r="138">
       <c r="A138" s="28" t="inlineStr">
         <is>
-          <t>ESZOPICLONA 3 MG COMPRIMIDO</t>
+          <t>METOCLOPRAMIDA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B138" s="28" t="inlineStr">
@@ -8407,19 +8223,19 @@
         </is>
       </c>
       <c r="C138" s="29" t="n">
-        <v>300</v>
+        <v>1224</v>
       </c>
       <c r="D138" s="29" t="n">
-        <v>3.7</v>
+        <v>15.3</v>
       </c>
       <c r="E138" s="29" t="n">
-        <v>477.2</v>
+        <v>240.7</v>
       </c>
       <c r="F138" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G138" s="29" t="n">
-        <v>1680</v>
+        <v>5832</v>
       </c>
       <c r="H138" s="28" t="inlineStr"/>
       <c r="I138" s="28" t="inlineStr"/>
@@ -8427,7 +8243,7 @@
     <row r="139">
       <c r="A139" s="28" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10 MG COMPRIMIDO</t>
+          <t>ESCITALOPRAM 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B139" s="28" t="inlineStr">
@@ -8436,19 +8252,19 @@
         </is>
       </c>
       <c r="C139" s="29" t="n">
-        <v>1224</v>
+        <v>0</v>
       </c>
       <c r="D139" s="29" t="n">
-        <v>15.3</v>
+        <v>0</v>
       </c>
       <c r="E139" s="29" t="n">
-        <v>240.7</v>
+        <v>598.3</v>
       </c>
       <c r="F139" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G139" s="29" t="n">
-        <v>5832</v>
+        <v>4350</v>
       </c>
       <c r="H139" s="28" t="inlineStr"/>
       <c r="I139" s="28" t="inlineStr"/>
@@ -8456,7 +8272,7 @@
     <row r="140">
       <c r="A140" s="28" t="inlineStr">
         <is>
-          <t>ESCITALOPRAM 20 MG COMPRIMIDO</t>
+          <t>LOPERAMIDA 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B140" s="28" t="inlineStr">
@@ -8465,19 +8281,19 @@
         </is>
       </c>
       <c r="C140" s="29" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="D140" s="29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E140" s="29" t="n">
-        <v>598.3</v>
+        <v>334.8</v>
       </c>
       <c r="F140" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G140" s="29" t="n">
-        <v>4350</v>
+        <v>1560</v>
       </c>
       <c r="H140" s="28" t="inlineStr"/>
       <c r="I140" s="28" t="inlineStr"/>
@@ -8485,7 +8301,7 @@
     <row r="141">
       <c r="A141" s="28" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2 MG COMPRIMIDO</t>
+          <t>TRIHEXIFENIDILO CM 2 MG</t>
         </is>
       </c>
       <c r="B141" s="28" t="inlineStr">
@@ -8494,19 +8310,19 @@
         </is>
       </c>
       <c r="C141" s="29" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="D141" s="29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E141" s="29" t="n">
-        <v>334.8</v>
+        <v>446.4</v>
       </c>
       <c r="F141" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G141" s="29" t="n">
-        <v>1560</v>
+        <v>800</v>
       </c>
       <c r="H141" s="28" t="inlineStr"/>
       <c r="I141" s="28" t="inlineStr"/>
@@ -8514,7 +8330,7 @@
     <row r="142">
       <c r="A142" s="28" t="inlineStr">
         <is>
-          <t>TRIHEXIFENIDILO CM 2 MG</t>
+          <t>ALOPURINOL 300 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B142" s="28" t="inlineStr">
@@ -8523,19 +8339,19 @@
         </is>
       </c>
       <c r="C142" s="29" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D142" s="29" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="E142" s="29" t="n">
-        <v>446.4</v>
+        <v>469.3</v>
       </c>
       <c r="F142" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G142" s="29" t="n">
-        <v>800</v>
+        <v>5800</v>
       </c>
       <c r="H142" s="28" t="inlineStr"/>
       <c r="I142" s="28" t="inlineStr"/>
@@ -8543,7 +8359,7 @@
     <row r="143">
       <c r="A143" s="28" t="inlineStr">
         <is>
-          <t>ALOPURINOL 300 MG COMPRIMIDO</t>
+          <t>CARBONATO DE LITIO 300 MG CM</t>
         </is>
       </c>
       <c r="B143" s="28" t="inlineStr">
@@ -8552,19 +8368,19 @@
         </is>
       </c>
       <c r="C143" s="29" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="D143" s="29" t="n">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="E143" s="29" t="n">
-        <v>469.3</v>
+        <v>369.5</v>
       </c>
       <c r="F143" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G143" s="29" t="n">
-        <v>5800</v>
+        <v>5450</v>
       </c>
       <c r="H143" s="28" t="inlineStr"/>
       <c r="I143" s="28" t="inlineStr"/>
@@ -8572,7 +8388,7 @@
     <row r="144">
       <c r="A144" s="28" t="inlineStr">
         <is>
-          <t>CARBONATO DE LITIO 300 MG CM</t>
+          <t>ACIDO VALPROICO 200 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B144" s="28" t="inlineStr">
@@ -8581,19 +8397,19 @@
         </is>
       </c>
       <c r="C144" s="29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D144" s="29" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="E144" s="29" t="n">
-        <v>369.5</v>
+        <v>768.8</v>
       </c>
       <c r="F144" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G144" s="29" t="n">
-        <v>5450</v>
+        <v>1200</v>
       </c>
       <c r="H144" s="28" t="inlineStr"/>
       <c r="I144" s="28" t="inlineStr"/>
@@ -8601,7 +8417,7 @@
     <row r="145">
       <c r="A145" s="28" t="inlineStr">
         <is>
-          <t>ACIDO VALPROICO 200 MG COMPRIMIDO</t>
+          <t>ACIDO VALPROICO 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B145" s="28" t="inlineStr">
@@ -8616,13 +8432,13 @@
         <v>0</v>
       </c>
       <c r="E145" s="29" t="n">
-        <v>768.8</v>
+        <v>431.7</v>
       </c>
       <c r="F145" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G145" s="29" t="n">
-        <v>1200</v>
+        <v>9720</v>
       </c>
       <c r="H145" s="28" t="inlineStr"/>
       <c r="I145" s="28" t="inlineStr"/>
@@ -8630,7 +8446,7 @@
     <row r="146">
       <c r="A146" s="28" t="inlineStr">
         <is>
-          <t>ACIDO VALPROICO 250 MG COMPRIMIDO</t>
+          <t>INDOMETACINA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B146" s="28" t="inlineStr">
@@ -8645,13 +8461,13 @@
         <v>0</v>
       </c>
       <c r="E146" s="29" t="n">
-        <v>431.7</v>
+        <v>168.9</v>
       </c>
       <c r="F146" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G146" s="29" t="n">
-        <v>9720</v>
+        <v>1500</v>
       </c>
       <c r="H146" s="28" t="inlineStr"/>
       <c r="I146" s="28" t="inlineStr"/>
@@ -8659,7 +8475,7 @@
     <row r="147">
       <c r="A147" s="28" t="inlineStr">
         <is>
-          <t>INDOMETACINA 25 MG COMPRIMIDO</t>
+          <t>TOLTERODINA CM 2 MG</t>
         </is>
       </c>
       <c r="B147" s="28" t="inlineStr">
@@ -8674,13 +8490,13 @@
         <v>0</v>
       </c>
       <c r="E147" s="29" t="n">
-        <v>168.9</v>
+        <v>487.3</v>
       </c>
       <c r="F147" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G147" s="29" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="H147" s="28" t="inlineStr"/>
       <c r="I147" s="28" t="inlineStr"/>
@@ -8688,7 +8504,7 @@
     <row r="148">
       <c r="A148" s="28" t="inlineStr">
         <is>
-          <t>TOLTERODINA CM 2 MG</t>
+          <t>LEVETIRACETAM 1000 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B148" s="28" t="inlineStr">
@@ -8697,19 +8513,19 @@
         </is>
       </c>
       <c r="C148" s="29" t="n">
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="D148" s="29" t="n">
-        <v>8.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="E148" s="29" t="n">
-        <v>487.3</v>
+        <v>468.4</v>
       </c>
       <c r="F148" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G148" s="29" t="n">
-        <v>2100</v>
+        <v>210</v>
       </c>
       <c r="H148" s="28" t="inlineStr"/>
       <c r="I148" s="28" t="inlineStr"/>
@@ -8717,7 +8533,7 @@
     <row r="149">
       <c r="A149" s="28" t="inlineStr">
         <is>
-          <t>LEVETIRACETAM 1000 MG COMPRIMIDO</t>
+          <t>CICLOBENZAPRINA CM 10 MG</t>
         </is>
       </c>
       <c r="B149" s="28" t="inlineStr">
@@ -8726,19 +8542,19 @@
         </is>
       </c>
       <c r="C149" s="29" t="n">
-        <v>690</v>
+        <v>0</v>
       </c>
       <c r="D149" s="29" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="E149" s="29" t="n">
-        <v>468.4</v>
+        <v>460.2</v>
       </c>
       <c r="F149" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G149" s="29" t="n">
-        <v>210</v>
+        <v>8510</v>
       </c>
       <c r="H149" s="28" t="inlineStr"/>
       <c r="I149" s="28" t="inlineStr"/>
@@ -8746,7 +8562,7 @@
     <row r="150">
       <c r="A150" s="28" t="inlineStr">
         <is>
-          <t>CICLOBENZAPRINA CM 10 MG</t>
+          <t>CARVEDILOL 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B150" s="28" t="inlineStr">
@@ -8761,13 +8577,13 @@
         <v>0</v>
       </c>
       <c r="E150" s="29" t="n">
-        <v>460.2</v>
+        <v>290.1</v>
       </c>
       <c r="F150" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G150" s="29" t="n">
-        <v>8510</v>
+        <v>9390</v>
       </c>
       <c r="H150" s="28" t="inlineStr"/>
       <c r="I150" s="28" t="inlineStr"/>
@@ -8775,7 +8591,7 @@
     <row r="151">
       <c r="A151" s="28" t="inlineStr">
         <is>
-          <t>CARVEDILOL 25 MG COMPRIMIDO</t>
+          <t>LEVETIRACETAM 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B151" s="28" t="inlineStr">
@@ -8784,19 +8600,19 @@
         </is>
       </c>
       <c r="C151" s="29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D151" s="29" t="n">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="E151" s="29" t="n">
-        <v>290.1</v>
+        <v>431.8</v>
       </c>
       <c r="F151" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G151" s="29" t="n">
-        <v>9390</v>
+        <v>6760</v>
       </c>
       <c r="H151" s="28" t="inlineStr"/>
       <c r="I151" s="28" t="inlineStr"/>
@@ -8804,7 +8620,7 @@
     <row r="152">
       <c r="A152" s="28" t="inlineStr">
         <is>
-          <t>LEVETIRACETAM 500 MG COMPRIMIDO</t>
+          <t>BACLOFENO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B152" s="28" t="inlineStr">
@@ -8813,19 +8629,19 @@
         </is>
       </c>
       <c r="C152" s="29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D152" s="29" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="E152" s="29" t="n">
-        <v>431.8</v>
+        <v>638.2</v>
       </c>
       <c r="F152" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G152" s="29" t="n">
-        <v>6760</v>
+        <v>20</v>
       </c>
       <c r="H152" s="28" t="inlineStr"/>
       <c r="I152" s="28" t="inlineStr"/>
@@ -8833,7 +8649,7 @@
     <row r="153">
       <c r="A153" s="28" t="inlineStr">
         <is>
-          <t>BACLOFENO 10 MG COMPRIMIDO</t>
+          <t>BETAHISTINA 16 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B153" s="28" t="inlineStr">
@@ -8842,19 +8658,19 @@
         </is>
       </c>
       <c r="C153" s="29" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D153" s="29" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="E153" s="29" t="n">
-        <v>638.2</v>
+        <v>230.8</v>
       </c>
       <c r="F153" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G153" s="29" t="n">
-        <v>20</v>
+        <v>5224</v>
       </c>
       <c r="H153" s="28" t="inlineStr"/>
       <c r="I153" s="28" t="inlineStr"/>
@@ -8862,7 +8678,7 @@
     <row r="154">
       <c r="A154" s="28" t="inlineStr">
         <is>
-          <t>BETAHISTINA 16 MG COMPRIMIDO</t>
+          <t>AZATIOPRINA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B154" s="28" t="inlineStr">
@@ -8871,19 +8687,19 @@
         </is>
       </c>
       <c r="C154" s="29" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D154" s="29" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="E154" s="29" t="n">
-        <v>230.8</v>
+        <v>590.2</v>
       </c>
       <c r="F154" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G154" s="29" t="n">
-        <v>5224</v>
+        <v>23700</v>
       </c>
       <c r="H154" s="28" t="inlineStr"/>
       <c r="I154" s="28" t="inlineStr"/>
@@ -8891,7 +8707,7 @@
     <row r="155">
       <c r="A155" s="28" t="inlineStr">
         <is>
-          <t>AZATIOPRINA 50 MG COMPRIMIDO</t>
+          <t>PROPANOLOL 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B155" s="28" t="inlineStr">
@@ -8900,19 +8716,19 @@
         </is>
       </c>
       <c r="C155" s="29" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D155" s="29" t="n">
-        <v>8.5</v>
+        <v>17.1</v>
       </c>
       <c r="E155" s="29" t="n">
-        <v>590.2</v>
+        <v>343</v>
       </c>
       <c r="F155" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G155" s="29" t="n">
-        <v>23700</v>
+        <v>7000</v>
       </c>
       <c r="H155" s="28" t="inlineStr"/>
       <c r="I155" s="28" t="inlineStr"/>
@@ -8920,7 +8736,7 @@
     <row r="156">
       <c r="A156" s="28" t="inlineStr">
         <is>
-          <t>PROPANOLOL 40 MG COMPRIMIDO</t>
+          <t>ACETATO DE CALCIO 667 MG CM UD</t>
         </is>
       </c>
       <c r="B156" s="28" t="inlineStr">
@@ -8929,19 +8745,19 @@
         </is>
       </c>
       <c r="C156" s="29" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="D156" s="29" t="n">
-        <v>17.1</v>
+        <v>10.5</v>
       </c>
       <c r="E156" s="29" t="n">
-        <v>343</v>
+        <v>974.9</v>
       </c>
       <c r="F156" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G156" s="29" t="n">
-        <v>7000</v>
+        <v>10440</v>
       </c>
       <c r="H156" s="28" t="inlineStr"/>
       <c r="I156" s="28" t="inlineStr"/>
@@ -8949,7 +8765,7 @@
     <row r="157">
       <c r="A157" s="28" t="inlineStr">
         <is>
-          <t>ACETATO DE CALCIO 667 MG CM UD</t>
+          <t>LAMOTRIGINA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B157" s="28" t="inlineStr">
@@ -8958,19 +8774,19 @@
         </is>
       </c>
       <c r="C157" s="29" t="n">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="D157" s="29" t="n">
-        <v>10.5</v>
+        <v>28.4</v>
       </c>
       <c r="E157" s="29" t="n">
-        <v>974.9</v>
+        <v>564.9</v>
       </c>
       <c r="F157" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G157" s="29" t="n">
-        <v>10440</v>
+        <v>10400</v>
       </c>
       <c r="H157" s="28" t="inlineStr"/>
       <c r="I157" s="28" t="inlineStr"/>
@@ -8978,7 +8794,7 @@
     <row r="158">
       <c r="A158" s="28" t="inlineStr">
         <is>
-          <t>LAMOTRIGINA 50 MG COMPRIMIDO</t>
+          <t>DUTASTERIDA 500 MCG + TAMSULOSINA 400 MCG CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B158" s="28" t="inlineStr">
@@ -8987,19 +8803,19 @@
         </is>
       </c>
       <c r="C158" s="29" t="n">
-        <v>1600</v>
+        <v>570</v>
       </c>
       <c r="D158" s="29" t="n">
-        <v>28.4</v>
+        <v>10.2</v>
       </c>
       <c r="E158" s="29" t="n">
-        <v>564.9</v>
+        <v>393.8</v>
       </c>
       <c r="F158" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G158" s="29" t="n">
-        <v>10400</v>
+        <v>6030</v>
       </c>
       <c r="H158" s="28" t="inlineStr"/>
       <c r="I158" s="28" t="inlineStr"/>
@@ -9007,7 +8823,7 @@
     <row r="159">
       <c r="A159" s="28" t="inlineStr">
         <is>
-          <t>DUTASTERIDA 500 MCG + TAMSULOSINA 400 MCG CAPSULA LIBERACION MODIFICADA</t>
+          <t>TAPENTADOL 50 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B159" s="28" t="inlineStr">
@@ -9016,19 +8832,19 @@
         </is>
       </c>
       <c r="C159" s="29" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="D159" s="29" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="E159" s="29" t="n">
-        <v>393.8</v>
+        <v>324.3</v>
       </c>
       <c r="F159" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G159" s="29" t="n">
-        <v>6030</v>
+        <v>0</v>
       </c>
       <c r="H159" s="28" t="inlineStr"/>
       <c r="I159" s="28" t="inlineStr"/>
@@ -9036,7 +8852,7 @@
     <row r="160">
       <c r="A160" s="28" t="inlineStr">
         <is>
-          <t>TAPENTADOL 50 MG CM LIBERACION MODIFICADA</t>
+          <t>TIAMAZOL 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B160" s="28" t="inlineStr">
@@ -9045,19 +8861,19 @@
         </is>
       </c>
       <c r="C160" s="29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D160" s="29" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="E160" s="29" t="n">
-        <v>324.3</v>
+        <v>442.2</v>
       </c>
       <c r="F160" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G160" s="29" t="n">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="H160" s="28" t="inlineStr"/>
       <c r="I160" s="28" t="inlineStr"/>
@@ -9065,7 +8881,7 @@
     <row r="161">
       <c r="A161" s="28" t="inlineStr">
         <is>
-          <t>TIAMAZOL 10 MG COMPRIMIDO</t>
+          <t>ALOPURINOL 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B161" s="28" t="inlineStr">
@@ -9074,19 +8890,19 @@
         </is>
       </c>
       <c r="C161" s="29" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="D161" s="29" t="n">
-        <v>18.5</v>
+        <v>11.2</v>
       </c>
       <c r="E161" s="29" t="n">
-        <v>442.2</v>
+        <v>308.9</v>
       </c>
       <c r="F161" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G161" s="29" t="n">
-        <v>2900</v>
+        <v>6600</v>
       </c>
       <c r="H161" s="28" t="inlineStr"/>
       <c r="I161" s="28" t="inlineStr"/>
@@ -9094,7 +8910,7 @@
     <row r="162">
       <c r="A162" s="28" t="inlineStr">
         <is>
-          <t>ALOPURINOL 100 MG COMPRIMIDO</t>
+          <t>OXIBUTININA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B162" s="28" t="inlineStr">
@@ -9103,19 +8919,19 @@
         </is>
       </c>
       <c r="C162" s="29" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="D162" s="29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E162" s="29" t="n">
-        <v>308.9</v>
+        <v>357</v>
       </c>
       <c r="F162" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G162" s="29" t="n">
-        <v>6600</v>
+        <v>11950</v>
       </c>
       <c r="H162" s="28" t="inlineStr"/>
       <c r="I162" s="28" t="inlineStr"/>
@@ -9123,7 +8939,7 @@
     <row r="163">
       <c r="A163" s="28" t="inlineStr">
         <is>
-          <t>OXIBUTININA 5 MG COMPRIMIDO</t>
+          <t>PAROXETINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B163" s="28" t="inlineStr">
@@ -9132,19 +8948,19 @@
         </is>
       </c>
       <c r="C163" s="29" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="D163" s="29" t="n">
-        <v>11.5</v>
+        <v>19.2</v>
       </c>
       <c r="E163" s="29" t="n">
-        <v>357</v>
+        <v>355.9</v>
       </c>
       <c r="F163" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G163" s="29" t="n">
-        <v>11950</v>
+        <v>13000</v>
       </c>
       <c r="H163" s="28" t="inlineStr"/>
       <c r="I163" s="28" t="inlineStr"/>
@@ -9152,7 +8968,7 @@
     <row r="164">
       <c r="A164" s="28" t="inlineStr">
         <is>
-          <t>PAROXETINA 20 MG COMPRIMIDO</t>
+          <t>DONEPEZILO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B164" s="28" t="inlineStr">
@@ -9161,19 +8977,19 @@
         </is>
       </c>
       <c r="C164" s="29" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="D164" s="29" t="n">
-        <v>19.2</v>
+        <v>4.2</v>
       </c>
       <c r="E164" s="29" t="n">
-        <v>355.9</v>
+        <v>252.9</v>
       </c>
       <c r="F164" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G164" s="29" t="n">
-        <v>13000</v>
+        <v>1890</v>
       </c>
       <c r="H164" s="28" t="inlineStr"/>
       <c r="I164" s="28" t="inlineStr"/>
@@ -9181,7 +8997,7 @@
     <row r="165">
       <c r="A165" s="28" t="inlineStr">
         <is>
-          <t>DONEPEZILO 10 MG COMPRIMIDO</t>
+          <t>TRAZODONA CLORHIDRATO 25 MG CM</t>
         </is>
       </c>
       <c r="B165" s="28" t="inlineStr">
@@ -9190,19 +9006,19 @@
         </is>
       </c>
       <c r="C165" s="29" t="n">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="D165" s="29" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="E165" s="29" t="n">
-        <v>252.9</v>
+        <v>337.3</v>
       </c>
       <c r="F165" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G165" s="29" t="n">
-        <v>1890</v>
+        <v>2400</v>
       </c>
       <c r="H165" s="28" t="inlineStr"/>
       <c r="I165" s="28" t="inlineStr"/>
@@ -9210,7 +9026,7 @@
     <row r="166">
       <c r="A166" s="28" t="inlineStr">
         <is>
-          <t>TRAZODONA CLORHIDRATO 25 MG CM</t>
+          <t>SULFASALAZINA 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B166" s="28" t="inlineStr">
@@ -9219,19 +9035,19 @@
         </is>
       </c>
       <c r="C166" s="29" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D166" s="29" t="n">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="E166" s="29" t="n">
-        <v>337.3</v>
+        <v>487.9</v>
       </c>
       <c r="F166" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G166" s="29" t="n">
-        <v>2400</v>
+        <v>8300</v>
       </c>
       <c r="H166" s="28" t="inlineStr"/>
       <c r="I166" s="28" t="inlineStr"/>
@@ -9239,7 +9055,7 @@
     <row r="167">
       <c r="A167" s="28" t="inlineStr">
         <is>
-          <t>SULFASALAZINA 500 MG COMPRIMIDO</t>
+          <t>MIRTAZAPINA 15 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B167" s="28" t="inlineStr">
@@ -9248,19 +9064,19 @@
         </is>
       </c>
       <c r="C167" s="29" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D167" s="29" t="n">
-        <v>10.1</v>
+        <v>6.4</v>
       </c>
       <c r="E167" s="29" t="n">
-        <v>487.9</v>
+        <v>280.9</v>
       </c>
       <c r="F167" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G167" s="29" t="n">
-        <v>8300</v>
+        <v>7020</v>
       </c>
       <c r="H167" s="28" t="inlineStr"/>
       <c r="I167" s="28" t="inlineStr"/>
@@ -9268,7 +9084,7 @@
     <row r="168">
       <c r="A168" s="28" t="inlineStr">
         <is>
-          <t>MIRTAZAPINA 15 MG COMPRIMIDO</t>
+          <t>PROPANOLOL 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B168" s="28" t="inlineStr">
@@ -9277,19 +9093,19 @@
         </is>
       </c>
       <c r="C168" s="29" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="D168" s="29" t="n">
-        <v>6.4</v>
+        <v>21.5</v>
       </c>
       <c r="E168" s="29" t="n">
-        <v>280.9</v>
+        <v>271.9</v>
       </c>
       <c r="F168" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G168" s="29" t="n">
-        <v>7020</v>
+        <v>5000</v>
       </c>
       <c r="H168" s="28" t="inlineStr"/>
       <c r="I168" s="28" t="inlineStr"/>
@@ -9297,7 +9113,7 @@
     <row r="169">
       <c r="A169" s="28" t="inlineStr">
         <is>
-          <t>PROPANOLOL 10 MG COMPRIMIDO</t>
+          <t>NAPROXENO 550 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B169" s="28" t="inlineStr">
@@ -9306,19 +9122,19 @@
         </is>
       </c>
       <c r="C169" s="29" t="n">
-        <v>1000</v>
+        <v>2900</v>
       </c>
       <c r="D169" s="29" t="n">
-        <v>21.5</v>
+        <v>62.7</v>
       </c>
       <c r="E169" s="29" t="n">
-        <v>271.9</v>
+        <v>248.7</v>
       </c>
       <c r="F169" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G169" s="29" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H169" s="28" t="inlineStr"/>
       <c r="I169" s="28" t="inlineStr"/>
@@ -9326,7 +9142,7 @@
     <row r="170">
       <c r="A170" s="28" t="inlineStr">
         <is>
-          <t>NAPROXENO 550 MG COMPRIMIDO</t>
+          <t>ACIDO FOLICO CM 1 MG</t>
         </is>
       </c>
       <c r="B170" s="28" t="inlineStr">
@@ -9335,19 +9151,19 @@
         </is>
       </c>
       <c r="C170" s="29" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="D170" s="29" t="n">
-        <v>75.7</v>
+        <v>0</v>
       </c>
       <c r="E170" s="29" t="n">
-        <v>248.7</v>
+        <v>284.9</v>
       </c>
       <c r="F170" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G170" s="29" t="n">
-        <v>0</v>
+        <v>13640</v>
       </c>
       <c r="H170" s="28" t="inlineStr"/>
       <c r="I170" s="28" t="inlineStr"/>
@@ -9355,7 +9171,7 @@
     <row r="171">
       <c r="A171" s="28" t="inlineStr">
         <is>
-          <t>ACIDO FOLICO CM 1 MG</t>
+          <t>TOPIRAMATO 50 MG CM</t>
         </is>
       </c>
       <c r="B171" s="28" t="inlineStr">
@@ -9370,13 +9186,13 @@
         <v>0</v>
       </c>
       <c r="E171" s="29" t="n">
-        <v>284.9</v>
+        <v>215.5</v>
       </c>
       <c r="F171" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G171" s="29" t="n">
-        <v>13640</v>
+        <v>2760</v>
       </c>
       <c r="H171" s="28" t="inlineStr"/>
       <c r="I171" s="28" t="inlineStr"/>
@@ -9384,7 +9200,7 @@
     <row r="172">
       <c r="A172" s="28" t="inlineStr">
         <is>
-          <t>TOPIRAMATO 50 MG CM</t>
+          <t>DIAZEPAM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B172" s="28" t="inlineStr">
@@ -9399,13 +9215,13 @@
         <v>0</v>
       </c>
       <c r="E172" s="29" t="n">
-        <v>215.5</v>
+        <v>236.9</v>
       </c>
       <c r="F172" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G172" s="29" t="n">
-        <v>2760</v>
+        <v>0</v>
       </c>
       <c r="H172" s="28" t="inlineStr"/>
       <c r="I172" s="28" t="inlineStr"/>
@@ -9413,7 +9229,7 @@
     <row r="173">
       <c r="A173" s="28" t="inlineStr">
         <is>
-          <t>DIAZEPAM 10 MG COMPRIMIDO</t>
+          <t>LORAZEPAM 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B173" s="28" t="inlineStr">
@@ -9428,7 +9244,7 @@
         <v>0</v>
       </c>
       <c r="E173" s="29" t="n">
-        <v>236.9</v>
+        <v>259.2</v>
       </c>
       <c r="F173" s="29" t="n">
         <v>0</v>
@@ -9442,7 +9258,7 @@
     <row r="174">
       <c r="A174" s="28" t="inlineStr">
         <is>
-          <t>LORAZEPAM 2 MG COMPRIMIDO</t>
+          <t>BISOPROLOL 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B174" s="28" t="inlineStr">
@@ -9457,7 +9273,7 @@
         <v>0</v>
       </c>
       <c r="E174" s="29" t="n">
-        <v>259.2</v>
+        <v>281.6</v>
       </c>
       <c r="F174" s="29" t="n">
         <v>0</v>
@@ -9471,7 +9287,7 @@
     <row r="175">
       <c r="A175" s="28" t="inlineStr">
         <is>
-          <t>BISOPROLOL 5 MG COMPRIMIDO</t>
+          <t>COLCHICINA 0,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B175" s="28" t="inlineStr">
@@ -9486,13 +9302,13 @@
         <v>0</v>
       </c>
       <c r="E175" s="29" t="n">
-        <v>281.6</v>
+        <v>188</v>
       </c>
       <c r="F175" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G175" s="29" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="H175" s="28" t="inlineStr"/>
       <c r="I175" s="28" t="inlineStr"/>
@@ -9500,7 +9316,7 @@
     <row r="176">
       <c r="A176" s="28" t="inlineStr">
         <is>
-          <t>COLCHICINA 0,5 MG COMPRIMIDO</t>
+          <t>PIRIDOSTIGMINA 60 MG COMPRIMIDOS O GRAGEAS.</t>
         </is>
       </c>
       <c r="B176" s="28" t="inlineStr">
@@ -9515,13 +9331,13 @@
         <v>0</v>
       </c>
       <c r="E176" s="29" t="n">
-        <v>188</v>
+        <v>130.9</v>
       </c>
       <c r="F176" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G176" s="29" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="H176" s="28" t="inlineStr"/>
       <c r="I176" s="28" t="inlineStr"/>
@@ -9529,7 +9345,7 @@
     <row r="177">
       <c r="A177" s="28" t="inlineStr">
         <is>
-          <t>PIRIDOSTIGMINA 60 MG COMPRIMIDOS O GRAGEAS.</t>
+          <t>TRIMEBUTINA 200 MG CM /CR</t>
         </is>
       </c>
       <c r="B177" s="28" t="inlineStr">
@@ -9544,13 +9360,13 @@
         <v>0</v>
       </c>
       <c r="E177" s="29" t="n">
-        <v>130.9</v>
+        <v>271.5</v>
       </c>
       <c r="F177" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G177" s="29" t="n">
-        <v>1100</v>
+        <v>2000</v>
       </c>
       <c r="H177" s="28" t="inlineStr"/>
       <c r="I177" s="28" t="inlineStr"/>
@@ -9558,7 +9374,7 @@
     <row r="178">
       <c r="A178" s="28" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200 MG CM /CR</t>
+          <t>SACUBITRILO VALSARTAN 100 MG</t>
         </is>
       </c>
       <c r="B178" s="28" t="inlineStr">
@@ -9573,13 +9389,13 @@
         <v>0</v>
       </c>
       <c r="E178" s="29" t="n">
-        <v>271.5</v>
+        <v>85</v>
       </c>
       <c r="F178" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G178" s="29" t="n">
-        <v>2000</v>
+        <v>3300</v>
       </c>
       <c r="H178" s="28" t="inlineStr"/>
       <c r="I178" s="28" t="inlineStr"/>
@@ -9587,7 +9403,7 @@
     <row r="179">
       <c r="A179" s="28" t="inlineStr">
         <is>
-          <t>SACUBITRILO VALSARTAN 100 MG</t>
+          <t>ONDANSETRON 8 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B179" s="28" t="inlineStr">
@@ -9596,19 +9412,19 @@
         </is>
       </c>
       <c r="C179" s="29" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D179" s="29" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E179" s="29" t="n">
-        <v>85</v>
+        <v>197.1</v>
       </c>
       <c r="F179" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G179" s="29" t="n">
-        <v>3300</v>
+        <v>9950</v>
       </c>
       <c r="H179" s="28" t="inlineStr"/>
       <c r="I179" s="28" t="inlineStr"/>
@@ -9616,7 +9432,7 @@
     <row r="180">
       <c r="A180" s="28" t="inlineStr">
         <is>
-          <t>ONDANSETRON 8 MG COMPRIMIDO</t>
+          <t>LORATADINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B180" s="28" t="inlineStr">
@@ -9625,19 +9441,19 @@
         </is>
       </c>
       <c r="C180" s="29" t="n">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="D180" s="29" t="n">
-        <v>8.199999999999999</v>
+        <v>42.2</v>
       </c>
       <c r="E180" s="29" t="n">
-        <v>197.1</v>
+        <v>154.9</v>
       </c>
       <c r="F180" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G180" s="29" t="n">
-        <v>9950</v>
+        <v>3000</v>
       </c>
       <c r="H180" s="28" t="inlineStr"/>
       <c r="I180" s="28" t="inlineStr"/>
@@ -9645,7 +9461,7 @@
     <row r="181">
       <c r="A181" s="28" t="inlineStr">
         <is>
-          <t>LORATADINA 10 MG COMPRIMIDO</t>
+          <t>PREDNISONA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B181" s="28" t="inlineStr">
@@ -9654,19 +9470,19 @@
         </is>
       </c>
       <c r="C181" s="29" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="D181" s="29" t="n">
-        <v>42.2</v>
+        <v>34</v>
       </c>
       <c r="E181" s="29" t="n">
-        <v>154.9</v>
+        <v>352.5</v>
       </c>
       <c r="F181" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G181" s="29" t="n">
-        <v>3000</v>
+        <v>1700</v>
       </c>
       <c r="H181" s="28" t="inlineStr"/>
       <c r="I181" s="28" t="inlineStr"/>
@@ -9674,7 +9490,7 @@
     <row r="182">
       <c r="A182" s="28" t="inlineStr">
         <is>
-          <t>PREDNISONA 20 MG COMPRIMIDO</t>
+          <t>NIFEDIPINO 20 MG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B182" s="28" t="inlineStr">
@@ -9683,19 +9499,19 @@
         </is>
       </c>
       <c r="C182" s="29" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="D182" s="29" t="n">
-        <v>42.6</v>
+        <v>0</v>
       </c>
       <c r="E182" s="29" t="n">
-        <v>352.5</v>
+        <v>393.3</v>
       </c>
       <c r="F182" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G182" s="29" t="n">
-        <v>1700</v>
+        <v>9000</v>
       </c>
       <c r="H182" s="28" t="inlineStr"/>
       <c r="I182" s="28" t="inlineStr"/>
@@ -9703,7 +9519,7 @@
     <row r="183">
       <c r="A183" s="28" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 20 MG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>ATROPINA SULFATO 0,5 MG + PAPAVERINA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B183" s="28" t="inlineStr">
@@ -9712,19 +9528,19 @@
         </is>
       </c>
       <c r="C183" s="29" t="n">
-        <v>0</v>
+        <v>795</v>
       </c>
       <c r="D183" s="29" t="n">
-        <v>0</v>
+        <v>24.1</v>
       </c>
       <c r="E183" s="29" t="n">
-        <v>393.3</v>
+        <v>234.7</v>
       </c>
       <c r="F183" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G183" s="29" t="n">
-        <v>9000</v>
+        <v>13560</v>
       </c>
       <c r="H183" s="28" t="inlineStr"/>
       <c r="I183" s="28" t="inlineStr"/>
@@ -9732,7 +9548,7 @@
     <row r="184">
       <c r="A184" s="28" t="inlineStr">
         <is>
-          <t>ATROPINA SULFATO 0,5 MG + PAPAVERINA 40 MG COMPRIMIDO</t>
+          <t>HEPARINA SODICA 25.000 U.I./5 ML FA/JRP</t>
         </is>
       </c>
       <c r="B184" s="28" t="inlineStr">
@@ -9741,19 +9557,19 @@
         </is>
       </c>
       <c r="C184" s="29" t="n">
-        <v>795</v>
+        <v>0</v>
       </c>
       <c r="D184" s="29" t="n">
-        <v>24.1</v>
+        <v>0</v>
       </c>
       <c r="E184" s="29" t="n">
-        <v>234.7</v>
+        <v>218.5</v>
       </c>
       <c r="F184" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G184" s="29" t="n">
-        <v>13560</v>
+        <v>2550</v>
       </c>
       <c r="H184" s="28" t="inlineStr"/>
       <c r="I184" s="28" t="inlineStr"/>
@@ -9761,7 +9577,7 @@
     <row r="185">
       <c r="A185" s="28" t="inlineStr">
         <is>
-          <t>HEPARINA SODICA 25.000 U.I./5 ML FA/JRP</t>
+          <t>HALOPERIDOL 1 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B185" s="28" t="inlineStr">
@@ -9776,13 +9592,13 @@
         <v>0</v>
       </c>
       <c r="E185" s="29" t="n">
-        <v>218.5</v>
+        <v>233.8</v>
       </c>
       <c r="F185" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G185" s="29" t="n">
-        <v>2550</v>
+        <v>3840</v>
       </c>
       <c r="H185" s="28" t="inlineStr"/>
       <c r="I185" s="28" t="inlineStr"/>
@@ -9790,7 +9606,7 @@
     <row r="186">
       <c r="A186" s="28" t="inlineStr">
         <is>
-          <t>HALOPERIDOL 1 MG COMPRIMIDO</t>
+          <t>MIRTAZAPINA 30 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B186" s="28" t="inlineStr">
@@ -9799,19 +9615,19 @@
         </is>
       </c>
       <c r="C186" s="29" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D186" s="29" t="n">
-        <v>0</v>
+        <v>20.4</v>
       </c>
       <c r="E186" s="29" t="n">
-        <v>233.8</v>
+        <v>224.2</v>
       </c>
       <c r="F186" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G186" s="29" t="n">
-        <v>3840</v>
+        <v>3210</v>
       </c>
       <c r="H186" s="28" t="inlineStr"/>
       <c r="I186" s="28" t="inlineStr"/>
@@ -9819,7 +9635,7 @@
     <row r="187">
       <c r="A187" s="28" t="inlineStr">
         <is>
-          <t>MIRTAZAPINA 30 MG COMPRIMIDO</t>
+          <t>IBUPROFENO 400 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B187" s="28" t="inlineStr">
@@ -9828,19 +9644,19 @@
         </is>
       </c>
       <c r="C187" s="29" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D187" s="29" t="n">
-        <v>20.4</v>
+        <v>17.2</v>
       </c>
       <c r="E187" s="29" t="n">
-        <v>224.2</v>
+        <v>217.9</v>
       </c>
       <c r="F187" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G187" s="29" t="n">
-        <v>3210</v>
+        <v>2000</v>
       </c>
       <c r="H187" s="28" t="inlineStr"/>
       <c r="I187" s="28" t="inlineStr"/>
@@ -9848,7 +9664,7 @@
     <row r="188">
       <c r="A188" s="28" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400 MG COMPRIMIDO</t>
+          <t>TRAMADOL 100 MG CM L.P</t>
         </is>
       </c>
       <c r="B188" s="28" t="inlineStr">
@@ -9857,19 +9673,19 @@
         </is>
       </c>
       <c r="C188" s="29" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D188" s="29" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="E188" s="29" t="n">
-        <v>217.9</v>
+        <v>194.1</v>
       </c>
       <c r="F188" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G188" s="29" t="n">
-        <v>2000</v>
+        <v>15520</v>
       </c>
       <c r="H188" s="28" t="inlineStr"/>
       <c r="I188" s="28" t="inlineStr"/>
@@ -9877,7 +9693,7 @@
     <row r="189">
       <c r="A189" s="28" t="inlineStr">
         <is>
-          <t>TRAMADOL 100 MG CM L.P</t>
+          <t>CLORFENAMINA 4 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B189" s="28" t="inlineStr">
@@ -9886,19 +9702,19 @@
         </is>
       </c>
       <c r="C189" s="29" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="D189" s="29" t="n">
-        <v>20.7</v>
+        <v>45.4</v>
       </c>
       <c r="E189" s="29" t="n">
-        <v>194.1</v>
+        <v>296.6</v>
       </c>
       <c r="F189" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G189" s="29" t="n">
-        <v>15520</v>
+        <v>3880</v>
       </c>
       <c r="H189" s="28" t="inlineStr"/>
       <c r="I189" s="28" t="inlineStr"/>
@@ -9906,7 +9722,7 @@
     <row r="190">
       <c r="A190" s="28" t="inlineStr">
         <is>
-          <t>CLORFENAMINA 4 MG COMPRIMIDO</t>
+          <t>TOPIRAMATO 100 MG CM</t>
         </is>
       </c>
       <c r="B190" s="28" t="inlineStr">
@@ -9915,19 +9731,19 @@
         </is>
       </c>
       <c r="C190" s="29" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="D190" s="29" t="n">
-        <v>45.4</v>
+        <v>0</v>
       </c>
       <c r="E190" s="29" t="n">
-        <v>296.6</v>
+        <v>159.2</v>
       </c>
       <c r="F190" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G190" s="29" t="n">
-        <v>3880</v>
+        <v>280</v>
       </c>
       <c r="H190" s="28" t="inlineStr"/>
       <c r="I190" s="28" t="inlineStr"/>
@@ -9935,7 +9751,7 @@
     <row r="191">
       <c r="A191" s="28" t="inlineStr">
         <is>
-          <t>TOPIRAMATO 100 MG CM</t>
+          <t>METILFENIDATO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B191" s="28" t="inlineStr">
@@ -9950,13 +9766,13 @@
         <v>0</v>
       </c>
       <c r="E191" s="29" t="n">
-        <v>159.2</v>
+        <v>237.3</v>
       </c>
       <c r="F191" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G191" s="29" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="H191" s="28" t="inlineStr"/>
       <c r="I191" s="28" t="inlineStr"/>
@@ -9964,7 +9780,7 @@
     <row r="192">
       <c r="A192" s="28" t="inlineStr">
         <is>
-          <t>METILFENIDATO 10 MG COMPRIMIDO</t>
+          <t>MULTIVITAMINICO COMPRIMIDO</t>
         </is>
       </c>
       <c r="B192" s="28" t="inlineStr">
@@ -9973,19 +9789,19 @@
         </is>
       </c>
       <c r="C192" s="29" t="n">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="D192" s="29" t="n">
-        <v>0</v>
+        <v>28.3</v>
       </c>
       <c r="E192" s="29" t="n">
-        <v>237.3</v>
+        <v>262.1</v>
       </c>
       <c r="F192" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G192" s="29" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H192" s="28" t="inlineStr"/>
       <c r="I192" s="28" t="inlineStr"/>
@@ -9993,7 +9809,7 @@
     <row r="193">
       <c r="A193" s="28" t="inlineStr">
         <is>
-          <t>MULTIVITAMINICO COMPRIMIDO</t>
+          <t>CETIRIZINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B193" s="28" t="inlineStr">
@@ -10002,19 +9818,19 @@
         </is>
       </c>
       <c r="C193" s="29" t="n">
-        <v>769</v>
+        <v>0</v>
       </c>
       <c r="D193" s="29" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="E193" s="29" t="n">
-        <v>262.1</v>
+        <v>209.1</v>
       </c>
       <c r="F193" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G193" s="29" t="n">
-        <v>2100</v>
+        <v>150</v>
       </c>
       <c r="H193" s="28" t="inlineStr"/>
       <c r="I193" s="28" t="inlineStr"/>
@@ -10022,7 +9838,7 @@
     <row r="194">
       <c r="A194" s="28" t="inlineStr">
         <is>
-          <t>CETIRIZINA 10 MG COMPRIMIDO</t>
+          <t>PRAMIPEXOL 0,25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B194" s="28" t="inlineStr">
@@ -10037,13 +9853,13 @@
         <v>0</v>
       </c>
       <c r="E194" s="29" t="n">
-        <v>209.1</v>
+        <v>262.2</v>
       </c>
       <c r="F194" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G194" s="29" t="n">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="H194" s="28" t="inlineStr"/>
       <c r="I194" s="28" t="inlineStr"/>
@@ -10051,7 +9867,7 @@
     <row r="195">
       <c r="A195" s="28" t="inlineStr">
         <is>
-          <t>PRAMIPEXOL 0,25 MG COMPRIMIDO</t>
+          <t>SEVELAMER 800 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B195" s="28" t="inlineStr">
@@ -10060,19 +9876,19 @@
         </is>
       </c>
       <c r="C195" s="29" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="D195" s="29" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="E195" s="29" t="n">
-        <v>262.2</v>
+        <v>168.6</v>
       </c>
       <c r="F195" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G195" s="29" t="n">
-        <v>750</v>
+        <v>4680</v>
       </c>
       <c r="H195" s="28" t="inlineStr"/>
       <c r="I195" s="28" t="inlineStr"/>
@@ -10080,7 +9896,7 @@
     <row r="196">
       <c r="A196" s="28" t="inlineStr">
         <is>
-          <t>SEVELAMER 800 MG COMPRIMIDO</t>
+          <t>DIGOXINA 0,25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B196" s="28" t="inlineStr">
@@ -10089,19 +9905,19 @@
         </is>
       </c>
       <c r="C196" s="29" t="n">
-        <v>360</v>
+        <v>960</v>
       </c>
       <c r="D196" s="29" t="n">
-        <v>14.2</v>
+        <v>38.4</v>
       </c>
       <c r="E196" s="29" t="n">
-        <v>168.6</v>
+        <v>239</v>
       </c>
       <c r="F196" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G196" s="29" t="n">
-        <v>4680</v>
+        <v>4800</v>
       </c>
       <c r="H196" s="28" t="inlineStr"/>
       <c r="I196" s="28" t="inlineStr"/>
@@ -10109,7 +9925,7 @@
     <row r="197">
       <c r="A197" s="28" t="inlineStr">
         <is>
-          <t>DIGOXINA 0,25 MG COMPRIMIDO</t>
+          <t>FAMOTIDINA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B197" s="28" t="inlineStr">
@@ -10118,19 +9934,19 @@
         </is>
       </c>
       <c r="C197" s="29" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="D197" s="29" t="n">
-        <v>38.4</v>
+        <v>0</v>
       </c>
       <c r="E197" s="29" t="n">
-        <v>239</v>
+        <v>162</v>
       </c>
       <c r="F197" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G197" s="29" t="n">
-        <v>4800</v>
+        <v>500</v>
       </c>
       <c r="H197" s="28" t="inlineStr"/>
       <c r="I197" s="28" t="inlineStr"/>
@@ -10138,7 +9954,7 @@
     <row r="198">
       <c r="A198" s="28" t="inlineStr">
         <is>
-          <t>FAMOTIDINA 40 MG COMPRIMIDO</t>
+          <t>CLORPROMAZINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B198" s="28" t="inlineStr">
@@ -10153,13 +9969,13 @@
         <v>0</v>
       </c>
       <c r="E198" s="29" t="n">
-        <v>162</v>
+        <v>262.5</v>
       </c>
       <c r="F198" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G198" s="29" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H198" s="28" t="inlineStr"/>
       <c r="I198" s="28" t="inlineStr"/>
@@ -10167,7 +9983,7 @@
     <row r="199">
       <c r="A199" s="28" t="inlineStr">
         <is>
-          <t>CLORPROMAZINA 100 MG COMPRIMIDO</t>
+          <t>HALOPERIDOL 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B199" s="28" t="inlineStr">
@@ -10176,19 +9992,19 @@
         </is>
       </c>
       <c r="C199" s="29" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D199" s="29" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="E199" s="29" t="n">
-        <v>262.5</v>
+        <v>150.2</v>
       </c>
       <c r="F199" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G199" s="29" t="n">
-        <v>0</v>
+        <v>5460</v>
       </c>
       <c r="H199" s="28" t="inlineStr"/>
       <c r="I199" s="28" t="inlineStr"/>
@@ -10196,7 +10012,7 @@
     <row r="200">
       <c r="A200" s="28" t="inlineStr">
         <is>
-          <t>HALOPERIDOL 5 MG COMPRIMIDO</t>
+          <t>ERITROPOYETINA 4.000 UI</t>
         </is>
       </c>
       <c r="B200" s="28" t="inlineStr">
@@ -10205,19 +10021,19 @@
         </is>
       </c>
       <c r="C200" s="29" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D200" s="29" t="n">
-        <v>24.8</v>
+        <v>0</v>
       </c>
       <c r="E200" s="29" t="n">
-        <v>150.2</v>
+        <v>168.8</v>
       </c>
       <c r="F200" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G200" s="29" t="n">
-        <v>5460</v>
+        <v>1650</v>
       </c>
       <c r="H200" s="28" t="inlineStr"/>
       <c r="I200" s="28" t="inlineStr"/>
@@ -10225,7 +10041,7 @@
     <row r="201">
       <c r="A201" s="28" t="inlineStr">
         <is>
-          <t>ERITROPOYETINA 4.000 UI</t>
+          <t>CITALOPRAM 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B201" s="28" t="inlineStr">
@@ -10234,19 +10050,19 @@
         </is>
       </c>
       <c r="C201" s="29" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="D201" s="29" t="n">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E201" s="29" t="n">
-        <v>168.8</v>
+        <v>318.5</v>
       </c>
       <c r="F201" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G201" s="29" t="n">
-        <v>1650</v>
+        <v>11640</v>
       </c>
       <c r="H201" s="28" t="inlineStr"/>
       <c r="I201" s="28" t="inlineStr"/>
@@ -10254,7 +10070,7 @@
     <row r="202">
       <c r="A202" s="28" t="inlineStr">
         <is>
-          <t>CITALOPRAM 20 MG COMPRIMIDO</t>
+          <t>ACETAZOLAMIDA CM 250 MG</t>
         </is>
       </c>
       <c r="B202" s="28" t="inlineStr">
@@ -10263,19 +10079,19 @@
         </is>
       </c>
       <c r="C202" s="29" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="D202" s="29" t="n">
-        <v>96.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="E202" s="29" t="n">
-        <v>318.5</v>
+        <v>159.6</v>
       </c>
       <c r="F202" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G202" s="29" t="n">
-        <v>11640</v>
+        <v>2200</v>
       </c>
       <c r="H202" s="28" t="inlineStr"/>
       <c r="I202" s="28" t="inlineStr"/>
@@ -10283,7 +10099,7 @@
     <row r="203">
       <c r="A203" s="28" t="inlineStr">
         <is>
-          <t>ACETAZOLAMIDA CM 250 MG</t>
+          <t>GEMFIBROZILO 600 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B203" s="28" t="inlineStr">
@@ -10298,13 +10114,13 @@
         <v>0</v>
       </c>
       <c r="E203" s="29" t="n">
-        <v>159.6</v>
+        <v>243.8</v>
       </c>
       <c r="F203" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G203" s="29" t="n">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="H203" s="28" t="inlineStr"/>
       <c r="I203" s="28" t="inlineStr"/>
@@ -10312,7 +10128,7 @@
     <row r="204">
       <c r="A204" s="28" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO 600 MG COMPRIMIDO</t>
+          <t>BUPRENORFINA 35 MCG/HR PARC</t>
         </is>
       </c>
       <c r="B204" s="28" t="inlineStr">
@@ -10327,13 +10143,13 @@
         <v>0</v>
       </c>
       <c r="E204" s="29" t="n">
-        <v>243.8</v>
+        <v>168.4</v>
       </c>
       <c r="F204" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G204" s="29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H204" s="28" t="inlineStr"/>
       <c r="I204" s="28" t="inlineStr"/>
@@ -10341,7 +10157,7 @@
     <row r="205">
       <c r="A205" s="28" t="inlineStr">
         <is>
-          <t>BUPRENORFINA 35 MCG/HR PARC</t>
+          <t>FENITOINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B205" s="28" t="inlineStr">
@@ -10356,13 +10172,13 @@
         <v>0</v>
       </c>
       <c r="E205" s="29" t="n">
-        <v>168.4</v>
+        <v>206.2</v>
       </c>
       <c r="F205" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G205" s="29" t="n">
-        <v>0</v>
+        <v>5760</v>
       </c>
       <c r="H205" s="28" t="inlineStr"/>
       <c r="I205" s="28" t="inlineStr"/>
@@ -10370,7 +10186,7 @@
     <row r="206">
       <c r="A206" s="28" t="inlineStr">
         <is>
-          <t>FENITOINA 100 MG COMPRIMIDO</t>
+          <t>MONTELUKAST 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B206" s="28" t="inlineStr">
@@ -10379,19 +10195,19 @@
         </is>
       </c>
       <c r="C206" s="29" t="n">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="D206" s="29" t="n">
-        <v>20.4</v>
+        <v>15.2</v>
       </c>
       <c r="E206" s="29" t="n">
-        <v>206.2</v>
+        <v>243.7</v>
       </c>
       <c r="F206" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G206" s="29" t="n">
-        <v>5760</v>
+        <v>2160</v>
       </c>
       <c r="H206" s="28" t="inlineStr"/>
       <c r="I206" s="28" t="inlineStr"/>
@@ -10399,7 +10215,7 @@
     <row r="207">
       <c r="A207" s="28" t="inlineStr">
         <is>
-          <t>MONTELUKAST 10 MG COMPRIMIDO</t>
+          <t>CLORURO DE POTASIO 600 MG (POTASIO 8 MEQ) COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B207" s="28" t="inlineStr">
@@ -10408,19 +10224,19 @@
         </is>
       </c>
       <c r="C207" s="29" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D207" s="29" t="n">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="E207" s="29" t="n">
-        <v>243.7</v>
+        <v>6.3</v>
       </c>
       <c r="F207" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G207" s="29" t="n">
-        <v>2160</v>
+        <v>1000</v>
       </c>
       <c r="H207" s="28" t="inlineStr"/>
       <c r="I207" s="28" t="inlineStr"/>
@@ -10428,7 +10244,7 @@
     <row r="208">
       <c r="A208" s="28" t="inlineStr">
         <is>
-          <t>CLORURO DE POTASIO 600 MG (POTASIO 8 MEQ) COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B208" s="28" t="inlineStr">
@@ -10437,19 +10253,19 @@
         </is>
       </c>
       <c r="C208" s="29" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D208" s="29" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="E208" s="29" t="n">
-        <v>6.3</v>
+        <v>243.8</v>
       </c>
       <c r="F208" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G208" s="29" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="H208" s="28" t="inlineStr"/>
       <c r="I208" s="28" t="inlineStr"/>
@@ -10457,7 +10273,7 @@
     <row r="209">
       <c r="A209" s="28" t="inlineStr">
         <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
+          <t>LEVODOPA 250 MG - CARBIDOPA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B209" s="28" t="inlineStr">
@@ -10466,19 +10282,19 @@
         </is>
       </c>
       <c r="C209" s="29" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="D209" s="29" t="n">
-        <v>4.8</v>
+        <v>24.6</v>
       </c>
       <c r="E209" s="29" t="n">
-        <v>243.8</v>
+        <v>168.6</v>
       </c>
       <c r="F209" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G209" s="29" t="n">
-        <v>390</v>
+        <v>1140</v>
       </c>
       <c r="H209" s="28" t="inlineStr"/>
       <c r="I209" s="28" t="inlineStr"/>
@@ -10486,7 +10302,7 @@
     <row r="210">
       <c r="A210" s="28" t="inlineStr">
         <is>
-          <t>LEVODOPA 250 MG - CARBIDOPA 25 MG COMPRIMIDO</t>
+          <t>AMOXICILINA 500 MG CAPSULA</t>
         </is>
       </c>
       <c r="B210" s="28" t="inlineStr">
@@ -10495,19 +10311,19 @@
         </is>
       </c>
       <c r="C210" s="29" t="n">
-        <v>450</v>
+        <v>331</v>
       </c>
       <c r="D210" s="29" t="n">
-        <v>24.6</v>
+        <v>18.6</v>
       </c>
       <c r="E210" s="29" t="n">
-        <v>168.6</v>
+        <v>126.8</v>
       </c>
       <c r="F210" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G210" s="29" t="n">
-        <v>1140</v>
+        <v>6687</v>
       </c>
       <c r="H210" s="28" t="inlineStr"/>
       <c r="I210" s="28" t="inlineStr"/>
@@ -10515,7 +10331,7 @@
     <row r="211">
       <c r="A211" s="28" t="inlineStr">
         <is>
-          <t>AMOXICILINA 500 MG CAPSULA</t>
+          <t>MESALAZINA 500 MG SUPOSITORIO.</t>
         </is>
       </c>
       <c r="B211" s="28" t="inlineStr">
@@ -10524,19 +10340,19 @@
         </is>
       </c>
       <c r="C211" s="29" t="n">
-        <v>331</v>
+        <v>100</v>
       </c>
       <c r="D211" s="29" t="n">
-        <v>18.6</v>
+        <v>5.8</v>
       </c>
       <c r="E211" s="29" t="n">
-        <v>126.8</v>
+        <v>149.9</v>
       </c>
       <c r="F211" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G211" s="29" t="n">
-        <v>6687</v>
+        <v>1200</v>
       </c>
       <c r="H211" s="28" t="inlineStr"/>
       <c r="I211" s="28" t="inlineStr"/>
@@ -10544,7 +10360,7 @@
     <row r="212">
       <c r="A212" s="28" t="inlineStr">
         <is>
-          <t>MESALAZINA 500 MG SUPOSITORIO.</t>
+          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
         </is>
       </c>
       <c r="B212" s="28" t="inlineStr">
@@ -10553,19 +10369,19 @@
         </is>
       </c>
       <c r="C212" s="29" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D212" s="29" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="E212" s="29" t="n">
-        <v>149.9</v>
+        <v>107.3</v>
       </c>
       <c r="F212" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G212" s="29" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="H212" s="28" t="inlineStr"/>
       <c r="I212" s="28" t="inlineStr"/>
@@ -10573,7 +10389,7 @@
     <row r="213">
       <c r="A213" s="28" t="inlineStr">
         <is>
-          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
+          <t>SILDENAFIL CM 50 MG</t>
         </is>
       </c>
       <c r="B213" s="28" t="inlineStr">
@@ -10582,19 +10398,19 @@
         </is>
       </c>
       <c r="C213" s="29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D213" s="29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E213" s="29" t="n">
-        <v>107.3</v>
+        <v>137.4</v>
       </c>
       <c r="F213" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G213" s="29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H213" s="28" t="inlineStr"/>
       <c r="I213" s="28" t="inlineStr"/>
@@ -10602,7 +10418,7 @@
     <row r="214">
       <c r="A214" s="28" t="inlineStr">
         <is>
-          <t>SILDENAFIL CM 50 MG</t>
+          <t>FERROSO SULFATO 200 MG CM</t>
         </is>
       </c>
       <c r="B214" s="28" t="inlineStr">
@@ -10617,13 +10433,13 @@
         <v>0</v>
       </c>
       <c r="E214" s="29" t="n">
-        <v>137.4</v>
+        <v>121.8</v>
       </c>
       <c r="F214" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G214" s="29" t="n">
-        <v>1000</v>
+        <v>22000</v>
       </c>
       <c r="H214" s="28" t="inlineStr"/>
       <c r="I214" s="28" t="inlineStr"/>
@@ -10631,7 +10447,7 @@
     <row r="215">
       <c r="A215" s="28" t="inlineStr">
         <is>
-          <t>FERROSO SULFATO 200 MG CM</t>
+          <t>PROGESTERONA 200 MG CM MICRONIZADA</t>
         </is>
       </c>
       <c r="B215" s="28" t="inlineStr">
@@ -10640,19 +10456,19 @@
         </is>
       </c>
       <c r="C215" s="29" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D215" s="29" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E215" s="29" t="n">
-        <v>121.8</v>
+        <v>74.8</v>
       </c>
       <c r="F215" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G215" s="29" t="n">
-        <v>22000</v>
+        <v>2640</v>
       </c>
       <c r="H215" s="28" t="inlineStr"/>
       <c r="I215" s="28" t="inlineStr"/>
@@ -10660,7 +10476,7 @@
     <row r="216">
       <c r="A216" s="28" t="inlineStr">
         <is>
-          <t>PROGESTERONA 200 MG CM MICRONIZADA</t>
+          <t>METRONIDAZOL 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B216" s="28" t="inlineStr">
@@ -10669,19 +10485,19 @@
         </is>
       </c>
       <c r="C216" s="29" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D216" s="29" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="E216" s="29" t="n">
-        <v>74.8</v>
+        <v>155.2</v>
       </c>
       <c r="F216" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G216" s="29" t="n">
-        <v>2640</v>
+        <v>8000</v>
       </c>
       <c r="H216" s="28" t="inlineStr"/>
       <c r="I216" s="28" t="inlineStr"/>
@@ -10689,7 +10505,7 @@
     <row r="217">
       <c r="A217" s="28" t="inlineStr">
         <is>
-          <t>METRONIDAZOL 500 MG COMPRIMIDO</t>
+          <t>CALCITRIOL 0,25 MCG CP</t>
         </is>
       </c>
       <c r="B217" s="28" t="inlineStr">
@@ -10698,19 +10514,19 @@
         </is>
       </c>
       <c r="C217" s="29" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D217" s="29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E217" s="29" t="n">
-        <v>155.2</v>
+        <v>75</v>
       </c>
       <c r="F217" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G217" s="29" t="n">
-        <v>8000</v>
+        <v>600</v>
       </c>
       <c r="H217" s="28" t="inlineStr"/>
       <c r="I217" s="28" t="inlineStr"/>
@@ -10718,7 +10534,7 @@
     <row r="218">
       <c r="A218" s="28" t="inlineStr">
         <is>
-          <t>CALCITRIOL 0,25 MCG CP</t>
+          <t>FLUNARIZINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B218" s="28" t="inlineStr">
@@ -10727,19 +10543,19 @@
         </is>
       </c>
       <c r="C218" s="29" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D218" s="29" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E218" s="29" t="n">
-        <v>75</v>
+        <v>37.4</v>
       </c>
       <c r="F218" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G218" s="29" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H218" s="28" t="inlineStr"/>
       <c r="I218" s="28" t="inlineStr"/>
@@ -10747,7 +10563,7 @@
     <row r="219">
       <c r="A219" s="28" t="inlineStr">
         <is>
-          <t>FLUNARIZINA 10 MG COMPRIMIDO</t>
+          <t>AMOXICILINA 875 MG - ACIDO CLAVULANICO 125 MG COMPRIMIDO.</t>
         </is>
       </c>
       <c r="B219" s="28" t="inlineStr">
@@ -10756,19 +10572,19 @@
         </is>
       </c>
       <c r="C219" s="29" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D219" s="29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E219" s="29" t="n">
-        <v>37.4</v>
+        <v>71.7</v>
       </c>
       <c r="F219" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G219" s="29" t="n">
-        <v>1000</v>
+        <v>6500</v>
       </c>
       <c r="H219" s="28" t="inlineStr"/>
       <c r="I219" s="28" t="inlineStr"/>
@@ -10776,7 +10592,7 @@
     <row r="220">
       <c r="A220" s="28" t="inlineStr">
         <is>
-          <t>AMOXICILINA 875 MG - ACIDO CLAVULANICO 125 MG COMPRIMIDO.</t>
+          <t>WARFARINA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B220" s="28" t="inlineStr">
@@ -10785,19 +10601,19 @@
         </is>
       </c>
       <c r="C220" s="29" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="D220" s="29" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="E220" s="29" t="n">
-        <v>71.7</v>
+        <v>57.4</v>
       </c>
       <c r="F220" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G220" s="29" t="n">
-        <v>6500</v>
+        <v>480</v>
       </c>
       <c r="H220" s="28" t="inlineStr"/>
       <c r="I220" s="28" t="inlineStr"/>
@@ -10805,7 +10621,7 @@
     <row r="221">
       <c r="A221" s="28" t="inlineStr">
         <is>
-          <t>WARFARINA 5 MG COMPRIMIDO</t>
+          <t>METILPREDNISOLONA 4 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B221" s="28" t="inlineStr">
@@ -10814,19 +10630,19 @@
         </is>
       </c>
       <c r="C221" s="29" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D221" s="29" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="E221" s="29" t="n">
-        <v>57.4</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F221" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G221" s="29" t="n">
-        <v>480</v>
+        <v>140</v>
       </c>
       <c r="H221" s="28" t="inlineStr"/>
       <c r="I221" s="28" t="inlineStr"/>
@@ -10834,7 +10650,7 @@
     <row r="222">
       <c r="A222" s="28" t="inlineStr">
         <is>
-          <t>METILPREDNISOLONA 4 MG COMPRIMIDO</t>
+          <t>DIFENIDOL CM 25 MG</t>
         </is>
       </c>
       <c r="B222" s="28" t="inlineStr">
@@ -10843,19 +10659,19 @@
         </is>
       </c>
       <c r="C222" s="29" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D222" s="29" t="n">
-        <v>14.2</v>
+        <v>29.1</v>
       </c>
       <c r="E222" s="29" t="n">
-        <v>77.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="F222" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G222" s="29" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="H222" s="28" t="inlineStr"/>
       <c r="I222" s="28" t="inlineStr"/>
@@ -10863,7 +10679,7 @@
     <row r="223">
       <c r="A223" s="28" t="inlineStr">
         <is>
-          <t>DIFENIDOL CM 25 MG</t>
+          <t>NITROFURANTOINA MACROCRISTALES 100 MG CAP</t>
         </is>
       </c>
       <c r="B223" s="28" t="inlineStr">
@@ -10872,19 +10688,19 @@
         </is>
       </c>
       <c r="C223" s="29" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="D223" s="29" t="n">
-        <v>29.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="E223" s="29" t="n">
-        <v>50</v>
+        <v>116.4</v>
       </c>
       <c r="F223" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G223" s="29" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H223" s="28" t="inlineStr"/>
       <c r="I223" s="28" t="inlineStr"/>
@@ -10892,7 +10708,7 @@
     <row r="224">
       <c r="A224" s="28" t="inlineStr">
         <is>
-          <t>NITROFURANTOINA MACROCRISTALES 100 MG CAP</t>
+          <t>HIDROCORTISONA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B224" s="28" t="inlineStr">
@@ -10901,19 +10717,19 @@
         </is>
       </c>
       <c r="C224" s="29" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="D224" s="29" t="n">
-        <v>90.09999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="E224" s="29" t="n">
-        <v>116.4</v>
+        <v>134.3</v>
       </c>
       <c r="F224" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G224" s="29" t="n">
-        <v>2000</v>
+        <v>720</v>
       </c>
       <c r="H224" s="28" t="inlineStr"/>
       <c r="I224" s="28" t="inlineStr"/>
@@ -10921,7 +10737,7 @@
     <row r="225">
       <c r="A225" s="28" t="inlineStr">
         <is>
-          <t>HIDROCORTISONA 20 MG COMPRIMIDO</t>
+          <t>ALPRAZOLAM CM 0,5 MG</t>
         </is>
       </c>
       <c r="B225" s="28" t="inlineStr">
@@ -10930,19 +10746,19 @@
         </is>
       </c>
       <c r="C225" s="29" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D225" s="29" t="n">
-        <v>15.6</v>
+        <v>0</v>
       </c>
       <c r="E225" s="29" t="n">
-        <v>134.3</v>
+        <v>165.8</v>
       </c>
       <c r="F225" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G225" s="29" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="H225" s="28" t="inlineStr"/>
       <c r="I225" s="28" t="inlineStr"/>
@@ -10950,7 +10766,7 @@
     <row r="226">
       <c r="A226" s="28" t="inlineStr">
         <is>
-          <t>ALPRAZOLAM CM 0,5 MG</t>
+          <t>KETOPROFENO 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B226" s="28" t="inlineStr">
@@ -10965,13 +10781,13 @@
         <v>0</v>
       </c>
       <c r="E226" s="29" t="n">
-        <v>165.8</v>
+        <v>83.7</v>
       </c>
       <c r="F226" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G226" s="29" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="H226" s="28" t="inlineStr"/>
       <c r="I226" s="28" t="inlineStr"/>
@@ -10979,7 +10795,7 @@
     <row r="227">
       <c r="A227" s="28" t="inlineStr">
         <is>
-          <t>KETOPROFENO 100 MG COMPRIMIDO</t>
+          <t>LATANOPROST 0,005% COLIRIO</t>
         </is>
       </c>
       <c r="B227" s="28" t="inlineStr">
@@ -10988,19 +10804,19 @@
         </is>
       </c>
       <c r="C227" s="29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D227" s="29" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E227" s="29" t="n">
-        <v>83.7</v>
+        <v>94.3</v>
       </c>
       <c r="F227" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G227" s="29" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="H227" s="28" t="inlineStr"/>
       <c r="I227" s="28" t="inlineStr"/>
@@ -11008,7 +10824,7 @@
     <row r="228">
       <c r="A228" s="28" t="inlineStr">
         <is>
-          <t>LATANOPROST 0,005% COLIRIO</t>
+          <t>PRIMIDONA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B228" s="28" t="inlineStr">
@@ -11017,19 +10833,19 @@
         </is>
       </c>
       <c r="C228" s="29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D228" s="29" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E228" s="29" t="n">
-        <v>94.3</v>
+        <v>37.5</v>
       </c>
       <c r="F228" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G228" s="29" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H228" s="28" t="inlineStr"/>
       <c r="I228" s="28" t="inlineStr"/>
@@ -11037,7 +10853,7 @@
     <row r="229">
       <c r="A229" s="28" t="inlineStr">
         <is>
-          <t>PRIMIDONA 250 MG COMPRIMIDO</t>
+          <t>VITAMINAS B1/B6/B12 100 MG/100 MG/10 MG AMP</t>
         </is>
       </c>
       <c r="B229" s="28" t="inlineStr">
@@ -11046,19 +10862,19 @@
         </is>
       </c>
       <c r="C229" s="29" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D229" s="29" t="n">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="E229" s="29" t="n">
-        <v>37.5</v>
+        <v>73.8</v>
       </c>
       <c r="F229" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G229" s="29" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="H229" s="28" t="inlineStr"/>
       <c r="I229" s="28" t="inlineStr"/>
@@ -11066,7 +10882,7 @@
     <row r="230">
       <c r="A230" s="28" t="inlineStr">
         <is>
-          <t>VITAMINAS B1/B6/B12 100 MG/100 MG/10 MG AMP</t>
+          <t>PRAMIPEXOL 1 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B230" s="28" t="inlineStr">
@@ -11075,19 +10891,19 @@
         </is>
       </c>
       <c r="C230" s="29" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D230" s="29" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="E230" s="29" t="n">
-        <v>73.8</v>
+        <v>103</v>
       </c>
       <c r="F230" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G230" s="29" t="n">
-        <v>900</v>
+        <v>1020</v>
       </c>
       <c r="H230" s="28" t="inlineStr"/>
       <c r="I230" s="28" t="inlineStr"/>
@@ -11095,7 +10911,7 @@
     <row r="231">
       <c r="A231" s="28" t="inlineStr">
         <is>
-          <t>PRAMIPEXOL 1 MG COMPRIMIDO</t>
+          <t>TRIMETAZIDINA 35 MG CM LIBERACION PROLONGADA (XR)</t>
         </is>
       </c>
       <c r="B231" s="28" t="inlineStr">
@@ -11110,13 +10926,13 @@
         <v>0</v>
       </c>
       <c r="E231" s="29" t="n">
-        <v>103</v>
+        <v>112.5</v>
       </c>
       <c r="F231" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G231" s="29" t="n">
-        <v>1020</v>
+        <v>750</v>
       </c>
       <c r="H231" s="28" t="inlineStr"/>
       <c r="I231" s="28" t="inlineStr"/>
@@ -11124,7 +10940,7 @@
     <row r="232">
       <c r="A232" s="28" t="inlineStr">
         <is>
-          <t>TRIMETAZIDINA 35 MG CM LIBERACION PROLONGADA (XR)</t>
+          <t>VITAMINA D3 50.000 UI SOBRE</t>
         </is>
       </c>
       <c r="B232" s="28" t="inlineStr">
@@ -11133,19 +10949,19 @@
         </is>
       </c>
       <c r="C232" s="29" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="D232" s="29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E232" s="29" t="n">
-        <v>112.5</v>
+        <v>83.7</v>
       </c>
       <c r="F232" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G232" s="29" t="n">
-        <v>750</v>
+        <v>4090</v>
       </c>
       <c r="H232" s="28" t="inlineStr"/>
       <c r="I232" s="28" t="inlineStr"/>
@@ -11153,7 +10969,7 @@
     <row r="233">
       <c r="A233" s="28" t="inlineStr">
         <is>
-          <t>VITAMINA D3 50.000 UI SOBRE</t>
+          <t>SULFAMETOXAZOL 800 MG + TRIMETOPRIMA 160 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B233" s="28" t="inlineStr">
@@ -11162,19 +10978,19 @@
         </is>
       </c>
       <c r="C233" s="29" t="n">
-        <v>234</v>
+        <v>700</v>
       </c>
       <c r="D233" s="29" t="n">
-        <v>21</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E233" s="29" t="n">
-        <v>83.7</v>
+        <v>88.2</v>
       </c>
       <c r="F233" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G233" s="29" t="n">
-        <v>4090</v>
+        <v>4000</v>
       </c>
       <c r="H233" s="28" t="inlineStr"/>
       <c r="I233" s="28" t="inlineStr"/>
@@ -11182,7 +10998,7 @@
     <row r="234">
       <c r="A234" s="28" t="inlineStr">
         <is>
-          <t>SULFAMETOXAZOL 800 MG + TRIMETOPRIMA 160 MG COMPRIMIDO</t>
+          <t>POLIESTIRENO SULFONATO CALCICO 15 GR SO</t>
         </is>
       </c>
       <c r="B234" s="28" t="inlineStr">
@@ -11191,19 +11007,19 @@
         </is>
       </c>
       <c r="C234" s="29" t="n">
-        <v>700</v>
+        <v>26</v>
       </c>
       <c r="D234" s="29" t="n">
-        <v>64.90000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="E234" s="29" t="n">
-        <v>88.2</v>
+        <v>93.8</v>
       </c>
       <c r="F234" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G234" s="29" t="n">
-        <v>4000</v>
+        <v>420</v>
       </c>
       <c r="H234" s="28" t="inlineStr"/>
       <c r="I234" s="28" t="inlineStr"/>
@@ -12032,10 +11848,10 @@
         </is>
       </c>
       <c r="C263" s="29" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D263" s="29" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="E263" s="29" t="n">
         <v>27.5</v>
@@ -12264,10 +12080,10 @@
         </is>
       </c>
       <c r="C271" s="29" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D271" s="29" t="n">
-        <v>56.1</v>
+        <v>0</v>
       </c>
       <c r="E271" s="29" t="n">
         <v>0</v>
@@ -12496,10 +12312,10 @@
         </is>
       </c>
       <c r="C279" s="29" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D279" s="29" t="n">
-        <v>76.2</v>
+        <v>38.1</v>
       </c>
       <c r="E279" s="29" t="n">
         <v>25.6</v>
@@ -12989,10 +12805,10 @@
         </is>
       </c>
       <c r="C296" s="29" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D296" s="29" t="n">
-        <v>34.8</v>
+        <v>20.9</v>
       </c>
       <c r="E296" s="29" t="n">
         <v>11.9</v>
@@ -13366,10 +13182,10 @@
         </is>
       </c>
       <c r="C309" s="29" t="n">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="D309" s="29" t="n">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="E309" s="29" t="n">
         <v>1.2</v>
@@ -15367,7 +15183,7 @@
         </is>
       </c>
       <c r="C378" s="29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D378" s="29" t="n">
         <v>0</v>
@@ -16966,7 +16782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -17469,7 +17285,7 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
+          <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -17478,32 +17294,32 @@
         </is>
       </c>
       <c r="C12" s="21" t="n">
-        <v>71</v>
+        <v>763</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>3393.5</v>
+        <v>1992.9</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>187.5</v>
+        <v>23.4</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>4033.3</v>
+        <v>2960</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>1287</v>
+        <v>60</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>1287</v>
+        <v>60</v>
       </c>
       <c r="J12" s="21" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1287 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr"/>
@@ -17511,7 +17327,7 @@
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+          <t>ISOSORBIDA DINITRATO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -17520,40 +17336,44 @@
         </is>
       </c>
       <c r="C13" s="21" t="n">
-        <v>463</v>
+        <v>120</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>2098.9</v>
+        <v>1231.1</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>66.7</v>
+        <v>117</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>3075.3</v>
+        <v>1794.7</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="K13" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 390 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L13" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 373 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
+          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
@@ -17562,40 +17382,44 @@
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>793</v>
+        <v>356</v>
       </c>
       <c r="D14" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>1992.9</v>
+        <v>984.3</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>23.4</v>
+        <v>4.7</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>2960</v>
+        <v>1325.5</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K14" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L14" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 38 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>ISOSORBIDA DINITRATO 10 MG COMPRIMIDO</t>
+          <t>CARVEDILOL 12,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -17604,44 +17428,40 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>120</v>
+        <v>245</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>1231.1</v>
+        <v>1152.5</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>117</v>
+        <v>103.1</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>1794.7</v>
+        <v>937</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>373</v>
+        <v>240</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="K15" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L15" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 373 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 240 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>PREDNISONA 5 MG COMPRIMIDO</t>
+          <t>SEVELAMER 800 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -17650,32 +17470,32 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>958</v>
+        <v>56.2</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>15</v>
+        <v>126.6</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>1142</v>
+        <v>0</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="J16" s="21" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 66 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 57 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr"/>
@@ -17683,7 +17503,7 @@
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>CARVEDILOL 12,5 MG COMPRIMIDO</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -17692,32 +17512,32 @@
         </is>
       </c>
       <c r="C17" s="21" t="n">
-        <v>245</v>
+        <v>6</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>1152.5</v>
+        <v>25.6</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>103.1</v>
+        <v>0.9</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>937</v>
+        <v>39.1</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="J17" s="21" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 240 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 20 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr"/>
@@ -17725,7 +17545,7 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>SEVELAMER 800 MG COMPRIMIDO</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
@@ -17734,40 +17554,44 @@
         </is>
       </c>
       <c r="C18" s="21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>56.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>126.6</v>
+        <v>11.6</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K18" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 57 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L18" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 5 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -17776,40 +17600,44 @@
         </is>
       </c>
       <c r="C19" s="21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>25.6</v>
+        <v>13.1</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>39.1</v>
+        <v>19.7</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J19" s="21" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K19" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 20 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L19" s="20" t="inlineStr"/>
+          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 90 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
@@ -17818,362 +17646,228 @@
         </is>
       </c>
       <c r="C20" s="21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="E20" s="21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>AMOXICILINA + AC. CLAVULANICO 500/125 MG CM</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E21" s="6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="F20" s="21" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="G20" s="21" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="H20" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="K20" s="20" t="inlineStr">
-        <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L20" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 5 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="n">
+      <c r="F21" s="6" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 3 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E21" s="21" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G21" s="21" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H21" s="21" t="n">
-        <v>100</v>
-      </c>
-      <c r="I21" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="K21" s="20" t="inlineStr">
-        <is>
-          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L21" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 90 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" s="21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F22" s="21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H22" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="20" t="inlineStr">
-        <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L22" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+      <c r="D22" s="6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>470</v>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 470 ud.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>IBUPROFENO 400 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>85</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>106.6</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>144.5</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>AMOXICILINA + AC. CLAVULANICO 500/125 MG CM</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 3 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr"/>
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>4-BAJO</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>118</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E23" s="23" t="n">
+        <v>243.8</v>
+      </c>
+      <c r="F23" s="23" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="G23" s="23" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="H23" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="I23" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="J23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 150 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>470</v>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 470 ud.</t>
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>4-BAJO</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="n">
-        <v>118</v>
-      </c>
-      <c r="D26" s="23" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E26" s="23" t="n">
-        <v>243.8</v>
-      </c>
-      <c r="F26" s="23" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="G26" s="23" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="H26" s="23" t="n">
-        <v>150</v>
-      </c>
-      <c r="I26" s="23" t="n">
-        <v>150</v>
-      </c>
-      <c r="J26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 150 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L26" s="22" t="inlineStr"/>
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>CRITICO  —  sin stock ni respaldo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>URGENTE  —  cobertura critica</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>LEYENDA DE COLORES</t>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO  —  sin stock ni respaldo</t>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>URGENTE  —  cobertura critica</t>
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>MODERADO  —  reponer pronto (Farmacia)</t>
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>BAJO  —  vigilar (Farmacia)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>BAJO  —  stock suficiente (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -18426,7 +18120,7 @@
         <v>1325.5</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>1957</v>
+        <v>2017</v>
       </c>
       <c r="I6" s="19" t="n">
         <v>0</v>
@@ -18438,7 +18132,7 @@
       </c>
       <c r="K6" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1957 ud.</t>
+          <t>COMPRA EXTERNA 2017 ud.</t>
         </is>
       </c>
     </row>
@@ -19121,7 +18815,7 @@
         <v>3525.8</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>179</v>
+        <v>249</v>
       </c>
       <c r="I23" s="21" t="n">
         <v>0</v>
@@ -19133,87 +18827,87 @@
       </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 179 ud.</t>
+          <t>COMPRA EXTERNA 249 ud.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="26" t="inlineStr">
         <is>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>3-ALTO</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D24" s="27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E24" s="27" t="n">
+        <v>4687.9</v>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>3075.3</v>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>330</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>2520</v>
+      </c>
+      <c r="J24" s="26" t="inlineStr">
+        <is>
+          <t>TRASPASAR 330 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K24" s="26" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
           <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>3-ALTO</t>
         </is>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C25" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="D24" s="27" t="n">
+      <c r="D25" s="27" t="n">
         <v>4.4</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E25" s="27" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="F24" s="27" t="n">
+      <c r="F25" s="27" t="n">
         <v>0.9</v>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="G25" s="27" t="n">
         <v>39.1</v>
       </c>
-      <c r="H24" s="27" t="n">
+      <c r="H25" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="I24" s="27" t="n">
+      <c r="I25" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="J24" s="26" t="inlineStr">
+      <c r="J25" s="26" t="inlineStr">
         <is>
           <t>TRASPASAR 6 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="K24" s="26" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>4-MODERADO</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>3510</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>4687.9</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>3075.3</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>330</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>2520</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 330 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr"/>
+      <c r="K25" s="26" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -19227,10 +18921,10 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>3690</v>
+        <v>3660</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>4558.7</v>
@@ -19242,14 +18936,14 @@
         <v>2960</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>15810</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 90 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr"/>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1441,20 +1441,20 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>AGUA BIDESTILADA MATRAZ 500 ML</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="E28" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR DESDE BODEGA FARMACOS (190 ud. disponibles)</t>
+          <t>TRASPASAR DESDE BODEGA FARMACOS (1600 ud. disponibles)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
+          <t>ACETATO DE CALCIO 667 MG CM UD</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="D29" s="10" t="n">
         <v>1</v>
@@ -1492,21 +1492,21 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>TRASPASAR DESDE BODEGA FARMACOS (100 ud. disponibles)</t>
+          <t>TRASPASAR DESDE BODEGA FARMACOS (10440 ud. disponibles)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>AGUA BIDESTILADA MATRAZ 500 ML</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D30" s="10" t="n">
         <v>1</v>
@@ -1521,68 +1521,126 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
+          <t>TRASPASAR DESDE BODEGA FARMACOS (190 ud. disponibles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>[BAJO] BAJO — TRASPASO BOD.FARMACOS</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>TRASPASAR DESDE BODEGA FARMACOS (100 ud. disponibles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>KETOROLACO AMP 30 MG/ML</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>[BAJO] BAJO — TRASPASO BOD.FARMACOS</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
           <t>TRASPASAR DESDE BODEGA FARMACOS (2600 ud. disponibles)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -1599,7 +1657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1956,7 +2014,7 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>MICOFENOLATO 500 MG CR</t>
+          <t>ACETATO DE CALCIO 667 MG CM UD</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -1971,16 +2029,16 @@
         <v>0</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>169</v>
+        <v>730.2</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>85</v>
+        <v>207</v>
       </c>
       <c r="G10" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>85</v>
+        <v>207</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
@@ -1989,14 +2047,14 @@
       </c>
       <c r="J10" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 85 ud.</t>
+          <t>GESTIONAR EXTERNO 207 ud.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>MEMANTINA 10 MG COMPRIMIDO</t>
+          <t>MICOFENOLATO 500 MG CR</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -2011,16 +2069,16 @@
         <v>0</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>88.3</v>
+        <v>169</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="G11" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
@@ -2029,14 +2087,14 @@
       </c>
       <c r="J11" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 36 ud.</t>
+          <t>GESTIONAR EXTERNO 85 ud.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
+          <t>MEMANTINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -2051,16 +2109,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>103.2</v>
+        <v>88.3</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="G12" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
@@ -2069,14 +2127,14 @@
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 102 ud.</t>
+          <t>GESTIONAR EXTERNO 36 ud.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -2091,16 +2149,16 @@
         <v>0</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>37.7</v>
+        <v>103.2</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="G13" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
@@ -2109,14 +2167,14 @@
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 37 ud.</t>
+          <t>GESTIONAR EXTERNO 102 ud.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
@@ -2131,16 +2189,16 @@
         <v>0</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>11.7</v>
+        <v>37.7</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="G14" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
@@ -2149,14 +2207,14 @@
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
+          <t>GESTIONAR EXTERNO 37 ud.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -2171,16 +2229,16 @@
         <v>0</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>31.8</v>
+        <v>11.7</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="G15" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
@@ -2189,14 +2247,14 @@
       </c>
       <c r="J15" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 28 ud.</t>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -2211,16 +2269,16 @@
         <v>0</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>11.8</v>
+        <v>31.8</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G16" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
@@ -2229,14 +2287,14 @@
       </c>
       <c r="J16" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 12 ud.</t>
+          <t>GESTIONAR EXTERNO 28 ud.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -2251,16 +2309,16 @@
         <v>0</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>12.8</v>
+        <v>11.9</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
@@ -2269,14 +2327,14 @@
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 9 ud.</t>
+          <t>GESTIONAR EXTERNO 8 ud.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>APIXABAN 2,5 MG CM</t>
+          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
@@ -2291,16 +2349,16 @@
         <v>0</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>21.2</v>
+        <v>11.8</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="G18" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
@@ -2309,14 +2367,14 @@
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 60 ud.</t>
+          <t>GESTIONAR EXTERNO 12 ud.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>RISPERIDONA 25 MG FA</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -2331,16 +2389,16 @@
         <v>0</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>6.8</v>
+        <v>12.8</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G19" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
@@ -2349,14 +2407,14 @@
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 7 ud.</t>
+          <t>GESTIONAR EXTERNO 9 ud.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>UREA 10% CREMA 20 GR</t>
+          <t>APIXABAN 2,5 MG CM</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
@@ -2371,16 +2429,16 @@
         <v>0</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>14.8</v>
+        <v>21.2</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G20" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
@@ -2389,14 +2447,14 @@
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 15 ud.</t>
+          <t>GESTIONAR EXTERNO 60 ud.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>VASELINA SOLIDA UNGUENTO</t>
+          <t>RISPERIDONA 25 MG FA</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -2411,16 +2469,16 @@
         <v>0</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
@@ -2429,14 +2487,14 @@
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 6 ud.</t>
+          <t>GESTIONAR EXTERNO 7 ud.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>UREA 10% CREMA 20 GR</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -2451,16 +2509,16 @@
         <v>0</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>2.3</v>
+        <v>14.8</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G22" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -2469,14 +2527,14 @@
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2 ud.</t>
+          <t>GESTIONAR EXTERNO 15 ud.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
+          <t>VASELINA SOLIDA UNGUENTO</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
@@ -2491,16 +2549,16 @@
         <v>0</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G23" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
@@ -2509,14 +2567,14 @@
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2 ud.</t>
+          <t>GESTIONAR EXTERNO 6 ud.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
@@ -2531,16 +2589,16 @@
         <v>0</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -2549,14 +2607,14 @@
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 2 ud.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
+          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -2571,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="F25" s="21" t="n">
         <v>2</v>
@@ -2596,7 +2654,7 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
@@ -2611,16 +2669,16 @@
         <v>0</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -2629,14 +2687,14 @@
       </c>
       <c r="J26" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2 ud.</t>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>ETONOGESTREL 68 MG IMPLANTE</t>
+          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -2651,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
@@ -2669,14 +2727,14 @@
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 2 ud.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
+          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
@@ -2691,16 +2749,16 @@
         <v>0</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -2709,14 +2767,14 @@
       </c>
       <c r="J28" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 2 ud.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
+          <t>ETONOGESTREL 68 MG IMPLANTE</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -2731,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="21" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F29" s="21" t="n">
         <v>1</v>
@@ -2756,7 +2814,7 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
+          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
@@ -2771,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F30" s="21" t="n">
         <v>1</v>
@@ -2796,7 +2854,7 @@
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
+          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -2836,7 +2894,7 @@
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
@@ -2874,85 +2932,89 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="n">
-        <v>936</v>
-      </c>
-      <c r="D33" s="23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E33" s="23" t="n">
-        <v>2304.4</v>
-      </c>
-      <c r="F33" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="G33" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="H33" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 11 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J33" s="22" t="inlineStr"/>
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>116</v>
-      </c>
-      <c r="D34" s="23" t="n">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="E34" s="23" t="n">
-        <v>1202.2</v>
-      </c>
-      <c r="F34" s="23" t="n">
-        <v>335</v>
-      </c>
-      <c r="G34" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="23" t="n">
-        <v>335</v>
-      </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="F34" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
-      <c r="J34" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 335 ud.</t>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>METFORMINA 850 MG COMPRIMIDO</t>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
         </is>
       </c>
       <c r="B35" s="22" t="inlineStr">
@@ -2961,26 +3023,26 @@
         </is>
       </c>
       <c r="C35" s="23" t="n">
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="23" t="n">
-        <v>443.6</v>
+        <v>2304.4</v>
       </c>
       <c r="F35" s="23" t="n">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="G35" s="23" t="n">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="H35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 169 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 321 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr"/>
@@ -2988,7 +3050,7 @@
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>RIFAXIMINA 200 MG CP</t>
+          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
@@ -2997,34 +3059,38 @@
         </is>
       </c>
       <c r="C36" s="23" t="n">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E36" s="23" t="n">
-        <v>338.1</v>
+        <v>1202.2</v>
       </c>
       <c r="F36" s="23" t="n">
-        <v>48</v>
+        <v>335</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="I36" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 48 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J36" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 335 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>ACETATO DE CALCIO 667 MG CM UD</t>
+          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
         </is>
       </c>
       <c r="B37" s="22" t="inlineStr">
@@ -3033,38 +3099,34 @@
         </is>
       </c>
       <c r="C37" s="23" t="n">
-        <v>120</v>
+        <v>326</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="E37" s="23" t="n">
-        <v>730.2</v>
+        <v>786.2</v>
       </c>
       <c r="F37" s="23" t="n">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="G37" s="23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="I37" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J37" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 87 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J37" s="22" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>VITAMINA D3 50.000 UI SOBRE</t>
+          <t>BUPROPION (ANFEBUTAMONA) 150 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
@@ -3073,26 +3135,26 @@
         </is>
       </c>
       <c r="C38" s="23" t="n">
-        <v>10</v>
+        <v>270</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="E38" s="23" t="n">
-        <v>44.9</v>
+        <v>813.1</v>
       </c>
       <c r="F38" s="23" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G38" s="23" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H38" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 35 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 44 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J38" s="22" t="inlineStr"/>
@@ -3100,7 +3162,7 @@
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
+          <t>RIFAXIMINA 200 MG CP</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
@@ -3109,26 +3171,26 @@
         </is>
       </c>
       <c r="C39" s="23" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E39" s="23" t="n">
-        <v>49.4</v>
+        <v>338.1</v>
       </c>
       <c r="F39" s="23" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H39" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 48 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J39" s="22" t="inlineStr"/>
@@ -3136,7 +3198,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
@@ -3145,22 +3207,22 @@
         </is>
       </c>
       <c r="C40" s="23" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="E40" s="23" t="n">
-        <v>11.9</v>
+        <v>77.7</v>
       </c>
       <c r="F40" s="23" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="G40" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="23" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="I40" s="22" t="inlineStr">
         <is>
@@ -3169,14 +3231,14 @@
       </c>
       <c r="J40" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 4 ud.</t>
+          <t>GESTIONAR EXTERNO 46 ud.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>VITAMINA D3 50.000 UI SOBRE</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
@@ -3185,38 +3247,34 @@
         </is>
       </c>
       <c r="C41" s="23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E41" s="23" t="n">
-        <v>20.5</v>
+        <v>44.9</v>
       </c>
       <c r="F41" s="23" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G41" s="23" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H41" s="23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I41" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J41" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 19 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 39 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J41" s="22" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>ACIDO ACETILSALICILICO CM 500 MG</t>
+          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
@@ -3231,20 +3289,20 @@
         <v>0</v>
       </c>
       <c r="E42" s="23" t="n">
-        <v>17.7</v>
+        <v>49.4</v>
       </c>
       <c r="F42" s="23" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="G42" s="23" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H42" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 18 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J42" s="22" t="inlineStr"/>
@@ -3252,7 +3310,7 @@
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
@@ -3261,22 +3319,22 @@
         </is>
       </c>
       <c r="C43" s="23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="E43" s="23" t="n">
-        <v>8.6</v>
+        <v>20.5</v>
       </c>
       <c r="F43" s="23" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G43" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="23" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I43" s="22" t="inlineStr">
         <is>
@@ -3285,14 +3343,14 @@
       </c>
       <c r="J43" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 19 ud.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+          <t>ACIDO ACETILSALICILICO CM 500 MG</t>
         </is>
       </c>
       <c r="B44" s="22" t="inlineStr">
@@ -3307,32 +3365,28 @@
         <v>0</v>
       </c>
       <c r="E44" s="23" t="n">
-        <v>10.5</v>
+        <v>17.7</v>
       </c>
       <c r="F44" s="23" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G44" s="23" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H44" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I44" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J44" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 4 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 18 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J44" s="22" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="22" t="inlineStr">
         <is>
-          <t>METILPREDNISOLONA ACETATO 40 MG/ML IM INTRARTICULAR</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B45" s="22" t="inlineStr">
@@ -3341,150 +3395,154 @@
         </is>
       </c>
       <c r="C45" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E45" s="23" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="F45" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G45" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H45" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 4 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J45" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J45" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
+          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F46" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H46" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J46" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 4 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>METILPREDNISOLONA ACETATO 40 MG/ML IM INTRARTICULAR</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F47" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 4 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J47" s="22" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
           <t>LEVETIRACETAM 100 MG/ML FC 300 ML</t>
         </is>
       </c>
-      <c r="B46" s="22" t="inlineStr">
+      <c r="B48" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C46" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="23" t="n">
+      <c r="C48" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="23" t="n">
         <v>2.2</v>
       </c>
-      <c r="F46" s="23" t="n">
+      <c r="F48" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="G46" s="23" t="n">
+      <c r="G48" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H46" s="23" t="n">
+      <c r="H48" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="I46" s="22" t="inlineStr">
+      <c r="I48" s="22" t="inlineStr">
         <is>
           <t>TRASPASAR 3 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="J46" s="22" t="inlineStr">
+      <c r="J48" s="22" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 7 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>MESALAZINA 500 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>356</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E47" s="6" t="n">
-        <v>1095.1</v>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 400 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="D48" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E48" s="6" t="n">
-        <v>174.7</v>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 30 ud.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>MESALAZINA 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -3493,38 +3551,34 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>36</v>
+        <v>356</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>2.1</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>77.7</v>
+        <v>1095.1</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>42</v>
+        <v>400</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 42 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 400 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>MESALAZINA 500 MG SUPOSITORIO.</t>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -3533,34 +3587,38 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>88.3</v>
+        <v>174.7</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 30 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>AMOXICILINA 875 MG - ACIDO CLAVULANICO 125 MG COMPRIMIDO.</t>
+          <t>MESALAZINA 500 MG SUPOSITORIO.</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -3569,26 +3627,26 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>42.3</v>
+        <v>88.3</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 100 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr"/>
@@ -3596,7 +3654,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>AMANTADINA 100 MG CAPSULA</t>
+          <t>AMOXICILINA 875 MG - ACIDO CLAVULANICO 125 MG COMPRIMIDO.</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -3605,38 +3663,34 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>102.4</v>
+        <v>42.3</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 60 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -3645,22 +3699,22 @@
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>13.1</v>
+        <v>40.9</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
@@ -3669,14 +3723,14 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
+          <t>GESTIONAR EXTERNO 4 ud.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
+          <t>AMANTADINA 100 MG CAPSULA</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -3685,22 +3739,22 @@
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>10.5</v>
+        <v>102.4</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
@@ -3709,14 +3763,14 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 60 ud.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -3725,132 +3779,284 @@
         </is>
       </c>
       <c r="C55" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D55" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D55" s="6" t="n">
-        <v>3.6</v>
-      </c>
       <c r="E55" s="6" t="n">
-        <v>7.9</v>
+        <v>32.5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 6 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
+          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 6 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
           <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>3-MODERADO</t>
         </is>
       </c>
-      <c r="C56" s="6" t="n">
+      <c r="C60" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="D60" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E60" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F60" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="G56" s="6" t="n">
+      <c r="G60" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H56" s="6" t="n">
+      <c r="H60" s="6" t="n">
         <v>470</v>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="J56" s="5" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 470 ud.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="13" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="14" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="15" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="15" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="16" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="17" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -4314,7 +4520,7 @@
         <v>1419.7</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="G13" s="21" t="n">
         <v>0</v>
@@ -4326,7 +4532,7 @@
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 450 ud.</t>
+          <t>COMPRA EXTERNA 510 ud.</t>
         </is>
       </c>
     </row>
@@ -4388,14 +4594,14 @@
         <v>1178.6</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G15" s="21" t="n">
         <v>7620</v>
       </c>
       <c r="H15" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 150 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr"/>
@@ -4491,14 +4697,14 @@
         <v>900.9</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G18" s="21" t="n">
         <v>2100</v>
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 500 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 600 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr"/>
@@ -4561,14 +4767,14 @@
         <v>556</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>286</v>
+        <v>346</v>
       </c>
       <c r="G20" s="21" t="n">
         <v>22260</v>
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 286 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 346 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr"/>
@@ -4627,14 +4833,14 @@
         <v>635.6</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G22" s="21" t="n">
         <v>4350</v>
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 150 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr"/>
@@ -4660,14 +4866,14 @@
         <v>730.2</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>611</v>
+        <v>731</v>
       </c>
       <c r="G23" s="21" t="n">
         <v>10440</v>
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 611 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 731 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr"/>
@@ -4819,7 +5025,7 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>BISOPROLOL 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
@@ -4834,10 +5040,10 @@
         <v>0</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>328.1</v>
+        <v>250.3</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="G28" s="21" t="n">
         <v>0</v>
@@ -4849,14 +5055,14 @@
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 81 ud.</t>
+          <t>COMPRA EXTERNA 11 ud.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>MEMANTINA 10 MG COMPRIMIDO</t>
+          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -4871,10 +5077,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="21" t="n">
-        <v>176.6</v>
+        <v>328.1</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="G29" s="21" t="n">
         <v>0</v>
@@ -4886,14 +5092,14 @@
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 177 ud.</t>
+          <t>COMPRA EXTERNA 111 ud.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
+          <t>TRIMEBUTINA 200 MG CM /CR</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
@@ -4908,29 +5114,25 @@
         <v>0</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>215.3</v>
+        <v>315.4</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>216</v>
+        <v>15</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H30" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I30" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 216 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 15 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>CETIRIZINA 10 MG COMPRIMIDO</t>
+          <t>MEMANTINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -4945,25 +5147,29 @@
         <v>0</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>254.5</v>
+        <v>176.6</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 35 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I31" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 177 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>CLOBAZAM 10 MG COMPRIMIDO</t>
+          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
@@ -4978,10 +5184,10 @@
         <v>0</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>150.2</v>
+        <v>215.3</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>57</v>
+        <v>216</v>
       </c>
       <c r="G32" s="21" t="n">
         <v>0</v>
@@ -4993,14 +5199,14 @@
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 57 ud.</t>
+          <t>COMPRA EXTERNA 216 ud.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
+          <t>CETIRIZINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
@@ -5015,17 +5221,17 @@
         <v>0</v>
       </c>
       <c r="E33" s="21" t="n">
-        <v>174.7</v>
+        <v>254.5</v>
       </c>
       <c r="F33" s="21" t="n">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>390</v>
+        <v>150</v>
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 35 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr"/>
@@ -5033,7 +5239,7 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>ACETAZOLAMIDA CM 250 MG</t>
+          <t>CLOBAZAM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
@@ -5048,25 +5254,29 @@
         <v>0</v>
       </c>
       <c r="E34" s="21" t="n">
-        <v>210.2</v>
+        <v>150.2</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="H34" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 57 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -5081,29 +5291,25 @@
         <v>0</v>
       </c>
       <c r="E35" s="21" t="n">
-        <v>117.2</v>
+        <v>174.7</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I35" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 82 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I35" s="20" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>ACETAZOLAMIDA CM 250 MG</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
@@ -5118,29 +5324,25 @@
         <v>0</v>
       </c>
       <c r="E36" s="21" t="n">
-        <v>113.2</v>
+        <v>210.2</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="H36" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I36" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 61 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I36" s="20" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>AMANTADINA 100 MG CAPSULA</t>
+          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -5155,25 +5357,29 @@
         <v>0</v>
       </c>
       <c r="E37" s="21" t="n">
-        <v>173</v>
+        <v>117.2</v>
       </c>
       <c r="F37" s="21" t="n">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="G37" s="21" t="n">
-        <v>3210</v>
+        <v>0</v>
       </c>
       <c r="H37" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 150 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I37" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 86 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
+          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
@@ -5188,10 +5394,10 @@
         <v>0</v>
       </c>
       <c r="E38" s="21" t="n">
-        <v>111.3</v>
+        <v>113.2</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G38" s="21" t="n">
         <v>0</v>
@@ -5203,14 +5409,14 @@
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 45 ud.</t>
+          <t>COMPRA EXTERNA 77 ud.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>AMANTADINA 100 MG CAPSULA</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
@@ -5225,29 +5431,25 @@
         <v>0</v>
       </c>
       <c r="E39" s="21" t="n">
-        <v>71.90000000000001</v>
+        <v>173</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="G39" s="21" t="n">
-        <v>0</v>
+        <v>3210</v>
       </c>
       <c r="H39" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I39" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 72 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 150 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
@@ -5262,25 +5464,29 @@
         <v>0</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>41.1</v>
+        <v>111.3</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>7900</v>
+        <v>0</v>
       </c>
       <c r="H40" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I40" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 45 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -5295,25 +5501,29 @@
         <v>0</v>
       </c>
       <c r="E41" s="21" t="n">
-        <v>57.6</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H41" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I41" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 72 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>MODAFINILO 200 MG COMPRIMIDO</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
@@ -5328,17 +5538,17 @@
         <v>0</v>
       </c>
       <c r="E42" s="21" t="n">
-        <v>74.09999999999999</v>
+        <v>41.1</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>570</v>
+        <v>7900</v>
       </c>
       <c r="H42" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I42" s="20" t="inlineStr"/>
@@ -5346,7 +5556,7 @@
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -5361,29 +5571,25 @@
         <v>0</v>
       </c>
       <c r="E43" s="21" t="n">
-        <v>31.8</v>
+        <v>57.6</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H43" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I43" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 32 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I43" s="20" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>MODAFINILO 200 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
@@ -5398,17 +5604,17 @@
         <v>0</v>
       </c>
       <c r="E44" s="21" t="n">
-        <v>26.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>1600</v>
+        <v>570</v>
       </c>
       <c r="H44" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I44" s="20" t="inlineStr"/>
@@ -5416,7 +5622,7 @@
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
@@ -5431,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="E45" s="21" t="n">
-        <v>38.2</v>
+        <v>31.8</v>
       </c>
       <c r="F45" s="21" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G45" s="21" t="n">
         <v>0</v>
@@ -5446,14 +5652,14 @@
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 37 ud.</t>
+          <t>COMPRA EXTERNA 32 ud.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
@@ -5468,17 +5674,17 @@
         <v>0</v>
       </c>
       <c r="E46" s="21" t="n">
-        <v>30.6</v>
+        <v>26.5</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>60</v>
+        <v>1600</v>
       </c>
       <c r="H46" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 31 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 27 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I46" s="20" t="inlineStr"/>
@@ -5486,7 +5692,7 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
@@ -5501,25 +5707,29 @@
         <v>0</v>
       </c>
       <c r="E47" s="21" t="n">
-        <v>22.8</v>
+        <v>38.2</v>
       </c>
       <c r="F47" s="21" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G47" s="21" t="n">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="H47" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I47" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 37 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
@@ -5534,29 +5744,25 @@
         <v>0</v>
       </c>
       <c r="E48" s="21" t="n">
-        <v>25.4</v>
+        <v>30.6</v>
       </c>
       <c r="F48" s="21" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H48" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I48" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 50 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 31 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I48" s="20" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>SALMETEROL /FLUTICASONA 250 MG/25 MG INH UD</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
@@ -5571,17 +5777,17 @@
         <v>0</v>
       </c>
       <c r="E49" s="21" t="n">
-        <v>34.2</v>
+        <v>22.8</v>
       </c>
       <c r="F49" s="21" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G49" s="21" t="n">
-        <v>520</v>
+        <v>2600</v>
       </c>
       <c r="H49" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 13 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I49" s="20" t="inlineStr"/>
@@ -5589,7 +5795,7 @@
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>APIXABAN 2,5 MG CM</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B50" s="20" t="inlineStr">
@@ -5604,25 +5810,29 @@
         <v>0</v>
       </c>
       <c r="E50" s="21" t="n">
-        <v>21.2</v>
+        <v>25.4</v>
       </c>
       <c r="F50" s="21" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="H50" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I50" s="20" t="inlineStr"/>
+          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I50" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 50 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>SALMETEROL /FLUTICASONA 250 MG/25 MG INH UD</t>
         </is>
       </c>
       <c r="B51" s="20" t="inlineStr">
@@ -5637,17 +5847,17 @@
         <v>0</v>
       </c>
       <c r="E51" s="21" t="n">
-        <v>18.6</v>
+        <v>34.2</v>
       </c>
       <c r="F51" s="21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G51" s="21" t="n">
-        <v>5700</v>
+        <v>520</v>
       </c>
       <c r="H51" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 14 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 15 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I51" s="20" t="inlineStr"/>
@@ -5655,7 +5865,7 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>FENTANILO 25 MCG/HORA PARCHE</t>
+          <t>APIXABAN 2,5 MG CM</t>
         </is>
       </c>
       <c r="B52" s="20" t="inlineStr">
@@ -5670,29 +5880,25 @@
         <v>0</v>
       </c>
       <c r="E52" s="21" t="n">
-        <v>38.1</v>
+        <v>21.2</v>
       </c>
       <c r="F52" s="21" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H52" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I52" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 5 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I52" s="20" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>RISPERIDONA 25 MG FA</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B53" s="20" t="inlineStr">
@@ -5707,29 +5913,25 @@
         <v>0</v>
       </c>
       <c r="E53" s="21" t="n">
-        <v>16.8</v>
+        <v>18.6</v>
       </c>
       <c r="F53" s="21" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G53" s="21" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="H53" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I53" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 17 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 14 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>UREA 10% CREMA 20 GR</t>
+          <t>FENTANILO 25 MCG/HORA PARCHE</t>
         </is>
       </c>
       <c r="B54" s="20" t="inlineStr">
@@ -5744,10 +5946,10 @@
         <v>0</v>
       </c>
       <c r="E54" s="21" t="n">
-        <v>21.9</v>
+        <v>38.1</v>
       </c>
       <c r="F54" s="21" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G54" s="21" t="n">
         <v>0</v>
@@ -5759,14 +5961,14 @@
       </c>
       <c r="I54" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 22 ud.</t>
+          <t>COMPRA EXTERNA 5 ud.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="20" t="inlineStr">
         <is>
-          <t>VASELINA SOLIDA UNGUENTO</t>
+          <t>RISPERIDONA 25 MG FA</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
@@ -5781,10 +5983,10 @@
         <v>0</v>
       </c>
       <c r="E55" s="21" t="n">
-        <v>18</v>
+        <v>16.8</v>
       </c>
       <c r="F55" s="21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G55" s="21" t="n">
         <v>0</v>
@@ -5796,14 +5998,14 @@
       </c>
       <c r="I55" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 18 ud.</t>
+          <t>COMPRA EXTERNA 17 ud.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+          <t>UREA 10% CREMA 20 GR</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
@@ -5818,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="E56" s="21" t="n">
-        <v>28.7</v>
+        <v>21.9</v>
       </c>
       <c r="F56" s="21" t="n">
         <v>22</v>
@@ -5840,7 +6042,7 @@
     <row r="57">
       <c r="A57" s="20" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>VASELINA SOLIDA UNGUENTO</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
@@ -5855,25 +6057,29 @@
         <v>0</v>
       </c>
       <c r="E57" s="21" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="F57" s="21" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G57" s="21" t="n">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H57" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 9 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I57" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I57" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 18 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
+          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
         </is>
       </c>
       <c r="B58" s="20" t="inlineStr">
@@ -5888,10 +6094,10 @@
         <v>0</v>
       </c>
       <c r="E58" s="21" t="n">
-        <v>30.5</v>
+        <v>28.7</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G58" s="21" t="n">
         <v>0</v>
@@ -5903,14 +6109,14 @@
       </c>
       <c r="I58" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 21 ud.</t>
+          <t>COMPRA EXTERNA 22 ud.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="20" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B59" s="20" t="inlineStr">
@@ -5925,29 +6131,25 @@
         <v>0</v>
       </c>
       <c r="E59" s="21" t="n">
-        <v>14.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F59" s="21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G59" s="21" t="n">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="H59" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I59" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 12 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 9 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I59" s="20" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
+          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
         </is>
       </c>
       <c r="B60" s="20" t="inlineStr">
@@ -5962,10 +6164,10 @@
         <v>0</v>
       </c>
       <c r="E60" s="21" t="n">
-        <v>3.1</v>
+        <v>30.5</v>
       </c>
       <c r="F60" s="21" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G60" s="21" t="n">
         <v>0</v>
@@ -5977,14 +6179,14 @@
       </c>
       <c r="I60" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 4 ud.</t>
+          <t>COMPRA EXTERNA 21 ud.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="20" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
         </is>
       </c>
       <c r="B61" s="20" t="inlineStr">
@@ -5999,25 +6201,29 @@
         <v>0</v>
       </c>
       <c r="E61" s="21" t="n">
-        <v>0.7</v>
+        <v>14.3</v>
       </c>
       <c r="F61" s="21" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G61" s="21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H61" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I61" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I61" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 12 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
+          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B62" s="20" t="inlineStr">
@@ -6032,10 +6238,10 @@
         <v>0</v>
       </c>
       <c r="E62" s="21" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="F62" s="21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" s="21" t="n">
         <v>0</v>
@@ -6047,14 +6253,14 @@
       </c>
       <c r="I62" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3 ud.</t>
+          <t>COMPRA EXTERNA 4 ud.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="20" t="inlineStr">
         <is>
-          <t>LEVETIRACETAM 100 MG/ML FC 300 ML</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
@@ -6069,17 +6275,17 @@
         <v>0</v>
       </c>
       <c r="E63" s="21" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="F63" s="21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G63" s="21" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H63" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 10 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I63" s="20" t="inlineStr"/>
@@ -6087,7 +6293,7 @@
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
+          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
         </is>
       </c>
       <c r="B64" s="20" t="inlineStr">
@@ -6102,10 +6308,10 @@
         <v>0</v>
       </c>
       <c r="E64" s="21" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="F64" s="21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64" s="21" t="n">
         <v>0</v>
@@ -6117,14 +6323,14 @@
       </c>
       <c r="I64" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2 ud.</t>
+          <t>COMPRA EXTERNA 3 ud.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="20" t="inlineStr">
         <is>
-          <t>ETONOGESTREL 68 MG IMPLANTE</t>
+          <t>LEVETIRACETAM 100 MG/ML FC 300 ML</t>
         </is>
       </c>
       <c r="B65" s="20" t="inlineStr">
@@ -6139,17 +6345,17 @@
         <v>0</v>
       </c>
       <c r="E65" s="21" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="F65" s="21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G65" s="21" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="H65" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 10 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I65" s="20" t="inlineStr"/>
@@ -6157,7 +6363,7 @@
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
+          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
         </is>
       </c>
       <c r="B66" s="20" t="inlineStr">
@@ -6172,25 +6378,29 @@
         <v>0</v>
       </c>
       <c r="E66" s="21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F66" s="21" t="n">
         <v>2</v>
       </c>
       <c r="G66" s="21" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H66" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I66" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I66" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 2 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="20" t="inlineStr">
         <is>
-          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
+          <t>ETONOGESTREL 68 MG IMPLANTE</t>
         </is>
       </c>
       <c r="B67" s="20" t="inlineStr">
@@ -6205,13 +6415,13 @@
         <v>0</v>
       </c>
       <c r="E67" s="21" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="F67" s="21" t="n">
         <v>2</v>
       </c>
       <c r="G67" s="21" t="n">
-        <v>450</v>
+        <v>11</v>
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
@@ -6223,7 +6433,7 @@
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>ALTEPLASA 50 MG FA UD</t>
+          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
         </is>
       </c>
       <c r="B68" s="20" t="inlineStr">
@@ -6238,29 +6448,25 @@
         <v>0</v>
       </c>
       <c r="E68" s="21" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="F68" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" s="21" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H68" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I68" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I68" s="20" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="20" t="inlineStr">
         <is>
-          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
+          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
         </is>
       </c>
       <c r="B69" s="20" t="inlineStr">
@@ -6275,17 +6481,17 @@
         <v>0</v>
       </c>
       <c r="E69" s="21" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="F69" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="21" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="H69" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I69" s="20" t="inlineStr"/>
@@ -6293,7 +6499,7 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
+          <t>ALTEPLASA 50 MG FA UD</t>
         </is>
       </c>
       <c r="B70" s="20" t="inlineStr">
@@ -6314,19 +6520,23 @@
         <v>1</v>
       </c>
       <c r="G70" s="21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H70" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I70" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I70" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
+          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
         </is>
       </c>
       <c r="B71" s="20" t="inlineStr">
@@ -6347,7 +6557,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H71" s="20" t="inlineStr">
         <is>
@@ -6359,7 +6569,7 @@
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
         </is>
       </c>
       <c r="B72" s="20" t="inlineStr">
@@ -6380,89 +6590,85 @@
         <v>1</v>
       </c>
       <c r="G72" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="H72" s="20" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I72" s="20" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F73" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I73" s="20" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F74" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="21" t="n">
         <v>115</v>
       </c>
-      <c r="H72" s="20" t="inlineStr">
+      <c r="H74" s="20" t="inlineStr">
         <is>
           <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="I72" s="20" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="22" t="inlineStr">
-        <is>
-          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B73" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C73" s="23" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D73" s="23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E73" s="23" t="n">
-        <v>6284.1</v>
-      </c>
-      <c r="F73" s="23" t="n">
-        <v>800</v>
-      </c>
-      <c r="G73" s="23" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H73" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 800 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I73" s="22" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="22" t="inlineStr">
-        <is>
-          <t>PREGABALINA 75 MG CAPSULA</t>
-        </is>
-      </c>
-      <c r="B74" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C74" s="23" t="n">
-        <v>780</v>
-      </c>
-      <c r="D74" s="23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E74" s="23" t="n">
-        <v>5562.8</v>
-      </c>
-      <c r="F74" s="23" t="n">
-        <v>1916</v>
-      </c>
-      <c r="G74" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="22" t="inlineStr">
-        <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I74" s="22" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1916 ud.</t>
-        </is>
-      </c>
+      <c r="I74" s="20" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="22" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
+          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B75" s="22" t="inlineStr">
@@ -6471,35 +6677,31 @@
         </is>
       </c>
       <c r="C75" s="23" t="n">
-        <v>240</v>
+        <v>1400</v>
       </c>
       <c r="D75" s="23" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="E75" s="23" t="n">
-        <v>2879.5</v>
+        <v>6284.1</v>
       </c>
       <c r="F75" s="23" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="G75" s="23" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="H75" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I75" s="22" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1200 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 800 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I75" s="22" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="22" t="inlineStr">
         <is>
-          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
+          <t>PREGABALINA 75 MG CAPSULA</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
@@ -6508,16 +6710,16 @@
         </is>
       </c>
       <c r="C76" s="23" t="n">
-        <v>414</v>
+        <v>900</v>
       </c>
       <c r="D76" s="23" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="E76" s="23" t="n">
-        <v>1492.4</v>
+        <v>5562.8</v>
       </c>
       <c r="F76" s="23" t="n">
-        <v>663</v>
+        <v>2036</v>
       </c>
       <c r="G76" s="23" t="n">
         <v>0</v>
@@ -6529,14 +6731,14 @@
       </c>
       <c r="I76" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 663 ud.</t>
+          <t>COMPRA EXTERNA 2036 ud.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="22" t="inlineStr">
         <is>
-          <t>RIFAXIMINA 200 MG CP</t>
+          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
         </is>
       </c>
       <c r="B77" s="22" t="inlineStr">
@@ -6545,31 +6747,35 @@
         </is>
       </c>
       <c r="C77" s="23" t="n">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="D77" s="23" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E77" s="23" t="n">
-        <v>707.8</v>
+        <v>2879.5</v>
       </c>
       <c r="F77" s="23" t="n">
-        <v>384</v>
+        <v>1260</v>
       </c>
       <c r="G77" s="23" t="n">
-        <v>23640</v>
+        <v>0</v>
       </c>
       <c r="H77" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 384 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I77" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I77" s="22" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1260 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="22" t="inlineStr">
         <is>
-          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
+          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
@@ -6578,16 +6784,16 @@
         </is>
       </c>
       <c r="C78" s="23" t="n">
-        <v>30</v>
+        <v>403</v>
       </c>
       <c r="D78" s="23" t="n">
         <v>1.8</v>
       </c>
       <c r="E78" s="23" t="n">
-        <v>129.2</v>
+        <v>1492.4</v>
       </c>
       <c r="F78" s="23" t="n">
-        <v>24</v>
+        <v>754</v>
       </c>
       <c r="G78" s="23" t="n">
         <v>0</v>
@@ -6599,117 +6805,121 @@
       </c>
       <c r="I78" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 24 ud.</t>
+          <t>COMPRA EXTERNA 754 ud.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="22" t="inlineStr">
         <is>
+          <t>RIFAXIMINA 200 MG CP</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C79" s="23" t="n">
+        <v>192</v>
+      </c>
+      <c r="D79" s="23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E79" s="23" t="n">
+        <v>707.8</v>
+      </c>
+      <c r="F79" s="23" t="n">
+        <v>384</v>
+      </c>
+      <c r="G79" s="23" t="n">
+        <v>23640</v>
+      </c>
+      <c r="H79" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 384 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I79" s="22" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="22" t="inlineStr">
+        <is>
+          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C80" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="D80" s="23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E80" s="23" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="F80" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="G80" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I80" s="22" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 24 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="inlineStr">
+        <is>
           <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
-      <c r="B79" s="22" t="inlineStr">
+      <c r="B81" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C79" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D79" s="23" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E79" s="23" t="n">
+      <c r="C81" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E81" s="23" t="n">
         <v>71.3</v>
       </c>
-      <c r="F79" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="G79" s="23" t="n">
+      <c r="F81" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="G81" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H79" s="22" t="inlineStr">
+      <c r="H81" s="22" t="inlineStr">
         <is>
           <t>TRASPASAR 20 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="I79" s="22" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 11 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="26" t="inlineStr">
-        <is>
-          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B80" s="26" t="inlineStr">
-        <is>
-          <t>3-ALTO</t>
-        </is>
-      </c>
-      <c r="C80" s="27" t="n">
-        <v>2688</v>
-      </c>
-      <c r="D80" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="E80" s="27" t="n">
-        <v>7110.5</v>
-      </c>
-      <c r="F80" s="27" t="n">
-        <v>879</v>
-      </c>
-      <c r="G80" s="27" t="n">
-        <v>10024</v>
-      </c>
-      <c r="H80" s="26" t="inlineStr">
-        <is>
-          <t>TRASPASAR 879 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I80" s="26" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="26" t="inlineStr">
-        <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
-        </is>
-      </c>
-      <c r="B81" s="26" t="inlineStr">
-        <is>
-          <t>3-ALTO</t>
-        </is>
-      </c>
-      <c r="C81" s="27" t="n">
-        <v>2280</v>
-      </c>
-      <c r="D81" s="27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E81" s="27" t="n">
-        <v>4792.7</v>
-      </c>
-      <c r="F81" s="27" t="n">
-        <v>1230</v>
-      </c>
-      <c r="G81" s="27" t="n">
-        <v>2520</v>
-      </c>
-      <c r="H81" s="26" t="inlineStr">
-        <is>
-          <t>TRASPASAR 1230 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I81" s="26" t="inlineStr"/>
+      <c r="I81" s="22" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 16 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="26" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
+          <t>LOSARTAN 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B82" s="26" t="inlineStr">
@@ -6718,23 +6928,23 @@
         </is>
       </c>
       <c r="C82" s="27" t="n">
-        <v>1920</v>
+        <v>4500</v>
       </c>
       <c r="D82" s="27" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="E82" s="27" t="n">
-        <v>4746.9</v>
+        <v>9049.299999999999</v>
       </c>
       <c r="F82" s="27" t="n">
-        <v>1110</v>
+        <v>1200</v>
       </c>
       <c r="G82" s="27" t="n">
-        <v>13290</v>
+        <v>32400</v>
       </c>
       <c r="H82" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1110 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1200 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I82" s="26" t="inlineStr"/>
@@ -6742,7 +6952,7 @@
     <row r="83">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>HIDROXICLOROQUINA CM 200 MG</t>
+          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B83" s="26" t="inlineStr">
@@ -6751,23 +6961,23 @@
         </is>
       </c>
       <c r="C83" s="27" t="n">
-        <v>1200</v>
+        <v>2688</v>
       </c>
       <c r="D83" s="27" t="n">
         <v>3</v>
       </c>
       <c r="E83" s="27" t="n">
-        <v>3350.6</v>
+        <v>7110.5</v>
       </c>
       <c r="F83" s="27" t="n">
-        <v>840</v>
+        <v>1089</v>
       </c>
       <c r="G83" s="27" t="n">
-        <v>45840</v>
+        <v>10024</v>
       </c>
       <c r="H83" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 840 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1089 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I83" s="26" t="inlineStr"/>
@@ -6775,214 +6985,238 @@
     <row r="84">
       <c r="A84" s="26" t="inlineStr">
         <is>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+        </is>
+      </c>
+      <c r="B84" s="26" t="inlineStr">
+        <is>
+          <t>3-ALTO</t>
+        </is>
+      </c>
+      <c r="C84" s="27" t="n">
+        <v>2280</v>
+      </c>
+      <c r="D84" s="27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E84" s="27" t="n">
+        <v>4792.7</v>
+      </c>
+      <c r="F84" s="27" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G84" s="27" t="n">
+        <v>2520</v>
+      </c>
+      <c r="H84" s="26" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1380 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I84" s="26" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="26" t="inlineStr">
+        <is>
+          <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B85" s="26" t="inlineStr">
+        <is>
+          <t>3-ALTO</t>
+        </is>
+      </c>
+      <c r="C85" s="27" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D85" s="27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E85" s="27" t="n">
+        <v>4746.9</v>
+      </c>
+      <c r="F85" s="27" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G85" s="27" t="n">
+        <v>13290</v>
+      </c>
+      <c r="H85" s="26" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1320 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I85" s="26" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="26" t="inlineStr">
+        <is>
+          <t>HIDROXICLOROQUINA CM 200 MG</t>
+        </is>
+      </c>
+      <c r="B86" s="26" t="inlineStr">
+        <is>
+          <t>3-ALTO</t>
+        </is>
+      </c>
+      <c r="C86" s="27" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D86" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" s="27" t="n">
+        <v>3350.6</v>
+      </c>
+      <c r="F86" s="27" t="n">
+        <v>840</v>
+      </c>
+      <c r="G86" s="27" t="n">
+        <v>45840</v>
+      </c>
+      <c r="H86" s="26" t="inlineStr">
+        <is>
+          <t>TRASPASAR 840 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I86" s="26" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
+          <t>DULOXETINA 60 MG CAPSULA</t>
+        </is>
+      </c>
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>3-ALTO</t>
+        </is>
+      </c>
+      <c r="C87" s="27" t="n">
+        <v>600</v>
+      </c>
+      <c r="D87" s="27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E87" s="27" t="n">
+        <v>912.2</v>
+      </c>
+      <c r="F87" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="G87" s="27" t="n">
+        <v>3810</v>
+      </c>
+      <c r="H87" s="26" t="inlineStr">
+        <is>
+          <t>TRASPASAR 30 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I87" s="26" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="26" t="inlineStr">
+        <is>
           <t>DULOXETINA 30 MG CAPSULA</t>
         </is>
       </c>
-      <c r="B84" s="26" t="inlineStr">
+      <c r="B88" s="26" t="inlineStr">
         <is>
           <t>3-ALTO</t>
         </is>
       </c>
-      <c r="C84" s="27" t="n">
+      <c r="C88" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="D84" s="27" t="n">
+      <c r="D88" s="27" t="n">
         <v>4.4</v>
       </c>
-      <c r="E84" s="27" t="n">
+      <c r="E88" s="27" t="n">
         <v>1177.4</v>
       </c>
-      <c r="F84" s="27" t="n">
-        <v>150</v>
-      </c>
-      <c r="G84" s="27" t="n">
+      <c r="F88" s="27" t="n">
+        <v>270</v>
+      </c>
+      <c r="G88" s="27" t="n">
         <v>2430</v>
       </c>
-      <c r="H84" s="26" t="inlineStr">
-        <is>
-          <t>TRASPASAR 150 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I84" s="26" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="28" t="inlineStr">
-        <is>
-          <t>PARACETAMOL 500 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B85" s="28" t="inlineStr">
-        <is>
-          <t>5-OK</t>
-        </is>
-      </c>
-      <c r="C85" s="29" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D85" s="29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="E85" s="29" t="n">
-        <v>15662.3</v>
-      </c>
-      <c r="F85" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="29" t="n">
-        <v>170000</v>
-      </c>
-      <c r="H85" s="28" t="inlineStr"/>
-      <c r="I85" s="28" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="28" t="inlineStr">
-        <is>
-          <t>LOSARTAN 50 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B86" s="28" t="inlineStr">
-        <is>
-          <t>5-OK</t>
-        </is>
-      </c>
-      <c r="C86" s="29" t="n">
-        <v>4500</v>
-      </c>
-      <c r="D86" s="29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E86" s="29" t="n">
-        <v>9049.299999999999</v>
-      </c>
-      <c r="F86" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="29" t="n">
-        <v>32400</v>
-      </c>
-      <c r="H86" s="28" t="inlineStr"/>
-      <c r="I86" s="28" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="28" t="inlineStr">
-        <is>
-          <t>OMEPRAZOL 20 MG CAPSULA</t>
-        </is>
-      </c>
-      <c r="B87" s="28" t="inlineStr">
-        <is>
-          <t>5-OK</t>
-        </is>
-      </c>
-      <c r="C87" s="29" t="n">
-        <v>4900</v>
-      </c>
-      <c r="D87" s="29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E87" s="29" t="n">
-        <v>8206.4</v>
-      </c>
-      <c r="F87" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="29" t="n">
-        <v>53000</v>
-      </c>
-      <c r="H87" s="28" t="inlineStr"/>
-      <c r="I87" s="28" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="28" t="inlineStr">
-        <is>
-          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
-        </is>
-      </c>
-      <c r="B88" s="28" t="inlineStr">
-        <is>
-          <t>5-OK</t>
-        </is>
-      </c>
-      <c r="C88" s="29" t="n">
-        <v>4700</v>
-      </c>
-      <c r="D88" s="29" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E88" s="29" t="n">
-        <v>6283.7</v>
-      </c>
-      <c r="F88" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="29" t="n">
-        <v>45000</v>
-      </c>
-      <c r="H88" s="28" t="inlineStr"/>
-      <c r="I88" s="28" t="inlineStr"/>
+      <c r="H88" s="26" t="inlineStr">
+        <is>
+          <t>TRASPASAR 270 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I88" s="26" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="28" t="inlineStr">
-        <is>
-          <t>CALCIO CARBONATO C/VITAMINA D CM O CP</t>
-        </is>
-      </c>
-      <c r="B89" s="28" t="inlineStr">
-        <is>
-          <t>5-OK</t>
-        </is>
-      </c>
-      <c r="C89" s="29" t="n">
-        <v>9100</v>
-      </c>
-      <c r="D89" s="29" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E89" s="29" t="n">
-        <v>6279.2</v>
-      </c>
-      <c r="F89" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="29" t="n">
-        <v>92100</v>
-      </c>
-      <c r="H89" s="28" t="inlineStr"/>
-      <c r="I89" s="28" t="inlineStr"/>
+      <c r="A89" s="26" t="inlineStr">
+        <is>
+          <t>TRAZODONA CM 100 MG</t>
+        </is>
+      </c>
+      <c r="B89" s="26" t="inlineStr">
+        <is>
+          <t>3-ALTO</t>
+        </is>
+      </c>
+      <c r="C89" s="27" t="n">
+        <v>400</v>
+      </c>
+      <c r="D89" s="27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E89" s="27" t="n">
+        <v>829.3</v>
+      </c>
+      <c r="F89" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="G89" s="27" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H89" s="26" t="inlineStr">
+        <is>
+          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I89" s="26" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="28" t="inlineStr">
-        <is>
-          <t>DABIGATRAN ETEXILATO CP 150 MG</t>
-        </is>
-      </c>
-      <c r="B90" s="28" t="inlineStr">
-        <is>
-          <t>5-OK</t>
-        </is>
-      </c>
-      <c r="C90" s="29" t="n">
-        <v>5190</v>
-      </c>
-      <c r="D90" s="29" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E90" s="29" t="n">
-        <v>4986.9</v>
-      </c>
-      <c r="F90" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="29" t="n">
-        <v>24420</v>
-      </c>
-      <c r="H90" s="28" t="inlineStr"/>
-      <c r="I90" s="28" t="inlineStr"/>
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>TRAMADOL CP 50 MG</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>4-MODERADO</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>1855.4</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>7700</v>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="28" t="inlineStr">
         <is>
-          <t>METFORMINA 1000 MG CM LIBERACION MODIFICADA</t>
+          <t>PARACETAMOL 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B91" s="28" t="inlineStr">
@@ -6991,19 +7225,19 @@
         </is>
       </c>
       <c r="C91" s="29" t="n">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="D91" s="29" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="E91" s="29" t="n">
-        <v>4767.4</v>
+        <v>15662.3</v>
       </c>
       <c r="F91" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="29" t="n">
-        <v>9500</v>
+        <v>170000</v>
       </c>
       <c r="H91" s="28" t="inlineStr"/>
       <c r="I91" s="28" t="inlineStr"/>
@@ -7011,7 +7245,7 @@
     <row r="92">
       <c r="A92" s="28" t="inlineStr">
         <is>
-          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
+          <t>OMEPRAZOL 20 MG CAPSULA</t>
         </is>
       </c>
       <c r="B92" s="28" t="inlineStr">
@@ -7020,19 +7254,19 @@
         </is>
       </c>
       <c r="C92" s="29" t="n">
-        <v>4989</v>
+        <v>4800</v>
       </c>
       <c r="D92" s="29" t="n">
-        <v>7.9</v>
+        <v>4.8</v>
       </c>
       <c r="E92" s="29" t="n">
-        <v>4510.4</v>
+        <v>8206.4</v>
       </c>
       <c r="F92" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="29" t="n">
-        <v>0</v>
+        <v>53000</v>
       </c>
       <c r="H92" s="28" t="inlineStr"/>
       <c r="I92" s="28" t="inlineStr"/>
@@ -7040,7 +7274,7 @@
     <row r="93">
       <c r="A93" s="28" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 40 MG COMPRIMIDO</t>
+          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
         </is>
       </c>
       <c r="B93" s="28" t="inlineStr">
@@ -7049,19 +7283,19 @@
         </is>
       </c>
       <c r="C93" s="29" t="n">
-        <v>3320</v>
+        <v>4700</v>
       </c>
       <c r="D93" s="29" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="E93" s="29" t="n">
-        <v>4591.6</v>
+        <v>6283.7</v>
       </c>
       <c r="F93" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="29" t="n">
-        <v>11700</v>
+        <v>45000</v>
       </c>
       <c r="H93" s="28" t="inlineStr"/>
       <c r="I93" s="28" t="inlineStr"/>
@@ -7069,7 +7303,7 @@
     <row r="94">
       <c r="A94" s="28" t="inlineStr">
         <is>
-          <t>DABIGATRAN ETEXILATO CP 110 MG</t>
+          <t>CALCIO CARBONATO C/VITAMINA D CM O CP</t>
         </is>
       </c>
       <c r="B94" s="28" t="inlineStr">
@@ -7078,19 +7312,19 @@
         </is>
       </c>
       <c r="C94" s="29" t="n">
-        <v>3840</v>
+        <v>9100</v>
       </c>
       <c r="D94" s="29" t="n">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="E94" s="29" t="n">
-        <v>3711.3</v>
+        <v>6279.2</v>
       </c>
       <c r="F94" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="29" t="n">
-        <v>4260</v>
+        <v>92100</v>
       </c>
       <c r="H94" s="28" t="inlineStr"/>
       <c r="I94" s="28" t="inlineStr"/>
@@ -7098,7 +7332,7 @@
     <row r="95">
       <c r="A95" s="28" t="inlineStr">
         <is>
-          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
+          <t>DABIGATRAN ETEXILATO CP 150 MG</t>
         </is>
       </c>
       <c r="B95" s="28" t="inlineStr">
@@ -7107,19 +7341,19 @@
         </is>
       </c>
       <c r="C95" s="29" t="n">
-        <v>700</v>
+        <v>5190</v>
       </c>
       <c r="D95" s="29" t="n">
-        <v>1.3</v>
+        <v>7.9</v>
       </c>
       <c r="E95" s="29" t="n">
-        <v>3679.1</v>
+        <v>4986.9</v>
       </c>
       <c r="F95" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="29" t="n">
-        <v>1600</v>
+        <v>24420</v>
       </c>
       <c r="H95" s="28" t="inlineStr"/>
       <c r="I95" s="28" t="inlineStr"/>
@@ -7127,7 +7361,7 @@
     <row r="96">
       <c r="A96" s="28" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 20 MG COMPRIMIDO</t>
+          <t>METFORMINA 1000 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B96" s="28" t="inlineStr">
@@ -7136,19 +7370,19 @@
         </is>
       </c>
       <c r="C96" s="29" t="n">
-        <v>3700</v>
+        <v>4000</v>
       </c>
       <c r="D96" s="29" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="E96" s="29" t="n">
-        <v>3834.1</v>
+        <v>4767.4</v>
       </c>
       <c r="F96" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="29" t="n">
-        <v>47000</v>
+        <v>9500</v>
       </c>
       <c r="H96" s="28" t="inlineStr"/>
       <c r="I96" s="28" t="inlineStr"/>
@@ -7156,7 +7390,7 @@
     <row r="97">
       <c r="A97" s="28" t="inlineStr">
         <is>
-          <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
         </is>
       </c>
       <c r="B97" s="28" t="inlineStr">
@@ -7165,19 +7399,19 @@
         </is>
       </c>
       <c r="C97" s="29" t="n">
-        <v>3200</v>
+        <v>4679</v>
       </c>
       <c r="D97" s="29" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="E97" s="29" t="n">
-        <v>3010.2</v>
+        <v>4510.4</v>
       </c>
       <c r="F97" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="29" t="n">
-        <v>25180</v>
+        <v>0</v>
       </c>
       <c r="H97" s="28" t="inlineStr"/>
       <c r="I97" s="28" t="inlineStr"/>
@@ -7185,7 +7419,7 @@
     <row r="98">
       <c r="A98" s="28" t="inlineStr">
         <is>
-          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
+          <t>ATORVASTATINA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B98" s="28" t="inlineStr">
@@ -7194,19 +7428,19 @@
         </is>
       </c>
       <c r="C98" s="29" t="n">
-        <v>3090</v>
+        <v>3320</v>
       </c>
       <c r="D98" s="29" t="n">
-        <v>7.7</v>
+        <v>5.5</v>
       </c>
       <c r="E98" s="29" t="n">
-        <v>2650.9</v>
+        <v>4591.6</v>
       </c>
       <c r="F98" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="29" t="n">
-        <v>3060</v>
+        <v>11700</v>
       </c>
       <c r="H98" s="28" t="inlineStr"/>
       <c r="I98" s="28" t="inlineStr"/>
@@ -7214,7 +7448,7 @@
     <row r="99">
       <c r="A99" s="28" t="inlineStr">
         <is>
-          <t>TRAMADOL + PARACETAMOL 37,5 MG/325 MG CM</t>
+          <t>DABIGATRAN ETEXILATO CP 110 MG</t>
         </is>
       </c>
       <c r="B99" s="28" t="inlineStr">
@@ -7223,19 +7457,19 @@
         </is>
       </c>
       <c r="C99" s="29" t="n">
-        <v>2700</v>
+        <v>3840</v>
       </c>
       <c r="D99" s="29" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="E99" s="29" t="n">
-        <v>2661.8</v>
+        <v>3711.3</v>
       </c>
       <c r="F99" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="29" t="n">
-        <v>0</v>
+        <v>4260</v>
       </c>
       <c r="H99" s="28" t="inlineStr"/>
       <c r="I99" s="28" t="inlineStr"/>
@@ -7243,7 +7477,7 @@
     <row r="100">
       <c r="A100" s="28" t="inlineStr">
         <is>
-          <t>SERTRALINA CM 50 MG</t>
+          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
         </is>
       </c>
       <c r="B100" s="28" t="inlineStr">
@@ -7252,19 +7486,19 @@
         </is>
       </c>
       <c r="C100" s="29" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="D100" s="29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="E100" s="29" t="n">
-        <v>2458.6</v>
+        <v>3679.1</v>
       </c>
       <c r="F100" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="29" t="n">
-        <v>14000</v>
+        <v>1600</v>
       </c>
       <c r="H100" s="28" t="inlineStr"/>
       <c r="I100" s="28" t="inlineStr"/>
@@ -7272,7 +7506,7 @@
     <row r="101">
       <c r="A101" s="28" t="inlineStr">
         <is>
-          <t>QUETIAPINA 100 MG COMPRIMIDO</t>
+          <t>ATORVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B101" s="28" t="inlineStr">
@@ -7281,19 +7515,19 @@
         </is>
       </c>
       <c r="C101" s="29" t="n">
-        <v>2000</v>
+        <v>3700</v>
       </c>
       <c r="D101" s="29" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="E101" s="29" t="n">
-        <v>2642.1</v>
+        <v>3834.1</v>
       </c>
       <c r="F101" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="29" t="n">
-        <v>26000</v>
+        <v>47000</v>
       </c>
       <c r="H101" s="28" t="inlineStr"/>
       <c r="I101" s="28" t="inlineStr"/>
@@ -7301,7 +7535,7 @@
     <row r="102">
       <c r="A102" s="28" t="inlineStr">
         <is>
-          <t>QUETIAPINA 25 MG COMPRIMIDO</t>
+          <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B102" s="28" t="inlineStr">
@@ -7310,19 +7544,19 @@
         </is>
       </c>
       <c r="C102" s="29" t="n">
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="D102" s="29" t="n">
         <v>6.9</v>
       </c>
       <c r="E102" s="29" t="n">
-        <v>1969.1</v>
+        <v>3010.2</v>
       </c>
       <c r="F102" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G102" s="29" t="n">
-        <v>17000</v>
+        <v>25180</v>
       </c>
       <c r="H102" s="28" t="inlineStr"/>
       <c r="I102" s="28" t="inlineStr"/>
@@ -7330,7 +7564,7 @@
     <row r="103">
       <c r="A103" s="28" t="inlineStr">
         <is>
-          <t>METOTREXATO 2,5 MG COMPRIMIDO</t>
+          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B103" s="28" t="inlineStr">
@@ -7339,19 +7573,19 @@
         </is>
       </c>
       <c r="C103" s="29" t="n">
-        <v>0</v>
+        <v>3090</v>
       </c>
       <c r="D103" s="29" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E103" s="29" t="n">
-        <v>1821.9</v>
+        <v>2650.9</v>
       </c>
       <c r="F103" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G103" s="29" t="n">
-        <v>6000</v>
+        <v>3060</v>
       </c>
       <c r="H103" s="28" t="inlineStr"/>
       <c r="I103" s="28" t="inlineStr"/>
@@ -7359,7 +7593,7 @@
     <row r="104">
       <c r="A104" s="28" t="inlineStr">
         <is>
-          <t>CLOZAPINA 100 MG COMPRIMIDO</t>
+          <t>TRAMADOL + PARACETAMOL 37,5 MG/325 MG CM</t>
         </is>
       </c>
       <c r="B104" s="28" t="inlineStr">
@@ -7368,19 +7602,19 @@
         </is>
       </c>
       <c r="C104" s="29" t="n">
-        <v>1740</v>
+        <v>2700</v>
       </c>
       <c r="D104" s="29" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="E104" s="29" t="n">
-        <v>2050.7</v>
+        <v>2661.8</v>
       </c>
       <c r="F104" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G104" s="29" t="n">
-        <v>2310</v>
+        <v>0</v>
       </c>
       <c r="H104" s="28" t="inlineStr"/>
       <c r="I104" s="28" t="inlineStr"/>
@@ -7388,7 +7622,7 @@
     <row r="105">
       <c r="A105" s="28" t="inlineStr">
         <is>
-          <t>AMLODIPINO 10 MG COMPRIMIDO</t>
+          <t>SERTRALINA CM 50 MG</t>
         </is>
       </c>
       <c r="B105" s="28" t="inlineStr">
@@ -7397,19 +7631,19 @@
         </is>
       </c>
       <c r="C105" s="29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D105" s="29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="E105" s="29" t="n">
-        <v>2116.5</v>
+        <v>2458.6</v>
       </c>
       <c r="F105" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="29" t="n">
-        <v>26000</v>
+        <v>14000</v>
       </c>
       <c r="H105" s="28" t="inlineStr"/>
       <c r="I105" s="28" t="inlineStr"/>
@@ -7417,7 +7651,7 @@
     <row r="106">
       <c r="A106" s="28" t="inlineStr">
         <is>
-          <t>ZOPICLONA CM 7,5 MG</t>
+          <t>QUETIAPINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B106" s="28" t="inlineStr">
@@ -7426,19 +7660,19 @@
         </is>
       </c>
       <c r="C106" s="29" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="D106" s="29" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="E106" s="29" t="n">
-        <v>1937.8</v>
+        <v>2642.1</v>
       </c>
       <c r="F106" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G106" s="29" t="n">
-        <v>3000</v>
+        <v>26000</v>
       </c>
       <c r="H106" s="28" t="inlineStr"/>
       <c r="I106" s="28" t="inlineStr"/>
@@ -7446,7 +7680,7 @@
     <row r="107">
       <c r="A107" s="28" t="inlineStr">
         <is>
-          <t>VENLAFAXINA 75 MG COMPRIMIDOS LIBERACION MODIFICADA</t>
+          <t>QUETIAPINA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B107" s="28" t="inlineStr">
@@ -7458,16 +7692,16 @@
         <v>2000</v>
       </c>
       <c r="D107" s="29" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="E107" s="29" t="n">
-        <v>1623.9</v>
+        <v>1969.1</v>
       </c>
       <c r="F107" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G107" s="29" t="n">
-        <v>40500</v>
+        <v>17000</v>
       </c>
       <c r="H107" s="28" t="inlineStr"/>
       <c r="I107" s="28" t="inlineStr"/>
@@ -7475,7 +7709,7 @@
     <row r="108">
       <c r="A108" s="28" t="inlineStr">
         <is>
-          <t>PREDNISONA 5 MG COMPRIMIDO</t>
+          <t>METOTREXATO 2,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B108" s="28" t="inlineStr">
@@ -7484,19 +7718,19 @@
         </is>
       </c>
       <c r="C108" s="29" t="n">
-        <v>1110</v>
+        <v>0</v>
       </c>
       <c r="D108" s="29" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="E108" s="29" t="n">
-        <v>1752.8</v>
+        <v>1821.9</v>
       </c>
       <c r="F108" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="29" t="n">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="H108" s="28" t="inlineStr"/>
       <c r="I108" s="28" t="inlineStr"/>
@@ -7504,7 +7738,7 @@
     <row r="109">
       <c r="A109" s="28" t="inlineStr">
         <is>
-          <t>OLANZAPINA 10 MG CM UNIDAD</t>
+          <t>CLOZAPINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B109" s="28" t="inlineStr">
@@ -7513,19 +7747,19 @@
         </is>
       </c>
       <c r="C109" s="29" t="n">
-        <v>1000</v>
+        <v>1740</v>
       </c>
       <c r="D109" s="29" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="E109" s="29" t="n">
-        <v>1746.1</v>
+        <v>2050.7</v>
       </c>
       <c r="F109" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="29" t="n">
-        <v>9000</v>
+        <v>2310</v>
       </c>
       <c r="H109" s="28" t="inlineStr"/>
       <c r="I109" s="28" t="inlineStr"/>
@@ -7533,7 +7767,7 @@
     <row r="110">
       <c r="A110" s="28" t="inlineStr">
         <is>
-          <t>JERINGA P/INSULINA C/AGUJA 1 ML 100 UI/A. FIJA 29-31G X 6MM</t>
+          <t>AMLODIPINO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B110" s="28" t="inlineStr">
@@ -7542,19 +7776,19 @@
         </is>
       </c>
       <c r="C110" s="29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D110" s="29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="E110" s="29" t="n">
-        <v>1482.9</v>
+        <v>2116.5</v>
       </c>
       <c r="F110" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="29" t="n">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="H110" s="28" t="inlineStr"/>
       <c r="I110" s="28" t="inlineStr"/>
@@ -7562,7 +7796,7 @@
     <row r="111">
       <c r="A111" s="28" t="inlineStr">
         <is>
-          <t>BUPROPION (ANFEBUTAMONA) 150 MG CM LIBERACION MODIFICADA</t>
+          <t>ZOPICLONA CM 7,5 MG</t>
         </is>
       </c>
       <c r="B111" s="28" t="inlineStr">
@@ -7571,19 +7805,19 @@
         </is>
       </c>
       <c r="C111" s="29" t="n">
-        <v>3360</v>
+        <v>500</v>
       </c>
       <c r="D111" s="29" t="n">
-        <v>15.4</v>
+        <v>2</v>
       </c>
       <c r="E111" s="29" t="n">
-        <v>1670.9</v>
+        <v>1937.8</v>
       </c>
       <c r="F111" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="29" t="n">
-        <v>1650</v>
+        <v>3000</v>
       </c>
       <c r="H111" s="28" t="inlineStr"/>
       <c r="I111" s="28" t="inlineStr"/>
@@ -7591,7 +7825,7 @@
     <row r="112">
       <c r="A112" s="28" t="inlineStr">
         <is>
-          <t>FLUOXETINA 20 MG COMPRIMIDO</t>
+          <t>VENLAFAXINA 75 MG COMPRIMIDOS LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B112" s="28" t="inlineStr">
@@ -7600,19 +7834,19 @@
         </is>
       </c>
       <c r="C112" s="29" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="D112" s="29" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="E112" s="29" t="n">
-        <v>1603.1</v>
+        <v>1623.9</v>
       </c>
       <c r="F112" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="29" t="n">
-        <v>2000</v>
+        <v>40500</v>
       </c>
       <c r="H112" s="28" t="inlineStr"/>
       <c r="I112" s="28" t="inlineStr"/>
@@ -7620,7 +7854,7 @@
     <row r="113">
       <c r="A113" s="28" t="inlineStr">
         <is>
-          <t>CARVEDILOL 12,5 MG COMPRIMIDO</t>
+          <t>PREDNISONA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B113" s="28" t="inlineStr">
@@ -7629,19 +7863,19 @@
         </is>
       </c>
       <c r="C113" s="29" t="n">
-        <v>480</v>
+        <v>1110</v>
       </c>
       <c r="D113" s="29" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="E113" s="29" t="n">
-        <v>1721.2</v>
+        <v>1752.8</v>
       </c>
       <c r="F113" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G113" s="29" t="n">
-        <v>36390</v>
+        <v>15000</v>
       </c>
       <c r="H113" s="28" t="inlineStr"/>
       <c r="I113" s="28" t="inlineStr"/>
@@ -7649,7 +7883,7 @@
     <row r="114">
       <c r="A114" s="28" t="inlineStr">
         <is>
-          <t>DIVALPROATO SODICO CM 500 MG LIBRACION MODIFICADA</t>
+          <t>OLANZAPINA 10 MG CM UNIDAD</t>
         </is>
       </c>
       <c r="B114" s="28" t="inlineStr">
@@ -7658,19 +7892,19 @@
         </is>
       </c>
       <c r="C114" s="29" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="D114" s="29" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="E114" s="29" t="n">
-        <v>1756.4</v>
+        <v>1746.1</v>
       </c>
       <c r="F114" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G114" s="29" t="n">
-        <v>43600</v>
+        <v>9000</v>
       </c>
       <c r="H114" s="28" t="inlineStr"/>
       <c r="I114" s="28" t="inlineStr"/>
@@ -7678,7 +7912,7 @@
     <row r="115">
       <c r="A115" s="28" t="inlineStr">
         <is>
-          <t>HIDRALAZINA 50 MG COMPRIMIDO</t>
+          <t>JERINGA P/INSULINA C/AGUJA 1 ML 100 UI/A. FIJA 29-31G X 6MM</t>
         </is>
       </c>
       <c r="B115" s="28" t="inlineStr">
@@ -7687,19 +7921,19 @@
         </is>
       </c>
       <c r="C115" s="29" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="D115" s="29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="E115" s="29" t="n">
-        <v>1417</v>
+        <v>1482.9</v>
       </c>
       <c r="F115" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="29" t="n">
-        <v>53790</v>
+        <v>0</v>
       </c>
       <c r="H115" s="28" t="inlineStr"/>
       <c r="I115" s="28" t="inlineStr"/>
@@ -7707,7 +7941,7 @@
     <row r="116">
       <c r="A116" s="28" t="inlineStr">
         <is>
-          <t>METILFENIDATO 10 MG CM LIBERACION MODIFICADA</t>
+          <t>BUPROPION (ANFEBUTAMONA) 150 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B116" s="28" t="inlineStr">
@@ -7716,19 +7950,19 @@
         </is>
       </c>
       <c r="C116" s="29" t="n">
-        <v>0</v>
+        <v>3316</v>
       </c>
       <c r="D116" s="29" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="E116" s="29" t="n">
-        <v>1608</v>
+        <v>1670.9</v>
       </c>
       <c r="F116" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="29" t="n">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="H116" s="28" t="inlineStr"/>
       <c r="I116" s="28" t="inlineStr"/>
@@ -7736,7 +7970,7 @@
     <row r="117">
       <c r="A117" s="28" t="inlineStr">
         <is>
-          <t>TRAMADOL CP 50 MG</t>
+          <t>FLUOXETINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B117" s="28" t="inlineStr">
@@ -7745,19 +7979,19 @@
         </is>
       </c>
       <c r="C117" s="29" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D117" s="29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E117" s="29" t="n">
+        <v>1603.1</v>
+      </c>
+      <c r="F117" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="29" t="n">
         <v>2000</v>
-      </c>
-      <c r="D117" s="29" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" s="29" t="n">
-        <v>1855.4</v>
-      </c>
-      <c r="F117" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" s="29" t="n">
-        <v>7700</v>
       </c>
       <c r="H117" s="28" t="inlineStr"/>
       <c r="I117" s="28" t="inlineStr"/>
@@ -7765,7 +7999,7 @@
     <row r="118">
       <c r="A118" s="28" t="inlineStr">
         <is>
-          <t>LEFLUNOMIDA 20 MG COMPRIMIDO</t>
+          <t>CARVEDILOL 12,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B118" s="28" t="inlineStr">
@@ -7774,19 +8008,19 @@
         </is>
       </c>
       <c r="C118" s="29" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="D118" s="29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="E118" s="29" t="n">
-        <v>1470.2</v>
+        <v>1721.2</v>
       </c>
       <c r="F118" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="29" t="n">
-        <v>12840</v>
+        <v>36390</v>
       </c>
       <c r="H118" s="28" t="inlineStr"/>
       <c r="I118" s="28" t="inlineStr"/>
@@ -7794,7 +8028,7 @@
     <row r="119">
       <c r="A119" s="28" t="inlineStr">
         <is>
-          <t>PREGABALINA 150 MG CAPSULA</t>
+          <t>DIVALPROATO SODICO CM 500 MG LIBRACION MODIFICADA</t>
         </is>
       </c>
       <c r="B119" s="28" t="inlineStr">
@@ -7803,19 +8037,19 @@
         </is>
       </c>
       <c r="C119" s="29" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="D119" s="29" t="n">
-        <v>15.6</v>
+        <v>5.9</v>
       </c>
       <c r="E119" s="29" t="n">
-        <v>1144.5</v>
+        <v>1756.4</v>
       </c>
       <c r="F119" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="29" t="n">
-        <v>5600</v>
+        <v>43600</v>
       </c>
       <c r="H119" s="28" t="inlineStr"/>
       <c r="I119" s="28" t="inlineStr"/>
@@ -7823,7 +8057,7 @@
     <row r="120">
       <c r="A120" s="28" t="inlineStr">
         <is>
-          <t>METILDOPA 250 MG COMPRIMIDO</t>
+          <t>HIDRALAZINA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B120" s="28" t="inlineStr">
@@ -7832,19 +8066,19 @@
         </is>
       </c>
       <c r="C120" s="29" t="n">
-        <v>2080</v>
+        <v>720</v>
       </c>
       <c r="D120" s="29" t="n">
-        <v>11.7</v>
+        <v>3.6</v>
       </c>
       <c r="E120" s="29" t="n">
-        <v>1480.3</v>
+        <v>1417</v>
       </c>
       <c r="F120" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G120" s="29" t="n">
-        <v>36000</v>
+        <v>53790</v>
       </c>
       <c r="H120" s="28" t="inlineStr"/>
       <c r="I120" s="28" t="inlineStr"/>
@@ -7852,7 +8086,7 @@
     <row r="121">
       <c r="A121" s="28" t="inlineStr">
         <is>
-          <t>MESALAZINA 500 MG COMPRIMIDO</t>
+          <t>METILFENIDATO 10 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B121" s="28" t="inlineStr">
@@ -7861,19 +8095,19 @@
         </is>
       </c>
       <c r="C121" s="29" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="D121" s="29" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="E121" s="29" t="n">
-        <v>1342.4</v>
+        <v>1608</v>
       </c>
       <c r="F121" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G121" s="29" t="n">
-        <v>9900</v>
+        <v>0</v>
       </c>
       <c r="H121" s="28" t="inlineStr"/>
       <c r="I121" s="28" t="inlineStr"/>
@@ -7881,7 +8115,7 @@
     <row r="122">
       <c r="A122" s="28" t="inlineStr">
         <is>
-          <t>RISPERIDONA CM 3 MG</t>
+          <t>LEFLUNOMIDA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B122" s="28" t="inlineStr">
@@ -7890,19 +8124,19 @@
         </is>
       </c>
       <c r="C122" s="29" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="D122" s="29" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="E122" s="29" t="n">
-        <v>1232.3</v>
+        <v>1470.2</v>
       </c>
       <c r="F122" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G122" s="29" t="n">
-        <v>19700</v>
+        <v>12840</v>
       </c>
       <c r="H122" s="28" t="inlineStr"/>
       <c r="I122" s="28" t="inlineStr"/>
@@ -7910,7 +8144,7 @@
     <row r="123">
       <c r="A123" s="28" t="inlineStr">
         <is>
-          <t>ARIPIPRAZOL 10 MG CM</t>
+          <t>PREGABALINA 150 MG CAPSULA</t>
         </is>
       </c>
       <c r="B123" s="28" t="inlineStr">
@@ -7919,19 +8153,19 @@
         </is>
       </c>
       <c r="C123" s="29" t="n">
-        <v>930</v>
+        <v>2800</v>
       </c>
       <c r="D123" s="29" t="n">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="E123" s="29" t="n">
-        <v>1360.4</v>
+        <v>1144.5</v>
       </c>
       <c r="F123" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="29" t="n">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="H123" s="28" t="inlineStr"/>
       <c r="I123" s="28" t="inlineStr"/>
@@ -7939,7 +8173,7 @@
     <row r="124">
       <c r="A124" s="28" t="inlineStr">
         <is>
-          <t>DULOXETINA 60 MG CAPSULA</t>
+          <t>METILDOPA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B124" s="28" t="inlineStr">
@@ -7948,19 +8182,19 @@
         </is>
       </c>
       <c r="C124" s="29" t="n">
-        <v>600</v>
+        <v>2100</v>
       </c>
       <c r="D124" s="29" t="n">
-        <v>3.7</v>
+        <v>11.8</v>
       </c>
       <c r="E124" s="29" t="n">
-        <v>912.2</v>
+        <v>1480.3</v>
       </c>
       <c r="F124" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G124" s="29" t="n">
-        <v>3810</v>
+        <v>36000</v>
       </c>
       <c r="H124" s="28" t="inlineStr"/>
       <c r="I124" s="28" t="inlineStr"/>
@@ -7968,7 +8202,7 @@
     <row r="125">
       <c r="A125" s="28" t="inlineStr">
         <is>
-          <t>ACIDO FOLICO CM 5 MG</t>
+          <t>MESALAZINA 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B125" s="28" t="inlineStr">
@@ -7977,19 +8211,19 @@
         </is>
       </c>
       <c r="C125" s="29" t="n">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="D125" s="29" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="E125" s="29" t="n">
-        <v>1429.6</v>
+        <v>1342.4</v>
       </c>
       <c r="F125" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="29" t="n">
-        <v>14890</v>
+        <v>9900</v>
       </c>
       <c r="H125" s="28" t="inlineStr"/>
       <c r="I125" s="28" t="inlineStr"/>
@@ -7997,7 +8231,7 @@
     <row r="126">
       <c r="A126" s="28" t="inlineStr">
         <is>
-          <t>AMLODIPINO 5 MG COMPRIMIDO</t>
+          <t>RISPERIDONA CM 3 MG</t>
         </is>
       </c>
       <c r="B126" s="28" t="inlineStr">
@@ -8006,19 +8240,19 @@
         </is>
       </c>
       <c r="C126" s="29" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="D126" s="29" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
       <c r="E126" s="29" t="n">
-        <v>1059.9</v>
+        <v>1232.3</v>
       </c>
       <c r="F126" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G126" s="29" t="n">
-        <v>12000</v>
+        <v>19700</v>
       </c>
       <c r="H126" s="28" t="inlineStr"/>
       <c r="I126" s="28" t="inlineStr"/>
@@ -8026,7 +8260,7 @@
     <row r="127">
       <c r="A127" s="28" t="inlineStr">
         <is>
-          <t>CLONAZEPAM CM 2 MG</t>
+          <t>ARIPIPRAZOL 10 MG CM</t>
         </is>
       </c>
       <c r="B127" s="28" t="inlineStr">
@@ -8035,13 +8269,13 @@
         </is>
       </c>
       <c r="C127" s="29" t="n">
-        <v>3600</v>
+        <v>930</v>
       </c>
       <c r="D127" s="29" t="n">
-        <v>24.8</v>
+        <v>5.6</v>
       </c>
       <c r="E127" s="29" t="n">
-        <v>1373.3</v>
+        <v>1360.4</v>
       </c>
       <c r="F127" s="29" t="n">
         <v>0</v>
@@ -8055,7 +8289,7 @@
     <row r="128">
       <c r="A128" s="28" t="inlineStr">
         <is>
-          <t>METFORMINA 850 MG COMPRIMIDO</t>
+          <t>ACIDO FOLICO CM 5 MG</t>
         </is>
       </c>
       <c r="B128" s="28" t="inlineStr">
@@ -8064,19 +8298,19 @@
         </is>
       </c>
       <c r="C128" s="29" t="n">
-        <v>2231</v>
+        <v>300</v>
       </c>
       <c r="D128" s="29" t="n">
-        <v>16</v>
+        <v>1.9</v>
       </c>
       <c r="E128" s="29" t="n">
-        <v>919.1</v>
+        <v>1429.6</v>
       </c>
       <c r="F128" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G128" s="29" t="n">
-        <v>32400</v>
+        <v>14890</v>
       </c>
       <c r="H128" s="28" t="inlineStr"/>
       <c r="I128" s="28" t="inlineStr"/>
@@ -8084,7 +8318,7 @@
     <row r="129">
       <c r="A129" s="28" t="inlineStr">
         <is>
-          <t>HIDROCLOROTIAZIDA 50 MG CM</t>
+          <t>AMLODIPINO 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B129" s="28" t="inlineStr">
@@ -8093,19 +8327,19 @@
         </is>
       </c>
       <c r="C129" s="29" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="D129" s="29" t="n">
-        <v>21.7</v>
+        <v>6.3</v>
       </c>
       <c r="E129" s="29" t="n">
-        <v>1109.4</v>
+        <v>1059.9</v>
       </c>
       <c r="F129" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G129" s="29" t="n">
-        <v>24000</v>
+        <v>12000</v>
       </c>
       <c r="H129" s="28" t="inlineStr"/>
       <c r="I129" s="28" t="inlineStr"/>
@@ -8113,7 +8347,7 @@
     <row r="130">
       <c r="A130" s="28" t="inlineStr">
         <is>
-          <t>TRAZODONA CM 100 MG</t>
+          <t>CLONAZEPAM CM 2 MG</t>
         </is>
       </c>
       <c r="B130" s="28" t="inlineStr">
@@ -8122,19 +8356,19 @@
         </is>
       </c>
       <c r="C130" s="29" t="n">
-        <v>400</v>
+        <v>3600</v>
       </c>
       <c r="D130" s="29" t="n">
-        <v>3.1</v>
+        <v>24.8</v>
       </c>
       <c r="E130" s="29" t="n">
-        <v>829.3</v>
+        <v>1373.3</v>
       </c>
       <c r="F130" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G130" s="29" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="H130" s="28" t="inlineStr"/>
       <c r="I130" s="28" t="inlineStr"/>
@@ -8142,7 +8376,7 @@
     <row r="131">
       <c r="A131" s="28" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG COMPRIMIDO</t>
+          <t>METFORMINA 850 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B131" s="28" t="inlineStr">
@@ -8151,19 +8385,19 @@
         </is>
       </c>
       <c r="C131" s="29" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="D131" s="29" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="E131" s="29" t="n">
-        <v>869.2</v>
+        <v>919.1</v>
       </c>
       <c r="F131" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G131" s="29" t="n">
-        <v>16700</v>
+        <v>32400</v>
       </c>
       <c r="H131" s="28" t="inlineStr"/>
       <c r="I131" s="28" t="inlineStr"/>
@@ -8171,7 +8405,7 @@
     <row r="132">
       <c r="A132" s="28" t="inlineStr">
         <is>
-          <t>TAMSULOSINA 400 MCG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>HIDROCLOROTIAZIDA 50 MG CM</t>
         </is>
       </c>
       <c r="B132" s="28" t="inlineStr">
@@ -8180,19 +8414,19 @@
         </is>
       </c>
       <c r="C132" s="29" t="n">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="D132" s="29" t="n">
-        <v>2.5</v>
+        <v>21.7</v>
       </c>
       <c r="E132" s="29" t="n">
-        <v>915.7</v>
+        <v>1109.4</v>
       </c>
       <c r="F132" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G132" s="29" t="n">
-        <v>9900</v>
+        <v>24000</v>
       </c>
       <c r="H132" s="28" t="inlineStr"/>
       <c r="I132" s="28" t="inlineStr"/>
@@ -8200,7 +8434,7 @@
     <row r="133">
       <c r="A133" s="28" t="inlineStr">
         <is>
-          <t>DESLORATADINA 5 MG COMPRIMIDO</t>
+          <t>RISPERIDONA 1 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B133" s="28" t="inlineStr">
@@ -8209,19 +8443,19 @@
         </is>
       </c>
       <c r="C133" s="29" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D133" s="29" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="E133" s="29" t="n">
-        <v>700.3</v>
+        <v>869.2</v>
       </c>
       <c r="F133" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G133" s="29" t="n">
-        <v>37000</v>
+        <v>16700</v>
       </c>
       <c r="H133" s="28" t="inlineStr"/>
       <c r="I133" s="28" t="inlineStr"/>
@@ -8229,7 +8463,7 @@
     <row r="134">
       <c r="A134" s="28" t="inlineStr">
         <is>
-          <t>ZOLPIDEM 10 MG COMPRIMIDO</t>
+          <t>TAMSULOSINA 400 MCG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B134" s="28" t="inlineStr">
@@ -8238,19 +8472,19 @@
         </is>
       </c>
       <c r="C134" s="29" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D134" s="29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E134" s="29" t="n">
-        <v>720.4</v>
+        <v>915.7</v>
       </c>
       <c r="F134" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="29" t="n">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="H134" s="28" t="inlineStr"/>
       <c r="I134" s="28" t="inlineStr"/>
@@ -8258,7 +8492,7 @@
     <row r="135">
       <c r="A135" s="28" t="inlineStr">
         <is>
-          <t>VENLAFAXINA 150 MG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>DESLORATADINA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B135" s="28" t="inlineStr">
@@ -8267,19 +8501,19 @@
         </is>
       </c>
       <c r="C135" s="29" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="D135" s="29" t="n">
-        <v>5.8</v>
+        <v>25.3</v>
       </c>
       <c r="E135" s="29" t="n">
-        <v>808.5</v>
+        <v>700.3</v>
       </c>
       <c r="F135" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G135" s="29" t="n">
-        <v>6990</v>
+        <v>37000</v>
       </c>
       <c r="H135" s="28" t="inlineStr"/>
       <c r="I135" s="28" t="inlineStr"/>
@@ -8287,7 +8521,7 @@
     <row r="136">
       <c r="A136" s="28" t="inlineStr">
         <is>
-          <t>DOMPERIDONA 10 MG CAPSULA</t>
+          <t>ZOLPIDEM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B136" s="28" t="inlineStr">
@@ -8296,19 +8530,19 @@
         </is>
       </c>
       <c r="C136" s="29" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="D136" s="29" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="E136" s="29" t="n">
-        <v>679.1</v>
+        <v>720.4</v>
       </c>
       <c r="F136" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G136" s="29" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="H136" s="28" t="inlineStr"/>
       <c r="I136" s="28" t="inlineStr"/>
@@ -8316,7 +8550,7 @@
     <row r="137">
       <c r="A137" s="28" t="inlineStr">
         <is>
-          <t>BICARBONATO DE SODIO CP. 500 M</t>
+          <t>VENLAFAXINA 150 MG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B137" s="28" t="inlineStr">
@@ -8325,19 +8559,19 @@
         </is>
       </c>
       <c r="C137" s="29" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D137" s="29" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="E137" s="29" t="n">
-        <v>457.5</v>
+        <v>808.5</v>
       </c>
       <c r="F137" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G137" s="29" t="n">
-        <v>1800</v>
+        <v>6990</v>
       </c>
       <c r="H137" s="28" t="inlineStr"/>
       <c r="I137" s="28" t="inlineStr"/>
@@ -8345,7 +8579,7 @@
     <row r="138">
       <c r="A138" s="28" t="inlineStr">
         <is>
-          <t>ESCITALOPRAM 10 MG COMPRIMIDO</t>
+          <t>DOMPERIDONA 10 MG CAPSULA</t>
         </is>
       </c>
       <c r="B138" s="28" t="inlineStr">
@@ -8354,19 +8588,19 @@
         </is>
       </c>
       <c r="C138" s="29" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="D138" s="29" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="E138" s="29" t="n">
-        <v>745</v>
+        <v>679.1</v>
       </c>
       <c r="F138" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G138" s="29" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="H138" s="28" t="inlineStr"/>
       <c r="I138" s="28" t="inlineStr"/>
@@ -8374,7 +8608,7 @@
     <row r="139">
       <c r="A139" s="28" t="inlineStr">
         <is>
-          <t>ACIDO URSODEOXICOLICO CM 250 MG</t>
+          <t>BICARBONATO DE SODIO CP. 500 M</t>
         </is>
       </c>
       <c r="B139" s="28" t="inlineStr">
@@ -8383,19 +8617,19 @@
         </is>
       </c>
       <c r="C139" s="29" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="D139" s="29" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="E139" s="29" t="n">
-        <v>568.5</v>
+        <v>457.5</v>
       </c>
       <c r="F139" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G139" s="29" t="n">
-        <v>4620</v>
+        <v>1800</v>
       </c>
       <c r="H139" s="28" t="inlineStr"/>
       <c r="I139" s="28" t="inlineStr"/>
@@ -8403,7 +8637,7 @@
     <row r="140">
       <c r="A140" s="28" t="inlineStr">
         <is>
-          <t>CARBAMAZEPINA 200 MG COMPRIMIDO</t>
+          <t>ESCITALOPRAM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B140" s="28" t="inlineStr">
@@ -8412,19 +8646,19 @@
         </is>
       </c>
       <c r="C140" s="29" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="D140" s="29" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="E140" s="29" t="n">
-        <v>647.2</v>
+        <v>745</v>
       </c>
       <c r="F140" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G140" s="29" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H140" s="28" t="inlineStr"/>
       <c r="I140" s="28" t="inlineStr"/>
@@ -8432,7 +8666,7 @@
     <row r="141">
       <c r="A141" s="28" t="inlineStr">
         <is>
-          <t>HIDROCLOROTIAZIDA 25 MG + TRIAMTERENO 50 MG COMPRIMIDO</t>
+          <t>ACIDO URSODEOXICOLICO CM 250 MG</t>
         </is>
       </c>
       <c r="B141" s="28" t="inlineStr">
@@ -8441,19 +8675,19 @@
         </is>
       </c>
       <c r="C141" s="29" t="n">
-        <v>180</v>
+        <v>660</v>
       </c>
       <c r="D141" s="29" t="n">
-        <v>2.1</v>
+        <v>6.7</v>
       </c>
       <c r="E141" s="29" t="n">
-        <v>552</v>
+        <v>568.5</v>
       </c>
       <c r="F141" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G141" s="29" t="n">
-        <v>15060</v>
+        <v>4620</v>
       </c>
       <c r="H141" s="28" t="inlineStr"/>
       <c r="I141" s="28" t="inlineStr"/>
@@ -8461,7 +8695,7 @@
     <row r="142">
       <c r="A142" s="28" t="inlineStr">
         <is>
-          <t>AMIODARONA 200 MG COMPRIMIDO</t>
+          <t>CARBAMAZEPINA 200 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B142" s="28" t="inlineStr">
@@ -8470,19 +8704,19 @@
         </is>
       </c>
       <c r="C142" s="29" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="D142" s="29" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="E142" s="29" t="n">
-        <v>474.5</v>
+        <v>647.2</v>
       </c>
       <c r="F142" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G142" s="29" t="n">
-        <v>10050</v>
+        <v>0</v>
       </c>
       <c r="H142" s="28" t="inlineStr"/>
       <c r="I142" s="28" t="inlineStr"/>
@@ -8490,7 +8724,7 @@
     <row r="143">
       <c r="A143" s="28" t="inlineStr">
         <is>
-          <t>ESZOPICLONA 3 MG COMPRIMIDO</t>
+          <t>HIDROCLOROTIAZIDA 25 MG + TRIAMTERENO 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B143" s="28" t="inlineStr">
@@ -8499,19 +8733,19 @@
         </is>
       </c>
       <c r="C143" s="29" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="D143" s="29" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="E143" s="29" t="n">
-        <v>508.2</v>
+        <v>552</v>
       </c>
       <c r="F143" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G143" s="29" t="n">
-        <v>1680</v>
+        <v>15060</v>
       </c>
       <c r="H143" s="28" t="inlineStr"/>
       <c r="I143" s="28" t="inlineStr"/>
@@ -8519,7 +8753,7 @@
     <row r="144">
       <c r="A144" s="28" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10 MG COMPRIMIDO</t>
+          <t>AMIODARONA 200 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B144" s="28" t="inlineStr">
@@ -8528,19 +8762,19 @@
         </is>
       </c>
       <c r="C144" s="29" t="n">
-        <v>1224</v>
+        <v>0</v>
       </c>
       <c r="D144" s="29" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="E144" s="29" t="n">
-        <v>217.9</v>
+        <v>474.5</v>
       </c>
       <c r="F144" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G144" s="29" t="n">
-        <v>5832</v>
+        <v>10050</v>
       </c>
       <c r="H144" s="28" t="inlineStr"/>
       <c r="I144" s="28" t="inlineStr"/>
@@ -8548,7 +8782,7 @@
     <row r="145">
       <c r="A145" s="28" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2 MG COMPRIMIDO</t>
+          <t>ESZOPICLONA 3 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B145" s="28" t="inlineStr">
@@ -8557,19 +8791,19 @@
         </is>
       </c>
       <c r="C145" s="29" t="n">
-        <v>540</v>
+        <v>300</v>
       </c>
       <c r="D145" s="29" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="E145" s="29" t="n">
-        <v>385.2</v>
+        <v>508.2</v>
       </c>
       <c r="F145" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G145" s="29" t="n">
-        <v>1560</v>
+        <v>1680</v>
       </c>
       <c r="H145" s="28" t="inlineStr"/>
       <c r="I145" s="28" t="inlineStr"/>
@@ -8577,7 +8811,7 @@
     <row r="146">
       <c r="A146" s="28" t="inlineStr">
         <is>
-          <t>TRIHEXIFENIDILO CM 2 MG</t>
+          <t>METOCLOPRAMIDA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B146" s="28" t="inlineStr">
@@ -8586,19 +8820,19 @@
         </is>
       </c>
       <c r="C146" s="29" t="n">
-        <v>0</v>
+        <v>1224</v>
       </c>
       <c r="D146" s="29" t="n">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="E146" s="29" t="n">
-        <v>537.9</v>
+        <v>217.9</v>
       </c>
       <c r="F146" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G146" s="29" t="n">
-        <v>800</v>
+        <v>5832</v>
       </c>
       <c r="H146" s="28" t="inlineStr"/>
       <c r="I146" s="28" t="inlineStr"/>
@@ -8606,7 +8840,7 @@
     <row r="147">
       <c r="A147" s="28" t="inlineStr">
         <is>
-          <t>ALOPURINOL 300 MG COMPRIMIDO</t>
+          <t>LOPERAMIDA 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B147" s="28" t="inlineStr">
@@ -8615,19 +8849,19 @@
         </is>
       </c>
       <c r="C147" s="29" t="n">
-        <v>400</v>
+        <v>540</v>
       </c>
       <c r="D147" s="29" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="E147" s="29" t="n">
-        <v>462.2</v>
+        <v>385.2</v>
       </c>
       <c r="F147" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G147" s="29" t="n">
-        <v>5800</v>
+        <v>1560</v>
       </c>
       <c r="H147" s="28" t="inlineStr"/>
       <c r="I147" s="28" t="inlineStr"/>
@@ -8635,7 +8869,7 @@
     <row r="148">
       <c r="A148" s="28" t="inlineStr">
         <is>
-          <t>CARBONATO DE LITIO 300 MG CM</t>
+          <t>TRIHEXIFENIDILO CM 2 MG</t>
         </is>
       </c>
       <c r="B148" s="28" t="inlineStr">
@@ -8644,19 +8878,19 @@
         </is>
       </c>
       <c r="C148" s="29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D148" s="29" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E148" s="29" t="n">
-        <v>328.2</v>
+        <v>537.9</v>
       </c>
       <c r="F148" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G148" s="29" t="n">
-        <v>5450</v>
+        <v>800</v>
       </c>
       <c r="H148" s="28" t="inlineStr"/>
       <c r="I148" s="28" t="inlineStr"/>
@@ -8664,7 +8898,7 @@
     <row r="149">
       <c r="A149" s="28" t="inlineStr">
         <is>
-          <t>ACIDO VALPROICO 200 MG COMPRIMIDO</t>
+          <t>ALOPURINOL 300 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B149" s="28" t="inlineStr">
@@ -8673,19 +8907,19 @@
         </is>
       </c>
       <c r="C149" s="29" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D149" s="29" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="E149" s="29" t="n">
-        <v>660.5</v>
+        <v>462.2</v>
       </c>
       <c r="F149" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G149" s="29" t="n">
-        <v>1200</v>
+        <v>5800</v>
       </c>
       <c r="H149" s="28" t="inlineStr"/>
       <c r="I149" s="28" t="inlineStr"/>
@@ -8693,7 +8927,7 @@
     <row r="150">
       <c r="A150" s="28" t="inlineStr">
         <is>
-          <t>LEVETIRACETAM 1000 MG COMPRIMIDO</t>
+          <t>CARBONATO DE LITIO 300 MG CM</t>
         </is>
       </c>
       <c r="B150" s="28" t="inlineStr">
@@ -8702,19 +8936,19 @@
         </is>
       </c>
       <c r="C150" s="29" t="n">
-        <v>690</v>
+        <v>1000</v>
       </c>
       <c r="D150" s="29" t="n">
-        <v>9.9</v>
+        <v>14.3</v>
       </c>
       <c r="E150" s="29" t="n">
-        <v>550.7</v>
+        <v>328.2</v>
       </c>
       <c r="F150" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G150" s="29" t="n">
-        <v>210</v>
+        <v>5450</v>
       </c>
       <c r="H150" s="28" t="inlineStr"/>
       <c r="I150" s="28" t="inlineStr"/>
@@ -8722,7 +8956,7 @@
     <row r="151">
       <c r="A151" s="28" t="inlineStr">
         <is>
-          <t>CARVEDILOL 25 MG COMPRIMIDO</t>
+          <t>ACIDO VALPROICO 200 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B151" s="28" t="inlineStr">
@@ -8737,13 +8971,13 @@
         <v>0</v>
       </c>
       <c r="E151" s="29" t="n">
-        <v>371.2</v>
+        <v>660.5</v>
       </c>
       <c r="F151" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G151" s="29" t="n">
-        <v>9390</v>
+        <v>1200</v>
       </c>
       <c r="H151" s="28" t="inlineStr"/>
       <c r="I151" s="28" t="inlineStr"/>
@@ -8751,7 +8985,7 @@
     <row r="152">
       <c r="A152" s="28" t="inlineStr">
         <is>
-          <t>ACIDO VALPROICO 250 MG COMPRIMIDO</t>
+          <t>LEVETIRACETAM 1000 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B152" s="28" t="inlineStr">
@@ -8760,19 +8994,19 @@
         </is>
       </c>
       <c r="C152" s="29" t="n">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="D152" s="29" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="E152" s="29" t="n">
-        <v>498.1</v>
+        <v>550.7</v>
       </c>
       <c r="F152" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G152" s="29" t="n">
-        <v>9720</v>
+        <v>210</v>
       </c>
       <c r="H152" s="28" t="inlineStr"/>
       <c r="I152" s="28" t="inlineStr"/>
@@ -8780,7 +9014,7 @@
     <row r="153">
       <c r="A153" s="28" t="inlineStr">
         <is>
-          <t>INDOMETACINA 25 MG COMPRIMIDO</t>
+          <t>CARVEDILOL 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B153" s="28" t="inlineStr">
@@ -8795,13 +9029,13 @@
         <v>0</v>
       </c>
       <c r="E153" s="29" t="n">
-        <v>222.6</v>
+        <v>371.2</v>
       </c>
       <c r="F153" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G153" s="29" t="n">
-        <v>1500</v>
+        <v>9390</v>
       </c>
       <c r="H153" s="28" t="inlineStr"/>
       <c r="I153" s="28" t="inlineStr"/>
@@ -8809,7 +9043,7 @@
     <row r="154">
       <c r="A154" s="28" t="inlineStr">
         <is>
-          <t>TOLTERODINA CM 2 MG</t>
+          <t>ACIDO VALPROICO 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B154" s="28" t="inlineStr">
@@ -8824,13 +9058,13 @@
         <v>0</v>
       </c>
       <c r="E154" s="29" t="n">
-        <v>473</v>
+        <v>498.1</v>
       </c>
       <c r="F154" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G154" s="29" t="n">
-        <v>2100</v>
+        <v>9720</v>
       </c>
       <c r="H154" s="28" t="inlineStr"/>
       <c r="I154" s="28" t="inlineStr"/>
@@ -8838,7 +9072,7 @@
     <row r="155">
       <c r="A155" s="28" t="inlineStr">
         <is>
-          <t>TAPENTADOL 50 MG CM LIBERACION MODIFICADA</t>
+          <t>INDOMETACINA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B155" s="28" t="inlineStr">
@@ -8853,13 +9087,13 @@
         <v>0</v>
       </c>
       <c r="E155" s="29" t="n">
-        <v>364.5</v>
+        <v>222.6</v>
       </c>
       <c r="F155" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G155" s="29" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H155" s="28" t="inlineStr"/>
       <c r="I155" s="28" t="inlineStr"/>
@@ -8867,7 +9101,7 @@
     <row r="156">
       <c r="A156" s="28" t="inlineStr">
         <is>
-          <t>LEVETIRACETAM 500 MG COMPRIMIDO</t>
+          <t>TOLTERODINA CM 2 MG</t>
         </is>
       </c>
       <c r="B156" s="28" t="inlineStr">
@@ -8876,19 +9110,19 @@
         </is>
       </c>
       <c r="C156" s="29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D156" s="29" t="n">
-        <v>16.6</v>
+        <v>0</v>
       </c>
       <c r="E156" s="29" t="n">
-        <v>385.2</v>
+        <v>473</v>
       </c>
       <c r="F156" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G156" s="29" t="n">
-        <v>6760</v>
+        <v>2100</v>
       </c>
       <c r="H156" s="28" t="inlineStr"/>
       <c r="I156" s="28" t="inlineStr"/>
@@ -8896,7 +9130,7 @@
     <row r="157">
       <c r="A157" s="28" t="inlineStr">
         <is>
-          <t>LAMOTRIGINA 50 MG COMPRIMIDO</t>
+          <t>TAPENTADOL 50 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B157" s="28" t="inlineStr">
@@ -8905,19 +9139,19 @@
         </is>
       </c>
       <c r="C157" s="29" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="D157" s="29" t="n">
-        <v>27.4</v>
+        <v>0</v>
       </c>
       <c r="E157" s="29" t="n">
-        <v>595</v>
+        <v>364.5</v>
       </c>
       <c r="F157" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G157" s="29" t="n">
-        <v>10400</v>
+        <v>0</v>
       </c>
       <c r="H157" s="28" t="inlineStr"/>
       <c r="I157" s="28" t="inlineStr"/>
@@ -8925,7 +9159,7 @@
     <row r="158">
       <c r="A158" s="28" t="inlineStr">
         <is>
-          <t>PROPANOLOL 40 MG COMPRIMIDO</t>
+          <t>LEVETIRACETAM 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B158" s="28" t="inlineStr">
@@ -8937,16 +9171,16 @@
         <v>1000</v>
       </c>
       <c r="D158" s="29" t="n">
-        <v>17.3</v>
+        <v>16.6</v>
       </c>
       <c r="E158" s="29" t="n">
-        <v>416.2</v>
+        <v>385.2</v>
       </c>
       <c r="F158" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G158" s="29" t="n">
-        <v>7000</v>
+        <v>6760</v>
       </c>
       <c r="H158" s="28" t="inlineStr"/>
       <c r="I158" s="28" t="inlineStr"/>
@@ -8954,7 +9188,7 @@
     <row r="159">
       <c r="A159" s="28" t="inlineStr">
         <is>
-          <t>DUTASTERIDA 500 MCG + TAMSULOSINA 400 MCG CAPSULA LIBERACION MODIFICADA</t>
+          <t>LAMOTRIGINA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B159" s="28" t="inlineStr">
@@ -8963,19 +9197,19 @@
         </is>
       </c>
       <c r="C159" s="29" t="n">
-        <v>270</v>
+        <v>1600</v>
       </c>
       <c r="D159" s="29" t="n">
-        <v>4.8</v>
+        <v>27.4</v>
       </c>
       <c r="E159" s="29" t="n">
-        <v>364.1</v>
+        <v>595</v>
       </c>
       <c r="F159" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G159" s="29" t="n">
-        <v>6030</v>
+        <v>10400</v>
       </c>
       <c r="H159" s="28" t="inlineStr"/>
       <c r="I159" s="28" t="inlineStr"/>
@@ -8983,7 +9217,7 @@
     <row r="160">
       <c r="A160" s="28" t="inlineStr">
         <is>
-          <t>BETAHISTINA 16 MG COMPRIMIDO</t>
+          <t>PROPANOLOL 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B160" s="28" t="inlineStr">
@@ -8992,19 +9226,19 @@
         </is>
       </c>
       <c r="C160" s="29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D160" s="29" t="n">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="E160" s="29" t="n">
-        <v>243.5</v>
+        <v>416.2</v>
       </c>
       <c r="F160" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G160" s="29" t="n">
-        <v>5224</v>
+        <v>7000</v>
       </c>
       <c r="H160" s="28" t="inlineStr"/>
       <c r="I160" s="28" t="inlineStr"/>
@@ -9012,7 +9246,7 @@
     <row r="161">
       <c r="A161" s="28" t="inlineStr">
         <is>
-          <t>AZATIOPRINA 50 MG COMPRIMIDO</t>
+          <t>DUTASTERIDA 500 MCG + TAMSULOSINA 400 MCG CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B161" s="28" t="inlineStr">
@@ -9021,19 +9255,19 @@
         </is>
       </c>
       <c r="C161" s="29" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="D161" s="29" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="E161" s="29" t="n">
-        <v>431.8</v>
+        <v>364.1</v>
       </c>
       <c r="F161" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G161" s="29" t="n">
-        <v>23700</v>
+        <v>6030</v>
       </c>
       <c r="H161" s="28" t="inlineStr"/>
       <c r="I161" s="28" t="inlineStr"/>
@@ -9041,7 +9275,7 @@
     <row r="162">
       <c r="A162" s="28" t="inlineStr">
         <is>
-          <t>TIAMAZOL 10 MG COMPRIMIDO</t>
+          <t>BETAHISTINA 16 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B162" s="28" t="inlineStr">
@@ -9050,19 +9284,19 @@
         </is>
       </c>
       <c r="C162" s="29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D162" s="29" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="E162" s="29" t="n">
-        <v>430.8</v>
+        <v>243.5</v>
       </c>
       <c r="F162" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G162" s="29" t="n">
-        <v>2900</v>
+        <v>5224</v>
       </c>
       <c r="H162" s="28" t="inlineStr"/>
       <c r="I162" s="28" t="inlineStr"/>
@@ -9070,7 +9304,7 @@
     <row r="163">
       <c r="A163" s="28" t="inlineStr">
         <is>
-          <t>ALOPURINOL 100 MG COMPRIMIDO</t>
+          <t>AZATIOPRINA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B163" s="28" t="inlineStr">
@@ -9079,19 +9313,19 @@
         </is>
       </c>
       <c r="C163" s="29" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D163" s="29" t="n">
-        <v>11.2</v>
+        <v>9</v>
       </c>
       <c r="E163" s="29" t="n">
-        <v>296</v>
+        <v>431.8</v>
       </c>
       <c r="F163" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G163" s="29" t="n">
-        <v>6600</v>
+        <v>23700</v>
       </c>
       <c r="H163" s="28" t="inlineStr"/>
       <c r="I163" s="28" t="inlineStr"/>
@@ -9099,7 +9333,7 @@
     <row r="164">
       <c r="A164" s="28" t="inlineStr">
         <is>
-          <t>OXIBUTININA 5 MG COMPRIMIDO</t>
+          <t>TIAMAZOL 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B164" s="28" t="inlineStr">
@@ -9108,19 +9342,19 @@
         </is>
       </c>
       <c r="C164" s="29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D164" s="29" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="E164" s="29" t="n">
-        <v>352</v>
+        <v>430.8</v>
       </c>
       <c r="F164" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G164" s="29" t="n">
-        <v>11950</v>
+        <v>2900</v>
       </c>
       <c r="H164" s="28" t="inlineStr"/>
       <c r="I164" s="28" t="inlineStr"/>
@@ -9128,7 +9362,7 @@
     <row r="165">
       <c r="A165" s="28" t="inlineStr">
         <is>
-          <t>PAROXETINA 20 MG COMPRIMIDO</t>
+          <t>ALOPURINOL 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B165" s="28" t="inlineStr">
@@ -9137,19 +9371,19 @@
         </is>
       </c>
       <c r="C165" s="29" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="D165" s="29" t="n">
-        <v>20.1</v>
+        <v>11.2</v>
       </c>
       <c r="E165" s="29" t="n">
-        <v>345.8</v>
+        <v>296</v>
       </c>
       <c r="F165" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G165" s="29" t="n">
-        <v>13000</v>
+        <v>6600</v>
       </c>
       <c r="H165" s="28" t="inlineStr"/>
       <c r="I165" s="28" t="inlineStr"/>
@@ -9157,7 +9391,7 @@
     <row r="166">
       <c r="A166" s="28" t="inlineStr">
         <is>
-          <t>TRAZODONA CLORHIDRATO 25 MG CM</t>
+          <t>OXIBUTININA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B166" s="28" t="inlineStr">
@@ -9166,19 +9400,19 @@
         </is>
       </c>
       <c r="C166" s="29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D166" s="29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="E166" s="29" t="n">
-        <v>331.5</v>
+        <v>352</v>
       </c>
       <c r="F166" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G166" s="29" t="n">
-        <v>2400</v>
+        <v>11950</v>
       </c>
       <c r="H166" s="28" t="inlineStr"/>
       <c r="I166" s="28" t="inlineStr"/>
@@ -9186,7 +9420,7 @@
     <row r="167">
       <c r="A167" s="28" t="inlineStr">
         <is>
-          <t>SULFASALAZINA 500 MG COMPRIMIDO</t>
+          <t>PAROXETINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B167" s="28" t="inlineStr">
@@ -9195,19 +9429,19 @@
         </is>
       </c>
       <c r="C167" s="29" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D167" s="29" t="n">
-        <v>10.7</v>
+        <v>20.1</v>
       </c>
       <c r="E167" s="29" t="n">
-        <v>501.5</v>
+        <v>345.8</v>
       </c>
       <c r="F167" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G167" s="29" t="n">
-        <v>8300</v>
+        <v>13000</v>
       </c>
       <c r="H167" s="28" t="inlineStr"/>
       <c r="I167" s="28" t="inlineStr"/>
@@ -9215,7 +9449,7 @@
     <row r="168">
       <c r="A168" s="28" t="inlineStr">
         <is>
-          <t>DONEPEZILO 10 MG COMPRIMIDO</t>
+          <t>TRAZODONA CLORHIDRATO 25 MG CM</t>
         </is>
       </c>
       <c r="B168" s="28" t="inlineStr">
@@ -9224,19 +9458,19 @@
         </is>
       </c>
       <c r="C168" s="29" t="n">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="D168" s="29" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="E168" s="29" t="n">
-        <v>206.2</v>
+        <v>331.5</v>
       </c>
       <c r="F168" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G168" s="29" t="n">
-        <v>1890</v>
+        <v>2400</v>
       </c>
       <c r="H168" s="28" t="inlineStr"/>
       <c r="I168" s="28" t="inlineStr"/>
@@ -9244,7 +9478,7 @@
     <row r="169">
       <c r="A169" s="28" t="inlineStr">
         <is>
-          <t>NAPROXENO 550 MG COMPRIMIDO</t>
+          <t>SULFASALAZINA 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B169" s="28" t="inlineStr">
@@ -9253,19 +9487,19 @@
         </is>
       </c>
       <c r="C169" s="29" t="n">
-        <v>2900</v>
+        <v>500</v>
       </c>
       <c r="D169" s="29" t="n">
-        <v>62.5</v>
+        <v>10.7</v>
       </c>
       <c r="E169" s="29" t="n">
-        <v>276.4</v>
+        <v>501.5</v>
       </c>
       <c r="F169" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G169" s="29" t="n">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="H169" s="28" t="inlineStr"/>
       <c r="I169" s="28" t="inlineStr"/>
@@ -9273,7 +9507,7 @@
     <row r="170">
       <c r="A170" s="28" t="inlineStr">
         <is>
-          <t>PROPANOLOL 10 MG COMPRIMIDO</t>
+          <t>DONEPEZILO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B170" s="28" t="inlineStr">
@@ -9282,19 +9516,19 @@
         </is>
       </c>
       <c r="C170" s="29" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="D170" s="29" t="n">
-        <v>22.4</v>
+        <v>4.5</v>
       </c>
       <c r="E170" s="29" t="n">
-        <v>326.7</v>
+        <v>206.2</v>
       </c>
       <c r="F170" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G170" s="29" t="n">
-        <v>5000</v>
+        <v>1890</v>
       </c>
       <c r="H170" s="28" t="inlineStr"/>
       <c r="I170" s="28" t="inlineStr"/>
@@ -9302,7 +9536,7 @@
     <row r="171">
       <c r="A171" s="28" t="inlineStr">
         <is>
-          <t>MIRTAZAPINA 15 MG COMPRIMIDO</t>
+          <t>NAPROXENO 550 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B171" s="28" t="inlineStr">
@@ -9311,19 +9545,19 @@
         </is>
       </c>
       <c r="C171" s="29" t="n">
-        <v>300</v>
+        <v>2900</v>
       </c>
       <c r="D171" s="29" t="n">
-        <v>6.8</v>
+        <v>62.5</v>
       </c>
       <c r="E171" s="29" t="n">
-        <v>342</v>
+        <v>276.4</v>
       </c>
       <c r="F171" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G171" s="29" t="n">
-        <v>7020</v>
+        <v>0</v>
       </c>
       <c r="H171" s="28" t="inlineStr"/>
       <c r="I171" s="28" t="inlineStr"/>
@@ -9331,7 +9565,7 @@
     <row r="172">
       <c r="A172" s="28" t="inlineStr">
         <is>
-          <t>ACIDO FOLICO CM 1 MG</t>
+          <t>PROPANOLOL 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B172" s="28" t="inlineStr">
@@ -9340,19 +9574,19 @@
         </is>
       </c>
       <c r="C172" s="29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D172" s="29" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="E172" s="29" t="n">
-        <v>300.7</v>
+        <v>326.7</v>
       </c>
       <c r="F172" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G172" s="29" t="n">
-        <v>13640</v>
+        <v>5000</v>
       </c>
       <c r="H172" s="28" t="inlineStr"/>
       <c r="I172" s="28" t="inlineStr"/>
@@ -9360,7 +9594,7 @@
     <row r="173">
       <c r="A173" s="28" t="inlineStr">
         <is>
-          <t>DIAZEPAM 10 MG COMPRIMIDO</t>
+          <t>MIRTAZAPINA 15 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B173" s="28" t="inlineStr">
@@ -9369,19 +9603,19 @@
         </is>
       </c>
       <c r="C173" s="29" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D173" s="29" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="E173" s="29" t="n">
-        <v>232.1</v>
+        <v>342</v>
       </c>
       <c r="F173" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G173" s="29" t="n">
-        <v>0</v>
+        <v>7020</v>
       </c>
       <c r="H173" s="28" t="inlineStr"/>
       <c r="I173" s="28" t="inlineStr"/>
@@ -9389,7 +9623,7 @@
     <row r="174">
       <c r="A174" s="28" t="inlineStr">
         <is>
-          <t>BISOPROLOL 5 MG COMPRIMIDO</t>
+          <t>ACIDO FOLICO CM 1 MG</t>
         </is>
       </c>
       <c r="B174" s="28" t="inlineStr">
@@ -9404,13 +9638,13 @@
         <v>0</v>
       </c>
       <c r="E174" s="29" t="n">
-        <v>250.3</v>
+        <v>300.7</v>
       </c>
       <c r="F174" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G174" s="29" t="n">
-        <v>0</v>
+        <v>13640</v>
       </c>
       <c r="H174" s="28" t="inlineStr"/>
       <c r="I174" s="28" t="inlineStr"/>
@@ -9418,7 +9652,7 @@
     <row r="175">
       <c r="A175" s="28" t="inlineStr">
         <is>
-          <t>TOPIRAMATO 50 MG CM</t>
+          <t>DIAZEPAM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B175" s="28" t="inlineStr">
@@ -9433,13 +9667,13 @@
         <v>0</v>
       </c>
       <c r="E175" s="29" t="n">
-        <v>220.3</v>
+        <v>232.1</v>
       </c>
       <c r="F175" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G175" s="29" t="n">
-        <v>2760</v>
+        <v>0</v>
       </c>
       <c r="H175" s="28" t="inlineStr"/>
       <c r="I175" s="28" t="inlineStr"/>
@@ -9447,7 +9681,7 @@
     <row r="176">
       <c r="A176" s="28" t="inlineStr">
         <is>
-          <t>LORAZEPAM 2 MG COMPRIMIDO</t>
+          <t>TOPIRAMATO 50 MG CM</t>
         </is>
       </c>
       <c r="B176" s="28" t="inlineStr">
@@ -9456,19 +9690,19 @@
         </is>
       </c>
       <c r="C176" s="29" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D176" s="29" t="n">
-        <v>71.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="E176" s="29" t="n">
-        <v>306.6</v>
+        <v>220.3</v>
       </c>
       <c r="F176" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G176" s="29" t="n">
-        <v>0</v>
+        <v>2760</v>
       </c>
       <c r="H176" s="28" t="inlineStr"/>
       <c r="I176" s="28" t="inlineStr"/>
@@ -9476,7 +9710,7 @@
     <row r="177">
       <c r="A177" s="28" t="inlineStr">
         <is>
-          <t>COLCHICINA 0,5 MG COMPRIMIDO</t>
+          <t>LORAZEPAM 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B177" s="28" t="inlineStr">
@@ -9485,19 +9719,19 @@
         </is>
       </c>
       <c r="C177" s="29" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D177" s="29" t="n">
-        <v>0</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E177" s="29" t="n">
-        <v>177</v>
+        <v>306.6</v>
       </c>
       <c r="F177" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G177" s="29" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="H177" s="28" t="inlineStr"/>
       <c r="I177" s="28" t="inlineStr"/>
@@ -9505,7 +9739,7 @@
     <row r="178">
       <c r="A178" s="28" t="inlineStr">
         <is>
-          <t>PIRIDOSTIGMINA 60 MG COMPRIMIDOS O GRAGEAS.</t>
+          <t>COLCHICINA 0,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B178" s="28" t="inlineStr">
@@ -9520,13 +9754,13 @@
         <v>0</v>
       </c>
       <c r="E178" s="29" t="n">
-        <v>73.90000000000001</v>
+        <v>177</v>
       </c>
       <c r="F178" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G178" s="29" t="n">
-        <v>1100</v>
+        <v>2400</v>
       </c>
       <c r="H178" s="28" t="inlineStr"/>
       <c r="I178" s="28" t="inlineStr"/>
@@ -9534,7 +9768,7 @@
     <row r="179">
       <c r="A179" s="28" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200 MG CM /CR</t>
+          <t>PIRIDOSTIGMINA 60 MG COMPRIMIDOS O GRAGEAS.</t>
         </is>
       </c>
       <c r="B179" s="28" t="inlineStr">
@@ -9549,13 +9783,13 @@
         <v>0</v>
       </c>
       <c r="E179" s="29" t="n">
-        <v>315.4</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F179" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G179" s="29" t="n">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H179" s="28" t="inlineStr"/>
       <c r="I179" s="28" t="inlineStr"/>
@@ -10993,10 +11227,10 @@
         </is>
       </c>
       <c r="C229" s="29" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D229" s="29" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="E229" s="29" t="n">
         <v>88.40000000000001</v>
@@ -12037,10 +12271,10 @@
         </is>
       </c>
       <c r="C265" s="29" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D265" s="29" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="E265" s="29" t="n">
         <v>22.2</v>
@@ -13313,10 +13547,10 @@
         </is>
       </c>
       <c r="C309" s="29" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D309" s="29" t="n">
-        <v>105.2</v>
+        <v>104.1</v>
       </c>
       <c r="E309" s="29" t="n">
         <v>0</v>
@@ -16855,7 +17089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -17128,7 +17362,7 @@
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
+          <t>ACETATO DE CALCIO 667 MG CM UD</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
@@ -17143,22 +17377,22 @@
         <v>0</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>103.2</v>
+        <v>730.2</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>1.6</v>
+        <v>198.5</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>130.6</v>
+        <v>146</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>104</v>
+        <v>487</v>
       </c>
       <c r="I7" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="21" t="n">
-        <v>104</v>
+        <v>487</v>
       </c>
       <c r="K7" s="20" t="inlineStr">
         <is>
@@ -17167,14 +17401,14 @@
       </c>
       <c r="L7" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 104 ud.</t>
+          <t>GESTIONAR EXTERNO 487 ud.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
@@ -17189,22 +17423,22 @@
         <v>0</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>37.7</v>
+        <v>103.2</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>48.5</v>
+        <v>130.6</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="I8" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="21" t="n">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="K8" s="20" t="inlineStr">
         <is>
@@ -17213,14 +17447,14 @@
       </c>
       <c r="L8" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 38 ud.</t>
+          <t>GESTIONAR EXTERNO 104 ud.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -17235,22 +17469,22 @@
         <v>0</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>11.7</v>
+        <v>37.7</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>35.3</v>
+        <v>1.8</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>11.8</v>
+        <v>48.5</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="I9" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="21" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="K9" s="20" t="inlineStr">
         <is>
@@ -17259,14 +17493,14 @@
       </c>
       <c r="L9" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
+          <t>GESTIONAR EXTERNO 38 ud.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -17281,13 +17515,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>16.5</v>
+        <v>11.7</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>38.2</v>
+        <v>35.3</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>100</v>
@@ -17312,7 +17546,7 @@
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -17327,22 +17561,22 @@
         <v>0</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>31.8</v>
+        <v>16.5</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>4.4</v>
+        <v>38.2</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="I11" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="21" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="K11" s="20" t="inlineStr">
         <is>
@@ -17351,14 +17585,14 @@
       </c>
       <c r="L11" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 32 ud.</t>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -17373,22 +17607,22 @@
         <v>0</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>12.8</v>
+        <v>31.8</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>13.5</v>
+        <v>26.5</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I12" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="K12" s="20" t="inlineStr">
         <is>
@@ -17397,14 +17631,14 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 13 ud.</t>
+          <t>GESTIONAR EXTERNO 32 ud.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -17419,22 +17653,22 @@
         <v>0</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>2.3</v>
+        <v>11.9</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>2.8</v>
+        <v>10.9</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>8.699999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I13" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K13" s="20" t="inlineStr">
         <is>
@@ -17443,14 +17677,14 @@
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3 ud.</t>
+          <t>GESTIONAR EXTERNO 12 ud.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
@@ -17465,22 +17699,22 @@
         <v>0</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>0.7</v>
+        <v>12.8</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>0.7</v>
+        <v>13.5</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I14" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K14" s="20" t="inlineStr">
         <is>
@@ -17489,14 +17723,14 @@
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 13 ud.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -17511,22 +17745,22 @@
         <v>0</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" s="20" t="inlineStr">
         <is>
@@ -17535,14 +17769,14 @@
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 3 ud.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>ALTEPLASA 50 MG FA UD</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -17557,13 +17791,13 @@
         <v>0</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>1</v>
@@ -17586,97 +17820,101 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="n">
-        <v>936</v>
-      </c>
-      <c r="D17" s="23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E17" s="23" t="n">
-        <v>2304.4</v>
-      </c>
-      <c r="F17" s="23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G17" s="23" t="n">
-        <v>3147.1</v>
-      </c>
-      <c r="H17" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="I17" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="J17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 12 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L17" s="22" t="inlineStr"/>
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="n">
-        <v>116</v>
-      </c>
-      <c r="D18" s="23" t="n">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>ALTEPLASA 50 MG FA UD</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="E18" s="23" t="n">
-        <v>1202.2</v>
-      </c>
-      <c r="F18" s="23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>1299</v>
-      </c>
-      <c r="H18" s="23" t="n">
-        <v>337</v>
-      </c>
-      <c r="I18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="23" t="n">
-        <v>337</v>
-      </c>
-      <c r="K18" s="22" t="inlineStr">
+      <c r="F18" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
-      <c r="L18" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 337 ud.</t>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>ACETATO DE CALCIO 667 MG CM UD</t>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
@@ -17685,44 +17923,40 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>120</v>
+        <v>626</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>730.2</v>
+        <v>2304.4</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>198.5</v>
+        <v>4.4</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>146</v>
+        <v>3147.1</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>367</v>
+        <v>322</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="K19" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L19" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 367 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 322 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
@@ -17731,28 +17965,28 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>11.9</v>
+        <v>1202.2</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>10.9</v>
+        <v>4.4</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>17.8</v>
+        <v>1299</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>8</v>
+        <v>337</v>
       </c>
       <c r="I20" s="23" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="23" t="n">
-        <v>8</v>
+        <v>337</v>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
@@ -17761,7 +17995,7 @@
       </c>
       <c r="L20" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 8 ud.</t>
+          <t>GESTIONAR EXTERNO 337 ud.</t>
         </is>
       </c>
     </row>
@@ -17823,10 +18057,10 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>174.7</v>
@@ -17902,7 +18136,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -17911,44 +18145,40 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>13.1</v>
+        <v>32.5</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>18.8</v>
+        <v>37.6</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>AMOXICILINA + AC. CLAVULANICO 500/125 MG CM</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -17957,140 +18187,186 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>8.5</v>
+        <v>0.1</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>4.4</v>
+        <v>18.8</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>AMOXICILINA + AC. CLAVULANICO 500/125 MG CM</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>3-MODERADO</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C27" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D27" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E27" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F27" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G27" s="6" t="n">
         <v>2.9</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H27" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I27" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J27" s="6" t="n">
         <v>470</v>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 470 ud.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
+          <t>MODERADO  —  reponer pronto (Farmacia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
+          <t>BAJO  —  vigilar (Farmacia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -18107,7 +18383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -18546,14 +18822,14 @@
         <v>766.9</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I11" s="21" t="n">
         <v>7620</v>
       </c>
       <c r="J11" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 150 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr"/>
@@ -18624,14 +18900,14 @@
         <v>542.4</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I13" s="21" t="n">
         <v>2100</v>
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 500 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 600 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr"/>
@@ -18663,14 +18939,14 @@
         <v>393.2</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I14" s="21" t="n">
         <v>4350</v>
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 150 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr"/>
@@ -18702,14 +18978,14 @@
         <v>146</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>611</v>
+        <v>731</v>
       </c>
       <c r="I15" s="21" t="n">
         <v>10440</v>
       </c>
       <c r="J15" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 611 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 731 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr"/>
@@ -19069,14 +19345,14 @@
         <v>17.8</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I24" s="21" t="n">
         <v>1600</v>
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 27 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr"/>
@@ -19190,14 +19466,14 @@
         <v>17.8</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I27" s="21" t="n">
         <v>520</v>
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 13 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 15 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr"/>
@@ -19452,10 +19728,10 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>780</v>
+        <v>900</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="E34" s="23" t="n">
         <v>5562.8</v>
@@ -19467,7 +19743,7 @@
         <v>3436.3</v>
       </c>
       <c r="H34" s="23" t="n">
-        <v>1916</v>
+        <v>2036</v>
       </c>
       <c r="I34" s="23" t="n">
         <v>0</v>
@@ -19479,7 +19755,7 @@
       </c>
       <c r="K34" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1916 ud.</t>
+          <t>COMPRA EXTERNA 2036 ud.</t>
         </is>
       </c>
     </row>
@@ -19495,10 +19771,10 @@
         </is>
       </c>
       <c r="C35" s="23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>71.3</v>
@@ -19510,7 +19786,7 @@
         <v>37.6</v>
       </c>
       <c r="H35" s="23" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I35" s="23" t="n">
         <v>20</v>
@@ -19522,14 +19798,14 @@
       </c>
       <c r="K35" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 11 ud.</t>
+          <t>COMPRA EXTERNA 16 ud.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
+          <t>LOSARTAN 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B36" s="26" t="inlineStr">
@@ -19538,29 +19814,29 @@
         </is>
       </c>
       <c r="C36" s="27" t="n">
-        <v>2688</v>
+        <v>4500</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="E36" s="27" t="n">
-        <v>7110.5</v>
+        <v>9049.299999999999</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>48.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>4422.4</v>
+        <v>6018.5</v>
       </c>
       <c r="H36" s="27" t="n">
-        <v>879</v>
+        <v>1200</v>
       </c>
       <c r="I36" s="27" t="n">
-        <v>10024</v>
+        <v>32400</v>
       </c>
       <c r="J36" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 879 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1200 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K36" s="26" t="inlineStr"/>
@@ -19568,7 +19844,7 @@
     <row r="37">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B37" s="26" t="inlineStr">
@@ -19577,29 +19853,29 @@
         </is>
       </c>
       <c r="C37" s="27" t="n">
-        <v>2280</v>
+        <v>2688</v>
       </c>
       <c r="D37" s="27" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="E37" s="27" t="n">
-        <v>4792.7</v>
+        <v>7110.5</v>
       </c>
       <c r="F37" s="27" t="n">
-        <v>76</v>
+        <v>48.5</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>2965</v>
+        <v>4422.4</v>
       </c>
       <c r="H37" s="27" t="n">
-        <v>1230</v>
+        <v>1089</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>2520</v>
+        <v>10024</v>
       </c>
       <c r="J37" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1230 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1089 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K37" s="26" t="inlineStr"/>
@@ -19607,100 +19883,139 @@
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
         <is>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>3-ALTO</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="n">
+        <v>2280</v>
+      </c>
+      <c r="D38" s="27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E38" s="27" t="n">
+        <v>4792.7</v>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>76</v>
+      </c>
+      <c r="G38" s="27" t="n">
+        <v>2965</v>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>1380</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>2520</v>
+      </c>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1380 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K38" s="26" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
           <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>3-ALTO</t>
         </is>
       </c>
-      <c r="C38" s="27" t="n">
+      <c r="C39" s="27" t="n">
         <v>1920</v>
       </c>
-      <c r="D38" s="27" t="n">
+      <c r="D39" s="27" t="n">
         <v>3.3</v>
       </c>
-      <c r="E38" s="27" t="n">
+      <c r="E39" s="27" t="n">
         <v>4746.9</v>
       </c>
-      <c r="F38" s="27" t="n">
+      <c r="F39" s="27" t="n">
         <v>26.5</v>
       </c>
-      <c r="G38" s="27" t="n">
+      <c r="G39" s="27" t="n">
         <v>2880.7</v>
       </c>
-      <c r="H38" s="27" t="n">
-        <v>1110</v>
-      </c>
-      <c r="I38" s="27" t="n">
+      <c r="H39" s="27" t="n">
+        <v>1320</v>
+      </c>
+      <c r="I39" s="27" t="n">
         <v>13290</v>
       </c>
-      <c r="J38" s="26" t="inlineStr">
-        <is>
-          <t>TRASPASAR 1110 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K38" s="26" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="J39" s="26" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1320 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K39" s="26" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
+          <t>MODERADO  —  reponer pronto (Farmacia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
+          <t>BAJO  —  vigilar (Farmacia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -1657,7 +1657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2174,7 +2174,7 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
@@ -2189,16 +2189,16 @@
         <v>0</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>37.7</v>
+        <v>174.7</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="G14" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
@@ -2207,14 +2207,14 @@
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 37 ud.</t>
+          <t>GESTIONAR EXTERNO 120 ud.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -2229,16 +2229,16 @@
         <v>0</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>11.7</v>
+        <v>37.7</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="G15" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
@@ -2247,14 +2247,14 @@
       </c>
       <c r="J15" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
+          <t>GESTIONAR EXTERNO 37 ud.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -2269,16 +2269,16 @@
         <v>0</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>31.8</v>
+        <v>11.7</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="G16" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
@@ -2287,14 +2287,14 @@
       </c>
       <c r="J16" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 28 ud.</t>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -2309,16 +2309,16 @@
         <v>0</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>11.9</v>
+        <v>31.8</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G17" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
@@ -2327,14 +2327,14 @@
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 8 ud.</t>
+          <t>GESTIONAR EXTERNO 28 ud.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
@@ -2349,16 +2349,16 @@
         <v>0</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G18" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
@@ -2367,14 +2367,14 @@
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 12 ud.</t>
+          <t>GESTIONAR EXTERNO 8 ud.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -2389,16 +2389,16 @@
         <v>0</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G19" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
@@ -2407,14 +2407,14 @@
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 9 ud.</t>
+          <t>GESTIONAR EXTERNO 12 ud.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>APIXABAN 2,5 MG CM</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
@@ -2429,16 +2429,16 @@
         <v>0</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>21.2</v>
+        <v>12.8</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="G20" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
@@ -2447,14 +2447,14 @@
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 60 ud.</t>
+          <t>GESTIONAR EXTERNO 9 ud.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>RISPERIDONA 25 MG FA</t>
+          <t>APIXABAN 2,5 MG CM</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -2469,16 +2469,16 @@
         <v>0</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>6.8</v>
+        <v>21.2</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="G21" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
@@ -2487,14 +2487,14 @@
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 7 ud.</t>
+          <t>GESTIONAR EXTERNO 60 ud.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>UREA 10% CREMA 20 GR</t>
+          <t>RISPERIDONA 25 MG FA</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -2509,16 +2509,16 @@
         <v>0</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>14.8</v>
+        <v>6.8</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G22" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -2527,14 +2527,14 @@
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 15 ud.</t>
+          <t>GESTIONAR EXTERNO 7 ud.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>VASELINA SOLIDA UNGUENTO</t>
+          <t>UREA 10% CREMA 20 GR</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
@@ -2549,16 +2549,16 @@
         <v>0</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>5.7</v>
+        <v>14.8</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G23" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
@@ -2567,14 +2567,14 @@
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 6 ud.</t>
+          <t>GESTIONAR EXTERNO 15 ud.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>VASELINA SOLIDA UNGUENTO</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
@@ -2589,16 +2589,16 @@
         <v>0</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G24" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -2607,14 +2607,14 @@
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2 ud.</t>
+          <t>GESTIONAR EXTERNO 6 ud.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="F25" s="21" t="n">
         <v>2</v>
@@ -2654,7 +2654,7 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
@@ -2669,16 +2669,16 @@
         <v>0</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -2687,14 +2687,14 @@
       </c>
       <c r="J26" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 2 ud.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
@@ -2727,14 +2727,14 @@
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2 ud.</t>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
+          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F28" s="21" t="n">
         <v>2</v>
@@ -2774,7 +2774,7 @@
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>ETONOGESTREL 68 MG IMPLANTE</t>
+          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -2789,16 +2789,16 @@
         <v>0</v>
       </c>
       <c r="E29" s="21" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
@@ -2807,14 +2807,14 @@
       </c>
       <c r="J29" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 2 ud.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
+          <t>ETONOGESTREL 68 MG IMPLANTE</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F30" s="21" t="n">
         <v>1</v>
@@ -2854,7 +2854,7 @@
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
+          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F31" s="21" t="n">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
+          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
+          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
@@ -2974,7 +2974,7 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
@@ -3012,45 +3012,49 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
-        <is>
-          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="n">
-        <v>626</v>
-      </c>
-      <c r="D35" s="23" t="n">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F35" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="23" t="n">
-        <v>2304.4</v>
-      </c>
-      <c r="F35" s="23" t="n">
-        <v>321</v>
-      </c>
-      <c r="G35" s="23" t="n">
-        <v>321</v>
-      </c>
-      <c r="H35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 321 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J35" s="22" t="inlineStr"/>
+      <c r="G35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="20" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J35" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
+          <t>CALCIO CARBONATO C/VITAMINA D CM O CP</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
@@ -3059,38 +3063,34 @@
         </is>
       </c>
       <c r="C36" s="23" t="n">
-        <v>116</v>
+        <v>1423</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="E36" s="23" t="n">
-        <v>1202.2</v>
+        <v>3581.1</v>
       </c>
       <c r="F36" s="23" t="n">
-        <v>335</v>
+        <v>134</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="I36" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J36" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 335 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 134 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
         </is>
       </c>
       <c r="B37" s="22" t="inlineStr">
@@ -3099,26 +3099,26 @@
         </is>
       </c>
       <c r="C37" s="23" t="n">
-        <v>326</v>
+        <v>566</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="E37" s="23" t="n">
-        <v>786.2</v>
+        <v>2304.4</v>
       </c>
       <c r="F37" s="23" t="n">
-        <v>10</v>
+        <v>381</v>
       </c>
       <c r="G37" s="23" t="n">
-        <v>10</v>
+        <v>381</v>
       </c>
       <c r="H37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 381 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J37" s="22" t="inlineStr"/>
@@ -3126,7 +3126,7 @@
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>BUPROPION (ANFEBUTAMONA) 150 MG CM LIBERACION MODIFICADA</t>
+          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
@@ -3135,34 +3135,38 @@
         </is>
       </c>
       <c r="C38" s="23" t="n">
-        <v>270</v>
+        <v>86</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="E38" s="23" t="n">
-        <v>813.1</v>
+        <v>1202.2</v>
       </c>
       <c r="F38" s="23" t="n">
-        <v>44</v>
+        <v>365</v>
       </c>
       <c r="G38" s="23" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H38" s="23" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="I38" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 44 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J38" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J38" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 365 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>RIFAXIMINA 200 MG CP</t>
+          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
@@ -3171,26 +3175,26 @@
         </is>
       </c>
       <c r="C39" s="23" t="n">
-        <v>86</v>
+        <v>326</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="E39" s="23" t="n">
-        <v>338.1</v>
+        <v>786.2</v>
       </c>
       <c r="F39" s="23" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="H39" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 48 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J39" s="22" t="inlineStr"/>
@@ -3198,7 +3202,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>BUPROPION (ANFEBUTAMONA) 150 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
@@ -3207,38 +3211,34 @@
         </is>
       </c>
       <c r="C40" s="23" t="n">
-        <v>32</v>
+        <v>210</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E40" s="23" t="n">
-        <v>77.7</v>
+        <v>813.1</v>
       </c>
       <c r="F40" s="23" t="n">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H40" s="23" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I40" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J40" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 46 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 104 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>VITAMINA D3 50.000 UI SOBRE</t>
+          <t>RIFAXIMINA 200 MG CP</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
@@ -3247,26 +3247,26 @@
         </is>
       </c>
       <c r="C41" s="23" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E41" s="23" t="n">
-        <v>44.9</v>
+        <v>338.1</v>
       </c>
       <c r="F41" s="23" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G41" s="23" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H41" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 39 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 48 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J41" s="22" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
+          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
@@ -3283,34 +3283,38 @@
         </is>
       </c>
       <c r="C42" s="23" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="E42" s="23" t="n">
-        <v>49.4</v>
+        <v>77.7</v>
       </c>
       <c r="F42" s="23" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G42" s="23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H42" s="23" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I42" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J42" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J42" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 46 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>VITAMINA D3 50.000 UI SOBRE</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
@@ -3319,38 +3323,34 @@
         </is>
       </c>
       <c r="C43" s="23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E43" s="23" t="n">
-        <v>20.5</v>
+        <v>44.9</v>
       </c>
       <c r="F43" s="23" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G43" s="23" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H43" s="23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I43" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J43" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 19 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 39 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J43" s="22" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>ACIDO ACETILSALICILICO CM 500 MG</t>
+          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B44" s="22" t="inlineStr">
@@ -3365,20 +3365,20 @@
         <v>0</v>
       </c>
       <c r="E44" s="23" t="n">
-        <v>17.7</v>
+        <v>49.4</v>
       </c>
       <c r="F44" s="23" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="G44" s="23" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H44" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 18 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J44" s="22" t="inlineStr"/>
@@ -3386,7 +3386,7 @@
     <row r="45">
       <c r="A45" s="22" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B45" s="22" t="inlineStr">
@@ -3395,22 +3395,22 @@
         </is>
       </c>
       <c r="C45" s="23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="E45" s="23" t="n">
-        <v>8.6</v>
+        <v>20.5</v>
       </c>
       <c r="F45" s="23" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G45" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="23" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I45" s="22" t="inlineStr">
         <is>
@@ -3419,14 +3419,14 @@
       </c>
       <c r="J45" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 19 ud.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+          <t>ACIDO ACETILSALICILICO CM 500 MG</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
@@ -3441,32 +3441,28 @@
         <v>0</v>
       </c>
       <c r="E46" s="23" t="n">
-        <v>10.5</v>
+        <v>17.7</v>
       </c>
       <c r="F46" s="23" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G46" s="23" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H46" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I46" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J46" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 4 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 18 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J46" s="22" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>METILPREDNISOLONA ACETATO 40 MG/ML IM INTRARTICULAR</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
@@ -3475,150 +3471,154 @@
         </is>
       </c>
       <c r="C47" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E47" s="23" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="F47" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G47" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H47" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 4 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J47" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J47" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
         <is>
+          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F48" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="G48" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H48" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J48" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 4 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>METILPREDNISOLONA ACETATO 40 MG/ML IM INTRARTICULAR</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F49" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H49" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 4 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J49" s="22" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
           <t>LEVETIRACETAM 100 MG/ML FC 300 ML</t>
         </is>
       </c>
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B50" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C48" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="23" t="n">
+      <c r="C50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="23" t="n">
         <v>2.2</v>
       </c>
-      <c r="F48" s="23" t="n">
+      <c r="F50" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="G48" s="23" t="n">
+      <c r="G50" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="23" t="n">
+      <c r="H50" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="I48" s="22" t="inlineStr">
+      <c r="I50" s="22" t="inlineStr">
         <is>
           <t>TRASPASAR 3 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="J48" s="22" t="inlineStr">
+      <c r="J50" s="22" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 7 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>MESALAZINA 500 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>356</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>1095.1</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 400 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="D50" s="6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E50" s="6" t="n">
-        <v>174.7</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 30 ud.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>MESALAZINA 500 MG SUPOSITORIO.</t>
+          <t>METILDOPA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -3627,13 +3627,13 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>80</v>
+        <v>396</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>88.3</v>
+        <v>1073.9</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>100</v>
@@ -3654,7 +3654,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>AMOXICILINA 875 MG - ACIDO CLAVULANICO 125 MG COMPRIMIDO.</t>
+          <t>MESALAZINA 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -3663,26 +3663,26 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>41</v>
+        <v>356</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>42.3</v>
+        <v>1095.1</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 400 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>MESALAZINA 500 MG SUPOSITORIO.</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -3699,38 +3699,34 @@
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>40.9</v>
+        <v>88.3</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 4 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>AMANTADINA 100 MG CAPSULA</t>
+          <t>AMOXICILINA 875 MG - ACIDO CLAVULANICO 125 MG COMPRIMIDO.</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -3739,38 +3735,34 @@
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>102.4</v>
+        <v>42.3</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 60 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -3779,34 +3771,38 @@
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>32.5</v>
+        <v>40.9</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 8 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
+          <t>AMANTADINA 100 MG CAPSULA</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -3815,34 +3811,38 @@
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>13.4</v>
+        <v>102.4</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 60 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -3851,38 +3851,34 @@
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>13.1</v>
+        <v>32.5</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
+          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -3891,38 +3887,34 @@
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>10.5</v>
+        <v>13.4</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -3931,22 +3923,22 @@
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>7.9</v>
+        <v>13.1</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
@@ -3955,108 +3947,188 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 6 ud.</t>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
+          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 6 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
           <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>3-MODERADO</t>
         </is>
       </c>
-      <c r="C60" s="6" t="n">
+      <c r="C62" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="D62" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E62" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F62" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="G60" s="6" t="n">
+      <c r="G62" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H60" s="6" t="n">
+      <c r="H62" s="6" t="n">
         <v>470</v>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 470 ud.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="15" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="15" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="16" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="16" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="17" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -4376,7 +4448,7 @@
         <v>2510.8</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>2395</v>
+        <v>2425</v>
       </c>
       <c r="G9" s="21" t="n">
         <v>0</v>
@@ -4388,7 +4460,7 @@
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2395 ud.</t>
+          <t>COMPRA EXTERNA 2425 ud.</t>
         </is>
       </c>
     </row>
@@ -4660,7 +4732,7 @@
         <v>631</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="G17" s="21" t="n">
         <v>0</v>
@@ -4672,7 +4744,7 @@
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 245 ud.</t>
+          <t>COMPRA EXTERNA 305 ud.</t>
         </is>
       </c>
     </row>
@@ -4767,14 +4839,14 @@
         <v>556</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="G20" s="21" t="n">
         <v>22260</v>
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 346 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 376 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr"/>
@@ -5006,7 +5078,7 @@
         <v>300</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G27" s="21" t="n">
         <v>0</v>
@@ -5018,7 +5090,7 @@
       </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 120 ud.</t>
+          <t>COMPRA EXTERNA 180 ud.</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5152,7 @@
         <v>328.1</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G29" s="21" t="n">
         <v>0</v>
@@ -5092,7 +5164,7 @@
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 111 ud.</t>
+          <t>COMPRA EXTERNA 119 ud.</t>
         </is>
       </c>
     </row>
@@ -5294,14 +5366,14 @@
         <v>174.7</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G35" s="21" t="n">
         <v>390</v>
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr"/>
@@ -5397,7 +5469,7 @@
         <v>113.2</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G38" s="21" t="n">
         <v>0</v>
@@ -5409,7 +5481,7 @@
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 77 ud.</t>
+          <t>COMPRA EXTERNA 81 ud.</t>
         </is>
       </c>
     </row>
@@ -5850,14 +5922,14 @@
         <v>34.2</v>
       </c>
       <c r="F51" s="21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G51" s="21" t="n">
         <v>520</v>
       </c>
       <c r="H51" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 15 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 16 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I51" s="20" t="inlineStr"/>
@@ -6686,14 +6758,14 @@
         <v>6284.1</v>
       </c>
       <c r="F75" s="23" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="G75" s="23" t="n">
         <v>8000</v>
       </c>
       <c r="H75" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 800 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1600 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I75" s="22" t="inlineStr"/>
@@ -6719,7 +6791,7 @@
         <v>5562.8</v>
       </c>
       <c r="F76" s="23" t="n">
-        <v>2036</v>
+        <v>2066</v>
       </c>
       <c r="G76" s="23" t="n">
         <v>0</v>
@@ -6731,7 +6803,7 @@
       </c>
       <c r="I76" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2036 ud.</t>
+          <t>COMPRA EXTERNA 2066 ud.</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6828,7 @@
         <v>2879.5</v>
       </c>
       <c r="F77" s="23" t="n">
-        <v>1260</v>
+        <v>1290</v>
       </c>
       <c r="G77" s="23" t="n">
         <v>0</v>
@@ -6768,7 +6840,7 @@
       </c>
       <c r="I77" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1260 ud.</t>
+          <t>COMPRA EXTERNA 1290 ud.</t>
         </is>
       </c>
     </row>
@@ -6891,16 +6963,16 @@
         </is>
       </c>
       <c r="C81" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D81" s="23" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E81" s="23" t="n">
         <v>71.3</v>
       </c>
       <c r="F81" s="23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G81" s="23" t="n">
         <v>20</v>
@@ -6912,7 +6984,7 @@
       </c>
       <c r="I81" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 16 ud.</t>
+          <t>COMPRA EXTERNA 17 ud.</t>
         </is>
       </c>
     </row>
@@ -6970,14 +7042,14 @@
         <v>7110.5</v>
       </c>
       <c r="F83" s="27" t="n">
-        <v>1089</v>
+        <v>1179</v>
       </c>
       <c r="G83" s="27" t="n">
         <v>10024</v>
       </c>
       <c r="H83" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1089 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1179 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I83" s="26" t="inlineStr"/>
@@ -7003,14 +7075,14 @@
         <v>4792.7</v>
       </c>
       <c r="F84" s="27" t="n">
-        <v>1380</v>
+        <v>1560</v>
       </c>
       <c r="G84" s="27" t="n">
         <v>2520</v>
       </c>
       <c r="H84" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1380 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1560 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I84" s="26" t="inlineStr"/>
@@ -7036,14 +7108,14 @@
         <v>4746.9</v>
       </c>
       <c r="F85" s="27" t="n">
-        <v>1320</v>
+        <v>1350</v>
       </c>
       <c r="G85" s="27" t="n">
         <v>13290</v>
       </c>
       <c r="H85" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1320 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1350 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I85" s="26" t="inlineStr"/>
@@ -7312,10 +7384,10 @@
         </is>
       </c>
       <c r="C94" s="29" t="n">
-        <v>9100</v>
+        <v>8966</v>
       </c>
       <c r="D94" s="29" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="E94" s="29" t="n">
         <v>6279.2</v>
@@ -7399,10 +7471,10 @@
         </is>
       </c>
       <c r="C97" s="29" t="n">
-        <v>4679</v>
+        <v>4619</v>
       </c>
       <c r="D97" s="29" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="E97" s="29" t="n">
         <v>4510.4</v>
@@ -7950,10 +8022,10 @@
         </is>
       </c>
       <c r="C116" s="29" t="n">
-        <v>3316</v>
+        <v>3256</v>
       </c>
       <c r="D116" s="29" t="n">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="E116" s="29" t="n">
         <v>1670.9</v>
@@ -8182,10 +8254,10 @@
         </is>
       </c>
       <c r="C124" s="29" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="D124" s="29" t="n">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="E124" s="29" t="n">
         <v>1480.3</v>
@@ -17089,7 +17161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -17454,7 +17526,7 @@
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -17469,22 +17541,22 @@
         <v>0</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>37.7</v>
+        <v>174.7</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>1.8</v>
+        <v>46.3</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>48.5</v>
+        <v>57.4</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="I9" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="21" t="n">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="K9" s="20" t="inlineStr">
         <is>
@@ -17493,14 +17565,14 @@
       </c>
       <c r="L9" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 38 ud.</t>
+          <t>GESTIONAR EXTERNO 180 ud.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -17515,22 +17587,22 @@
         <v>0</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>11.7</v>
+        <v>37.7</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>35.3</v>
+        <v>1.8</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>11.8</v>
+        <v>48.5</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="I10" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="21" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="K10" s="20" t="inlineStr">
         <is>
@@ -17539,14 +17611,14 @@
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
+          <t>GESTIONAR EXTERNO 38 ud.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -17561,13 +17633,13 @@
         <v>0</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>16.5</v>
+        <v>11.7</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>38.2</v>
+        <v>35.3</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>100</v>
@@ -17592,7 +17664,7 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -17607,22 +17679,22 @@
         <v>0</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>31.8</v>
+        <v>16.5</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>4.4</v>
+        <v>38.2</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="I12" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="K12" s="20" t="inlineStr">
         <is>
@@ -17631,14 +17703,14 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 32 ud.</t>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -17653,22 +17725,22 @@
         <v>0</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>11.9</v>
+        <v>31.8</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>10.9</v>
+        <v>4.4</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>17.8</v>
+        <v>26.5</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I13" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="K13" s="20" t="inlineStr">
         <is>
@@ -17677,14 +17749,14 @@
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 12 ud.</t>
+          <t>GESTIONAR EXTERNO 32 ud.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
@@ -17699,22 +17771,22 @@
         <v>0</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>12.8</v>
+        <v>11.9</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>6.3</v>
+        <v>10.9</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>13.5</v>
+        <v>17.8</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I14" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K14" s="20" t="inlineStr">
         <is>
@@ -17723,14 +17795,14 @@
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 13 ud.</t>
+          <t>GESTIONAR EXTERNO 12 ud.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -17745,22 +17817,22 @@
         <v>0</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>2.3</v>
+        <v>12.8</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>8.699999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I15" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K15" s="20" t="inlineStr">
         <is>
@@ -17769,14 +17841,14 @@
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3 ud.</t>
+          <t>GESTIONAR EXTERNO 13 ud.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -17791,22 +17863,22 @@
         <v>0</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>0.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" s="20" t="inlineStr">
         <is>
@@ -17815,14 +17887,14 @@
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 3 ud.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -17837,13 +17909,13 @@
         <v>0</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>1</v>
@@ -17868,7 +17940,7 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>ALTEPLASA 50 MG FA UD</t>
+          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
@@ -17883,10 +17955,10 @@
         <v>0</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G18" s="21" t="n">
         <v>0</v>
@@ -17912,51 +17984,55 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="n">
-        <v>626</v>
-      </c>
-      <c r="D19" s="23" t="n">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>ALTEPLASA 50 MG FA UD</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="23" t="n">
-        <v>2304.4</v>
-      </c>
-      <c r="F19" s="23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G19" s="23" t="n">
-        <v>3147.1</v>
-      </c>
-      <c r="H19" s="23" t="n">
-        <v>322</v>
-      </c>
-      <c r="I19" s="23" t="n">
-        <v>322</v>
-      </c>
-      <c r="J19" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 322 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L19" s="22" t="inlineStr"/>
+      <c r="I19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
+          <t>CALCIO CARBONATO C/VITAMINA D CM O CP</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
@@ -17965,178 +18041,174 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>116</v>
+        <v>1423</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>1202.2</v>
+        <v>3581.1</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>4.4</v>
+        <v>255.9</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>1299</v>
+        <v>3576.6</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>337</v>
+        <v>245</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="J20" s="23" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L20" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 337 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 245 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
         <is>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="n">
+        <v>566</v>
+      </c>
+      <c r="D21" s="23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E21" s="23" t="n">
+        <v>2304.4</v>
+      </c>
+      <c r="F21" s="23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G21" s="23" t="n">
+        <v>3147.1</v>
+      </c>
+      <c r="H21" s="23" t="n">
+        <v>382</v>
+      </c>
+      <c r="I21" s="23" t="n">
+        <v>382</v>
+      </c>
+      <c r="J21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 382 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n">
+        <v>86</v>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E22" s="23" t="n">
+        <v>1202.2</v>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G22" s="23" t="n">
+        <v>1299</v>
+      </c>
+      <c r="H22" s="23" t="n">
+        <v>367</v>
+      </c>
+      <c r="I22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>367</v>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 367 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
           <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C21" s="23" t="n">
+      <c r="C23" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D23" s="23" t="n">
         <v>1.6</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E23" s="23" t="n">
         <v>8.6</v>
       </c>
-      <c r="F21" s="23" t="n">
+      <c r="F23" s="23" t="n">
         <v>5.3</v>
       </c>
-      <c r="G21" s="23" t="n">
+      <c r="G23" s="23" t="n">
         <v>10.1</v>
       </c>
-      <c r="H21" s="23" t="n">
+      <c r="H23" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="I21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="23" t="n">
+      <c r="I23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="K21" s="22" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
-      <c r="L21" s="22" t="inlineStr">
+      <c r="L23" s="22" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 4 ud.</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>174.7</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 120 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>AMOXICILINA 875 MG - ACIDO CLAVULANICO 125 MG COMPRIMIDO.</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>METILDOPA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -18145,32 +18217,32 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>31</v>
+        <v>396</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>32.5</v>
+        <v>1073.9</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.9</v>
+        <v>167.6</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>37.6</v>
+        <v>723.7</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 300 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
@@ -18178,7 +18250,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>AMOXICILINA 875 MG - ACIDO CLAVULANICO 125 MG COMPRIMIDO.</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -18187,44 +18259,40 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>13.1</v>
+        <v>42.3</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>18.8</v>
+        <v>69.3</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>AMOXICILINA + AC. CLAVULANICO 500/125 MG CM</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -18233,32 +18301,32 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>12.7</v>
+        <v>32.5</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>8.5</v>
+        <v>0.9</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>4.4</v>
+        <v>37.6</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 3 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr"/>
@@ -18266,107 +18334,195 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>AMOXICILINA + AC. CLAVULANICO 500/125 MG CM</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 7 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>DOMPERIDONA 10 MG/ML GOTAS ORALES FRASCO DE 20 A 30 ML</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>3-MODERADO</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C29" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D29" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E29" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F29" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G29" s="6" t="n">
         <v>2.9</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H29" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I29" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J29" s="6" t="n">
         <v>470</v>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 470 ud.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -18740,7 +18896,7 @@
         <v>1299</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>2395</v>
+        <v>2425</v>
       </c>
       <c r="I9" s="21" t="n">
         <v>0</v>
@@ -18752,7 +18908,7 @@
       </c>
       <c r="K9" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2395 ud.</t>
+          <t>COMPRA EXTERNA 2425 ud.</t>
         </is>
       </c>
     </row>
@@ -19056,7 +19212,7 @@
         <v>209.6</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I17" s="21" t="n">
         <v>0</v>
@@ -19068,7 +19224,7 @@
       </c>
       <c r="K17" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 120 ud.</t>
+          <t>COMPRA EXTERNA 180 ud.</t>
         </is>
       </c>
     </row>
@@ -19142,14 +19298,14 @@
         <v>57.4</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I19" s="21" t="n">
         <v>390</v>
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr"/>
@@ -19466,14 +19622,14 @@
         <v>17.8</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I27" s="21" t="n">
         <v>520</v>
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 15 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 16 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr"/>
@@ -19704,14 +19860,14 @@
         <v>4172.6</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="I33" s="23" t="n">
         <v>8000</v>
       </c>
       <c r="J33" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 800 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1600 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr"/>
@@ -19743,7 +19899,7 @@
         <v>3436.3</v>
       </c>
       <c r="H34" s="23" t="n">
-        <v>2036</v>
+        <v>2066</v>
       </c>
       <c r="I34" s="23" t="n">
         <v>0</v>
@@ -19755,7 +19911,7 @@
       </c>
       <c r="K34" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2036 ud.</t>
+          <t>COMPRA EXTERNA 2066 ud.</t>
         </is>
       </c>
     </row>
@@ -19771,10 +19927,10 @@
         </is>
       </c>
       <c r="C35" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>71.3</v>
@@ -19786,7 +19942,7 @@
         <v>37.6</v>
       </c>
       <c r="H35" s="23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I35" s="23" t="n">
         <v>20</v>
@@ -19798,7 +19954,7 @@
       </c>
       <c r="K35" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 16 ud.</t>
+          <t>COMPRA EXTERNA 17 ud.</t>
         </is>
       </c>
     </row>
@@ -19868,14 +20024,14 @@
         <v>4422.4</v>
       </c>
       <c r="H37" s="27" t="n">
-        <v>1089</v>
+        <v>1179</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>10024</v>
       </c>
       <c r="J37" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1089 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1179 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K37" s="26" t="inlineStr"/>
@@ -19907,14 +20063,14 @@
         <v>2965</v>
       </c>
       <c r="H38" s="27" t="n">
-        <v>1380</v>
+        <v>1560</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>2520</v>
       </c>
       <c r="J38" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1380 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1560 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K38" s="26" t="inlineStr"/>
@@ -19946,14 +20102,14 @@
         <v>2880.7</v>
       </c>
       <c r="H39" s="27" t="n">
-        <v>1320</v>
+        <v>1350</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>13290</v>
       </c>
       <c r="J39" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1320 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1350 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K39" s="26" t="inlineStr"/>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -3063,26 +3063,26 @@
         </is>
       </c>
       <c r="C36" s="23" t="n">
-        <v>1423</v>
+        <v>1303</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>3581.1</v>
       </c>
       <c r="F36" s="23" t="n">
-        <v>134</v>
+        <v>254</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>134</v>
+        <v>254</v>
       </c>
       <c r="H36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 134 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 254 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J36" s="22" t="inlineStr"/>
@@ -3135,22 +3135,22 @@
         </is>
       </c>
       <c r="C38" s="23" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>1202.2</v>
       </c>
       <c r="F38" s="23" t="n">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="G38" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="23" t="n">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="I38" s="22" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="J38" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 365 ud.</t>
+          <t>GESTIONAR EXTERNO 395 ud.</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
         <v>2510.8</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>2425</v>
+        <v>2455</v>
       </c>
       <c r="G9" s="21" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2425 ud.</t>
+          <t>COMPRA EXTERNA 2455 ud.</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
         <v>2879.5</v>
       </c>
       <c r="F77" s="23" t="n">
-        <v>1290</v>
+        <v>1380</v>
       </c>
       <c r="G77" s="23" t="n">
         <v>0</v>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="I77" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1290 ud.</t>
+          <t>COMPRA EXTERNA 1380 ud.</t>
         </is>
       </c>
     </row>
@@ -7108,14 +7108,14 @@
         <v>4746.9</v>
       </c>
       <c r="F85" s="27" t="n">
-        <v>1350</v>
+        <v>1380</v>
       </c>
       <c r="G85" s="27" t="n">
         <v>13290</v>
       </c>
       <c r="H85" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1350 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1380 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I85" s="26" t="inlineStr"/>
@@ -7141,14 +7141,14 @@
         <v>3350.6</v>
       </c>
       <c r="F86" s="27" t="n">
-        <v>840</v>
+        <v>900</v>
       </c>
       <c r="G86" s="27" t="n">
         <v>45840</v>
       </c>
       <c r="H86" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 840 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 900 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I86" s="26" t="inlineStr"/>
@@ -7384,10 +7384,10 @@
         </is>
       </c>
       <c r="C94" s="29" t="n">
-        <v>8966</v>
+        <v>8846</v>
       </c>
       <c r="D94" s="29" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="E94" s="29" t="n">
         <v>6279.2</v>
@@ -18041,10 +18041,10 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>1423</v>
+        <v>1303</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>3581.1</v>
@@ -18056,17 +18056,17 @@
         <v>3576.6</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>245</v>
+        <v>365</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>245</v>
+        <v>365</v>
       </c>
       <c r="J20" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 245 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 365 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr"/>
@@ -18125,10 +18125,10 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>1202.2</v>
@@ -18140,13 +18140,13 @@
         <v>1299</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="I22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="23" t="n">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
       </c>
       <c r="L22" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 367 ud.</t>
+          <t>GESTIONAR EXTERNO 397 ud.</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
         <v>1299</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>2425</v>
+        <v>2455</v>
       </c>
       <c r="I9" s="21" t="n">
         <v>0</v>
@@ -18908,7 +18908,7 @@
       </c>
       <c r="K9" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2425 ud.</t>
+          <t>COMPRA EXTERNA 2455 ud.</t>
         </is>
       </c>
     </row>
@@ -20102,14 +20102,14 @@
         <v>2880.7</v>
       </c>
       <c r="H39" s="27" t="n">
-        <v>1350</v>
+        <v>1380</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>13290</v>
       </c>
       <c r="J39" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 1350 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1380 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K39" s="26" t="inlineStr"/>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1320,14 +1320,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>MORFINA 30 MG CAPSULA LIBERACION MODIFICADA</t>
+          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>1</v>
@@ -1349,14 +1349,14 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
+          <t>OXCARBAZEPINA 600 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>1</v>
@@ -1378,14 +1378,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>OXCARBAZEPINA 600 MG COMPRIMIDO</t>
+          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>1</v>
@@ -1405,48 +1405,48 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>[ALTO] ALTO — SIN RESPALDO</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>COMPRA URGENTE — SIN RESPALDO EN BODEGA FARMACOS</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>[BAJO] BAJO — TRASPASO BOD.FARMACOS</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>TRASPASAR DESDE BODEGA FARMACOS (50 ud. disponibles)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>5</v>
@@ -1458,27 +1458,27 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>TRASPASAR DESDE BODEGA FARMACOS (50 ud. disponibles)</t>
+          <t>TRASPASAR DESDE BODEGA FARMACOS (46 ud. disponibles)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
@@ -1487,27 +1487,27 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>TRASPASAR DESDE BODEGA FARMACOS (46 ud. disponibles)</t>
+          <t>TRASPASAR DESDE BODEGA FARMACOS (1600 ud. disponibles)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>AGUA BIDESTILADA MATRAZ 500 ML</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>TRASPASAR DESDE BODEGA FARMACOS (1600 ud. disponibles)</t>
+          <t>TRASPASAR DESDE BODEGA FARMACOS (125 ud. disponibles)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>AGUA BIDESTILADA MATRAZ 500 ML</t>
+          <t>BROMURO DE IPRATROPIO 0,25 MG/ML SOL. P/NEBULIZAR FC</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>1</v>
@@ -1545,21 +1545,21 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>TRASPASAR DESDE BODEGA FARMACOS (125 ud. disponibles)</t>
+          <t>TRASPASAR DESDE BODEGA FARMACOS (93 ud. disponibles)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 0,25 MG/ML SOL. P/NEBULIZAR FC</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>1</v>
@@ -1574,97 +1574,68 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>TRASPASAR DESDE BODEGA FARMACOS (93 ud. disponibles)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D33" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>[BAJO] BAJO — TRASPASO BOD.FARMACOS</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
           <t>TRASPASAR DESDE BODEGA FARMACOS (2200 ud. disponibles)</t>
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>LEYENDA DE COLORES</t>
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO  —  sin stock ni respaldo</t>
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>URGENTE  —  cobertura critica</t>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>MODERADO  —  reponer pronto (Farmacia)</t>
+          <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>BAJO  —  vigilar (Farmacia)</t>
+          <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>BAJO  —  stock suficiente (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -2078,7 +2049,7 @@
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>SACUBITRILO VALSARTAN 50 MG</t>
+          <t>RIFAXIMINA 200 MG CP</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
@@ -2087,22 +2058,22 @@
         </is>
       </c>
       <c r="C11" s="19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>337.9</v>
+        <v>399.6</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="G11" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
@@ -2111,14 +2082,14 @@
       </c>
       <c r="J11" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 124 ud.</t>
+          <t>GESTIONAR EXTERNO 192 ud.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>MICOFENOLATO 500 MG CR</t>
+          <t>SACUBITRILO VALSARTAN 50 MG</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
@@ -2133,16 +2104,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>119.7</v>
+        <v>337.9</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
@@ -2151,14 +2122,14 @@
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 60 ud.</t>
+          <t>GESTIONAR EXTERNO 124 ud.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>MEMANTINA 10 MG COMPRIMIDO</t>
+          <t>MICOFENOLATO 500 MG CR</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
@@ -2173,16 +2144,16 @@
         <v>0</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>83.40000000000001</v>
+        <v>119.7</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="G13" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
@@ -2191,14 +2162,14 @@
       </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 84 ud.</t>
+          <t>GESTIONAR EXTERNO 60 ud.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>MEMANTINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
@@ -2213,16 +2184,16 @@
         <v>0</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>66.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="G14" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="I14" s="18" t="inlineStr">
         <is>
@@ -2231,14 +2202,14 @@
       </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 67 ud.</t>
+          <t>GESTIONAR EXTERNO 84 ud.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B15" s="18" t="inlineStr">
@@ -2253,16 +2224,16 @@
         <v>0</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>35.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G15" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="I15" s="18" t="inlineStr">
         <is>
@@ -2271,14 +2242,14 @@
       </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 35 ud.</t>
+          <t>GESTIONAR EXTERNO 67 ud.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
@@ -2293,16 +2264,16 @@
         <v>0</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>22.2</v>
+        <v>35.9</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="I16" s="18" t="inlineStr">
         <is>
@@ -2311,14 +2282,14 @@
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
+          <t>GESTIONAR EXTERNO 35 ud.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
@@ -2333,16 +2304,16 @@
         <v>0</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>13.3</v>
+        <v>22.2</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G17" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I17" s="18" t="inlineStr">
         <is>
@@ -2351,14 +2322,14 @@
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 10 ud.</t>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
@@ -2373,16 +2344,16 @@
         <v>0</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="18" t="inlineStr">
         <is>
@@ -2391,14 +2362,14 @@
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 9 ud.</t>
+          <t>GESTIONAR EXTERNO 10 ud.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
@@ -2413,16 +2384,16 @@
         <v>0</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>11.2</v>
+        <v>13.6</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G19" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I19" s="18" t="inlineStr">
         <is>
@@ -2431,14 +2402,14 @@
       </c>
       <c r="J19" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 8 ud.</t>
+          <t>GESTIONAR EXTERNO 9 ud.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
@@ -2453,16 +2424,16 @@
         <v>0</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>13</v>
+        <v>11.2</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="G20" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="I20" s="18" t="inlineStr">
         <is>
@@ -2471,14 +2442,14 @@
       </c>
       <c r="J20" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
+          <t>GESTIONAR EXTERNO 8 ud.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>APIXABAN 2,5 MG CM</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
@@ -2493,16 +2464,16 @@
         <v>0</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>6.7</v>
+        <v>13</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G21" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I21" s="18" t="inlineStr">
         <is>
@@ -2511,14 +2482,14 @@
       </c>
       <c r="J21" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 60 ud.</t>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>UREA 10% CREMA 20 GR</t>
+          <t>APIXABAN 2,5 MG CM</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
@@ -2533,16 +2504,16 @@
         <v>0</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G22" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="I22" s="18" t="inlineStr">
         <is>
@@ -2551,14 +2522,14 @@
       </c>
       <c r="J22" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 10 ud.</t>
+          <t>GESTIONAR EXTERNO 60 ud.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>RISPERIDONA 25 MG FA</t>
+          <t>UREA 10% CREMA 20 GR</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
@@ -2573,16 +2544,16 @@
         <v>0</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
@@ -2591,14 +2562,14 @@
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 9 ud.</t>
+          <t>GESTIONAR EXTERNO 10 ud.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>VASELINA SOLIDA UNGUENTO</t>
+          <t>RISPERIDONA 25 MG FA</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -2613,16 +2584,16 @@
         <v>0</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
@@ -2631,14 +2602,14 @@
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 10 ud.</t>
+          <t>GESTIONAR EXTERNO 9 ud.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>VASELINA SOLIDA UNGUENTO</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
@@ -2653,16 +2624,16 @@
         <v>0</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
@@ -2671,14 +2642,14 @@
       </c>
       <c r="J25" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 4 ud.</t>
+          <t>GESTIONAR EXTERNO 10 ud.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
@@ -2693,16 +2664,16 @@
         <v>0</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I26" s="18" t="inlineStr">
         <is>
@@ -2711,14 +2682,14 @@
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2 ud.</t>
+          <t>GESTIONAR EXTERNO 4 ud.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
+          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
@@ -2733,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F27" s="19" t="n">
         <v>2</v>
@@ -2758,7 +2729,7 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
@@ -2773,16 +2744,16 @@
         <v>0</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="18" t="inlineStr">
         <is>
@@ -2791,14 +2762,14 @@
       </c>
       <c r="J28" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 2 ud.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
@@ -2813,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F29" s="19" t="n">
         <v>1</v>
@@ -2838,7 +2809,7 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>ACIDO VALPROICO 250 MG/5 ML FC 120 ML</t>
+          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
@@ -2853,16 +2824,16 @@
         <v>0</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="G30" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="I30" s="18" t="inlineStr">
         <is>
@@ -2871,14 +2842,14 @@
       </c>
       <c r="J30" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 120 ud.</t>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>ETONOGESTREL 68 MG IMPLANTE</t>
+          <t>ACIDO VALPROICO 250 MG/5 ML FC 120 ML</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
@@ -2893,16 +2864,16 @@
         <v>0</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="G31" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
@@ -2911,14 +2882,14 @@
       </c>
       <c r="J31" s="18" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 120 ud.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
+          <t>ETONOGESTREL 68 MG IMPLANTE</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
@@ -2933,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="F32" s="19" t="n">
         <v>1</v>
@@ -2958,7 +2929,7 @@
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
+          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
@@ -2973,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="F33" s="19" t="n">
         <v>1</v>
@@ -2998,7 +2969,7 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 0,25 MG/ML SOL. P/NEBULIZAR FC</t>
+          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
@@ -3013,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F34" s="19" t="n">
         <v>1</v>
@@ -3038,7 +3009,7 @@
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
+          <t>BROMURO DE IPRATROPIO 0,25 MG/ML SOL. P/NEBULIZAR FC</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
@@ -3078,7 +3049,7 @@
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
+          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
@@ -3118,7 +3089,7 @@
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
@@ -3156,45 +3127,49 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>PREGABALINA 75 MG CAPSULA</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="n">
-        <v>557</v>
-      </c>
-      <c r="D38" s="21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E38" s="21" t="n">
-        <v>2854.1</v>
-      </c>
-      <c r="F38" s="21" t="n">
-        <v>683</v>
-      </c>
-      <c r="G38" s="21" t="n">
-        <v>683</v>
-      </c>
-      <c r="H38" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="20" t="inlineStr">
-        <is>
-          <t>TRASPASAR 683 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J38" s="20" t="inlineStr"/>
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J38" s="18" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>HIDRALAZINA 50 MG COMPRIMIDO</t>
+          <t>PREGABALINA 75 MG CAPSULA</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
@@ -3203,26 +3178,26 @@
         </is>
       </c>
       <c r="C39" s="21" t="n">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="D39" s="21" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="E39" s="21" t="n">
-        <v>765.4</v>
+        <v>2854.1</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>90</v>
+        <v>863</v>
       </c>
       <c r="G39" s="21" t="n">
-        <v>90</v>
+        <v>863</v>
       </c>
       <c r="H39" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 90 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 863 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J39" s="20" t="inlineStr"/>
@@ -3230,7 +3205,7 @@
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
+          <t>HIDRALAZINA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
@@ -3239,26 +3214,26 @@
         </is>
       </c>
       <c r="C40" s="21" t="n">
-        <v>231</v>
+        <v>345</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>738.7</v>
+        <v>765.4</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="H40" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 109 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 90 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J40" s="20" t="inlineStr"/>
@@ -3266,7 +3241,7 @@
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>RIFAXIMINA 200 MG CP</t>
+          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -3275,26 +3250,26 @@
         </is>
       </c>
       <c r="C41" s="21" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E41" s="21" t="n">
-        <v>399.6</v>
+        <v>738.7</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="H41" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 192 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 139 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J41" s="20" t="inlineStr"/>
@@ -3302,7 +3277,7 @@
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>PROPANOLOL 10 MG COMPRIMIDO</t>
+          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
@@ -3311,34 +3286,38 @@
         </is>
       </c>
       <c r="C42" s="21" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E42" s="21" t="n">
-        <v>169.8</v>
+        <v>171.8</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 55 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J42" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J42" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 5 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
+          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -3347,38 +3326,34 @@
         </is>
       </c>
       <c r="C43" s="21" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D43" s="21" t="n">
         <v>1.7</v>
       </c>
       <c r="E43" s="21" t="n">
-        <v>70</v>
+        <v>110.6</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H43" s="21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J43" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 40 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 63 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J43" s="20" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
@@ -3387,22 +3362,22 @@
         </is>
       </c>
       <c r="C44" s="21" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D44" s="21" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="E44" s="21" t="n">
-        <v>51.3</v>
+        <v>70</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G44" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -3411,14 +3386,14 @@
       </c>
       <c r="J44" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 36 ud.</t>
+          <t>GESTIONAR EXTERNO 40 ud.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
@@ -3427,34 +3402,38 @@
         </is>
       </c>
       <c r="C45" s="21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D45" s="21" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E45" s="21" t="n">
-        <v>37.3</v>
+        <v>51.3</v>
       </c>
       <c r="F45" s="21" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G45" s="21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H45" s="21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 23 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J45" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J45" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 36 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>CEFADROXILO 500 MG CAPSULA</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
@@ -3463,26 +3442,26 @@
         </is>
       </c>
       <c r="C46" s="21" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D46" s="21" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="E46" s="21" t="n">
-        <v>34.7</v>
+        <v>37.3</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H46" s="21" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 40 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 23 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J46" s="20" t="inlineStr"/>
@@ -3490,7 +3469,7 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>CEFADROXILO 500 MG CAPSULA</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
@@ -3499,38 +3478,34 @@
         </is>
       </c>
       <c r="C47" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E47" s="21" t="n">
-        <v>18.2</v>
+        <v>34.7</v>
       </c>
       <c r="F47" s="21" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G47" s="21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H47" s="21" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I47" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J47" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 18 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 40 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J47" s="20" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
@@ -3539,34 +3514,38 @@
         </is>
       </c>
       <c r="C48" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D48" s="21" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="E48" s="21" t="n">
-        <v>10.9</v>
+        <v>18.2</v>
       </c>
       <c r="F48" s="21" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 6 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J48" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J48" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 18 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
@@ -3575,105 +3554,105 @@
         </is>
       </c>
       <c r="C49" s="21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D49" s="21" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="E49" s="21" t="n">
-        <v>9.300000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="F49" s="21" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G49" s="21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H49" s="21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I49" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J49" s="20" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 3 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 9 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J49" s="20" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E50" s="21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F50" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="20" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J50" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 3 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
           <t>LEVETIRACETAM 100 MG/ML FC 300 ML</t>
         </is>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C50" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="21" t="n">
+      <c r="C51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="21" t="n">
         <v>1.4</v>
       </c>
-      <c r="F50" s="21" t="n">
+      <c r="F51" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G50" s="21" t="n">
+      <c r="G51" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="H50" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="20" t="inlineStr">
+      <c r="H51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="20" t="inlineStr">
         <is>
           <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="J50" s="20" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E51" s="6" t="n">
-        <v>110.6</v>
-      </c>
-      <c r="F51" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 47 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr"/>
+      <c r="J51" s="20" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -3687,22 +3666,22 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>54.7</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
@@ -3711,7 +3690,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 11 ud.</t>
+          <t>GESTIONAR EXTERNO 15 ud.</t>
         </is>
       </c>
     </row>
@@ -3727,22 +3706,22 @@
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>14.9</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
@@ -3751,7 +3730,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 9 ud.</t>
+          <t>GESTIONAR EXTERNO 10 ud.</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4086,7 @@
         <v>4791.5</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>272</v>
+        <v>462</v>
       </c>
       <c r="G4" s="19" t="n">
         <v>0</v>
@@ -4119,7 +4098,7 @@
       </c>
       <c r="I4" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 272 ud.</t>
+          <t>COMPRA EXTERNA 462 ud.</t>
         </is>
       </c>
     </row>
@@ -4144,14 +4123,14 @@
         <v>3722.6</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G5" s="19" t="n">
         <v>1400</v>
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 200 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 300 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I5" s="18" t="inlineStr"/>
@@ -4214,7 +4193,7 @@
         <v>3301.8</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>2550</v>
+        <v>2610</v>
       </c>
       <c r="G7" s="19" t="n">
         <v>0</v>
@@ -4226,7 +4205,7 @@
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2550 ud.</t>
+          <t>COMPRA EXTERNA 2610 ud.</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4500,7 @@
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>LEVODOPA 200 MG - BENSERAZIDA 50 MG COMPRIMIDO</t>
+          <t>RIFAXIMINA 200 MG CP</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
@@ -4536,29 +4515,25 @@
         <v>0</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>572.3</v>
+        <v>828.8</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>247</v>
+        <v>840</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0</v>
+        <v>23424</v>
       </c>
       <c r="H16" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 247 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 840 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>VENLAFAXINA 150 MG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>LEVODOPA 200 MG - BENSERAZIDA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
@@ -4573,25 +4548,29 @@
         <v>0</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>903.1</v>
+        <v>572.3</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>6990</v>
+        <v>0</v>
       </c>
       <c r="H17" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 210 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 247 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>CARBONATO DE LITIO 450 MG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>VENLAFAXINA 150 MG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
@@ -4606,17 +4585,17 @@
         <v>0</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>611.2</v>
+        <v>903.1</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>12</v>
+        <v>210</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>21660</v>
+        <v>6990</v>
       </c>
       <c r="H18" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 12 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 210 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I18" s="18" t="inlineStr"/>
@@ -4624,7 +4603,7 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>SACUBITRILO VALSARTAN 50 MG</t>
+          <t>CARBONATO DE LITIO 450 MG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
@@ -4639,29 +4618,25 @@
         <v>0</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>772.1</v>
+        <v>611.2</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>773</v>
+        <v>42</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0</v>
+        <v>21660</v>
       </c>
       <c r="H19" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 773 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 42 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>BICARBONATO DE SODIO CP. 500 M</t>
+          <t>SACUBITRILO VALSARTAN 50 MG</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
@@ -4676,25 +4651,29 @@
         <v>0</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>471.9</v>
+        <v>772.1</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>262</v>
+        <v>773</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 262 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 773 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>ALOPURINOL 300 MG COMPRIMIDO</t>
+          <t>BICARBONATO DE SODIO CP. 500 M</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
@@ -4709,17 +4688,17 @@
         <v>0</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>447.7</v>
+        <v>471.9</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>5800</v>
+        <v>1800</v>
       </c>
       <c r="H21" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 262 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I21" s="18" t="inlineStr"/>
@@ -4727,7 +4706,7 @@
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>BACLOFENO 10 MG COMPRIMIDO</t>
+          <t>ALOPURINOL 300 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
@@ -4742,29 +4721,25 @@
         <v>0</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>658.1</v>
+        <v>447.7</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="H22" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 360 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I22" s="18" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>MICOFENOLATO 500 MG CR</t>
+          <t>BACLOFENO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
@@ -4779,10 +4754,10 @@
         <v>0</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>306.2</v>
+        <v>658.1</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>307</v>
+        <v>360</v>
       </c>
       <c r="G23" s="19" t="n">
         <v>0</v>
@@ -4794,14 +4769,14 @@
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 307 ud.</t>
+          <t>COMPRA EXTERNA 360 ud.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>MIRTAZAPINA 15 MG COMPRIMIDO</t>
+          <t>MICOFENOLATO 500 MG CR</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -4816,25 +4791,29 @@
         <v>0</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>444.1</v>
+        <v>306.2</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>150</v>
+        <v>307</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>7020</v>
+        <v>0</v>
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 150 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 307 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
+          <t>MIRTAZAPINA 15 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
@@ -4849,29 +4828,25 @@
         <v>0</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>349.9</v>
+        <v>444.1</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>0</v>
+        <v>7020</v>
       </c>
       <c r="H25" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 270 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 150 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 20 MG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>ACIDO FOLICO CM 1 MG</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
@@ -4886,13 +4861,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>282.1</v>
+        <v>336.2</v>
       </c>
       <c r="F26" s="19" t="n">
         <v>1000</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>9000</v>
+        <v>13640</v>
       </c>
       <c r="H26" s="18" t="inlineStr">
         <is>
@@ -4904,7 +4879,7 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
@@ -4919,10 +4894,10 @@
         <v>0</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>354</v>
+        <v>349.9</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G27" s="19" t="n">
         <v>0</v>
@@ -4934,14 +4909,14 @@
       </c>
       <c r="I27" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 277 ud.</t>
+          <t>COMPRA EXTERNA 270 ud.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>NIFEDIPINO 20 MG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
@@ -4956,29 +4931,25 @@
         <v>0</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>197.3</v>
+        <v>282.1</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="H28" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 23 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>MEMANTINA 10 MG COMPRIMIDO</t>
+          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
@@ -4993,10 +4964,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>180.1</v>
+        <v>354</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>181</v>
+        <v>288</v>
       </c>
       <c r="G29" s="19" t="n">
         <v>0</v>
@@ -5008,14 +4979,14 @@
       </c>
       <c r="I29" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 181 ud.</t>
+          <t>COMPRA EXTERNA 288 ud.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>CLOBAZAM 10 MG COMPRIMIDO</t>
+          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
@@ -5030,10 +5001,10 @@
         <v>0</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>170.1</v>
+        <v>197.3</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="G30" s="19" t="n">
         <v>0</v>
@@ -5045,14 +5016,14 @@
       </c>
       <c r="I30" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 77 ud.</t>
+          <t>COMPRA EXTERNA 29 ud.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
+          <t>MEMANTINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
@@ -5067,10 +5038,10 @@
         <v>0</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>135.7</v>
+        <v>180.1</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="G31" s="19" t="n">
         <v>0</v>
@@ -5082,14 +5053,14 @@
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 106 ud.</t>
+          <t>COMPRA EXTERNA 181 ud.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>CLOBAZAM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
@@ -5104,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>101.7</v>
+        <v>170.1</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G32" s="19" t="n">
         <v>0</v>
@@ -5119,14 +5090,14 @@
       </c>
       <c r="I32" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 86 ud.</t>
+          <t>COMPRA EXTERNA 77 ud.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
@@ -5141,10 +5112,10 @@
         <v>0</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>139.3</v>
+        <v>135.7</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="G33" s="19" t="n">
         <v>0</v>
@@ -5156,14 +5127,14 @@
       </c>
       <c r="I33" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 140 ud.</t>
+          <t>COMPRA EXTERNA 106 ud.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>FLUNARIZINA 10 MG COMPRIMIDO</t>
+          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
@@ -5178,25 +5149,29 @@
         <v>0</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>83.40000000000001</v>
+        <v>101.7</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H34" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I34" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 86 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>WARFARINA 5 MG COMPRIMIDO</t>
+          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
@@ -5211,25 +5186,29 @@
         <v>0</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>112.5</v>
+        <v>139.3</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="H35" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I35" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 140 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>KETOPROFENO 100 MG COMPRIMIDO</t>
+          <t>FLUNARIZINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
@@ -5244,17 +5223,17 @@
         <v>0</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>114.4</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>5400</v>
+        <v>1000</v>
       </c>
       <c r="H36" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I36" s="18" t="inlineStr"/>
@@ -5262,7 +5241,7 @@
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
+          <t>WARFARINA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
@@ -5277,29 +5256,25 @@
         <v>0</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>106</v>
+        <v>112.5</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="H37" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I37" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 62 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 30 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>KETOPROFENO 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
@@ -5314,29 +5289,25 @@
         <v>0</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>71.8</v>
+        <v>114.4</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="H38" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I38" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 72 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
@@ -5351,25 +5322,29 @@
         <v>0</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>56.6</v>
+        <v>106</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>7900</v>
+        <v>0</v>
       </c>
       <c r="H39" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I39" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 66 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
@@ -5384,25 +5359,29 @@
         <v>0</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>69.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="G40" s="19" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H40" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I40" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 72 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
@@ -5417,29 +5396,25 @@
         <v>0</v>
       </c>
       <c r="E41" s="19" t="n">
-        <v>20</v>
+        <v>56.6</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="H41" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I41" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 20 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>MORFINA 30 MG CAPSULA LIBERACION MODIFICADA</t>
+          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
@@ -5454,29 +5429,25 @@
         <v>0</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>21.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="G42" s="19" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H42" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I42" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 22 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>CALCITRIOL 0,5 MCG CAPSULA</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
@@ -5491,25 +5462,29 @@
         <v>0</v>
       </c>
       <c r="E43" s="19" t="n">
-        <v>36.7</v>
+        <v>20</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="H43" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I43" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 20 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>CALCITRIOL 0,5 MCG CAPSULA</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
@@ -5524,17 +5499,17 @@
         <v>0</v>
       </c>
       <c r="E44" s="19" t="n">
-        <v>33.3</v>
+        <v>36.7</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G44" s="19" t="n">
-        <v>1600</v>
+        <v>840</v>
       </c>
       <c r="H44" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 34 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I44" s="18" t="inlineStr"/>
@@ -5542,7 +5517,7 @@
     <row r="45">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
@@ -5557,29 +5532,25 @@
         <v>0</v>
       </c>
       <c r="E45" s="19" t="n">
-        <v>38.6</v>
+        <v>33.3</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="H45" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I45" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 38 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 34 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
@@ -5597,22 +5568,26 @@
         <v>38.6</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="G46" s="19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H46" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 9 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I46" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 38 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>TRAMADOL FRASCO GOTAS 100 MG/ML /10 ML</t>
+          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
@@ -5627,17 +5602,17 @@
         <v>0</v>
       </c>
       <c r="E47" s="19" t="n">
-        <v>37.3</v>
+        <v>38.6</v>
       </c>
       <c r="F47" s="19" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G47" s="19" t="n">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H47" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 13 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I47" s="18" t="inlineStr"/>
@@ -5645,7 +5620,7 @@
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>TRAMADOL FRASCO GOTAS 100 MG/ML /10 ML</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
@@ -5660,17 +5635,17 @@
         <v>0</v>
       </c>
       <c r="E48" s="19" t="n">
-        <v>22.8</v>
+        <v>37.3</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G48" s="19" t="n">
-        <v>2200</v>
+        <v>114</v>
       </c>
       <c r="H48" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I48" s="18" t="inlineStr"/>
@@ -5678,7 +5653,7 @@
     <row r="49">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
@@ -5693,29 +5668,25 @@
         <v>0</v>
       </c>
       <c r="E49" s="19" t="n">
-        <v>25.7</v>
+        <v>22.8</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="G49" s="19" t="n">
-        <v>50</v>
+        <v>2200</v>
       </c>
       <c r="H49" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I49" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 50 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>APIXABAN 2,5 MG CM</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
@@ -5730,25 +5701,29 @@
         <v>0</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>13.3</v>
+        <v>25.7</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G50" s="19" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="H50" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I50" s="18" t="inlineStr"/>
+          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 50 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>FENTANILO 25 MCG/HORA PARCHE</t>
+          <t>APIXABAN 2,5 MG CM</t>
         </is>
       </c>
       <c r="B51" s="18" t="inlineStr">
@@ -5763,29 +5738,25 @@
         <v>0</v>
       </c>
       <c r="E51" s="19" t="n">
-        <v>35.7</v>
+        <v>13.3</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H51" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I51" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 7 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>FENTANILO 25 MCG/HORA PARCHE</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
@@ -5800,25 +5771,29 @@
         <v>0</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>20.8</v>
+        <v>35.7</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G52" s="19" t="n">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="H52" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I52" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 7 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>UREA 10% CREMA 20 GR</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B53" s="18" t="inlineStr">
@@ -5833,29 +5808,25 @@
         <v>0</v>
       </c>
       <c r="E53" s="19" t="n">
-        <v>17.1</v>
+        <v>20.8</v>
       </c>
       <c r="F53" s="19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G53" s="19" t="n">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I53" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 18 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I53" s="18" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>RISPERIDONA 25 MG FA</t>
+          <t>UREA 10% CREMA 20 GR</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
@@ -5870,10 +5841,10 @@
         <v>0</v>
       </c>
       <c r="E54" s="19" t="n">
-        <v>18.7</v>
+        <v>17.1</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G54" s="19" t="n">
         <v>0</v>
@@ -5885,14 +5856,14 @@
       </c>
       <c r="I54" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 19 ud.</t>
+          <t>COMPRA EXTERNA 18 ud.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>VASELINA SOLIDA UNGUENTO</t>
+          <t>RISPERIDONA 25 MG FA</t>
         </is>
       </c>
       <c r="B55" s="18" t="inlineStr">
@@ -5907,10 +5878,10 @@
         <v>0</v>
       </c>
       <c r="E55" s="19" t="n">
-        <v>24.7</v>
+        <v>18.7</v>
       </c>
       <c r="F55" s="19" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G55" s="19" t="n">
         <v>0</v>
@@ -5922,14 +5893,14 @@
       </c>
       <c r="I55" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 25 ud.</t>
+          <t>COMPRA EXTERNA 19 ud.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>CLOTRIMAZOL 1% (10 MG/G) CREMA</t>
+          <t>VASELINA SOLIDA UNGUENTO</t>
         </is>
       </c>
       <c r="B56" s="18" t="inlineStr">
@@ -5944,25 +5915,29 @@
         <v>0</v>
       </c>
       <c r="E56" s="19" t="n">
-        <v>15.7</v>
+        <v>24.7</v>
       </c>
       <c r="F56" s="19" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G56" s="19" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H56" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I56" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I56" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 25 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+          <t>CLOTRIMAZOL 1% (10 MG/G) CREMA</t>
         </is>
       </c>
       <c r="B57" s="18" t="inlineStr">
@@ -5977,29 +5952,25 @@
         <v>0</v>
       </c>
       <c r="E57" s="19" t="n">
-        <v>32.1</v>
+        <v>15.7</v>
       </c>
       <c r="F57" s="19" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G57" s="19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I57" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 27 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
         </is>
       </c>
       <c r="B58" s="18" t="inlineStr">
@@ -6014,25 +5985,29 @@
         <v>0</v>
       </c>
       <c r="E58" s="19" t="n">
-        <v>13.8</v>
+        <v>32.1</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G58" s="19" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H58" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 14 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I58" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I58" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 28 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B59" s="18" t="inlineStr">
@@ -6047,29 +6022,25 @@
         <v>0</v>
       </c>
       <c r="E59" s="19" t="n">
-        <v>33.3</v>
+        <v>13.8</v>
       </c>
       <c r="F59" s="19" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G59" s="19" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H59" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I59" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 27 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 14 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I59" s="18" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>OXCARBAZEPINA 600 MG COMPRIMIDO</t>
+          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
         </is>
       </c>
       <c r="B60" s="18" t="inlineStr">
@@ -6084,10 +6055,10 @@
         <v>0</v>
       </c>
       <c r="E60" s="19" t="n">
-        <v>6.7</v>
+        <v>33.3</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G60" s="19" t="n">
         <v>0</v>
@@ -6099,14 +6070,14 @@
       </c>
       <c r="I60" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 7 ud.</t>
+          <t>COMPRA EXTERNA 27 ud.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>CINTA PARA DETERMINACION GLUCOSA USO CLINICO X 50 UD</t>
+          <t>OXCARBAZEPINA 600 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B61" s="18" t="inlineStr">
@@ -6121,10 +6092,10 @@
         <v>0</v>
       </c>
       <c r="E61" s="19" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="F61" s="19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G61" s="19" t="n">
         <v>0</v>
@@ -6136,14 +6107,14 @@
       </c>
       <c r="I61" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 5 ud.</t>
+          <t>COMPRA EXTERNA 7 ud.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>CEFTRIAXONA 1G FA</t>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO CLINICO X 50 UD</t>
         </is>
       </c>
       <c r="B62" s="18" t="inlineStr">
@@ -6158,25 +6129,29 @@
         <v>0</v>
       </c>
       <c r="E62" s="19" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G62" s="19" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="H62" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I62" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 5 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>CEFTRIAXONA 1G FA</t>
         </is>
       </c>
       <c r="B63" s="18" t="inlineStr">
@@ -6191,29 +6166,25 @@
         <v>0</v>
       </c>
       <c r="E63" s="19" t="n">
-        <v>12.8</v>
+        <v>8.6</v>
       </c>
       <c r="F63" s="19" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="G63" s="19" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="H63" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I63" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 9 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="18" t="inlineStr">
         <is>
-          <t>LORATADINA 5 MG/5 ML FC 120 ML</t>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
         </is>
       </c>
       <c r="B64" s="18" t="inlineStr">
@@ -6228,25 +6199,29 @@
         <v>0</v>
       </c>
       <c r="E64" s="19" t="n">
-        <v>2.1</v>
+        <v>12.8</v>
       </c>
       <c r="F64" s="19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G64" s="19" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="H64" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I64" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 9 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
+          <t>LORATADINA 5 MG/5 ML FC 120 ML</t>
         </is>
       </c>
       <c r="B65" s="18" t="inlineStr">
@@ -6261,29 +6236,25 @@
         <v>0</v>
       </c>
       <c r="E65" s="19" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="F65" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65" s="19" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="H65" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I65" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 3 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
+          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B66" s="18" t="inlineStr">
@@ -6298,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="E66" s="19" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="F66" s="19" t="n">
         <v>3</v>
@@ -6320,7 +6291,7 @@
     <row r="67">
       <c r="A67" s="18" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10 MG/2 ML (5 MG/ML) INYECTABLE</t>
+          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
         </is>
       </c>
       <c r="B67" s="18" t="inlineStr">
@@ -6335,25 +6306,29 @@
         <v>0</v>
       </c>
       <c r="E67" s="19" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="F67" s="19" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G67" s="19" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="H67" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 24 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I67" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I67" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 3 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>METOCLOPRAMIDA 10 MG/2 ML (5 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B68" s="18" t="inlineStr">
@@ -6368,17 +6343,17 @@
         <v>0</v>
       </c>
       <c r="E68" s="19" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F68" s="19" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G68" s="19" t="n">
-        <v>46</v>
+        <v>2400</v>
       </c>
       <c r="H68" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 24 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I68" s="18" t="inlineStr"/>
@@ -6386,7 +6361,7 @@
     <row r="69">
       <c r="A69" s="18" t="inlineStr">
         <is>
-          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B69" s="18" t="inlineStr">
@@ -6407,23 +6382,19 @@
         <v>1</v>
       </c>
       <c r="G69" s="19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H69" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I69" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>ACIDO VALPROICO 250 MG/5 ML FC 120 ML</t>
+          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
         </is>
       </c>
       <c r="B70" s="18" t="inlineStr">
@@ -6438,10 +6409,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="19" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="F70" s="19" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="G70" s="19" t="n">
         <v>0</v>
@@ -6453,14 +6424,14 @@
       </c>
       <c r="I70" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 120 ud.</t>
+          <t>COMPRA EXTERNA 1 ud.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>ETONOGESTREL 68 MG IMPLANTE</t>
+          <t>ACIDO VALPROICO 250 MG/5 ML FC 120 ML</t>
         </is>
       </c>
       <c r="B71" s="18" t="inlineStr">
@@ -6475,25 +6446,29 @@
         <v>0</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H71" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I71" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 120 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>HIERRO CARBOXIMALTOSA 500 MG/10 ML FA</t>
+          <t>ETONOGESTREL 68 MG IMPLANTE</t>
         </is>
       </c>
       <c r="B72" s="18" t="inlineStr">
@@ -6508,29 +6483,25 @@
         <v>0</v>
       </c>
       <c r="E72" s="19" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="F72" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" s="19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H72" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I72" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="18" t="inlineStr">
         <is>
-          <t>AGUA BIDESTILADA MATRAZ 500 ML</t>
+          <t>HIERRO CARBOXIMALTOSA 500 MG/10 ML FA</t>
         </is>
       </c>
       <c r="B73" s="18" t="inlineStr">
@@ -6545,25 +6516,29 @@
         <v>0</v>
       </c>
       <c r="E73" s="19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F73" s="19" t="n">
         <v>1</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="H73" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I73" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="18" t="inlineStr">
         <is>
-          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
+          <t>AGUA BIDESTILADA MATRAZ 500 ML</t>
         </is>
       </c>
       <c r="B74" s="18" t="inlineStr">
@@ -6584,7 +6559,7 @@
         <v>1</v>
       </c>
       <c r="G74" s="19" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="H74" s="18" t="inlineStr">
         <is>
@@ -6596,7 +6571,7 @@
     <row r="75">
       <c r="A75" s="18" t="inlineStr">
         <is>
-          <t>FITOMENADIONA 10 MG/ML INTRAMUSCULAR</t>
+          <t>BETAMETASONA FOSFATO DISODICO 4 MG/1ML AM</t>
         </is>
       </c>
       <c r="B75" s="18" t="inlineStr">
@@ -6617,7 +6592,7 @@
         <v>1</v>
       </c>
       <c r="G75" s="19" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H75" s="18" t="inlineStr">
         <is>
@@ -6629,7 +6604,7 @@
     <row r="76">
       <c r="A76" s="18" t="inlineStr">
         <is>
-          <t>GENTAMICINA 80 MG/2 ML (40 MG/ML) INYECTABLE</t>
+          <t>FITOMENADIONA 10 MG/ML INTRAMUSCULAR</t>
         </is>
       </c>
       <c r="B76" s="18" t="inlineStr">
@@ -6650,7 +6625,7 @@
         <v>1</v>
       </c>
       <c r="G76" s="19" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H76" s="18" t="inlineStr">
         <is>
@@ -6662,7 +6637,7 @@
     <row r="77">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
+          <t>GENTAMICINA 80 MG/2 ML (40 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B77" s="18" t="inlineStr">
@@ -6677,29 +6652,25 @@
         <v>0</v>
       </c>
       <c r="E77" s="19" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="F77" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77" s="19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H77" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I77" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 2 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="18" t="inlineStr">
         <is>
-          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
+          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
         </is>
       </c>
       <c r="B78" s="18" t="inlineStr">
@@ -6720,19 +6691,23 @@
         <v>2</v>
       </c>
       <c r="G78" s="19" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="H78" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I78" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I78" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 2 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="18" t="inlineStr">
         <is>
-          <t>ALTEPLASA 50 MG FA UD</t>
+          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
         </is>
       </c>
       <c r="B79" s="18" t="inlineStr">
@@ -6747,29 +6722,25 @@
         <v>0</v>
       </c>
       <c r="E79" s="19" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="F79" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" s="19" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="H79" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I79" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I79" s="18" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="18" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 0,25 MG/ML SOL. P/NEBULIZAR FC</t>
+          <t>ALTEPLASA 50 MG FA UD</t>
         </is>
       </c>
       <c r="B80" s="18" t="inlineStr">
@@ -6790,19 +6761,23 @@
         <v>1</v>
       </c>
       <c r="G80" s="19" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H80" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I80" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="18" t="inlineStr">
         <is>
-          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
+          <t>BROMURO DE IPRATROPIO 0,25 MG/ML SOL. P/NEBULIZAR FC</t>
         </is>
       </c>
       <c r="B81" s="18" t="inlineStr">
@@ -6823,7 +6798,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="19" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H81" s="18" t="inlineStr">
         <is>
@@ -6835,7 +6810,7 @@
     <row r="82">
       <c r="A82" s="18" t="inlineStr">
         <is>
-          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
+          <t>DICLOFENACO 75 MG/3ML SOL. IM AM</t>
         </is>
       </c>
       <c r="B82" s="18" t="inlineStr">
@@ -6856,7 +6831,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H82" s="18" t="inlineStr">
         <is>
@@ -6868,7 +6843,7 @@
     <row r="83">
       <c r="A83" s="18" t="inlineStr">
         <is>
-          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+          <t>LINEZOLID 600 MG/300 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B83" s="18" t="inlineStr">
@@ -6889,52 +6864,52 @@
         <v>1</v>
       </c>
       <c r="G83" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I83" s="18" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL 5MG/ML SOL.NEBU FRA 20ML</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F84" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="19" t="n">
         <v>115</v>
       </c>
-      <c r="H83" s="18" t="inlineStr">
+      <c r="H84" s="18" t="inlineStr">
         <is>
           <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="I83" s="18" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
-        </is>
-      </c>
-      <c r="B84" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C84" s="21" t="n">
-        <v>1700</v>
-      </c>
-      <c r="D84" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E84" s="21" t="n">
-        <v>6317.1</v>
-      </c>
-      <c r="F84" s="21" t="n">
-        <v>1140</v>
-      </c>
-      <c r="G84" s="21" t="n">
-        <v>45000</v>
-      </c>
-      <c r="H84" s="20" t="inlineStr">
-        <is>
-          <t>TRASPASAR 1140 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I84" s="20" t="inlineStr"/>
+      <c r="I84" s="18" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>PREGABALINA 75 MG CAPSULA</t>
+          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
         </is>
       </c>
       <c r="B85" s="20" t="inlineStr">
@@ -6943,35 +6918,31 @@
         </is>
       </c>
       <c r="C85" s="21" t="n">
-        <v>217</v>
+        <v>1700</v>
       </c>
       <c r="D85" s="21" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="E85" s="21" t="n">
-        <v>5789.9</v>
+        <v>6317.1</v>
       </c>
       <c r="F85" s="21" t="n">
-        <v>4333</v>
+        <v>1200</v>
       </c>
       <c r="G85" s="21" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="H85" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I85" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 4333 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1200 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I85" s="20" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
+          <t>PREGABALINA 75 MG CAPSULA</t>
         </is>
       </c>
       <c r="B86" s="20" t="inlineStr">
@@ -6980,16 +6951,16 @@
         </is>
       </c>
       <c r="C86" s="21" t="n">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="D86" s="21" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="E86" s="21" t="n">
-        <v>1537.7</v>
+        <v>5789.9</v>
       </c>
       <c r="F86" s="21" t="n">
-        <v>1062</v>
+        <v>4513</v>
       </c>
       <c r="G86" s="21" t="n">
         <v>0</v>
@@ -7001,14 +6972,14 @@
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1062 ud.</t>
+          <t>COMPRA EXTERNA 4513 ud.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>DULOXETINA 30 MG CAPSULA</t>
+          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
         </is>
       </c>
       <c r="B87" s="20" t="inlineStr">
@@ -7017,31 +6988,35 @@
         </is>
       </c>
       <c r="C87" s="21" t="n">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="D87" s="21" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="E87" s="21" t="n">
-        <v>1208</v>
+        <v>1537.7</v>
       </c>
       <c r="F87" s="21" t="n">
-        <v>90</v>
+        <v>1092</v>
       </c>
       <c r="G87" s="21" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 90 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I87" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I87" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1092 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>RIFAXIMINA 200 MG CP</t>
+          <t>DULOXETINA 30 MG CAPSULA</t>
         </is>
       </c>
       <c r="B88" s="20" t="inlineStr">
@@ -7050,23 +7025,23 @@
         </is>
       </c>
       <c r="C88" s="21" t="n">
-        <v>264</v>
+        <v>150</v>
       </c>
       <c r="D88" s="21" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="E88" s="21" t="n">
-        <v>828.8</v>
+        <v>1208</v>
       </c>
       <c r="F88" s="21" t="n">
-        <v>384</v>
+        <v>120</v>
       </c>
       <c r="G88" s="21" t="n">
-        <v>23424</v>
+        <v>1980</v>
       </c>
       <c r="H88" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 384 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I88" s="20" t="inlineStr"/>
@@ -7195,7 +7170,7 @@
         <v>4981.7</v>
       </c>
       <c r="F92" s="27" t="n">
-        <v>660</v>
+        <v>720</v>
       </c>
       <c r="G92" s="27" t="n">
         <v>0</v>
@@ -7207,7 +7182,7 @@
       </c>
       <c r="I92" s="26" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 660 ud.</t>
+          <t>COMPRA EXTERNA 720 ud.</t>
         </is>
       </c>
     </row>
@@ -7232,14 +7207,14 @@
         <v>3484.6</v>
       </c>
       <c r="F93" s="27" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="G93" s="27" t="n">
         <v>44340</v>
       </c>
       <c r="H93" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 180 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 240 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I93" s="26" t="inlineStr"/>
@@ -7298,14 +7273,14 @@
         <v>4995.5</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>10290</v>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 90 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr"/>
@@ -9509,7 +9484,7 @@
         <v>0</v>
       </c>
       <c r="G171" s="29" t="n">
-        <v>6030</v>
+        <v>5970</v>
       </c>
       <c r="H171" s="28" t="inlineStr"/>
       <c r="I171" s="28" t="inlineStr"/>
@@ -9865,7 +9840,7 @@
     <row r="184">
       <c r="A184" s="28" t="inlineStr">
         <is>
-          <t>ACIDO FOLICO CM 1 MG</t>
+          <t>PROPANOLOL 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B184" s="28" t="inlineStr">
@@ -9880,13 +9855,13 @@
         <v>0</v>
       </c>
       <c r="E184" s="29" t="n">
-        <v>336.2</v>
+        <v>352.9</v>
       </c>
       <c r="F184" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G184" s="29" t="n">
-        <v>13640</v>
+        <v>5000</v>
       </c>
       <c r="H184" s="28" t="inlineStr"/>
       <c r="I184" s="28" t="inlineStr"/>
@@ -9894,7 +9869,7 @@
     <row r="185">
       <c r="A185" s="28" t="inlineStr">
         <is>
-          <t>PROPANOLOL 10 MG COMPRIMIDO</t>
+          <t>DIAZEPAM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B185" s="28" t="inlineStr">
@@ -9903,19 +9878,19 @@
         </is>
       </c>
       <c r="C185" s="29" t="n">
-        <v>945</v>
+        <v>0</v>
       </c>
       <c r="D185" s="29" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E185" s="29" t="n">
-        <v>352.9</v>
+        <v>260.6</v>
       </c>
       <c r="F185" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G185" s="29" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H185" s="28" t="inlineStr"/>
       <c r="I185" s="28" t="inlineStr"/>
@@ -9923,7 +9898,7 @@
     <row r="186">
       <c r="A186" s="28" t="inlineStr">
         <is>
-          <t>DIAZEPAM 10 MG COMPRIMIDO</t>
+          <t>LORAZEPAM 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B186" s="28" t="inlineStr">
@@ -9932,13 +9907,13 @@
         </is>
       </c>
       <c r="C186" s="29" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D186" s="29" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E186" s="29" t="n">
-        <v>260.6</v>
+        <v>378.5</v>
       </c>
       <c r="F186" s="29" t="n">
         <v>0</v>
@@ -9952,7 +9927,7 @@
     <row r="187">
       <c r="A187" s="28" t="inlineStr">
         <is>
-          <t>LORAZEPAM 2 MG COMPRIMIDO</t>
+          <t>BISOPROLOL 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B187" s="28" t="inlineStr">
@@ -9961,13 +9936,13 @@
         </is>
       </c>
       <c r="C187" s="29" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D187" s="29" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E187" s="29" t="n">
-        <v>378.5</v>
+        <v>218.5</v>
       </c>
       <c r="F187" s="29" t="n">
         <v>0</v>
@@ -9981,7 +9956,7 @@
     <row r="188">
       <c r="A188" s="28" t="inlineStr">
         <is>
-          <t>BISOPROLOL 5 MG COMPRIMIDO</t>
+          <t>COLCHICINA 0,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B188" s="28" t="inlineStr">
@@ -9990,19 +9965,19 @@
         </is>
       </c>
       <c r="C188" s="29" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D188" s="29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E188" s="29" t="n">
-        <v>218.5</v>
+        <v>219.8</v>
       </c>
       <c r="F188" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G188" s="29" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="H188" s="28" t="inlineStr"/>
       <c r="I188" s="28" t="inlineStr"/>
@@ -10010,7 +9985,7 @@
     <row r="189">
       <c r="A189" s="28" t="inlineStr">
         <is>
-          <t>COLCHICINA 0,5 MG COMPRIMIDO</t>
+          <t>TRIMEBUTINA 200 MG CM /CR</t>
         </is>
       </c>
       <c r="B189" s="28" t="inlineStr">
@@ -10019,19 +9994,19 @@
         </is>
       </c>
       <c r="C189" s="29" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="D189" s="29" t="n">
-        <v>5</v>
+        <v>26.8</v>
       </c>
       <c r="E189" s="29" t="n">
-        <v>219.8</v>
+        <v>379.9</v>
       </c>
       <c r="F189" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G189" s="29" t="n">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="H189" s="28" t="inlineStr"/>
       <c r="I189" s="28" t="inlineStr"/>
@@ -10039,7 +10014,7 @@
     <row r="190">
       <c r="A190" s="28" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200 MG CM /CR</t>
+          <t>PIRIDOSTIGMINA 60 MG COMPRIMIDOS O GRAGEAS.</t>
         </is>
       </c>
       <c r="B190" s="28" t="inlineStr">
@@ -10048,19 +10023,19 @@
         </is>
       </c>
       <c r="C190" s="29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D190" s="29" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="E190" s="29" t="n">
-        <v>379.9</v>
+        <v>95.8</v>
       </c>
       <c r="F190" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G190" s="29" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="H190" s="28" t="inlineStr"/>
       <c r="I190" s="28" t="inlineStr"/>
@@ -10068,7 +10043,7 @@
     <row r="191">
       <c r="A191" s="28" t="inlineStr">
         <is>
-          <t>PIRIDOSTIGMINA 60 MG COMPRIMIDOS O GRAGEAS.</t>
+          <t>SACUBITRILO VALSARTAN 100 MG</t>
         </is>
       </c>
       <c r="B191" s="28" t="inlineStr">
@@ -10083,13 +10058,13 @@
         <v>0</v>
       </c>
       <c r="E191" s="29" t="n">
-        <v>95.8</v>
+        <v>140.3</v>
       </c>
       <c r="F191" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G191" s="29" t="n">
-        <v>1100</v>
+        <v>3300</v>
       </c>
       <c r="H191" s="28" t="inlineStr"/>
       <c r="I191" s="28" t="inlineStr"/>
@@ -10097,7 +10072,7 @@
     <row r="192">
       <c r="A192" s="28" t="inlineStr">
         <is>
-          <t>SACUBITRILO VALSARTAN 100 MG</t>
+          <t>ONDANSETRON 8 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B192" s="28" t="inlineStr">
@@ -10106,19 +10081,19 @@
         </is>
       </c>
       <c r="C192" s="29" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D192" s="29" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="E192" s="29" t="n">
-        <v>140.3</v>
+        <v>237.4</v>
       </c>
       <c r="F192" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G192" s="29" t="n">
-        <v>3300</v>
+        <v>9950</v>
       </c>
       <c r="H192" s="28" t="inlineStr"/>
       <c r="I192" s="28" t="inlineStr"/>
@@ -10126,7 +10101,7 @@
     <row r="193">
       <c r="A193" s="28" t="inlineStr">
         <is>
-          <t>ONDANSETRON 8 MG COMPRIMIDO</t>
+          <t>PREDNISONA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B193" s="28" t="inlineStr">
@@ -10135,19 +10110,19 @@
         </is>
       </c>
       <c r="C193" s="29" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="D193" s="29" t="n">
-        <v>8.5</v>
+        <v>29.2</v>
       </c>
       <c r="E193" s="29" t="n">
-        <v>237.4</v>
+        <v>268.1</v>
       </c>
       <c r="F193" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G193" s="29" t="n">
-        <v>9950</v>
+        <v>1700</v>
       </c>
       <c r="H193" s="28" t="inlineStr"/>
       <c r="I193" s="28" t="inlineStr"/>
@@ -10155,7 +10130,7 @@
     <row r="194">
       <c r="A194" s="28" t="inlineStr">
         <is>
-          <t>PREDNISONA 20 MG COMPRIMIDO</t>
+          <t>LORATADINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B194" s="28" t="inlineStr">
@@ -10167,16 +10142,16 @@
         <v>1000</v>
       </c>
       <c r="D194" s="29" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="E194" s="29" t="n">
-        <v>268.1</v>
+        <v>168.9</v>
       </c>
       <c r="F194" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G194" s="29" t="n">
-        <v>1700</v>
+        <v>3000</v>
       </c>
       <c r="H194" s="28" t="inlineStr"/>
       <c r="I194" s="28" t="inlineStr"/>
@@ -10184,7 +10159,7 @@
     <row r="195">
       <c r="A195" s="28" t="inlineStr">
         <is>
-          <t>LORATADINA 10 MG COMPRIMIDO</t>
+          <t>MULTIVITAMINICO COMPRIMIDO</t>
         </is>
       </c>
       <c r="B195" s="28" t="inlineStr">
@@ -10193,19 +10168,19 @@
         </is>
       </c>
       <c r="C195" s="29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D195" s="29" t="n">
-        <v>29.3</v>
+        <v>0</v>
       </c>
       <c r="E195" s="29" t="n">
-        <v>168.9</v>
+        <v>282.9</v>
       </c>
       <c r="F195" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G195" s="29" t="n">
-        <v>3000</v>
+        <v>2100</v>
       </c>
       <c r="H195" s="28" t="inlineStr"/>
       <c r="I195" s="28" t="inlineStr"/>
@@ -10213,7 +10188,7 @@
     <row r="196">
       <c r="A196" s="28" t="inlineStr">
         <is>
-          <t>MULTIVITAMINICO COMPRIMIDO</t>
+          <t>HEPARINA SODICA 25.000 U.I./5 ML FA/JRP</t>
         </is>
       </c>
       <c r="B196" s="28" t="inlineStr">
@@ -10228,13 +10203,13 @@
         <v>0</v>
       </c>
       <c r="E196" s="29" t="n">
-        <v>282.9</v>
+        <v>211.3</v>
       </c>
       <c r="F196" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G196" s="29" t="n">
-        <v>2100</v>
+        <v>2450</v>
       </c>
       <c r="H196" s="28" t="inlineStr"/>
       <c r="I196" s="28" t="inlineStr"/>
@@ -10242,7 +10217,7 @@
     <row r="197">
       <c r="A197" s="28" t="inlineStr">
         <is>
-          <t>HEPARINA SODICA 25.000 U.I./5 ML FA/JRP</t>
+          <t>IBUPROFENO 400 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B197" s="28" t="inlineStr">
@@ -10251,19 +10226,19 @@
         </is>
       </c>
       <c r="C197" s="29" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D197" s="29" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="E197" s="29" t="n">
-        <v>211.3</v>
+        <v>233</v>
       </c>
       <c r="F197" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G197" s="29" t="n">
-        <v>2450</v>
+        <v>2000</v>
       </c>
       <c r="H197" s="28" t="inlineStr"/>
       <c r="I197" s="28" t="inlineStr"/>
@@ -10271,7 +10246,7 @@
     <row r="198">
       <c r="A198" s="28" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400 MG COMPRIMIDO</t>
+          <t>HALOPERIDOL 1 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B198" s="28" t="inlineStr">
@@ -10280,19 +10255,19 @@
         </is>
       </c>
       <c r="C198" s="29" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D198" s="29" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="E198" s="29" t="n">
-        <v>233</v>
+        <v>274.5</v>
       </c>
       <c r="F198" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G198" s="29" t="n">
-        <v>2000</v>
+        <v>3840</v>
       </c>
       <c r="H198" s="28" t="inlineStr"/>
       <c r="I198" s="28" t="inlineStr"/>
@@ -10300,7 +10275,7 @@
     <row r="199">
       <c r="A199" s="28" t="inlineStr">
         <is>
-          <t>HALOPERIDOL 1 MG COMPRIMIDO</t>
+          <t>ATROPINA SULFATO 0,5 MG + PAPAVERINA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B199" s="28" t="inlineStr">
@@ -10309,19 +10284,19 @@
         </is>
       </c>
       <c r="C199" s="29" t="n">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="D199" s="29" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="E199" s="29" t="n">
-        <v>274.5</v>
+        <v>236.8</v>
       </c>
       <c r="F199" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G199" s="29" t="n">
-        <v>3840</v>
+        <v>13560</v>
       </c>
       <c r="H199" s="28" t="inlineStr"/>
       <c r="I199" s="28" t="inlineStr"/>
@@ -10329,7 +10304,7 @@
     <row r="200">
       <c r="A200" s="28" t="inlineStr">
         <is>
-          <t>ATROPINA SULFATO 0,5 MG + PAPAVERINA 40 MG COMPRIMIDO</t>
+          <t>TOPIRAMATO 100 MG CM</t>
         </is>
       </c>
       <c r="B200" s="28" t="inlineStr">
@@ -10338,19 +10313,19 @@
         </is>
       </c>
       <c r="C200" s="29" t="n">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="D200" s="29" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="E200" s="29" t="n">
-        <v>236.8</v>
+        <v>154.7</v>
       </c>
       <c r="F200" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G200" s="29" t="n">
-        <v>13560</v>
+        <v>112</v>
       </c>
       <c r="H200" s="28" t="inlineStr"/>
       <c r="I200" s="28" t="inlineStr"/>
@@ -10358,7 +10333,7 @@
     <row r="201">
       <c r="A201" s="28" t="inlineStr">
         <is>
-          <t>TOPIRAMATO 100 MG CM</t>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B201" s="28" t="inlineStr">
@@ -10373,13 +10348,13 @@
         <v>0</v>
       </c>
       <c r="E201" s="29" t="n">
-        <v>154.7</v>
+        <v>99.2</v>
       </c>
       <c r="F201" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G201" s="29" t="n">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="H201" s="28" t="inlineStr"/>
       <c r="I201" s="28" t="inlineStr"/>
@@ -10387,7 +10362,7 @@
     <row r="202">
       <c r="A202" s="28" t="inlineStr">
         <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
+          <t>METILFENIDATO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B202" s="28" t="inlineStr">
@@ -10402,13 +10377,13 @@
         <v>0</v>
       </c>
       <c r="E202" s="29" t="n">
-        <v>99.2</v>
+        <v>387.7</v>
       </c>
       <c r="F202" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G202" s="29" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H202" s="28" t="inlineStr"/>
       <c r="I202" s="28" t="inlineStr"/>
@@ -10416,7 +10391,7 @@
     <row r="203">
       <c r="A203" s="28" t="inlineStr">
         <is>
-          <t>METILFENIDATO 10 MG COMPRIMIDO</t>
+          <t>CLORPROMAZINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B203" s="28" t="inlineStr">
@@ -10431,7 +10406,7 @@
         <v>0</v>
       </c>
       <c r="E203" s="29" t="n">
-        <v>387.7</v>
+        <v>227</v>
       </c>
       <c r="F203" s="29" t="n">
         <v>0</v>
@@ -10445,7 +10420,7 @@
     <row r="204">
       <c r="A204" s="28" t="inlineStr">
         <is>
-          <t>CLORPROMAZINA 100 MG COMPRIMIDO</t>
+          <t>CITALOPRAM 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B204" s="28" t="inlineStr">
@@ -10454,19 +10429,19 @@
         </is>
       </c>
       <c r="C204" s="29" t="n">
-        <v>0</v>
+        <v>1950</v>
       </c>
       <c r="D204" s="29" t="n">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="E204" s="29" t="n">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="F204" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G204" s="29" t="n">
-        <v>0</v>
+        <v>11640</v>
       </c>
       <c r="H204" s="28" t="inlineStr"/>
       <c r="I204" s="28" t="inlineStr"/>
@@ -10474,7 +10449,7 @@
     <row r="205">
       <c r="A205" s="28" t="inlineStr">
         <is>
-          <t>CITALOPRAM 20 MG COMPRIMIDO</t>
+          <t>FAMOTIDINA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B205" s="28" t="inlineStr">
@@ -10483,19 +10458,19 @@
         </is>
       </c>
       <c r="C205" s="29" t="n">
-        <v>1950</v>
+        <v>0</v>
       </c>
       <c r="D205" s="29" t="n">
-        <v>69.2</v>
+        <v>0</v>
       </c>
       <c r="E205" s="29" t="n">
-        <v>279</v>
+        <v>138.8</v>
       </c>
       <c r="F205" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G205" s="29" t="n">
-        <v>11640</v>
+        <v>500</v>
       </c>
       <c r="H205" s="28" t="inlineStr"/>
       <c r="I205" s="28" t="inlineStr"/>
@@ -10503,7 +10478,7 @@
     <row r="206">
       <c r="A206" s="28" t="inlineStr">
         <is>
-          <t>FAMOTIDINA 40 MG COMPRIMIDO</t>
+          <t>MIRTAZAPINA 30 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B206" s="28" t="inlineStr">
@@ -10512,19 +10487,19 @@
         </is>
       </c>
       <c r="C206" s="29" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D206" s="29" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="E206" s="29" t="n">
-        <v>138.8</v>
+        <v>238.4</v>
       </c>
       <c r="F206" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G206" s="29" t="n">
-        <v>500</v>
+        <v>3210</v>
       </c>
       <c r="H206" s="28" t="inlineStr"/>
       <c r="I206" s="28" t="inlineStr"/>
@@ -10532,7 +10507,7 @@
     <row r="207">
       <c r="A207" s="28" t="inlineStr">
         <is>
-          <t>MIRTAZAPINA 30 MG COMPRIMIDO</t>
+          <t>CLORFENAMINA 4 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B207" s="28" t="inlineStr">
@@ -10541,19 +10516,19 @@
         </is>
       </c>
       <c r="C207" s="29" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="D207" s="29" t="n">
-        <v>21.6</v>
+        <v>47.5</v>
       </c>
       <c r="E207" s="29" t="n">
-        <v>238.4</v>
+        <v>325.1</v>
       </c>
       <c r="F207" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G207" s="29" t="n">
-        <v>3210</v>
+        <v>3880</v>
       </c>
       <c r="H207" s="28" t="inlineStr"/>
       <c r="I207" s="28" t="inlineStr"/>
@@ -10561,7 +10536,7 @@
     <row r="208">
       <c r="A208" s="28" t="inlineStr">
         <is>
-          <t>CLORFENAMINA 4 MG COMPRIMIDO</t>
+          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
         </is>
       </c>
       <c r="B208" s="28" t="inlineStr">
@@ -10570,19 +10545,19 @@
         </is>
       </c>
       <c r="C208" s="29" t="n">
-        <v>1300</v>
+        <v>197</v>
       </c>
       <c r="D208" s="29" t="n">
-        <v>47.5</v>
+        <v>7.4</v>
       </c>
       <c r="E208" s="29" t="n">
-        <v>325.1</v>
+        <v>225.9</v>
       </c>
       <c r="F208" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G208" s="29" t="n">
-        <v>3880</v>
+        <v>400</v>
       </c>
       <c r="H208" s="28" t="inlineStr"/>
       <c r="I208" s="28" t="inlineStr"/>
@@ -10590,7 +10565,7 @@
     <row r="209">
       <c r="A209" s="28" t="inlineStr">
         <is>
-          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
+          <t>PRAMIPEXOL 0,25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B209" s="28" t="inlineStr">
@@ -10599,19 +10574,19 @@
         </is>
       </c>
       <c r="C209" s="29" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="D209" s="29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E209" s="29" t="n">
-        <v>225.9</v>
+        <v>133.5</v>
       </c>
       <c r="F209" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G209" s="29" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
       <c r="H209" s="28" t="inlineStr"/>
       <c r="I209" s="28" t="inlineStr"/>
@@ -10619,7 +10594,7 @@
     <row r="210">
       <c r="A210" s="28" t="inlineStr">
         <is>
-          <t>PRAMIPEXOL 0,25 MG COMPRIMIDO</t>
+          <t>TRAMADOL 100 MG CM L.P</t>
         </is>
       </c>
       <c r="B210" s="28" t="inlineStr">
@@ -10628,19 +10603,19 @@
         </is>
       </c>
       <c r="C210" s="29" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D210" s="29" t="n">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="E210" s="29" t="n">
-        <v>133.5</v>
+        <v>144.3</v>
       </c>
       <c r="F210" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G210" s="29" t="n">
-        <v>750</v>
+        <v>15520</v>
       </c>
       <c r="H210" s="28" t="inlineStr"/>
       <c r="I210" s="28" t="inlineStr"/>
@@ -10648,7 +10623,7 @@
     <row r="211">
       <c r="A211" s="28" t="inlineStr">
         <is>
-          <t>TRAMADOL 100 MG CM L.P</t>
+          <t>CETIRIZINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B211" s="28" t="inlineStr">
@@ -10657,19 +10632,19 @@
         </is>
       </c>
       <c r="C211" s="29" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="D211" s="29" t="n">
-        <v>23.3</v>
+        <v>6.2</v>
       </c>
       <c r="E211" s="29" t="n">
-        <v>144.3</v>
+        <v>287.5</v>
       </c>
       <c r="F211" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G211" s="29" t="n">
-        <v>15520</v>
+        <v>0</v>
       </c>
       <c r="H211" s="28" t="inlineStr"/>
       <c r="I211" s="28" t="inlineStr"/>
@@ -10677,7 +10652,7 @@
     <row r="212">
       <c r="A212" s="28" t="inlineStr">
         <is>
-          <t>CETIRIZINA 10 MG COMPRIMIDO</t>
+          <t>DIGOXINA 0,25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B212" s="28" t="inlineStr">
@@ -10686,19 +10661,19 @@
         </is>
       </c>
       <c r="C212" s="29" t="n">
-        <v>150</v>
+        <v>960</v>
       </c>
       <c r="D212" s="29" t="n">
-        <v>6.2</v>
+        <v>40.2</v>
       </c>
       <c r="E212" s="29" t="n">
-        <v>287.5</v>
+        <v>235.4</v>
       </c>
       <c r="F212" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G212" s="29" t="n">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="H212" s="28" t="inlineStr"/>
       <c r="I212" s="28" t="inlineStr"/>
@@ -10706,7 +10681,7 @@
     <row r="213">
       <c r="A213" s="28" t="inlineStr">
         <is>
-          <t>DIGOXINA 0,25 MG COMPRIMIDO</t>
+          <t>ERITROPOYETINA 4.000 UI</t>
         </is>
       </c>
       <c r="B213" s="28" t="inlineStr">
@@ -10715,19 +10690,19 @@
         </is>
       </c>
       <c r="C213" s="29" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="D213" s="29" t="n">
-        <v>40.2</v>
+        <v>0</v>
       </c>
       <c r="E213" s="29" t="n">
-        <v>235.4</v>
+        <v>144.5</v>
       </c>
       <c r="F213" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G213" s="29" t="n">
-        <v>4800</v>
+        <v>1450</v>
       </c>
       <c r="H213" s="28" t="inlineStr"/>
       <c r="I213" s="28" t="inlineStr"/>
@@ -10735,7 +10710,7 @@
     <row r="214">
       <c r="A214" s="28" t="inlineStr">
         <is>
-          <t>ERITROPOYETINA 4.000 UI</t>
+          <t>SEVELAMER 800 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B214" s="28" t="inlineStr">
@@ -10744,19 +10719,19 @@
         </is>
       </c>
       <c r="C214" s="29" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D214" s="29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E214" s="29" t="n">
-        <v>144.5</v>
+        <v>209.8</v>
       </c>
       <c r="F214" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G214" s="29" t="n">
-        <v>1450</v>
+        <v>4680</v>
       </c>
       <c r="H214" s="28" t="inlineStr"/>
       <c r="I214" s="28" t="inlineStr"/>
@@ -10764,7 +10739,7 @@
     <row r="215">
       <c r="A215" s="28" t="inlineStr">
         <is>
-          <t>SEVELAMER 800 MG COMPRIMIDO</t>
+          <t>HALOPERIDOL 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B215" s="28" t="inlineStr">
@@ -10773,19 +10748,19 @@
         </is>
       </c>
       <c r="C215" s="29" t="n">
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="D215" s="29" t="n">
-        <v>8</v>
+        <v>26.8</v>
       </c>
       <c r="E215" s="29" t="n">
-        <v>209.8</v>
+        <v>192.8</v>
       </c>
       <c r="F215" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G215" s="29" t="n">
-        <v>4680</v>
+        <v>5460</v>
       </c>
       <c r="H215" s="28" t="inlineStr"/>
       <c r="I215" s="28" t="inlineStr"/>
@@ -10793,7 +10768,7 @@
     <row r="216">
       <c r="A216" s="28" t="inlineStr">
         <is>
-          <t>HALOPERIDOL 5 MG COMPRIMIDO</t>
+          <t>GEMFIBROZILO 600 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B216" s="28" t="inlineStr">
@@ -10802,19 +10777,19 @@
         </is>
       </c>
       <c r="C216" s="29" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D216" s="29" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="E216" s="29" t="n">
-        <v>192.8</v>
+        <v>331.4</v>
       </c>
       <c r="F216" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G216" s="29" t="n">
-        <v>5460</v>
+        <v>3000</v>
       </c>
       <c r="H216" s="28" t="inlineStr"/>
       <c r="I216" s="28" t="inlineStr"/>
@@ -10822,7 +10797,7 @@
     <row r="217">
       <c r="A217" s="28" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO 600 MG COMPRIMIDO</t>
+          <t>BUPRENORFINA 35 MCG/HR PARC</t>
         </is>
       </c>
       <c r="B217" s="28" t="inlineStr">
@@ -10837,13 +10812,13 @@
         <v>0</v>
       </c>
       <c r="E217" s="29" t="n">
-        <v>331.4</v>
+        <v>138.6</v>
       </c>
       <c r="F217" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G217" s="29" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H217" s="28" t="inlineStr"/>
       <c r="I217" s="28" t="inlineStr"/>
@@ -10851,7 +10826,7 @@
     <row r="218">
       <c r="A218" s="28" t="inlineStr">
         <is>
-          <t>BUPRENORFINA 35 MCG/HR PARC</t>
+          <t>ARIPIPRAZOL 15 MG CM</t>
         </is>
       </c>
       <c r="B218" s="28" t="inlineStr">
@@ -10866,7 +10841,7 @@
         <v>0</v>
       </c>
       <c r="E218" s="29" t="n">
-        <v>138.6</v>
+        <v>228.3</v>
       </c>
       <c r="F218" s="29" t="n">
         <v>0</v>
@@ -10880,7 +10855,7 @@
     <row r="219">
       <c r="A219" s="28" t="inlineStr">
         <is>
-          <t>ARIPIPRAZOL 15 MG CM</t>
+          <t>LEVODOPA 250 MG - CARBIDOPA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B219" s="28" t="inlineStr">
@@ -10889,19 +10864,19 @@
         </is>
       </c>
       <c r="C219" s="29" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="D219" s="29" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E219" s="29" t="n">
-        <v>228.3</v>
+        <v>173.4</v>
       </c>
       <c r="F219" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G219" s="29" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="H219" s="28" t="inlineStr"/>
       <c r="I219" s="28" t="inlineStr"/>
@@ -10909,7 +10884,7 @@
     <row r="220">
       <c r="A220" s="28" t="inlineStr">
         <is>
-          <t>LEVODOPA 250 MG - CARBIDOPA 25 MG COMPRIMIDO</t>
+          <t>ACETAZOLAMIDA CM 250 MG</t>
         </is>
       </c>
       <c r="B220" s="28" t="inlineStr">
@@ -10918,19 +10893,19 @@
         </is>
       </c>
       <c r="C220" s="29" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="D220" s="29" t="n">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="E220" s="29" t="n">
-        <v>173.4</v>
+        <v>235.3</v>
       </c>
       <c r="F220" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G220" s="29" t="n">
-        <v>1140</v>
+        <v>2100</v>
       </c>
       <c r="H220" s="28" t="inlineStr"/>
       <c r="I220" s="28" t="inlineStr"/>
@@ -10938,7 +10913,7 @@
     <row r="221">
       <c r="A221" s="28" t="inlineStr">
         <is>
-          <t>ACETAZOLAMIDA CM 250 MG</t>
+          <t>MONTELUKAST 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B221" s="28" t="inlineStr">
@@ -10947,19 +10922,19 @@
         </is>
       </c>
       <c r="C221" s="29" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D221" s="29" t="n">
-        <v>5.2</v>
+        <v>15.7</v>
       </c>
       <c r="E221" s="29" t="n">
-        <v>235.3</v>
+        <v>226.5</v>
       </c>
       <c r="F221" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G221" s="29" t="n">
-        <v>2100</v>
+        <v>2160</v>
       </c>
       <c r="H221" s="28" t="inlineStr"/>
       <c r="I221" s="28" t="inlineStr"/>
@@ -10967,7 +10942,7 @@
     <row r="222">
       <c r="A222" s="28" t="inlineStr">
         <is>
-          <t>MONTELUKAST 10 MG COMPRIMIDO</t>
+          <t>FENITOINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B222" s="28" t="inlineStr">
@@ -10976,19 +10951,19 @@
         </is>
       </c>
       <c r="C222" s="29" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D222" s="29" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="E222" s="29" t="n">
-        <v>226.5</v>
+        <v>199.9</v>
       </c>
       <c r="F222" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G222" s="29" t="n">
-        <v>2160</v>
+        <v>5520</v>
       </c>
       <c r="H222" s="28" t="inlineStr"/>
       <c r="I222" s="28" t="inlineStr"/>
@@ -10996,7 +10971,7 @@
     <row r="223">
       <c r="A223" s="28" t="inlineStr">
         <is>
-          <t>FENITOINA 100 MG COMPRIMIDO</t>
+          <t>AMOXICILINA 500 MG CAPSULA</t>
         </is>
       </c>
       <c r="B223" s="28" t="inlineStr">
@@ -11011,13 +10986,13 @@
         <v>0</v>
       </c>
       <c r="E223" s="29" t="n">
-        <v>199.9</v>
+        <v>189.4</v>
       </c>
       <c r="F223" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G223" s="29" t="n">
-        <v>5520</v>
+        <v>6687</v>
       </c>
       <c r="H223" s="28" t="inlineStr"/>
       <c r="I223" s="28" t="inlineStr"/>
@@ -11025,7 +11000,7 @@
     <row r="224">
       <c r="A224" s="28" t="inlineStr">
         <is>
-          <t>AMOXICILINA 500 MG CAPSULA</t>
+          <t>MESALAZINA 500 MG SUPOSITORIO.</t>
         </is>
       </c>
       <c r="B224" s="28" t="inlineStr">
@@ -11034,19 +11009,19 @@
         </is>
       </c>
       <c r="C224" s="29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D224" s="29" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="E224" s="29" t="n">
-        <v>189.4</v>
+        <v>98.3</v>
       </c>
       <c r="F224" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G224" s="29" t="n">
-        <v>6687</v>
+        <v>1200</v>
       </c>
       <c r="H224" s="28" t="inlineStr"/>
       <c r="I224" s="28" t="inlineStr"/>
@@ -11054,7 +11029,7 @@
     <row r="225">
       <c r="A225" s="28" t="inlineStr">
         <is>
-          <t>MESALAZINA 500 MG SUPOSITORIO.</t>
+          <t>CLORURO DE POTASIO 600 MG (POTASIO 8 MEQ) COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B225" s="28" t="inlineStr">
@@ -11063,19 +11038,19 @@
         </is>
       </c>
       <c r="C225" s="29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D225" s="29" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="E225" s="29" t="n">
-        <v>98.3</v>
+        <v>49.8</v>
       </c>
       <c r="F225" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G225" s="29" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H225" s="28" t="inlineStr"/>
       <c r="I225" s="28" t="inlineStr"/>
@@ -11083,7 +11058,7 @@
     <row r="226">
       <c r="A226" s="28" t="inlineStr">
         <is>
-          <t>CLORURO DE POTASIO 600 MG (POTASIO 8 MEQ) COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>FERROSO SULFATO 200 MG CM</t>
         </is>
       </c>
       <c r="B226" s="28" t="inlineStr">
@@ -11098,13 +11073,13 @@
         <v>0</v>
       </c>
       <c r="E226" s="29" t="n">
-        <v>49.8</v>
+        <v>191.8</v>
       </c>
       <c r="F226" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G226" s="29" t="n">
-        <v>1000</v>
+        <v>22000</v>
       </c>
       <c r="H226" s="28" t="inlineStr"/>
       <c r="I226" s="28" t="inlineStr"/>
@@ -11112,7 +11087,7 @@
     <row r="227">
       <c r="A227" s="28" t="inlineStr">
         <is>
-          <t>FERROSO SULFATO 200 MG CM</t>
+          <t>METRONIDAZOL 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B227" s="28" t="inlineStr">
@@ -11127,13 +11102,13 @@
         <v>0</v>
       </c>
       <c r="E227" s="29" t="n">
-        <v>191.8</v>
+        <v>150.7</v>
       </c>
       <c r="F227" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G227" s="29" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="H227" s="28" t="inlineStr"/>
       <c r="I227" s="28" t="inlineStr"/>
@@ -11141,7 +11116,7 @@
     <row r="228">
       <c r="A228" s="28" t="inlineStr">
         <is>
-          <t>METRONIDAZOL 500 MG COMPRIMIDO</t>
+          <t>SILDENAFIL CM 50 MG</t>
         </is>
       </c>
       <c r="B228" s="28" t="inlineStr">
@@ -11150,19 +11125,19 @@
         </is>
       </c>
       <c r="C228" s="29" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D228" s="29" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="E228" s="29" t="n">
-        <v>150.7</v>
+        <v>155</v>
       </c>
       <c r="F228" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G228" s="29" t="n">
-        <v>8000</v>
+        <v>880</v>
       </c>
       <c r="H228" s="28" t="inlineStr"/>
       <c r="I228" s="28" t="inlineStr"/>
@@ -11170,7 +11145,7 @@
     <row r="229">
       <c r="A229" s="28" t="inlineStr">
         <is>
-          <t>SILDENAFIL CM 50 MG</t>
+          <t>ALPRAZOLAM CM 0,5 MG</t>
         </is>
       </c>
       <c r="B229" s="28" t="inlineStr">
@@ -11179,19 +11154,19 @@
         </is>
       </c>
       <c r="C229" s="29" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D229" s="29" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="E229" s="29" t="n">
-        <v>155</v>
+        <v>185.8</v>
       </c>
       <c r="F229" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G229" s="29" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="H229" s="28" t="inlineStr"/>
       <c r="I229" s="28" t="inlineStr"/>
@@ -11199,7 +11174,7 @@
     <row r="230">
       <c r="A230" s="28" t="inlineStr">
         <is>
-          <t>ALPRAZOLAM CM 0,5 MG</t>
+          <t>PROGESTERONA 200 MG CM MICRONIZADA</t>
         </is>
       </c>
       <c r="B230" s="28" t="inlineStr">
@@ -11208,19 +11183,19 @@
         </is>
       </c>
       <c r="C230" s="29" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D230" s="29" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="E230" s="29" t="n">
-        <v>185.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F230" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G230" s="29" t="n">
-        <v>0</v>
+        <v>2640</v>
       </c>
       <c r="H230" s="28" t="inlineStr"/>
       <c r="I230" s="28" t="inlineStr"/>
@@ -11228,7 +11203,7 @@
     <row r="231">
       <c r="A231" s="28" t="inlineStr">
         <is>
-          <t>PROGESTERONA 200 MG CM MICRONIZADA</t>
+          <t>AMOXICILINA 875 MG - ACIDO CLAVULANICO 125 MG COMPRIMIDO.</t>
         </is>
       </c>
       <c r="B231" s="28" t="inlineStr">
@@ -11237,19 +11212,19 @@
         </is>
       </c>
       <c r="C231" s="29" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D231" s="29" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="E231" s="29" t="n">
-        <v>91.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="F231" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G231" s="29" t="n">
-        <v>2640</v>
+        <v>6500</v>
       </c>
       <c r="H231" s="28" t="inlineStr"/>
       <c r="I231" s="28" t="inlineStr"/>
@@ -11257,7 +11232,7 @@
     <row r="232">
       <c r="A232" s="28" t="inlineStr">
         <is>
-          <t>AMOXICILINA 875 MG - ACIDO CLAVULANICO 125 MG COMPRIMIDO.</t>
+          <t>CALCITRIOL 0,25 MCG CP</t>
         </is>
       </c>
       <c r="B232" s="28" t="inlineStr">
@@ -11266,19 +11241,19 @@
         </is>
       </c>
       <c r="C232" s="29" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D232" s="29" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="E232" s="29" t="n">
-        <v>89.5</v>
+        <v>116.6</v>
       </c>
       <c r="F232" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G232" s="29" t="n">
-        <v>6500</v>
+        <v>600</v>
       </c>
       <c r="H232" s="28" t="inlineStr"/>
       <c r="I232" s="28" t="inlineStr"/>
@@ -11286,7 +11261,7 @@
     <row r="233">
       <c r="A233" s="28" t="inlineStr">
         <is>
-          <t>CALCITRIOL 0,25 MCG CP</t>
+          <t>NITROFURANTOINA MACROCRISTALES 100 MG CAP</t>
         </is>
       </c>
       <c r="B233" s="28" t="inlineStr">
@@ -11295,19 +11270,19 @@
         </is>
       </c>
       <c r="C233" s="29" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="D233" s="29" t="n">
-        <v>21.2</v>
+        <v>94.7</v>
       </c>
       <c r="E233" s="29" t="n">
-        <v>116.6</v>
+        <v>125.6</v>
       </c>
       <c r="F233" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G233" s="29" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="H233" s="28" t="inlineStr"/>
       <c r="I233" s="28" t="inlineStr"/>
@@ -11315,7 +11290,7 @@
     <row r="234">
       <c r="A234" s="28" t="inlineStr">
         <is>
-          <t>NITROFURANTOINA MACROCRISTALES 100 MG CAP</t>
+          <t>AMANTADINA 100 MG CAPSULA</t>
         </is>
       </c>
       <c r="B234" s="28" t="inlineStr">
@@ -11324,19 +11299,19 @@
         </is>
       </c>
       <c r="C234" s="29" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="D234" s="29" t="n">
-        <v>94.7</v>
+        <v>0</v>
       </c>
       <c r="E234" s="29" t="n">
-        <v>125.6</v>
+        <v>140.1</v>
       </c>
       <c r="F234" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G234" s="29" t="n">
-        <v>2000</v>
+        <v>2910</v>
       </c>
       <c r="H234" s="28" t="inlineStr"/>
       <c r="I234" s="28" t="inlineStr"/>
@@ -11344,7 +11319,7 @@
     <row r="235">
       <c r="A235" s="28" t="inlineStr">
         <is>
-          <t>AMANTADINA 100 MG CAPSULA</t>
+          <t>METILPREDNISOLONA 4 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B235" s="28" t="inlineStr">
@@ -11353,19 +11328,19 @@
         </is>
       </c>
       <c r="C235" s="29" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D235" s="29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E235" s="29" t="n">
-        <v>140.1</v>
+        <v>122.6</v>
       </c>
       <c r="F235" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G235" s="29" t="n">
-        <v>2910</v>
+        <v>140</v>
       </c>
       <c r="H235" s="28" t="inlineStr"/>
       <c r="I235" s="28" t="inlineStr"/>
@@ -11373,7 +11348,7 @@
     <row r="236">
       <c r="A236" s="28" t="inlineStr">
         <is>
-          <t>METILPREDNISOLONA 4 MG COMPRIMIDO</t>
+          <t>DIFENIDOL CM 25 MG</t>
         </is>
       </c>
       <c r="B236" s="28" t="inlineStr">
@@ -11382,19 +11357,19 @@
         </is>
       </c>
       <c r="C236" s="29" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D236" s="29" t="n">
-        <v>16</v>
+        <v>32.7</v>
       </c>
       <c r="E236" s="29" t="n">
-        <v>122.6</v>
+        <v>84.5</v>
       </c>
       <c r="F236" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G236" s="29" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="H236" s="28" t="inlineStr"/>
       <c r="I236" s="28" t="inlineStr"/>
@@ -11402,7 +11377,7 @@
     <row r="237">
       <c r="A237" s="28" t="inlineStr">
         <is>
-          <t>DIFENIDOL CM 25 MG</t>
+          <t>HIDROCORTISONA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B237" s="28" t="inlineStr">
@@ -11411,19 +11386,19 @@
         </is>
       </c>
       <c r="C237" s="29" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D237" s="29" t="n">
-        <v>32.7</v>
+        <v>16.4</v>
       </c>
       <c r="E237" s="29" t="n">
-        <v>84.5</v>
+        <v>119.4</v>
       </c>
       <c r="F237" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G237" s="29" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="H237" s="28" t="inlineStr"/>
       <c r="I237" s="28" t="inlineStr"/>
@@ -11431,7 +11406,7 @@
     <row r="238">
       <c r="A238" s="28" t="inlineStr">
         <is>
-          <t>HIDROCORTISONA 20 MG COMPRIMIDO</t>
+          <t>LATANOPROST 0,005% COLIRIO</t>
         </is>
       </c>
       <c r="B238" s="28" t="inlineStr">
@@ -11440,19 +11415,19 @@
         </is>
       </c>
       <c r="C238" s="29" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D238" s="29" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="E238" s="29" t="n">
-        <v>119.4</v>
+        <v>100.8</v>
       </c>
       <c r="F238" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G238" s="29" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="H238" s="28" t="inlineStr"/>
       <c r="I238" s="28" t="inlineStr"/>
@@ -11460,7 +11435,7 @@
     <row r="239">
       <c r="A239" s="28" t="inlineStr">
         <is>
-          <t>LATANOPROST 0,005% COLIRIO</t>
+          <t>DEXAMETASONA 4 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B239" s="28" t="inlineStr">
@@ -11469,19 +11444,19 @@
         </is>
       </c>
       <c r="C239" s="29" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D239" s="29" t="n">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="E239" s="29" t="n">
-        <v>100.8</v>
+        <v>41.3</v>
       </c>
       <c r="F239" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G239" s="29" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="H239" s="28" t="inlineStr"/>
       <c r="I239" s="28" t="inlineStr"/>
@@ -11489,7 +11464,7 @@
     <row r="240">
       <c r="A240" s="28" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG COMPRIMIDO</t>
+          <t>VITAMINAS B1/B6/B12 100 MG/100 MG/10 MG AMP</t>
         </is>
       </c>
       <c r="B240" s="28" t="inlineStr">
@@ -11501,16 +11476,16 @@
         <v>200</v>
       </c>
       <c r="D240" s="29" t="n">
-        <v>17.2</v>
+        <v>18.1</v>
       </c>
       <c r="E240" s="29" t="n">
-        <v>41.3</v>
+        <v>72</v>
       </c>
       <c r="F240" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G240" s="29" t="n">
-        <v>2400</v>
+        <v>900</v>
       </c>
       <c r="H240" s="28" t="inlineStr"/>
       <c r="I240" s="28" t="inlineStr"/>
@@ -11518,7 +11493,7 @@
     <row r="241">
       <c r="A241" s="28" t="inlineStr">
         <is>
-          <t>VITAMINAS B1/B6/B12 100 MG/100 MG/10 MG AMP</t>
+          <t>VITAMINA D3 50.000 UI SOBRE</t>
         </is>
       </c>
       <c r="B241" s="28" t="inlineStr">
@@ -11527,19 +11502,19 @@
         </is>
       </c>
       <c r="C241" s="29" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="D241" s="29" t="n">
-        <v>18.1</v>
+        <v>12.7</v>
       </c>
       <c r="E241" s="29" t="n">
-        <v>72</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F241" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G241" s="29" t="n">
-        <v>900</v>
+        <v>4090</v>
       </c>
       <c r="H241" s="28" t="inlineStr"/>
       <c r="I241" s="28" t="inlineStr"/>
@@ -11547,7 +11522,7 @@
     <row r="242">
       <c r="A242" s="28" t="inlineStr">
         <is>
-          <t>VITAMINA D3 50.000 UI SOBRE</t>
+          <t>PRIMIDONA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B242" s="28" t="inlineStr">
@@ -11556,19 +11531,19 @@
         </is>
       </c>
       <c r="C242" s="29" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="D242" s="29" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="E242" s="29" t="n">
-        <v>90.59999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="F242" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G242" s="29" t="n">
-        <v>4090</v>
+        <v>200</v>
       </c>
       <c r="H242" s="28" t="inlineStr"/>
       <c r="I242" s="28" t="inlineStr"/>
@@ -11576,7 +11551,7 @@
     <row r="243">
       <c r="A243" s="28" t="inlineStr">
         <is>
-          <t>PRIMIDONA 250 MG COMPRIMIDO</t>
+          <t>SULFAMETOXAZOL 800 MG + TRIMETOPRIMA 160 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B243" s="28" t="inlineStr">
@@ -11585,19 +11560,19 @@
         </is>
       </c>
       <c r="C243" s="29" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="D243" s="29" t="n">
-        <v>0</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E243" s="29" t="n">
-        <v>6.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F243" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G243" s="29" t="n">
-        <v>200</v>
+        <v>4000</v>
       </c>
       <c r="H243" s="28" t="inlineStr"/>
       <c r="I243" s="28" t="inlineStr"/>
@@ -11605,7 +11580,7 @@
     <row r="244">
       <c r="A244" s="28" t="inlineStr">
         <is>
-          <t>SULFAMETOXAZOL 800 MG + TRIMETOPRIMA 160 MG COMPRIMIDO</t>
+          <t>PRAMIPEXOL 1 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B244" s="28" t="inlineStr">
@@ -11614,19 +11589,19 @@
         </is>
       </c>
       <c r="C244" s="29" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="D244" s="29" t="n">
-        <v>65.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="E244" s="29" t="n">
-        <v>85.09999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="F244" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G244" s="29" t="n">
-        <v>4000</v>
+        <v>930</v>
       </c>
       <c r="H244" s="28" t="inlineStr"/>
       <c r="I244" s="28" t="inlineStr"/>
@@ -11634,7 +11609,7 @@
     <row r="245">
       <c r="A245" s="28" t="inlineStr">
         <is>
-          <t>PRAMIPEXOL 1 MG COMPRIMIDO</t>
+          <t>TRIMETAZIDINA 35 MG CM LIBERACION PROLONGADA (XR)</t>
         </is>
       </c>
       <c r="B245" s="28" t="inlineStr">
@@ -11649,13 +11624,13 @@
         <v>0</v>
       </c>
       <c r="E245" s="29" t="n">
-        <v>58.2</v>
+        <v>126.6</v>
       </c>
       <c r="F245" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G245" s="29" t="n">
-        <v>930</v>
+        <v>750</v>
       </c>
       <c r="H245" s="28" t="inlineStr"/>
       <c r="I245" s="28" t="inlineStr"/>
@@ -11663,7 +11638,7 @@
     <row r="246">
       <c r="A246" s="28" t="inlineStr">
         <is>
-          <t>TRIMETAZIDINA 35 MG CM LIBERACION PROLONGADA (XR)</t>
+          <t>MOMETASONA 50 MCG/DOSIS SUSPENSION NASAL</t>
         </is>
       </c>
       <c r="B246" s="28" t="inlineStr">
@@ -11672,19 +11647,19 @@
         </is>
       </c>
       <c r="C246" s="29" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D246" s="29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="E246" s="29" t="n">
-        <v>126.6</v>
+        <v>77.5</v>
       </c>
       <c r="F246" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G246" s="29" t="n">
-        <v>750</v>
+        <v>109</v>
       </c>
       <c r="H246" s="28" t="inlineStr"/>
       <c r="I246" s="28" t="inlineStr"/>
@@ -11692,7 +11667,7 @@
     <row r="247">
       <c r="A247" s="28" t="inlineStr">
         <is>
-          <t>MOMETASONA 50 MCG/DOSIS SUSPENSION NASAL</t>
+          <t>ATENOLOL 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B247" s="28" t="inlineStr">
@@ -11701,19 +11676,19 @@
         </is>
       </c>
       <c r="C247" s="29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D247" s="29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="E247" s="29" t="n">
-        <v>77.5</v>
+        <v>145.1</v>
       </c>
       <c r="F247" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G247" s="29" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H247" s="28" t="inlineStr"/>
       <c r="I247" s="28" t="inlineStr"/>
@@ -11721,7 +11696,7 @@
     <row r="248">
       <c r="A248" s="28" t="inlineStr">
         <is>
-          <t>ATENOLOL 50 MG COMPRIMIDO</t>
+          <t>LISDEXANFETAMINA 50 MG CM</t>
         </is>
       </c>
       <c r="B248" s="28" t="inlineStr">
@@ -11736,7 +11711,7 @@
         <v>0</v>
       </c>
       <c r="E248" s="29" t="n">
-        <v>145.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F248" s="29" t="n">
         <v>0</v>
@@ -11750,7 +11725,7 @@
     <row r="249">
       <c r="A249" s="28" t="inlineStr">
         <is>
-          <t>LISDEXANFETAMINA 50 MG CM</t>
+          <t>POLIESTIRENO SULFONATO CALCICO 15 GR SO</t>
         </is>
       </c>
       <c r="B249" s="28" t="inlineStr">
@@ -11765,13 +11740,13 @@
         <v>0</v>
       </c>
       <c r="E249" s="29" t="n">
-        <v>90.09999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="F249" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G249" s="29" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="H249" s="28" t="inlineStr"/>
       <c r="I249" s="28" t="inlineStr"/>
@@ -11779,7 +11754,7 @@
     <row r="250">
       <c r="A250" s="28" t="inlineStr">
         <is>
-          <t>POLIESTIRENO SULFONATO CALCICO 15 GR SO</t>
+          <t>LISDEXANFETAMINA 70 MG CAP UD</t>
         </is>
       </c>
       <c r="B250" s="28" t="inlineStr">
@@ -11794,13 +11769,13 @@
         <v>0</v>
       </c>
       <c r="E250" s="29" t="n">
-        <v>16.7</v>
+        <v>98.7</v>
       </c>
       <c r="F250" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G250" s="29" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="H250" s="28" t="inlineStr"/>
       <c r="I250" s="28" t="inlineStr"/>
@@ -11808,7 +11783,7 @@
     <row r="251">
       <c r="A251" s="28" t="inlineStr">
         <is>
-          <t>LISDEXANFETAMINA 70 MG CAP UD</t>
+          <t>FLUDROCORTISONA 100 MCG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B251" s="28" t="inlineStr">
@@ -11817,19 +11792,19 @@
         </is>
       </c>
       <c r="C251" s="29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D251" s="29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E251" s="29" t="n">
-        <v>98.7</v>
+        <v>70</v>
       </c>
       <c r="F251" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G251" s="29" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H251" s="28" t="inlineStr"/>
       <c r="I251" s="28" t="inlineStr"/>
@@ -11837,7 +11812,7 @@
     <row r="252">
       <c r="A252" s="28" t="inlineStr">
         <is>
-          <t>FLUDROCORTISONA 100 MCG COMPRIMIDO</t>
+          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B252" s="28" t="inlineStr">
@@ -11846,19 +11821,19 @@
         </is>
       </c>
       <c r="C252" s="29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D252" s="29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E252" s="29" t="n">
-        <v>70</v>
+        <v>43.3</v>
       </c>
       <c r="F252" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G252" s="29" t="n">
-        <v>500</v>
+        <v>1260</v>
       </c>
       <c r="H252" s="28" t="inlineStr"/>
       <c r="I252" s="28" t="inlineStr"/>
@@ -11866,7 +11841,7 @@
     <row r="253">
       <c r="A253" s="28" t="inlineStr">
         <is>
-          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
+          <t>HIDROXICARBAMIDA 500 MG CAPSULA</t>
         </is>
       </c>
       <c r="B253" s="28" t="inlineStr">
@@ -11881,13 +11856,13 @@
         <v>0</v>
       </c>
       <c r="E253" s="29" t="n">
-        <v>43.3</v>
+        <v>98.3</v>
       </c>
       <c r="F253" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G253" s="29" t="n">
-        <v>1260</v>
+        <v>1100</v>
       </c>
       <c r="H253" s="28" t="inlineStr"/>
       <c r="I253" s="28" t="inlineStr"/>
@@ -11895,7 +11870,7 @@
     <row r="254">
       <c r="A254" s="28" t="inlineStr">
         <is>
-          <t>HIDROXICARBAMIDA 500 MG CAPSULA</t>
+          <t>ESTRIOL 0,5 MG OVULO</t>
         </is>
       </c>
       <c r="B254" s="28" t="inlineStr">
@@ -11904,19 +11879,19 @@
         </is>
       </c>
       <c r="C254" s="29" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="D254" s="29" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="E254" s="29" t="n">
-        <v>98.3</v>
+        <v>66</v>
       </c>
       <c r="F254" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G254" s="29" t="n">
-        <v>1100</v>
+        <v>690</v>
       </c>
       <c r="H254" s="28" t="inlineStr"/>
       <c r="I254" s="28" t="inlineStr"/>
@@ -11924,7 +11899,7 @@
     <row r="255">
       <c r="A255" s="28" t="inlineStr">
         <is>
-          <t>ESTRIOL 0,5 MG OVULO</t>
+          <t>LINAGLIPTINA 5 MG CM</t>
         </is>
       </c>
       <c r="B255" s="28" t="inlineStr">
@@ -11933,19 +11908,19 @@
         </is>
       </c>
       <c r="C255" s="29" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="D255" s="29" t="n">
-        <v>26.2</v>
+        <v>0</v>
       </c>
       <c r="E255" s="29" t="n">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F255" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G255" s="29" t="n">
-        <v>690</v>
+        <v>120</v>
       </c>
       <c r="H255" s="28" t="inlineStr"/>
       <c r="I255" s="28" t="inlineStr"/>
@@ -11953,7 +11928,7 @@
     <row r="256">
       <c r="A256" s="28" t="inlineStr">
         <is>
-          <t>LINAGLIPTINA 5 MG CM</t>
+          <t>INSULINA HUMANA NPH 1000 UI/10 ML (100 UI/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B256" s="28" t="inlineStr">
@@ -11968,13 +11943,13 @@
         <v>0</v>
       </c>
       <c r="E256" s="29" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F256" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G256" s="29" t="n">
-        <v>120</v>
+        <v>410</v>
       </c>
       <c r="H256" s="28" t="inlineStr"/>
       <c r="I256" s="28" t="inlineStr"/>
@@ -11982,7 +11957,7 @@
     <row r="257">
       <c r="A257" s="28" t="inlineStr">
         <is>
-          <t>INSULINA HUMANA NPH 1000 UI/10 ML (100 UI/ML) INYECTABLE</t>
+          <t>MODAFINILO 200 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B257" s="28" t="inlineStr">
@@ -11991,19 +11966,19 @@
         </is>
       </c>
       <c r="C257" s="29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D257" s="29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E257" s="29" t="n">
-        <v>42</v>
+        <v>91.7</v>
       </c>
       <c r="F257" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G257" s="29" t="n">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="H257" s="28" t="inlineStr"/>
       <c r="I257" s="28" t="inlineStr"/>
@@ -12011,7 +11986,7 @@
     <row r="258">
       <c r="A258" s="28" t="inlineStr">
         <is>
-          <t>MODAFINILO 200 MG COMPRIMIDO</t>
+          <t>VIGABATRINA 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B258" s="28" t="inlineStr">
@@ -12020,19 +11995,19 @@
         </is>
       </c>
       <c r="C258" s="29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D258" s="29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E258" s="29" t="n">
-        <v>91.7</v>
+        <v>13.3</v>
       </c>
       <c r="F258" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G258" s="29" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="H258" s="28" t="inlineStr"/>
       <c r="I258" s="28" t="inlineStr"/>
@@ -12040,7 +12015,7 @@
     <row r="259">
       <c r="A259" s="28" t="inlineStr">
         <is>
-          <t>VIGABATRINA 500 MG COMPRIMIDO</t>
+          <t>CEFADROXILO 500 MG CAPSULA</t>
         </is>
       </c>
       <c r="B259" s="28" t="inlineStr">
@@ -12049,19 +12024,19 @@
         </is>
       </c>
       <c r="C259" s="29" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="D259" s="29" t="n">
-        <v>0</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E259" s="29" t="n">
-        <v>13.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F259" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G259" s="29" t="n">
-        <v>300</v>
+        <v>3800</v>
       </c>
       <c r="H259" s="28" t="inlineStr"/>
       <c r="I259" s="28" t="inlineStr"/>
@@ -12069,7 +12044,7 @@
     <row r="260">
       <c r="A260" s="28" t="inlineStr">
         <is>
-          <t>CEFADROXILO 500 MG CAPSULA</t>
+          <t>CIANOCOBALAMINA AMP 0,1 MG/1 ML</t>
         </is>
       </c>
       <c r="B260" s="28" t="inlineStr">
@@ -12078,19 +12053,19 @@
         </is>
       </c>
       <c r="C260" s="29" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="D260" s="29" t="n">
-        <v>64.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="E260" s="29" t="n">
-        <v>76.90000000000001</v>
+        <v>25.8</v>
       </c>
       <c r="F260" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G260" s="29" t="n">
-        <v>3800</v>
+        <v>1300</v>
       </c>
       <c r="H260" s="28" t="inlineStr"/>
       <c r="I260" s="28" t="inlineStr"/>
@@ -12098,7 +12073,7 @@
     <row r="261">
       <c r="A261" s="28" t="inlineStr">
         <is>
-          <t>CIANOCOBALAMINA AMP 0,1 MG/1 ML</t>
+          <t>DORZOLAMIDA + TIMOLOL 2G/0,5G/100 ML SOL. OFT. FC 5 ML</t>
         </is>
       </c>
       <c r="B261" s="28" t="inlineStr">
@@ -12107,19 +12082,19 @@
         </is>
       </c>
       <c r="C261" s="29" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D261" s="29" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E261" s="29" t="n">
-        <v>25.8</v>
+        <v>47.3</v>
       </c>
       <c r="F261" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G261" s="29" t="n">
-        <v>1300</v>
+        <v>475</v>
       </c>
       <c r="H261" s="28" t="inlineStr"/>
       <c r="I261" s="28" t="inlineStr"/>
@@ -12127,7 +12102,7 @@
     <row r="262">
       <c r="A262" s="28" t="inlineStr">
         <is>
-          <t>DORZOLAMIDA + TIMOLOL 2G/0,5G/100 ML SOL. OFT. FC 5 ML</t>
+          <t>MORFINA 30 MG CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B262" s="28" t="inlineStr">
@@ -12136,19 +12111,19 @@
         </is>
       </c>
       <c r="C262" s="29" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D262" s="29" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E262" s="29" t="n">
-        <v>47.3</v>
+        <v>21.7</v>
       </c>
       <c r="F262" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G262" s="29" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H262" s="28" t="inlineStr"/>
       <c r="I262" s="28" t="inlineStr"/>
@@ -12455,10 +12430,10 @@
         </is>
       </c>
       <c r="C273" s="29" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D273" s="29" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="E273" s="29" t="n">
         <v>22.8</v>
@@ -17950,10 +17925,10 @@
         </is>
       </c>
       <c r="C20" s="21" t="n">
-        <v>557</v>
+        <v>377</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>2854.1</v>
@@ -17965,17 +17940,17 @@
         <v>3482.9</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>698</v>
+        <v>878</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>698</v>
+        <v>878</v>
       </c>
       <c r="J20" s="21" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 698 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 878 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr"/>
@@ -18025,7 +18000,7 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -18034,32 +18009,32 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>37.3</v>
+        <v>110.6</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>38.8</v>
+        <v>131</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="J22" s="21" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 24 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 65 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr"/>
@@ -18067,90 +18042,90 @@
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="D23" s="21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G23" s="21" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="J23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>TRASPASAR 24 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
           <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C24" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D23" s="21" t="n">
+      <c r="D24" s="21" t="n">
         <v>1.3</v>
       </c>
-      <c r="E23" s="21" t="n">
+      <c r="E24" s="21" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="F23" s="21" t="n">
+      <c r="F24" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="21" t="n">
+      <c r="G24" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="H23" s="21" t="n">
+      <c r="H24" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="I23" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="21" t="n">
+      <c r="I24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="K23" s="20" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
-      <c r="L23" s="20" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 6 ud.</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>LAGRIMAS ARTIFICIALES 0,4% X 10 ML</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>110.6</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>131</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 49 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -18394,7 +18369,7 @@
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
+          <t>PREGABALINA 75 MG CAPSULA</t>
         </is>
       </c>
       <c r="B4" s="18" t="inlineStr">
@@ -18403,22 +18378,22 @@
         </is>
       </c>
       <c r="C4" s="19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D4" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>4791.5</v>
+        <v>5789.9</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>4.2</v>
+        <v>42.4</v>
       </c>
       <c r="G4" s="19" t="n">
-        <v>3229.9</v>
+        <v>3482.9</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>272</v>
+        <v>4513</v>
       </c>
       <c r="I4" s="19" t="n">
         <v>0</v>
@@ -18430,14 +18405,14 @@
       </c>
       <c r="K4" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 272 ud.</t>
+          <t>COMPRA EXTERNA 4513 ud.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
         </is>
       </c>
       <c r="B5" s="18" t="inlineStr">
@@ -18452,31 +18427,35 @@
         <v>0</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>3722.6</v>
+        <v>4791.5</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>85.40000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>2610.6</v>
+        <v>3229.9</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>200</v>
+        <v>462</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="J5" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 200 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K5" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 462 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>VILDAGLIPTINA 50 MG CM</t>
+          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
         </is>
       </c>
       <c r="B6" s="18" t="inlineStr">
@@ -18491,35 +18470,31 @@
         <v>0</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>4162.7</v>
+        <v>3722.6</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>8.300000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>2638.3</v>
+        <v>2610.6</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>4200</v>
+        <v>300</v>
       </c>
       <c r="I6" s="19" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="J6" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 4200 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 300 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>ISOSORBIDA DINITRATO 10 MG COMPRIMIDO</t>
+          <t>VILDAGLIPTINA 50 MG CM</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
@@ -18534,16 +18509,16 @@
         <v>0</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>2577.7</v>
+        <v>4162.7</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>186</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>1751.5</v>
+        <v>2638.3</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>2578</v>
+        <v>4200</v>
       </c>
       <c r="I7" s="19" t="n">
         <v>0</v>
@@ -18555,14 +18530,14 @@
       </c>
       <c r="K7" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2578 ud.</t>
+          <t>COMPRA EXTERNA 4200 ud.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>ESOMEPRAZOL 20 MG CM</t>
+          <t>ISOSORBIDA DINITRATO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
@@ -18577,16 +18552,16 @@
         <v>0</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>2652.7</v>
+        <v>2577.7</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>8.300000000000001</v>
+        <v>186</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>1819.6</v>
+        <v>1751.5</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>2653</v>
+        <v>2578</v>
       </c>
       <c r="I8" s="19" t="n">
         <v>0</v>
@@ -18598,14 +18573,14 @@
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2653 ud.</t>
+          <t>COMPRA EXTERNA 2578 ud.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
+          <t>ESOMEPRAZOL 20 MG CM</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
@@ -18620,16 +18595,16 @@
         <v>0</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>2479.7</v>
+        <v>2652.7</v>
       </c>
       <c r="F9" s="19" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>1269.9</v>
+        <v>1819.6</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>2480</v>
+        <v>2653</v>
       </c>
       <c r="I9" s="19" t="n">
         <v>0</v>
@@ -18641,14 +18616,14 @@
       </c>
       <c r="K9" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2480 ud.</t>
+          <t>COMPRA EXTERNA 2653 ud.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>EZETIMIBE 10 MG CM UNIDAD</t>
+          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
         </is>
       </c>
       <c r="B10" s="18" t="inlineStr">
@@ -18663,16 +18638,16 @@
         <v>0</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>1714.8</v>
+        <v>2479.7</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>1029.2</v>
+        <v>1269.9</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>1715</v>
+        <v>2480</v>
       </c>
       <c r="I10" s="19" t="n">
         <v>0</v>
@@ -18684,14 +18659,14 @@
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1715 ud.</t>
+          <t>COMPRA EXTERNA 2480 ud.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
+          <t>EZETIMIBE 10 MG CM UNIDAD</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
@@ -18706,16 +18681,16 @@
         <v>0</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>349.9</v>
+        <v>1714.8</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>206.2</v>
+        <v>1029.2</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>270</v>
+        <v>1715</v>
       </c>
       <c r="I11" s="19" t="n">
         <v>0</v>
@@ -18727,14 +18702,14 @@
       </c>
       <c r="K11" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 270 ud.</t>
+          <t>COMPRA EXTERNA 1715 ud.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 20 MG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
@@ -18749,31 +18724,35 @@
         <v>0</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>282.1</v>
+        <v>349.9</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>29.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>176.8</v>
+        <v>206.2</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 270 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>NIFEDIPINO 20 MG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
@@ -18788,35 +18767,31 @@
         <v>0</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>197.3</v>
+        <v>282.1</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>0.4</v>
+        <v>29.2</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>150.7</v>
+        <v>176.8</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 23 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
@@ -18831,16 +18806,16 @@
         <v>0</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>71.8</v>
+        <v>197.3</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>49.2</v>
+        <v>150.7</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="I14" s="19" t="n">
         <v>0</v>
@@ -18852,14 +18827,14 @@
       </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 72 ud.</t>
+          <t>COMPRA EXTERNA 29 ud.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B15" s="18" t="inlineStr">
@@ -18874,31 +18849,35 @@
         <v>0</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>56.6</v>
+        <v>71.8</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>33.3</v>
+        <v>1.7</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>11.1</v>
+        <v>49.2</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>7900</v>
+        <v>0</v>
       </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K15" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 72 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
@@ -18913,19 +18892,19 @@
         <v>0</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>69.90000000000001</v>
+        <v>56.6</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>36.1</v>
+        <v>33.3</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H16" s="19" t="n">
         <v>100</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>900</v>
+        <v>7500</v>
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
@@ -18937,7 +18916,7 @@
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
@@ -18952,35 +18931,31 @@
         <v>0</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>20</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>8.300000000000001</v>
+        <v>36.1</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K17" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 20 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>CALCITRIOL 0,5 MCG CAPSULA</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
@@ -18995,31 +18970,35 @@
         <v>0</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>36.7</v>
+        <v>20</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>16.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K18" s="18" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 20 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>CALCITRIOL 0,5 MCG CAPSULA</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
@@ -19034,23 +19013,23 @@
         <v>0</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>33.3</v>
+        <v>36.7</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>11</v>
+        <v>16.7</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>16.8</v>
+        <v>12.5</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>1600</v>
+        <v>840</v>
       </c>
       <c r="J19" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 34 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K19" s="18" t="inlineStr"/>
@@ -19058,7 +19037,7 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
@@ -19073,23 +19052,23 @@
         <v>0</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>22.8</v>
+        <v>33.3</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>6.7</v>
+        <v>11</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>13.2</v>
+        <v>16.8</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="J20" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 34 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K20" s="18" t="inlineStr"/>
@@ -19097,7 +19076,7 @@
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
@@ -19112,35 +19091,31 @@
         <v>0</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>25.7</v>
+        <v>22.8</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>0.1</v>
+        <v>6.7</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>19.2</v>
+        <v>13.2</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>50</v>
+        <v>2200</v>
       </c>
       <c r="J21" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 50 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K21" s="18" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
@@ -19155,31 +19130,35 @@
         <v>0</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>20.8</v>
+        <v>25.7</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>10</v>
+        <v>19.2</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>5300</v>
+        <v>50</v>
       </c>
       <c r="J22" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="inlineStr"/>
+          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 50 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>CLOTRIMAZOL 1% (10 MG/G) CREMA</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
@@ -19194,23 +19173,23 @@
         <v>0</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>15.7</v>
+        <v>20.8</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>11.8</v>
+        <v>10</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>90</v>
+        <v>5300</v>
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 17 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K23" s="18" t="inlineStr"/>
@@ -19218,7 +19197,7 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>CLOTRIMAZOL 1% (10 MG/G) CREMA</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -19233,23 +19212,23 @@
         <v>0</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>13.8</v>
+        <v>15.7</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>8.199999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>3000</v>
+        <v>90</v>
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 14 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K24" s="18" t="inlineStr"/>
@@ -19257,7 +19236,7 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
@@ -19272,23 +19251,23 @@
         <v>0</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>0.6</v>
+        <v>13.8</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>46</v>
+        <v>3000</v>
       </c>
       <c r="J25" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 14 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K25" s="18" t="inlineStr"/>
@@ -19296,7 +19275,7 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
@@ -19311,23 +19290,23 @@
         <v>0</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>450</v>
+        <v>46</v>
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K26" s="18" t="inlineStr"/>
@@ -19335,89 +19314,89 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
+          <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>450</v>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
           <t>ALTEPLASA 50 MG FA UD</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>1-CRITICO</t>
         </is>
       </c>
-      <c r="C27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="19" t="n">
+      <c r="C28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F28" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="G27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="19" t="n">
+      <c r="G28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="18" t="inlineStr">
+      <c r="I28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="18" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="K27" s="18" t="inlineStr">
+      <c r="K28" s="18" t="inlineStr">
         <is>
           <t>COMPRA EXTERNA 1 ud.</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="n">
-        <v>1700</v>
-      </c>
-      <c r="D28" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" s="21" t="n">
-        <v>6317.1</v>
-      </c>
-      <c r="F28" s="21" t="n">
-        <v>291.7</v>
-      </c>
-      <c r="G28" s="21" t="n">
-        <v>4039.9</v>
-      </c>
-      <c r="H28" s="21" t="n">
-        <v>1140</v>
-      </c>
-      <c r="I28" s="21" t="n">
-        <v>45000</v>
-      </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>TRASPASAR 1140 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K28" s="20" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>PREGABALINA 75 MG CAPSULA</t>
+          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -19426,36 +19405,32 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>202</v>
+        <v>1700</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="21" t="n">
-        <v>5789.9</v>
+        <v>6317.1</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>42.4</v>
+        <v>291.7</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>3482.9</v>
+        <v>4039.9</v>
       </c>
       <c r="H29" s="21" t="n">
-        <v>4333</v>
+        <v>1200</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="J29" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K29" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 4333 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1200 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K29" s="20" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
@@ -19566,7 +19541,7 @@
         <v>3011.1</v>
       </c>
       <c r="H32" s="27" t="n">
-        <v>660</v>
+        <v>720</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>0</v>
@@ -19578,7 +19553,7 @@
       </c>
       <c r="K32" s="26" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 660 ud.</t>
+          <t>COMPRA EXTERNA 720 ud.</t>
         </is>
       </c>
     </row>
@@ -19648,14 +19623,14 @@
         <v>2924.9</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>10290</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 90 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr"/>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -663,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -867,20 +867,20 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>SACUBITRILO VALSARTAN 50 MG</t>
+          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2545</v>
+        <v>283</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -896,20 +896,20 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>UREA 10% CREMA 20 GR</t>
+          <t>SACUBITRILO VALSARTAN 50 MG</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>116</v>
+        <v>2545</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -925,20 +925,20 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
+          <t>UREA 10% CREMA 20 GR</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1333</v>
+        <v>116</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -954,20 +954,20 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
+          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1068</v>
+        <v>1333</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -983,20 +983,20 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>71</v>
+        <v>1068</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1012,20 +1012,20 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>RISPERIDONA 25 MG FA</t>
+          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1041,20 +1041,20 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>VASELINA SOLIDA UNGUENTO</t>
+          <t>RISPERIDONA 25 MG FA</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>14</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1070,20 +1070,20 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>VASELINA SOLIDA UNGUENTO</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1099,56 +1099,56 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>[CRITICO] CRITICO — SIN RESPALDO</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>COMPRA URGENTE — SIN RESPALDO EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>LIDOCAINA 5% (700 MG) PARCHE</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="4" t="n">
+      <c r="B17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>152</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E17" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>[CRITICO] CRITICO — SIN RESPALDO</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>COMPRA URGENTE — SIN RESPALDO EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>[ALTO] ALTO — SIN RESPALDO</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>COMPRA URGENTE — SIN RESPALDO EN BODEGA FARMACOS</t>
         </is>
@@ -1157,17 +1157,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
+          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>9</v>
@@ -1186,20 +1186,20 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>LAMOTRIGINA 100 MG COMPRIMIDO</t>
+          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>140</v>
+        <v>10</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -1215,20 +1215,20 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>LAMOTRIGINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -1244,20 +1244,20 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO CP 300 MG</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>67</v>
+        <v>240</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -1273,17 +1273,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>ACIDO VALPROICO 250 MG/5 ML FC 120 ML</t>
+          <t>GEMFIBROZILO CP 300 MG</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>2</v>
@@ -1302,20 +1302,20 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>CINTA PARA DETERMINACION GLUCOSA USO CLINICO X 50 UD</t>
+          <t>ACIDO VALPROICO 250 MG/5 ML FC 120 ML</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -1331,14 +1331,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO CLINICO X 50 UD</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>1</v>
@@ -1679,14 +1679,14 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D36" s="10" t="n">
         <v>1</v>
@@ -1701,68 +1701,97 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
+          <t>TRASPASAR DESDE BODEGA FARMACOS (600 ud. disponibles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>KETOROLACO AMP 30 MG/ML</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>[BAJO] BAJO — TRASPASO BOD.FARMACOS</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
           <t>TRASPASAR DESDE BODEGA FARMACOS (2200 ud. disponibles)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
+          <t>MODERADO  —  reponer pronto (Farmacia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
+          <t>BAJO  —  vigilar (Farmacia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -1779,7 +1808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2376,7 +2405,7 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
+          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -2391,16 +2420,16 @@
         <v>0</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>64.8</v>
+        <v>163.9</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
@@ -2409,14 +2438,14 @@
       </c>
       <c r="J16" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 65 ud.</t>
+          <t>GESTIONAR EXTERNO 66 ud.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -2431,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>66.5</v>
+        <v>64.8</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G17" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
@@ -2449,14 +2478,14 @@
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 67 ud.</t>
+          <t>GESTIONAR EXTERNO 65 ud.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
@@ -2471,16 +2500,16 @@
         <v>0</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>31.4</v>
+        <v>66.5</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G18" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
@@ -2489,14 +2518,14 @@
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 31 ud.</t>
+          <t>GESTIONAR EXTERNO 67 ud.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -2511,16 +2540,16 @@
         <v>0</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>27</v>
+        <v>31.4</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="G19" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
@@ -2529,14 +2558,14 @@
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
+          <t>GESTIONAR EXTERNO 31 ud.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
@@ -2551,16 +2580,16 @@
         <v>0</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="G20" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
@@ -2569,14 +2598,14 @@
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 9 ud.</t>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -2591,16 +2620,16 @@
         <v>0</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G21" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
@@ -2609,14 +2638,14 @@
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 7 ud.</t>
+          <t>GESTIONAR EXTERNO 9 ud.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -2631,16 +2660,16 @@
         <v>0</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>11.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="G22" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -2649,14 +2678,14 @@
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 100 ud.</t>
+          <t>GESTIONAR EXTERNO 7 ud.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>UREA 10% CREMA 20 GR</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
@@ -2671,16 +2700,16 @@
         <v>0</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>6.5</v>
+        <v>11.4</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="G23" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
@@ -2689,14 +2718,14 @@
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 7 ud.</t>
+          <t>GESTIONAR EXTERNO 100 ud.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>VASELINA SOLIDA UNGUENTO</t>
+          <t>UREA 10% CREMA 20 GR</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
@@ -2711,16 +2740,16 @@
         <v>0</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>11.3</v>
+        <v>6.5</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G24" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -2729,14 +2758,14 @@
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 12 ud.</t>
+          <t>GESTIONAR EXTERNO 7 ud.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>RISPERIDONA 25 MG FA</t>
+          <t>VASELINA SOLIDA UNGUENTO</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -2751,16 +2780,16 @@
         <v>0</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>9.199999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G25" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I25" s="20" t="inlineStr">
         <is>
@@ -2769,14 +2798,14 @@
       </c>
       <c r="J25" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 10 ud.</t>
+          <t>GESTIONAR EXTERNO 12 ud.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+          <t>RISPERIDONA 25 MG FA</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
@@ -2791,16 +2820,16 @@
         <v>0</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>16.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G26" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -2809,14 +2838,14 @@
       </c>
       <c r="J26" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 17 ud.</t>
+          <t>GESTIONAR EXTERNO 10 ud.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -2831,16 +2860,16 @@
         <v>0</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>5.4</v>
+        <v>16.8</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G27" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
@@ -2849,14 +2878,14 @@
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 5 ud.</t>
+          <t>GESTIONAR EXTERNO 17 ud.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
@@ -2871,16 +2900,16 @@
         <v>0</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G28" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -2889,14 +2918,14 @@
       </c>
       <c r="J28" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 2 ud.</t>
+          <t>GESTIONAR EXTERNO 5 ud.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
+          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -2936,7 +2965,7 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>ETONOGESTREL 68 MG IMPLANTE</t>
+          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
@@ -2951,16 +2980,16 @@
         <v>0</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -2969,85 +2998,89 @@
       </c>
       <c r="J30" s="20" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 1 ud.</t>
+          <t>GESTIONAR EXTERNO 2 ud.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
+          <t>ETONOGESTREL 68 MG IMPLANTE</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 1 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
           <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>1-CRITICO</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="21" t="n">
+      <c r="C32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="21" t="n">
         <v>1.1</v>
       </c>
-      <c r="F31" s="21" t="n">
+      <c r="F32" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="21" t="n">
+      <c r="G32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="20" t="inlineStr">
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
-      <c r="J31" s="20" t="inlineStr">
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 2 ud.</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>PARACETAMOL 500 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="n">
-        <v>1621</v>
-      </c>
-      <c r="D32" s="23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E32" s="23" t="n">
-        <v>7597.3</v>
-      </c>
-      <c r="F32" s="23" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G32" s="23" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H32" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 2000 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J32" s="22" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
@@ -3061,10 +3094,10 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>935</v>
+        <v>605</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E33" s="23" t="n">
         <v>4050.6</v>
@@ -3128,7 +3161,7 @@
     <row r="35">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
         </is>
       </c>
       <c r="B35" s="22" t="inlineStr">
@@ -3137,38 +3170,34 @@
         </is>
       </c>
       <c r="C35" s="23" t="n">
-        <v>343</v>
+        <v>639</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E35" s="23" t="n">
-        <v>1434.4</v>
+        <v>2237.7</v>
       </c>
       <c r="F35" s="23" t="n">
         <v>240</v>
       </c>
       <c r="G35" s="23" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H35" s="23" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I35" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J35" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 240 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 240 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J35" s="22" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
@@ -3177,38 +3206,34 @@
         </is>
       </c>
       <c r="C36" s="23" t="n">
-        <v>7</v>
+        <v>723</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="E36" s="23" t="n">
-        <v>163.9</v>
+        <v>2222.9</v>
       </c>
       <c r="F36" s="23" t="n">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="I36" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J36" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 59 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
         </is>
       </c>
       <c r="B37" s="22" t="inlineStr">
@@ -3217,22 +3242,22 @@
         </is>
       </c>
       <c r="C37" s="23" t="n">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E37" s="23" t="n">
-        <v>36.4</v>
+        <v>1434.4</v>
       </c>
       <c r="F37" s="23" t="n">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="G37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="I37" s="22" t="inlineStr">
         <is>
@@ -3241,14 +3266,14 @@
       </c>
       <c r="J37" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 30 ud.</t>
+          <t>GESTIONAR EXTERNO 480 ud.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
+          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
@@ -3257,22 +3282,22 @@
         </is>
       </c>
       <c r="C38" s="23" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="E38" s="23" t="n">
-        <v>48.6</v>
+        <v>36.4</v>
       </c>
       <c r="F38" s="23" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G38" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="23" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I38" s="22" t="inlineStr">
         <is>
@@ -3281,14 +3306,14 @@
       </c>
       <c r="J38" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 29 ud.</t>
+          <t>GESTIONAR EXTERNO 36 ud.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
@@ -3297,38 +3322,38 @@
         </is>
       </c>
       <c r="C39" s="23" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="E39" s="23" t="n">
-        <v>35.7</v>
+        <v>48.6</v>
       </c>
       <c r="F39" s="23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H39" s="23" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I39" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 25 ud. DESDE BODEGA AA</t>
+          <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
       <c r="J39" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 3 ud.</t>
+          <t>GESTIONAR EXTERNO 29 ud.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
@@ -3337,38 +3362,38 @@
         </is>
       </c>
       <c r="C40" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E40" s="23" t="n">
-        <v>16.2</v>
+        <v>35.7</v>
       </c>
       <c r="F40" s="23" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H40" s="23" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I40" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
+          <t>TRASPASAR 25 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J40" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 16 ud.</t>
+          <t>GESTIONAR EXTERNO 5 ud.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% (500 MCG/G) CREMA</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
@@ -3377,29 +3402,33 @@
         </is>
       </c>
       <c r="C41" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E41" s="23" t="n">
-        <v>8.1</v>
+        <v>16.2</v>
       </c>
       <c r="F41" s="23" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G41" s="23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H41" s="23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I41" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 9 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J41" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J41" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 16 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
@@ -3444,7 +3473,7 @@
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>UMECLIDINIO/VILANTEROL 55/22 INH</t>
+          <t>ADIFENINA 50 MG + PROPIFENAZONA 440 MG SUPOSITORIO</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
@@ -3453,26 +3482,26 @@
         </is>
       </c>
       <c r="C43" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="E43" s="23" t="n">
-        <v>4.9</v>
+        <v>8.1</v>
       </c>
       <c r="F43" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G43" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H43" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 9 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J43" s="22" t="inlineStr"/>
@@ -3565,26 +3594,26 @@
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>40.1</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 3 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 9 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr"/>
@@ -3708,7 +3737,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>ADIFENINA 50 MG + PROPIFENAZONA 440 MG SUPOSITORIO</t>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -3717,34 +3746,38 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>8.1</v>
+        <v>5.9</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 3 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>AEROCAMARA ADULTO BIVAL 451/ 800 ML</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -3753,200 +3786,124 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>5.9</v>
+        <v>3.2</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 3 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>AEROCAMARA ADULTO BIVAL 451/ 800 ML</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="n">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>ACIDO VALPROICO 375 MG/ML GOTAS 25 ML</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>4-BAJO</t>
+        </is>
+      </c>
+      <c r="C52" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="25" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E52" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F52" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D52" s="6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E52" s="6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>CETIRIZINA 10 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B53" s="24" t="inlineStr">
-        <is>
-          <t>4-BAJO</t>
-        </is>
-      </c>
-      <c r="C53" s="25" t="n">
-        <v>145</v>
-      </c>
-      <c r="D53" s="25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E53" s="25" t="n">
-        <v>156.7</v>
-      </c>
-      <c r="F53" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="G53" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="H53" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="24" t="inlineStr">
-        <is>
-          <t>TRASPASAR 12 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J53" s="24" t="inlineStr"/>
+      <c r="G52" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J52" s="24" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="24" t="inlineStr">
-        <is>
-          <t>ACIDO VALPROICO 375 MG/ML GOTAS 25 ML</t>
-        </is>
-      </c>
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t>4-BAJO</t>
-        </is>
-      </c>
-      <c r="C54" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="25" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="E54" s="25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F54" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="24" t="inlineStr">
-        <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J54" s="24" t="inlineStr"/>
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>CRITICO  —  sin stock ni respaldo</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>LEYENDA DE COLORES</t>
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>CRITICO  —  sin stock ni respaldo</t>
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>URGENTE  —  cobertura critica</t>
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>MODERADO  —  reponer pronto (Farmacia)</t>
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="15" t="inlineStr">
-        <is>
-          <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="inlineStr">
-        <is>
-          <t>BAJO  —  vigilar (Farmacia)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>BAJO  —  stock suficiente (Bodega)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -4108,7 +4065,7 @@
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
+          <t>METFORMINA 1000 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
@@ -4123,29 +4080,25 @@
         <v>0</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>4815.9</v>
+        <v>5312.9</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>756</v>
+        <v>2000</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 756 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2000 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>DABIGATRAN ETEXILATO CP 110 MG</t>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
@@ -4160,25 +4113,29 @@
         <v>0</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>3829.9</v>
+        <v>4815.9</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>446</v>
+        <v>941</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>4260</v>
+        <v>0</v>
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 446 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I6" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 941 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
+          <t>DABIGATRAN ETEXILATO CP 110 MG</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
@@ -4193,17 +4150,17 @@
         <v>0</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>3643.3</v>
+        <v>3829.9</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>500</v>
+        <v>566</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>1400</v>
+        <v>4260</v>
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 500 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 566 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr"/>
@@ -4211,7 +4168,7 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>VILDAGLIPTINA 50 MG CM</t>
+          <t>LEVOTIROXINA 100 MCG COMPRIMIDO.</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
@@ -4226,29 +4183,25 @@
         <v>0</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>4367.6</v>
+        <v>3643.3</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>4380</v>
+        <v>700</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 4380 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 700 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
+          <t>VILDAGLIPTINA 50 MG CM</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -4263,10 +4216,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>3502.1</v>
+        <v>4367.6</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>3180</v>
+        <v>4380</v>
       </c>
       <c r="G9" s="21" t="n">
         <v>0</v>
@@ -4278,14 +4231,14 @@
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3180 ud.</t>
+          <t>COMPRA EXTERNA 4380 ud.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>ISOSORBIDA DINITRATO 10 MG COMPRIMIDO</t>
+          <t>EMPAGLIFLOZINA 25 MG CM UD</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -4300,10 +4253,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>2509.8</v>
+        <v>3502.1</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>2510</v>
+        <v>3420</v>
       </c>
       <c r="G10" s="21" t="n">
         <v>0</v>
@@ -4315,14 +4268,14 @@
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2510 ud.</t>
+          <t>COMPRA EXTERNA 3420 ud.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>ESOMEPRAZOL 20 MG CM</t>
+          <t>ISOSORBIDA DINITRATO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -4337,10 +4290,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>2719.4</v>
+        <v>2509.8</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>2720</v>
+        <v>2510</v>
       </c>
       <c r="G11" s="21" t="n">
         <v>0</v>
@@ -4352,14 +4305,14 @@
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2720 ud.</t>
+          <t>COMPRA EXTERNA 2510 ud.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>QUETIAPINA 100 MG COMPRIMIDO</t>
+          <t>ESOMEPRAZOL 20 MG CM</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -4374,25 +4327,29 @@
         <v>0</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>2505.4</v>
+        <v>2719.4</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>1000</v>
+        <v>2720</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 2720 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>VITAMINA D3 800 UI CM</t>
+          <t>QUETIAPINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -4407,17 +4364,17 @@
         <v>0</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>1671.3</v>
+        <v>2505.4</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>1672</v>
+        <v>1000</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>3000</v>
+        <v>26000</v>
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1672 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr"/>
@@ -4425,7 +4382,7 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
+          <t>VITAMINA D3 800 UI CM</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
@@ -4440,29 +4397,25 @@
         <v>0</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>2411.2</v>
+        <v>1671.3</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>2412</v>
+        <v>1672</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 2412 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1672 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
+          <t>FUMARATO FERROSO + CIANOCOBALAMINA + ACIDO ASCORBICO + ACIDO FOLICO 330/1/100/2 MG CP</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -4477,10 +4430,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>1552.2</v>
+        <v>2411.2</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>1553</v>
+        <v>2412</v>
       </c>
       <c r="G15" s="21" t="n">
         <v>0</v>
@@ -4492,14 +4445,14 @@
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1553 ud.</t>
+          <t>COMPRA EXTERNA 2412 ud.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>EZETIMIBE 10 MG CM UNIDAD</t>
+          <t>POLIETILENGLICOL 17 G POLVO PARA PREPARADO ORAL</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -4514,10 +4467,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>1776.1</v>
+        <v>1552.2</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>1777</v>
+        <v>1553</v>
       </c>
       <c r="G16" s="21" t="n">
         <v>0</v>
@@ -4529,14 +4482,14 @@
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1777 ud.</t>
+          <t>COMPRA EXTERNA 1553 ud.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>DULOXETINA 60 MG CAPSULA</t>
+          <t>EZETIMIBE 10 MG CM UNIDAD</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -4551,25 +4504,29 @@
         <v>0</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>1113</v>
+        <v>1776.1</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>690</v>
+        <v>1777</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>3510</v>
+        <v>0</v>
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 690 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1777 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>LAMOTRIGINA 100 MG COMPRIMIDO</t>
+          <t>DULOXETINA 60 MG CAPSULA</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
@@ -4584,29 +4541,25 @@
         <v>0</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>830</v>
+        <v>1113</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>840</v>
+        <v>690</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>0</v>
+        <v>3510</v>
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 840 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 690 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>RIFAXIMINA 200 MG CP</t>
+          <t>LAMOTRIGINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -4621,25 +4574,29 @@
         <v>0</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="F19" s="21" t="n">
         <v>840</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>23424</v>
+        <v>0</v>
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 840 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 840 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>LEVODOPA 200 MG - BENSERAZIDA 50 MG COMPRIMIDO</t>
+          <t>RIFAXIMINA 200 MG CP</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
@@ -4654,29 +4611,25 @@
         <v>0</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>612.2</v>
+        <v>837</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>527</v>
+        <v>840</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>0</v>
+        <v>23424</v>
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 527 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 840 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>VENLAFAXINA 150 MG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>LEVODOPA 200 MG - BENSERAZIDA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -4691,25 +4644,29 @@
         <v>0</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>898.3</v>
+        <v>612.2</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>390</v>
+        <v>527</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>6990</v>
+        <v>0</v>
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 390 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I21" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 527 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>SACUBITRILO VALSARTAN 50 MG</t>
+          <t>VENLAFAXINA 150 MG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -4724,29 +4681,25 @@
         <v>0</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>844.6</v>
+        <v>898.3</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>845</v>
+        <v>390</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>0</v>
+        <v>6990</v>
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 845 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 390 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>CARBONATO DE LITIO 450 MG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>SACUBITRILO VALSARTAN 50 MG</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
@@ -4761,25 +4714,29 @@
         <v>0</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>652.3</v>
+        <v>844.6</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>83</v>
+        <v>845</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>21660</v>
+        <v>0</v>
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 83 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 845 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>ACIDO URSODEOXICOLICO CM 250 MG</t>
+          <t>CARBONATO DE LITIO 450 MG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
@@ -4794,17 +4751,17 @@
         <v>0</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>744.8</v>
+        <v>652.3</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>4620</v>
+        <v>21660</v>
       </c>
       <c r="H24" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 83 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr"/>
@@ -4812,7 +4769,7 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>ALOPURINOL 300 MG COMPRIMIDO</t>
+          <t>ESCITALOPRAM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -4827,17 +4784,17 @@
         <v>0</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>415.9</v>
+        <v>769.7</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>5800</v>
+        <v>3000</v>
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 20 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 500 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr"/>
@@ -4845,7 +4802,7 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>BACLOFENO 10 MG COMPRIMIDO</t>
+          <t>ACIDO URSODEOXICOLICO CM 250 MG</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
@@ -4860,17 +4817,17 @@
         <v>0</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>565.2</v>
+        <v>744.8</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>800</v>
+        <v>4620</v>
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 320 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr"/>
@@ -4878,7 +4835,7 @@
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>TOLTERODINA CM 2 MG</t>
+          <t>HIDROCLOROTIAZIDA 25 MG + TRIAMTERENO 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -4893,17 +4850,17 @@
         <v>0</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>583.1</v>
+        <v>620.7</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>2100</v>
+        <v>15000</v>
       </c>
       <c r="H27" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 28 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr"/>
@@ -4911,7 +4868,7 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>MICOFENOLATO 500 MG CR</t>
+          <t>AMITRIPTILINA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
@@ -4926,17 +4883,17 @@
         <v>0</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>363</v>
+        <v>736</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>363</v>
+        <v>100</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="H28" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 363 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr"/>
@@ -4944,7 +4901,7 @@
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>BETAHISTINA 16 MG COMPRIMIDO</t>
+          <t>ALOPURINOL 300 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -4959,17 +4916,17 @@
         <v>0</v>
       </c>
       <c r="E29" s="21" t="n">
-        <v>277.4</v>
+        <v>415.9</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>5224</v>
+        <v>5800</v>
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 56 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 20 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr"/>
@@ -4977,7 +4934,7 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>MIRTAZAPINA 15 MG COMPRIMIDO</t>
+          <t>BACLOFENO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
@@ -4992,17 +4949,17 @@
         <v>0</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>480.8</v>
+        <v>565.2</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>7020</v>
+        <v>800</v>
       </c>
       <c r="H30" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 210 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 320 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr"/>
@@ -5010,7 +4967,7 @@
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>ACIDO FOLICO CM 1 MG</t>
+          <t>TOLTERODINA CM 2 MG</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -5025,17 +4982,17 @@
         <v>0</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>352</v>
+        <v>583.1</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>13640</v>
+        <v>2100</v>
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr"/>
@@ -5043,7 +5000,7 @@
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
+          <t>MICOFENOLATO 500 MG CR</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
@@ -5058,29 +5015,25 @@
         <v>0</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>376.2</v>
+        <v>363</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>390</v>
+        <v>363</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H32" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I32" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 390 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 363 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>BETAHISTINA 16 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
@@ -5095,29 +5048,25 @@
         <v>0</v>
       </c>
       <c r="E33" s="21" t="n">
-        <v>355.3</v>
+        <v>277.4</v>
       </c>
       <c r="F33" s="21" t="n">
-        <v>349</v>
+        <v>56</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>0</v>
+        <v>5224</v>
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I33" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 349 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 56 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>BISOPROLOL 5 MG COMPRIMIDO</t>
+          <t>MIRTAZAPINA 15 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
@@ -5132,29 +5081,25 @@
         <v>0</v>
       </c>
       <c r="E34" s="21" t="n">
-        <v>211</v>
+        <v>480.8</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>0</v>
+        <v>7020</v>
       </c>
       <c r="H34" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 210 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>ACIDO FOLICO CM 1 MG</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -5169,29 +5114,25 @@
         <v>0</v>
       </c>
       <c r="E35" s="21" t="n">
-        <v>193.7</v>
+        <v>352</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>47</v>
+        <v>1000</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>0</v>
+        <v>13640</v>
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I35" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 47 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1000 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I35" s="20" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>CLOBAZAM 10 MG COMPRIMIDO</t>
+          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
@@ -5206,29 +5147,25 @@
         <v>0</v>
       </c>
       <c r="E36" s="21" t="n">
-        <v>184.5</v>
+        <v>376.2</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>127</v>
+        <v>390</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H36" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I36" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 127 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 390 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I36" s="20" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
+          <t>INSULINA GLARGINA 450 UI/1,5 ML (300 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -5243,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="E37" s="21" t="n">
-        <v>127.8</v>
+        <v>355.3</v>
       </c>
       <c r="F37" s="21" t="n">
-        <v>128</v>
+        <v>356</v>
       </c>
       <c r="G37" s="21" t="n">
         <v>0</v>
@@ -5258,14 +5195,14 @@
       </c>
       <c r="I37" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 128 ud.</t>
+          <t>COMPRA EXTERNA 356 ud.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>BISOPROLOL 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
@@ -5280,10 +5217,10 @@
         <v>0</v>
       </c>
       <c r="E38" s="21" t="n">
-        <v>97.90000000000001</v>
+        <v>211</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="G38" s="21" t="n">
         <v>0</v>
@@ -5295,14 +5232,14 @@
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 91 ud.</t>
+          <t>COMPRA EXTERNA 1 ud.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
@@ -5317,10 +5254,10 @@
         <v>0</v>
       </c>
       <c r="E39" s="21" t="n">
-        <v>141.7</v>
+        <v>193.7</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="G39" s="21" t="n">
         <v>0</v>
@@ -5332,14 +5269,14 @@
       </c>
       <c r="I39" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 142 ud.</t>
+          <t>COMPRA EXTERNA 57 ud.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>FLUNARIZINA 10 MG COMPRIMIDO</t>
+          <t>CETIRIZINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
@@ -5354,25 +5291,29 @@
         <v>0</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>103.9</v>
+        <v>296.2</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H40" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 21 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I40" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 2 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>WARFARINA 5 MG COMPRIMIDO</t>
+          <t>CLOBAZAM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -5387,25 +5328,29 @@
         <v>0</v>
       </c>
       <c r="E41" s="21" t="n">
-        <v>134.8</v>
+        <v>184.5</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="H41" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I41" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 127 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>KETOPROFENO 100 MG COMPRIMIDO</t>
+          <t>LIDOCAINA 5% (700 MG) PARCHE</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
@@ -5420,25 +5365,29 @@
         <v>0</v>
       </c>
       <c r="E42" s="21" t="n">
-        <v>108.1</v>
+        <v>127.8</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="H42" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I42" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 128 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>LATANOPROST 0,005% COLIRIO</t>
+          <t>INSULINA ASPARTA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -5453,10 +5402,10 @@
         <v>0</v>
       </c>
       <c r="E43" s="21" t="n">
-        <v>98.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="G43" s="21" t="n">
         <v>0</v>
@@ -5468,14 +5417,14 @@
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 5 ud.</t>
+          <t>COMPRA EXTERNA 97 ud.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
+          <t>INSULINA GLULISINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
@@ -5490,10 +5439,10 @@
         <v>0</v>
       </c>
       <c r="E44" s="21" t="n">
-        <v>99.8</v>
+        <v>141.7</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="G44" s="21" t="n">
         <v>0</v>
@@ -5505,14 +5454,14 @@
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 80 ud.</t>
+          <t>COMPRA EXTERNA 142 ud.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>FLUNARIZINA 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
@@ -5527,29 +5476,25 @@
         <v>0</v>
       </c>
       <c r="E45" s="21" t="n">
-        <v>70.2</v>
+        <v>103.9</v>
       </c>
       <c r="F45" s="21" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="G45" s="21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H45" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I45" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 71 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 21 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I45" s="20" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>WARFARINA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
@@ -5564,17 +5509,17 @@
         <v>0</v>
       </c>
       <c r="E46" s="21" t="n">
-        <v>67</v>
+        <v>134.8</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>7500</v>
+        <v>480</v>
       </c>
       <c r="H46" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 30 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I46" s="20" t="inlineStr"/>
@@ -5582,7 +5527,7 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>KETOPROFENO 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
@@ -5597,29 +5542,25 @@
         <v>0</v>
       </c>
       <c r="E47" s="21" t="n">
-        <v>73</v>
+        <v>108.1</v>
       </c>
       <c r="F47" s="21" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="G47" s="21" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="H47" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I47" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 41 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
+          <t>LATANOPROST 0,005% COLIRIO</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
@@ -5634,25 +5575,29 @@
         <v>0</v>
       </c>
       <c r="E48" s="21" t="n">
-        <v>75.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="F48" s="21" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H48" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I48" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I48" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 5 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>MORFINA 30 MG CAPSULA LIBERACION MODIFICADA</t>
+          <t>METOTREXATO 20 MG/0,4 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
@@ -5667,10 +5612,10 @@
         <v>0</v>
       </c>
       <c r="E49" s="21" t="n">
-        <v>42.2</v>
+        <v>99.8</v>
       </c>
       <c r="F49" s="21" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="G49" s="21" t="n">
         <v>0</v>
@@ -5682,14 +5627,14 @@
       </c>
       <c r="I49" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 18 ud.</t>
+          <t>COMPRA EXTERNA 80 ud.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B50" s="20" t="inlineStr">
@@ -5704,10 +5649,10 @@
         <v>0</v>
       </c>
       <c r="E50" s="21" t="n">
-        <v>13</v>
+        <v>70.2</v>
       </c>
       <c r="F50" s="21" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G50" s="21" t="n">
         <v>0</v>
@@ -5719,14 +5664,14 @@
       </c>
       <c r="I50" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 13 ud.</t>
+          <t>COMPRA EXTERNA 71 ud.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>CALCITRIOL 0,5 MCG CAPSULA</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B51" s="20" t="inlineStr">
@@ -5741,17 +5686,17 @@
         <v>0</v>
       </c>
       <c r="E51" s="21" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="F51" s="21" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="G51" s="21" t="n">
-        <v>840</v>
+        <v>7500</v>
       </c>
       <c r="H51" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I51" s="20" t="inlineStr"/>
@@ -5759,7 +5704,7 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B52" s="20" t="inlineStr">
@@ -5774,25 +5719,29 @@
         <v>0</v>
       </c>
       <c r="E52" s="21" t="n">
-        <v>38.5</v>
+        <v>73</v>
       </c>
       <c r="F52" s="21" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="H52" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 39 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I52" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I52" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 43 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B53" s="20" t="inlineStr">
@@ -5807,17 +5756,17 @@
         <v>0</v>
       </c>
       <c r="E53" s="21" t="n">
-        <v>39.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F53" s="21" t="n">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="G53" s="21" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="H53" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 39 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I53" s="20" t="inlineStr"/>
@@ -5825,7 +5774,7 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
+          <t>MORFINA 30 MG CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B54" s="20" t="inlineStr">
@@ -5840,25 +5789,29 @@
         <v>0</v>
       </c>
       <c r="E54" s="21" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="F54" s="21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H54" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 20 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I54" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I54" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 18 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="20" t="inlineStr">
         <is>
-          <t>TRAMADOL FRASCO GOTAS 100 MG/ML /10 ML</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
@@ -5873,25 +5826,29 @@
         <v>0</v>
       </c>
       <c r="E55" s="21" t="n">
-        <v>38.9</v>
+        <v>13</v>
       </c>
       <c r="F55" s="21" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G55" s="21" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="H55" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 24 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I55" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 13 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>CALCITRIOL 0,5 MCG CAPSULA</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
@@ -5906,17 +5863,17 @@
         <v>0</v>
       </c>
       <c r="E56" s="21" t="n">
-        <v>22.5</v>
+        <v>39</v>
       </c>
       <c r="F56" s="21" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G56" s="21" t="n">
-        <v>2200</v>
+        <v>840</v>
       </c>
       <c r="H56" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I56" s="20" t="inlineStr"/>
@@ -5924,7 +5881,7 @@
     <row r="57">
       <c r="A57" s="20" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
@@ -5939,29 +5896,25 @@
         <v>0</v>
       </c>
       <c r="E57" s="21" t="n">
-        <v>24.6</v>
+        <v>38.5</v>
       </c>
       <c r="F57" s="21" t="n">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="G57" s="21" t="n">
-        <v>50</v>
+        <v>1600</v>
       </c>
       <c r="H57" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I57" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 50 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 39 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I57" s="20" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>APIXABAN 2,5 MG CM</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B58" s="20" t="inlineStr">
@@ -5976,17 +5929,17 @@
         <v>0</v>
       </c>
       <c r="E58" s="21" t="n">
-        <v>13</v>
+        <v>39.8</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G58" s="21" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="H58" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 39 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I58" s="20" t="inlineStr"/>
@@ -5994,7 +5947,7 @@
     <row r="59">
       <c r="A59" s="20" t="inlineStr">
         <is>
-          <t>UREA 10% CREMA 20 GR</t>
+          <t>METOTREXATO 10 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B59" s="20" t="inlineStr">
@@ -6009,29 +5962,25 @@
         <v>0</v>
       </c>
       <c r="E59" s="21" t="n">
-        <v>13.8</v>
+        <v>41.3</v>
       </c>
       <c r="F59" s="21" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G59" s="21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H59" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I59" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 14 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 20 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I59" s="20" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>FENTANILO 25 MCG/HORA PARCHE</t>
+          <t>TRAMADOL FRASCO GOTAS 100 MG/ML /10 ML</t>
         </is>
       </c>
       <c r="B60" s="20" t="inlineStr">
@@ -6046,29 +5995,25 @@
         <v>0</v>
       </c>
       <c r="E60" s="21" t="n">
-        <v>33.1</v>
+        <v>38.9</v>
       </c>
       <c r="F60" s="21" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G60" s="21" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="H60" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I60" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 5 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 24 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I60" s="20" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="20" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B61" s="20" t="inlineStr">
@@ -6083,17 +6028,17 @@
         <v>0</v>
       </c>
       <c r="E61" s="21" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="F61" s="21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G61" s="21" t="n">
-        <v>5300</v>
+        <v>2200</v>
       </c>
       <c r="H61" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I61" s="20" t="inlineStr"/>
@@ -6101,7 +6046,7 @@
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>VASELINA SOLIDA UNGUENTO</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B62" s="20" t="inlineStr">
@@ -6116,29 +6061,29 @@
         <v>0</v>
       </c>
       <c r="E62" s="21" t="n">
-        <v>28.9</v>
+        <v>24.6</v>
       </c>
       <c r="F62" s="21" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="G62" s="21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H62" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
+          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I62" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 29 ud.</t>
+          <t>COMPRA EXTERNA 50 ud.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="20" t="inlineStr">
         <is>
-          <t>RISPERIDONA 25 MG FA</t>
+          <t>APIXABAN 2,5 MG CM</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
@@ -6153,29 +6098,25 @@
         <v>0</v>
       </c>
       <c r="E63" s="21" t="n">
-        <v>19.9</v>
+        <v>13</v>
       </c>
       <c r="F63" s="21" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G63" s="21" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H63" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I63" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 20 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I63" s="20" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>CLOTRIMAZOL 1% (10 MG/G) CREMA</t>
+          <t>UREA 10% CREMA 20 GR</t>
         </is>
       </c>
       <c r="B64" s="20" t="inlineStr">
@@ -6190,25 +6131,29 @@
         <v>0</v>
       </c>
       <c r="E64" s="21" t="n">
-        <v>17</v>
+        <v>13.8</v>
       </c>
       <c r="F64" s="21" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G64" s="21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H64" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 9 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I64" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I64" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 14 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="20" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+          <t>FENTANILO 25 MCG/HORA PARCHE</t>
         </is>
       </c>
       <c r="B65" s="20" t="inlineStr">
@@ -6223,10 +6168,10 @@
         <v>0</v>
       </c>
       <c r="E65" s="21" t="n">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
       <c r="F65" s="21" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="G65" s="21" t="n">
         <v>0</v>
@@ -6238,14 +6183,14 @@
       </c>
       <c r="I65" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 34 ud.</t>
+          <t>COMPRA EXTERNA 5 ud.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B66" s="20" t="inlineStr">
@@ -6260,13 +6205,13 @@
         <v>0</v>
       </c>
       <c r="E66" s="21" t="n">
-        <v>18.1</v>
+        <v>22.4</v>
       </c>
       <c r="F66" s="21" t="n">
         <v>19</v>
       </c>
       <c r="G66" s="21" t="n">
-        <v>3000</v>
+        <v>5300</v>
       </c>
       <c r="H66" s="20" t="inlineStr">
         <is>
@@ -6278,7 +6223,7 @@
     <row r="67">
       <c r="A67" s="20" t="inlineStr">
         <is>
-          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
+          <t>VASELINA SOLIDA UNGUENTO</t>
         </is>
       </c>
       <c r="B67" s="20" t="inlineStr">
@@ -6293,10 +6238,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="21" t="n">
-        <v>33.3</v>
+        <v>28.9</v>
       </c>
       <c r="F67" s="21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G67" s="21" t="n">
         <v>0</v>
@@ -6308,14 +6253,14 @@
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 27 ud.</t>
+          <t>COMPRA EXTERNA 29 ud.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>OXCARBAZEPINA 600 MG COMPRIMIDO</t>
+          <t>RISPERIDONA 25 MG FA</t>
         </is>
       </c>
       <c r="B68" s="20" t="inlineStr">
@@ -6330,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="E68" s="21" t="n">
-        <v>13</v>
+        <v>19.9</v>
       </c>
       <c r="F68" s="21" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G68" s="21" t="n">
         <v>0</v>
@@ -6345,14 +6290,14 @@
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 13 ud.</t>
+          <t>COMPRA EXTERNA 20 ud.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="20" t="inlineStr">
         <is>
-          <t>CINTA PARA DETERMINACION GLUCOSA USO CLINICO X 50 UD</t>
+          <t>CLOTRIMAZOL 1% (10 MG/G) CREMA</t>
         </is>
       </c>
       <c r="B69" s="20" t="inlineStr">
@@ -6367,29 +6312,25 @@
         <v>0</v>
       </c>
       <c r="E69" s="21" t="n">
-        <v>9.699999999999999</v>
+        <v>17</v>
       </c>
       <c r="F69" s="21" t="n">
         <v>10</v>
       </c>
       <c r="G69" s="21" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H69" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I69" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 10 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 10 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I69" s="20" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>CEFTRIAXONA 1G FA</t>
+          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
         </is>
       </c>
       <c r="B70" s="20" t="inlineStr">
@@ -6404,25 +6345,29 @@
         <v>0</v>
       </c>
       <c r="E70" s="21" t="n">
-        <v>10.4</v>
+        <v>33.5</v>
       </c>
       <c r="F70" s="21" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G70" s="21" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="H70" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I70" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I70" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 34 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B71" s="20" t="inlineStr">
@@ -6437,29 +6382,25 @@
         <v>0</v>
       </c>
       <c r="E71" s="21" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="F71" s="21" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G71" s="21" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H71" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I71" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 9 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I71" s="20" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>LORATADINA 5 MG/5 ML FC 120 ML</t>
+          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
         </is>
       </c>
       <c r="B72" s="20" t="inlineStr">
@@ -6474,25 +6415,29 @@
         <v>0</v>
       </c>
       <c r="E72" s="21" t="n">
-        <v>2.4</v>
+        <v>33.3</v>
       </c>
       <c r="F72" s="21" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G72" s="21" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="H72" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I72" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I72" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 27 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
+          <t>OXCARBAZEPINA 600 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B73" s="20" t="inlineStr">
@@ -6507,10 +6452,10 @@
         <v>0</v>
       </c>
       <c r="E73" s="21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F73" s="21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G73" s="21" t="n">
         <v>0</v>
@@ -6522,14 +6467,14 @@
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3 ud.</t>
+          <t>COMPRA EXTERNA 13 ud.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO CLINICO X 50 UD</t>
         </is>
       </c>
       <c r="B74" s="20" t="inlineStr">
@@ -6544,10 +6489,10 @@
         <v>0</v>
       </c>
       <c r="E74" s="21" t="n">
-        <v>2.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F74" s="21" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G74" s="21" t="n">
         <v>0</v>
@@ -6559,14 +6504,14 @@
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3 ud.</t>
+          <t>COMPRA EXTERNA 10 ud.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10 MG/2 ML (5 MG/ML) INYECTABLE</t>
+          <t>CEFTRIAXONA 1G FA</t>
         </is>
       </c>
       <c r="B75" s="20" t="inlineStr">
@@ -6581,17 +6526,17 @@
         <v>0</v>
       </c>
       <c r="E75" s="21" t="n">
-        <v>1.3</v>
+        <v>10.4</v>
       </c>
       <c r="F75" s="21" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="G75" s="21" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="H75" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 24 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I75" s="20" t="inlineStr"/>
@@ -6599,7 +6544,7 @@
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>LIRAGLUTIDA 6 MG/ML SOL.INY UD</t>
         </is>
       </c>
       <c r="B76" s="20" t="inlineStr">
@@ -6614,25 +6559,29 @@
         <v>0</v>
       </c>
       <c r="E76" s="21" t="n">
-        <v>0.4</v>
+        <v>12.1</v>
       </c>
       <c r="F76" s="21" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G76" s="21" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H76" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I76" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I76" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 9 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="20" t="inlineStr">
         <is>
-          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
+          <t>LORATADINA 5 MG/5 ML FC 120 ML</t>
         </is>
       </c>
       <c r="B77" s="20" t="inlineStr">
@@ -6647,29 +6596,25 @@
         <v>0</v>
       </c>
       <c r="E77" s="21" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="F77" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" s="21" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="H77" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I77" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I77" s="20" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>ETONOGESTREL 68 MG IMPLANTE</t>
+          <t>ZUCLOPENTIXOL DECANOATO 200 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B78" s="20" t="inlineStr">
@@ -6684,25 +6629,29 @@
         <v>0</v>
       </c>
       <c r="E78" s="21" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="F78" s="21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" s="21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H78" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I78" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I78" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 3 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="20" t="inlineStr">
         <is>
-          <t>HIERRO CARBOXIMALTOSA 500 MG/10 ML FA</t>
+          <t>CASEINATO CALCIO PROTEINA SUERO+LECITINA DE SOYA UD SIN ESPECIFICAR</t>
         </is>
       </c>
       <c r="B79" s="20" t="inlineStr">
@@ -6717,10 +6666,10 @@
         <v>0</v>
       </c>
       <c r="E79" s="21" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="F79" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G79" s="21" t="n">
         <v>0</v>
@@ -6732,14 +6681,14 @@
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1 ud.</t>
+          <t>COMPRA EXTERNA 3 ud.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>AGUA BIDESTILADA MATRAZ 500 ML</t>
+          <t>METOCLOPRAMIDA 10 MG/2 ML (5 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B80" s="20" t="inlineStr">
@@ -6754,17 +6703,17 @@
         <v>0</v>
       </c>
       <c r="E80" s="21" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="F80" s="21" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G80" s="21" t="n">
-        <v>125</v>
+        <v>2400</v>
       </c>
       <c r="H80" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 24 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr"/>
@@ -6772,7 +6721,7 @@
     <row r="81">
       <c r="A81" s="20" t="inlineStr">
         <is>
-          <t>FITOMENADIONA 10 MG/ML INTRAMUSCULAR</t>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
         </is>
       </c>
       <c r="B81" s="20" t="inlineStr">
@@ -6793,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="21" t="n">
-        <v>300</v>
+        <v>46</v>
       </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
@@ -6805,7 +6754,7 @@
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>GENTAMICINA 80 MG/2 ML (40 MG/ML) INYECTABLE</t>
+          <t>NISTATINA 100.000 UI/G UNGUENTO</t>
         </is>
       </c>
       <c r="B82" s="20" t="inlineStr">
@@ -6820,25 +6769,29 @@
         <v>0</v>
       </c>
       <c r="E82" s="21" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F82" s="21" t="n">
         <v>1</v>
       </c>
       <c r="G82" s="21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H82" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I82" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I82" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
+          <t>ETONOGESTREL 68 MG IMPLANTE</t>
         </is>
       </c>
       <c r="B83" s="20" t="inlineStr">
@@ -6853,359 +6806,363 @@
         <v>0</v>
       </c>
       <c r="E83" s="21" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="F83" s="21" t="n">
         <v>2</v>
       </c>
       <c r="G83" s="21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I83" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 2 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I83" s="20" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="20" t="inlineStr">
         <is>
+          <t>HIERRO CARBOXIMALTOSA 500 MG/10 ML FA</t>
+        </is>
+      </c>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F84" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="20" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I84" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20" t="inlineStr">
+        <is>
+          <t>AGUA BIDESTILADA MATRAZ 500 ML</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F85" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="21" t="n">
+        <v>125</v>
+      </c>
+      <c r="H85" s="20" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I85" s="20" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>FITOMENADIONA 10 MG/ML INTRAMUSCULAR</t>
+        </is>
+      </c>
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C86" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F86" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="21" t="n">
+        <v>300</v>
+      </c>
+      <c r="H86" s="20" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I86" s="20" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>GENTAMICINA 80 MG/2 ML (40 MG/ML) INYECTABLE</t>
+        </is>
+      </c>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F87" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="H87" s="20" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I87" s="20" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>METILPREDNISOLONA 500 MG INYECTABLE</t>
+        </is>
+      </c>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F88" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="20" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I88" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 2 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="20" t="inlineStr">
+        <is>
           <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
         </is>
       </c>
-      <c r="B84" s="20" t="inlineStr">
+      <c r="B89" s="20" t="inlineStr">
         <is>
           <t>1-CRITICO</t>
         </is>
       </c>
-      <c r="C84" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="21" t="n">
+      <c r="C89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="21" t="n">
         <v>1.7</v>
       </c>
-      <c r="F84" s="21" t="n">
+      <c r="F89" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G84" s="21" t="n">
+      <c r="G89" s="21" t="n">
         <v>450</v>
       </c>
-      <c r="H84" s="20" t="inlineStr">
+      <c r="H89" s="20" t="inlineStr">
         <is>
           <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="I84" s="20" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="22" t="inlineStr">
+      <c r="I89" s="20" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="22" t="inlineStr">
         <is>
           <t>PARACETAMOL 500 MG COMPRIMIDO</t>
         </is>
       </c>
-      <c r="B85" s="22" t="inlineStr">
+      <c r="B90" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C85" s="23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D85" s="23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E85" s="23" t="n">
+      <c r="C90" s="23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D90" s="23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E90" s="23" t="n">
         <v>17383.4</v>
       </c>
-      <c r="F85" s="23" t="n">
+      <c r="F90" s="23" t="n">
         <v>9000</v>
       </c>
-      <c r="G85" s="23" t="n">
+      <c r="G90" s="23" t="n">
         <v>160000</v>
       </c>
-      <c r="H85" s="22" t="inlineStr">
+      <c r="H90" s="22" t="inlineStr">
         <is>
           <t>TRASPASAR 9000 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="I85" s="22" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="22" t="inlineStr">
+      <c r="I90" s="22" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="22" t="inlineStr">
         <is>
           <t>ACIDO ACETILSALICILICO CM 100 MG</t>
         </is>
       </c>
-      <c r="B86" s="22" t="inlineStr">
+      <c r="B91" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C86" s="23" t="n">
+      <c r="C91" s="23" t="n">
         <v>1700</v>
       </c>
-      <c r="D86" s="23" t="n">
+      <c r="D91" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E86" s="23" t="n">
+      <c r="E91" s="23" t="n">
         <v>6049</v>
       </c>
-      <c r="F86" s="23" t="n">
-        <v>1681</v>
-      </c>
-      <c r="G86" s="23" t="n">
+      <c r="F91" s="23" t="n">
+        <v>1966</v>
+      </c>
+      <c r="G91" s="23" t="n">
         <v>67000</v>
       </c>
-      <c r="H86" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 1681 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I86" s="22" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="22" t="inlineStr">
+      <c r="H91" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1966 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I91" s="22" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
         <is>
           <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
         </is>
       </c>
-      <c r="B87" s="22" t="inlineStr">
+      <c r="B92" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C87" s="23" t="n">
+      <c r="C92" s="23" t="n">
         <v>1200</v>
       </c>
-      <c r="D87" s="23" t="n">
+      <c r="D92" s="23" t="n">
         <v>2.6</v>
       </c>
-      <c r="E87" s="23" t="n">
+      <c r="E92" s="23" t="n">
         <v>3314.7</v>
       </c>
-      <c r="F87" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="G87" s="23" t="n">
+      <c r="F92" s="23" t="n">
+        <v>460</v>
+      </c>
+      <c r="G92" s="23" t="n">
         <v>36580</v>
       </c>
-      <c r="H87" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 400 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I87" s="22" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="22" t="inlineStr">
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 460 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I92" s="22" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="22" t="inlineStr">
         <is>
           <t>DULOXETINA 30 MG CAPSULA</t>
         </is>
       </c>
-      <c r="B88" s="22" t="inlineStr">
+      <c r="B93" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C88" s="23" t="n">
+      <c r="C93" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="D88" s="23" t="n">
+      <c r="D93" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E88" s="23" t="n">
+      <c r="E93" s="23" t="n">
         <v>1178.7</v>
       </c>
-      <c r="F88" s="23" t="n">
-        <v>330</v>
-      </c>
-      <c r="G88" s="23" t="n">
+      <c r="F93" s="23" t="n">
+        <v>420</v>
+      </c>
+      <c r="G93" s="23" t="n">
         <v>1980</v>
       </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 330 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I88" s="22" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="22" t="inlineStr">
-        <is>
-          <t>HIDROCLOROTIAZIDA 25 MG + TRIAMTERENO 50 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B89" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C89" s="23" t="n">
-        <v>240</v>
-      </c>
-      <c r="D89" s="23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E89" s="23" t="n">
-        <v>620.7</v>
-      </c>
-      <c r="F89" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="G89" s="23" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H89" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 28 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I89" s="22" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="28" t="inlineStr">
-        <is>
-          <t>LOSARTAN 50 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B90" s="28" t="inlineStr">
-        <is>
-          <t>3-ALTO</t>
-        </is>
-      </c>
-      <c r="C90" s="29" t="n">
-        <v>5700</v>
-      </c>
-      <c r="D90" s="29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E90" s="29" t="n">
-        <v>9495.6</v>
-      </c>
-      <c r="F90" s="29" t="n">
-        <v>2400</v>
-      </c>
-      <c r="G90" s="29" t="n">
-        <v>30000</v>
-      </c>
-      <c r="H90" s="28" t="inlineStr">
-        <is>
-          <t>TRASPASAR 2400 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I90" s="28" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="28" t="inlineStr">
-        <is>
-          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B91" s="28" t="inlineStr">
-        <is>
-          <t>3-ALTO</t>
-        </is>
-      </c>
-      <c r="C91" s="29" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D91" s="29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E91" s="29" t="n">
-        <v>7400.4</v>
-      </c>
-      <c r="F91" s="29" t="n">
-        <v>967</v>
-      </c>
-      <c r="G91" s="29" t="n">
-        <v>26936</v>
-      </c>
-      <c r="H91" s="28" t="inlineStr">
-        <is>
-          <t>TRASPASAR 967 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I91" s="28" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="28" t="inlineStr">
-        <is>
-          <t>DABIGATRAN ETEXILATO CP 150 MG</t>
-        </is>
-      </c>
-      <c r="B92" s="28" t="inlineStr">
-        <is>
-          <t>3-ALTO</t>
-        </is>
-      </c>
-      <c r="C92" s="29" t="n">
-        <v>2490</v>
-      </c>
-      <c r="D92" s="29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E92" s="29" t="n">
-        <v>5013.9</v>
-      </c>
-      <c r="F92" s="29" t="n">
-        <v>325</v>
-      </c>
-      <c r="G92" s="29" t="n">
-        <v>24420</v>
-      </c>
-      <c r="H92" s="28" t="inlineStr">
-        <is>
-          <t>TRASPASAR 325 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I92" s="28" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="28" t="inlineStr">
-        <is>
-          <t>METFORMINA 1000 MG CM LIBERACION MODIFICADA</t>
-        </is>
-      </c>
-      <c r="B93" s="28" t="inlineStr">
-        <is>
-          <t>3-ALTO</t>
-        </is>
-      </c>
-      <c r="C93" s="29" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D93" s="29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E93" s="29" t="n">
-        <v>5312.9</v>
-      </c>
-      <c r="F93" s="29" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G93" s="29" t="n">
-        <v>9500</v>
-      </c>
-      <c r="H93" s="28" t="inlineStr">
-        <is>
-          <t>TRASPASAR 2000 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I93" s="28" t="inlineStr"/>
+      <c r="H93" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 420 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I93" s="22" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="28" t="inlineStr">
         <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+          <t>LOSARTAN 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B94" s="28" t="inlineStr">
@@ -7214,35 +7171,31 @@
         </is>
       </c>
       <c r="C94" s="29" t="n">
-        <v>2700</v>
+        <v>5700</v>
       </c>
       <c r="D94" s="29" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="E94" s="29" t="n">
-        <v>4895.4</v>
+        <v>9495.6</v>
       </c>
       <c r="F94" s="29" t="n">
-        <v>1320</v>
+        <v>2400</v>
       </c>
       <c r="G94" s="29" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="H94" s="28" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I94" s="28" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1320 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2400 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I94" s="28" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="28" t="inlineStr">
         <is>
-          <t>HIDROXICLOROQUINA CM 200 MG</t>
+          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B95" s="28" t="inlineStr">
@@ -7251,23 +7204,23 @@
         </is>
       </c>
       <c r="C95" s="29" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="D95" s="29" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="E95" s="29" t="n">
-        <v>3513.8</v>
+        <v>7400.4</v>
       </c>
       <c r="F95" s="29" t="n">
-        <v>960</v>
+        <v>1339</v>
       </c>
       <c r="G95" s="29" t="n">
-        <v>44340</v>
+        <v>26936</v>
       </c>
       <c r="H95" s="28" t="inlineStr">
         <is>
-          <t>TRASPASAR 960 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1339 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I95" s="28" t="inlineStr"/>
@@ -7275,7 +7228,7 @@
     <row r="96">
       <c r="A96" s="28" t="inlineStr">
         <is>
-          <t>DIVALPROATO SODICO CM 500 MG LIBRACION MODIFICADA</t>
+          <t>DABIGATRAN ETEXILATO CP 150 MG</t>
         </is>
       </c>
       <c r="B96" s="28" t="inlineStr">
@@ -7284,23 +7237,23 @@
         </is>
       </c>
       <c r="C96" s="29" t="n">
-        <v>700</v>
+        <v>2490</v>
       </c>
       <c r="D96" s="29" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E96" s="29" t="n">
-        <v>2114.8</v>
+        <v>5013.9</v>
       </c>
       <c r="F96" s="29" t="n">
-        <v>22</v>
+        <v>565</v>
       </c>
       <c r="G96" s="29" t="n">
-        <v>43100</v>
+        <v>24420</v>
       </c>
       <c r="H96" s="28" t="inlineStr">
         <is>
-          <t>TRASPASAR 22 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 565 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I96" s="28" t="inlineStr"/>
@@ -7308,7 +7261,7 @@
     <row r="97">
       <c r="A97" s="28" t="inlineStr">
         <is>
-          <t>AMITRIPTILINA 25 MG COMPRIMIDO</t>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
         </is>
       </c>
       <c r="B97" s="28" t="inlineStr">
@@ -7317,225 +7270,233 @@
         </is>
       </c>
       <c r="C97" s="29" t="n">
-        <v>400</v>
+        <v>2460</v>
       </c>
       <c r="D97" s="29" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="E97" s="29" t="n">
-        <v>736</v>
+        <v>4895.4</v>
       </c>
       <c r="F97" s="29" t="n">
-        <v>100</v>
+        <v>1560</v>
       </c>
       <c r="G97" s="29" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H97" s="28" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I97" s="28" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I97" s="28" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1560 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="28" t="inlineStr">
         <is>
+          <t>HIDROXICLOROQUINA CM 200 MG</t>
+        </is>
+      </c>
+      <c r="B98" s="28" t="inlineStr">
+        <is>
+          <t>3-ALTO</t>
+        </is>
+      </c>
+      <c r="C98" s="29" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D98" s="29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E98" s="29" t="n">
+        <v>3513.8</v>
+      </c>
+      <c r="F98" s="29" t="n">
+        <v>960</v>
+      </c>
+      <c r="G98" s="29" t="n">
+        <v>44340</v>
+      </c>
+      <c r="H98" s="28" t="inlineStr">
+        <is>
+          <t>TRASPASAR 960 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I98" s="28" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="28" t="inlineStr">
+        <is>
+          <t>DIVALPROATO SODICO CM 500 MG LIBRACION MODIFICADA</t>
+        </is>
+      </c>
+      <c r="B99" s="28" t="inlineStr">
+        <is>
+          <t>3-ALTO</t>
+        </is>
+      </c>
+      <c r="C99" s="29" t="n">
+        <v>700</v>
+      </c>
+      <c r="D99" s="29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E99" s="29" t="n">
+        <v>2114.8</v>
+      </c>
+      <c r="F99" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="G99" s="29" t="n">
+        <v>43100</v>
+      </c>
+      <c r="H99" s="28" t="inlineStr">
+        <is>
+          <t>TRASPASAR 22 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I99" s="28" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="28" t="inlineStr">
+        <is>
           <t>MOMETASONA 50 MCG/DOSIS SUSPENSION NASAL</t>
         </is>
       </c>
-      <c r="B98" s="28" t="inlineStr">
+      <c r="B100" s="28" t="inlineStr">
         <is>
           <t>3-ALTO</t>
         </is>
       </c>
-      <c r="C98" s="29" t="n">
+      <c r="C100" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="D98" s="29" t="n">
+      <c r="D100" s="29" t="n">
         <v>3.1</v>
       </c>
-      <c r="E98" s="29" t="n">
+      <c r="E100" s="29" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="F98" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G98" s="29" t="n">
+      <c r="F100" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G100" s="29" t="n">
         <v>109</v>
       </c>
-      <c r="H98" s="28" t="inlineStr">
-        <is>
-          <t>TRASPASAR 4 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I98" s="28" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>4-MODERADO</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="n">
-        <v>3300</v>
-      </c>
-      <c r="D99" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E99" s="6" t="n">
-        <v>4990.7</v>
-      </c>
-      <c r="F99" s="6" t="n">
-        <v>810</v>
-      </c>
-      <c r="G99" s="6" t="n">
-        <v>10290</v>
-      </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 810 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>CETIRIZINA 10 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>4-MODERADO</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="n">
-        <v>138</v>
-      </c>
-      <c r="D100" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E100" s="6" t="n">
-        <v>296.2</v>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G100" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 2 ud.</t>
-        </is>
-      </c>
+      <c r="H100" s="28" t="inlineStr">
+        <is>
+          <t>TRASPASAR 8 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I100" s="28" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
+          <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>4-MODERADO</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>3120</v>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>4990.7</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>990</v>
+      </c>
+      <c r="G101" s="6" t="n">
+        <v>10290</v>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 990 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>ATORVASTATINA 40 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>4-MODERADO</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>3320</v>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>5014.3</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G102" s="6" t="n">
+        <v>11700</v>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
           <t>MODAFINILO 200 MG COMPRIMIDO</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>4-MODERADO</t>
         </is>
       </c>
-      <c r="C101" s="6" t="n">
+      <c r="C103" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D103" s="6" t="n">
         <v>5.7</v>
       </c>
-      <c r="E101" s="6" t="n">
+      <c r="E103" s="6" t="n">
         <v>100.6</v>
       </c>
-      <c r="F101" s="6" t="n">
+      <c r="F103" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="G101" s="6" t="n">
+      <c r="G103" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H103" s="5" t="inlineStr">
         <is>
           <t>TRASPASAR 15 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="30" t="inlineStr">
-        <is>
-          <t>OMEPRAZOL 20 MG CAPSULA</t>
-        </is>
-      </c>
-      <c r="B102" s="30" t="inlineStr">
-        <is>
-          <t>5-OK</t>
-        </is>
-      </c>
-      <c r="C102" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="31" t="n">
-        <v>7946.1</v>
-      </c>
-      <c r="F102" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="31" t="n">
-        <v>49000</v>
-      </c>
-      <c r="H102" s="30" t="inlineStr"/>
-      <c r="I102" s="30" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="30" t="inlineStr">
-        <is>
-          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B103" s="30" t="inlineStr">
-        <is>
-          <t>5-OK</t>
-        </is>
-      </c>
-      <c r="C103" s="31" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D103" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E103" s="31" t="n">
-        <v>6002.8</v>
-      </c>
-      <c r="F103" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="31" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H103" s="30" t="inlineStr"/>
-      <c r="I103" s="30" t="inlineStr"/>
+      <c r="I103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="30" t="inlineStr">
         <is>
-          <t>CALCIO CARBONATO C/VITAMINA D CM O CP</t>
+          <t>OMEPRAZOL 20 MG CAPSULA</t>
         </is>
       </c>
       <c r="B104" s="30" t="inlineStr">
@@ -7544,19 +7505,19 @@
         </is>
       </c>
       <c r="C104" s="31" t="n">
-        <v>4090</v>
+        <v>0</v>
       </c>
       <c r="D104" s="31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="E104" s="31" t="n">
-        <v>5539.2</v>
+        <v>7946.1</v>
       </c>
       <c r="F104" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G104" s="31" t="n">
-        <v>91650</v>
+        <v>49000</v>
       </c>
       <c r="H104" s="30" t="inlineStr"/>
       <c r="I104" s="30" t="inlineStr"/>
@@ -7564,7 +7525,7 @@
     <row r="105">
       <c r="A105" s="30" t="inlineStr">
         <is>
-          <t>CELECOXIB 200 MG CAPSULA</t>
+          <t>FUROSEMIDA 40 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B105" s="30" t="inlineStr">
@@ -7573,19 +7534,19 @@
         </is>
       </c>
       <c r="C105" s="31" t="n">
-        <v>3500</v>
+        <v>600</v>
       </c>
       <c r="D105" s="31" t="n">
-        <v>5.5</v>
+        <v>0.7</v>
       </c>
       <c r="E105" s="31" t="n">
-        <v>5120.3</v>
+        <v>6002.8</v>
       </c>
       <c r="F105" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="31" t="n">
-        <v>18500</v>
+        <v>4000</v>
       </c>
       <c r="H105" s="30" t="inlineStr"/>
       <c r="I105" s="30" t="inlineStr"/>
@@ -7593,7 +7554,7 @@
     <row r="106">
       <c r="A106" s="30" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 40 MG COMPRIMIDO</t>
+          <t>CALCIO CARBONATO C/VITAMINA D CM O CP</t>
         </is>
       </c>
       <c r="B106" s="30" t="inlineStr">
@@ -7602,19 +7563,19 @@
         </is>
       </c>
       <c r="C106" s="31" t="n">
-        <v>3320</v>
+        <v>4090</v>
       </c>
       <c r="D106" s="31" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="E106" s="31" t="n">
-        <v>5014.3</v>
+        <v>5539.2</v>
       </c>
       <c r="F106" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G106" s="31" t="n">
-        <v>11700</v>
+        <v>91650</v>
       </c>
       <c r="H106" s="30" t="inlineStr"/>
       <c r="I106" s="30" t="inlineStr"/>
@@ -7622,7 +7583,7 @@
     <row r="107">
       <c r="A107" s="30" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 20 MG COMPRIMIDO</t>
+          <t>CELECOXIB 200 MG CAPSULA</t>
         </is>
       </c>
       <c r="B107" s="30" t="inlineStr">
@@ -7631,19 +7592,19 @@
         </is>
       </c>
       <c r="C107" s="31" t="n">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="D107" s="31" t="n">
-        <v>7.3</v>
+        <v>5.5</v>
       </c>
       <c r="E107" s="31" t="n">
-        <v>3618.2</v>
+        <v>5120.3</v>
       </c>
       <c r="F107" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G107" s="31" t="n">
-        <v>47000</v>
+        <v>18500</v>
       </c>
       <c r="H107" s="30" t="inlineStr"/>
       <c r="I107" s="30" t="inlineStr"/>
@@ -7651,7 +7612,7 @@
     <row r="108">
       <c r="A108" s="30" t="inlineStr">
         <is>
-          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
+          <t>ATORVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B108" s="30" t="inlineStr">
@@ -7660,19 +7621,19 @@
         </is>
       </c>
       <c r="C108" s="31" t="n">
-        <v>3090</v>
+        <v>3700</v>
       </c>
       <c r="D108" s="31" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="E108" s="31" t="n">
-        <v>2819.1</v>
+        <v>3618.2</v>
       </c>
       <c r="F108" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="31" t="n">
-        <v>3060</v>
+        <v>47000</v>
       </c>
       <c r="H108" s="30" t="inlineStr"/>
       <c r="I108" s="30" t="inlineStr"/>
@@ -7680,7 +7641,7 @@
     <row r="109">
       <c r="A109" s="30" t="inlineStr">
         <is>
-          <t>TRAMADOL + PARACETAMOL 37,5 MG/325 MG CM</t>
+          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B109" s="30" t="inlineStr">
@@ -7689,19 +7650,19 @@
         </is>
       </c>
       <c r="C109" s="31" t="n">
-        <v>1800</v>
+        <v>2490</v>
       </c>
       <c r="D109" s="31" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="E109" s="31" t="n">
-        <v>2724</v>
+        <v>2819.1</v>
       </c>
       <c r="F109" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="31" t="n">
-        <v>0</v>
+        <v>15060</v>
       </c>
       <c r="H109" s="30" t="inlineStr"/>
       <c r="I109" s="30" t="inlineStr"/>
@@ -7709,7 +7670,7 @@
     <row r="110">
       <c r="A110" s="30" t="inlineStr">
         <is>
-          <t>SERTRALINA CM 50 MG</t>
+          <t>TRAMADOL + PARACETAMOL 37,5 MG/325 MG CM</t>
         </is>
       </c>
       <c r="B110" s="30" t="inlineStr">
@@ -7718,19 +7679,19 @@
         </is>
       </c>
       <c r="C110" s="31" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="D110" s="31" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="E110" s="31" t="n">
-        <v>2425.2</v>
+        <v>2724</v>
       </c>
       <c r="F110" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="31" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="H110" s="30" t="inlineStr"/>
       <c r="I110" s="30" t="inlineStr"/>
@@ -7738,7 +7699,7 @@
     <row r="111">
       <c r="A111" s="30" t="inlineStr">
         <is>
-          <t>ENALAPRIL 10 MG COMPRIMIDO</t>
+          <t>SERTRALINA CM 50 MG</t>
         </is>
       </c>
       <c r="B111" s="30" t="inlineStr">
@@ -7747,19 +7708,19 @@
         </is>
       </c>
       <c r="C111" s="31" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="D111" s="31" t="n">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="E111" s="31" t="n">
-        <v>2881.6</v>
+        <v>2425.2</v>
       </c>
       <c r="F111" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="31" t="n">
-        <v>22000</v>
+        <v>13000</v>
       </c>
       <c r="H111" s="30" t="inlineStr"/>
       <c r="I111" s="30" t="inlineStr"/>
@@ -7767,7 +7728,7 @@
     <row r="112">
       <c r="A112" s="30" t="inlineStr">
         <is>
-          <t>QUETIAPINA 25 MG COMPRIMIDO</t>
+          <t>ENALAPRIL 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B112" s="30" t="inlineStr">
@@ -7776,19 +7737,19 @@
         </is>
       </c>
       <c r="C112" s="31" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="D112" s="31" t="n">
-        <v>6.7</v>
+        <v>11.9</v>
       </c>
       <c r="E112" s="31" t="n">
-        <v>2022.9</v>
+        <v>2881.6</v>
       </c>
       <c r="F112" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="31" t="n">
-        <v>17000</v>
+        <v>22000</v>
       </c>
       <c r="H112" s="30" t="inlineStr"/>
       <c r="I112" s="30" t="inlineStr"/>
@@ -7796,7 +7757,7 @@
     <row r="113">
       <c r="A113" s="30" t="inlineStr">
         <is>
-          <t>AMLODIPINO 10 MG COMPRIMIDO</t>
+          <t>QUETIAPINA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B113" s="30" t="inlineStr">
@@ -7808,16 +7769,16 @@
         <v>2000</v>
       </c>
       <c r="D113" s="31" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="E113" s="31" t="n">
-        <v>2073.8</v>
+        <v>2022.9</v>
       </c>
       <c r="F113" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G113" s="31" t="n">
-        <v>21000</v>
+        <v>17000</v>
       </c>
       <c r="H113" s="30" t="inlineStr"/>
       <c r="I113" s="30" t="inlineStr"/>
@@ -7825,7 +7786,7 @@
     <row r="114">
       <c r="A114" s="30" t="inlineStr">
         <is>
-          <t>METOTREXATO 2,5 MG COMPRIMIDO</t>
+          <t>AMLODIPINO 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B114" s="30" t="inlineStr">
@@ -7840,13 +7801,13 @@
         <v>0</v>
       </c>
       <c r="E114" s="31" t="n">
-        <v>2060.9</v>
+        <v>2073.8</v>
       </c>
       <c r="F114" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G114" s="31" t="n">
-        <v>5900</v>
+        <v>21000</v>
       </c>
       <c r="H114" s="30" t="inlineStr"/>
       <c r="I114" s="30" t="inlineStr"/>
@@ -7854,7 +7815,7 @@
     <row r="115">
       <c r="A115" s="30" t="inlineStr">
         <is>
-          <t>ZOPICLONA CM 7,5 MG</t>
+          <t>METOTREXATO 2,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B115" s="30" t="inlineStr">
@@ -7863,19 +7824,19 @@
         </is>
       </c>
       <c r="C115" s="31" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D115" s="31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="E115" s="31" t="n">
-        <v>1695.4</v>
+        <v>2060.9</v>
       </c>
       <c r="F115" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="31" t="n">
-        <v>3000</v>
+        <v>5900</v>
       </c>
       <c r="H115" s="30" t="inlineStr"/>
       <c r="I115" s="30" t="inlineStr"/>
@@ -7883,7 +7844,7 @@
     <row r="116">
       <c r="A116" s="30" t="inlineStr">
         <is>
-          <t>CLOZAPINA 100 MG COMPRIMIDO</t>
+          <t>ZOPICLONA CM 7,5 MG</t>
         </is>
       </c>
       <c r="B116" s="30" t="inlineStr">
@@ -7892,19 +7853,19 @@
         </is>
       </c>
       <c r="C116" s="31" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="D116" s="31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="E116" s="31" t="n">
-        <v>2081.1</v>
+        <v>1695.4</v>
       </c>
       <c r="F116" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="31" t="n">
-        <v>2110</v>
+        <v>3000</v>
       </c>
       <c r="H116" s="30" t="inlineStr"/>
       <c r="I116" s="30" t="inlineStr"/>
@@ -7912,7 +7873,7 @@
     <row r="117">
       <c r="A117" s="30" t="inlineStr">
         <is>
-          <t>VENLAFAXINA 75 MG COMPRIMIDOS LIBERACION MODIFICADA</t>
+          <t>CLOZAPINA 100 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B117" s="30" t="inlineStr">
@@ -7921,19 +7882,19 @@
         </is>
       </c>
       <c r="C117" s="31" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="D117" s="31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="E117" s="31" t="n">
-        <v>1957.5</v>
+        <v>2081.1</v>
       </c>
       <c r="F117" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G117" s="31" t="n">
-        <v>40500</v>
+        <v>2110</v>
       </c>
       <c r="H117" s="30" t="inlineStr"/>
       <c r="I117" s="30" t="inlineStr"/>
@@ -7941,7 +7902,7 @@
     <row r="118">
       <c r="A118" s="30" t="inlineStr">
         <is>
-          <t>HIDRALAZINA 50 MG COMPRIMIDO</t>
+          <t>VENLAFAXINA 75 MG COMPRIMIDOS LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B118" s="30" t="inlineStr">
@@ -7950,19 +7911,19 @@
         </is>
       </c>
       <c r="C118" s="31" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
       <c r="D118" s="31" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="E118" s="31" t="n">
-        <v>967.6</v>
+        <v>1957.5</v>
       </c>
       <c r="F118" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="31" t="n">
-        <v>52290</v>
+        <v>40500</v>
       </c>
       <c r="H118" s="30" t="inlineStr"/>
       <c r="I118" s="30" t="inlineStr"/>
@@ -7970,7 +7931,7 @@
     <row r="119">
       <c r="A119" s="30" t="inlineStr">
         <is>
-          <t>PREDNISONA 5 MG COMPRIMIDO</t>
+          <t>HIDRALAZINA 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B119" s="30" t="inlineStr">
@@ -7979,19 +7940,19 @@
         </is>
       </c>
       <c r="C119" s="31" t="n">
-        <v>1110</v>
+        <v>1320</v>
       </c>
       <c r="D119" s="31" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="E119" s="31" t="n">
-        <v>1681</v>
+        <v>967.6</v>
       </c>
       <c r="F119" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="31" t="n">
-        <v>15000</v>
+        <v>52290</v>
       </c>
       <c r="H119" s="30" t="inlineStr"/>
       <c r="I119" s="30" t="inlineStr"/>
@@ -7999,7 +7960,7 @@
     <row r="120">
       <c r="A120" s="30" t="inlineStr">
         <is>
-          <t>OLANZAPINA 10 MG CM UNIDAD</t>
+          <t>PREDNISONA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B120" s="30" t="inlineStr">
@@ -8008,19 +7969,19 @@
         </is>
       </c>
       <c r="C120" s="31" t="n">
-        <v>1000</v>
+        <v>1110</v>
       </c>
       <c r="D120" s="31" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="E120" s="31" t="n">
-        <v>1916.4</v>
+        <v>1681</v>
       </c>
       <c r="F120" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G120" s="31" t="n">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="H120" s="30" t="inlineStr"/>
       <c r="I120" s="30" t="inlineStr"/>
@@ -8028,7 +7989,7 @@
     <row r="121">
       <c r="A121" s="30" t="inlineStr">
         <is>
-          <t>BUPROPION (ANFEBUTAMONA) 150 MG CM LIBERACION MODIFICADA</t>
+          <t>OLANZAPINA 10 MG CM UNIDAD</t>
         </is>
       </c>
       <c r="B121" s="30" t="inlineStr">
@@ -8037,19 +7998,19 @@
         </is>
       </c>
       <c r="C121" s="31" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="D121" s="31" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="E121" s="31" t="n">
-        <v>1757.1</v>
+        <v>1916.4</v>
       </c>
       <c r="F121" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G121" s="31" t="n">
-        <v>1650</v>
+        <v>8000</v>
       </c>
       <c r="H121" s="30" t="inlineStr"/>
       <c r="I121" s="30" t="inlineStr"/>
@@ -8057,7 +8018,7 @@
     <row r="122">
       <c r="A122" s="30" t="inlineStr">
         <is>
-          <t>CARVEDILOL 12,5 MG COMPRIMIDO</t>
+          <t>BUPROPION (ANFEBUTAMONA) 150 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B122" s="30" t="inlineStr">
@@ -8066,19 +8027,19 @@
         </is>
       </c>
       <c r="C122" s="31" t="n">
-        <v>2460</v>
+        <v>1800</v>
       </c>
       <c r="D122" s="31" t="n">
-        <v>11.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E122" s="31" t="n">
-        <v>1452.9</v>
+        <v>1757.1</v>
       </c>
       <c r="F122" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G122" s="31" t="n">
-        <v>34410</v>
+        <v>1650</v>
       </c>
       <c r="H122" s="30" t="inlineStr"/>
       <c r="I122" s="30" t="inlineStr"/>
@@ -8086,7 +8047,7 @@
     <row r="123">
       <c r="A123" s="30" t="inlineStr">
         <is>
-          <t>JERINGA P/INSULINA C/AGUJA 1 ML 100 UI/A. FIJA 29-31G X 6MM</t>
+          <t>CARVEDILOL 12,5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B123" s="30" t="inlineStr">
@@ -8095,19 +8056,19 @@
         </is>
       </c>
       <c r="C123" s="31" t="n">
-        <v>0</v>
+        <v>2460</v>
       </c>
       <c r="D123" s="31" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="E123" s="31" t="n">
-        <v>1677.9</v>
+        <v>1452.9</v>
       </c>
       <c r="F123" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="31" t="n">
-        <v>0</v>
+        <v>34410</v>
       </c>
       <c r="H123" s="30" t="inlineStr"/>
       <c r="I123" s="30" t="inlineStr"/>
@@ -8115,7 +8076,7 @@
     <row r="124">
       <c r="A124" s="30" t="inlineStr">
         <is>
-          <t>METILDOPA 250 MG COMPRIMIDO</t>
+          <t>JERINGA P/INSULINA C/AGUJA 1 ML 100 UI/A. FIJA 29-31G X 6MM</t>
         </is>
       </c>
       <c r="B124" s="30" t="inlineStr">
@@ -8124,19 +8085,19 @@
         </is>
       </c>
       <c r="C124" s="31" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D124" s="31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="E124" s="31" t="n">
-        <v>960</v>
+        <v>1677.9</v>
       </c>
       <c r="F124" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G124" s="31" t="n">
-        <v>35700</v>
+        <v>0</v>
       </c>
       <c r="H124" s="30" t="inlineStr"/>
       <c r="I124" s="30" t="inlineStr"/>
@@ -8144,7 +8105,7 @@
     <row r="125">
       <c r="A125" s="30" t="inlineStr">
         <is>
-          <t>FLUOXETINA 20 MG COMPRIMIDO</t>
+          <t>METILDOPA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B125" s="30" t="inlineStr">
@@ -8153,19 +8114,19 @@
         </is>
       </c>
       <c r="C125" s="31" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="D125" s="31" t="n">
-        <v>5.9</v>
+        <v>2.8</v>
       </c>
       <c r="E125" s="31" t="n">
-        <v>1617</v>
+        <v>960</v>
       </c>
       <c r="F125" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="31" t="n">
-        <v>2000</v>
+        <v>35700</v>
       </c>
       <c r="H125" s="30" t="inlineStr"/>
       <c r="I125" s="30" t="inlineStr"/>
@@ -8173,7 +8134,7 @@
     <row r="126">
       <c r="A126" s="30" t="inlineStr">
         <is>
-          <t>TRAMADOL CP 50 MG</t>
+          <t>FLUOXETINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B126" s="30" t="inlineStr">
@@ -8182,19 +8143,19 @@
         </is>
       </c>
       <c r="C126" s="31" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="D126" s="31" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="E126" s="31" t="n">
-        <v>1851.4</v>
+        <v>1617</v>
       </c>
       <c r="F126" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G126" s="31" t="n">
-        <v>6700</v>
+        <v>2000</v>
       </c>
       <c r="H126" s="30" t="inlineStr"/>
       <c r="I126" s="30" t="inlineStr"/>
@@ -8202,7 +8163,7 @@
     <row r="127">
       <c r="A127" s="30" t="inlineStr">
         <is>
-          <t>METILFENIDATO 10 MG CM LIBERACION MODIFICADA</t>
+          <t>TRAMADOL CP 50 MG</t>
         </is>
       </c>
       <c r="B127" s="30" t="inlineStr">
@@ -8211,19 +8172,19 @@
         </is>
       </c>
       <c r="C127" s="31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D127" s="31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E127" s="31" t="n">
-        <v>1866.3</v>
+        <v>1851.4</v>
       </c>
       <c r="F127" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G127" s="31" t="n">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="H127" s="30" t="inlineStr"/>
       <c r="I127" s="30" t="inlineStr"/>
@@ -8231,7 +8192,7 @@
     <row r="128">
       <c r="A128" s="30" t="inlineStr">
         <is>
-          <t>CLOPIDOGREL 75 MG COMPRIMIDO</t>
+          <t>METILFENIDATO 10 MG CM LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B128" s="30" t="inlineStr">
@@ -8240,19 +8201,19 @@
         </is>
       </c>
       <c r="C128" s="31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D128" s="31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="E128" s="31" t="n">
-        <v>1556.7</v>
+        <v>1866.3</v>
       </c>
       <c r="F128" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G128" s="31" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="H128" s="30" t="inlineStr"/>
       <c r="I128" s="30" t="inlineStr"/>
@@ -8260,7 +8221,7 @@
     <row r="129">
       <c r="A129" s="30" t="inlineStr">
         <is>
-          <t>ACIDO FOLICO CM 5 MG</t>
+          <t>CLOPIDOGREL 75 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B129" s="30" t="inlineStr">
@@ -8269,19 +8230,19 @@
         </is>
       </c>
       <c r="C129" s="31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D129" s="31" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="E129" s="31" t="n">
-        <v>739</v>
+        <v>1556.7</v>
       </c>
       <c r="F129" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G129" s="31" t="n">
-        <v>14890</v>
+        <v>24000</v>
       </c>
       <c r="H129" s="30" t="inlineStr"/>
       <c r="I129" s="30" t="inlineStr"/>
@@ -8289,7 +8250,7 @@
     <row r="130">
       <c r="A130" s="30" t="inlineStr">
         <is>
-          <t>PREGABALINA 150 MG CAPSULA</t>
+          <t>ACIDO FOLICO CM 5 MG</t>
         </is>
       </c>
       <c r="B130" s="30" t="inlineStr">
@@ -8298,19 +8259,19 @@
         </is>
       </c>
       <c r="C130" s="31" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="D130" s="31" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="E130" s="31" t="n">
-        <v>1439.3</v>
+        <v>739</v>
       </c>
       <c r="F130" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G130" s="31" t="n">
-        <v>5600</v>
+        <v>14890</v>
       </c>
       <c r="H130" s="30" t="inlineStr"/>
       <c r="I130" s="30" t="inlineStr"/>
@@ -8318,7 +8279,7 @@
     <row r="131">
       <c r="A131" s="30" t="inlineStr">
         <is>
-          <t>LEFLUNOMIDA 20 MG COMPRIMIDO</t>
+          <t>PREGABALINA 150 MG CAPSULA</t>
         </is>
       </c>
       <c r="B131" s="30" t="inlineStr">
@@ -8327,19 +8288,19 @@
         </is>
       </c>
       <c r="C131" s="31" t="n">
-        <v>1200</v>
+        <v>2200</v>
       </c>
       <c r="D131" s="31" t="n">
-        <v>6.7</v>
+        <v>11.7</v>
       </c>
       <c r="E131" s="31" t="n">
-        <v>1450.7</v>
+        <v>1439.3</v>
       </c>
       <c r="F131" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G131" s="31" t="n">
-        <v>11640</v>
+        <v>5600</v>
       </c>
       <c r="H131" s="30" t="inlineStr"/>
       <c r="I131" s="30" t="inlineStr"/>
@@ -8347,7 +8308,7 @@
     <row r="132">
       <c r="A132" s="30" t="inlineStr">
         <is>
-          <t>CLONAZEPAM CM 0,5 MG</t>
+          <t>LEFLUNOMIDA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B132" s="30" t="inlineStr">
@@ -8356,19 +8317,19 @@
         </is>
       </c>
       <c r="C132" s="31" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="D132" s="31" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="E132" s="31" t="n">
-        <v>1618.2</v>
+        <v>1450.7</v>
       </c>
       <c r="F132" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G132" s="31" t="n">
-        <v>0</v>
+        <v>11640</v>
       </c>
       <c r="H132" s="30" t="inlineStr"/>
       <c r="I132" s="30" t="inlineStr"/>
@@ -8376,7 +8337,7 @@
     <row r="133">
       <c r="A133" s="30" t="inlineStr">
         <is>
-          <t>ARIPIPRAZOL 10 MG CM</t>
+          <t>CLONAZEPAM CM 0,5 MG</t>
         </is>
       </c>
       <c r="B133" s="30" t="inlineStr">
@@ -8385,13 +8346,13 @@
         </is>
       </c>
       <c r="C133" s="31" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="D133" s="31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="E133" s="31" t="n">
-        <v>1409.4</v>
+        <v>1618.2</v>
       </c>
       <c r="F133" s="31" t="n">
         <v>0</v>
@@ -8405,7 +8366,7 @@
     <row r="134">
       <c r="A134" s="30" t="inlineStr">
         <is>
-          <t>RISPERIDONA CM 3 MG</t>
+          <t>ARIPIPRAZOL 10 MG CM</t>
         </is>
       </c>
       <c r="B134" s="30" t="inlineStr">
@@ -8414,19 +8375,19 @@
         </is>
       </c>
       <c r="C134" s="31" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="D134" s="31" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="E134" s="31" t="n">
-        <v>1328.7</v>
+        <v>1409.4</v>
       </c>
       <c r="F134" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="31" t="n">
-        <v>19700</v>
+        <v>0</v>
       </c>
       <c r="H134" s="30" t="inlineStr"/>
       <c r="I134" s="30" t="inlineStr"/>
@@ -8434,7 +8395,7 @@
     <row r="135">
       <c r="A135" s="30" t="inlineStr">
         <is>
-          <t>MESALAZINA 500 MG COMPRIMIDO</t>
+          <t>RISPERIDONA CM 3 MG</t>
         </is>
       </c>
       <c r="B135" s="30" t="inlineStr">
@@ -8443,19 +8404,19 @@
         </is>
       </c>
       <c r="C135" s="31" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D135" s="31" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="E135" s="31" t="n">
-        <v>546.5</v>
+        <v>1328.7</v>
       </c>
       <c r="F135" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G135" s="31" t="n">
-        <v>9900</v>
+        <v>19700</v>
       </c>
       <c r="H135" s="30" t="inlineStr"/>
       <c r="I135" s="30" t="inlineStr"/>
@@ -8463,7 +8424,7 @@
     <row r="136">
       <c r="A136" s="30" t="inlineStr">
         <is>
-          <t>LEVOCETIRIZINA 5 MG COMPRIMIDO</t>
+          <t>MESALAZINA 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B136" s="30" t="inlineStr">
@@ -8472,19 +8433,19 @@
         </is>
       </c>
       <c r="C136" s="31" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D136" s="31" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="E136" s="31" t="n">
-        <v>1268.9</v>
+        <v>546.5</v>
       </c>
       <c r="F136" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G136" s="31" t="n">
-        <v>6420</v>
+        <v>9900</v>
       </c>
       <c r="H136" s="30" t="inlineStr"/>
       <c r="I136" s="30" t="inlineStr"/>
@@ -8492,7 +8453,7 @@
     <row r="137">
       <c r="A137" s="30" t="inlineStr">
         <is>
-          <t>AMLODIPINO 5 MG COMPRIMIDO</t>
+          <t>LEVOCETIRIZINA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B137" s="30" t="inlineStr">
@@ -8501,19 +8462,19 @@
         </is>
       </c>
       <c r="C137" s="31" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="D137" s="31" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="E137" s="31" t="n">
-        <v>1220.8</v>
+        <v>1268.9</v>
       </c>
       <c r="F137" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G137" s="31" t="n">
-        <v>12000</v>
+        <v>6420</v>
       </c>
       <c r="H137" s="30" t="inlineStr"/>
       <c r="I137" s="30" t="inlineStr"/>
@@ -8521,7 +8482,7 @@
     <row r="138">
       <c r="A138" s="30" t="inlineStr">
         <is>
-          <t>METFORMINA 850 MG COMPRIMIDO</t>
+          <t>AMLODIPINO 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B138" s="30" t="inlineStr">
@@ -8530,19 +8491,19 @@
         </is>
       </c>
       <c r="C138" s="31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D138" s="31" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E138" s="31" t="n">
-        <v>1049.1</v>
+        <v>1220.8</v>
       </c>
       <c r="F138" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G138" s="31" t="n">
-        <v>32400</v>
+        <v>12000</v>
       </c>
       <c r="H138" s="30" t="inlineStr"/>
       <c r="I138" s="30" t="inlineStr"/>
@@ -8550,7 +8511,7 @@
     <row r="139">
       <c r="A139" s="30" t="inlineStr">
         <is>
-          <t>CLONAZEPAM CM 2 MG</t>
+          <t>METFORMINA 850 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B139" s="30" t="inlineStr">
@@ -8559,19 +8520,19 @@
         </is>
       </c>
       <c r="C139" s="31" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="D139" s="31" t="n">
-        <v>25.8</v>
+        <v>0</v>
       </c>
       <c r="E139" s="31" t="n">
-        <v>1484.1</v>
+        <v>1049.1</v>
       </c>
       <c r="F139" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G139" s="31" t="n">
-        <v>0</v>
+        <v>32400</v>
       </c>
       <c r="H139" s="30" t="inlineStr"/>
       <c r="I139" s="30" t="inlineStr"/>
@@ -8579,7 +8540,7 @@
     <row r="140">
       <c r="A140" s="30" t="inlineStr">
         <is>
-          <t>TRAZODONA CM 100 MG</t>
+          <t>CLONAZEPAM CM 2 MG</t>
         </is>
       </c>
       <c r="B140" s="30" t="inlineStr">
@@ -8588,19 +8549,19 @@
         </is>
       </c>
       <c r="C140" s="31" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="D140" s="31" t="n">
-        <v>0</v>
+        <v>25.8</v>
       </c>
       <c r="E140" s="31" t="n">
-        <v>737.3</v>
+        <v>1484.1</v>
       </c>
       <c r="F140" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G140" s="31" t="n">
-        <v>4900</v>
+        <v>0</v>
       </c>
       <c r="H140" s="30" t="inlineStr"/>
       <c r="I140" s="30" t="inlineStr"/>
@@ -8608,7 +8569,7 @@
     <row r="141">
       <c r="A141" s="30" t="inlineStr">
         <is>
-          <t>HIDROCLOROTIAZIDA 50 MG CM</t>
+          <t>TRAZODONA CM 100 MG</t>
         </is>
       </c>
       <c r="B141" s="30" t="inlineStr">
@@ -8617,19 +8578,19 @@
         </is>
       </c>
       <c r="C141" s="31" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D141" s="31" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E141" s="31" t="n">
-        <v>1202.8</v>
+        <v>737.3</v>
       </c>
       <c r="F141" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G141" s="31" t="n">
-        <v>24000</v>
+        <v>4900</v>
       </c>
       <c r="H141" s="30" t="inlineStr"/>
       <c r="I141" s="30" t="inlineStr"/>
@@ -8637,7 +8598,7 @@
     <row r="142">
       <c r="A142" s="30" t="inlineStr">
         <is>
-          <t>GABAPENTINA 300 MG CAPSULA</t>
+          <t>HIDROCLOROTIAZIDA 50 MG CM</t>
         </is>
       </c>
       <c r="B142" s="30" t="inlineStr">
@@ -8646,19 +8607,19 @@
         </is>
       </c>
       <c r="C142" s="31" t="n">
-        <v>900</v>
+        <v>3000</v>
       </c>
       <c r="D142" s="31" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="E142" s="31" t="n">
-        <v>1130</v>
+        <v>1202.8</v>
       </c>
       <c r="F142" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G142" s="31" t="n">
-        <v>10170</v>
+        <v>24000</v>
       </c>
       <c r="H142" s="30" t="inlineStr"/>
       <c r="I142" s="30" t="inlineStr"/>
@@ -8666,7 +8627,7 @@
     <row r="143">
       <c r="A143" s="30" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG COMPRIMIDO</t>
+          <t>GABAPENTINA 300 MG CAPSULA</t>
         </is>
       </c>
       <c r="B143" s="30" t="inlineStr">
@@ -8675,19 +8636,19 @@
         </is>
       </c>
       <c r="C143" s="31" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D143" s="31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="E143" s="31" t="n">
-        <v>961.5</v>
+        <v>1130</v>
       </c>
       <c r="F143" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G143" s="31" t="n">
-        <v>15800</v>
+        <v>10170</v>
       </c>
       <c r="H143" s="30" t="inlineStr"/>
       <c r="I143" s="30" t="inlineStr"/>
@@ -8695,7 +8656,7 @@
     <row r="144">
       <c r="A144" s="30" t="inlineStr">
         <is>
-          <t>TAMSULOSINA 400 MCG COMPRIMIDO LIBERACION MODIFICADA</t>
+          <t>RISPERIDONA 1 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B144" s="30" t="inlineStr">
@@ -8704,19 +8665,19 @@
         </is>
       </c>
       <c r="C144" s="31" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D144" s="31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="E144" s="31" t="n">
-        <v>868.1</v>
+        <v>961.5</v>
       </c>
       <c r="F144" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G144" s="31" t="n">
-        <v>9900</v>
+        <v>15800</v>
       </c>
       <c r="H144" s="30" t="inlineStr"/>
       <c r="I144" s="30" t="inlineStr"/>
@@ -8724,7 +8685,7 @@
     <row r="145">
       <c r="A145" s="30" t="inlineStr">
         <is>
-          <t>DESLORATADINA 5 MG COMPRIMIDO</t>
+          <t>TAMSULOSINA 400 MCG COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
       <c r="B145" s="30" t="inlineStr">
@@ -8733,19 +8694,19 @@
         </is>
       </c>
       <c r="C145" s="31" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D145" s="31" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="E145" s="31" t="n">
-        <v>736.7</v>
+        <v>868.1</v>
       </c>
       <c r="F145" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G145" s="31" t="n">
-        <v>37000</v>
+        <v>9900</v>
       </c>
       <c r="H145" s="30" t="inlineStr"/>
       <c r="I145" s="30" t="inlineStr"/>
@@ -8753,7 +8714,7 @@
     <row r="146">
       <c r="A146" s="30" t="inlineStr">
         <is>
-          <t>ZOLPIDEM 10 MG COMPRIMIDO</t>
+          <t>DESLORATADINA 5 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B146" s="30" t="inlineStr">
@@ -8762,19 +8723,19 @@
         </is>
       </c>
       <c r="C146" s="31" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D146" s="31" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="E146" s="31" t="n">
-        <v>843.2</v>
+        <v>736.7</v>
       </c>
       <c r="F146" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G146" s="31" t="n">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="H146" s="30" t="inlineStr"/>
       <c r="I146" s="30" t="inlineStr"/>
@@ -8782,7 +8743,7 @@
     <row r="147">
       <c r="A147" s="30" t="inlineStr">
         <is>
-          <t>ACETATO DE CALCIO 667 MG CM UD</t>
+          <t>ZOLPIDEM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B147" s="30" t="inlineStr">
@@ -8797,13 +8758,13 @@
         <v>0</v>
       </c>
       <c r="E147" s="31" t="n">
-        <v>19.9</v>
+        <v>843.2</v>
       </c>
       <c r="F147" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G147" s="31" t="n">
-        <v>9540</v>
+        <v>0</v>
       </c>
       <c r="H147" s="30" t="inlineStr"/>
       <c r="I147" s="30" t="inlineStr"/>
@@ -8811,7 +8772,7 @@
     <row r="148">
       <c r="A148" s="30" t="inlineStr">
         <is>
-          <t>APIXABAN 5 MG CM</t>
+          <t>ACETATO DE CALCIO 667 MG CM UD</t>
         </is>
       </c>
       <c r="B148" s="30" t="inlineStr">
@@ -8820,19 +8781,19 @@
         </is>
       </c>
       <c r="C148" s="31" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="D148" s="31" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="E148" s="31" t="n">
-        <v>862.8</v>
+        <v>19.9</v>
       </c>
       <c r="F148" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G148" s="31" t="n">
-        <v>600</v>
+        <v>9540</v>
       </c>
       <c r="H148" s="30" t="inlineStr"/>
       <c r="I148" s="30" t="inlineStr"/>
@@ -8840,7 +8801,7 @@
     <row r="149">
       <c r="A149" s="30" t="inlineStr">
         <is>
-          <t>ESCITALOPRAM 10 MG COMPRIMIDO</t>
+          <t>APIXABAN 5 MG CM</t>
         </is>
       </c>
       <c r="B149" s="30" t="inlineStr">
@@ -8849,19 +8810,19 @@
         </is>
       </c>
       <c r="C149" s="31" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D149" s="31" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="E149" s="31" t="n">
-        <v>769.7</v>
+        <v>862.8</v>
       </c>
       <c r="F149" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G149" s="31" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="H149" s="30" t="inlineStr"/>
       <c r="I149" s="30" t="inlineStr"/>
@@ -9081,10 +9042,10 @@
         </is>
       </c>
       <c r="C157" s="31" t="n">
-        <v>1224</v>
+        <v>984</v>
       </c>
       <c r="D157" s="31" t="n">
-        <v>16.4</v>
+        <v>13.2</v>
       </c>
       <c r="E157" s="31" t="n">
         <v>385.3</v>
@@ -9122,7 +9083,7 @@
         <v>0</v>
       </c>
       <c r="G158" s="31" t="n">
-        <v>1560</v>
+        <v>3360</v>
       </c>
       <c r="H158" s="30" t="inlineStr"/>
       <c r="I158" s="30" t="inlineStr"/>
@@ -9197,10 +9158,10 @@
         </is>
       </c>
       <c r="C161" s="31" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D161" s="31" t="n">
-        <v>14.4</v>
+        <v>7.2</v>
       </c>
       <c r="E161" s="31" t="n">
         <v>439.4</v>
@@ -9284,10 +9245,10 @@
         </is>
       </c>
       <c r="C164" s="31" t="n">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="D164" s="31" t="n">
-        <v>7.2</v>
+        <v>2.7</v>
       </c>
       <c r="E164" s="31" t="n">
         <v>504.5</v>
@@ -9371,10 +9332,10 @@
         </is>
       </c>
       <c r="C167" s="31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D167" s="31" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="E167" s="31" t="n">
         <v>363.5</v>
@@ -10067,10 +10028,10 @@
         </is>
       </c>
       <c r="C191" s="31" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D191" s="31" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="E191" s="31" t="n">
         <v>236.3</v>
@@ -10369,7 +10330,7 @@
         <v>0</v>
       </c>
       <c r="G201" s="31" t="n">
-        <v>3210</v>
+        <v>4110</v>
       </c>
       <c r="H201" s="30" t="inlineStr"/>
       <c r="I201" s="30" t="inlineStr"/>
@@ -10792,10 +10753,10 @@
         </is>
       </c>
       <c r="C216" s="31" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D216" s="31" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="E216" s="31" t="n">
         <v>207.6</v>
@@ -10995,10 +10956,10 @@
         </is>
       </c>
       <c r="C223" s="31" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D223" s="31" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="E223" s="31" t="n">
         <v>164.2</v>
@@ -11169,10 +11130,10 @@
         </is>
       </c>
       <c r="C229" s="31" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D229" s="31" t="n">
-        <v>21.8</v>
+        <v>0</v>
       </c>
       <c r="E229" s="31" t="n">
         <v>116.7</v>
@@ -11285,10 +11246,10 @@
         </is>
       </c>
       <c r="C233" s="31" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D233" s="31" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="E233" s="31" t="n">
         <v>91.2</v>
@@ -12300,10 +12261,10 @@
         </is>
       </c>
       <c r="C268" s="31" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D268" s="31" t="n">
-        <v>8.9</v>
+        <v>3.7</v>
       </c>
       <c r="E268" s="31" t="n">
         <v>23.2</v>
@@ -12851,10 +12812,10 @@
         </is>
       </c>
       <c r="C287" s="31" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D287" s="31" t="n">
-        <v>54.9</v>
+        <v>51</v>
       </c>
       <c r="E287" s="31" t="n">
         <v>19.5</v>
@@ -13083,10 +13044,10 @@
         </is>
       </c>
       <c r="C295" s="31" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D295" s="31" t="n">
-        <v>31.4</v>
+        <v>18.8</v>
       </c>
       <c r="E295" s="31" t="n">
         <v>11.7</v>
@@ -13112,10 +13073,10 @@
         </is>
       </c>
       <c r="C296" s="31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D296" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="E296" s="31" t="n">
         <v>9.800000000000001</v>
@@ -13257,10 +13218,10 @@
         </is>
       </c>
       <c r="C301" s="31" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="D301" s="31" t="n">
-        <v>181.2</v>
+        <v>151</v>
       </c>
       <c r="E301" s="31" t="n">
         <v>7.4</v>
@@ -13373,10 +13334,10 @@
         </is>
       </c>
       <c r="C305" s="31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D305" s="31" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E305" s="31" t="n">
         <v>9.9</v>
@@ -14852,10 +14813,10 @@
         </is>
       </c>
       <c r="C356" s="31" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D356" s="31" t="n">
-        <v>554.9</v>
+        <v>431.6</v>
       </c>
       <c r="E356" s="31" t="n">
         <v>0.6</v>
@@ -15009,7 +14970,7 @@
         <v>0</v>
       </c>
       <c r="G361" s="31" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H361" s="30" t="inlineStr"/>
       <c r="I361" s="30" t="inlineStr"/>
@@ -15635,7 +15596,7 @@
         </is>
       </c>
       <c r="C383" s="31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D383" s="31" t="n">
         <v>0</v>
@@ -16459,7 +16420,7 @@
         <v>0</v>
       </c>
       <c r="G411" s="31" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="H411" s="30" t="inlineStr"/>
       <c r="I411" s="30" t="inlineStr"/>
@@ -16563,7 +16524,7 @@
         </is>
       </c>
       <c r="C415" s="31" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D415" s="31" t="n">
         <v>0</v>
@@ -17868,7 +17829,7 @@
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>PARACETAMOL 500 MG COMPRIMIDO</t>
+          <t>LOSARTAN 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
@@ -17877,32 +17838,32 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>1621</v>
+        <v>605</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>7597.3</v>
+        <v>4050.6</v>
       </c>
       <c r="F18" s="23" t="n">
-        <v>128.8</v>
+        <v>89.2</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>11176.8</v>
+        <v>6048.1</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="J18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 2000 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1200 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr"/>
@@ -17910,7 +17871,7 @@
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>LOSARTAN 50 MG COMPRIMIDO</t>
+          <t>PREGABALINA 75 MG CAPSULA</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
@@ -17919,40 +17880,44 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>935</v>
+        <v>0</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>4050.6</v>
+        <v>2589.2</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>89.2</v>
+        <v>41.2</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>6048.1</v>
+        <v>3495.9</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>1200</v>
+        <v>1036</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="K19" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1200 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L19" s="22" t="inlineStr"/>
+          <t>TRASPASAR 900 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 136 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>PREGABALINA 75 MG CAPSULA</t>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
@@ -17961,44 +17926,40 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>2589.2</v>
+        <v>2237.7</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>41.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>3495.9</v>
+        <v>3039.2</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>1036</v>
+        <v>270</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>900</v>
+        <v>270</v>
       </c>
       <c r="J20" s="23" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 900 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L20" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 136 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 270 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+          <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B21" s="22" t="inlineStr">
@@ -18007,32 +17968,32 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>895</v>
+        <v>723</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E21" s="23" t="n">
-        <v>2237.7</v>
+        <v>2222.9</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>86.09999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>3039.2</v>
+        <v>2943.1</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="J21" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr"/>
@@ -18049,10 +18010,10 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>35.7</v>
@@ -18064,13 +18025,13 @@
         <v>38.4</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I22" s="23" t="n">
         <v>25</v>
       </c>
       <c r="J22" s="23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -18079,7 +18040,7 @@
       </c>
       <c r="L22" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 4 ud.</t>
+          <t>GESTIONAR EXTERNO 6 ud.</t>
         </is>
       </c>
     </row>
@@ -18287,7 +18248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -18480,7 +18441,7 @@
         <v>3191.2</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>756</v>
+        <v>941</v>
       </c>
       <c r="I5" s="21" t="n">
         <v>0</v>
@@ -18492,7 +18453,7 @@
       </c>
       <c r="K5" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 756 ud.</t>
+          <t>COMPRA EXTERNA 941 ud.</t>
         </is>
       </c>
     </row>
@@ -18523,14 +18484,14 @@
         <v>2598.9</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="I6" s="21" t="n">
         <v>1400</v>
       </c>
       <c r="J6" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 500 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 700 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr"/>
@@ -18753,7 +18714,7 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>TOLTERODINA CM 2 MG</t>
+          <t>ESCITALOPRAM 10 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -18768,23 +18729,23 @@
         <v>0</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>583.1</v>
+        <v>769.7</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>8.1</v>
+        <v>12.2</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>312.2</v>
+        <v>483.8</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>2100</v>
+        <v>3000</v>
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 500 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr"/>
@@ -18792,7 +18753,7 @@
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
+          <t>TOLTERODINA CM 2 MG</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -18807,35 +18768,31 @@
         <v>0</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>376.2</v>
+        <v>583.1</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>8.1</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>208.8</v>
+        <v>312.2</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>390</v>
+        <v>120</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K13" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 390 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
+          <t>DOXAZOSINA 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
@@ -18850,35 +18807,31 @@
         <v>0</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>193.7</v>
+        <v>376.2</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>0.4</v>
+        <v>8.1</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>150.5</v>
+        <v>208.8</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>47</v>
+        <v>390</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K14" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 47 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 390 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
+          <t>INSULINA GLARGINA 300 UI/3 ML (100 UI/ML) INYECTABLE EN LAPIZ PRELLENADO</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -18893,16 +18846,16 @@
         <v>0</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>70.2</v>
+        <v>193.7</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>49.7</v>
+        <v>150.5</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="I15" s="21" t="n">
         <v>0</v>
@@ -18914,14 +18867,14 @@
       </c>
       <c r="K15" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 71 ud.</t>
+          <t>COMPRA EXTERNA 57 ud.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>TIAMINA 30 MG/ML INYECTABLE</t>
+          <t>LACTULOSA 65% (9,75 G/15 ML) SOLUCION ORAL</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -18936,31 +18889,35 @@
         <v>0</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>67</v>
+        <v>70.2</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>32.4</v>
+        <v>1.6</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>10.8</v>
+        <v>49.7</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="J16" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K16" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 71 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>TIAMINA 30 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -18975,35 +18932,31 @@
         <v>0</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>0.8</v>
+        <v>32.4</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>38.4</v>
+        <v>10.8</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K17" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 41 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
@@ -19018,31 +18971,35 @@
         <v>0</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>35.1</v>
+        <v>0.8</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>0</v>
+        <v>38.4</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K18" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 43 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
+          <t>PIRIDOXINA 100 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -19057,35 +19014,31 @@
         <v>0</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>13</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>8.1</v>
+        <v>35.1</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K19" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 13 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>CALCITRIOL 0,5 MCG CAPSULA</t>
+          <t>LOVASTATINA 20 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
@@ -19100,31 +19053,35 @@
         <v>0</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>16.2</v>
+        <v>8.1</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>12.2</v>
+        <v>24.3</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K20" s="20" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 13 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
+          <t>CALCITRIOL 0,5 MCG CAPSULA</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -19139,23 +19096,23 @@
         <v>0</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>10.7</v>
+        <v>16.2</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>17</v>
+        <v>12.2</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>1600</v>
+        <v>840</v>
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 39 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr"/>
@@ -19163,7 +19120,7 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>KETOROLACO AMP 30 MG/ML</t>
+          <t>METAMIZOL SODICO AMP 1000 MG/2 ML</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -19178,23 +19135,23 @@
         <v>0</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>22.5</v>
+        <v>38.5</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>6.5</v>
+        <v>10.7</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>13.6</v>
+        <v>17</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 39 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr"/>
@@ -19202,7 +19159,7 @@
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>KETOROLACO AMP 30 MG/ML</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
@@ -19217,35 +19174,31 @@
         <v>0</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>24.6</v>
+        <v>22.5</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>0.1</v>
+        <v>6.5</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>18.8</v>
+        <v>13.6</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>50</v>
+        <v>2200</v>
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K23" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 50 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 23 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
@@ -19260,31 +19213,35 @@
         <v>0</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>22.4</v>
+        <v>24.6</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>4.9</v>
+        <v>0.1</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>9.699999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>5300</v>
+        <v>50</v>
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K24" s="20" t="inlineStr"/>
+          <t>TRASPASAR 50 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 50 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>CLOTRIMAZOL 1% (10 MG/G) CREMA</t>
+          <t>KETOPROFENO ENDOVENOSO 100 MG/2 ML (50 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -19299,23 +19256,23 @@
         <v>0</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>17</v>
+        <v>22.4</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>0.1</v>
+        <v>4.9</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>12.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>90</v>
+        <v>5300</v>
       </c>
       <c r="J25" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 9 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr"/>
@@ -19323,7 +19280,7 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
+          <t>CLOTRIMAZOL 1% (10 MG/G) CREMA</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
@@ -19338,23 +19295,23 @@
         <v>0</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>8</v>
+        <v>12.3</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>3000</v>
+        <v>90</v>
       </c>
       <c r="J26" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 10 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr"/>
@@ -19362,7 +19319,7 @@
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+          <t>ONDANSETRON 4 MG/2 ML (2 MG/ML) INYECTABLE</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -19377,23 +19334,23 @@
         <v>0</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>0.4</v>
+        <v>18.1</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>46</v>
+        <v>3000</v>
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 19 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr"/>
@@ -19401,85 +19358,85 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
+          <t>MUPIROCINA 2% (20 MG/G) UNGUENTO</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>1-CRITICO</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K28" s="20" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
           <t>SODIO BICARBONATO 8,4 % AM 10 ML</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>1-CRITICO</t>
         </is>
       </c>
-      <c r="C28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="21" t="n">
+      <c r="C29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="21" t="n">
         <v>1.7</v>
       </c>
-      <c r="F28" s="21" t="n">
+      <c r="F29" s="21" t="n">
         <v>0.3</v>
       </c>
-      <c r="G28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="21" t="n">
+      <c r="G29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="21" t="n">
+      <c r="I29" s="21" t="n">
         <v>450</v>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>TRASPASAR 2 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="K28" s="20" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>PARACETAMOL 500 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="inlineStr">
-        <is>
-          <t>2-URGENTE</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D29" s="23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E29" s="23" t="n">
-        <v>17383.4</v>
-      </c>
-      <c r="F29" s="23" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="G29" s="23" t="n">
-        <v>11176.8</v>
-      </c>
-      <c r="H29" s="23" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I29" s="23" t="n">
-        <v>160000</v>
-      </c>
-      <c r="J29" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 9000 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K29" s="22" t="inlineStr"/>
+      <c r="K29" s="20" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
+          <t>PARACETAMOL 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
@@ -19488,29 +19445,29 @@
         </is>
       </c>
       <c r="C30" s="23" t="n">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E30" s="23" t="n">
-        <v>6049</v>
+        <v>17383.4</v>
       </c>
       <c r="F30" s="23" t="n">
-        <v>283.8</v>
+        <v>128.8</v>
       </c>
       <c r="G30" s="23" t="n">
-        <v>4032</v>
+        <v>11176.8</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>1681</v>
+        <v>9000</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>67000</v>
+        <v>160000</v>
       </c>
       <c r="J30" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1681 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 9000 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr"/>
@@ -19518,85 +19475,85 @@
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
+          <t>ACIDO ACETILSALICILICO CM 100 MG</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="n">
+        <v>1700</v>
+      </c>
+      <c r="D31" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>6049</v>
+      </c>
+      <c r="F31" s="23" t="n">
+        <v>283.8</v>
+      </c>
+      <c r="G31" s="23" t="n">
+        <v>4032</v>
+      </c>
+      <c r="H31" s="23" t="n">
+        <v>1966</v>
+      </c>
+      <c r="I31" s="23" t="n">
+        <v>67000</v>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1966 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
           <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C32" s="23" t="n">
         <v>1200</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D32" s="23" t="n">
         <v>2.6</v>
       </c>
-      <c r="E31" s="23" t="n">
+      <c r="E32" s="23" t="n">
         <v>3314.7</v>
       </c>
-      <c r="F31" s="23" t="n">
+      <c r="F32" s="23" t="n">
         <v>4.1</v>
       </c>
-      <c r="G31" s="23" t="n">
+      <c r="G32" s="23" t="n">
         <v>2277.6</v>
       </c>
-      <c r="H31" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="I31" s="23" t="n">
+      <c r="H32" s="23" t="n">
+        <v>460</v>
+      </c>
+      <c r="I32" s="23" t="n">
         <v>36580</v>
       </c>
-      <c r="J31" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 400 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K31" s="22" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>LOSARTAN 50 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B32" s="28" t="inlineStr">
-        <is>
-          <t>3-ALTO</t>
-        </is>
-      </c>
-      <c r="C32" s="29" t="n">
-        <v>5700</v>
-      </c>
-      <c r="D32" s="29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E32" s="29" t="n">
-        <v>9495.6</v>
-      </c>
-      <c r="F32" s="29" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="G32" s="29" t="n">
-        <v>6048.1</v>
-      </c>
-      <c r="H32" s="29" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J32" s="28" t="inlineStr">
-        <is>
-          <t>TRASPASAR 2400 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K32" s="28" t="inlineStr"/>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 460 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
+          <t>LOSARTAN 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B33" s="28" t="inlineStr">
@@ -19605,29 +19562,29 @@
         </is>
       </c>
       <c r="C33" s="29" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="D33" s="29" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="E33" s="29" t="n">
-        <v>7400.4</v>
+        <v>9495.6</v>
       </c>
       <c r="F33" s="29" t="n">
-        <v>64.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="G33" s="29" t="n">
-        <v>4487.6</v>
+        <v>6048.1</v>
       </c>
       <c r="H33" s="29" t="n">
-        <v>967</v>
+        <v>2400</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>26936</v>
+        <v>30000</v>
       </c>
       <c r="J33" s="28" t="inlineStr">
         <is>
-          <t>TRASPASAR 967 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2400 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K33" s="28" t="inlineStr"/>
@@ -19635,143 +19592,221 @@
     <row r="34">
       <c r="A34" s="28" t="inlineStr">
         <is>
+          <t>BISOPROLOL 2,5 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>3-ALTO</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D34" s="29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <v>7400.4</v>
+      </c>
+      <c r="F34" s="29" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <v>4487.6</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <v>1339</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <v>26936</v>
+      </c>
+      <c r="J34" s="28" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1339 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K34" s="28" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
           <t>MELATONINA 3 MG COMPRIMIDOS</t>
         </is>
       </c>
-      <c r="B34" s="28" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>3-ALTO</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
-        <v>2670</v>
-      </c>
-      <c r="D34" s="29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E34" s="29" t="n">
+      <c r="C35" s="29" t="n">
+        <v>2430</v>
+      </c>
+      <c r="D35" s="29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E35" s="29" t="n">
         <v>4895.4</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F35" s="29" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="G34" s="29" t="n">
+      <c r="G35" s="29" t="n">
         <v>3039.2</v>
       </c>
-      <c r="H34" s="29" t="n">
-        <v>1320</v>
-      </c>
-      <c r="I34" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="28" t="inlineStr">
+      <c r="H35" s="29" t="n">
+        <v>1560</v>
+      </c>
+      <c r="I35" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="28" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA FARMACOS</t>
         </is>
       </c>
-      <c r="K34" s="28" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 1320 ud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="K35" s="28" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 1560 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>ATORVASTATINA 80 MG COMPRIMIDO</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>4-MODERADO</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n">
-        <v>3300</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E35" s="6" t="n">
+      <c r="C36" s="6" t="n">
+        <v>3120</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E36" s="6" t="n">
         <v>4990.7</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F36" s="6" t="n">
         <v>44.6</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G36" s="6" t="n">
         <v>2943.1</v>
       </c>
-      <c r="H35" s="6" t="n">
-        <v>810</v>
-      </c>
-      <c r="I35" s="6" t="n">
+      <c r="H36" s="6" t="n">
+        <v>990</v>
+      </c>
+      <c r="I36" s="6" t="n">
         <v>10290</v>
       </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 810 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 990 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>ATORVASTATINA 40 MG COMPRIMIDO</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>4-MODERADO</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>3320</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>5014.3</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>2931.6</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>11700</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 120 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="C49" s="23" t="n">
-        <v>1858</v>
+        <v>1756</v>
       </c>
       <c r="D49" s="23" t="n">
         <v>0.5</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="C50" s="23" t="n">
-        <v>1916</v>
+        <v>1899</v>
       </c>
       <c r="D50" s="23" t="n">
         <v>1.8</v>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="C51" s="23" t="n">
-        <v>1500</v>
+        <v>1470</v>
       </c>
       <c r="D51" s="23" t="n">
         <v>1.4</v>
@@ -3844,13 +3844,13 @@
         <v>5944.8</v>
       </c>
       <c r="F51" s="23" t="n">
-        <v>1320</v>
+        <v>1350</v>
       </c>
       <c r="G51" s="23" t="n">
         <v>540</v>
       </c>
       <c r="H51" s="23" t="n">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="I51" s="22" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J51" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 780 ud.</t>
+          <t>GESTIONAR EXTERNO 810 ud.</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="C52" s="23" t="n">
-        <v>1707</v>
+        <v>1692</v>
       </c>
       <c r="D52" s="23" t="n">
         <v>1.8</v>
@@ -3884,17 +3884,17 @@
         <v>4915.1</v>
       </c>
       <c r="F52" s="23" t="n">
-        <v>622</v>
+        <v>637</v>
       </c>
       <c r="G52" s="23" t="n">
-        <v>622</v>
+        <v>637</v>
       </c>
       <c r="H52" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 622 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 637 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J52" s="22" t="inlineStr"/>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="C53" s="23" t="n">
-        <v>1523</v>
+        <v>1478</v>
       </c>
       <c r="D53" s="23" t="n">
         <v>1.7</v>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="C59" s="23" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E59" s="23" t="n">
         <v>1054.9</v>
@@ -4171,26 +4171,26 @@
         </is>
       </c>
       <c r="C60" s="23" t="n">
-        <v>281</v>
+        <v>221</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="E60" s="23" t="n">
         <v>1279.6</v>
       </c>
       <c r="F60" s="23" t="n">
-        <v>387</v>
+        <v>447</v>
       </c>
       <c r="G60" s="23" t="n">
-        <v>387</v>
+        <v>447</v>
       </c>
       <c r="H60" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 387 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 447 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J60" s="22" t="inlineStr"/>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="C62" s="23" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D62" s="23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="E62" s="23" t="n">
         <v>791.4</v>
@@ -6170,7 +6170,7 @@
         <v>10770.9</v>
       </c>
       <c r="F3" s="21" t="n">
-        <v>8760</v>
+        <v>8790</v>
       </c>
       <c r="G3" s="21" t="n">
         <v>8040</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="I3" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 720 ud.</t>
+          <t>COMPRA EXTERNA 750 ud.</t>
         </is>
       </c>
     </row>
@@ -6622,18 +6622,14 @@
         <v>707</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA EXTERNA 707 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 707 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
@@ -6759,14 +6755,14 @@
         <v>732.9</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="G20" s="21" t="n">
         <v>1500</v>
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 270 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 330 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr"/>
@@ -6828,7 +6824,7 @@
         <v>296</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
@@ -8513,7 +8509,7 @@
         <v>5</v>
       </c>
       <c r="G71" s="21" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H71" s="20" t="inlineStr">
         <is>
@@ -9474,14 +9470,14 @@
         <v>6695</v>
       </c>
       <c r="F99" s="23" t="n">
-        <v>1858</v>
+        <v>1918</v>
       </c>
       <c r="G99" s="23" t="n">
         <v>19920</v>
       </c>
       <c r="H99" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1858 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1918 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I99" s="22" t="inlineStr"/>
@@ -9935,7 +9931,7 @@
         </is>
       </c>
       <c r="C113" s="29" t="n">
-        <v>3298</v>
+        <v>3283</v>
       </c>
       <c r="D113" s="29" t="n">
         <v>3.5</v>
@@ -9944,14 +9940,14 @@
         <v>9262.5</v>
       </c>
       <c r="F113" s="29" t="n">
-        <v>3636</v>
+        <v>3651</v>
       </c>
       <c r="G113" s="29" t="n">
         <v>21336</v>
       </c>
       <c r="H113" s="28" t="inlineStr">
         <is>
-          <t>TRASPASAR 3636 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3651 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I113" s="28" t="inlineStr"/>
@@ -10529,23 +10525,23 @@
         </is>
       </c>
       <c r="C131" s="6" t="n">
-        <v>1113</v>
+        <v>1053</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="E131" s="6" t="n">
         <v>2313.9</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>533</v>
+        <v>593</v>
       </c>
       <c r="G131" s="6" t="n">
         <v>41600</v>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 533 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 593 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr"/>
@@ -20272,7 +20268,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>1858</v>
+        <v>1756</v>
       </c>
       <c r="D15" s="23" t="n">
         <v>0.5</v>
@@ -20314,7 +20310,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>1916</v>
+        <v>1899</v>
       </c>
       <c r="D16" s="23" t="n">
         <v>1.8</v>
@@ -20356,7 +20352,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>1500</v>
+        <v>1470</v>
       </c>
       <c r="D17" s="23" t="n">
         <v>1.4</v>
@@ -20371,13 +20367,13 @@
         <v>5233.3</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>1320</v>
+        <v>1350</v>
       </c>
       <c r="I17" s="23" t="n">
         <v>540</v>
       </c>
       <c r="J17" s="23" t="n">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
@@ -20386,7 +20382,7 @@
       </c>
       <c r="L17" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 780 ud.</t>
+          <t>GESTIONAR EXTERNO 810 ud.</t>
         </is>
       </c>
     </row>
@@ -20402,7 +20398,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>1707</v>
+        <v>1692</v>
       </c>
       <c r="D18" s="23" t="n">
         <v>1.8</v>
@@ -20417,17 +20413,17 @@
         <v>4605.8</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="J18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 654 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 669 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr"/>
@@ -20444,7 +20440,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>1523</v>
+        <v>1478</v>
       </c>
       <c r="D19" s="23" t="n">
         <v>1.7</v>
@@ -20574,10 +20570,10 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>1054.9</v>
@@ -21175,7 +21171,7 @@
         <v>5233.3</v>
       </c>
       <c r="H3" s="21" t="n">
-        <v>8760</v>
+        <v>8790</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>8040</v>
@@ -21187,7 +21183,7 @@
       </c>
       <c r="K3" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 720 ud.</t>
+          <t>COMPRA EXTERNA 750 ud.</t>
         </is>
       </c>
     </row>
@@ -22366,7 +22362,7 @@
         </is>
       </c>
       <c r="C33" s="29" t="n">
-        <v>3266</v>
+        <v>3251</v>
       </c>
       <c r="D33" s="29" t="n">
         <v>3.5</v>
@@ -22381,14 +22377,14 @@
         <v>4605.8</v>
       </c>
       <c r="H33" s="29" t="n">
-        <v>3636</v>
+        <v>3651</v>
       </c>
       <c r="I33" s="29" t="n">
         <v>21336</v>
       </c>
       <c r="J33" s="28" t="inlineStr">
         <is>
-          <t>TRASPASAR 3636 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3651 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K33" s="28" t="inlineStr"/>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -4329,26 +4329,26 @@
         </is>
       </c>
       <c r="C59" s="23" t="n">
-        <v>1620</v>
+        <v>1590</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E59" s="23" t="n">
         <v>5053.1</v>
       </c>
       <c r="F59" s="23" t="n">
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="H59" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 660 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 690 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J59" s="22" t="inlineStr"/>
@@ -4525,26 +4525,26 @@
         </is>
       </c>
       <c r="C64" s="23" t="n">
-        <v>1078</v>
+        <v>1048</v>
       </c>
       <c r="D64" s="23" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E64" s="23" t="n">
         <v>2938.4</v>
       </c>
       <c r="F64" s="23" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="G64" s="23" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="H64" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 300 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 330 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J64" s="22" t="inlineStr"/>
@@ -6037,26 +6037,26 @@
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="E104" s="6" t="n">
         <v>1135.6</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G104" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H104" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 30 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr"/>
@@ -6149,26 +6149,26 @@
         </is>
       </c>
       <c r="C107" s="6" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E107" s="6" t="n">
         <v>135</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H107" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 29 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 31 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr"/>
@@ -8148,14 +8148,14 @@
         <v>814.9</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="G35" s="21" t="n">
         <v>2760</v>
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 480 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 540 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr"/>
@@ -11379,14 +11379,14 @@
         <v>3625.5</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>2340</v>
+        <v>2400</v>
       </c>
       <c r="G130" s="23" t="n">
         <v>41340</v>
       </c>
       <c r="H130" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 2340 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 2400 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I130" s="22" t="inlineStr"/>
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="C135" s="29" t="n">
-        <v>4140</v>
+        <v>4110</v>
       </c>
       <c r="D135" s="29" t="n">
         <v>4</v>
@@ -11548,7 +11548,7 @@
         <v>9065.1</v>
       </c>
       <c r="F135" s="29" t="n">
-        <v>2670</v>
+        <v>2700</v>
       </c>
       <c r="G135" s="29" t="n">
         <v>0</v>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="I135" s="28" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2670 ud.</t>
+          <t>COMPRA EXTERNA 2700 ud.</t>
         </is>
       </c>
     </row>
@@ -11642,16 +11642,16 @@
         </is>
       </c>
       <c r="C138" s="29" t="n">
-        <v>810</v>
+        <v>780</v>
       </c>
       <c r="D138" s="29" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E138" s="29" t="n">
         <v>1884</v>
       </c>
       <c r="F138" s="29" t="n">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="G138" s="29" t="n">
         <v>476</v>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="I138" s="28" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 38 ud.</t>
+          <t>COMPRA EXTERNA 68 ud.</t>
         </is>
       </c>
     </row>
@@ -12059,10 +12059,10 @@
         </is>
       </c>
       <c r="C151" s="31" t="n">
-        <v>6450</v>
+        <v>6420</v>
       </c>
       <c r="D151" s="31" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="E151" s="31" t="n">
         <v>5335</v>
@@ -14611,7 +14611,7 @@
         </is>
       </c>
       <c r="C239" s="31" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D239" s="31" t="n">
         <v>4.6</v>
@@ -21323,10 +21323,10 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>1620</v>
+        <v>1590</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>5053.1</v>
@@ -21338,17 +21338,17 @@
         <v>5140.4</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="J17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 660 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 690 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr"/>
@@ -21503,10 +21503,10 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>1078</v>
+        <v>1048</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E21" s="23" t="n">
         <v>2938.4</v>
@@ -21518,17 +21518,17 @@
         <v>3043.7</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="J21" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 300 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 330 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr"/>
@@ -22195,10 +22195,10 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>1135.6</v>
@@ -22210,17 +22210,17 @@
         <v>1076.4</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="J37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 33 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 63 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr"/>
@@ -22237,10 +22237,10 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>135</v>
@@ -22252,17 +22252,17 @@
         <v>139.3</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 31 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 33 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr"/>
@@ -23972,7 +23972,7 @@
         </is>
       </c>
       <c r="C38" s="29" t="n">
-        <v>4140</v>
+        <v>4110</v>
       </c>
       <c r="D38" s="29" t="n">
         <v>4</v>
@@ -23987,7 +23987,7 @@
         <v>5140.4</v>
       </c>
       <c r="H38" s="29" t="n">
-        <v>2670</v>
+        <v>2700</v>
       </c>
       <c r="I38" s="29" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="K38" s="28" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2670 ud.</t>
+          <t>COMPRA EXTERNA 2700 ud.</t>
         </is>
       </c>
     </row>
@@ -24015,10 +24015,10 @@
         </is>
       </c>
       <c r="C39" s="29" t="n">
-        <v>807</v>
+        <v>777</v>
       </c>
       <c r="D39" s="29" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E39" s="29" t="n">
         <v>1884</v>
@@ -24030,7 +24030,7 @@
         <v>1076.4</v>
       </c>
       <c r="H39" s="29" t="n">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="I39" s="29" t="n">
         <v>476</v>
@@ -24042,7 +24042,7 @@
       </c>
       <c r="K39" s="28" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 38 ud.</t>
+          <t>COMPRA EXTERNA 68 ud.</t>
         </is>
       </c>
     </row>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -4142,26 +4142,26 @@
         </is>
       </c>
       <c r="C55" s="23" t="n">
-        <v>599</v>
+        <v>449</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E55" s="23" t="n">
         <v>5004.1</v>
       </c>
       <c r="F55" s="23" t="n">
-        <v>1590</v>
+        <v>1740</v>
       </c>
       <c r="G55" s="23" t="n">
-        <v>1590</v>
+        <v>1740</v>
       </c>
       <c r="H55" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1590 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1740 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J55" s="22" t="inlineStr"/>
@@ -4178,26 +4178,26 @@
         </is>
       </c>
       <c r="C56" s="23" t="n">
-        <v>539</v>
+        <v>449</v>
       </c>
       <c r="D56" s="23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E56" s="23" t="n">
         <v>3391.7</v>
       </c>
       <c r="F56" s="23" t="n">
-        <v>1020</v>
+        <v>1080</v>
       </c>
       <c r="G56" s="23" t="n">
-        <v>1020</v>
+        <v>1080</v>
       </c>
       <c r="H56" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1020 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1080 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J56" s="22" t="inlineStr"/>
@@ -4214,26 +4214,26 @@
         </is>
       </c>
       <c r="C57" s="23" t="n">
-        <v>832</v>
+        <v>802</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E57" s="23" t="n">
         <v>2565.7</v>
       </c>
       <c r="F57" s="23" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="G57" s="23" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="H57" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 280 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 320 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J57" s="22" t="inlineStr"/>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="C60" s="23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="23" t="n">
         <v>898.1</v>
@@ -5670,14 +5670,14 @@
         <v>5111.8</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>1560</v>
+        <v>1620</v>
       </c>
       <c r="G8" s="21" t="n">
         <v>4620</v>
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1560 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1620 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr"/>
@@ -6049,14 +6049,14 @@
         <v>1460.1</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>201</v>
+        <v>261</v>
       </c>
       <c r="G19" s="21" t="n">
         <v>27600</v>
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 201 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 261 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr"/>
@@ -9131,14 +9131,14 @@
         <v>6501.3</v>
       </c>
       <c r="F109" s="23" t="n">
-        <v>1785</v>
+        <v>1995</v>
       </c>
       <c r="G109" s="23" t="n">
         <v>26100</v>
       </c>
       <c r="H109" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1785 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1995 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I109" s="22" t="inlineStr"/>
@@ -9164,7 +9164,7 @@
         <v>5666.1</v>
       </c>
       <c r="F110" s="23" t="n">
-        <v>2561</v>
+        <v>2741</v>
       </c>
       <c r="G110" s="23" t="n">
         <v>0</v>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="I110" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 2561 ud.</t>
+          <t>COMPRA EXTERNA 2741 ud.</t>
         </is>
       </c>
     </row>
@@ -9201,14 +9201,14 @@
         <v>8760.9</v>
       </c>
       <c r="F111" s="27" t="n">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="G111" s="27" t="n">
         <v>14504</v>
       </c>
       <c r="H111" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 101 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 191 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I111" s="26" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="C116" s="29" t="n">
-        <v>8910</v>
+        <v>8760</v>
       </c>
       <c r="D116" s="29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="E116" s="29" t="n">
         <v>9211.6</v>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="C121" s="29" t="n">
-        <v>7980</v>
+        <v>7920</v>
       </c>
       <c r="D121" s="29" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="E121" s="29" t="n">
         <v>5989.2</v>
@@ -9585,10 +9585,10 @@
         </is>
       </c>
       <c r="C124" s="29" t="n">
-        <v>6520</v>
+        <v>6480</v>
       </c>
       <c r="D124" s="29" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="E124" s="29" t="n">
         <v>4653.1</v>
@@ -19826,10 +19826,10 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>599</v>
+        <v>449</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E16" s="23" t="n">
         <v>5004.1</v>
@@ -19841,17 +19841,17 @@
         <v>5180.1</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>1590</v>
+        <v>1740</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>1590</v>
+        <v>1740</v>
       </c>
       <c r="J16" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1590 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1740 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr"/>
@@ -19868,10 +19868,10 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>539</v>
+        <v>449</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>3391.7</v>
@@ -19883,17 +19883,17 @@
         <v>3499.9</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>1020</v>
+        <v>1080</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>1020</v>
+        <v>1080</v>
       </c>
       <c r="J17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1020 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1080 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr"/>
@@ -19910,10 +19910,10 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>832</v>
+        <v>802</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E18" s="23" t="n">
         <v>2565.7</v>
@@ -19925,17 +19925,17 @@
         <v>2331.5</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="J18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 280 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 320 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr"/>
@@ -20687,14 +20687,14 @@
         <v>2727.6</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>1560</v>
+        <v>1620</v>
       </c>
       <c r="I7" s="21" t="n">
         <v>4620</v>
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 1560 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1620 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr"/>
@@ -21858,14 +21858,14 @@
         <v>3690.8</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>1785</v>
+        <v>1995</v>
       </c>
       <c r="I36" s="23" t="n">
         <v>26100</v>
       </c>
       <c r="J36" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1785 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 1995 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr"/>
@@ -21897,14 +21897,14 @@
         <v>4745.6</v>
       </c>
       <c r="H37" s="27" t="n">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>14504</v>
       </c>
       <c r="J37" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 101 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 191 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K37" s="26" t="inlineStr"/>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -1721,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3487,26 +3487,26 @@
         </is>
       </c>
       <c r="C45" s="23" t="n">
-        <v>644</v>
+        <v>459</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E45" s="23" t="n">
         <v>4912.3</v>
       </c>
       <c r="F45" s="23" t="n">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="G45" s="23" t="n">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="H45" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1500 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1750 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J45" s="22" t="inlineStr"/>
@@ -3523,26 +3523,26 @@
         </is>
       </c>
       <c r="C46" s="23" t="n">
-        <v>1140</v>
+        <v>870</v>
       </c>
       <c r="D46" s="23" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E46" s="23" t="n">
         <v>4927.5</v>
       </c>
       <c r="F46" s="23" t="n">
-        <v>1230</v>
+        <v>1500</v>
       </c>
       <c r="G46" s="23" t="n">
-        <v>1230</v>
+        <v>1500</v>
       </c>
       <c r="H46" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1230 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1500 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J46" s="22" t="inlineStr"/>
@@ -3550,7 +3550,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 40 MG COMPRIMIDO</t>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
@@ -3559,26 +3559,26 @@
         </is>
       </c>
       <c r="C47" s="23" t="n">
-        <v>209</v>
+        <v>560</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E47" s="23" t="n">
-        <v>3329</v>
+        <v>2888.9</v>
       </c>
       <c r="F47" s="23" t="n">
-        <v>1500</v>
+        <v>720</v>
       </c>
       <c r="G47" s="23" t="n">
-        <v>1500</v>
+        <v>720</v>
       </c>
       <c r="H47" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1500 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 720 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J47" s="22" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
@@ -3595,34 +3595,38 @@
         </is>
       </c>
       <c r="C48" s="23" t="n">
-        <v>750</v>
+        <v>1170</v>
       </c>
       <c r="D48" s="23" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="E48" s="23" t="n">
-        <v>2888.9</v>
+        <v>3093.6</v>
       </c>
       <c r="F48" s="23" t="n">
-        <v>540</v>
+        <v>190</v>
       </c>
       <c r="G48" s="23" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="H48" s="23" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="I48" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 540 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J48" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J48" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 190 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="22" t="inlineStr">
         <is>
-          <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
+          <t>VILDAGLIPTINA 50 MG CM</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
@@ -3631,26 +3635,26 @@
         </is>
       </c>
       <c r="C49" s="23" t="n">
-        <v>892</v>
+        <v>930</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E49" s="23" t="n">
-        <v>2532</v>
+        <v>2810.6</v>
       </c>
       <c r="F49" s="23" t="n">
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="G49" s="23" t="n">
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="H49" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 320 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 420 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J49" s="22" t="inlineStr"/>
@@ -3658,7 +3662,7 @@
     <row r="50">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
+          <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
@@ -3667,26 +3671,26 @@
         </is>
       </c>
       <c r="C50" s="23" t="n">
-        <v>292</v>
+        <v>757</v>
       </c>
       <c r="D50" s="23" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="E50" s="23" t="n">
-        <v>2040</v>
+        <v>2532</v>
       </c>
       <c r="F50" s="23" t="n">
-        <v>630</v>
+        <v>440</v>
       </c>
       <c r="G50" s="23" t="n">
-        <v>630</v>
+        <v>440</v>
       </c>
       <c r="H50" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 630 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 440 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J50" s="22" t="inlineStr"/>
@@ -3694,7 +3698,7 @@
     <row r="51">
       <c r="A51" s="22" t="inlineStr">
         <is>
-          <t>HIDROXICLOROQUINA CM 200 MG</t>
+          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B51" s="22" t="inlineStr">
@@ -3703,26 +3707,26 @@
         </is>
       </c>
       <c r="C51" s="23" t="n">
-        <v>729</v>
+        <v>292</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="E51" s="23" t="n">
-        <v>1817.9</v>
+        <v>2040</v>
       </c>
       <c r="F51" s="23" t="n">
-        <v>180</v>
+        <v>630</v>
       </c>
       <c r="G51" s="23" t="n">
-        <v>180</v>
+        <v>630</v>
       </c>
       <c r="H51" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 630 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J51" s="22" t="inlineStr"/>
@@ -3730,7 +3734,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>DULOXETINA 60 MG CAPSULA</t>
+          <t>HIDROXICLOROQUINA CM 200 MG</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
@@ -3739,26 +3743,26 @@
         </is>
       </c>
       <c r="C52" s="23" t="n">
-        <v>282</v>
+        <v>699</v>
       </c>
       <c r="D52" s="23" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="E52" s="23" t="n">
-        <v>892.5</v>
+        <v>1817.9</v>
       </c>
       <c r="F52" s="23" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G52" s="23" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="H52" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 150 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J52" s="22" t="inlineStr"/>
@@ -3766,7 +3770,7 @@
     <row r="53">
       <c r="A53" s="22" t="inlineStr">
         <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
+          <t>DULOXETINA 60 MG CAPSULA</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
@@ -3775,38 +3779,34 @@
         </is>
       </c>
       <c r="C53" s="23" t="n">
-        <v>7</v>
+        <v>252</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="E53" s="23" t="n">
-        <v>85.3</v>
+        <v>892.5</v>
       </c>
       <c r="F53" s="23" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G53" s="23" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H53" s="23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I53" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J53" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 60 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J53" s="22" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="22" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
@@ -3815,34 +3815,38 @@
         </is>
       </c>
       <c r="C54" s="23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E54" s="23" t="n">
-        <v>48.3</v>
+        <v>85.3</v>
       </c>
       <c r="F54" s="23" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="G54" s="23" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H54" s="23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I54" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 44 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J54" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J54" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 60 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="22" t="inlineStr">
         <is>
-          <t>AEROCAMARA ADULTO BIVAL 451/ 800 ML</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
@@ -3851,26 +3855,26 @@
         </is>
       </c>
       <c r="C55" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="23" t="n">
         <v>0.2</v>
       </c>
       <c r="E55" s="23" t="n">
-        <v>28.9</v>
+        <v>48.3</v>
       </c>
       <c r="F55" s="23" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G55" s="23" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H55" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 28 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 46 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J55" s="22" t="inlineStr"/>
@@ -3878,7 +3882,7 @@
     <row r="56">
       <c r="A56" s="22" t="inlineStr">
         <is>
-          <t>VIGABATRINA 500 MG COMPRIMIDO</t>
+          <t>AEROCAMARA ADULTO BIVAL 451/ 800 ML</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
@@ -3893,20 +3897,20 @@
         <v>0</v>
       </c>
       <c r="E56" s="23" t="n">
-        <v>20.8</v>
+        <v>28.9</v>
       </c>
       <c r="F56" s="23" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="G56" s="23" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="H56" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 29 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J56" s="22" t="inlineStr"/>
@@ -3914,7 +3918,7 @@
     <row r="57">
       <c r="A57" s="22" t="inlineStr">
         <is>
-          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
+          <t>VIGABATRINA 500 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B57" s="22" t="inlineStr">
@@ -3923,38 +3927,34 @@
         </is>
       </c>
       <c r="C57" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E57" s="23" t="n">
-        <v>24.8</v>
+        <v>20.8</v>
       </c>
       <c r="F57" s="23" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="G57" s="23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H57" s="23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I57" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J57" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 24 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J57" s="22" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>LACTULOSA FC 65% X 200 ML</t>
+          <t>DEXAMETASONA 4 MG/ML INYECTABLE</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
@@ -3963,34 +3963,38 @@
         </is>
       </c>
       <c r="C58" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="E58" s="23" t="n">
-        <v>14.5</v>
+        <v>24.8</v>
       </c>
       <c r="F58" s="23" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G58" s="23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H58" s="23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I58" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J58" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J58" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 24 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="22" t="inlineStr">
         <is>
-          <t>PARACETAMOL 100 MG/ML GOTAS ORALES</t>
+          <t>LACTULOSA FC 65% X 200 ML</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
@@ -3999,26 +4003,26 @@
         </is>
       </c>
       <c r="C59" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E59" s="23" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="F59" s="23" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H59" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 25 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 12 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J59" s="22" t="inlineStr"/>
@@ -4026,7 +4030,7 @@
     <row r="60">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
+          <t>PARACETAMOL 100 MG/ML GOTAS ORALES</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
@@ -4035,38 +4039,34 @@
         </is>
       </c>
       <c r="C60" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="E60" s="23" t="n">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="F60" s="23" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G60" s="23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H60" s="23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I60" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J60" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 6 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 25 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J60" s="22" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="22" t="inlineStr">
         <is>
-          <t>UMECLIDINIO/VILANTEROL 55/22 INH</t>
+          <t>HALOPERIDOL DECANOATO 50 MG. A</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
@@ -4075,142 +4075,146 @@
         </is>
       </c>
       <c r="C61" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="E61" s="23" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="F61" s="23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G61" s="23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H61" s="23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I61" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J61" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J61" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 6 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="22" t="inlineStr">
         <is>
+          <t>VASELINA SOLIDA UNGUENTO</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C62" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" s="23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E62" s="23" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F62" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="G62" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="H62" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 9 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J62" s="22" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>UMECLIDINIO/VILANTEROL 55/22 INH</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E63" s="23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F63" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="G63" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H63" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J63" s="22" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
           <t>AZITROMICINA 400 MG/5 ML POLVO PARA PREPARADO ORAL</t>
         </is>
       </c>
-      <c r="B62" s="22" t="inlineStr">
+      <c r="B64" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C62" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="23" t="n">
+      <c r="C64" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="F62" s="23" t="n">
+      <c r="F64" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="23" t="n">
+      <c r="G64" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H62" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="22" t="inlineStr">
+      <c r="H64" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="22" t="inlineStr">
         <is>
           <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="J62" s="22" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>VILDAGLIPTINA 50 MG CM</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="n">
-        <v>1260</v>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E63" s="6" t="n">
-        <v>2810.6</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="G63" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 120 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>LOPERAMIDA 2 MG COMPRIMIDO</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="n">
-        <v>196</v>
-      </c>
-      <c r="D64" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E64" s="6" t="n">
-        <v>472.5</v>
-      </c>
-      <c r="F64" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G64" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="H64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 12 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="inlineStr"/>
+      <c r="J64" s="22" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>PRIMIDONA 250 MG COMPRIMIDO</t>
+          <t>LOSARTAN 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -4219,38 +4223,34 @@
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>30</v>
+        <v>2754</v>
       </c>
       <c r="D65" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>75.8</v>
+        <v>5878.9</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>50</v>
+        <v>1200</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 50 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 1200 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>SALES PARA REHIDRATACION ORAL 90 MEQ</t>
+          <t>EZETIMIBE 10 MG CM UNIDAD</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -4259,26 +4259,26 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>58</v>
+        <v>496</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>59.7</v>
+        <v>1070.7</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 63 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr"/>
@@ -4286,7 +4286,7 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
+          <t>LOPERAMIDA 2 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -4295,26 +4295,26 @@
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>40.6</v>
+        <v>472.5</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H67" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 42 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr"/>
@@ -4322,7 +4322,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>LISDEXANFETAMINA 50 MG CM</t>
+          <t>PRIMIDONA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -4331,22 +4331,22 @@
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D68" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>46.9</v>
+        <v>75.8</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
@@ -4355,14 +4355,14 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 32 ud.</t>
+          <t>GESTIONAR EXTERNO 50 ud.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>IBUPROFENO 200 MG/5 ML SUSP 100 ML</t>
+          <t>SALES PARA REHIDRATACION ORAL 90 MEQ</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -4371,26 +4371,26 @@
         </is>
       </c>
       <c r="C69" s="6" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>28.5</v>
+        <v>59.7</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H69" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 25 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr"/>
@@ -4398,7 +4398,7 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>TRAMADOL FRASCO GOTAS 100 MG/ML /10 ML</t>
+          <t>TERBINAFINA 250 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -4407,26 +4407,26 @@
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>29.5</v>
+        <v>40.6</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 12 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 60 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr"/>
@@ -4434,7 +4434,7 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>SALMETEROL /FLUTICASONA 250 MG/25 MG INH UD</t>
+          <t>LISDEXANFETAMINA 50 MG CM</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -4443,34 +4443,38 @@
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>17</v>
+        <v>46.9</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 32 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
+          <t>IBUPROFENO 200 MG/5 ML SUSP 100 ML</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -4479,38 +4483,34 @@
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>21.9</v>
+        <v>28.5</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 20 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 80 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 25 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>VASELINA SOLIDA UNGUENTO</t>
+          <t>TRAMADOL FRASCO GOTAS 100 MG/ML /10 ML</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -4519,26 +4519,26 @@
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>12.9</v>
+        <v>29.5</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H73" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 3 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 13 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr"/>
@@ -4546,7 +4546,7 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
+          <t>SALMETEROL /FLUTICASONA 250 MG/25 MG INH UD</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -4555,26 +4555,26 @@
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>9.699999999999999</v>
+        <v>17</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr"/>
@@ -4582,7 +4582,7 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>DICLOFENACO SODICO 12,5 MG SUPOSITORIO</t>
+          <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -4591,34 +4591,38 @@
         </is>
       </c>
       <c r="C75" s="6" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>5.3</v>
+        <v>21.9</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr"/>
+          <t>TRASPASAR 20 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 80 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>FENOTEROL/IPRATROPIO 05/025 MG/ML SOL. P/NEBULIZAR FC 20 ML</t>
+          <t>PALIPERIDONA 100 MG JER.PC UNIDAD</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -4627,132 +4631,204 @@
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>4.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 2 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 2 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
+          <t>DICLOFENACO SODICO 12,5 MG SUPOSITORIO</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>FENOTEROL/IPRATROPIO 05/025 MG/ML SOL. P/NEBULIZAR FC 20 ML</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 2 ud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
           <t>CEFTRIAXONA 1G FA</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>3-MODERADO</t>
         </is>
       </c>
-      <c r="C77" s="6" t="n">
+      <c r="C79" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D79" s="6" t="n">
         <v>2.3</v>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E79" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F77" s="6" t="n">
+      <c r="F79" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="G77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="6" t="n">
+      <c r="G79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>SIN STOCK EN BODEGA AA</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 50 ud.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="11" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="12" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="13" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="14" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="15" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="15" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="16" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="16" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="17" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -4858,7 +4934,7 @@
         <v>5762.8</v>
       </c>
       <c r="F3" s="21" t="n">
-        <v>4263</v>
+        <v>4593</v>
       </c>
       <c r="G3" s="21" t="n">
         <v>0</v>
@@ -4870,7 +4946,7 @@
       </c>
       <c r="I3" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 4263 ud.</t>
+          <t>COMPRA EXTERNA 4593 ud.</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4971,7 @@
         <v>5556.5</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>3605</v>
+        <v>3739</v>
       </c>
       <c r="G4" s="21" t="n">
         <v>0</v>
@@ -4907,7 +4983,7 @@
       </c>
       <c r="I4" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3605 ud.</t>
+          <t>COMPRA EXTERNA 3739 ud.</t>
         </is>
       </c>
     </row>
@@ -4932,17 +5008,21 @@
         <v>3847.5</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>2963</v>
+        <v>3043</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>8100</v>
+        <v>2100</v>
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 2963 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr"/>
+          <t>TRASPASAR 2100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 943 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -4965,7 +5045,7 @@
         <v>3438.6</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>259</v>
+        <v>319</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>0</v>
@@ -4977,7 +5057,7 @@
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 259 ud.</t>
+          <t>COMPRA EXTERNA 319 ud.</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5152,7 @@
         <v>1292.2</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G9" s="21" t="n">
         <v>0</v>
@@ -5084,7 +5164,7 @@
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 120 ud.</t>
+          <t>COMPRA EXTERNA 240 ud.</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5189,7 @@
         <v>1087.4</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G10" s="21" t="n">
         <v>0</v>
@@ -5121,7 +5201,7 @@
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 400 ud.</t>
+          <t>COMPRA EXTERNA 500 ud.</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5370,7 @@
         <v>378</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="G15" s="21" t="n">
         <v>0</v>
@@ -5302,7 +5382,7 @@
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 139 ud.</t>
+          <t>COMPRA EXTERNA 152 ud.</t>
         </is>
       </c>
     </row>
@@ -5397,14 +5477,14 @@
         <v>156.8</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G18" s="21" t="n">
         <v>300</v>
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 42 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 46 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr"/>
@@ -7374,14 +7454,14 @@
         <v>6469.5</v>
       </c>
       <c r="F75" s="23" t="n">
-        <v>3495</v>
+        <v>3749</v>
       </c>
       <c r="G75" s="23" t="n">
         <v>24900</v>
       </c>
       <c r="H75" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 3495 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3749 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I75" s="22" t="inlineStr"/>
@@ -7398,16 +7478,16 @@
         </is>
       </c>
       <c r="C76" s="23" t="n">
-        <v>960</v>
+        <v>780</v>
       </c>
       <c r="D76" s="23" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E76" s="23" t="n">
         <v>5623.7</v>
       </c>
       <c r="F76" s="23" t="n">
-        <v>3390</v>
+        <v>3570</v>
       </c>
       <c r="G76" s="23" t="n">
         <v>0</v>
@@ -7419,7 +7499,7 @@
       </c>
       <c r="I76" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3390 ud.</t>
+          <t>COMPRA EXTERNA 3570 ud.</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7524,7 @@
         <v>4086.3</v>
       </c>
       <c r="F77" s="23" t="n">
-        <v>1740</v>
+        <v>1920</v>
       </c>
       <c r="G77" s="23" t="n">
         <v>0</v>
@@ -7456,7 +7536,7 @@
       </c>
       <c r="I77" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1740 ud.</t>
+          <t>COMPRA EXTERNA 1920 ud.</t>
         </is>
       </c>
     </row>
@@ -7481,14 +7561,14 @@
         <v>2087.1</v>
       </c>
       <c r="F78" s="23" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="G78" s="23" t="n">
         <v>15000</v>
       </c>
       <c r="H78" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 88 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 103 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I78" s="22" t="inlineStr"/>
@@ -7514,14 +7594,14 @@
         <v>8854</v>
       </c>
       <c r="F79" s="27" t="n">
-        <v>3404</v>
+        <v>3584</v>
       </c>
       <c r="G79" s="27" t="n">
         <v>14504</v>
       </c>
       <c r="H79" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 3404 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3584 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I79" s="26" t="inlineStr"/>
@@ -7538,23 +7618,23 @@
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>6270</v>
+        <v>6000</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="E80" s="6" t="n">
         <v>8994.6</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>360</v>
+        <v>630</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>5040</v>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 360 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 630 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
@@ -7637,10 +7717,10 @@
         </is>
       </c>
       <c r="C83" s="29" t="n">
-        <v>19200</v>
+        <v>10800</v>
       </c>
       <c r="D83" s="29" t="n">
-        <v>15.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E83" s="29" t="n">
         <v>11009.4</v>
@@ -7666,10 +7746,10 @@
         </is>
       </c>
       <c r="C84" s="29" t="n">
-        <v>23000</v>
+        <v>22750</v>
       </c>
       <c r="D84" s="29" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="E84" s="29" t="n">
         <v>9880.299999999999</v>
@@ -7753,10 +7833,10 @@
         </is>
       </c>
       <c r="C87" s="29" t="n">
-        <v>21500</v>
+        <v>14750</v>
       </c>
       <c r="D87" s="29" t="n">
-        <v>25.6</v>
+        <v>17.6</v>
       </c>
       <c r="E87" s="29" t="n">
         <v>7954.2</v>
@@ -7811,10 +7891,10 @@
         </is>
       </c>
       <c r="C89" s="29" t="n">
-        <v>5100</v>
+        <v>4500</v>
       </c>
       <c r="D89" s="29" t="n">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="E89" s="29" t="n">
         <v>5807</v>
@@ -7898,10 +7978,10 @@
         </is>
       </c>
       <c r="C92" s="29" t="n">
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="D92" s="29" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="E92" s="29" t="n">
         <v>4915.2</v>
@@ -7985,10 +8065,10 @@
         </is>
       </c>
       <c r="C95" s="29" t="n">
-        <v>5280</v>
+        <v>5160</v>
       </c>
       <c r="D95" s="29" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="E95" s="29" t="n">
         <v>4512.9</v>
@@ -8188,10 +8268,10 @@
         </is>
       </c>
       <c r="C102" s="29" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="D102" s="29" t="n">
-        <v>10.2</v>
+        <v>6.8</v>
       </c>
       <c r="E102" s="29" t="n">
         <v>2916.4</v>
@@ -8536,10 +8616,10 @@
         </is>
       </c>
       <c r="C114" s="29" t="n">
-        <v>2800</v>
+        <v>2737</v>
       </c>
       <c r="D114" s="29" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="E114" s="29" t="n">
         <v>1916.4</v>
@@ -8826,10 +8906,10 @@
         </is>
       </c>
       <c r="C124" s="29" t="n">
-        <v>3000</v>
+        <v>1560</v>
       </c>
       <c r="D124" s="29" t="n">
-        <v>16.4</v>
+        <v>8.5</v>
       </c>
       <c r="E124" s="29" t="n">
         <v>1570.2</v>
@@ -8971,10 +9051,10 @@
         </is>
       </c>
       <c r="C129" s="29" t="n">
-        <v>1222</v>
+        <v>1192</v>
       </c>
       <c r="D129" s="29" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="E129" s="29" t="n">
         <v>1604.2</v>
@@ -9899,10 +9979,10 @@
         </is>
       </c>
       <c r="C161" s="29" t="n">
-        <v>1488</v>
+        <v>1458</v>
       </c>
       <c r="D161" s="29" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="E161" s="29" t="n">
         <v>817.3</v>
@@ -12202,7 +12282,7 @@
         <v>0</v>
       </c>
       <c r="G240" s="29" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H240" s="28" t="inlineStr"/>
       <c r="I240" s="28" t="inlineStr"/>
@@ -12712,10 +12792,10 @@
         </is>
       </c>
       <c r="C258" s="29" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D258" s="29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="E258" s="29" t="n">
         <v>96.90000000000001</v>
@@ -13292,10 +13372,10 @@
         </is>
       </c>
       <c r="C278" s="29" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D278" s="29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="E278" s="29" t="n">
         <v>54.8</v>
@@ -13582,10 +13662,10 @@
         </is>
       </c>
       <c r="C288" s="29" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D288" s="29" t="n">
-        <v>33.3</v>
+        <v>33.1</v>
       </c>
       <c r="E288" s="29" t="n">
         <v>50.4</v>
@@ -13756,10 +13836,10 @@
         </is>
       </c>
       <c r="C294" s="29" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D294" s="29" t="n">
-        <v>63.6</v>
+        <v>63.1</v>
       </c>
       <c r="E294" s="29" t="n">
         <v>34.9</v>
@@ -14452,10 +14532,10 @@
         </is>
       </c>
       <c r="C318" s="29" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D318" s="29" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="E318" s="29" t="n">
         <v>18.6</v>
@@ -15798,7 +15878,7 @@
         <v>0</v>
       </c>
       <c r="G364" s="29" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H364" s="28" t="inlineStr"/>
       <c r="I364" s="28" t="inlineStr"/>
@@ -18400,7 +18480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -18912,10 +18992,10 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>644</v>
+        <v>459</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>4912.3</v>
@@ -18927,17 +19007,17 @@
         <v>5147.5</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="J12" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1500 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1750 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr"/>
@@ -18954,10 +19034,10 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>1140</v>
+        <v>870</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>4927.5</v>
@@ -18969,17 +19049,17 @@
         <v>5240</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>1230</v>
+        <v>1500</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>1230</v>
+        <v>1500</v>
       </c>
       <c r="J13" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1230 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1500 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L13" s="22" t="inlineStr"/>
@@ -18987,7 +19067,7 @@
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 40 MG COMPRIMIDO</t>
+          <t>MELATONINA 3 MG COMPRIMIDOS</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
@@ -18996,32 +19076,32 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>209</v>
+        <v>560</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>3329</v>
+        <v>2888.9</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>32.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>3573.3</v>
+        <v>3142</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="J14" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1500 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 750 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr"/>
@@ -19029,7 +19109,7 @@
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>MELATONINA 3 MG COMPRIMIDOS</t>
+          <t>CINTA PARA DETERMINACION GLUCOSA USO PACIENTE UD.</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
@@ -19038,40 +19118,44 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>750</v>
+        <v>1170</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="E15" s="23" t="n">
-        <v>2888.9</v>
+        <v>3093.6</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>67.90000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>3142</v>
+        <v>3134.4</v>
       </c>
       <c r="H15" s="23" t="n">
-        <v>570</v>
+        <v>191</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="J15" s="23" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="K15" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 570 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L15" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 191 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
+          <t>VILDAGLIPTINA 50 MG CM</t>
         </is>
       </c>
       <c r="B16" s="22" t="inlineStr">
@@ -19080,32 +19164,32 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>892</v>
+        <v>930</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E16" s="23" t="n">
-        <v>2532</v>
+        <v>2810.6</v>
       </c>
       <c r="F16" s="23" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>2362.9</v>
+        <v>2759.8</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="J16" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 320 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 420 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr"/>
@@ -19113,7 +19197,7 @@
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
+          <t>ESPIRONOLACTONA 25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
@@ -19122,32 +19206,32 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>292</v>
+        <v>757</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>2040</v>
+        <v>2532</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>76.09999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>2047.2</v>
+        <v>2362.9</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>660</v>
+        <v>440</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>660</v>
+        <v>440</v>
       </c>
       <c r="J17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 660 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 440 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr"/>
@@ -19155,7 +19239,7 @@
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>HIDROXICLOROQUINA CM 200 MG</t>
+          <t>CARVEDILOL 6,25 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
@@ -19164,32 +19248,32 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>729</v>
+        <v>292</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>1817.9</v>
+        <v>2040</v>
       </c>
       <c r="F18" s="23" t="n">
-        <v>2.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>2086.4</v>
+        <v>2047.2</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>180</v>
+        <v>660</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>180</v>
+        <v>660</v>
       </c>
       <c r="J18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 660 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr"/>
@@ -19197,7 +19281,7 @@
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>CINACALCET 30 MG COMPRIMIDO</t>
+          <t>HIDROXICLOROQUINA CM 200 MG</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
@@ -19206,44 +19290,40 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>7</v>
+        <v>699</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>85.3</v>
+        <v>1817.9</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>43.5</v>
+        <v>2.2</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>92.5</v>
+        <v>2086.4</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K19" s="22" t="inlineStr">
         <is>
-          <t>SIN STOCK EN BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L19" s="22" t="inlineStr">
-        <is>
-          <t>GESTIONAR EXTERNO 90 ud.</t>
-        </is>
-      </c>
+          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
+          <t>CINACALCET 30 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
@@ -19252,40 +19332,44 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>48.3</v>
+        <v>85.3</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>0.5</v>
+        <v>43.5</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>56.2</v>
+        <v>92.5</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J20" s="23" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 45 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L20" s="22" t="inlineStr"/>
+          <t>SIN STOCK EN BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>GESTIONAR EXTERNO 90 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>AEROCAMARA ADULTO BIVAL 451/ 800 ML</t>
+          <t>BROMURO DE IPRATROPIO 20 MCG/DO AEROSOL PARA INHALACION</t>
         </is>
       </c>
       <c r="B21" s="22" t="inlineStr">
@@ -19294,32 +19378,32 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="23" t="n">
         <v>0.2</v>
       </c>
       <c r="E21" s="23" t="n">
-        <v>28.9</v>
+        <v>48.3</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>31.7</v>
+        <v>56.2</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="J21" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 28 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 47 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr"/>
@@ -19327,91 +19411,91 @@
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
+          <t>AEROCAMARA ADULTO BIVAL 451/ 800 ML</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>2-URGENTE</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="23" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G22" s="23" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="H22" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="I22" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 29 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
           <t>LACTULOSA FC 65% X 200 ML</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>2-URGENTE</t>
         </is>
       </c>
-      <c r="C22" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" s="23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E22" s="23" t="n">
+      <c r="C23" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E23" s="23" t="n">
         <v>14.5</v>
       </c>
-      <c r="F22" s="23" t="n">
+      <c r="F23" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="G22" s="23" t="n">
+      <c r="G23" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H22" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="I22" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="22" t="inlineStr">
-        <is>
-          <t>TRASPASAR 10 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L22" s="22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>VILDAGLIPTINA 50 MG CM</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>3-MODERADO</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>1260</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>2810.6</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>2759.8</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>TRASPASAR 120 ud. DESDE BODEGA AA</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr"/>
+      <c r="H23" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="J23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>TRASPASAR 12 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>SALMETEROL /FLUTICASONA 250 MG/25 MG INH UD</t>
+          <t>LOSARTAN 50 MG COMPRIMIDO</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -19420,32 +19504,32 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>16</v>
+        <v>2754</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>17</v>
+        <v>5878.9</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.1</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>21</v>
+        <v>6080.7</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1200 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
@@ -19453,149 +19537,233 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>EZETIMIBE 10 MG CM UNIDAD</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>496</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>1070.7</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1115.9</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 68 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>SALMETEROL /FLUTICASONA 250 MG/25 MG INH UD</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>3-MODERADO</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>TRASPASAR 1 ud. DESDE BODEGA AA</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>RISPERIDONA 1 MG/ ML FC X 30 ML.</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>3-MODERADO</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C27" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D27" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E27" s="6" t="n">
         <v>21.9</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F27" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G27" s="6" t="n">
         <v>19.9</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H27" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I27" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J27" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>TRASPASAR 20 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>GESTIONAR EXTERNO 80 ud.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="32" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>HEPARINA SODICA 25.000 U.I./5 ML FA/JRP</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>4-BAJO</t>
         </is>
       </c>
-      <c r="C26" s="33" t="n">
+      <c r="C28" s="33" t="n">
         <v>149</v>
       </c>
-      <c r="D26" s="33" t="n">
+      <c r="D28" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="E26" s="33" t="n">
+      <c r="E28" s="33" t="n">
         <v>151.1</v>
       </c>
-      <c r="F26" s="33" t="n">
+      <c r="F28" s="33" t="n">
         <v>119.6</v>
       </c>
-      <c r="G26" s="33" t="n">
+      <c r="G28" s="33" t="n">
         <v>29.3</v>
       </c>
-      <c r="H26" s="33" t="n">
+      <c r="H28" s="33" t="n">
         <v>50</v>
       </c>
-      <c r="I26" s="33" t="n">
+      <c r="I28" s="33" t="n">
         <v>50</v>
       </c>
-      <c r="J26" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="32" t="inlineStr">
+      <c r="J28" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="32" t="inlineStr">
         <is>
           <t>TRASPASAR 50 ud. DESDE BODEGA AA</t>
         </is>
       </c>
-      <c r="L26" s="32" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="L28" s="32" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>CRITICO  —  sin stock ni respaldo</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>URGENTE  —  cobertura critica</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>ALTO  —  cobertura &lt; 1 semana (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  reponer pronto (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>MODERADO  —  cobertura &lt; 2 sem. (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  vigilar (Farmacia)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>BAJO  —  stock suficiente (Bodega)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>SUFICIENTE  —  sin necesidad</t>
         </is>
@@ -19719,7 +19887,7 @@
         <v>3134.4</v>
       </c>
       <c r="H3" s="21" t="n">
-        <v>4263</v>
+        <v>4593</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>0</v>
@@ -19731,7 +19899,7 @@
       </c>
       <c r="K3" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 4263 ud.</t>
+          <t>COMPRA EXTERNA 4593 ud.</t>
         </is>
       </c>
     </row>
@@ -19762,17 +19930,21 @@
         <v>1981.8</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>2963</v>
+        <v>3043</v>
       </c>
       <c r="I4" s="21" t="n">
-        <v>8100</v>
+        <v>2100</v>
       </c>
       <c r="J4" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 2963 ud. DESDE BODEGA FARMACOS</t>
-        </is>
-      </c>
-      <c r="K4" s="20" t="inlineStr"/>
+          <t>TRASPASAR 2100 ud. DESDE BODEGA FARMACOS</t>
+        </is>
+      </c>
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>COMPRA EXTERNA 943 ud.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -19801,7 +19973,7 @@
         <v>1830.1</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>259</v>
+        <v>319</v>
       </c>
       <c r="I5" s="21" t="n">
         <v>0</v>
@@ -19813,7 +19985,7 @@
       </c>
       <c r="K5" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 259 ud.</t>
+          <t>COMPRA EXTERNA 319 ud.</t>
         </is>
       </c>
     </row>
@@ -19844,7 +20016,7 @@
         <v>644.4</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I6" s="21" t="n">
         <v>0</v>
@@ -19856,7 +20028,7 @@
       </c>
       <c r="K6" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 400 ud.</t>
+          <t>COMPRA EXTERNA 500 ud.</t>
         </is>
       </c>
     </row>
@@ -20012,14 +20184,14 @@
         <v>86.5</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I10" s="21" t="n">
         <v>300</v>
       </c>
       <c r="J10" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 42 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 46 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr"/>
@@ -20621,14 +20793,14 @@
         <v>3697</v>
       </c>
       <c r="H25" s="23" t="n">
-        <v>3495</v>
+        <v>3749</v>
       </c>
       <c r="I25" s="23" t="n">
         <v>24900</v>
       </c>
       <c r="J25" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 3495 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3749 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr"/>
@@ -20645,10 +20817,10 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>930</v>
+        <v>750</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E26" s="23" t="n">
         <v>5623.7</v>
@@ -20660,7 +20832,7 @@
         <v>3142</v>
       </c>
       <c r="H26" s="23" t="n">
-        <v>3390</v>
+        <v>3570</v>
       </c>
       <c r="I26" s="23" t="n">
         <v>0</v>
@@ -20672,7 +20844,7 @@
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3390 ud.</t>
+          <t>COMPRA EXTERNA 3570 ud.</t>
         </is>
       </c>
     </row>
@@ -20703,14 +20875,14 @@
         <v>1162.7</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>15000</v>
       </c>
       <c r="J27" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 88 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 103 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr"/>
@@ -20742,14 +20914,14 @@
         <v>4799.7</v>
       </c>
       <c r="H28" s="27" t="n">
-        <v>3404</v>
+        <v>3584</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>14504</v>
       </c>
       <c r="J28" s="26" t="inlineStr">
         <is>
-          <t>TRASPASAR 3404 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3584 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K28" s="26" t="inlineStr"/>
@@ -20766,10 +20938,10 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>6270</v>
+        <v>6000</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>8994.6</v>
@@ -20781,14 +20953,14 @@
         <v>5240</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>360</v>
+        <v>630</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>5040</v>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 360 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 630 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr"/>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="C46" s="23" t="n">
-        <v>2304</v>
+        <v>2274</v>
       </c>
       <c r="D46" s="23" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="E46" s="23" t="n">
         <v>5475.2</v>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="C47" s="23" t="n">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E47" s="23" t="n">
         <v>4805</v>
@@ -3622,26 +3622,26 @@
         </is>
       </c>
       <c r="C48" s="23" t="n">
-        <v>390</v>
+        <v>270</v>
       </c>
       <c r="D48" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E48" s="23" t="n">
         <v>4604.3</v>
       </c>
       <c r="F48" s="23" t="n">
-        <v>1650</v>
+        <v>1770</v>
       </c>
       <c r="G48" s="23" t="n">
-        <v>1650</v>
+        <v>1770</v>
       </c>
       <c r="H48" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1650 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1770 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J48" s="22" t="inlineStr"/>
@@ -3658,26 +3658,26 @@
         </is>
       </c>
       <c r="C49" s="23" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E49" s="23" t="n">
         <v>2773.3</v>
       </c>
       <c r="F49" s="23" t="n">
-        <v>660</v>
+        <v>720</v>
       </c>
       <c r="G49" s="23" t="n">
-        <v>660</v>
+        <v>720</v>
       </c>
       <c r="H49" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 660 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 720 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J49" s="22" t="inlineStr"/>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="C50" s="23" t="n">
-        <v>880</v>
+        <v>850</v>
       </c>
       <c r="D50" s="23" t="n">
         <v>1.4</v>
@@ -3703,13 +3703,13 @@
         <v>2990.6</v>
       </c>
       <c r="F50" s="23" t="n">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="G50" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="23" t="n">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="I50" s="22" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="J50" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 377 ud.</t>
+          <t>GESTIONAR EXTERNO 407 ud.</t>
         </is>
       </c>
     </row>
@@ -3734,26 +3734,26 @@
         </is>
       </c>
       <c r="C51" s="23" t="n">
-        <v>720</v>
+        <v>630</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="E51" s="23" t="n">
         <v>2633.5</v>
       </c>
       <c r="F51" s="23" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="G51" s="23" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="H51" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 480 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 540 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J51" s="22" t="inlineStr"/>
@@ -3806,26 +3806,26 @@
         </is>
       </c>
       <c r="C53" s="23" t="n">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E53" s="23" t="n">
         <v>1933</v>
       </c>
       <c r="F53" s="23" t="n">
-        <v>660</v>
+        <v>720</v>
       </c>
       <c r="G53" s="23" t="n">
-        <v>660</v>
+        <v>720</v>
       </c>
       <c r="H53" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 660 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 720 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J53" s="22" t="inlineStr"/>
@@ -3954,26 +3954,26 @@
         </is>
       </c>
       <c r="C57" s="23" t="n">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="E57" s="23" t="n">
         <v>958.2</v>
       </c>
       <c r="F57" s="23" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="G57" s="23" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="H57" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 130 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 160 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J57" s="22" t="inlineStr"/>
@@ -5145,7 +5145,7 @@
         <v>5587</v>
       </c>
       <c r="F3" s="21" t="n">
-        <v>4707</v>
+        <v>4737</v>
       </c>
       <c r="G3" s="21" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="I3" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 4707 ud.</t>
+          <t>COMPRA EXTERNA 4737 ud.</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
         <v>368.6</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G14" s="21" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 176 ud.</t>
+          <t>COMPRA EXTERNA 184 ud.</t>
         </is>
       </c>
     </row>
@@ -5659,14 +5659,14 @@
         <v>149.6</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G17" s="21" t="n">
         <v>300</v>
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 39 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 42 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr"/>
@@ -7706,14 +7706,14 @@
         <v>6380.1</v>
       </c>
       <c r="F76" s="23" t="n">
-        <v>3690</v>
+        <v>3750</v>
       </c>
       <c r="G76" s="23" t="n">
         <v>24900</v>
       </c>
       <c r="H76" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 3690 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3750 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I76" s="22" t="inlineStr"/>
@@ -7730,16 +7730,16 @@
         </is>
       </c>
       <c r="C77" s="23" t="n">
-        <v>840</v>
+        <v>780</v>
       </c>
       <c r="D77" s="23" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E77" s="23" t="n">
         <v>5533.8</v>
       </c>
       <c r="F77" s="23" t="n">
-        <v>3540</v>
+        <v>3600</v>
       </c>
       <c r="G77" s="23" t="n">
         <v>0</v>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="I77" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3540 ud.</t>
+          <t>COMPRA EXTERNA 3600 ud.</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7776,7 @@
         <v>3816.5</v>
       </c>
       <c r="F78" s="23" t="n">
-        <v>1770</v>
+        <v>1830</v>
       </c>
       <c r="G78" s="23" t="n">
         <v>0</v>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="I78" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1770 ud.</t>
+          <t>COMPRA EXTERNA 1830 ud.</t>
         </is>
       </c>
     </row>
@@ -7813,14 +7813,14 @@
         <v>2084.2</v>
       </c>
       <c r="F79" s="23" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="G79" s="23" t="n">
         <v>15000</v>
       </c>
       <c r="H79" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 280 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 295 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I79" s="22" t="inlineStr"/>
@@ -7907,23 +7907,23 @@
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>5850</v>
+        <v>5730</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="E82" s="6" t="n">
         <v>8600.1</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>720</v>
+        <v>840</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>5040</v>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 720 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 840 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
         <v>5507.7</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>0</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 500 ud.</t>
+          <t>COMPRA EXTERNA 1000 ud.</t>
         </is>
       </c>
     </row>
@@ -8267,10 +8267,10 @@
         </is>
       </c>
       <c r="C94" s="29" t="n">
-        <v>4140</v>
+        <v>4080</v>
       </c>
       <c r="D94" s="29" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="E94" s="29" t="n">
         <v>4620.8</v>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="C98" s="29" t="n">
-        <v>5340</v>
+        <v>5280</v>
       </c>
       <c r="D98" s="29" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="E98" s="29" t="n">
         <v>3908.5</v>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="C116" s="29" t="n">
-        <v>2670</v>
+        <v>2640</v>
       </c>
       <c r="D116" s="29" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="E116" s="29" t="n">
         <v>1803.9</v>
@@ -19269,10 +19269,10 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>2304</v>
+        <v>2274</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>5475.2</v>
@@ -19311,10 +19311,10 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>4805</v>
@@ -19353,10 +19353,10 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>390</v>
+        <v>270</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E15" s="23" t="n">
         <v>4604.3</v>
@@ -19368,17 +19368,17 @@
         <v>5240</v>
       </c>
       <c r="H15" s="23" t="n">
-        <v>1650</v>
+        <v>1770</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>1650</v>
+        <v>1770</v>
       </c>
       <c r="J15" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 1650 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 1770 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr"/>
@@ -19395,10 +19395,10 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E16" s="23" t="n">
         <v>2773.3</v>
@@ -19410,17 +19410,17 @@
         <v>3142</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>690</v>
+        <v>750</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>690</v>
+        <v>750</v>
       </c>
       <c r="J16" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 690 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 750 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr"/>
@@ -19437,7 +19437,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>880</v>
+        <v>850</v>
       </c>
       <c r="D17" s="23" t="n">
         <v>1.4</v>
@@ -19452,13 +19452,13 @@
         <v>3134.4</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="I17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="23" t="n">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="L17" s="22" t="inlineStr">
         <is>
-          <t>GESTIONAR EXTERNO 378 ud.</t>
+          <t>GESTIONAR EXTERNO 408 ud.</t>
         </is>
       </c>
     </row>
@@ -19483,10 +19483,10 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>720</v>
+        <v>630</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="E18" s="23" t="n">
         <v>2633.5</v>
@@ -19498,17 +19498,17 @@
         <v>2759.8</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="J18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 480 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 540 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr"/>
@@ -19525,7 +19525,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>1015</v>
+        <v>1000</v>
       </c>
       <c r="D19" s="23" t="n">
         <v>1.8</v>
@@ -19609,10 +19609,10 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E21" s="23" t="n">
         <v>1933</v>
@@ -19624,17 +19624,17 @@
         <v>2047.2</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>690</v>
+        <v>750</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>690</v>
+        <v>750</v>
       </c>
       <c r="J21" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 690 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 750 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr"/>
@@ -19739,10 +19739,10 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="E24" s="23" t="n">
         <v>958.2</v>
@@ -19754,17 +19754,17 @@
         <v>1115.9</v>
       </c>
       <c r="H24" s="23" t="n">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="I24" s="23" t="n">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="J24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 133 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 163 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr"/>
@@ -20210,7 +20210,7 @@
         <v>3134.4</v>
       </c>
       <c r="H3" s="21" t="n">
-        <v>4707</v>
+        <v>4737</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>0</v>
@@ -20222,7 +20222,7 @@
       </c>
       <c r="K3" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 4707 ud.</t>
+          <t>COMPRA EXTERNA 4737 ud.</t>
         </is>
       </c>
     </row>
@@ -20511,14 +20511,14 @@
         <v>86.5</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I10" s="21" t="n">
         <v>300</v>
       </c>
       <c r="J10" s="20" t="inlineStr">
         <is>
-          <t>TRASPASAR 39 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 42 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr"/>
@@ -21202,14 +21202,14 @@
         <v>3697</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>3690</v>
+        <v>3750</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>24900</v>
       </c>
       <c r="J27" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 3690 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 3750 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr"/>
@@ -21226,10 +21226,10 @@
         </is>
       </c>
       <c r="C28" s="23" t="n">
-        <v>810</v>
+        <v>750</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E28" s="23" t="n">
         <v>5533.8</v>
@@ -21241,7 +21241,7 @@
         <v>3142</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>3540</v>
+        <v>3600</v>
       </c>
       <c r="I28" s="23" t="n">
         <v>0</v>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="K28" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3540 ud.</t>
+          <t>COMPRA EXTERNA 3600 ud.</t>
         </is>
       </c>
     </row>
@@ -21284,14 +21284,14 @@
         <v>1162.7</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="I29" s="23" t="n">
         <v>15000</v>
       </c>
       <c r="J29" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 280 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 295 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr"/>
@@ -21347,10 +21347,10 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>5850</v>
+        <v>5730</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>8600.1</v>
@@ -21362,14 +21362,14 @@
         <v>5240</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>720</v>
+        <v>840</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>5040</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>TRASPASAR 720 ud. DESDE BODEGA FARMACOS</t>
+          <t>TRASPASAR 840 ud. DESDE BODEGA FARMACOS</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr"/>

--- a/Resumen_Pedidos_AA.xlsx
+++ b/Resumen_Pedidos_AA.xlsx
@@ -3734,26 +3734,26 @@
         </is>
       </c>
       <c r="C51" s="23" t="n">
-        <v>630</v>
+        <v>570</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E51" s="23" t="n">
         <v>2633.5</v>
       </c>
       <c r="F51" s="23" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="G51" s="23" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="H51" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 540 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 600 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J51" s="22" t="inlineStr"/>
@@ -3990,26 +3990,26 @@
         </is>
       </c>
       <c r="C58" s="23" t="n">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="E58" s="23" t="n">
         <v>848</v>
       </c>
       <c r="F58" s="23" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G58" s="23" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="H58" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 150 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 180 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="J58" s="22" t="inlineStr"/>
@@ -5182,7 +5182,7 @@
         <v>5386.7</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>3629</v>
+        <v>3689</v>
       </c>
       <c r="G4" s="21" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="I4" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 3629 ud.</t>
+          <t>COMPRA EXTERNA 3689 ud.</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
         <v>1259.3</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="G9" s="21" t="n">
         <v>0</v>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 210 ud.</t>
+          <t>COMPRA EXTERNA 240 ud.</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
         <v>368.6</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G14" s="21" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 184 ud.</t>
+          <t>COMPRA EXTERNA 190 ud.</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7776,7 @@
         <v>3816.5</v>
       </c>
       <c r="F78" s="23" t="n">
-        <v>1830</v>
+        <v>1860</v>
       </c>
       <c r="G78" s="23" t="n">
         <v>0</v>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="I78" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 1830 ud.</t>
+          <t>COMPRA EXTERNA 1860 ud.</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
         <v>201.9</v>
       </c>
       <c r="F81" s="23" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="G81" s="23" t="n">
         <v>0</v>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="I81" s="22" t="inlineStr">
         <is>
-          <t>COMPRA EXTERNA 16 ud.</t>
+          <t>COMPRA EXTERNA 46 ud.</t>
         </is>
       </c>
     </row>
@@ -8267,10 +8267,10 @@
         </is>
       </c>
       <c r="C94" s="29" t="n">
-        <v>4080</v>
+        <v>4020</v>
       </c>
       <c r="D94" s="29" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="E94" s="29" t="n">
         <v>4620.8</v>
@@ -9340,10 +9340,10 @@
         </is>
       </c>
       <c r="C131" s="29" t="n">
-        <v>1222</v>
+        <v>1192</v>
       </c>
       <c r="D131" s="29" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="E131" s="29" t="n">
         <v>1529</v>
@@ -19483,10 +19483,10 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>630</v>
+        <v>570</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E18" s="23" t="n">
         <v>2633.5</v>
@@ -19498,17 +19498,17 @@
         <v>2759.8</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="J18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>TRASPASAR 540 ud. DESDE BODEGA AA</t>
+          <t>TRASPASAR 600 ud. DESDE BODEGA AA</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr"/>
